--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="345">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1047,6 +1047,9 @@
   <si>
     <t>['11', '17']</t>
   </si>
+  <si>
+    <t>['36', '63', '90+3']</t>
+  </si>
 </sst>
 </file>
 
@@ -1407,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP219"/>
+  <dimension ref="A1:BP220"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1947,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ3">
         <v>1.64</v>
@@ -4007,7 +4010,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ13">
         <v>1.4</v>
@@ -4216,7 +4219,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ14">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -8748,7 +8751,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ36">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR36">
         <v>1.46</v>
@@ -9569,7 +9572,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ40">
         <v>1.09</v>
@@ -12044,7 +12047,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ52">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR52">
         <v>1.92</v>
@@ -13895,7 +13898,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ61">
         <v>0.82</v>
@@ -14516,7 +14519,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ64">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR64">
         <v>1.02</v>
@@ -18636,7 +18639,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ84">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR84">
         <v>1.49</v>
@@ -19045,7 +19048,7 @@
         <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ86">
         <v>1.18</v>
@@ -22138,7 +22141,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ101">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR101">
         <v>1.42</v>
@@ -23577,7 +23580,7 @@
         <v>0.75</v>
       </c>
       <c r="AP108">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ108">
         <v>1.4</v>
@@ -26667,7 +26670,7 @@
         <v>1.67</v>
       </c>
       <c r="AP123">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ123">
         <v>2</v>
@@ -28112,7 +28115,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ130">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR130">
         <v>1.48</v>
@@ -29345,7 +29348,7 @@
         <v>1.5</v>
       </c>
       <c r="AP136">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ136">
         <v>1.64</v>
@@ -30996,7 +30999,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ144">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR144">
         <v>1.48</v>
@@ -33465,7 +33468,7 @@
         <v>0.43</v>
       </c>
       <c r="AP156">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ156">
         <v>0.91</v>
@@ -36349,7 +36352,7 @@
         <v>0.88</v>
       </c>
       <c r="AP170">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ170">
         <v>0.64</v>
@@ -38000,7 +38003,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ178">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR178">
         <v>1.5</v>
@@ -39937,7 +39940,7 @@
         <v>187</v>
       </c>
       <c r="B188">
-        <v>7492339</v>
+        <v>7492346</v>
       </c>
       <c r="C188" t="s">
         <v>68</v>
@@ -39952,190 +39955,190 @@
         <v>20</v>
       </c>
       <c r="G188" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H188" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I188">
         <v>0</v>
       </c>
       <c r="J188">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K188">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M188">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N188">
+        <v>0</v>
+      </c>
+      <c r="O188" t="s">
+        <v>92</v>
+      </c>
+      <c r="P188" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q188">
+        <v>5</v>
+      </c>
+      <c r="R188">
+        <v>2.3</v>
+      </c>
+      <c r="S188">
+        <v>2.25</v>
+      </c>
+      <c r="T188">
+        <v>1.36</v>
+      </c>
+      <c r="U188">
+        <v>3</v>
+      </c>
+      <c r="V188">
+        <v>2.63</v>
+      </c>
+      <c r="W188">
+        <v>1.44</v>
+      </c>
+      <c r="X188">
+        <v>7</v>
+      </c>
+      <c r="Y188">
+        <v>1.1</v>
+      </c>
+      <c r="Z188">
+        <v>4.2</v>
+      </c>
+      <c r="AA188">
         <v>4</v>
       </c>
-      <c r="O188" t="s">
-        <v>163</v>
-      </c>
-      <c r="P188" t="s">
-        <v>331</v>
-      </c>
-      <c r="Q188">
-        <v>2.75</v>
-      </c>
-      <c r="R188">
-        <v>2</v>
-      </c>
-      <c r="S188">
-        <v>4.75</v>
-      </c>
-      <c r="T188">
-        <v>1.53</v>
-      </c>
-      <c r="U188">
-        <v>2.38</v>
-      </c>
-      <c r="V188">
-        <v>3.5</v>
-      </c>
-      <c r="W188">
-        <v>1.29</v>
-      </c>
-      <c r="X188">
-        <v>11</v>
-      </c>
-      <c r="Y188">
-        <v>1.05</v>
-      </c>
-      <c r="Z188">
-        <v>2.25</v>
-      </c>
-      <c r="AA188">
+      <c r="AB188">
+        <v>1.75</v>
+      </c>
+      <c r="AC188">
+        <v>1.04</v>
+      </c>
+      <c r="AD188">
+        <v>13</v>
+      </c>
+      <c r="AE188">
+        <v>1.26</v>
+      </c>
+      <c r="AF188">
+        <v>4</v>
+      </c>
+      <c r="AG188">
+        <v>1.62</v>
+      </c>
+      <c r="AH188">
+        <v>2.15</v>
+      </c>
+      <c r="AI188">
+        <v>1.8</v>
+      </c>
+      <c r="AJ188">
+        <v>1.95</v>
+      </c>
+      <c r="AK188">
+        <v>2.1</v>
+      </c>
+      <c r="AL188">
+        <v>1.25</v>
+      </c>
+      <c r="AM188">
+        <v>1.19</v>
+      </c>
+      <c r="AN188">
+        <v>1.44</v>
+      </c>
+      <c r="AO188">
+        <v>2</v>
+      </c>
+      <c r="AP188">
+        <v>1.27</v>
+      </c>
+      <c r="AQ188">
+        <v>2</v>
+      </c>
+      <c r="AR188">
+        <v>1.04</v>
+      </c>
+      <c r="AS188">
+        <v>1.7</v>
+      </c>
+      <c r="AT188">
+        <v>2.74</v>
+      </c>
+      <c r="AU188">
+        <v>4</v>
+      </c>
+      <c r="AV188">
+        <v>3</v>
+      </c>
+      <c r="AW188">
+        <v>4</v>
+      </c>
+      <c r="AX188">
+        <v>1</v>
+      </c>
+      <c r="AY188">
+        <v>13</v>
+      </c>
+      <c r="AZ188">
+        <v>5</v>
+      </c>
+      <c r="BA188">
+        <v>5</v>
+      </c>
+      <c r="BB188">
+        <v>3</v>
+      </c>
+      <c r="BC188">
+        <v>8</v>
+      </c>
+      <c r="BD188">
+        <v>3.15</v>
+      </c>
+      <c r="BE188">
+        <v>6.75</v>
+      </c>
+      <c r="BF188">
+        <v>1.44</v>
+      </c>
+      <c r="BG188">
+        <v>1.28</v>
+      </c>
+      <c r="BH188">
         <v>3.2</v>
       </c>
-      <c r="AB188">
-        <v>3.4</v>
-      </c>
-      <c r="AC188">
-        <v>1.1</v>
-      </c>
-      <c r="AD188">
-        <v>7.5</v>
-      </c>
-      <c r="AE188">
-        <v>1.47</v>
-      </c>
-      <c r="AF188">
-        <v>2.75</v>
-      </c>
-      <c r="AG188">
-        <v>2.3</v>
-      </c>
-      <c r="AH188">
-        <v>1.55</v>
-      </c>
-      <c r="AI188">
-        <v>2.05</v>
-      </c>
-      <c r="AJ188">
-        <v>1.7</v>
-      </c>
-      <c r="AK188">
-        <v>1.25</v>
-      </c>
-      <c r="AL188">
-        <v>1.35</v>
-      </c>
-      <c r="AM188">
-        <v>1.72</v>
-      </c>
-      <c r="AN188">
-        <v>0.78</v>
-      </c>
-      <c r="AO188">
-        <v>0.44</v>
-      </c>
-      <c r="AP188">
-        <v>0.73</v>
-      </c>
-      <c r="AQ188">
-        <v>0.64</v>
-      </c>
-      <c r="AR188">
-        <v>0.97</v>
-      </c>
-      <c r="AS188">
-        <v>1.11</v>
-      </c>
-      <c r="AT188">
-        <v>2.08</v>
-      </c>
-      <c r="AU188">
-        <v>6</v>
-      </c>
-      <c r="AV188">
-        <v>7</v>
-      </c>
-      <c r="AW188">
-        <v>6</v>
-      </c>
-      <c r="AX188">
-        <v>5</v>
-      </c>
-      <c r="AY188">
-        <v>16</v>
-      </c>
-      <c r="AZ188">
-        <v>15</v>
-      </c>
-      <c r="BA188">
-        <v>9</v>
-      </c>
-      <c r="BB188">
-        <v>2</v>
-      </c>
-      <c r="BC188">
-        <v>11</v>
-      </c>
-      <c r="BD188">
-        <v>1.65</v>
-      </c>
-      <c r="BE188">
-        <v>6.5</v>
-      </c>
-      <c r="BF188">
-        <v>2.48</v>
-      </c>
-      <c r="BG188">
-        <v>1.3</v>
-      </c>
-      <c r="BH188">
-        <v>3.15</v>
-      </c>
       <c r="BI188">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="BJ188">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BK188">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="BL188">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="BM188">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="BN188">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="BO188">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="BP188">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="189" spans="1:68">
@@ -40143,7 +40146,7 @@
         <v>188</v>
       </c>
       <c r="B189">
-        <v>7492346</v>
+        <v>7492339</v>
       </c>
       <c r="C189" t="s">
         <v>68</v>
@@ -40158,190 +40161,190 @@
         <v>20</v>
       </c>
       <c r="G189" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H189" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I189">
         <v>0</v>
       </c>
       <c r="J189">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K189">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M189">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N189">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O189" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>92</v>
+        <v>331</v>
       </c>
       <c r="Q189">
+        <v>2.75</v>
+      </c>
+      <c r="R189">
+        <v>2</v>
+      </c>
+      <c r="S189">
+        <v>4.75</v>
+      </c>
+      <c r="T189">
+        <v>1.53</v>
+      </c>
+      <c r="U189">
+        <v>2.38</v>
+      </c>
+      <c r="V189">
+        <v>3.5</v>
+      </c>
+      <c r="W189">
+        <v>1.29</v>
+      </c>
+      <c r="X189">
+        <v>11</v>
+      </c>
+      <c r="Y189">
+        <v>1.05</v>
+      </c>
+      <c r="Z189">
+        <v>2.25</v>
+      </c>
+      <c r="AA189">
+        <v>3.2</v>
+      </c>
+      <c r="AB189">
+        <v>3.4</v>
+      </c>
+      <c r="AC189">
+        <v>1.1</v>
+      </c>
+      <c r="AD189">
+        <v>7.5</v>
+      </c>
+      <c r="AE189">
+        <v>1.47</v>
+      </c>
+      <c r="AF189">
+        <v>2.75</v>
+      </c>
+      <c r="AG189">
+        <v>2.3</v>
+      </c>
+      <c r="AH189">
+        <v>1.55</v>
+      </c>
+      <c r="AI189">
+        <v>2.05</v>
+      </c>
+      <c r="AJ189">
+        <v>1.7</v>
+      </c>
+      <c r="AK189">
+        <v>1.25</v>
+      </c>
+      <c r="AL189">
+        <v>1.35</v>
+      </c>
+      <c r="AM189">
+        <v>1.72</v>
+      </c>
+      <c r="AN189">
+        <v>0.78</v>
+      </c>
+      <c r="AO189">
+        <v>0.44</v>
+      </c>
+      <c r="AP189">
+        <v>0.73</v>
+      </c>
+      <c r="AQ189">
+        <v>0.83</v>
+      </c>
+      <c r="AR189">
+        <v>0.97</v>
+      </c>
+      <c r="AS189">
+        <v>1.11</v>
+      </c>
+      <c r="AT189">
+        <v>2.08</v>
+      </c>
+      <c r="AU189">
+        <v>6</v>
+      </c>
+      <c r="AV189">
+        <v>7</v>
+      </c>
+      <c r="AW189">
+        <v>6</v>
+      </c>
+      <c r="AX189">
         <v>5</v>
       </c>
-      <c r="R189">
-        <v>2.3</v>
-      </c>
-      <c r="S189">
-        <v>2.25</v>
-      </c>
-      <c r="T189">
-        <v>1.36</v>
-      </c>
-      <c r="U189">
-        <v>3</v>
-      </c>
-      <c r="V189">
-        <v>2.63</v>
-      </c>
-      <c r="W189">
-        <v>1.44</v>
-      </c>
-      <c r="X189">
-        <v>7</v>
-      </c>
-      <c r="Y189">
-        <v>1.1</v>
-      </c>
-      <c r="Z189">
-        <v>4.2</v>
-      </c>
-      <c r="AA189">
-        <v>4</v>
-      </c>
-      <c r="AB189">
-        <v>1.75</v>
-      </c>
-      <c r="AC189">
-        <v>1.04</v>
-      </c>
-      <c r="AD189">
-        <v>13</v>
-      </c>
-      <c r="AE189">
-        <v>1.26</v>
-      </c>
-      <c r="AF189">
-        <v>4</v>
-      </c>
-      <c r="AG189">
-        <v>1.62</v>
-      </c>
-      <c r="AH189">
-        <v>2.15</v>
-      </c>
-      <c r="AI189">
-        <v>1.8</v>
-      </c>
-      <c r="AJ189">
-        <v>1.95</v>
-      </c>
-      <c r="AK189">
-        <v>2.1</v>
-      </c>
-      <c r="AL189">
-        <v>1.25</v>
-      </c>
-      <c r="AM189">
-        <v>1.19</v>
-      </c>
-      <c r="AN189">
-        <v>1.44</v>
-      </c>
-      <c r="AO189">
-        <v>2</v>
-      </c>
-      <c r="AP189">
-        <v>1.27</v>
-      </c>
-      <c r="AQ189">
-        <v>2</v>
-      </c>
-      <c r="AR189">
-        <v>1.04</v>
-      </c>
-      <c r="AS189">
-        <v>1.7</v>
-      </c>
-      <c r="AT189">
-        <v>2.74</v>
-      </c>
-      <c r="AU189">
-        <v>4</v>
-      </c>
-      <c r="AV189">
-        <v>3</v>
-      </c>
-      <c r="AW189">
-        <v>4</v>
-      </c>
-      <c r="AX189">
-        <v>1</v>
-      </c>
       <c r="AY189">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AZ189">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="BA189">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BB189">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC189">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BD189">
+        <v>1.65</v>
+      </c>
+      <c r="BE189">
+        <v>6.5</v>
+      </c>
+      <c r="BF189">
+        <v>2.48</v>
+      </c>
+      <c r="BG189">
+        <v>1.3</v>
+      </c>
+      <c r="BH189">
         <v>3.15</v>
       </c>
-      <c r="BE189">
-        <v>6.75</v>
-      </c>
-      <c r="BF189">
-        <v>1.44</v>
-      </c>
-      <c r="BG189">
-        <v>1.28</v>
-      </c>
-      <c r="BH189">
-        <v>3.2</v>
-      </c>
       <c r="BI189">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="BJ189">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="BK189">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="BL189">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="BM189">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="BN189">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="BO189">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="BP189">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="190" spans="1:68">
@@ -43562,7 +43565,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ205">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR205">
         <v>1.37</v>
@@ -43765,7 +43768,7 @@
         <v>0.3</v>
       </c>
       <c r="AP206">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ206">
         <v>0.36</v>
@@ -46522,6 +46525,212 @@
       </c>
       <c r="BP219">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="220" spans="1:68">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>7492375</v>
+      </c>
+      <c r="C220" t="s">
+        <v>68</v>
+      </c>
+      <c r="D220" t="s">
+        <v>69</v>
+      </c>
+      <c r="E220" s="2">
+        <v>45688.69791666666</v>
+      </c>
+      <c r="F220">
+        <v>23</v>
+      </c>
+      <c r="G220" t="s">
+        <v>71</v>
+      </c>
+      <c r="H220" t="s">
+        <v>78</v>
+      </c>
+      <c r="I220">
+        <v>1</v>
+      </c>
+      <c r="J220">
+        <v>1</v>
+      </c>
+      <c r="K220">
+        <v>2</v>
+      </c>
+      <c r="L220">
+        <v>1</v>
+      </c>
+      <c r="M220">
+        <v>3</v>
+      </c>
+      <c r="N220">
+        <v>4</v>
+      </c>
+      <c r="O220" t="s">
+        <v>211</v>
+      </c>
+      <c r="P220" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q220">
+        <v>2.75</v>
+      </c>
+      <c r="R220">
+        <v>2.2</v>
+      </c>
+      <c r="S220">
+        <v>3.75</v>
+      </c>
+      <c r="T220">
+        <v>1.36</v>
+      </c>
+      <c r="U220">
+        <v>3</v>
+      </c>
+      <c r="V220">
+        <v>2.75</v>
+      </c>
+      <c r="W220">
+        <v>1.4</v>
+      </c>
+      <c r="X220">
+        <v>8</v>
+      </c>
+      <c r="Y220">
+        <v>1.08</v>
+      </c>
+      <c r="Z220">
+        <v>2.08</v>
+      </c>
+      <c r="AA220">
+        <v>3.44</v>
+      </c>
+      <c r="AB220">
+        <v>3.54</v>
+      </c>
+      <c r="AC220">
+        <v>1.05</v>
+      </c>
+      <c r="AD220">
+        <v>11</v>
+      </c>
+      <c r="AE220">
+        <v>1.3</v>
+      </c>
+      <c r="AF220">
+        <v>3.6</v>
+      </c>
+      <c r="AG220">
+        <v>2</v>
+      </c>
+      <c r="AH220">
+        <v>1.81</v>
+      </c>
+      <c r="AI220">
+        <v>1.67</v>
+      </c>
+      <c r="AJ220">
+        <v>2.1</v>
+      </c>
+      <c r="AK220">
+        <v>1.33</v>
+      </c>
+      <c r="AL220">
+        <v>1.28</v>
+      </c>
+      <c r="AM220">
+        <v>1.72</v>
+      </c>
+      <c r="AN220">
+        <v>1.09</v>
+      </c>
+      <c r="AO220">
+        <v>0.64</v>
+      </c>
+      <c r="AP220">
+        <v>1</v>
+      </c>
+      <c r="AQ220">
+        <v>0.83</v>
+      </c>
+      <c r="AR220">
+        <v>1.37</v>
+      </c>
+      <c r="AS220">
+        <v>1.13</v>
+      </c>
+      <c r="AT220">
+        <v>2.5</v>
+      </c>
+      <c r="AU220">
+        <v>8</v>
+      </c>
+      <c r="AV220">
+        <v>4</v>
+      </c>
+      <c r="AW220">
+        <v>12</v>
+      </c>
+      <c r="AX220">
+        <v>4</v>
+      </c>
+      <c r="AY220">
+        <v>26</v>
+      </c>
+      <c r="AZ220">
+        <v>10</v>
+      </c>
+      <c r="BA220">
+        <v>3</v>
+      </c>
+      <c r="BB220">
+        <v>2</v>
+      </c>
+      <c r="BC220">
+        <v>5</v>
+      </c>
+      <c r="BD220">
+        <v>1.65</v>
+      </c>
+      <c r="BE220">
+        <v>6.75</v>
+      </c>
+      <c r="BF220">
+        <v>2.48</v>
+      </c>
+      <c r="BG220">
+        <v>1.25</v>
+      </c>
+      <c r="BH220">
+        <v>3.45</v>
+      </c>
+      <c r="BI220">
+        <v>1.44</v>
+      </c>
+      <c r="BJ220">
+        <v>2.55</v>
+      </c>
+      <c r="BK220">
+        <v>1.72</v>
+      </c>
+      <c r="BL220">
+        <v>1.98</v>
+      </c>
+      <c r="BM220">
+        <v>2.12</v>
+      </c>
+      <c r="BN220">
+        <v>1.62</v>
+      </c>
+      <c r="BO220">
+        <v>2.7</v>
+      </c>
+      <c r="BP220">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="350">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -718,6 +718,18 @@
     <t>['61', '84']</t>
   </si>
   <si>
+    <t>['47', '52', '84']</t>
+  </si>
+  <si>
+    <t>['25', '66']</t>
+  </si>
+  <si>
+    <t>['61', '64', '90', '90+2']</t>
+  </si>
+  <si>
+    <t>['9', '30']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1049,6 +1061,9 @@
   </si>
   <si>
     <t>['36', '63', '90+3']</t>
+  </si>
+  <si>
+    <t>['64', '78']</t>
   </si>
 </sst>
 </file>
@@ -1410,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP220"/>
+  <dimension ref="A1:BP226"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1666,7 +1681,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2284,7 +2299,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2365,7 +2380,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ5">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2490,7 +2505,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2568,7 +2583,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ6">
         <v>1.09</v>
@@ -3108,7 +3123,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3189,7 +3204,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ9">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3314,7 +3329,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3598,10 +3613,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ11">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3726,7 +3741,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q12">
         <v>3.75</v>
@@ -3804,7 +3819,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ12">
         <v>1.64</v>
@@ -3932,7 +3947,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4344,7 +4359,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q15">
         <v>3.3</v>
@@ -4422,10 +4437,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ15">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4834,10 +4849,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ17">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5168,7 +5183,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5249,7 +5264,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ19">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5455,7 +5470,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ20">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR20">
         <v>1.16</v>
@@ -5580,7 +5595,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5786,7 +5801,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5867,7 +5882,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ22">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6198,7 +6213,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6276,10 +6291,10 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ24">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR24">
         <v>2.04</v>
@@ -6610,7 +6625,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q26">
         <v>2</v>
@@ -6816,7 +6831,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7022,7 +7037,7 @@
         <v>92</v>
       </c>
       <c r="P28" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -7103,7 +7118,7 @@
         <v>1</v>
       </c>
       <c r="AQ28">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR28">
         <v>1.56</v>
@@ -7228,7 +7243,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q29">
         <v>2.25</v>
@@ -7306,7 +7321,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ29">
         <v>0.64</v>
@@ -7512,10 +7527,10 @@
         <v>0.5</v>
       </c>
       <c r="AP30">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ30">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR30">
         <v>0.95</v>
@@ -7718,7 +7733,7 @@
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ31">
         <v>0.82</v>
@@ -7846,7 +7861,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8339,7 +8354,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ34">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR34">
         <v>2.22</v>
@@ -8464,7 +8479,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q35">
         <v>4</v>
@@ -8876,7 +8891,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
@@ -8954,7 +8969,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ37">
         <v>1.64</v>
@@ -9082,7 +9097,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9288,7 +9303,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9366,7 +9381,7 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ39">
         <v>2.6</v>
@@ -9494,7 +9509,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9700,7 +9715,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9781,7 +9796,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ41">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR41">
         <v>1.35</v>
@@ -9906,7 +9921,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9987,7 +10002,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ42">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR42">
         <v>1.4</v>
@@ -10112,7 +10127,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10193,7 +10208,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ43">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR43">
         <v>0.93</v>
@@ -10399,7 +10414,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ44">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR44">
         <v>1.37</v>
@@ -10602,7 +10617,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ45">
         <v>2.36</v>
@@ -10730,7 +10745,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10936,7 +10951,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11014,7 +11029,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ47">
         <v>1.64</v>
@@ -11142,7 +11157,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11220,7 +11235,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ48">
         <v>1.55</v>
@@ -11554,7 +11569,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11760,7 +11775,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -11838,10 +11853,10 @@
         <v>0.33</v>
       </c>
       <c r="AP51">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ51">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR51">
         <v>1.68</v>
@@ -12172,7 +12187,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12250,7 +12265,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ53">
         <v>2.6</v>
@@ -12378,7 +12393,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12584,7 +12599,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12662,7 +12677,7 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ55">
         <v>2</v>
@@ -12790,7 +12805,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13077,7 +13092,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ57">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR57">
         <v>2.07</v>
@@ -13202,7 +13217,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13283,7 +13298,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ58">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR58">
         <v>1.29</v>
@@ -13820,7 +13835,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14107,7 +14122,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ62">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR62">
         <v>1.6</v>
@@ -14313,7 +14328,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ63">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR63">
         <v>0.9</v>
@@ -14516,7 +14531,7 @@
         <v>0.33</v>
       </c>
       <c r="AP64">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ64">
         <v>0.83</v>
@@ -14644,7 +14659,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14722,10 +14737,10 @@
         <v>1.5</v>
       </c>
       <c r="AP65">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ65">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR65">
         <v>1.65</v>
@@ -14850,7 +14865,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -14931,7 +14946,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ66">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR66">
         <v>1.21</v>
@@ -15056,7 +15071,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15134,7 +15149,7 @@
         <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ67">
         <v>0.82</v>
@@ -15340,7 +15355,7 @@
         <v>0.5</v>
       </c>
       <c r="AP68">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ68">
         <v>0.73</v>
@@ -15468,7 +15483,7 @@
         <v>140</v>
       </c>
       <c r="P69" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q69">
         <v>2.2</v>
@@ -15549,7 +15564,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ69">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR69">
         <v>1.44</v>
@@ -15674,7 +15689,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -15752,7 +15767,7 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ70">
         <v>0.82</v>
@@ -15958,7 +15973,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ71">
         <v>1.4</v>
@@ -16292,7 +16307,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16782,7 +16797,7 @@
         <v>1</v>
       </c>
       <c r="AP75">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ75">
         <v>1.64</v>
@@ -16910,7 +16925,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17116,7 +17131,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17322,7 +17337,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17528,7 +17543,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17609,7 +17624,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ79">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR79">
         <v>1.44</v>
@@ -17940,7 +17955,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18224,7 +18239,7 @@
         <v>1.33</v>
       </c>
       <c r="AP82">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ82">
         <v>0.82</v>
@@ -18433,7 +18448,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ83">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR83">
         <v>1.23</v>
@@ -18764,7 +18779,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -18842,10 +18857,10 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ85">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR85">
         <v>1.74</v>
@@ -19051,7 +19066,7 @@
         <v>1</v>
       </c>
       <c r="AQ86">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR86">
         <v>1.33</v>
@@ -19257,7 +19272,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ87">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR87">
         <v>1.49</v>
@@ -19382,7 +19397,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19460,10 +19475,10 @@
         <v>0.2</v>
       </c>
       <c r="AP88">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ88">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR88">
         <v>0.85</v>
@@ -19588,7 +19603,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19794,7 +19809,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -19872,7 +19887,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ90">
         <v>0.82</v>
@@ -20081,7 +20096,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ91">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR91">
         <v>1.25</v>
@@ -20206,7 +20221,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20412,7 +20427,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20618,7 +20633,7 @@
         <v>92</v>
       </c>
       <c r="P94" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q94">
         <v>6.5</v>
@@ -20824,7 +20839,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -21030,7 +21045,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -21108,7 +21123,7 @@
         <v>0.75</v>
       </c>
       <c r="AP96">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ96">
         <v>0.73</v>
@@ -21314,7 +21329,7 @@
         <v>1.25</v>
       </c>
       <c r="AP97">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ97">
         <v>0.64</v>
@@ -21442,7 +21457,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21648,7 +21663,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21935,7 +21950,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ100">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR100">
         <v>1.81</v>
@@ -22138,7 +22153,7 @@
         <v>0.2</v>
       </c>
       <c r="AP101">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ101">
         <v>0.83</v>
@@ -22266,7 +22281,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22344,7 +22359,7 @@
         <v>2</v>
       </c>
       <c r="AP102">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ102">
         <v>1.64</v>
@@ -22550,7 +22565,7 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ103">
         <v>1.4</v>
@@ -22678,7 +22693,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22884,7 +22899,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23090,7 +23105,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23377,7 +23392,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ107">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR107">
         <v>1.54</v>
@@ -23583,7 +23598,7 @@
         <v>1</v>
       </c>
       <c r="AQ108">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR108">
         <v>1.36</v>
@@ -23789,7 +23804,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ109">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR109">
         <v>0.82</v>
@@ -23914,7 +23929,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24120,7 +24135,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24201,7 +24216,7 @@
         <v>1</v>
       </c>
       <c r="AQ111">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR111">
         <v>1.25</v>
@@ -24326,7 +24341,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24407,7 +24422,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ112">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR112">
         <v>1.28</v>
@@ -24532,7 +24547,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24738,7 +24753,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25022,10 +25037,10 @@
         <v>1.17</v>
       </c>
       <c r="AP115">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ115">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR115">
         <v>1.54</v>
@@ -25150,7 +25165,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25228,7 +25243,7 @@
         <v>0.8</v>
       </c>
       <c r="AP116">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ116">
         <v>1.09</v>
@@ -25356,7 +25371,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25562,7 +25577,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25640,10 +25655,10 @@
         <v>0.6</v>
       </c>
       <c r="AP118">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ118">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR118">
         <v>1.7</v>
@@ -25846,7 +25861,7 @@
         <v>1.2</v>
       </c>
       <c r="AP119">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ119">
         <v>1.64</v>
@@ -26180,7 +26195,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26592,7 +26607,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26798,7 +26813,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27004,7 +27019,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27210,7 +27225,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27828,7 +27843,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -28321,7 +28336,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ131">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR131">
         <v>1.36</v>
@@ -28733,7 +28748,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ133">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR133">
         <v>1.55</v>
@@ -28936,10 +28951,10 @@
         <v>0.29</v>
       </c>
       <c r="AP134">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ134">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR134">
         <v>1.52</v>
@@ -29064,7 +29079,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29142,10 +29157,10 @@
         <v>1.2</v>
       </c>
       <c r="AP135">
+        <v>1.42</v>
+      </c>
+      <c r="AQ135">
         <v>1.27</v>
-      </c>
-      <c r="AQ135">
-        <v>1.4</v>
       </c>
       <c r="AR135">
         <v>1.11</v>
@@ -29476,7 +29491,7 @@
         <v>92</v>
       </c>
       <c r="P137" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q137">
         <v>5</v>
@@ -29682,7 +29697,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29888,7 +29903,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30378,7 +30393,7 @@
         <v>1.33</v>
       </c>
       <c r="AP141">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ141">
         <v>1.4</v>
@@ -30587,7 +30602,7 @@
         <v>1</v>
       </c>
       <c r="AQ142">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR142">
         <v>1.3</v>
@@ -30712,7 +30727,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30790,7 +30805,7 @@
         <v>1.57</v>
       </c>
       <c r="AP143">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ143">
         <v>1.55</v>
@@ -30918,7 +30933,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31202,7 +31217,7 @@
         <v>0.83</v>
       </c>
       <c r="AP145">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ145">
         <v>0.82</v>
@@ -31330,7 +31345,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31411,7 +31426,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ146">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR146">
         <v>1.08</v>
@@ -31536,7 +31551,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31617,7 +31632,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ147">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR147">
         <v>1.55</v>
@@ -31948,7 +31963,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32026,7 +32041,7 @@
         <v>0.71</v>
       </c>
       <c r="AP149">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ149">
         <v>1.09</v>
@@ -32235,7 +32250,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ150">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR150">
         <v>0.84</v>
@@ -32360,7 +32375,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32566,7 +32581,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32644,7 +32659,7 @@
         <v>2</v>
       </c>
       <c r="AP152">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ152">
         <v>2.36</v>
@@ -32772,7 +32787,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -32850,10 +32865,10 @@
         <v>0.25</v>
       </c>
       <c r="AP153">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ153">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR153">
         <v>1.41</v>
@@ -32978,7 +32993,7 @@
         <v>192</v>
       </c>
       <c r="P154" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33262,7 +33277,7 @@
         <v>2</v>
       </c>
       <c r="AP155">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ155">
         <v>1.64</v>
@@ -33390,7 +33405,7 @@
         <v>193</v>
       </c>
       <c r="P156" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q156">
         <v>2.4</v>
@@ -33471,7 +33486,7 @@
         <v>1</v>
       </c>
       <c r="AQ156">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR156">
         <v>1.24</v>
@@ -33883,7 +33898,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ158">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR158">
         <v>1.52</v>
@@ -34008,7 +34023,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34420,7 +34435,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34626,7 +34641,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34832,7 +34847,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35244,7 +35259,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35450,7 +35465,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35528,10 +35543,10 @@
         <v>1.5</v>
       </c>
       <c r="AP166">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ166">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR166">
         <v>1.76</v>
@@ -35656,7 +35671,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35734,7 +35749,7 @@
         <v>1.86</v>
       </c>
       <c r="AP167">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ167">
         <v>1.64</v>
@@ -35862,7 +35877,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -35940,7 +35955,7 @@
         <v>1</v>
       </c>
       <c r="AP168">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ168">
         <v>1.09</v>
@@ -36149,7 +36164,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ169">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR169">
         <v>1.57</v>
@@ -36480,7 +36495,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36561,7 +36576,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ171">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR171">
         <v>0.88</v>
@@ -36686,7 +36701,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36892,7 +36907,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37098,7 +37113,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37176,10 +37191,10 @@
         <v>1.22</v>
       </c>
       <c r="AP174">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ174">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR174">
         <v>1.03</v>
@@ -37385,7 +37400,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ175">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR175">
         <v>1.48</v>
@@ -37510,7 +37525,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -37588,7 +37603,7 @@
         <v>1.75</v>
       </c>
       <c r="AP176">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ176">
         <v>1.64</v>
@@ -38128,7 +38143,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38206,10 +38221,10 @@
         <v>0.75</v>
       </c>
       <c r="AP179">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ179">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR179">
         <v>1.61</v>
@@ -38334,7 +38349,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38415,7 +38430,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ180">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR180">
         <v>1.47</v>
@@ -38540,7 +38555,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38618,7 +38633,7 @@
         <v>2.22</v>
       </c>
       <c r="AP181">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ181">
         <v>2.36</v>
@@ -38952,7 +38967,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39030,7 +39045,7 @@
         <v>0.63</v>
       </c>
       <c r="AP183">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ183">
         <v>0.82</v>
@@ -39239,7 +39254,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ184">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR184">
         <v>1.31</v>
@@ -39776,7 +39791,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39857,7 +39872,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ187">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR187">
         <v>1.47</v>
@@ -40060,7 +40075,7 @@
         <v>2</v>
       </c>
       <c r="AP188">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ188">
         <v>2</v>
@@ -40188,7 +40203,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40600,7 +40615,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41218,7 +41233,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41296,7 +41311,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP194">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ194">
         <v>0.82</v>
@@ -41505,7 +41520,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ195">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR195">
         <v>1.59</v>
@@ -41708,7 +41723,7 @@
         <v>1.67</v>
       </c>
       <c r="AP196">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ196">
         <v>1.64</v>
@@ -41836,7 +41851,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42120,7 +42135,7 @@
         <v>1.89</v>
       </c>
       <c r="AP198">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ198">
         <v>1.64</v>
@@ -42248,7 +42263,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42454,7 +42469,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42535,7 +42550,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ200">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR200">
         <v>1.55</v>
@@ -42660,7 +42675,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -42738,7 +42753,7 @@
         <v>0.78</v>
       </c>
       <c r="AP201">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ201">
         <v>0.64</v>
@@ -42944,7 +42959,7 @@
         <v>1.56</v>
       </c>
       <c r="AP202">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ202">
         <v>1.4</v>
@@ -43072,7 +43087,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43150,7 +43165,7 @@
         <v>2.3</v>
       </c>
       <c r="AP203">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ203">
         <v>2.36</v>
@@ -43356,10 +43371,10 @@
         <v>1.2</v>
       </c>
       <c r="AP204">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ204">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR204">
         <v>1.51</v>
@@ -43484,7 +43499,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43771,7 +43786,7 @@
         <v>1</v>
       </c>
       <c r="AQ206">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR206">
         <v>1.29</v>
@@ -43896,7 +43911,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44102,7 +44117,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44183,7 +44198,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ208">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR208">
         <v>1.57</v>
@@ -44720,7 +44735,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45338,7 +45353,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45544,7 +45559,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45622,7 +45637,7 @@
         <v>0.6</v>
       </c>
       <c r="AP215">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ215">
         <v>0.82</v>
@@ -45750,7 +45765,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -45956,7 +45971,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46162,7 +46177,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46243,7 +46258,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ218">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR218">
         <v>1.35</v>
@@ -46574,7 +46589,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46731,6 +46746,1242 @@
       </c>
       <c r="BP220">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:68">
+      <c r="A221" s="1">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>7492377</v>
+      </c>
+      <c r="C221" t="s">
+        <v>68</v>
+      </c>
+      <c r="D221" t="s">
+        <v>69</v>
+      </c>
+      <c r="E221" s="2">
+        <v>45689.45833333334</v>
+      </c>
+      <c r="F221">
+        <v>23</v>
+      </c>
+      <c r="G221" t="s">
+        <v>80</v>
+      </c>
+      <c r="H221" t="s">
+        <v>87</v>
+      </c>
+      <c r="I221">
+        <v>0</v>
+      </c>
+      <c r="J221">
+        <v>0</v>
+      </c>
+      <c r="K221">
+        <v>0</v>
+      </c>
+      <c r="L221">
+        <v>3</v>
+      </c>
+      <c r="M221">
+        <v>2</v>
+      </c>
+      <c r="N221">
+        <v>5</v>
+      </c>
+      <c r="O221" t="s">
+        <v>234</v>
+      </c>
+      <c r="P221" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q221">
+        <v>2.5</v>
+      </c>
+      <c r="R221">
+        <v>2.1</v>
+      </c>
+      <c r="S221">
+        <v>4.75</v>
+      </c>
+      <c r="T221">
+        <v>1.44</v>
+      </c>
+      <c r="U221">
+        <v>2.63</v>
+      </c>
+      <c r="V221">
+        <v>3.25</v>
+      </c>
+      <c r="W221">
+        <v>1.33</v>
+      </c>
+      <c r="X221">
+        <v>9</v>
+      </c>
+      <c r="Y221">
+        <v>1.07</v>
+      </c>
+      <c r="Z221">
+        <v>1.84</v>
+      </c>
+      <c r="AA221">
+        <v>3.68</v>
+      </c>
+      <c r="AB221">
+        <v>4.6</v>
+      </c>
+      <c r="AC221">
+        <v>1.06</v>
+      </c>
+      <c r="AD221">
+        <v>10</v>
+      </c>
+      <c r="AE221">
+        <v>1.35</v>
+      </c>
+      <c r="AF221">
+        <v>3.25</v>
+      </c>
+      <c r="AG221">
+        <v>2.03</v>
+      </c>
+      <c r="AH221">
+        <v>1.79</v>
+      </c>
+      <c r="AI221">
+        <v>1.91</v>
+      </c>
+      <c r="AJ221">
+        <v>1.91</v>
+      </c>
+      <c r="AK221">
+        <v>1.21</v>
+      </c>
+      <c r="AL221">
+        <v>1.3</v>
+      </c>
+      <c r="AM221">
+        <v>1.9</v>
+      </c>
+      <c r="AN221">
+        <v>1.27</v>
+      </c>
+      <c r="AO221">
+        <v>0.36</v>
+      </c>
+      <c r="AP221">
+        <v>1.42</v>
+      </c>
+      <c r="AQ221">
+        <v>0.33</v>
+      </c>
+      <c r="AR221">
+        <v>1.06</v>
+      </c>
+      <c r="AS221">
+        <v>0.9</v>
+      </c>
+      <c r="AT221">
+        <v>1.96</v>
+      </c>
+      <c r="AU221">
+        <v>6</v>
+      </c>
+      <c r="AV221">
+        <v>4</v>
+      </c>
+      <c r="AW221">
+        <v>8</v>
+      </c>
+      <c r="AX221">
+        <v>11</v>
+      </c>
+      <c r="AY221">
+        <v>16</v>
+      </c>
+      <c r="AZ221">
+        <v>18</v>
+      </c>
+      <c r="BA221">
+        <v>4</v>
+      </c>
+      <c r="BB221">
+        <v>6</v>
+      </c>
+      <c r="BC221">
+        <v>10</v>
+      </c>
+      <c r="BD221">
+        <v>1.56</v>
+      </c>
+      <c r="BE221">
+        <v>6.75</v>
+      </c>
+      <c r="BF221">
+        <v>2.65</v>
+      </c>
+      <c r="BG221">
+        <v>1.26</v>
+      </c>
+      <c r="BH221">
+        <v>3.4</v>
+      </c>
+      <c r="BI221">
+        <v>1.47</v>
+      </c>
+      <c r="BJ221">
+        <v>2.48</v>
+      </c>
+      <c r="BK221">
+        <v>1.75</v>
+      </c>
+      <c r="BL221">
+        <v>1.95</v>
+      </c>
+      <c r="BM221">
+        <v>2.18</v>
+      </c>
+      <c r="BN221">
+        <v>1.58</v>
+      </c>
+      <c r="BO221">
+        <v>2.8</v>
+      </c>
+      <c r="BP221">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="222" spans="1:68">
+      <c r="A222" s="1">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>7492374</v>
+      </c>
+      <c r="C222" t="s">
+        <v>68</v>
+      </c>
+      <c r="D222" t="s">
+        <v>69</v>
+      </c>
+      <c r="E222" s="2">
+        <v>45689.45833333334</v>
+      </c>
+      <c r="F222">
+        <v>23</v>
+      </c>
+      <c r="G222" t="s">
+        <v>82</v>
+      </c>
+      <c r="H222" t="s">
+        <v>75</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+      <c r="J222">
+        <v>1</v>
+      </c>
+      <c r="K222">
+        <v>1</v>
+      </c>
+      <c r="L222">
+        <v>0</v>
+      </c>
+      <c r="M222">
+        <v>1</v>
+      </c>
+      <c r="N222">
+        <v>1</v>
+      </c>
+      <c r="O222" t="s">
+        <v>92</v>
+      </c>
+      <c r="P222" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q222">
+        <v>2.88</v>
+      </c>
+      <c r="R222">
+        <v>2.05</v>
+      </c>
+      <c r="S222">
+        <v>4</v>
+      </c>
+      <c r="T222">
+        <v>1.44</v>
+      </c>
+      <c r="U222">
+        <v>2.63</v>
+      </c>
+      <c r="V222">
+        <v>3.4</v>
+      </c>
+      <c r="W222">
+        <v>1.3</v>
+      </c>
+      <c r="X222">
+        <v>10</v>
+      </c>
+      <c r="Y222">
+        <v>1.06</v>
+      </c>
+      <c r="Z222">
+        <v>2.16</v>
+      </c>
+      <c r="AA222">
+        <v>3.38</v>
+      </c>
+      <c r="AB222">
+        <v>3.63</v>
+      </c>
+      <c r="AC222">
+        <v>1.07</v>
+      </c>
+      <c r="AD222">
+        <v>9</v>
+      </c>
+      <c r="AE222">
+        <v>1.4</v>
+      </c>
+      <c r="AF222">
+        <v>3</v>
+      </c>
+      <c r="AG222">
+        <v>1.8</v>
+      </c>
+      <c r="AH222">
+        <v>1.95</v>
+      </c>
+      <c r="AI222">
+        <v>1.91</v>
+      </c>
+      <c r="AJ222">
+        <v>1.91</v>
+      </c>
+      <c r="AK222">
+        <v>1.31</v>
+      </c>
+      <c r="AL222">
+        <v>1.32</v>
+      </c>
+      <c r="AM222">
+        <v>1.66</v>
+      </c>
+      <c r="AN222">
+        <v>0.55</v>
+      </c>
+      <c r="AO222">
+        <v>0.91</v>
+      </c>
+      <c r="AP222">
+        <v>0.5</v>
+      </c>
+      <c r="AQ222">
+        <v>1.08</v>
+      </c>
+      <c r="AR222">
+        <v>1.17</v>
+      </c>
+      <c r="AS222">
+        <v>1.07</v>
+      </c>
+      <c r="AT222">
+        <v>2.24</v>
+      </c>
+      <c r="AU222">
+        <v>3</v>
+      </c>
+      <c r="AV222">
+        <v>5</v>
+      </c>
+      <c r="AW222">
+        <v>7</v>
+      </c>
+      <c r="AX222">
+        <v>8</v>
+      </c>
+      <c r="AY222">
+        <v>12</v>
+      </c>
+      <c r="AZ222">
+        <v>14</v>
+      </c>
+      <c r="BA222">
+        <v>7</v>
+      </c>
+      <c r="BB222">
+        <v>3</v>
+      </c>
+      <c r="BC222">
+        <v>10</v>
+      </c>
+      <c r="BD222">
+        <v>1.6</v>
+      </c>
+      <c r="BE222">
+        <v>6.4</v>
+      </c>
+      <c r="BF222">
+        <v>2.6</v>
+      </c>
+      <c r="BG222">
+        <v>1.4</v>
+      </c>
+      <c r="BH222">
+        <v>2.7</v>
+      </c>
+      <c r="BI222">
+        <v>1.66</v>
+      </c>
+      <c r="BJ222">
+        <v>2.06</v>
+      </c>
+      <c r="BK222">
+        <v>2.08</v>
+      </c>
+      <c r="BL222">
+        <v>1.65</v>
+      </c>
+      <c r="BM222">
+        <v>2.65</v>
+      </c>
+      <c r="BN222">
+        <v>1.41</v>
+      </c>
+      <c r="BO222">
+        <v>3.55</v>
+      </c>
+      <c r="BP222">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="223" spans="1:68">
+      <c r="A223" s="1">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>7492368</v>
+      </c>
+      <c r="C223" t="s">
+        <v>68</v>
+      </c>
+      <c r="D223" t="s">
+        <v>69</v>
+      </c>
+      <c r="E223" s="2">
+        <v>45689.58333333334</v>
+      </c>
+      <c r="F223">
+        <v>23</v>
+      </c>
+      <c r="G223" t="s">
+        <v>89</v>
+      </c>
+      <c r="H223" t="s">
+        <v>83</v>
+      </c>
+      <c r="I223">
+        <v>1</v>
+      </c>
+      <c r="J223">
+        <v>1</v>
+      </c>
+      <c r="K223">
+        <v>2</v>
+      </c>
+      <c r="L223">
+        <v>1</v>
+      </c>
+      <c r="M223">
+        <v>1</v>
+      </c>
+      <c r="N223">
+        <v>2</v>
+      </c>
+      <c r="O223" t="s">
+        <v>189</v>
+      </c>
+      <c r="P223" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q223">
+        <v>1.95</v>
+      </c>
+      <c r="R223">
+        <v>2.3</v>
+      </c>
+      <c r="S223">
+        <v>7.5</v>
+      </c>
+      <c r="T223">
+        <v>1.4</v>
+      </c>
+      <c r="U223">
+        <v>2.75</v>
+      </c>
+      <c r="V223">
+        <v>2.75</v>
+      </c>
+      <c r="W223">
+        <v>1.4</v>
+      </c>
+      <c r="X223">
+        <v>8</v>
+      </c>
+      <c r="Y223">
+        <v>1.08</v>
+      </c>
+      <c r="Z223">
+        <v>1.42</v>
+      </c>
+      <c r="AA223">
+        <v>4.8</v>
+      </c>
+      <c r="AB223">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC223">
+        <v>1.04</v>
+      </c>
+      <c r="AD223">
+        <v>13</v>
+      </c>
+      <c r="AE223">
+        <v>1.3</v>
+      </c>
+      <c r="AF223">
+        <v>3.6</v>
+      </c>
+      <c r="AG223">
+        <v>1.88</v>
+      </c>
+      <c r="AH223">
+        <v>1.93</v>
+      </c>
+      <c r="AI223">
+        <v>2.1</v>
+      </c>
+      <c r="AJ223">
+        <v>1.67</v>
+      </c>
+      <c r="AK223">
+        <v>1.08</v>
+      </c>
+      <c r="AL223">
+        <v>1.19</v>
+      </c>
+      <c r="AM223">
+        <v>2.85</v>
+      </c>
+      <c r="AN223">
+        <v>2.2</v>
+      </c>
+      <c r="AO223">
+        <v>1.18</v>
+      </c>
+      <c r="AP223">
+        <v>2.09</v>
+      </c>
+      <c r="AQ223">
+        <v>1.17</v>
+      </c>
+      <c r="AR223">
+        <v>1.8</v>
+      </c>
+      <c r="AS223">
+        <v>1.11</v>
+      </c>
+      <c r="AT223">
+        <v>2.91</v>
+      </c>
+      <c r="AU223">
+        <v>11</v>
+      </c>
+      <c r="AV223">
+        <v>4</v>
+      </c>
+      <c r="AW223">
+        <v>11</v>
+      </c>
+      <c r="AX223">
+        <v>2</v>
+      </c>
+      <c r="AY223">
+        <v>26</v>
+      </c>
+      <c r="AZ223">
+        <v>8</v>
+      </c>
+      <c r="BA223">
+        <v>8</v>
+      </c>
+      <c r="BB223">
+        <v>0</v>
+      </c>
+      <c r="BC223">
+        <v>8</v>
+      </c>
+      <c r="BD223">
+        <v>1.25</v>
+      </c>
+      <c r="BE223">
+        <v>7.5</v>
+      </c>
+      <c r="BF223">
+        <v>4.3</v>
+      </c>
+      <c r="BG223">
+        <v>1.44</v>
+      </c>
+      <c r="BH223">
+        <v>2.55</v>
+      </c>
+      <c r="BI223">
+        <v>1.74</v>
+      </c>
+      <c r="BJ223">
+        <v>1.96</v>
+      </c>
+      <c r="BK223">
+        <v>2.18</v>
+      </c>
+      <c r="BL223">
+        <v>1.58</v>
+      </c>
+      <c r="BM223">
+        <v>2.8</v>
+      </c>
+      <c r="BN223">
+        <v>1.36</v>
+      </c>
+      <c r="BO223">
+        <v>3.8</v>
+      </c>
+      <c r="BP223">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="224" spans="1:68">
+      <c r="A224" s="1">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>7492369</v>
+      </c>
+      <c r="C224" t="s">
+        <v>68</v>
+      </c>
+      <c r="D224" t="s">
+        <v>69</v>
+      </c>
+      <c r="E224" s="2">
+        <v>45689.69791666666</v>
+      </c>
+      <c r="F224">
+        <v>23</v>
+      </c>
+      <c r="G224" t="s">
+        <v>74</v>
+      </c>
+      <c r="H224" t="s">
+        <v>88</v>
+      </c>
+      <c r="I224">
+        <v>1</v>
+      </c>
+      <c r="J224">
+        <v>0</v>
+      </c>
+      <c r="K224">
+        <v>1</v>
+      </c>
+      <c r="L224">
+        <v>2</v>
+      </c>
+      <c r="M224">
+        <v>0</v>
+      </c>
+      <c r="N224">
+        <v>2</v>
+      </c>
+      <c r="O224" t="s">
+        <v>235</v>
+      </c>
+      <c r="P224" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q224">
+        <v>2.5</v>
+      </c>
+      <c r="R224">
+        <v>2.2</v>
+      </c>
+      <c r="S224">
+        <v>4.75</v>
+      </c>
+      <c r="T224">
+        <v>1.4</v>
+      </c>
+      <c r="U224">
+        <v>2.75</v>
+      </c>
+      <c r="V224">
+        <v>3</v>
+      </c>
+      <c r="W224">
+        <v>1.36</v>
+      </c>
+      <c r="X224">
+        <v>8</v>
+      </c>
+      <c r="Y224">
+        <v>1.08</v>
+      </c>
+      <c r="Z224">
+        <v>1.84</v>
+      </c>
+      <c r="AA224">
+        <v>3.73</v>
+      </c>
+      <c r="AB224">
+        <v>4.5</v>
+      </c>
+      <c r="AC224">
+        <v>1.06</v>
+      </c>
+      <c r="AD224">
+        <v>10</v>
+      </c>
+      <c r="AE224">
+        <v>1.35</v>
+      </c>
+      <c r="AF224">
+        <v>3.25</v>
+      </c>
+      <c r="AG224">
+        <v>1.95</v>
+      </c>
+      <c r="AH224">
+        <v>1.86</v>
+      </c>
+      <c r="AI224">
+        <v>1.8</v>
+      </c>
+      <c r="AJ224">
+        <v>1.95</v>
+      </c>
+      <c r="AK224">
+        <v>1.21</v>
+      </c>
+      <c r="AL224">
+        <v>1.29</v>
+      </c>
+      <c r="AM224">
+        <v>1.93</v>
+      </c>
+      <c r="AN224">
+        <v>1.7</v>
+      </c>
+      <c r="AO224">
+        <v>0.64</v>
+      </c>
+      <c r="AP224">
+        <v>1.82</v>
+      </c>
+      <c r="AQ224">
+        <v>0.58</v>
+      </c>
+      <c r="AR224">
+        <v>1.75</v>
+      </c>
+      <c r="AS224">
+        <v>1.36</v>
+      </c>
+      <c r="AT224">
+        <v>3.11</v>
+      </c>
+      <c r="AU224">
+        <v>5</v>
+      </c>
+      <c r="AV224">
+        <v>2</v>
+      </c>
+      <c r="AW224">
+        <v>11</v>
+      </c>
+      <c r="AX224">
+        <v>8</v>
+      </c>
+      <c r="AY224">
+        <v>21</v>
+      </c>
+      <c r="AZ224">
+        <v>13</v>
+      </c>
+      <c r="BA224">
+        <v>4</v>
+      </c>
+      <c r="BB224">
+        <v>2</v>
+      </c>
+      <c r="BC224">
+        <v>6</v>
+      </c>
+      <c r="BD224">
+        <v>1.54</v>
+      </c>
+      <c r="BE224">
+        <v>6.75</v>
+      </c>
+      <c r="BF224">
+        <v>2.75</v>
+      </c>
+      <c r="BG224">
+        <v>1.36</v>
+      </c>
+      <c r="BH224">
+        <v>2.8</v>
+      </c>
+      <c r="BI224">
+        <v>1.62</v>
+      </c>
+      <c r="BJ224">
+        <v>2.12</v>
+      </c>
+      <c r="BK224">
+        <v>2</v>
+      </c>
+      <c r="BL224">
+        <v>1.71</v>
+      </c>
+      <c r="BM224">
+        <v>2.55</v>
+      </c>
+      <c r="BN224">
+        <v>1.44</v>
+      </c>
+      <c r="BO224">
+        <v>3.4</v>
+      </c>
+      <c r="BP224">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="225" spans="1:68">
+      <c r="A225" s="1">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>7492372</v>
+      </c>
+      <c r="C225" t="s">
+        <v>68</v>
+      </c>
+      <c r="D225" t="s">
+        <v>69</v>
+      </c>
+      <c r="E225" s="2">
+        <v>45690.35416666666</v>
+      </c>
+      <c r="F225">
+        <v>23</v>
+      </c>
+      <c r="G225" t="s">
+        <v>79</v>
+      </c>
+      <c r="H225" t="s">
+        <v>72</v>
+      </c>
+      <c r="I225">
+        <v>0</v>
+      </c>
+      <c r="J225">
+        <v>1</v>
+      </c>
+      <c r="K225">
+        <v>1</v>
+      </c>
+      <c r="L225">
+        <v>4</v>
+      </c>
+      <c r="M225">
+        <v>1</v>
+      </c>
+      <c r="N225">
+        <v>5</v>
+      </c>
+      <c r="O225" t="s">
+        <v>236</v>
+      </c>
+      <c r="P225" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q225">
+        <v>1.91</v>
+      </c>
+      <c r="R225">
+        <v>2.25</v>
+      </c>
+      <c r="S225">
+        <v>9</v>
+      </c>
+      <c r="T225">
+        <v>1.4</v>
+      </c>
+      <c r="U225">
+        <v>2.75</v>
+      </c>
+      <c r="V225">
+        <v>3</v>
+      </c>
+      <c r="W225">
+        <v>1.36</v>
+      </c>
+      <c r="X225">
+        <v>9</v>
+      </c>
+      <c r="Y225">
+        <v>1.07</v>
+      </c>
+      <c r="Z225">
+        <v>1.41</v>
+      </c>
+      <c r="AA225">
+        <v>4.7</v>
+      </c>
+      <c r="AB225">
+        <v>9</v>
+      </c>
+      <c r="AC225">
+        <v>1.05</v>
+      </c>
+      <c r="AD225">
+        <v>11</v>
+      </c>
+      <c r="AE225">
+        <v>1.33</v>
+      </c>
+      <c r="AF225">
+        <v>3.4</v>
+      </c>
+      <c r="AG225">
+        <v>2.01</v>
+      </c>
+      <c r="AH225">
+        <v>1.81</v>
+      </c>
+      <c r="AI225">
+        <v>2.5</v>
+      </c>
+      <c r="AJ225">
+        <v>1.5</v>
+      </c>
+      <c r="AK225">
+        <v>1.07</v>
+      </c>
+      <c r="AL225">
+        <v>1.18</v>
+      </c>
+      <c r="AM225">
+        <v>3</v>
+      </c>
+      <c r="AN225">
+        <v>1.73</v>
+      </c>
+      <c r="AO225">
+        <v>1.18</v>
+      </c>
+      <c r="AP225">
+        <v>1.83</v>
+      </c>
+      <c r="AQ225">
+        <v>1.08</v>
+      </c>
+      <c r="AR225">
+        <v>1.48</v>
+      </c>
+      <c r="AS225">
+        <v>0.98</v>
+      </c>
+      <c r="AT225">
+        <v>2.46</v>
+      </c>
+      <c r="AU225">
+        <v>9</v>
+      </c>
+      <c r="AV225">
+        <v>4</v>
+      </c>
+      <c r="AW225">
+        <v>16</v>
+      </c>
+      <c r="AX225">
+        <v>7</v>
+      </c>
+      <c r="AY225">
+        <v>28</v>
+      </c>
+      <c r="AZ225">
+        <v>14</v>
+      </c>
+      <c r="BA225">
+        <v>8</v>
+      </c>
+      <c r="BB225">
+        <v>6</v>
+      </c>
+      <c r="BC225">
+        <v>14</v>
+      </c>
+      <c r="BD225">
+        <v>1.25</v>
+      </c>
+      <c r="BE225">
+        <v>11</v>
+      </c>
+      <c r="BF225">
+        <v>5.1</v>
+      </c>
+      <c r="BG225">
+        <v>1.2</v>
+      </c>
+      <c r="BH225">
+        <v>3.68</v>
+      </c>
+      <c r="BI225">
+        <v>1.41</v>
+      </c>
+      <c r="BJ225">
+        <v>2.6</v>
+      </c>
+      <c r="BK225">
+        <v>1.73</v>
+      </c>
+      <c r="BL225">
+        <v>1.99</v>
+      </c>
+      <c r="BM225">
+        <v>2.17</v>
+      </c>
+      <c r="BN225">
+        <v>1.58</v>
+      </c>
+      <c r="BO225">
+        <v>2.83</v>
+      </c>
+      <c r="BP225">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="226" spans="1:68">
+      <c r="A226" s="1">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>7492371</v>
+      </c>
+      <c r="C226" t="s">
+        <v>68</v>
+      </c>
+      <c r="D226" t="s">
+        <v>69</v>
+      </c>
+      <c r="E226" s="2">
+        <v>45690.45833333334</v>
+      </c>
+      <c r="F226">
+        <v>23</v>
+      </c>
+      <c r="G226" t="s">
+        <v>84</v>
+      </c>
+      <c r="H226" t="s">
+        <v>70</v>
+      </c>
+      <c r="I226">
+        <v>2</v>
+      </c>
+      <c r="J226">
+        <v>0</v>
+      </c>
+      <c r="K226">
+        <v>2</v>
+      </c>
+      <c r="L226">
+        <v>2</v>
+      </c>
+      <c r="M226">
+        <v>1</v>
+      </c>
+      <c r="N226">
+        <v>3</v>
+      </c>
+      <c r="O226" t="s">
+        <v>237</v>
+      </c>
+      <c r="P226" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q226">
+        <v>2.25</v>
+      </c>
+      <c r="R226">
+        <v>2.2</v>
+      </c>
+      <c r="S226">
+        <v>5.5</v>
+      </c>
+      <c r="T226">
+        <v>1.44</v>
+      </c>
+      <c r="U226">
+        <v>2.63</v>
+      </c>
+      <c r="V226">
+        <v>3</v>
+      </c>
+      <c r="W226">
+        <v>1.36</v>
+      </c>
+      <c r="X226">
+        <v>9</v>
+      </c>
+      <c r="Y226">
+        <v>1.07</v>
+      </c>
+      <c r="Z226">
+        <v>1.62</v>
+      </c>
+      <c r="AA226">
+        <v>4.1</v>
+      </c>
+      <c r="AB226">
+        <v>5.8</v>
+      </c>
+      <c r="AC226">
+        <v>1.06</v>
+      </c>
+      <c r="AD226">
+        <v>10</v>
+      </c>
+      <c r="AE226">
+        <v>1.36</v>
+      </c>
+      <c r="AF226">
+        <v>3.2</v>
+      </c>
+      <c r="AG226">
+        <v>1.98</v>
+      </c>
+      <c r="AH226">
+        <v>1.83</v>
+      </c>
+      <c r="AI226">
+        <v>2</v>
+      </c>
+      <c r="AJ226">
+        <v>1.75</v>
+      </c>
+      <c r="AK226">
+        <v>1.15</v>
+      </c>
+      <c r="AL226">
+        <v>1.25</v>
+      </c>
+      <c r="AM226">
+        <v>2.2</v>
+      </c>
+      <c r="AN226">
+        <v>1.8</v>
+      </c>
+      <c r="AO226">
+        <v>1.4</v>
+      </c>
+      <c r="AP226">
+        <v>1.91</v>
+      </c>
+      <c r="AQ226">
+        <v>1.27</v>
+      </c>
+      <c r="AR226">
+        <v>1.59</v>
+      </c>
+      <c r="AS226">
+        <v>0.96</v>
+      </c>
+      <c r="AT226">
+        <v>2.55</v>
+      </c>
+      <c r="AU226">
+        <v>6</v>
+      </c>
+      <c r="AV226">
+        <v>4</v>
+      </c>
+      <c r="AW226">
+        <v>2</v>
+      </c>
+      <c r="AX226">
+        <v>14</v>
+      </c>
+      <c r="AY226">
+        <v>10</v>
+      </c>
+      <c r="AZ226">
+        <v>21</v>
+      </c>
+      <c r="BA226">
+        <v>1</v>
+      </c>
+      <c r="BB226">
+        <v>8</v>
+      </c>
+      <c r="BC226">
+        <v>9</v>
+      </c>
+      <c r="BD226">
+        <v>1.3</v>
+      </c>
+      <c r="BE226">
+        <v>10.25</v>
+      </c>
+      <c r="BF226">
+        <v>4.55</v>
+      </c>
+      <c r="BG226">
+        <v>1.28</v>
+      </c>
+      <c r="BH226">
+        <v>3.08</v>
+      </c>
+      <c r="BI226">
+        <v>1.54</v>
+      </c>
+      <c r="BJ226">
+        <v>2.25</v>
+      </c>
+      <c r="BK226">
+        <v>1.95</v>
+      </c>
+      <c r="BL226">
+        <v>1.76</v>
+      </c>
+      <c r="BM226">
+        <v>2.54</v>
+      </c>
+      <c r="BN226">
+        <v>1.43</v>
+      </c>
+      <c r="BO226">
+        <v>3.42</v>
+      </c>
+      <c r="BP226">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="352">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -730,6 +730,9 @@
     <t>['9', '30']</t>
   </si>
   <si>
+    <t>['55']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1024,9 +1027,6 @@
     <t>['6', '11', '90+1']</t>
   </si>
   <si>
-    <t>['55']</t>
-  </si>
-  <si>
     <t>['58', '90+8']</t>
   </si>
   <si>
@@ -1064,6 +1064,12 @@
   </si>
   <si>
     <t>['64', '78']</t>
+  </si>
+  <si>
+    <t>['29']</t>
+  </si>
+  <si>
+    <t>['41', '64']</t>
   </si>
 </sst>
 </file>
@@ -1425,7 +1431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP226"/>
+  <dimension ref="A1:BP229"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1681,7 +1687,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1762,7 +1768,7 @@
         <v>1</v>
       </c>
       <c r="AQ2">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2299,7 +2305,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2377,7 +2383,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ5">
         <v>1.17</v>
@@ -2505,7 +2511,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2792,7 +2798,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ7">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2995,7 +3001,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ8">
         <v>0.82</v>
@@ -3123,7 +3129,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3329,7 +3335,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3741,7 +3747,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q12">
         <v>3.75</v>
@@ -3822,7 +3828,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ12">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3947,7 +3953,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4359,7 +4365,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q15">
         <v>3.3</v>
@@ -5183,7 +5189,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5261,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ19">
         <v>1.08</v>
@@ -5467,7 +5473,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ20">
         <v>0.58</v>
@@ -5595,7 +5601,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5801,7 +5807,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6213,7 +6219,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6625,7 +6631,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q26">
         <v>2</v>
@@ -6831,7 +6837,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7037,7 +7043,7 @@
         <v>92</v>
       </c>
       <c r="P28" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q28">
         <v>2.75</v>
@@ -7243,7 +7249,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q29">
         <v>2.25</v>
@@ -7861,7 +7867,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8351,7 +8357,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ34">
         <v>0.33</v>
@@ -8479,7 +8485,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q35">
         <v>4</v>
@@ -8891,7 +8897,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
@@ -9097,7 +9103,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9175,10 +9181,10 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ38">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AR38">
         <v>1.24</v>
@@ -9303,7 +9309,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9384,7 +9390,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ39">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AR39">
         <v>1.18</v>
@@ -9509,7 +9515,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9715,7 +9721,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9921,7 +9927,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9999,7 +10005,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ42">
         <v>1.08</v>
@@ -10127,7 +10133,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10620,7 +10626,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ45">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AR45">
         <v>1.23</v>
@@ -10745,7 +10751,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10951,7 +10957,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11032,7 +11038,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ47">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR47">
         <v>1.69</v>
@@ -11157,7 +11163,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11441,7 +11447,7 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ49">
         <v>1.09</v>
@@ -11569,7 +11575,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11775,7 +11781,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12059,7 +12065,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ52">
         <v>0.83</v>
@@ -12187,7 +12193,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12268,7 +12274,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ53">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AR53">
         <v>1.05</v>
@@ -12393,7 +12399,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12599,7 +12605,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12805,7 +12811,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -12886,7 +12892,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ56">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR56">
         <v>1.02</v>
@@ -13089,7 +13095,7 @@
         <v>0.33</v>
       </c>
       <c r="AP57">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ57">
         <v>0.33</v>
@@ -13217,7 +13223,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13835,7 +13841,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14659,7 +14665,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14865,7 +14871,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15071,7 +15077,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15483,7 +15489,7 @@
         <v>140</v>
       </c>
       <c r="P69" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q69">
         <v>2.2</v>
@@ -15689,7 +15695,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -16307,7 +16313,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16591,7 +16597,7 @@
         <v>1.33</v>
       </c>
       <c r="AP74">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ74">
         <v>1.09</v>
@@ -16800,7 +16806,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ75">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR75">
         <v>1.37</v>
@@ -16925,7 +16931,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17006,7 +17012,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ76">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AR76">
         <v>0.85</v>
@@ -17131,7 +17137,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17337,7 +17343,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17543,7 +17549,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17621,7 +17627,7 @@
         <v>1.75</v>
       </c>
       <c r="AP79">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ79">
         <v>1.17</v>
@@ -17827,10 +17833,10 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ80">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AR80">
         <v>2.02</v>
@@ -17955,7 +17961,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18779,7 +18785,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19397,7 +19403,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19603,7 +19609,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19809,7 +19815,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20221,7 +20227,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20299,7 +20305,7 @@
         <v>1.25</v>
       </c>
       <c r="AP92">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ92">
         <v>1.55</v>
@@ -20427,7 +20433,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20505,10 +20511,10 @@
         <v>1.75</v>
       </c>
       <c r="AP93">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ93">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AR93">
         <v>1.71</v>
@@ -20633,7 +20639,7 @@
         <v>92</v>
       </c>
       <c r="P94" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q94">
         <v>6.5</v>
@@ -20714,7 +20720,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ94">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AR94">
         <v>0.91</v>
@@ -20839,7 +20845,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -21045,7 +21051,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -21457,7 +21463,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21663,7 +21669,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21744,7 +21750,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ99">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR99">
         <v>1.62</v>
@@ -21947,7 +21953,7 @@
         <v>1.4</v>
       </c>
       <c r="AP100">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ100">
         <v>1.17</v>
@@ -22281,7 +22287,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22693,7 +22699,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22899,7 +22905,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23105,7 +23111,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23929,7 +23935,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24135,7 +24141,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24341,7 +24347,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24547,7 +24553,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24753,7 +24759,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -24831,7 +24837,7 @@
         <v>1.4</v>
       </c>
       <c r="AP114">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ114">
         <v>1.4</v>
@@ -25165,7 +25171,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25371,7 +25377,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25449,7 +25455,7 @@
         <v>1.6</v>
       </c>
       <c r="AP117">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ117">
         <v>1.55</v>
@@ -25577,7 +25583,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25864,7 +25870,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ119">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR119">
         <v>0.96</v>
@@ -26070,7 +26076,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ120">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AR120">
         <v>1.62</v>
@@ -26195,7 +26201,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26276,7 +26282,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ121">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AR121">
         <v>1.14</v>
@@ -26479,7 +26485,7 @@
         <v>2.2</v>
       </c>
       <c r="AP122">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ122">
         <v>1.64</v>
@@ -26607,7 +26613,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26813,7 +26819,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27019,7 +27025,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27225,7 +27231,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27843,7 +27849,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -28333,7 +28339,7 @@
         <v>0.5</v>
       </c>
       <c r="AP131">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ131">
         <v>1.08</v>
@@ -28745,7 +28751,7 @@
         <v>1.5</v>
       </c>
       <c r="AP133">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ133">
         <v>1.08</v>
@@ -29079,7 +29085,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29366,7 +29372,7 @@
         <v>1</v>
       </c>
       <c r="AQ136">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR136">
         <v>1.24</v>
@@ -29491,7 +29497,7 @@
         <v>92</v>
       </c>
       <c r="P137" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q137">
         <v>5</v>
@@ -29572,7 +29578,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ137">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AR137">
         <v>1.14</v>
@@ -29697,7 +29703,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29903,7 +29909,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -29981,7 +29987,7 @@
         <v>1.86</v>
       </c>
       <c r="AP139">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ139">
         <v>2</v>
@@ -30727,7 +30733,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30933,7 +30939,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31011,7 +31017,7 @@
         <v>0.57</v>
       </c>
       <c r="AP144">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ144">
         <v>0.83</v>
@@ -31345,7 +31351,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31551,7 +31557,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31838,7 +31844,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ148">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR148">
         <v>1.5</v>
@@ -31963,7 +31969,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32375,7 +32381,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32453,7 +32459,7 @@
         <v>2</v>
       </c>
       <c r="AP151">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ151">
         <v>2</v>
@@ -32581,7 +32587,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32662,7 +32668,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ152">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AR152">
         <v>1.05</v>
@@ -32787,7 +32793,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -32993,7 +32999,7 @@
         <v>192</v>
       </c>
       <c r="P154" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33405,7 +33411,7 @@
         <v>193</v>
       </c>
       <c r="P156" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q156">
         <v>2.4</v>
@@ -33895,7 +33901,7 @@
         <v>1.5</v>
       </c>
       <c r="AP158">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ158">
         <v>1.27</v>
@@ -34023,7 +34029,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34104,7 +34110,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ159">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AR159">
         <v>1.56</v>
@@ -34435,7 +34441,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34641,7 +34647,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34722,7 +34728,7 @@
         <v>1</v>
       </c>
       <c r="AQ162">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AR162">
         <v>1.24</v>
@@ -34847,7 +34853,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -34928,7 +34934,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ163">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR163">
         <v>1.36</v>
@@ -35131,7 +35137,7 @@
         <v>1</v>
       </c>
       <c r="AP164">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ164">
         <v>0.73</v>
@@ -35259,7 +35265,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35465,7 +35471,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35671,7 +35677,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35877,7 +35883,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36495,7 +36501,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36701,7 +36707,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36779,10 +36785,10 @@
         <v>2.43</v>
       </c>
       <c r="AP172">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ172">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AR172">
         <v>1.46</v>
@@ -36907,7 +36913,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37113,7 +37119,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37525,7 +37531,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -37809,7 +37815,7 @@
         <v>0.5</v>
       </c>
       <c r="AP177">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ177">
         <v>0.82</v>
@@ -38143,7 +38149,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38349,7 +38355,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38555,7 +38561,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38636,7 +38642,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ181">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AR181">
         <v>1.57</v>
@@ -38967,7 +38973,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39663,10 +39669,10 @@
         <v>1.67</v>
       </c>
       <c r="AP186">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ186">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR186">
         <v>1.62</v>
@@ -39791,7 +39797,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40203,7 +40209,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40615,7 +40621,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>336</v>
+        <v>238</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -40693,7 +40699,7 @@
         <v>0.89</v>
       </c>
       <c r="AP191">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ191">
         <v>0.82</v>
@@ -41108,7 +41114,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ193">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AR193">
         <v>1.41</v>
@@ -42469,7 +42475,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42547,7 +42553,7 @@
         <v>1.56</v>
       </c>
       <c r="AP200">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ200">
         <v>1.27</v>
@@ -43168,7 +43174,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ203">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AR203">
         <v>1.78</v>
@@ -43499,7 +43505,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43577,7 +43583,7 @@
         <v>0.7</v>
       </c>
       <c r="AP205">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ205">
         <v>0.83</v>
@@ -43992,7 +43998,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ207">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR207">
         <v>1.12</v>
@@ -45353,7 +45359,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45431,7 +45437,7 @@
         <v>0.8</v>
       </c>
       <c r="AP214">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ214">
         <v>0.73</v>
@@ -45846,7 +45852,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ216">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AR216">
         <v>1.3</v>
@@ -46177,7 +46183,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -47207,7 +47213,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47825,7 +47831,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>336</v>
+        <v>238</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -47982,6 +47988,624 @@
       </c>
       <c r="BP226">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="227" spans="1:68">
+      <c r="A227" s="1">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>7492373</v>
+      </c>
+      <c r="C227" t="s">
+        <v>68</v>
+      </c>
+      <c r="D227" t="s">
+        <v>69</v>
+      </c>
+      <c r="E227" s="2">
+        <v>45690.58333333334</v>
+      </c>
+      <c r="F227">
+        <v>23</v>
+      </c>
+      <c r="G227" t="s">
+        <v>73</v>
+      </c>
+      <c r="H227" t="s">
+        <v>81</v>
+      </c>
+      <c r="I227">
+        <v>1</v>
+      </c>
+      <c r="J227">
+        <v>0</v>
+      </c>
+      <c r="K227">
+        <v>1</v>
+      </c>
+      <c r="L227">
+        <v>1</v>
+      </c>
+      <c r="M227">
+        <v>1</v>
+      </c>
+      <c r="N227">
+        <v>2</v>
+      </c>
+      <c r="O227" t="s">
+        <v>143</v>
+      </c>
+      <c r="P227" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q227">
+        <v>4.33</v>
+      </c>
+      <c r="R227">
+        <v>2.25</v>
+      </c>
+      <c r="S227">
+        <v>2.5</v>
+      </c>
+      <c r="T227">
+        <v>1.36</v>
+      </c>
+      <c r="U227">
+        <v>3</v>
+      </c>
+      <c r="V227">
+        <v>2.63</v>
+      </c>
+      <c r="W227">
+        <v>1.44</v>
+      </c>
+      <c r="X227">
+        <v>7</v>
+      </c>
+      <c r="Y227">
+        <v>1.1</v>
+      </c>
+      <c r="Z227">
+        <v>3.81</v>
+      </c>
+      <c r="AA227">
+        <v>3.63</v>
+      </c>
+      <c r="AB227">
+        <v>2.01</v>
+      </c>
+      <c r="AC227">
+        <v>1.05</v>
+      </c>
+      <c r="AD227">
+        <v>12</v>
+      </c>
+      <c r="AE227">
+        <v>1.28</v>
+      </c>
+      <c r="AF227">
+        <v>3.75</v>
+      </c>
+      <c r="AG227">
+        <v>1.82</v>
+      </c>
+      <c r="AH227">
+        <v>2</v>
+      </c>
+      <c r="AI227">
+        <v>1.7</v>
+      </c>
+      <c r="AJ227">
+        <v>2.05</v>
+      </c>
+      <c r="AK227">
+        <v>1.77</v>
+      </c>
+      <c r="AL227">
+        <v>1.29</v>
+      </c>
+      <c r="AM227">
+        <v>1.28</v>
+      </c>
+      <c r="AN227">
+        <v>1.82</v>
+      </c>
+      <c r="AO227">
+        <v>2.6</v>
+      </c>
+      <c r="AP227">
+        <v>1.75</v>
+      </c>
+      <c r="AQ227">
+        <v>2.45</v>
+      </c>
+      <c r="AR227">
+        <v>1.73</v>
+      </c>
+      <c r="AS227">
+        <v>1.59</v>
+      </c>
+      <c r="AT227">
+        <v>3.32</v>
+      </c>
+      <c r="AU227">
+        <v>5</v>
+      </c>
+      <c r="AV227">
+        <v>7</v>
+      </c>
+      <c r="AW227">
+        <v>6</v>
+      </c>
+      <c r="AX227">
+        <v>11</v>
+      </c>
+      <c r="AY227">
+        <v>15</v>
+      </c>
+      <c r="AZ227">
+        <v>19</v>
+      </c>
+      <c r="BA227">
+        <v>8</v>
+      </c>
+      <c r="BB227">
+        <v>11</v>
+      </c>
+      <c r="BC227">
+        <v>19</v>
+      </c>
+      <c r="BD227">
+        <v>2.39</v>
+      </c>
+      <c r="BE227">
+        <v>8.4</v>
+      </c>
+      <c r="BF227">
+        <v>1.82</v>
+      </c>
+      <c r="BG227">
+        <v>1.32</v>
+      </c>
+      <c r="BH227">
+        <v>2.88</v>
+      </c>
+      <c r="BI227">
+        <v>1.6</v>
+      </c>
+      <c r="BJ227">
+        <v>2.14</v>
+      </c>
+      <c r="BK227">
+        <v>2.04</v>
+      </c>
+      <c r="BL227">
+        <v>1.69</v>
+      </c>
+      <c r="BM227">
+        <v>2.71</v>
+      </c>
+      <c r="BN227">
+        <v>1.38</v>
+      </c>
+      <c r="BO227">
+        <v>3.72</v>
+      </c>
+      <c r="BP227">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:68">
+      <c r="A228" s="1">
+        <v>227</v>
+      </c>
+      <c r="B228">
+        <v>7492376</v>
+      </c>
+      <c r="C228" t="s">
+        <v>68</v>
+      </c>
+      <c r="D228" t="s">
+        <v>69</v>
+      </c>
+      <c r="E228" s="2">
+        <v>45690.69791666666</v>
+      </c>
+      <c r="F228">
+        <v>23</v>
+      </c>
+      <c r="G228" t="s">
+        <v>86</v>
+      </c>
+      <c r="H228" t="s">
+        <v>85</v>
+      </c>
+      <c r="I228">
+        <v>0</v>
+      </c>
+      <c r="J228">
+        <v>1</v>
+      </c>
+      <c r="K228">
+        <v>1</v>
+      </c>
+      <c r="L228">
+        <v>1</v>
+      </c>
+      <c r="M228">
+        <v>1</v>
+      </c>
+      <c r="N228">
+        <v>2</v>
+      </c>
+      <c r="O228" t="s">
+        <v>165</v>
+      </c>
+      <c r="P228" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q228">
+        <v>3.6</v>
+      </c>
+      <c r="R228">
+        <v>2.1</v>
+      </c>
+      <c r="S228">
+        <v>3</v>
+      </c>
+      <c r="T228">
+        <v>1.44</v>
+      </c>
+      <c r="U228">
+        <v>2.63</v>
+      </c>
+      <c r="V228">
+        <v>3.25</v>
+      </c>
+      <c r="W228">
+        <v>1.33</v>
+      </c>
+      <c r="X228">
+        <v>9</v>
+      </c>
+      <c r="Y228">
+        <v>1.07</v>
+      </c>
+      <c r="Z228">
+        <v>3.14</v>
+      </c>
+      <c r="AA228">
+        <v>3.26</v>
+      </c>
+      <c r="AB228">
+        <v>2.44</v>
+      </c>
+      <c r="AC228">
+        <v>1.07</v>
+      </c>
+      <c r="AD228">
+        <v>9.5</v>
+      </c>
+      <c r="AE228">
+        <v>1.33</v>
+      </c>
+      <c r="AF228">
+        <v>3.3</v>
+      </c>
+      <c r="AG228">
+        <v>1.95</v>
+      </c>
+      <c r="AH228">
+        <v>1.75</v>
+      </c>
+      <c r="AI228">
+        <v>1.8</v>
+      </c>
+      <c r="AJ228">
+        <v>1.95</v>
+      </c>
+      <c r="AK228">
+        <v>1.57</v>
+      </c>
+      <c r="AL228">
+        <v>1.33</v>
+      </c>
+      <c r="AM228">
+        <v>1.36</v>
+      </c>
+      <c r="AN228">
+        <v>1.91</v>
+      </c>
+      <c r="AO228">
+        <v>2.36</v>
+      </c>
+      <c r="AP228">
+        <v>1.83</v>
+      </c>
+      <c r="AQ228">
+        <v>2.25</v>
+      </c>
+      <c r="AR228">
+        <v>1.58</v>
+      </c>
+      <c r="AS228">
+        <v>1.2</v>
+      </c>
+      <c r="AT228">
+        <v>2.78</v>
+      </c>
+      <c r="AU228">
+        <v>3</v>
+      </c>
+      <c r="AV228">
+        <v>3</v>
+      </c>
+      <c r="AW228">
+        <v>10</v>
+      </c>
+      <c r="AX228">
+        <v>3</v>
+      </c>
+      <c r="AY228">
+        <v>19</v>
+      </c>
+      <c r="AZ228">
+        <v>8</v>
+      </c>
+      <c r="BA228">
+        <v>2</v>
+      </c>
+      <c r="BB228">
+        <v>3</v>
+      </c>
+      <c r="BC228">
+        <v>5</v>
+      </c>
+      <c r="BD228">
+        <v>2.25</v>
+      </c>
+      <c r="BE228">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF228">
+        <v>1.92</v>
+      </c>
+      <c r="BG228">
+        <v>1.33</v>
+      </c>
+      <c r="BH228">
+        <v>2.83</v>
+      </c>
+      <c r="BI228">
+        <v>1.63</v>
+      </c>
+      <c r="BJ228">
+        <v>2.09</v>
+      </c>
+      <c r="BK228">
+        <v>2.09</v>
+      </c>
+      <c r="BL228">
+        <v>1.66</v>
+      </c>
+      <c r="BM228">
+        <v>2.78</v>
+      </c>
+      <c r="BN228">
+        <v>1.36</v>
+      </c>
+      <c r="BO228">
+        <v>3.82</v>
+      </c>
+      <c r="BP228">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="229" spans="1:68">
+      <c r="A229" s="1">
+        <v>228</v>
+      </c>
+      <c r="B229">
+        <v>7492370</v>
+      </c>
+      <c r="C229" t="s">
+        <v>68</v>
+      </c>
+      <c r="D229" t="s">
+        <v>69</v>
+      </c>
+      <c r="E229" s="2">
+        <v>45691.69791666666</v>
+      </c>
+      <c r="F229">
+        <v>23</v>
+      </c>
+      <c r="G229" t="s">
+        <v>76</v>
+      </c>
+      <c r="H229" t="s">
+        <v>77</v>
+      </c>
+      <c r="I229">
+        <v>0</v>
+      </c>
+      <c r="J229">
+        <v>1</v>
+      </c>
+      <c r="K229">
+        <v>1</v>
+      </c>
+      <c r="L229">
+        <v>1</v>
+      </c>
+      <c r="M229">
+        <v>2</v>
+      </c>
+      <c r="N229">
+        <v>3</v>
+      </c>
+      <c r="O229" t="s">
+        <v>238</v>
+      </c>
+      <c r="P229" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q229">
+        <v>4</v>
+      </c>
+      <c r="R229">
+        <v>2.2</v>
+      </c>
+      <c r="S229">
+        <v>2.63</v>
+      </c>
+      <c r="T229">
+        <v>1.36</v>
+      </c>
+      <c r="U229">
+        <v>3</v>
+      </c>
+      <c r="V229">
+        <v>2.75</v>
+      </c>
+      <c r="W229">
+        <v>1.4</v>
+      </c>
+      <c r="X229">
+        <v>8</v>
+      </c>
+      <c r="Y229">
+        <v>1.08</v>
+      </c>
+      <c r="Z229">
+        <v>3.75</v>
+      </c>
+      <c r="AA229">
+        <v>3.58</v>
+      </c>
+      <c r="AB229">
+        <v>2.05</v>
+      </c>
+      <c r="AC229">
+        <v>1.05</v>
+      </c>
+      <c r="AD229">
+        <v>11</v>
+      </c>
+      <c r="AE229">
+        <v>1.3</v>
+      </c>
+      <c r="AF229">
+        <v>3.6</v>
+      </c>
+      <c r="AG229">
+        <v>1.88</v>
+      </c>
+      <c r="AH229">
+        <v>1.93</v>
+      </c>
+      <c r="AI229">
+        <v>1.7</v>
+      </c>
+      <c r="AJ229">
+        <v>2.05</v>
+      </c>
+      <c r="AK229">
+        <v>1.75</v>
+      </c>
+      <c r="AL229">
+        <v>1.28</v>
+      </c>
+      <c r="AM229">
+        <v>1.29</v>
+      </c>
+      <c r="AN229">
+        <v>1.09</v>
+      </c>
+      <c r="AO229">
+        <v>1.64</v>
+      </c>
+      <c r="AP229">
+        <v>1</v>
+      </c>
+      <c r="AQ229">
+        <v>1.75</v>
+      </c>
+      <c r="AR229">
+        <v>1.45</v>
+      </c>
+      <c r="AS229">
+        <v>1.58</v>
+      </c>
+      <c r="AT229">
+        <v>3.03</v>
+      </c>
+      <c r="AU229">
+        <v>5</v>
+      </c>
+      <c r="AV229">
+        <v>7</v>
+      </c>
+      <c r="AW229">
+        <v>11</v>
+      </c>
+      <c r="AX229">
+        <v>5</v>
+      </c>
+      <c r="AY229">
+        <v>21</v>
+      </c>
+      <c r="AZ229">
+        <v>13</v>
+      </c>
+      <c r="BA229">
+        <v>7</v>
+      </c>
+      <c r="BB229">
+        <v>7</v>
+      </c>
+      <c r="BC229">
+        <v>14</v>
+      </c>
+      <c r="BD229">
+        <v>2.17</v>
+      </c>
+      <c r="BE229">
+        <v>6.5</v>
+      </c>
+      <c r="BF229">
+        <v>1.82</v>
+      </c>
+      <c r="BG229">
+        <v>1.23</v>
+      </c>
+      <c r="BH229">
+        <v>3.65</v>
+      </c>
+      <c r="BI229">
+        <v>1.41</v>
+      </c>
+      <c r="BJ229">
+        <v>2.65</v>
+      </c>
+      <c r="BK229">
+        <v>1.67</v>
+      </c>
+      <c r="BL229">
+        <v>2.05</v>
+      </c>
+      <c r="BM229">
+        <v>2.05</v>
+      </c>
+      <c r="BN229">
+        <v>1.67</v>
+      </c>
+      <c r="BO229">
+        <v>2.55</v>
+      </c>
+      <c r="BP229">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="353">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -730,6 +730,9 @@
     <t>['9', '30']</t>
   </si>
   <si>
+    <t>['59', '68', '89']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1431,7 +1434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP229"/>
+  <dimension ref="A1:BP230"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1687,7 +1690,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1768,7 +1771,7 @@
         <v>1</v>
       </c>
       <c r="AQ2">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2305,7 +2308,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2511,7 +2514,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -3129,7 +3132,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3335,7 +3338,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3747,7 +3750,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q12">
         <v>3.75</v>
@@ -3953,7 +3956,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4159,7 +4162,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4649,7 +4652,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>0.33</v>
@@ -5189,7 +5192,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5601,7 +5604,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5807,7 +5810,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6219,7 +6222,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6631,7 +6634,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6837,7 +6840,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7043,7 +7046,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7121,7 +7124,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ28">
         <v>0.64</v>
@@ -7249,7 +7252,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7867,7 +7870,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8485,7 +8488,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q35">
         <v>4</v>
@@ -8691,7 +8694,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -9103,7 +9106,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9309,7 +9312,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9390,7 +9393,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ39">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR39">
         <v>1.18</v>
@@ -9515,7 +9518,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9721,7 +9724,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9927,7 +9930,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10133,7 +10136,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10751,7 +10754,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10957,7 +10960,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11035,7 +11038,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ47">
         <v>1.75</v>
@@ -11163,7 +11166,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11575,7 +11578,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11781,7 +11784,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12193,7 +12196,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12274,7 +12277,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ53">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR53">
         <v>1.05</v>
@@ -12399,7 +12402,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12605,7 +12608,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12811,7 +12814,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13017,7 +13020,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13841,7 +13844,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14665,7 +14668,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14871,7 +14874,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15077,7 +15080,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15283,7 +15286,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q68">
         <v>2.2</v>
@@ -15695,7 +15698,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -15979,7 +15982,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ71">
         <v>1.4</v>
@@ -16313,7 +16316,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16931,7 +16934,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17137,7 +17140,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17343,7 +17346,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17549,7 +17552,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17836,7 +17839,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ80">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR80">
         <v>2.02</v>
@@ -17961,7 +17964,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18785,7 +18788,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19403,7 +19406,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19609,7 +19612,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19815,7 +19818,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -19893,7 +19896,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ90">
         <v>0.82</v>
@@ -20021,7 +20024,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20433,7 +20436,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20639,7 +20642,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20845,7 +20848,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -20926,7 +20929,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ95">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR95">
         <v>0.91</v>
@@ -21257,7 +21260,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21463,7 +21466,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21669,7 +21672,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22287,7 +22290,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22699,7 +22702,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22905,7 +22908,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23111,7 +23114,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23935,7 +23938,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24141,7 +24144,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24347,7 +24350,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24553,7 +24556,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24759,7 +24762,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25171,7 +25174,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25377,7 +25380,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25583,7 +25586,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25661,7 +25664,7 @@
         <v>0.6</v>
       </c>
       <c r="AP118">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ118">
         <v>1.08</v>
@@ -26201,7 +26204,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26282,7 +26285,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ121">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR121">
         <v>1.14</v>
@@ -26613,7 +26616,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26819,7 +26822,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27025,7 +27028,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27231,7 +27234,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27849,7 +27852,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -29085,7 +29088,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29291,7 +29294,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29703,7 +29706,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29909,7 +29912,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30733,7 +30736,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30939,7 +30942,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31223,7 +31226,7 @@
         <v>0.83</v>
       </c>
       <c r="AP145">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ145">
         <v>0.82</v>
@@ -31351,7 +31354,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31557,7 +31560,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31969,7 +31972,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32381,7 +32384,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32587,7 +32590,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32793,7 +32796,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -32999,7 +33002,7 @@
         <v>192</v>
       </c>
       <c r="P154" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33205,7 +33208,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -34029,7 +34032,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34110,7 +34113,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ159">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR159">
         <v>1.56</v>
@@ -34441,7 +34444,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34647,7 +34650,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34853,7 +34856,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35265,7 +35268,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35471,7 +35474,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35677,7 +35680,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35883,7 +35886,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -35961,7 +35964,7 @@
         <v>1</v>
       </c>
       <c r="AP168">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ168">
         <v>1.09</v>
@@ -36501,7 +36504,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36707,7 +36710,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36788,7 +36791,7 @@
         <v>1</v>
       </c>
       <c r="AQ172">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR172">
         <v>1.46</v>
@@ -36913,7 +36916,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37119,7 +37122,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37531,7 +37534,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -38149,7 +38152,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38355,7 +38358,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38561,7 +38564,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38639,7 +38642,7 @@
         <v>2.22</v>
       </c>
       <c r="AP181">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ181">
         <v>2.25</v>
@@ -38973,7 +38976,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39797,7 +39800,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40209,7 +40212,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40621,7 +40624,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41114,7 +41117,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ193">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR193">
         <v>1.41</v>
@@ -41239,7 +41242,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41857,7 +41860,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42269,7 +42272,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42475,7 +42478,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42681,7 +42684,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -43093,7 +43096,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43377,7 +43380,7 @@
         <v>1.2</v>
       </c>
       <c r="AP204">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ204">
         <v>1.17</v>
@@ -43505,7 +43508,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43917,7 +43920,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44123,7 +44126,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44741,7 +44744,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45359,7 +45362,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45565,7 +45568,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45771,7 +45774,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -45852,7 +45855,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ216">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR216">
         <v>1.3</v>
@@ -45977,7 +45980,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46183,7 +46186,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46595,7 +46598,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46801,7 +46804,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47213,7 +47216,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47625,7 +47628,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47831,7 +47834,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -47909,7 +47912,7 @@
         <v>1.4</v>
       </c>
       <c r="AP226">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ226">
         <v>1.27</v>
@@ -48118,7 +48121,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ227">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AR227">
         <v>1.73</v>
@@ -48243,7 +48246,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48449,7 +48452,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48606,6 +48609,212 @@
       </c>
       <c r="BP229">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="230" spans="1:68">
+      <c r="A230" s="1">
+        <v>229</v>
+      </c>
+      <c r="B230">
+        <v>7492281</v>
+      </c>
+      <c r="C230" t="s">
+        <v>68</v>
+      </c>
+      <c r="D230" t="s">
+        <v>69</v>
+      </c>
+      <c r="E230" s="2">
+        <v>45694.69791666666</v>
+      </c>
+      <c r="F230">
+        <v>14</v>
+      </c>
+      <c r="G230" t="s">
+        <v>83</v>
+      </c>
+      <c r="H230" t="s">
+        <v>82</v>
+      </c>
+      <c r="I230">
+        <v>0</v>
+      </c>
+      <c r="J230">
+        <v>0</v>
+      </c>
+      <c r="K230">
+        <v>0</v>
+      </c>
+      <c r="L230">
+        <v>3</v>
+      </c>
+      <c r="M230">
+        <v>0</v>
+      </c>
+      <c r="N230">
+        <v>3</v>
+      </c>
+      <c r="O230" t="s">
+        <v>238</v>
+      </c>
+      <c r="P230" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q230">
+        <v>4</v>
+      </c>
+      <c r="R230">
+        <v>2.25</v>
+      </c>
+      <c r="S230">
+        <v>2.63</v>
+      </c>
+      <c r="T230">
+        <v>1.36</v>
+      </c>
+      <c r="U230">
+        <v>3</v>
+      </c>
+      <c r="V230">
+        <v>2.63</v>
+      </c>
+      <c r="W230">
+        <v>1.44</v>
+      </c>
+      <c r="X230">
+        <v>7</v>
+      </c>
+      <c r="Y230">
+        <v>1.1</v>
+      </c>
+      <c r="Z230">
+        <v>3.5</v>
+      </c>
+      <c r="AA230">
+        <v>3.6</v>
+      </c>
+      <c r="AB230">
+        <v>2</v>
+      </c>
+      <c r="AC230">
+        <v>1.04</v>
+      </c>
+      <c r="AD230">
+        <v>13</v>
+      </c>
+      <c r="AE230">
+        <v>1.26</v>
+      </c>
+      <c r="AF230">
+        <v>4</v>
+      </c>
+      <c r="AG230">
+        <v>1.65</v>
+      </c>
+      <c r="AH230">
+        <v>2.15</v>
+      </c>
+      <c r="AI230">
+        <v>1.67</v>
+      </c>
+      <c r="AJ230">
+        <v>2.1</v>
+      </c>
+      <c r="AK230">
+        <v>1.83</v>
+      </c>
+      <c r="AL230">
+        <v>1.25</v>
+      </c>
+      <c r="AM230">
+        <v>1.3</v>
+      </c>
+      <c r="AN230">
+        <v>1.91</v>
+      </c>
+      <c r="AO230">
+        <v>2.45</v>
+      </c>
+      <c r="AP230">
+        <v>2</v>
+      </c>
+      <c r="AQ230">
+        <v>2.25</v>
+      </c>
+      <c r="AR230">
+        <v>1.55</v>
+      </c>
+      <c r="AS230">
+        <v>1.63</v>
+      </c>
+      <c r="AT230">
+        <v>3.18</v>
+      </c>
+      <c r="AU230">
+        <v>-1</v>
+      </c>
+      <c r="AV230">
+        <v>-1</v>
+      </c>
+      <c r="AW230">
+        <v>-1</v>
+      </c>
+      <c r="AX230">
+        <v>-1</v>
+      </c>
+      <c r="AY230">
+        <v>-1</v>
+      </c>
+      <c r="AZ230">
+        <v>-1</v>
+      </c>
+      <c r="BA230">
+        <v>1</v>
+      </c>
+      <c r="BB230">
+        <v>8</v>
+      </c>
+      <c r="BC230">
+        <v>9</v>
+      </c>
+      <c r="BD230">
+        <v>2.2</v>
+      </c>
+      <c r="BE230">
+        <v>6.1</v>
+      </c>
+      <c r="BF230">
+        <v>1.84</v>
+      </c>
+      <c r="BG230">
+        <v>1.46</v>
+      </c>
+      <c r="BH230">
+        <v>2.5</v>
+      </c>
+      <c r="BI230">
+        <v>1.77</v>
+      </c>
+      <c r="BJ230">
+        <v>1.92</v>
+      </c>
+      <c r="BK230">
+        <v>2.25</v>
+      </c>
+      <c r="BL230">
+        <v>1.55</v>
+      </c>
+      <c r="BM230">
+        <v>2.9</v>
+      </c>
+      <c r="BN230">
+        <v>1.34</v>
+      </c>
+      <c r="BO230">
+        <v>3.9</v>
+      </c>
+      <c r="BP230">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="354">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1074,6 +1074,9 @@
   <si>
     <t>['41', '64']</t>
   </si>
+  <si>
+    <t>['34', '89']</t>
+  </si>
 </sst>
 </file>
 
@@ -1434,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP230"/>
+  <dimension ref="A1:BP231"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -5685,7 +5688,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ21">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR21">
         <v>1.14</v>
@@ -7948,7 +7951,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ32">
         <v>1.55</v>
@@ -8157,7 +8160,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ33">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR33">
         <v>0.96</v>
@@ -12483,7 +12486,7 @@
         <v>1</v>
       </c>
       <c r="AQ54">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR54">
         <v>1.48</v>
@@ -13098,7 +13101,7 @@
         <v>1.5</v>
       </c>
       <c r="AP57">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ57">
         <v>1.08</v>
@@ -16188,7 +16191,7 @@
         <v>0.67</v>
       </c>
       <c r="AP72">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ72">
         <v>0.73</v>
@@ -19693,7 +19696,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ89">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR89">
         <v>1.46</v>
@@ -21750,7 +21753,7 @@
         <v>0.75</v>
       </c>
       <c r="AP99">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ99">
         <v>1.75</v>
@@ -22371,7 +22374,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ102">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR102">
         <v>1.16</v>
@@ -26491,7 +26494,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ122">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR122">
         <v>1.69</v>
@@ -27106,7 +27109,7 @@
         <v>1.83</v>
       </c>
       <c r="AP125">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ125">
         <v>1.64</v>
@@ -28548,7 +28551,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ132">
         <v>0.64</v>
@@ -29787,7 +29790,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ138">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR138">
         <v>1.39</v>
@@ -33698,7 +33701,7 @@
         <v>0.57</v>
       </c>
       <c r="AP157">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ157">
         <v>0.82</v>
@@ -35761,7 +35764,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ167">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR167">
         <v>1.14</v>
@@ -38024,7 +38027,7 @@
         <v>0.5</v>
       </c>
       <c r="AP178">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ178">
         <v>0.83</v>
@@ -40499,7 +40502,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ190">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR190">
         <v>1.04</v>
@@ -41938,7 +41941,7 @@
         <v>1.38</v>
       </c>
       <c r="AP197">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ197">
         <v>1.4</v>
@@ -42147,7 +42150,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ198">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR198">
         <v>1.78</v>
@@ -44410,7 +44413,7 @@
         <v>1.2</v>
       </c>
       <c r="AP209">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ209">
         <v>1.09</v>
@@ -44822,7 +44825,7 @@
         <v>1.91</v>
       </c>
       <c r="AP211">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ211">
         <v>2</v>
@@ -45031,7 +45034,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ212">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR212">
         <v>1.61</v>
@@ -48815,6 +48818,212 @@
       </c>
       <c r="BP230">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="231" spans="1:68">
+      <c r="A231" s="1">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>7492379</v>
+      </c>
+      <c r="C231" t="s">
+        <v>68</v>
+      </c>
+      <c r="D231" t="s">
+        <v>69</v>
+      </c>
+      <c r="E231" s="2">
+        <v>45695.69791666666</v>
+      </c>
+      <c r="F231">
+        <v>24</v>
+      </c>
+      <c r="G231" t="s">
+        <v>88</v>
+      </c>
+      <c r="H231" t="s">
+        <v>79</v>
+      </c>
+      <c r="I231">
+        <v>1</v>
+      </c>
+      <c r="J231">
+        <v>1</v>
+      </c>
+      <c r="K231">
+        <v>2</v>
+      </c>
+      <c r="L231">
+        <v>1</v>
+      </c>
+      <c r="M231">
+        <v>2</v>
+      </c>
+      <c r="N231">
+        <v>3</v>
+      </c>
+      <c r="O231" t="s">
+        <v>212</v>
+      </c>
+      <c r="P231" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q231">
+        <v>4.33</v>
+      </c>
+      <c r="R231">
+        <v>2.1</v>
+      </c>
+      <c r="S231">
+        <v>2.75</v>
+      </c>
+      <c r="T231">
+        <v>1.44</v>
+      </c>
+      <c r="U231">
+        <v>2.63</v>
+      </c>
+      <c r="V231">
+        <v>3.25</v>
+      </c>
+      <c r="W231">
+        <v>1.33</v>
+      </c>
+      <c r="X231">
+        <v>9</v>
+      </c>
+      <c r="Y231">
+        <v>1.07</v>
+      </c>
+      <c r="Z231">
+        <v>3.57</v>
+      </c>
+      <c r="AA231">
+        <v>3.37</v>
+      </c>
+      <c r="AB231">
+        <v>2.18</v>
+      </c>
+      <c r="AC231">
+        <v>1.07</v>
+      </c>
+      <c r="AD231">
+        <v>9.5</v>
+      </c>
+      <c r="AE231">
+        <v>1.36</v>
+      </c>
+      <c r="AF231">
+        <v>3.2</v>
+      </c>
+      <c r="AG231">
+        <v>2.03</v>
+      </c>
+      <c r="AH231">
+        <v>1.79</v>
+      </c>
+      <c r="AI231">
+        <v>1.8</v>
+      </c>
+      <c r="AJ231">
+        <v>1.95</v>
+      </c>
+      <c r="AK231">
+        <v>1.75</v>
+      </c>
+      <c r="AL231">
+        <v>1.28</v>
+      </c>
+      <c r="AM231">
+        <v>1.3</v>
+      </c>
+      <c r="AN231">
+        <v>1.36</v>
+      </c>
+      <c r="AO231">
+        <v>1.64</v>
+      </c>
+      <c r="AP231">
+        <v>1.25</v>
+      </c>
+      <c r="AQ231">
+        <v>1.75</v>
+      </c>
+      <c r="AR231">
+        <v>1.56</v>
+      </c>
+      <c r="AS231">
+        <v>1.3</v>
+      </c>
+      <c r="AT231">
+        <v>2.86</v>
+      </c>
+      <c r="AU231">
+        <v>7</v>
+      </c>
+      <c r="AV231">
+        <v>4</v>
+      </c>
+      <c r="AW231">
+        <v>10</v>
+      </c>
+      <c r="AX231">
+        <v>5</v>
+      </c>
+      <c r="AY231">
+        <v>21</v>
+      </c>
+      <c r="AZ231">
+        <v>11</v>
+      </c>
+      <c r="BA231">
+        <v>9</v>
+      </c>
+      <c r="BB231">
+        <v>1</v>
+      </c>
+      <c r="BC231">
+        <v>10</v>
+      </c>
+      <c r="BD231">
+        <v>2.15</v>
+      </c>
+      <c r="BE231">
+        <v>6.4</v>
+      </c>
+      <c r="BF231">
+        <v>1.86</v>
+      </c>
+      <c r="BG231">
+        <v>1.33</v>
+      </c>
+      <c r="BH231">
+        <v>2.95</v>
+      </c>
+      <c r="BI231">
+        <v>1.56</v>
+      </c>
+      <c r="BJ231">
+        <v>2.23</v>
+      </c>
+      <c r="BK231">
+        <v>1.92</v>
+      </c>
+      <c r="BL231">
+        <v>1.77</v>
+      </c>
+      <c r="BM231">
+        <v>2.4</v>
+      </c>
+      <c r="BN231">
+        <v>1.49</v>
+      </c>
+      <c r="BO231">
+        <v>3.15</v>
+      </c>
+      <c r="BP231">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -48966,16 +48966,16 @@
         <v>4</v>
       </c>
       <c r="AW231">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AX231">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY231">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ231">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA231">
         <v>9</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="357">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -733,6 +733,9 @@
     <t>['59', '68', '89']</t>
   </si>
   <si>
+    <t>['45+2']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1076,6 +1079,12 @@
   </si>
   <si>
     <t>['34', '89']</t>
+  </si>
+  <si>
+    <t>['21', '25', '37', '44', '56']</t>
+  </si>
+  <si>
+    <t>['68', '76']</t>
   </si>
 </sst>
 </file>
@@ -1437,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP231"/>
+  <dimension ref="A1:BP234"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1693,7 +1702,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2183,7 +2192,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ4">
         <v>0.64</v>
@@ -2311,7 +2320,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2517,7 +2526,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2801,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ7">
         <v>2.25</v>
@@ -3135,7 +3144,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3341,7 +3350,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3422,7 +3431,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ10">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3753,7 +3762,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q12">
         <v>3.75</v>
@@ -3959,7 +3968,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4040,7 +4049,7 @@
         <v>1</v>
       </c>
       <c r="AQ13">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR13">
         <v>1.45</v>
@@ -4165,7 +4174,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4246,7 +4255,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ14">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4861,10 +4870,10 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ17">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5195,7 +5204,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5607,7 +5616,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5685,7 +5694,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ21">
         <v>1.75</v>
@@ -5813,7 +5822,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6100,7 +6109,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ23">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR23">
         <v>1.3</v>
@@ -6225,7 +6234,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6637,7 +6646,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6718,7 +6727,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ26">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR26">
         <v>1.67</v>
@@ -6843,7 +6852,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7049,7 +7058,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7255,7 +7264,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7873,7 +7882,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8157,7 +8166,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ33">
         <v>1.75</v>
@@ -8491,7 +8500,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q35">
         <v>4</v>
@@ -8697,7 +8706,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -8981,7 +8990,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ37">
         <v>0.83</v>
@@ -9109,7 +9118,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9315,7 +9324,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9521,7 +9530,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9727,7 +9736,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9933,7 +9942,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10139,7 +10148,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10217,7 +10226,7 @@
         <v>2</v>
       </c>
       <c r="AP43">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ43">
         <v>1.17</v>
@@ -10426,7 +10435,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ44">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR44">
         <v>1.37</v>
@@ -10757,7 +10766,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10963,7 +10972,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11169,7 +11178,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11581,7 +11590,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11662,7 +11671,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ50">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR50">
         <v>1.2</v>
@@ -11787,7 +11796,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12199,7 +12208,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12405,7 +12414,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12611,7 +12620,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12692,7 +12701,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ55">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR55">
         <v>1.78</v>
@@ -12817,7 +12826,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -12895,7 +12904,7 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ56">
         <v>1.75</v>
@@ -13023,7 +13032,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13513,7 +13522,7 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ59">
         <v>1.64</v>
@@ -13847,7 +13856,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14337,7 +14346,7 @@
         <v>0.25</v>
       </c>
       <c r="AP63">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ63">
         <v>0.33</v>
@@ -14671,7 +14680,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14752,7 +14761,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ65">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR65">
         <v>1.65</v>
@@ -14877,7 +14886,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15083,7 +15092,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15289,7 +15298,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q68">
         <v>2.2</v>
@@ -15701,7 +15710,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -15988,7 +15997,7 @@
         <v>2</v>
       </c>
       <c r="AQ71">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR71">
         <v>1.68</v>
@@ -16319,7 +16328,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16937,7 +16946,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17015,7 +17024,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ76">
         <v>2.25</v>
@@ -17143,7 +17152,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17349,7 +17358,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17430,7 +17439,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ78">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR78">
         <v>1.31</v>
@@ -17555,7 +17564,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17967,7 +17976,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18045,7 +18054,7 @@
         <v>0.67</v>
       </c>
       <c r="AP81">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ81">
         <v>0.64</v>
@@ -18457,7 +18466,7 @@
         <v>0.8</v>
       </c>
       <c r="AP83">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ83">
         <v>0.58</v>
@@ -18791,7 +18800,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19284,7 +19293,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ87">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR87">
         <v>1.49</v>
@@ -19409,7 +19418,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19615,7 +19624,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19821,7 +19830,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20027,7 +20036,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20439,7 +20448,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20645,7 +20654,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20851,7 +20860,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -20929,7 +20938,7 @@
         <v>2</v>
       </c>
       <c r="AP95">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ95">
         <v>2.25</v>
@@ -21263,7 +21272,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21469,7 +21478,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21675,7 +21684,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22293,7 +22302,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22580,7 +22589,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ103">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR103">
         <v>0.9399999999999999</v>
@@ -22705,7 +22714,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22786,7 +22795,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ104">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR104">
         <v>1.61</v>
@@ -22911,7 +22920,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -22989,7 +22998,7 @@
         <v>1.6</v>
       </c>
       <c r="AP105">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ105">
         <v>1.64</v>
@@ -23117,7 +23126,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23195,7 +23204,7 @@
         <v>0.8</v>
       </c>
       <c r="AP106">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ106">
         <v>0.82</v>
@@ -23607,7 +23616,7 @@
         <v>0.67</v>
       </c>
       <c r="AP108">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ108">
         <v>0.58</v>
@@ -23816,7 +23825,7 @@
         <v>1</v>
       </c>
       <c r="AQ109">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR109">
         <v>1.36</v>
@@ -23941,7 +23950,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24147,7 +24156,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24353,7 +24362,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24559,7 +24568,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24765,7 +24774,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -24846,7 +24855,7 @@
         <v>1</v>
       </c>
       <c r="AQ114">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR114">
         <v>1.3</v>
@@ -25177,7 +25186,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25383,7 +25392,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25589,7 +25598,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -26207,7 +26216,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26285,7 +26294,7 @@
         <v>2.2</v>
       </c>
       <c r="AP121">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ121">
         <v>2.25</v>
@@ -26619,7 +26628,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26700,7 +26709,7 @@
         <v>1</v>
       </c>
       <c r="AQ123">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR123">
         <v>1.29</v>
@@ -26825,7 +26834,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27031,7 +27040,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27237,7 +27246,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27315,7 +27324,7 @@
         <v>1</v>
       </c>
       <c r="AP126">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ126">
         <v>0.64</v>
@@ -27855,7 +27864,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -27933,7 +27942,7 @@
         <v>0.67</v>
       </c>
       <c r="AP129">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ129">
         <v>1.09</v>
@@ -29091,7 +29100,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29172,7 +29181,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ135">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR135">
         <v>1.11</v>
@@ -29297,7 +29306,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29375,7 +29384,7 @@
         <v>1.83</v>
       </c>
       <c r="AP136">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ136">
         <v>2.25</v>
@@ -29709,7 +29718,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29915,7 +29924,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -29996,7 +30005,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ139">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR139">
         <v>1.59</v>
@@ -30408,7 +30417,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ141">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR141">
         <v>1.73</v>
@@ -30739,7 +30748,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30945,7 +30954,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31357,7 +31366,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31435,7 +31444,7 @@
         <v>1.29</v>
       </c>
       <c r="AP146">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ146">
         <v>1.08</v>
@@ -31563,7 +31572,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31975,7 +31984,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32259,7 +32268,7 @@
         <v>1</v>
       </c>
       <c r="AP150">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ150">
         <v>1.17</v>
@@ -32387,7 +32396,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32468,7 +32477,7 @@
         <v>1</v>
       </c>
       <c r="AQ151">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR151">
         <v>1.42</v>
@@ -32593,7 +32602,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32799,7 +32808,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -33005,7 +33014,7 @@
         <v>192</v>
       </c>
       <c r="P154" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33211,7 +33220,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -33910,7 +33919,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ158">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR158">
         <v>1.52</v>
@@ -34035,7 +34044,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34319,10 +34328,10 @@
         <v>1.14</v>
       </c>
       <c r="AP160">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ160">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR160">
         <v>1.12</v>
@@ -34447,7 +34456,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34525,7 +34534,7 @@
         <v>1.5</v>
       </c>
       <c r="AP161">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ161">
         <v>1.55</v>
@@ -34653,7 +34662,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34859,7 +34868,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35271,7 +35280,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35477,7 +35486,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35683,7 +35692,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35889,7 +35898,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36507,7 +36516,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36585,10 +36594,10 @@
         <v>1.43</v>
       </c>
       <c r="AP171">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ171">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR171">
         <v>0.88</v>
@@ -36713,7 +36722,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36919,7 +36928,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37000,7 +37009,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ173">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR173">
         <v>1.48</v>
@@ -37125,7 +37134,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37537,7 +37546,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -38155,7 +38164,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38361,7 +38370,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38567,7 +38576,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38851,7 +38860,7 @@
         <v>1.22</v>
       </c>
       <c r="AP182">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ182">
         <v>1.09</v>
@@ -38979,7 +38988,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39266,7 +39275,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ184">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR184">
         <v>1.31</v>
@@ -39469,7 +39478,7 @@
         <v>0.88</v>
       </c>
       <c r="AP185">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ185">
         <v>0.73</v>
@@ -39803,7 +39812,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40090,7 +40099,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ188">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR188">
         <v>1.04</v>
@@ -40215,7 +40224,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40293,7 +40302,7 @@
         <v>0.44</v>
       </c>
       <c r="AP189">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ189">
         <v>0.83</v>
@@ -40499,7 +40508,7 @@
         <v>2</v>
       </c>
       <c r="AP190">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ190">
         <v>1.75</v>
@@ -40627,7 +40636,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41245,7 +41254,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41863,7 +41872,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -41944,7 +41953,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ197">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR197">
         <v>1.54</v>
@@ -42275,7 +42284,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42481,7 +42490,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42562,7 +42571,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ200">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR200">
         <v>1.55</v>
@@ -42687,7 +42696,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -42974,7 +42983,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ202">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR202">
         <v>1.44</v>
@@ -43099,7 +43108,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43511,7 +43520,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43923,7 +43932,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44001,7 +44010,7 @@
         <v>1.5</v>
       </c>
       <c r="AP207">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ207">
         <v>1.75</v>
@@ -44129,7 +44138,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44619,7 +44628,7 @@
         <v>0.9</v>
       </c>
       <c r="AP210">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ210">
         <v>0.82</v>
@@ -44747,7 +44756,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -44828,7 +44837,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ211">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR211">
         <v>1.53</v>
@@ -45237,7 +45246,7 @@
         <v>1.6</v>
       </c>
       <c r="AP213">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ213">
         <v>1.55</v>
@@ -45365,7 +45374,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45571,7 +45580,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45777,7 +45786,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -45983,7 +45992,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46189,7 +46198,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46601,7 +46610,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46807,7 +46816,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47219,7 +47228,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47631,7 +47640,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47837,7 +47846,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -47918,7 +47927,7 @@
         <v>2</v>
       </c>
       <c r="AQ226">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR226">
         <v>1.59</v>
@@ -48249,7 +48258,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48455,7 +48464,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48754,22 +48763,22 @@
         <v>3.18</v>
       </c>
       <c r="AU230">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AV230">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW230">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AX230">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AY230">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AZ230">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BA230">
         <v>1</v>
@@ -48867,7 +48876,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49024,6 +49033,624 @@
       </c>
       <c r="BP231">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="232" spans="1:68">
+      <c r="A232" s="1">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>7492381</v>
+      </c>
+      <c r="C232" t="s">
+        <v>68</v>
+      </c>
+      <c r="D232" t="s">
+        <v>69</v>
+      </c>
+      <c r="E232" s="2">
+        <v>45696.45833333334</v>
+      </c>
+      <c r="F232">
+        <v>24</v>
+      </c>
+      <c r="G232" t="s">
+        <v>75</v>
+      </c>
+      <c r="H232" t="s">
+        <v>89</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
+        <v>4</v>
+      </c>
+      <c r="K232">
+        <v>4</v>
+      </c>
+      <c r="L232">
+        <v>0</v>
+      </c>
+      <c r="M232">
+        <v>5</v>
+      </c>
+      <c r="N232">
+        <v>5</v>
+      </c>
+      <c r="O232" t="s">
+        <v>92</v>
+      </c>
+      <c r="P232" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q232">
+        <v>6</v>
+      </c>
+      <c r="R232">
+        <v>2.38</v>
+      </c>
+      <c r="S232">
+        <v>2.05</v>
+      </c>
+      <c r="T232">
+        <v>1.33</v>
+      </c>
+      <c r="U232">
+        <v>3.25</v>
+      </c>
+      <c r="V232">
+        <v>2.63</v>
+      </c>
+      <c r="W232">
+        <v>1.44</v>
+      </c>
+      <c r="X232">
+        <v>6.5</v>
+      </c>
+      <c r="Y232">
+        <v>1.11</v>
+      </c>
+      <c r="Z232">
+        <v>6</v>
+      </c>
+      <c r="AA232">
+        <v>4.4</v>
+      </c>
+      <c r="AB232">
+        <v>1.55</v>
+      </c>
+      <c r="AC232">
+        <v>1.03</v>
+      </c>
+      <c r="AD232">
+        <v>15</v>
+      </c>
+      <c r="AE232">
+        <v>1.24</v>
+      </c>
+      <c r="AF232">
+        <v>4.2</v>
+      </c>
+      <c r="AG232">
+        <v>1.72</v>
+      </c>
+      <c r="AH232">
+        <v>2.12</v>
+      </c>
+      <c r="AI232">
+        <v>1.8</v>
+      </c>
+      <c r="AJ232">
+        <v>1.95</v>
+      </c>
+      <c r="AK232">
+        <v>2.4</v>
+      </c>
+      <c r="AL232">
+        <v>1.21</v>
+      </c>
+      <c r="AM232">
+        <v>1.14</v>
+      </c>
+      <c r="AN232">
+        <v>0.91</v>
+      </c>
+      <c r="AO232">
+        <v>2</v>
+      </c>
+      <c r="AP232">
+        <v>0.83</v>
+      </c>
+      <c r="AQ232">
+        <v>2.08</v>
+      </c>
+      <c r="AR232">
+        <v>1.18</v>
+      </c>
+      <c r="AS232">
+        <v>1.57</v>
+      </c>
+      <c r="AT232">
+        <v>2.75</v>
+      </c>
+      <c r="AU232">
+        <v>8</v>
+      </c>
+      <c r="AV232">
+        <v>8</v>
+      </c>
+      <c r="AW232">
+        <v>11</v>
+      </c>
+      <c r="AX232">
+        <v>10</v>
+      </c>
+      <c r="AY232">
+        <v>21</v>
+      </c>
+      <c r="AZ232">
+        <v>19</v>
+      </c>
+      <c r="BA232">
+        <v>7</v>
+      </c>
+      <c r="BB232">
+        <v>2</v>
+      </c>
+      <c r="BC232">
+        <v>9</v>
+      </c>
+      <c r="BD232">
+        <v>4.2</v>
+      </c>
+      <c r="BE232">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BF232">
+        <v>1.34</v>
+      </c>
+      <c r="BG232">
+        <v>1.31</v>
+      </c>
+      <c r="BH232">
+        <v>2.92</v>
+      </c>
+      <c r="BI232">
+        <v>1.59</v>
+      </c>
+      <c r="BJ232">
+        <v>2.16</v>
+      </c>
+      <c r="BK232">
+        <v>2.02</v>
+      </c>
+      <c r="BL232">
+        <v>1.71</v>
+      </c>
+      <c r="BM232">
+        <v>2.64</v>
+      </c>
+      <c r="BN232">
+        <v>1.4</v>
+      </c>
+      <c r="BO232">
+        <v>3.58</v>
+      </c>
+      <c r="BP232">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="233" spans="1:68">
+      <c r="A233" s="1">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>7492380</v>
+      </c>
+      <c r="C233" t="s">
+        <v>68</v>
+      </c>
+      <c r="D233" t="s">
+        <v>69</v>
+      </c>
+      <c r="E233" s="2">
+        <v>45696.58333333334</v>
+      </c>
+      <c r="F233">
+        <v>24</v>
+      </c>
+      <c r="G233" t="s">
+        <v>72</v>
+      </c>
+      <c r="H233" t="s">
+        <v>73</v>
+      </c>
+      <c r="I233">
+        <v>0</v>
+      </c>
+      <c r="J233">
+        <v>0</v>
+      </c>
+      <c r="K233">
+        <v>0</v>
+      </c>
+      <c r="L233">
+        <v>0</v>
+      </c>
+      <c r="M233">
+        <v>2</v>
+      </c>
+      <c r="N233">
+        <v>2</v>
+      </c>
+      <c r="O233" t="s">
+        <v>92</v>
+      </c>
+      <c r="P233" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q233">
+        <v>5.5</v>
+      </c>
+      <c r="R233">
+        <v>2.2</v>
+      </c>
+      <c r="S233">
+        <v>2.3</v>
+      </c>
+      <c r="T233">
+        <v>1.4</v>
+      </c>
+      <c r="U233">
+        <v>2.75</v>
+      </c>
+      <c r="V233">
+        <v>2.75</v>
+      </c>
+      <c r="W233">
+        <v>1.4</v>
+      </c>
+      <c r="X233">
+        <v>8</v>
+      </c>
+      <c r="Y233">
+        <v>1.08</v>
+      </c>
+      <c r="Z233">
+        <v>4.9</v>
+      </c>
+      <c r="AA233">
+        <v>3.85</v>
+      </c>
+      <c r="AB233">
+        <v>1.75</v>
+      </c>
+      <c r="AC233">
+        <v>1.07</v>
+      </c>
+      <c r="AD233">
+        <v>10</v>
+      </c>
+      <c r="AE233">
+        <v>1.3</v>
+      </c>
+      <c r="AF233">
+        <v>3.5</v>
+      </c>
+      <c r="AG233">
+        <v>1.92</v>
+      </c>
+      <c r="AH233">
+        <v>1.89</v>
+      </c>
+      <c r="AI233">
+        <v>1.91</v>
+      </c>
+      <c r="AJ233">
+        <v>1.91</v>
+      </c>
+      <c r="AK233">
+        <v>2.1</v>
+      </c>
+      <c r="AL233">
+        <v>1.26</v>
+      </c>
+      <c r="AM233">
+        <v>1.18</v>
+      </c>
+      <c r="AN233">
+        <v>0.73</v>
+      </c>
+      <c r="AO233">
+        <v>1.4</v>
+      </c>
+      <c r="AP233">
+        <v>0.67</v>
+      </c>
+      <c r="AQ233">
+        <v>1.55</v>
+      </c>
+      <c r="AR233">
+        <v>0.99</v>
+      </c>
+      <c r="AS233">
+        <v>1.44</v>
+      </c>
+      <c r="AT233">
+        <v>2.43</v>
+      </c>
+      <c r="AU233">
+        <v>0</v>
+      </c>
+      <c r="AV233">
+        <v>6</v>
+      </c>
+      <c r="AW233">
+        <v>9</v>
+      </c>
+      <c r="AX233">
+        <v>11</v>
+      </c>
+      <c r="AY233">
+        <v>10</v>
+      </c>
+      <c r="AZ233">
+        <v>17</v>
+      </c>
+      <c r="BA233">
+        <v>2</v>
+      </c>
+      <c r="BB233">
+        <v>6</v>
+      </c>
+      <c r="BC233">
+        <v>8</v>
+      </c>
+      <c r="BD233">
+        <v>2.92</v>
+      </c>
+      <c r="BE233">
+        <v>8.9</v>
+      </c>
+      <c r="BF233">
+        <v>1.58</v>
+      </c>
+      <c r="BG233">
+        <v>1.22</v>
+      </c>
+      <c r="BH233">
+        <v>3.5</v>
+      </c>
+      <c r="BI233">
+        <v>1.44</v>
+      </c>
+      <c r="BJ233">
+        <v>2.5</v>
+      </c>
+      <c r="BK233">
+        <v>1.8</v>
+      </c>
+      <c r="BL233">
+        <v>1.9</v>
+      </c>
+      <c r="BM233">
+        <v>2.28</v>
+      </c>
+      <c r="BN233">
+        <v>1.53</v>
+      </c>
+      <c r="BO233">
+        <v>3.04</v>
+      </c>
+      <c r="BP233">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="234" spans="1:68">
+      <c r="A234" s="1">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>7492386</v>
+      </c>
+      <c r="C234" t="s">
+        <v>68</v>
+      </c>
+      <c r="D234" t="s">
+        <v>69</v>
+      </c>
+      <c r="E234" s="2">
+        <v>45696.69791666666</v>
+      </c>
+      <c r="F234">
+        <v>24</v>
+      </c>
+      <c r="G234" t="s">
+        <v>84</v>
+      </c>
+      <c r="H234" t="s">
+        <v>70</v>
+      </c>
+      <c r="I234">
+        <v>1</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+      <c r="K234">
+        <v>1</v>
+      </c>
+      <c r="L234">
+        <v>1</v>
+      </c>
+      <c r="M234">
+        <v>1</v>
+      </c>
+      <c r="N234">
+        <v>2</v>
+      </c>
+      <c r="O234" t="s">
+        <v>239</v>
+      </c>
+      <c r="P234" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q234">
+        <v>3</v>
+      </c>
+      <c r="R234">
+        <v>1.91</v>
+      </c>
+      <c r="S234">
+        <v>4.33</v>
+      </c>
+      <c r="T234">
+        <v>1.57</v>
+      </c>
+      <c r="U234">
+        <v>2.25</v>
+      </c>
+      <c r="V234">
+        <v>3.75</v>
+      </c>
+      <c r="W234">
+        <v>1.25</v>
+      </c>
+      <c r="X234">
+        <v>13</v>
+      </c>
+      <c r="Y234">
+        <v>1.04</v>
+      </c>
+      <c r="Z234">
+        <v>2.07</v>
+      </c>
+      <c r="AA234">
+        <v>3.18</v>
+      </c>
+      <c r="AB234">
+        <v>4.2</v>
+      </c>
+      <c r="AC234">
+        <v>1.12</v>
+      </c>
+      <c r="AD234">
+        <v>7</v>
+      </c>
+      <c r="AE234">
+        <v>1.51</v>
+      </c>
+      <c r="AF234">
+        <v>2.55</v>
+      </c>
+      <c r="AG234">
+        <v>2.4</v>
+      </c>
+      <c r="AH234">
+        <v>1.5</v>
+      </c>
+      <c r="AI234">
+        <v>2.1</v>
+      </c>
+      <c r="AJ234">
+        <v>1.67</v>
+      </c>
+      <c r="AK234">
+        <v>1.26</v>
+      </c>
+      <c r="AL234">
+        <v>1.37</v>
+      </c>
+      <c r="AM234">
+        <v>1.66</v>
+      </c>
+      <c r="AN234">
+        <v>1.18</v>
+      </c>
+      <c r="AO234">
+        <v>1.27</v>
+      </c>
+      <c r="AP234">
+        <v>1.17</v>
+      </c>
+      <c r="AQ234">
+        <v>1.25</v>
+      </c>
+      <c r="AR234">
+        <v>1.14</v>
+      </c>
+      <c r="AS234">
+        <v>1.04</v>
+      </c>
+      <c r="AT234">
+        <v>2.18</v>
+      </c>
+      <c r="AU234">
+        <v>4</v>
+      </c>
+      <c r="AV234">
+        <v>3</v>
+      </c>
+      <c r="AW234">
+        <v>7</v>
+      </c>
+      <c r="AX234">
+        <v>4</v>
+      </c>
+      <c r="AY234">
+        <v>13</v>
+      </c>
+      <c r="AZ234">
+        <v>8</v>
+      </c>
+      <c r="BA234">
+        <v>4</v>
+      </c>
+      <c r="BB234">
+        <v>2</v>
+      </c>
+      <c r="BC234">
+        <v>6</v>
+      </c>
+      <c r="BD234">
+        <v>1.64</v>
+      </c>
+      <c r="BE234">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF234">
+        <v>2.76</v>
+      </c>
+      <c r="BG234">
+        <v>1.28</v>
+      </c>
+      <c r="BH234">
+        <v>3.05</v>
+      </c>
+      <c r="BI234">
+        <v>1.55</v>
+      </c>
+      <c r="BJ234">
+        <v>2.23</v>
+      </c>
+      <c r="BK234">
+        <v>1.96</v>
+      </c>
+      <c r="BL234">
+        <v>1.75</v>
+      </c>
+      <c r="BM234">
+        <v>2.57</v>
+      </c>
+      <c r="BN234">
+        <v>1.42</v>
+      </c>
+      <c r="BO234">
+        <v>3.48</v>
+      </c>
+      <c r="BP234">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="359">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -736,6 +736,15 @@
     <t>['45+2']</t>
   </si>
   <si>
+    <t>['31', '57', '63', '77', '88']</t>
+  </si>
+  <si>
+    <t>['57', '70']</t>
+  </si>
+  <si>
+    <t>['37']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -782,9 +791,6 @@
   </si>
   <si>
     <t>['76', '90+1']</t>
-  </si>
-  <si>
-    <t>['37']</t>
   </si>
   <si>
     <t>['15', '32']</t>
@@ -1446,7 +1452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP234"/>
+  <dimension ref="A1:BP239"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1702,7 +1708,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2195,7 +2201,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ4">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2320,7 +2326,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2526,7 +2532,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2607,7 +2613,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ6">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -3016,10 +3022,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ8">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3144,7 +3150,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3222,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ9">
         <v>0.33</v>
@@ -3350,7 +3356,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3428,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ10">
         <v>2.08</v>
@@ -3762,7 +3768,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q12">
         <v>3.75</v>
@@ -3968,7 +3974,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4174,7 +4180,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -5076,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ18">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5204,7 +5210,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5488,7 +5494,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ20">
         <v>0.58</v>
@@ -5616,7 +5622,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5822,7 +5828,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5900,7 +5906,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ22">
         <v>1.17</v>
@@ -6234,7 +6240,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6518,7 +6524,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ25">
         <v>0.82</v>
@@ -6646,7 +6652,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6724,7 +6730,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ26">
         <v>1.55</v>
@@ -6852,7 +6858,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -6930,10 +6936,10 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ27">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR27">
         <v>1.28</v>
@@ -7058,7 +7064,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7139,7 +7145,7 @@
         <v>2</v>
       </c>
       <c r="AQ28">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR28">
         <v>1.74</v>
@@ -7264,7 +7270,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7551,7 +7557,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ30">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR30">
         <v>1.66</v>
@@ -7882,7 +7888,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7963,7 +7969,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ32">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR32">
         <v>0</v>
@@ -8500,7 +8506,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="Q35">
         <v>4</v>
@@ -8581,7 +8587,7 @@
         <v>1</v>
       </c>
       <c r="AQ35">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR35">
         <v>1.23</v>
@@ -8706,7 +8712,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -9118,7 +9124,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9196,7 +9202,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ38">
         <v>2.25</v>
@@ -9324,7 +9330,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9530,7 +9536,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9611,7 +9617,7 @@
         <v>1</v>
       </c>
       <c r="AQ40">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR40">
         <v>1.32</v>
@@ -9736,7 +9742,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9814,7 +9820,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ41">
         <v>1.08</v>
@@ -9942,7 +9948,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10020,7 +10026,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ42">
         <v>1.08</v>
@@ -10148,7 +10154,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10432,7 +10438,7 @@
         <v>3</v>
       </c>
       <c r="AP44">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ44">
         <v>1.25</v>
@@ -10766,7 +10772,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10844,10 +10850,10 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ46">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR46">
         <v>1.54</v>
@@ -10972,7 +10978,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11178,7 +11184,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11259,7 +11265,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ48">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR48">
         <v>0.9399999999999999</v>
@@ -11465,7 +11471,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ49">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR49">
         <v>2.26</v>
@@ -11590,7 +11596,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11796,7 +11802,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12208,7 +12214,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12414,7 +12420,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12620,7 +12626,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12826,7 +12832,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13032,7 +13038,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13728,10 +13734,10 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ60">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR60">
         <v>1.84</v>
@@ -13856,7 +13862,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14140,7 +14146,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ62">
         <v>0.58</v>
@@ -14680,7 +14686,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14886,7 +14892,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15092,7 +15098,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15298,7 +15304,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q68">
         <v>2.2</v>
@@ -15376,7 +15382,7 @@
         <v>2.33</v>
       </c>
       <c r="AP68">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ68">
         <v>1.08</v>
@@ -15585,7 +15591,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ69">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR69">
         <v>1.35</v>
@@ -15710,7 +15716,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -15791,7 +15797,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ70">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR70">
         <v>0.9399999999999999</v>
@@ -16203,7 +16209,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ72">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR72">
         <v>1.87</v>
@@ -16328,7 +16334,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16409,7 +16415,7 @@
         <v>1</v>
       </c>
       <c r="AQ73">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR73">
         <v>1.29</v>
@@ -16615,7 +16621,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ74">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR74">
         <v>1.89</v>
@@ -16946,7 +16952,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17152,7 +17158,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17230,7 +17236,7 @@
         <v>0.67</v>
       </c>
       <c r="AP77">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ77">
         <v>1.64</v>
@@ -17358,7 +17364,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17436,7 +17442,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ78">
         <v>2.08</v>
@@ -17564,7 +17570,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17642,7 +17648,7 @@
         <v>1.75</v>
       </c>
       <c r="AP79">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ79">
         <v>1.17</v>
@@ -17976,7 +17982,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18057,7 +18063,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ81">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR81">
         <v>1.08</v>
@@ -18672,7 +18678,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ84">
         <v>0.83</v>
@@ -18800,7 +18806,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19290,7 +19296,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ87">
         <v>1.25</v>
@@ -19418,7 +19424,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19624,7 +19630,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19830,7 +19836,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -19911,7 +19917,7 @@
         <v>2</v>
       </c>
       <c r="AQ90">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR90">
         <v>1.56</v>
@@ -20036,7 +20042,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20114,10 +20120,10 @@
         <v>1.25</v>
       </c>
       <c r="AP91">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ91">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR91">
         <v>1.35</v>
@@ -20320,7 +20326,7 @@
         <v>0.75</v>
       </c>
       <c r="AP92">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ92">
         <v>1.08</v>
@@ -20448,7 +20454,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20654,7 +20660,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20732,10 +20738,10 @@
         <v>1</v>
       </c>
       <c r="AP94">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ94">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR94">
         <v>1.33</v>
@@ -20860,7 +20866,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -21147,7 +21153,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ96">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR96">
         <v>1.88</v>
@@ -21272,7 +21278,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21353,7 +21359,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ97">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR97">
         <v>1.44</v>
@@ -21478,7 +21484,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21684,7 +21690,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22302,7 +22308,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22714,7 +22720,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22792,7 +22798,7 @@
         <v>1.4</v>
       </c>
       <c r="AP104">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ104">
         <v>2.08</v>
@@ -22920,7 +22926,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23126,7 +23132,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23207,7 +23213,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ106">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR106">
         <v>1.19</v>
@@ -23950,7 +23956,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24028,7 +24034,7 @@
         <v>1</v>
       </c>
       <c r="AP110">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ110">
         <v>0.82</v>
@@ -24156,7 +24162,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24362,7 +24368,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24440,7 +24446,7 @@
         <v>1.6</v>
       </c>
       <c r="AP112">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ112">
         <v>1.08</v>
@@ -24568,7 +24574,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24646,10 +24652,10 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ113">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR113">
         <v>1.44</v>
@@ -24774,7 +24780,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -24852,7 +24858,7 @@
         <v>1.4</v>
       </c>
       <c r="AP114">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ114">
         <v>1.55</v>
@@ -25186,7 +25192,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25267,7 +25273,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ116">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR116">
         <v>1.85</v>
@@ -25392,7 +25398,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25473,7 +25479,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ117">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR117">
         <v>1.63</v>
@@ -25598,7 +25604,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -26216,7 +26222,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26628,7 +26634,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26834,7 +26840,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27040,7 +27046,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27246,7 +27252,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27327,7 +27333,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ126">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR126">
         <v>1.11</v>
@@ -27530,10 +27536,10 @@
         <v>0.67</v>
       </c>
       <c r="AP127">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ127">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR127">
         <v>1.54</v>
@@ -27736,10 +27742,10 @@
         <v>1.83</v>
       </c>
       <c r="AP128">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ128">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR128">
         <v>1.58</v>
@@ -27864,7 +27870,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -27945,7 +27951,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ129">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR129">
         <v>0.88</v>
@@ -28148,7 +28154,7 @@
         <v>0.17</v>
       </c>
       <c r="AP130">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ130">
         <v>0.83</v>
@@ -28354,7 +28360,7 @@
         <v>0.5</v>
       </c>
       <c r="AP131">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ131">
         <v>1.08</v>
@@ -28563,7 +28569,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ132">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR132">
         <v>1.48</v>
@@ -29100,7 +29106,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29306,7 +29312,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29718,7 +29724,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29796,7 +29802,7 @@
         <v>2</v>
       </c>
       <c r="AP138">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ138">
         <v>1.75</v>
@@ -29924,7 +29930,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30211,7 +30217,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ140">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR140">
         <v>1.57</v>
@@ -30748,7 +30754,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30829,7 +30835,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ143">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR143">
         <v>1.47</v>
@@ -30954,7 +30960,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31366,7 +31372,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31572,7 +31578,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31650,7 +31656,7 @@
         <v>0.63</v>
       </c>
       <c r="AP147">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ147">
         <v>0.58</v>
@@ -31856,7 +31862,7 @@
         <v>1.29</v>
       </c>
       <c r="AP148">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ148">
         <v>1.75</v>
@@ -31984,7 +31990,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32065,7 +32071,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ149">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR149">
         <v>1</v>
@@ -32396,7 +32402,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32474,7 +32480,7 @@
         <v>2</v>
       </c>
       <c r="AP151">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ151">
         <v>2.08</v>
@@ -32602,7 +32608,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32808,7 +32814,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -33014,7 +33020,7 @@
         <v>192</v>
       </c>
       <c r="P154" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33092,10 +33098,10 @@
         <v>1</v>
       </c>
       <c r="AP154">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ154">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR154">
         <v>1.38</v>
@@ -33220,7 +33226,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -33713,7 +33719,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ157">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR157">
         <v>1.44</v>
@@ -34044,7 +34050,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34122,7 +34128,7 @@
         <v>2.33</v>
       </c>
       <c r="AP159">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ159">
         <v>2.25</v>
@@ -34456,7 +34462,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34537,7 +34543,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ161">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR161">
         <v>1.07</v>
@@ -34662,7 +34668,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34868,7 +34874,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -34946,7 +34952,7 @@
         <v>1.5</v>
       </c>
       <c r="AP163">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ163">
         <v>1.75</v>
@@ -35155,7 +35161,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ164">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR164">
         <v>1.54</v>
@@ -35280,7 +35286,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35358,7 +35364,7 @@
         <v>0.71</v>
       </c>
       <c r="AP165">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ165">
         <v>0.82</v>
@@ -35486,7 +35492,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35692,7 +35698,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35898,7 +35904,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -35979,7 +35985,7 @@
         <v>2</v>
       </c>
       <c r="AQ168">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR168">
         <v>1.6</v>
@@ -36391,7 +36397,7 @@
         <v>1</v>
       </c>
       <c r="AQ170">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR170">
         <v>1.34</v>
@@ -36516,7 +36522,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36722,7 +36728,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36800,7 +36806,7 @@
         <v>2.43</v>
       </c>
       <c r="AP172">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ172">
         <v>2.25</v>
@@ -36928,7 +36934,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37006,7 +37012,7 @@
         <v>2.11</v>
       </c>
       <c r="AP173">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ173">
         <v>2.08</v>
@@ -37134,7 +37140,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37418,7 +37424,7 @@
         <v>0.33</v>
       </c>
       <c r="AP175">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ175">
         <v>0.33</v>
@@ -37546,7 +37552,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -37833,7 +37839,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ177">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR177">
         <v>1.56</v>
@@ -38164,7 +38170,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38370,7 +38376,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38448,7 +38454,7 @@
         <v>1.33</v>
       </c>
       <c r="AP180">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ180">
         <v>1.08</v>
@@ -38576,7 +38582,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38863,7 +38869,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ182">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR182">
         <v>1.12</v>
@@ -38988,7 +38994,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39272,7 +39278,7 @@
         <v>1.63</v>
       </c>
       <c r="AP184">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ184">
         <v>1.25</v>
@@ -39481,7 +39487,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ185">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR185">
         <v>1</v>
@@ -39812,7 +39818,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39890,7 +39896,7 @@
         <v>0.6</v>
       </c>
       <c r="AP187">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ187">
         <v>0.58</v>
@@ -40224,7 +40230,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40636,7 +40642,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -40923,7 +40929,7 @@
         <v>1</v>
       </c>
       <c r="AQ192">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR192">
         <v>1.24</v>
@@ -41126,7 +41132,7 @@
         <v>2.5</v>
       </c>
       <c r="AP193">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ193">
         <v>2.25</v>
@@ -41254,7 +41260,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41335,7 +41341,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ194">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR194">
         <v>1.66</v>
@@ -41538,7 +41544,7 @@
         <v>1</v>
       </c>
       <c r="AP195">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ195">
         <v>1.08</v>
@@ -41872,7 +41878,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42284,7 +42290,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42365,7 +42371,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ199">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR199">
         <v>1.57</v>
@@ -42490,7 +42496,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42696,7 +42702,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -42777,7 +42783,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ201">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR201">
         <v>1.71</v>
@@ -43108,7 +43114,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43520,7 +43526,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43598,7 +43604,7 @@
         <v>0.7</v>
       </c>
       <c r="AP205">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ205">
         <v>0.83</v>
@@ -43932,7 +43938,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44138,7 +44144,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44425,7 +44431,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ209">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR209">
         <v>1.52</v>
@@ -44756,7 +44762,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45040,7 +45046,7 @@
         <v>1.8</v>
       </c>
       <c r="AP212">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ212">
         <v>1.75</v>
@@ -45249,7 +45255,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ213">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR213">
         <v>1.04</v>
@@ -45374,7 +45380,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45455,7 +45461,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ214">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR214">
         <v>1.72</v>
@@ -45580,7 +45586,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45661,7 +45667,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ215">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR215">
         <v>1.04</v>
@@ -45786,7 +45792,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -45864,7 +45870,7 @@
         <v>2.56</v>
       </c>
       <c r="AP216">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ216">
         <v>2.25</v>
@@ -45992,7 +45998,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46070,7 +46076,7 @@
         <v>1.5</v>
       </c>
       <c r="AP217">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ217">
         <v>1.64</v>
@@ -46198,7 +46204,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46276,7 +46282,7 @@
         <v>0.9</v>
       </c>
       <c r="AP218">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ218">
         <v>1.08</v>
@@ -46485,7 +46491,7 @@
         <v>1</v>
       </c>
       <c r="AQ219">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR219">
         <v>1.25</v>
@@ -46610,7 +46616,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46816,7 +46822,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47228,7 +47234,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47640,7 +47646,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47846,7 +47852,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -48258,7 +48264,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48464,7 +48470,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48542,7 +48548,7 @@
         <v>1.64</v>
       </c>
       <c r="AP229">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ229">
         <v>1.75</v>
@@ -48876,7 +48882,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49082,7 +49088,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49288,7 +49294,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49494,7 +49500,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -49651,6 +49657,1036 @@
       </c>
       <c r="BP234">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="235" spans="1:68">
+      <c r="A235" s="1">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>7492387</v>
+      </c>
+      <c r="C235" t="s">
+        <v>68</v>
+      </c>
+      <c r="D235" t="s">
+        <v>69</v>
+      </c>
+      <c r="E235" s="2">
+        <v>45697.35416666666</v>
+      </c>
+      <c r="F235">
+        <v>24</v>
+      </c>
+      <c r="G235" t="s">
+        <v>87</v>
+      </c>
+      <c r="H235" t="s">
+        <v>86</v>
+      </c>
+      <c r="I235">
+        <v>0</v>
+      </c>
+      <c r="J235">
+        <v>0</v>
+      </c>
+      <c r="K235">
+        <v>0</v>
+      </c>
+      <c r="L235">
+        <v>0</v>
+      </c>
+      <c r="M235">
+        <v>1</v>
+      </c>
+      <c r="N235">
+        <v>1</v>
+      </c>
+      <c r="O235" t="s">
+        <v>92</v>
+      </c>
+      <c r="P235" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q235">
+        <v>4.75</v>
+      </c>
+      <c r="R235">
+        <v>2.25</v>
+      </c>
+      <c r="S235">
+        <v>2.3</v>
+      </c>
+      <c r="T235">
+        <v>1.36</v>
+      </c>
+      <c r="U235">
+        <v>3</v>
+      </c>
+      <c r="V235">
+        <v>2.63</v>
+      </c>
+      <c r="W235">
+        <v>1.44</v>
+      </c>
+      <c r="X235">
+        <v>7</v>
+      </c>
+      <c r="Y235">
+        <v>1.1</v>
+      </c>
+      <c r="Z235">
+        <v>4.7</v>
+      </c>
+      <c r="AA235">
+        <v>3.92</v>
+      </c>
+      <c r="AB235">
+        <v>1.76</v>
+      </c>
+      <c r="AC235">
+        <v>1.04</v>
+      </c>
+      <c r="AD235">
+        <v>13</v>
+      </c>
+      <c r="AE235">
+        <v>1.25</v>
+      </c>
+      <c r="AF235">
+        <v>4</v>
+      </c>
+      <c r="AG235">
+        <v>1.8</v>
+      </c>
+      <c r="AH235">
+        <v>2.02</v>
+      </c>
+      <c r="AI235">
+        <v>1.75</v>
+      </c>
+      <c r="AJ235">
+        <v>2</v>
+      </c>
+      <c r="AK235">
+        <v>2</v>
+      </c>
+      <c r="AL235">
+        <v>1.26</v>
+      </c>
+      <c r="AM235">
+        <v>1.21</v>
+      </c>
+      <c r="AN235">
+        <v>1.09</v>
+      </c>
+      <c r="AO235">
+        <v>0.82</v>
+      </c>
+      <c r="AP235">
+        <v>1</v>
+      </c>
+      <c r="AQ235">
+        <v>1</v>
+      </c>
+      <c r="AR235">
+        <v>1.34</v>
+      </c>
+      <c r="AS235">
+        <v>1.28</v>
+      </c>
+      <c r="AT235">
+        <v>2.62</v>
+      </c>
+      <c r="AU235">
+        <v>4</v>
+      </c>
+      <c r="AV235">
+        <v>6</v>
+      </c>
+      <c r="AW235">
+        <v>9</v>
+      </c>
+      <c r="AX235">
+        <v>8</v>
+      </c>
+      <c r="AY235">
+        <v>18</v>
+      </c>
+      <c r="AZ235">
+        <v>14</v>
+      </c>
+      <c r="BA235">
+        <v>4</v>
+      </c>
+      <c r="BB235">
+        <v>6</v>
+      </c>
+      <c r="BC235">
+        <v>10</v>
+      </c>
+      <c r="BD235">
+        <v>3.28</v>
+      </c>
+      <c r="BE235">
+        <v>9</v>
+      </c>
+      <c r="BF235">
+        <v>1.49</v>
+      </c>
+      <c r="BG235">
+        <v>1.29</v>
+      </c>
+      <c r="BH235">
+        <v>3.04</v>
+      </c>
+      <c r="BI235">
+        <v>1.56</v>
+      </c>
+      <c r="BJ235">
+        <v>2.21</v>
+      </c>
+      <c r="BK235">
+        <v>1.98</v>
+      </c>
+      <c r="BL235">
+        <v>1.74</v>
+      </c>
+      <c r="BM235">
+        <v>2.57</v>
+      </c>
+      <c r="BN235">
+        <v>1.42</v>
+      </c>
+      <c r="BO235">
+        <v>3.5</v>
+      </c>
+      <c r="BP235">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="236" spans="1:68">
+      <c r="A236" s="1">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>7492383</v>
+      </c>
+      <c r="C236" t="s">
+        <v>68</v>
+      </c>
+      <c r="D236" t="s">
+        <v>69</v>
+      </c>
+      <c r="E236" s="2">
+        <v>45697.45833333334</v>
+      </c>
+      <c r="F236">
+        <v>24</v>
+      </c>
+      <c r="G236" t="s">
+        <v>77</v>
+      </c>
+      <c r="H236" t="s">
+        <v>81</v>
+      </c>
+      <c r="I236">
+        <v>1</v>
+      </c>
+      <c r="J236">
+        <v>0</v>
+      </c>
+      <c r="K236">
+        <v>1</v>
+      </c>
+      <c r="L236">
+        <v>5</v>
+      </c>
+      <c r="M236">
+        <v>1</v>
+      </c>
+      <c r="N236">
+        <v>6</v>
+      </c>
+      <c r="O236" t="s">
+        <v>240</v>
+      </c>
+      <c r="P236" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q236">
+        <v>1.91</v>
+      </c>
+      <c r="R236">
+        <v>2.38</v>
+      </c>
+      <c r="S236">
+        <v>7.5</v>
+      </c>
+      <c r="T236">
+        <v>1.36</v>
+      </c>
+      <c r="U236">
+        <v>3</v>
+      </c>
+      <c r="V236">
+        <v>2.63</v>
+      </c>
+      <c r="W236">
+        <v>1.44</v>
+      </c>
+      <c r="X236">
+        <v>7</v>
+      </c>
+      <c r="Y236">
+        <v>1.1</v>
+      </c>
+      <c r="Z236">
+        <v>1.45</v>
+      </c>
+      <c r="AA236">
+        <v>4.8</v>
+      </c>
+      <c r="AB236">
+        <v>7.4</v>
+      </c>
+      <c r="AC236">
+        <v>1.04</v>
+      </c>
+      <c r="AD236">
+        <v>13</v>
+      </c>
+      <c r="AE236">
+        <v>1.26</v>
+      </c>
+      <c r="AF236">
+        <v>4</v>
+      </c>
+      <c r="AG236">
+        <v>1.81</v>
+      </c>
+      <c r="AH236">
+        <v>2.01</v>
+      </c>
+      <c r="AI236">
+        <v>2</v>
+      </c>
+      <c r="AJ236">
+        <v>1.75</v>
+      </c>
+      <c r="AK236">
+        <v>1.1</v>
+      </c>
+      <c r="AL236">
+        <v>1.19</v>
+      </c>
+      <c r="AM236">
+        <v>2.75</v>
+      </c>
+      <c r="AN236">
+        <v>1.91</v>
+      </c>
+      <c r="AO236">
+        <v>0.64</v>
+      </c>
+      <c r="AP236">
+        <v>2</v>
+      </c>
+      <c r="AQ236">
+        <v>0.58</v>
+      </c>
+      <c r="AR236">
+        <v>1.52</v>
+      </c>
+      <c r="AS236">
+        <v>0.88</v>
+      </c>
+      <c r="AT236">
+        <v>2.4</v>
+      </c>
+      <c r="AU236">
+        <v>10</v>
+      </c>
+      <c r="AV236">
+        <v>2</v>
+      </c>
+      <c r="AW236">
+        <v>17</v>
+      </c>
+      <c r="AX236">
+        <v>2</v>
+      </c>
+      <c r="AY236">
+        <v>31</v>
+      </c>
+      <c r="AZ236">
+        <v>4</v>
+      </c>
+      <c r="BA236">
+        <v>8</v>
+      </c>
+      <c r="BB236">
+        <v>1</v>
+      </c>
+      <c r="BC236">
+        <v>9</v>
+      </c>
+      <c r="BD236">
+        <v>1.24</v>
+      </c>
+      <c r="BE236">
+        <v>11</v>
+      </c>
+      <c r="BF236">
+        <v>5.25</v>
+      </c>
+      <c r="BG236">
+        <v>1.18</v>
+      </c>
+      <c r="BH236">
+        <v>3.86</v>
+      </c>
+      <c r="BI236">
+        <v>1.38</v>
+      </c>
+      <c r="BJ236">
+        <v>2.71</v>
+      </c>
+      <c r="BK236">
+        <v>1.68</v>
+      </c>
+      <c r="BL236">
+        <v>2.06</v>
+      </c>
+      <c r="BM236">
+        <v>2.1</v>
+      </c>
+      <c r="BN236">
+        <v>1.62</v>
+      </c>
+      <c r="BO236">
+        <v>2.74</v>
+      </c>
+      <c r="BP236">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="237" spans="1:68">
+      <c r="A237" s="1">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>7492378</v>
+      </c>
+      <c r="C237" t="s">
+        <v>68</v>
+      </c>
+      <c r="D237" t="s">
+        <v>69</v>
+      </c>
+      <c r="E237" s="2">
+        <v>45697.45833333334</v>
+      </c>
+      <c r="F237">
+        <v>24</v>
+      </c>
+      <c r="G237" t="s">
+        <v>76</v>
+      </c>
+      <c r="H237" t="s">
+        <v>71</v>
+      </c>
+      <c r="I237">
+        <v>0</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237">
+        <v>0</v>
+      </c>
+      <c r="L237">
+        <v>2</v>
+      </c>
+      <c r="M237">
+        <v>1</v>
+      </c>
+      <c r="N237">
+        <v>3</v>
+      </c>
+      <c r="O237" t="s">
+        <v>241</v>
+      </c>
+      <c r="P237" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q237">
+        <v>2.5</v>
+      </c>
+      <c r="R237">
+        <v>2.3</v>
+      </c>
+      <c r="S237">
+        <v>4</v>
+      </c>
+      <c r="T237">
+        <v>1.33</v>
+      </c>
+      <c r="U237">
+        <v>3.25</v>
+      </c>
+      <c r="V237">
+        <v>2.63</v>
+      </c>
+      <c r="W237">
+        <v>1.44</v>
+      </c>
+      <c r="X237">
+        <v>6.5</v>
+      </c>
+      <c r="Y237">
+        <v>1.11</v>
+      </c>
+      <c r="Z237">
+        <v>1.93</v>
+      </c>
+      <c r="AA237">
+        <v>3.74</v>
+      </c>
+      <c r="AB237">
+        <v>4</v>
+      </c>
+      <c r="AC237">
+        <v>1.04</v>
+      </c>
+      <c r="AD237">
+        <v>13</v>
+      </c>
+      <c r="AE237">
+        <v>1.24</v>
+      </c>
+      <c r="AF237">
+        <v>4.2</v>
+      </c>
+      <c r="AG237">
+        <v>1.7</v>
+      </c>
+      <c r="AH237">
+        <v>2.1</v>
+      </c>
+      <c r="AI237">
+        <v>1.62</v>
+      </c>
+      <c r="AJ237">
+        <v>2.2</v>
+      </c>
+      <c r="AK237">
+        <v>1.26</v>
+      </c>
+      <c r="AL237">
+        <v>1.28</v>
+      </c>
+      <c r="AM237">
+        <v>1.83</v>
+      </c>
+      <c r="AN237">
+        <v>1</v>
+      </c>
+      <c r="AO237">
+        <v>0.73</v>
+      </c>
+      <c r="AP237">
+        <v>1.15</v>
+      </c>
+      <c r="AQ237">
+        <v>0.67</v>
+      </c>
+      <c r="AR237">
+        <v>1.47</v>
+      </c>
+      <c r="AS237">
+        <v>1.2</v>
+      </c>
+      <c r="AT237">
+        <v>2.67</v>
+      </c>
+      <c r="AU237">
+        <v>4</v>
+      </c>
+      <c r="AV237">
+        <v>2</v>
+      </c>
+      <c r="AW237">
+        <v>11</v>
+      </c>
+      <c r="AX237">
+        <v>8</v>
+      </c>
+      <c r="AY237">
+        <v>16</v>
+      </c>
+      <c r="AZ237">
+        <v>13</v>
+      </c>
+      <c r="BA237">
+        <v>7</v>
+      </c>
+      <c r="BB237">
+        <v>6</v>
+      </c>
+      <c r="BC237">
+        <v>13</v>
+      </c>
+      <c r="BD237">
+        <v>1.58</v>
+      </c>
+      <c r="BE237">
+        <v>9.4</v>
+      </c>
+      <c r="BF237">
+        <v>2.88</v>
+      </c>
+      <c r="BG237">
+        <v>1.14</v>
+      </c>
+      <c r="BH237">
+        <v>4.4</v>
+      </c>
+      <c r="BI237">
+        <v>1.3</v>
+      </c>
+      <c r="BJ237">
+        <v>2.97</v>
+      </c>
+      <c r="BK237">
+        <v>1.55</v>
+      </c>
+      <c r="BL237">
+        <v>2.23</v>
+      </c>
+      <c r="BM237">
+        <v>1.94</v>
+      </c>
+      <c r="BN237">
+        <v>1.77</v>
+      </c>
+      <c r="BO237">
+        <v>2.5</v>
+      </c>
+      <c r="BP237">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="238" spans="1:68">
+      <c r="A238" s="1">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>7492384</v>
+      </c>
+      <c r="C238" t="s">
+        <v>68</v>
+      </c>
+      <c r="D238" t="s">
+        <v>69</v>
+      </c>
+      <c r="E238" s="2">
+        <v>45697.58333333334</v>
+      </c>
+      <c r="F238">
+        <v>24</v>
+      </c>
+      <c r="G238" t="s">
+        <v>78</v>
+      </c>
+      <c r="H238" t="s">
+        <v>74</v>
+      </c>
+      <c r="I238">
+        <v>0</v>
+      </c>
+      <c r="J238">
+        <v>0</v>
+      </c>
+      <c r="K238">
+        <v>0</v>
+      </c>
+      <c r="L238">
+        <v>0</v>
+      </c>
+      <c r="M238">
+        <v>0</v>
+      </c>
+      <c r="N238">
+        <v>0</v>
+      </c>
+      <c r="O238" t="s">
+        <v>92</v>
+      </c>
+      <c r="P238" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q238">
+        <v>4.75</v>
+      </c>
+      <c r="R238">
+        <v>2.05</v>
+      </c>
+      <c r="S238">
+        <v>2.6</v>
+      </c>
+      <c r="T238">
+        <v>1.5</v>
+      </c>
+      <c r="U238">
+        <v>2.5</v>
+      </c>
+      <c r="V238">
+        <v>3.4</v>
+      </c>
+      <c r="W238">
+        <v>1.3</v>
+      </c>
+      <c r="X238">
+        <v>10</v>
+      </c>
+      <c r="Y238">
+        <v>1.06</v>
+      </c>
+      <c r="Z238">
+        <v>4.4</v>
+      </c>
+      <c r="AA238">
+        <v>3.51</v>
+      </c>
+      <c r="AB238">
+        <v>1.91</v>
+      </c>
+      <c r="AC238">
+        <v>1.08</v>
+      </c>
+      <c r="AD238">
+        <v>9</v>
+      </c>
+      <c r="AE238">
+        <v>1.4</v>
+      </c>
+      <c r="AF238">
+        <v>3</v>
+      </c>
+      <c r="AG238">
+        <v>1.95</v>
+      </c>
+      <c r="AH238">
+        <v>1.8</v>
+      </c>
+      <c r="AI238">
+        <v>2</v>
+      </c>
+      <c r="AJ238">
+        <v>1.75</v>
+      </c>
+      <c r="AK238">
+        <v>1.85</v>
+      </c>
+      <c r="AL238">
+        <v>1.32</v>
+      </c>
+      <c r="AM238">
+        <v>1.22</v>
+      </c>
+      <c r="AN238">
+        <v>1.18</v>
+      </c>
+      <c r="AO238">
+        <v>1.55</v>
+      </c>
+      <c r="AP238">
+        <v>1.17</v>
+      </c>
+      <c r="AQ238">
+        <v>1.5</v>
+      </c>
+      <c r="AR238">
+        <v>1.34</v>
+      </c>
+      <c r="AS238">
+        <v>1.27</v>
+      </c>
+      <c r="AT238">
+        <v>2.61</v>
+      </c>
+      <c r="AU238">
+        <v>2</v>
+      </c>
+      <c r="AV238">
+        <v>3</v>
+      </c>
+      <c r="AW238">
+        <v>5</v>
+      </c>
+      <c r="AX238">
+        <v>6</v>
+      </c>
+      <c r="AY238">
+        <v>8</v>
+      </c>
+      <c r="AZ238">
+        <v>9</v>
+      </c>
+      <c r="BA238">
+        <v>6</v>
+      </c>
+      <c r="BB238">
+        <v>5</v>
+      </c>
+      <c r="BC238">
+        <v>11</v>
+      </c>
+      <c r="BD238">
+        <v>2.78</v>
+      </c>
+      <c r="BE238">
+        <v>8.5</v>
+      </c>
+      <c r="BF238">
+        <v>1.64</v>
+      </c>
+      <c r="BG238">
+        <v>1.36</v>
+      </c>
+      <c r="BH238">
+        <v>2.78</v>
+      </c>
+      <c r="BI238">
+        <v>1.68</v>
+      </c>
+      <c r="BJ238">
+        <v>2.06</v>
+      </c>
+      <c r="BK238">
+        <v>2.14</v>
+      </c>
+      <c r="BL238">
+        <v>1.6</v>
+      </c>
+      <c r="BM238">
+        <v>2.83</v>
+      </c>
+      <c r="BN238">
+        <v>1.33</v>
+      </c>
+      <c r="BO238">
+        <v>3.98</v>
+      </c>
+      <c r="BP238">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="239" spans="1:68">
+      <c r="A239" s="1">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>7492385</v>
+      </c>
+      <c r="C239" t="s">
+        <v>68</v>
+      </c>
+      <c r="D239" t="s">
+        <v>69</v>
+      </c>
+      <c r="E239" s="2">
+        <v>45697.69791666666</v>
+      </c>
+      <c r="F239">
+        <v>24</v>
+      </c>
+      <c r="G239" t="s">
+        <v>85</v>
+      </c>
+      <c r="H239" t="s">
+        <v>80</v>
+      </c>
+      <c r="I239">
+        <v>1</v>
+      </c>
+      <c r="J239">
+        <v>1</v>
+      </c>
+      <c r="K239">
+        <v>2</v>
+      </c>
+      <c r="L239">
+        <v>1</v>
+      </c>
+      <c r="M239">
+        <v>1</v>
+      </c>
+      <c r="N239">
+        <v>2</v>
+      </c>
+      <c r="O239" t="s">
+        <v>242</v>
+      </c>
+      <c r="P239" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q239">
+        <v>1.95</v>
+      </c>
+      <c r="R239">
+        <v>2.3</v>
+      </c>
+      <c r="S239">
+        <v>7.5</v>
+      </c>
+      <c r="T239">
+        <v>1.4</v>
+      </c>
+      <c r="U239">
+        <v>2.75</v>
+      </c>
+      <c r="V239">
+        <v>3</v>
+      </c>
+      <c r="W239">
+        <v>1.36</v>
+      </c>
+      <c r="X239">
+        <v>8</v>
+      </c>
+      <c r="Y239">
+        <v>1.08</v>
+      </c>
+      <c r="Z239">
+        <v>1.44</v>
+      </c>
+      <c r="AA239">
+        <v>4.6</v>
+      </c>
+      <c r="AB239">
+        <v>7.9</v>
+      </c>
+      <c r="AC239">
+        <v>1.04</v>
+      </c>
+      <c r="AD239">
+        <v>13</v>
+      </c>
+      <c r="AE239">
+        <v>1.3</v>
+      </c>
+      <c r="AF239">
+        <v>3.6</v>
+      </c>
+      <c r="AG239">
+        <v>1.96</v>
+      </c>
+      <c r="AH239">
+        <v>1.85</v>
+      </c>
+      <c r="AI239">
+        <v>2.2</v>
+      </c>
+      <c r="AJ239">
+        <v>1.62</v>
+      </c>
+      <c r="AK239">
+        <v>1.09</v>
+      </c>
+      <c r="AL239">
+        <v>1.21</v>
+      </c>
+      <c r="AM239">
+        <v>2.7</v>
+      </c>
+      <c r="AN239">
+        <v>2.45</v>
+      </c>
+      <c r="AO239">
+        <v>1.09</v>
+      </c>
+      <c r="AP239">
+        <v>2.33</v>
+      </c>
+      <c r="AQ239">
+        <v>1.08</v>
+      </c>
+      <c r="AR239">
+        <v>1.57</v>
+      </c>
+      <c r="AS239">
+        <v>1.35</v>
+      </c>
+      <c r="AT239">
+        <v>2.92</v>
+      </c>
+      <c r="AU239">
+        <v>5</v>
+      </c>
+      <c r="AV239">
+        <v>5</v>
+      </c>
+      <c r="AW239">
+        <v>14</v>
+      </c>
+      <c r="AX239">
+        <v>4</v>
+      </c>
+      <c r="AY239">
+        <v>23</v>
+      </c>
+      <c r="AZ239">
+        <v>10</v>
+      </c>
+      <c r="BA239">
+        <v>6</v>
+      </c>
+      <c r="BB239">
+        <v>6</v>
+      </c>
+      <c r="BC239">
+        <v>12</v>
+      </c>
+      <c r="BD239">
+        <v>1.22</v>
+      </c>
+      <c r="BE239">
+        <v>11.5</v>
+      </c>
+      <c r="BF239">
+        <v>5.55</v>
+      </c>
+      <c r="BG239">
+        <v>1.18</v>
+      </c>
+      <c r="BH239">
+        <v>3.9</v>
+      </c>
+      <c r="BI239">
+        <v>1.37</v>
+      </c>
+      <c r="BJ239">
+        <v>2.75</v>
+      </c>
+      <c r="BK239">
+        <v>1.67</v>
+      </c>
+      <c r="BL239">
+        <v>2.07</v>
+      </c>
+      <c r="BM239">
+        <v>2.09</v>
+      </c>
+      <c r="BN239">
+        <v>1.63</v>
+      </c>
+      <c r="BO239">
+        <v>2.7</v>
+      </c>
+      <c r="BP239">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="360">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -745,6 +745,9 @@
     <t>['37']</t>
   </si>
   <si>
+    <t>['28', '52']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1452,7 +1455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP239"/>
+  <dimension ref="A1:BP240"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1708,7 +1711,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1995,7 +1998,7 @@
         <v>1</v>
       </c>
       <c r="AQ3">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2326,7 +2329,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2532,7 +2535,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -3150,7 +3153,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3356,7 +3359,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3768,7 +3771,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q12">
         <v>3.75</v>
@@ -3974,7 +3977,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4180,7 +4183,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4464,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ15">
         <v>0.83</v>
@@ -5210,7 +5213,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5622,7 +5625,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5828,7 +5831,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6112,7 +6115,7 @@
         <v>1.5</v>
       </c>
       <c r="AP23">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ23">
         <v>2.08</v>
@@ -6240,7 +6243,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6652,7 +6655,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6858,7 +6861,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7064,7 +7067,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7270,7 +7273,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7888,7 +7891,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8712,7 +8715,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -8793,7 +8796,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ36">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR36">
         <v>0</v>
@@ -9124,7 +9127,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9330,7 +9333,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9536,7 +9539,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9742,7 +9745,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9948,7 +9951,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10154,7 +10157,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10772,7 +10775,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10978,7 +10981,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11184,7 +11187,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11596,7 +11599,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11674,7 +11677,7 @@
         <v>0.5</v>
       </c>
       <c r="AP50">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ50">
         <v>1.55</v>
@@ -11802,7 +11805,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12214,7 +12217,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12420,7 +12423,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12626,7 +12629,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12832,7 +12835,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13038,7 +13041,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13531,7 +13534,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ59">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR59">
         <v>0.91</v>
@@ -13862,7 +13865,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14686,7 +14689,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14892,7 +14895,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -14970,7 +14973,7 @@
         <v>2.33</v>
       </c>
       <c r="AP66">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ66">
         <v>1.17</v>
@@ -15098,7 +15101,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15304,7 +15307,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q68">
         <v>2.2</v>
@@ -15716,7 +15719,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -16334,7 +16337,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16952,7 +16955,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17158,7 +17161,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17239,7 +17242,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ77">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR77">
         <v>1.41</v>
@@ -17364,7 +17367,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17570,7 +17573,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17982,7 +17985,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18806,7 +18809,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19424,7 +19427,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19630,7 +19633,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19708,7 +19711,7 @@
         <v>2.33</v>
       </c>
       <c r="AP89">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ89">
         <v>1.75</v>
@@ -19836,7 +19839,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20042,7 +20045,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20454,7 +20457,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20660,7 +20663,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20866,7 +20869,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -21278,7 +21281,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21484,7 +21487,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21565,7 +21568,7 @@
         <v>1</v>
       </c>
       <c r="AQ98">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR98">
         <v>1.23</v>
@@ -21690,7 +21693,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22308,7 +22311,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22720,7 +22723,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22926,7 +22929,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23007,7 +23010,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ105">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR105">
         <v>1.14</v>
@@ -23132,7 +23135,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23416,7 +23419,7 @@
         <v>0.33</v>
       </c>
       <c r="AP107">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ107">
         <v>0.33</v>
@@ -23956,7 +23959,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24162,7 +24165,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24368,7 +24371,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24574,7 +24577,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24780,7 +24783,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25192,7 +25195,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25398,7 +25401,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25604,7 +25607,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -26094,7 +26097,7 @@
         <v>2</v>
       </c>
       <c r="AP120">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ120">
         <v>2.25</v>
@@ -26222,7 +26225,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26634,7 +26637,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26840,7 +26843,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27046,7 +27049,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27127,7 +27130,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ125">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR125">
         <v>1.5</v>
@@ -27252,7 +27255,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27870,7 +27873,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -29106,7 +29109,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29312,7 +29315,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29724,7 +29727,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29930,7 +29933,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30214,7 +30217,7 @@
         <v>1.17</v>
       </c>
       <c r="AP140">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ140">
         <v>0.67</v>
@@ -30754,7 +30757,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30960,7 +30963,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31372,7 +31375,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31578,7 +31581,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31990,7 +31993,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32402,7 +32405,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32608,7 +32611,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32814,7 +32817,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -33226,7 +33229,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -33513,7 +33516,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ156">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR156">
         <v>1.61</v>
@@ -34050,7 +34053,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34462,7 +34465,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34668,7 +34671,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34874,7 +34877,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35286,7 +35289,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35492,7 +35495,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35698,7 +35701,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35904,7 +35907,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36188,7 +36191,7 @@
         <v>0.67</v>
       </c>
       <c r="AP169">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ169">
         <v>0.58</v>
@@ -36522,7 +36525,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36728,7 +36731,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36934,7 +36937,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37140,7 +37143,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37552,7 +37555,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -37633,7 +37636,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ176">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR176">
         <v>1.42</v>
@@ -38170,7 +38173,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38376,7 +38379,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38582,7 +38585,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38994,7 +38997,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39818,7 +39821,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40230,7 +40233,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40642,7 +40645,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41260,7 +41263,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41753,7 +41756,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ196">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR196">
         <v>1.17</v>
@@ -41878,7 +41881,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42290,7 +42293,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42368,7 +42371,7 @@
         <v>1.67</v>
       </c>
       <c r="AP199">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ199">
         <v>1.5</v>
@@ -42496,7 +42499,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42702,7 +42705,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -43114,7 +43117,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43526,7 +43529,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43938,7 +43941,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44144,7 +44147,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44222,7 +44225,7 @@
         <v>1.3</v>
       </c>
       <c r="AP208">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ208">
         <v>1.08</v>
@@ -44762,7 +44765,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45380,7 +45383,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45586,7 +45589,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45792,7 +45795,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -45998,7 +46001,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46079,7 +46082,7 @@
         <v>2</v>
       </c>
       <c r="AQ217">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR217">
         <v>1.44</v>
@@ -46204,7 +46207,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46616,7 +46619,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46822,7 +46825,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47234,7 +47237,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47646,7 +47649,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47852,7 +47855,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -48264,7 +48267,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48470,7 +48473,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48882,7 +48885,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49088,7 +49091,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49294,7 +49297,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49500,7 +49503,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -49912,7 +49915,7 @@
         <v>240</v>
       </c>
       <c r="P236" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q236">
         <v>1.91</v>
@@ -50530,7 +50533,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -50687,6 +50690,212 @@
       </c>
       <c r="BP239">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="240" spans="1:68">
+      <c r="A240" s="1">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>7492382</v>
+      </c>
+      <c r="C240" t="s">
+        <v>68</v>
+      </c>
+      <c r="D240" t="s">
+        <v>69</v>
+      </c>
+      <c r="E240" s="2">
+        <v>45698.69791666666</v>
+      </c>
+      <c r="F240">
+        <v>24</v>
+      </c>
+      <c r="G240" t="s">
+        <v>82</v>
+      </c>
+      <c r="H240" t="s">
+        <v>83</v>
+      </c>
+      <c r="I240">
+        <v>1</v>
+      </c>
+      <c r="J240">
+        <v>1</v>
+      </c>
+      <c r="K240">
+        <v>2</v>
+      </c>
+      <c r="L240">
+        <v>2</v>
+      </c>
+      <c r="M240">
+        <v>1</v>
+      </c>
+      <c r="N240">
+        <v>3</v>
+      </c>
+      <c r="O240" t="s">
+        <v>243</v>
+      </c>
+      <c r="P240" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q240">
+        <v>1.95</v>
+      </c>
+      <c r="R240">
+        <v>2.4</v>
+      </c>
+      <c r="S240">
+        <v>6.5</v>
+      </c>
+      <c r="T240">
+        <v>1.33</v>
+      </c>
+      <c r="U240">
+        <v>3.25</v>
+      </c>
+      <c r="V240">
+        <v>2.5</v>
+      </c>
+      <c r="W240">
+        <v>1.5</v>
+      </c>
+      <c r="X240">
+        <v>6.5</v>
+      </c>
+      <c r="Y240">
+        <v>1.11</v>
+      </c>
+      <c r="Z240">
+        <v>1.47</v>
+      </c>
+      <c r="AA240">
+        <v>4.75</v>
+      </c>
+      <c r="AB240">
+        <v>7.1</v>
+      </c>
+      <c r="AC240">
+        <v>1.03</v>
+      </c>
+      <c r="AD240">
+        <v>15</v>
+      </c>
+      <c r="AE240">
+        <v>1.22</v>
+      </c>
+      <c r="AF240">
+        <v>4.33</v>
+      </c>
+      <c r="AG240">
+        <v>1.7</v>
+      </c>
+      <c r="AH240">
+        <v>2.05</v>
+      </c>
+      <c r="AI240">
+        <v>1.91</v>
+      </c>
+      <c r="AJ240">
+        <v>1.91</v>
+      </c>
+      <c r="AK240">
+        <v>1.12</v>
+      </c>
+      <c r="AL240">
+        <v>1.19</v>
+      </c>
+      <c r="AM240">
+        <v>2.6</v>
+      </c>
+      <c r="AN240">
+        <v>2.18</v>
+      </c>
+      <c r="AO240">
+        <v>1.64</v>
+      </c>
+      <c r="AP240">
+        <v>2.25</v>
+      </c>
+      <c r="AQ240">
+        <v>1.5</v>
+      </c>
+      <c r="AR240">
+        <v>1.63</v>
+      </c>
+      <c r="AS240">
+        <v>1.24</v>
+      </c>
+      <c r="AT240">
+        <v>2.87</v>
+      </c>
+      <c r="AU240">
+        <v>9</v>
+      </c>
+      <c r="AV240">
+        <v>3</v>
+      </c>
+      <c r="AW240">
+        <v>14</v>
+      </c>
+      <c r="AX240">
+        <v>5</v>
+      </c>
+      <c r="AY240">
+        <v>26</v>
+      </c>
+      <c r="AZ240">
+        <v>9</v>
+      </c>
+      <c r="BA240">
+        <v>8</v>
+      </c>
+      <c r="BB240">
+        <v>1</v>
+      </c>
+      <c r="BC240">
+        <v>9</v>
+      </c>
+      <c r="BD240">
+        <v>1.38</v>
+      </c>
+      <c r="BE240">
+        <v>9.4</v>
+      </c>
+      <c r="BF240">
+        <v>3.9</v>
+      </c>
+      <c r="BG240">
+        <v>1.33</v>
+      </c>
+      <c r="BH240">
+        <v>2.83</v>
+      </c>
+      <c r="BI240">
+        <v>1.63</v>
+      </c>
+      <c r="BJ240">
+        <v>2.09</v>
+      </c>
+      <c r="BK240">
+        <v>2.09</v>
+      </c>
+      <c r="BL240">
+        <v>1.66</v>
+      </c>
+      <c r="BM240">
+        <v>2.75</v>
+      </c>
+      <c r="BN240">
+        <v>1.37</v>
+      </c>
+      <c r="BO240">
+        <v>3.8</v>
+      </c>
+      <c r="BP240">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="362">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -748,6 +748,9 @@
     <t>['28', '52']</t>
   </si>
   <si>
+    <t>['20', '70', '90']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1094,6 +1097,9 @@
   </si>
   <si>
     <t>['68', '76']</t>
+  </si>
+  <si>
+    <t>['37', '65']</t>
   </si>
 </sst>
 </file>
@@ -1455,7 +1461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP240"/>
+  <dimension ref="A1:BP241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1711,7 +1717,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2329,7 +2335,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2410,7 +2416,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ5">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2535,7 +2541,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2613,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ6">
         <v>1.08</v>
@@ -3153,7 +3159,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3359,7 +3365,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3771,7 +3777,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q12">
         <v>3.75</v>
@@ -3977,7 +3983,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4183,7 +4189,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -5213,7 +5219,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5625,7 +5631,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5831,7 +5837,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5912,7 +5918,7 @@
         <v>1</v>
       </c>
       <c r="AQ22">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6243,7 +6249,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6321,7 +6327,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ24">
         <v>1.08</v>
@@ -6655,7 +6661,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6861,7 +6867,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7067,7 +7073,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7273,7 +7279,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7891,7 +7897,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8715,7 +8721,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -9127,7 +9133,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9333,7 +9339,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9539,7 +9545,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9745,7 +9751,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9951,7 +9957,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10157,7 +10163,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10238,7 +10244,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ43">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR43">
         <v>0.93</v>
@@ -10775,7 +10781,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10981,7 +10987,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11187,7 +11193,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11599,7 +11605,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11805,7 +11811,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12217,7 +12223,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12423,7 +12429,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12629,7 +12635,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12707,7 +12713,7 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ55">
         <v>2.08</v>
@@ -12835,7 +12841,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13041,7 +13047,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13865,7 +13871,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14689,7 +14695,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14895,7 +14901,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -14976,7 +14982,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ66">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR66">
         <v>1.21</v>
@@ -15101,7 +15107,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15307,7 +15313,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q68">
         <v>2.2</v>
@@ -15591,7 +15597,7 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ69">
         <v>0.67</v>
@@ -15719,7 +15725,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -16337,7 +16343,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16955,7 +16961,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17161,7 +17167,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17367,7 +17373,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17573,7 +17579,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17654,7 +17660,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ79">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR79">
         <v>1.44</v>
@@ -17985,7 +17991,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18809,7 +18815,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19427,7 +19433,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19633,7 +19639,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19839,7 +19845,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20045,7 +20051,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20457,7 +20463,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20663,7 +20669,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20869,7 +20875,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -21281,7 +21287,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21487,7 +21493,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21693,7 +21699,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21980,7 +21986,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ100">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR100">
         <v>1.81</v>
@@ -22183,7 +22189,7 @@
         <v>0.2</v>
       </c>
       <c r="AP101">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ101">
         <v>0.83</v>
@@ -22311,7 +22317,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22723,7 +22729,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22929,7 +22935,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23135,7 +23141,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23959,7 +23965,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24165,7 +24171,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24371,7 +24377,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24577,7 +24583,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24783,7 +24789,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25070,7 +25076,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ115">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR115">
         <v>1.54</v>
@@ -25195,7 +25201,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25401,7 +25407,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25607,7 +25613,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -26225,7 +26231,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26637,7 +26643,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26843,7 +26849,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27049,7 +27055,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27255,7 +27261,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27873,7 +27879,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -28981,7 +28987,7 @@
         <v>0.29</v>
       </c>
       <c r="AP134">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ134">
         <v>0.33</v>
@@ -29109,7 +29115,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29315,7 +29321,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29727,7 +29733,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29933,7 +29939,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30632,7 +30638,7 @@
         <v>1</v>
       </c>
       <c r="AQ142">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR142">
         <v>1.3</v>
@@ -30757,7 +30763,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30963,7 +30969,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31375,7 +31381,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31581,7 +31587,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31993,7 +31999,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32280,7 +32286,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ150">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR150">
         <v>0.84</v>
@@ -32405,7 +32411,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32611,7 +32617,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32817,7 +32823,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -33229,7 +33235,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -33513,7 +33519,7 @@
         <v>2</v>
       </c>
       <c r="AP156">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ156">
         <v>1.5</v>
@@ -34053,7 +34059,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34465,7 +34471,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34671,7 +34677,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34877,7 +34883,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35289,7 +35295,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35495,7 +35501,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35701,7 +35707,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35907,7 +35913,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36525,7 +36531,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36731,7 +36737,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36937,7 +36943,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37143,7 +37149,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37224,7 +37230,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ174">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR174">
         <v>1.03</v>
@@ -37555,7 +37561,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -38173,7 +38179,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38251,7 +38257,7 @@
         <v>0.75</v>
       </c>
       <c r="AP179">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ179">
         <v>1.08</v>
@@ -38379,7 +38385,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38585,7 +38591,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38997,7 +39003,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39821,7 +39827,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40233,7 +40239,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40645,7 +40651,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41263,7 +41269,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41341,7 +41347,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP194">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ194">
         <v>1</v>
@@ -41881,7 +41887,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42293,7 +42299,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42499,7 +42505,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42705,7 +42711,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -42783,7 +42789,7 @@
         <v>0.78</v>
       </c>
       <c r="AP201">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ201">
         <v>0.58</v>
@@ -43117,7 +43123,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43404,7 +43410,7 @@
         <v>2</v>
       </c>
       <c r="AQ204">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR204">
         <v>1.51</v>
@@ -43529,7 +43535,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43941,7 +43947,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44147,7 +44153,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44765,7 +44771,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45383,7 +45389,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45589,7 +45595,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45795,7 +45801,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -46001,7 +46007,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46207,7 +46213,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46619,7 +46625,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46825,7 +46831,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47237,7 +47243,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47318,7 +47324,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ223">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR223">
         <v>1.8</v>
@@ -47521,7 +47527,7 @@
         <v>0.64</v>
       </c>
       <c r="AP224">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ224">
         <v>0.58</v>
@@ -47649,7 +47655,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47855,7 +47861,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -48267,7 +48273,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48473,7 +48479,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48885,7 +48891,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49091,7 +49097,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49297,7 +49303,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49503,7 +49509,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -49915,7 +49921,7 @@
         <v>240</v>
       </c>
       <c r="P236" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q236">
         <v>1.91</v>
@@ -50533,7 +50539,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -50896,6 +50902,212 @@
       </c>
       <c r="BP240">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="241" spans="1:68">
+      <c r="A241" s="1">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>7492389</v>
+      </c>
+      <c r="C241" t="s">
+        <v>68</v>
+      </c>
+      <c r="D241" t="s">
+        <v>69</v>
+      </c>
+      <c r="E241" s="2">
+        <v>45702.69791666666</v>
+      </c>
+      <c r="F241">
+        <v>25</v>
+      </c>
+      <c r="G241" t="s">
+        <v>74</v>
+      </c>
+      <c r="H241" t="s">
+        <v>84</v>
+      </c>
+      <c r="I241">
+        <v>1</v>
+      </c>
+      <c r="J241">
+        <v>1</v>
+      </c>
+      <c r="K241">
+        <v>2</v>
+      </c>
+      <c r="L241">
+        <v>3</v>
+      </c>
+      <c r="M241">
+        <v>2</v>
+      </c>
+      <c r="N241">
+        <v>5</v>
+      </c>
+      <c r="O241" t="s">
+        <v>244</v>
+      </c>
+      <c r="P241" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q241">
+        <v>2.5</v>
+      </c>
+      <c r="R241">
+        <v>2.05</v>
+      </c>
+      <c r="S241">
+        <v>5.5</v>
+      </c>
+      <c r="T241">
+        <v>1.5</v>
+      </c>
+      <c r="U241">
+        <v>2.5</v>
+      </c>
+      <c r="V241">
+        <v>3.5</v>
+      </c>
+      <c r="W241">
+        <v>1.29</v>
+      </c>
+      <c r="X241">
+        <v>11</v>
+      </c>
+      <c r="Y241">
+        <v>1.05</v>
+      </c>
+      <c r="Z241">
+        <v>1.76</v>
+      </c>
+      <c r="AA241">
+        <v>3.71</v>
+      </c>
+      <c r="AB241">
+        <v>5.1</v>
+      </c>
+      <c r="AC241">
+        <v>1.07</v>
+      </c>
+      <c r="AD241">
+        <v>9.5</v>
+      </c>
+      <c r="AE241">
+        <v>1.38</v>
+      </c>
+      <c r="AF241">
+        <v>3.1</v>
+      </c>
+      <c r="AG241">
+        <v>2.1</v>
+      </c>
+      <c r="AH241">
+        <v>1.67</v>
+      </c>
+      <c r="AI241">
+        <v>2.1</v>
+      </c>
+      <c r="AJ241">
+        <v>1.67</v>
+      </c>
+      <c r="AK241">
+        <v>1.19</v>
+      </c>
+      <c r="AL241">
+        <v>1.29</v>
+      </c>
+      <c r="AM241">
+        <v>1.98</v>
+      </c>
+      <c r="AN241">
+        <v>1.82</v>
+      </c>
+      <c r="AO241">
+        <v>1.17</v>
+      </c>
+      <c r="AP241">
+        <v>1.92</v>
+      </c>
+      <c r="AQ241">
+        <v>1.08</v>
+      </c>
+      <c r="AR241">
+        <v>1.74</v>
+      </c>
+      <c r="AS241">
+        <v>1.08</v>
+      </c>
+      <c r="AT241">
+        <v>2.82</v>
+      </c>
+      <c r="AU241">
+        <v>7</v>
+      </c>
+      <c r="AV241">
+        <v>5</v>
+      </c>
+      <c r="AW241">
+        <v>16</v>
+      </c>
+      <c r="AX241">
+        <v>3</v>
+      </c>
+      <c r="AY241">
+        <v>29</v>
+      </c>
+      <c r="AZ241">
+        <v>8</v>
+      </c>
+      <c r="BA241">
+        <v>8</v>
+      </c>
+      <c r="BB241">
+        <v>2</v>
+      </c>
+      <c r="BC241">
+        <v>10</v>
+      </c>
+      <c r="BD241">
+        <v>1.48</v>
+      </c>
+      <c r="BE241">
+        <v>6.75</v>
+      </c>
+      <c r="BF241">
+        <v>2.95</v>
+      </c>
+      <c r="BG241">
+        <v>1.44</v>
+      </c>
+      <c r="BH241">
+        <v>2.55</v>
+      </c>
+      <c r="BI241">
+        <v>1.75</v>
+      </c>
+      <c r="BJ241">
+        <v>1.95</v>
+      </c>
+      <c r="BK241">
+        <v>2.2</v>
+      </c>
+      <c r="BL241">
+        <v>1.58</v>
+      </c>
+      <c r="BM241">
+        <v>2.9</v>
+      </c>
+      <c r="BN241">
+        <v>1.35</v>
+      </c>
+      <c r="BO241">
+        <v>3.9</v>
+      </c>
+      <c r="BP241">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="364">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -751,6 +751,9 @@
     <t>['20', '70', '90']</t>
   </si>
   <si>
+    <t>['6', '87']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1100,6 +1103,9 @@
   </si>
   <si>
     <t>['37', '65']</t>
+  </si>
+  <si>
+    <t>['13', '64']</t>
   </si>
 </sst>
 </file>
@@ -1461,7 +1467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP241"/>
+  <dimension ref="A1:BP244"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1717,7 +1723,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2335,7 +2341,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2413,7 +2419,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ5">
         <v>1.08</v>
@@ -2541,7 +2547,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2828,7 +2834,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ7">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3159,7 +3165,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3237,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ9">
         <v>0.33</v>
@@ -3365,7 +3371,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3777,7 +3783,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q12">
         <v>3.75</v>
@@ -3983,7 +3989,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4189,7 +4195,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -5219,7 +5225,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5631,7 +5637,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5837,7 +5843,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6249,7 +6255,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6536,7 +6542,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ25">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR25">
         <v>1.74</v>
@@ -6661,7 +6667,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6739,7 +6745,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ26">
         <v>1.55</v>
@@ -6867,7 +6873,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7073,7 +7079,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7279,7 +7285,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7360,7 +7366,7 @@
         <v>1</v>
       </c>
       <c r="AQ29">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR29">
         <v>1.56</v>
@@ -7897,7 +7903,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8387,7 +8393,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ34">
         <v>0.33</v>
@@ -8721,7 +8727,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -8799,7 +8805,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
         <v>1.5</v>
@@ -9133,7 +9139,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9214,7 +9220,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ38">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR38">
         <v>1.24</v>
@@ -9339,7 +9345,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9545,7 +9551,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9751,7 +9757,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9829,10 +9835,10 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ41">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR41">
         <v>1.35</v>
@@ -9957,7 +9963,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10163,7 +10169,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10656,7 +10662,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ45">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR45">
         <v>1.23</v>
@@ -10781,7 +10787,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10987,7 +10993,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11193,7 +11199,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11605,7 +11611,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11811,7 +11817,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -11889,7 +11895,7 @@
         <v>0.33</v>
       </c>
       <c r="AP51">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ51">
         <v>0.58</v>
@@ -12095,7 +12101,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ52">
         <v>0.83</v>
@@ -12223,7 +12229,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12429,7 +12435,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12635,7 +12641,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12841,7 +12847,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13047,7 +13053,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13128,7 +13134,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ57">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR57">
         <v>1.29</v>
@@ -13871,7 +13877,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -13952,7 +13958,7 @@
         <v>1</v>
       </c>
       <c r="AQ61">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR61">
         <v>1.23</v>
@@ -14695,7 +14701,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14773,7 +14779,7 @@
         <v>1.5</v>
       </c>
       <c r="AP65">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ65">
         <v>1.25</v>
@@ -14901,7 +14907,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15107,7 +15113,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15188,7 +15194,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ67">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR67">
         <v>1.09</v>
@@ -15313,7 +15319,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q68">
         <v>2.2</v>
@@ -15391,7 +15397,7 @@
         <v>2.33</v>
       </c>
       <c r="AP68">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ68">
         <v>1.08</v>
@@ -15725,7 +15731,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -16343,7 +16349,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16627,7 +16633,7 @@
         <v>1.33</v>
       </c>
       <c r="AP74">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ74">
         <v>1.08</v>
@@ -16961,7 +16967,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17042,7 +17048,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ76">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR76">
         <v>0.85</v>
@@ -17167,7 +17173,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17373,7 +17379,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17579,7 +17585,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17991,7 +17997,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18278,7 +18284,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ82">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR82">
         <v>1.1</v>
@@ -18815,7 +18821,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -18893,10 +18899,10 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ85">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR85">
         <v>1.74</v>
@@ -19305,7 +19311,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ87">
         <v>1.25</v>
@@ -19433,7 +19439,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19639,7 +19645,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19845,7 +19851,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20051,7 +20057,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20338,7 +20344,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ92">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR92">
         <v>1.25</v>
@@ -20463,7 +20469,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20541,10 +20547,10 @@
         <v>1.75</v>
       </c>
       <c r="AP93">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ93">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR93">
         <v>1.71</v>
@@ -20669,7 +20675,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20875,7 +20881,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -21159,7 +21165,7 @@
         <v>1.25</v>
       </c>
       <c r="AP96">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ96">
         <v>0.58</v>
@@ -21287,7 +21293,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21493,7 +21499,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21699,7 +21705,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22317,7 +22323,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22729,7 +22735,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22935,7 +22941,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23141,7 +23147,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23965,7 +23971,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24043,10 +24049,10 @@
         <v>1</v>
       </c>
       <c r="AP110">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ110">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR110">
         <v>1.55</v>
@@ -24171,7 +24177,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24377,7 +24383,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24583,7 +24589,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24789,7 +24795,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25201,7 +25207,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25279,7 +25285,7 @@
         <v>0.8</v>
       </c>
       <c r="AP116">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ116">
         <v>1.08</v>
@@ -25407,7 +25413,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25613,7 +25619,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25694,7 +25700,7 @@
         <v>2</v>
       </c>
       <c r="AQ118">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR118">
         <v>1.7</v>
@@ -26106,7 +26112,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ120">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR120">
         <v>1.62</v>
@@ -26231,7 +26237,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26515,7 +26521,7 @@
         <v>2.2</v>
       </c>
       <c r="AP122">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ122">
         <v>1.75</v>
@@ -26643,7 +26649,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26849,7 +26855,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26930,7 +26936,7 @@
         <v>1</v>
       </c>
       <c r="AQ124">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR124">
         <v>1.24</v>
@@ -27055,7 +27061,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27261,7 +27267,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27751,7 +27757,7 @@
         <v>1.83</v>
       </c>
       <c r="AP128">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ128">
         <v>1.5</v>
@@ -27879,7 +27885,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -28372,7 +28378,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ131">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR131">
         <v>1.36</v>
@@ -28781,7 +28787,7 @@
         <v>1.5</v>
       </c>
       <c r="AP133">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ133">
         <v>1.08</v>
@@ -29115,7 +29121,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29321,7 +29327,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29402,7 +29408,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ136">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR136">
         <v>1.14</v>
@@ -29733,7 +29739,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29939,7 +29945,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30429,7 +30435,7 @@
         <v>1.33</v>
       </c>
       <c r="AP141">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ141">
         <v>1.55</v>
@@ -30763,7 +30769,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30969,7 +30975,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31256,7 +31262,7 @@
         <v>2</v>
       </c>
       <c r="AQ145">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR145">
         <v>1.69</v>
@@ -31381,7 +31387,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31587,7 +31593,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31999,7 +32005,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32411,7 +32417,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32617,7 +32623,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32698,7 +32704,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ152">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR152">
         <v>1.05</v>
@@ -32823,7 +32829,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -33235,7 +33241,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -33316,7 +33322,7 @@
         <v>1</v>
       </c>
       <c r="AQ155">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR155">
         <v>1.24</v>
@@ -33931,7 +33937,7 @@
         <v>1.5</v>
       </c>
       <c r="AP158">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ158">
         <v>1.25</v>
@@ -34059,7 +34065,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34137,7 +34143,7 @@
         <v>2.33</v>
       </c>
       <c r="AP159">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ159">
         <v>2.25</v>
@@ -34471,7 +34477,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34677,7 +34683,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34758,7 +34764,7 @@
         <v>1</v>
       </c>
       <c r="AQ162">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR162">
         <v>1.24</v>
@@ -34883,7 +34889,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35295,7 +35301,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35376,7 +35382,7 @@
         <v>1</v>
       </c>
       <c r="AQ165">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR165">
         <v>1.48</v>
@@ -35501,7 +35507,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35579,7 +35585,7 @@
         <v>1.5</v>
       </c>
       <c r="AP166">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ166">
         <v>1.08</v>
@@ -35707,7 +35713,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35913,7 +35919,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36531,7 +36537,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36737,7 +36743,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36943,7 +36949,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37021,7 +37027,7 @@
         <v>2.11</v>
       </c>
       <c r="AP173">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ173">
         <v>2.08</v>
@@ -37149,7 +37155,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37561,7 +37567,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -37845,7 +37851,7 @@
         <v>0.5</v>
       </c>
       <c r="AP177">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ177">
         <v>1</v>
@@ -38179,7 +38185,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38260,7 +38266,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ179">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR179">
         <v>1.61</v>
@@ -38385,7 +38391,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38591,7 +38597,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38672,7 +38678,7 @@
         <v>2</v>
       </c>
       <c r="AQ181">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR181">
         <v>1.57</v>
@@ -39003,7 +39009,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39084,7 +39090,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ183">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR183">
         <v>1.19</v>
@@ -39827,7 +39833,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39905,7 +39911,7 @@
         <v>0.6</v>
       </c>
       <c r="AP187">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ187">
         <v>0.58</v>
@@ -40239,7 +40245,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40651,7 +40657,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -40729,10 +40735,10 @@
         <v>0.89</v>
       </c>
       <c r="AP191">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ191">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR191">
         <v>1.6</v>
@@ -41269,7 +41275,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41556,7 +41562,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ195">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR195">
         <v>1.59</v>
@@ -41887,7 +41893,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42171,7 +42177,7 @@
         <v>1.89</v>
       </c>
       <c r="AP198">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ198">
         <v>1.75</v>
@@ -42299,7 +42305,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42505,7 +42511,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42711,7 +42717,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -43123,7 +43129,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43201,10 +43207,10 @@
         <v>2.3</v>
       </c>
       <c r="AP203">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ203">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR203">
         <v>1.78</v>
@@ -43535,7 +43541,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43947,7 +43953,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44153,7 +44159,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44646,7 +44652,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ210">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR210">
         <v>1.04</v>
@@ -44771,7 +44777,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45389,7 +45395,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45467,7 +45473,7 @@
         <v>0.8</v>
       </c>
       <c r="AP214">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ214">
         <v>0.67</v>
@@ -45595,7 +45601,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45801,7 +45807,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -46007,7 +46013,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46085,7 +46091,7 @@
         <v>1.5</v>
       </c>
       <c r="AP217">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ217">
         <v>1.5</v>
@@ -46213,7 +46219,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46294,7 +46300,7 @@
         <v>1</v>
       </c>
       <c r="AQ218">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR218">
         <v>1.35</v>
@@ -46625,7 +46631,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46831,7 +46837,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47118,7 +47124,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ222">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR222">
         <v>1.17</v>
@@ -47243,7 +47249,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47321,7 +47327,7 @@
         <v>1.18</v>
       </c>
       <c r="AP223">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ223">
         <v>1.08</v>
@@ -47655,7 +47661,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47861,7 +47867,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -48145,7 +48151,7 @@
         <v>2.6</v>
       </c>
       <c r="AP227">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ227">
         <v>2.25</v>
@@ -48273,7 +48279,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48354,7 +48360,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ228">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR228">
         <v>1.58</v>
@@ -48479,7 +48485,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48891,7 +48897,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49097,7 +49103,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49303,7 +49309,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49509,7 +49515,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -49921,7 +49927,7 @@
         <v>240</v>
       </c>
       <c r="P236" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q236">
         <v>1.91</v>
@@ -49999,7 +50005,7 @@
         <v>0.64</v>
       </c>
       <c r="AP236">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ236">
         <v>0.58</v>
@@ -50539,7 +50545,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -50951,7 +50957,7 @@
         <v>244</v>
       </c>
       <c r="P241" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q241">
         <v>2.5</v>
@@ -51108,6 +51114,624 @@
       </c>
       <c r="BP241">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="242" spans="1:68">
+      <c r="A242" s="1">
+        <v>241</v>
+      </c>
+      <c r="B242">
+        <v>7492388</v>
+      </c>
+      <c r="C242" t="s">
+        <v>68</v>
+      </c>
+      <c r="D242" t="s">
+        <v>69</v>
+      </c>
+      <c r="E242" s="2">
+        <v>45703.45833333334</v>
+      </c>
+      <c r="F242">
+        <v>25</v>
+      </c>
+      <c r="G242" t="s">
+        <v>89</v>
+      </c>
+      <c r="H242" t="s">
+        <v>76</v>
+      </c>
+      <c r="I242">
+        <v>0</v>
+      </c>
+      <c r="J242">
+        <v>0</v>
+      </c>
+      <c r="K242">
+        <v>0</v>
+      </c>
+      <c r="L242">
+        <v>0</v>
+      </c>
+      <c r="M242">
+        <v>0</v>
+      </c>
+      <c r="N242">
+        <v>0</v>
+      </c>
+      <c r="O242" t="s">
+        <v>92</v>
+      </c>
+      <c r="P242" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q242">
+        <v>1.91</v>
+      </c>
+      <c r="R242">
+        <v>2.5</v>
+      </c>
+      <c r="S242">
+        <v>6.5</v>
+      </c>
+      <c r="T242">
+        <v>1.29</v>
+      </c>
+      <c r="U242">
+        <v>3.5</v>
+      </c>
+      <c r="V242">
+        <v>2.38</v>
+      </c>
+      <c r="W242">
+        <v>1.53</v>
+      </c>
+      <c r="X242">
+        <v>5.5</v>
+      </c>
+      <c r="Y242">
+        <v>1.14</v>
+      </c>
+      <c r="Z242">
+        <v>1.4</v>
+      </c>
+      <c r="AA242">
+        <v>5.3</v>
+      </c>
+      <c r="AB242">
+        <v>7.6</v>
+      </c>
+      <c r="AC242">
+        <v>1.02</v>
+      </c>
+      <c r="AD242">
+        <v>19</v>
+      </c>
+      <c r="AE242">
+        <v>1.19</v>
+      </c>
+      <c r="AF242">
+        <v>4.75</v>
+      </c>
+      <c r="AG242">
+        <v>1.57</v>
+      </c>
+      <c r="AH242">
+        <v>2.31</v>
+      </c>
+      <c r="AI242">
+        <v>1.8</v>
+      </c>
+      <c r="AJ242">
+        <v>1.95</v>
+      </c>
+      <c r="AK242">
+        <v>1.1</v>
+      </c>
+      <c r="AL242">
+        <v>1.17</v>
+      </c>
+      <c r="AM242">
+        <v>2.85</v>
+      </c>
+      <c r="AN242">
+        <v>2.09</v>
+      </c>
+      <c r="AO242">
+        <v>0.82</v>
+      </c>
+      <c r="AP242">
+        <v>2</v>
+      </c>
+      <c r="AQ242">
+        <v>0.83</v>
+      </c>
+      <c r="AR242">
+        <v>1.88</v>
+      </c>
+      <c r="AS242">
+        <v>1.07</v>
+      </c>
+      <c r="AT242">
+        <v>2.95</v>
+      </c>
+      <c r="AU242">
+        <v>3</v>
+      </c>
+      <c r="AV242">
+        <v>0</v>
+      </c>
+      <c r="AW242">
+        <v>7</v>
+      </c>
+      <c r="AX242">
+        <v>4</v>
+      </c>
+      <c r="AY242">
+        <v>11</v>
+      </c>
+      <c r="AZ242">
+        <v>6</v>
+      </c>
+      <c r="BA242">
+        <v>8</v>
+      </c>
+      <c r="BB242">
+        <v>2</v>
+      </c>
+      <c r="BC242">
+        <v>10</v>
+      </c>
+      <c r="BD242">
+        <v>1.27</v>
+      </c>
+      <c r="BE242">
+        <v>7.5</v>
+      </c>
+      <c r="BF242">
+        <v>4.1</v>
+      </c>
+      <c r="BG242">
+        <v>1.38</v>
+      </c>
+      <c r="BH242">
+        <v>2.75</v>
+      </c>
+      <c r="BI242">
+        <v>1.65</v>
+      </c>
+      <c r="BJ242">
+        <v>2.08</v>
+      </c>
+      <c r="BK242">
+        <v>2.04</v>
+      </c>
+      <c r="BL242">
+        <v>1.68</v>
+      </c>
+      <c r="BM242">
+        <v>2.65</v>
+      </c>
+      <c r="BN242">
+        <v>1.41</v>
+      </c>
+      <c r="BO242">
+        <v>3.45</v>
+      </c>
+      <c r="BP242">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="243" spans="1:68">
+      <c r="A243" s="1">
+        <v>242</v>
+      </c>
+      <c r="B243">
+        <v>7492393</v>
+      </c>
+      <c r="C243" t="s">
+        <v>68</v>
+      </c>
+      <c r="D243" t="s">
+        <v>69</v>
+      </c>
+      <c r="E243" s="2">
+        <v>45703.58333333334</v>
+      </c>
+      <c r="F243">
+        <v>25</v>
+      </c>
+      <c r="G243" t="s">
+        <v>77</v>
+      </c>
+      <c r="H243" t="s">
+        <v>85</v>
+      </c>
+      <c r="I243">
+        <v>1</v>
+      </c>
+      <c r="J243">
+        <v>1</v>
+      </c>
+      <c r="K243">
+        <v>2</v>
+      </c>
+      <c r="L243">
+        <v>2</v>
+      </c>
+      <c r="M243">
+        <v>2</v>
+      </c>
+      <c r="N243">
+        <v>4</v>
+      </c>
+      <c r="O243" t="s">
+        <v>245</v>
+      </c>
+      <c r="P243" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q243">
+        <v>3.4</v>
+      </c>
+      <c r="R243">
+        <v>2.05</v>
+      </c>
+      <c r="S243">
+        <v>3.4</v>
+      </c>
+      <c r="T243">
+        <v>1.44</v>
+      </c>
+      <c r="U243">
+        <v>2.63</v>
+      </c>
+      <c r="V243">
+        <v>3.25</v>
+      </c>
+      <c r="W243">
+        <v>1.33</v>
+      </c>
+      <c r="X243">
+        <v>9</v>
+      </c>
+      <c r="Y243">
+        <v>1.07</v>
+      </c>
+      <c r="Z243">
+        <v>2.88</v>
+      </c>
+      <c r="AA243">
+        <v>3.3</v>
+      </c>
+      <c r="AB243">
+        <v>2.6</v>
+      </c>
+      <c r="AC243">
+        <v>1.08</v>
+      </c>
+      <c r="AD243">
+        <v>9</v>
+      </c>
+      <c r="AE243">
+        <v>1.38</v>
+      </c>
+      <c r="AF243">
+        <v>3.1</v>
+      </c>
+      <c r="AG243">
+        <v>2.02</v>
+      </c>
+      <c r="AH243">
+        <v>1.8</v>
+      </c>
+      <c r="AI243">
+        <v>1.8</v>
+      </c>
+      <c r="AJ243">
+        <v>1.95</v>
+      </c>
+      <c r="AK243">
+        <v>1.49</v>
+      </c>
+      <c r="AL243">
+        <v>1.33</v>
+      </c>
+      <c r="AM243">
+        <v>1.43</v>
+      </c>
+      <c r="AN243">
+        <v>2</v>
+      </c>
+      <c r="AO243">
+        <v>2.25</v>
+      </c>
+      <c r="AP243">
+        <v>1.92</v>
+      </c>
+      <c r="AQ243">
+        <v>2.15</v>
+      </c>
+      <c r="AR243">
+        <v>1.63</v>
+      </c>
+      <c r="AS243">
+        <v>1.17</v>
+      </c>
+      <c r="AT243">
+        <v>2.8</v>
+      </c>
+      <c r="AU243">
+        <v>6</v>
+      </c>
+      <c r="AV243">
+        <v>3</v>
+      </c>
+      <c r="AW243">
+        <v>7</v>
+      </c>
+      <c r="AX243">
+        <v>3</v>
+      </c>
+      <c r="AY243">
+        <v>14</v>
+      </c>
+      <c r="AZ243">
+        <v>7</v>
+      </c>
+      <c r="BA243">
+        <v>7</v>
+      </c>
+      <c r="BB243">
+        <v>1</v>
+      </c>
+      <c r="BC243">
+        <v>8</v>
+      </c>
+      <c r="BD243">
+        <v>1.9</v>
+      </c>
+      <c r="BE243">
+        <v>6.4</v>
+      </c>
+      <c r="BF243">
+        <v>2.08</v>
+      </c>
+      <c r="BG243">
+        <v>1.32</v>
+      </c>
+      <c r="BH243">
+        <v>3</v>
+      </c>
+      <c r="BI243">
+        <v>1.56</v>
+      </c>
+      <c r="BJ243">
+        <v>2.23</v>
+      </c>
+      <c r="BK243">
+        <v>1.9</v>
+      </c>
+      <c r="BL243">
+        <v>1.78</v>
+      </c>
+      <c r="BM243">
+        <v>2.4</v>
+      </c>
+      <c r="BN243">
+        <v>1.49</v>
+      </c>
+      <c r="BO243">
+        <v>3.15</v>
+      </c>
+      <c r="BP243">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="244" spans="1:68">
+      <c r="A244" s="1">
+        <v>243</v>
+      </c>
+      <c r="B244">
+        <v>7492394</v>
+      </c>
+      <c r="C244" t="s">
+        <v>68</v>
+      </c>
+      <c r="D244" t="s">
+        <v>69</v>
+      </c>
+      <c r="E244" s="2">
+        <v>45703.69791666666</v>
+      </c>
+      <c r="F244">
+        <v>25</v>
+      </c>
+      <c r="G244" t="s">
+        <v>73</v>
+      </c>
+      <c r="H244" t="s">
+        <v>75</v>
+      </c>
+      <c r="I244">
+        <v>0</v>
+      </c>
+      <c r="J244">
+        <v>0</v>
+      </c>
+      <c r="K244">
+        <v>0</v>
+      </c>
+      <c r="L244">
+        <v>1</v>
+      </c>
+      <c r="M244">
+        <v>0</v>
+      </c>
+      <c r="N244">
+        <v>1</v>
+      </c>
+      <c r="O244" t="s">
+        <v>136</v>
+      </c>
+      <c r="P244" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q244">
+        <v>1.83</v>
+      </c>
+      <c r="R244">
+        <v>2.5</v>
+      </c>
+      <c r="S244">
+        <v>7</v>
+      </c>
+      <c r="T244">
+        <v>1.3</v>
+      </c>
+      <c r="U244">
+        <v>3.4</v>
+      </c>
+      <c r="V244">
+        <v>2.38</v>
+      </c>
+      <c r="W244">
+        <v>1.53</v>
+      </c>
+      <c r="X244">
+        <v>6</v>
+      </c>
+      <c r="Y244">
+        <v>1.13</v>
+      </c>
+      <c r="Z244">
+        <v>1.38</v>
+      </c>
+      <c r="AA244">
+        <v>5.2</v>
+      </c>
+      <c r="AB244">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AC244">
+        <v>1.02</v>
+      </c>
+      <c r="AD244">
+        <v>17</v>
+      </c>
+      <c r="AE244">
+        <v>1.19</v>
+      </c>
+      <c r="AF244">
+        <v>4.75</v>
+      </c>
+      <c r="AG244">
+        <v>1.61</v>
+      </c>
+      <c r="AH244">
+        <v>2.2</v>
+      </c>
+      <c r="AI244">
+        <v>1.91</v>
+      </c>
+      <c r="AJ244">
+        <v>1.91</v>
+      </c>
+      <c r="AK244">
+        <v>1.08</v>
+      </c>
+      <c r="AL244">
+        <v>1.17</v>
+      </c>
+      <c r="AM244">
+        <v>3</v>
+      </c>
+      <c r="AN244">
+        <v>1.75</v>
+      </c>
+      <c r="AO244">
+        <v>1.08</v>
+      </c>
+      <c r="AP244">
+        <v>1.85</v>
+      </c>
+      <c r="AQ244">
+        <v>1</v>
+      </c>
+      <c r="AR244">
+        <v>1.7</v>
+      </c>
+      <c r="AS244">
+        <v>1.09</v>
+      </c>
+      <c r="AT244">
+        <v>2.79</v>
+      </c>
+      <c r="AU244">
+        <v>4</v>
+      </c>
+      <c r="AV244">
+        <v>3</v>
+      </c>
+      <c r="AW244">
+        <v>15</v>
+      </c>
+      <c r="AX244">
+        <v>5</v>
+      </c>
+      <c r="AY244">
+        <v>26</v>
+      </c>
+      <c r="AZ244">
+        <v>9</v>
+      </c>
+      <c r="BA244">
+        <v>10</v>
+      </c>
+      <c r="BB244">
+        <v>7</v>
+      </c>
+      <c r="BC244">
+        <v>17</v>
+      </c>
+      <c r="BD244">
+        <v>1.21</v>
+      </c>
+      <c r="BE244">
+        <v>8</v>
+      </c>
+      <c r="BF244">
+        <v>4.8</v>
+      </c>
+      <c r="BG244">
+        <v>1.27</v>
+      </c>
+      <c r="BH244">
+        <v>3.3</v>
+      </c>
+      <c r="BI244">
+        <v>1.47</v>
+      </c>
+      <c r="BJ244">
+        <v>2.48</v>
+      </c>
+      <c r="BK244">
+        <v>1.76</v>
+      </c>
+      <c r="BL244">
+        <v>1.94</v>
+      </c>
+      <c r="BM244">
+        <v>2.17</v>
+      </c>
+      <c r="BN244">
+        <v>1.6</v>
+      </c>
+      <c r="BO244">
+        <v>2.75</v>
+      </c>
+      <c r="BP244">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="366">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -754,6 +754,9 @@
     <t>['6', '87']</t>
   </si>
   <si>
+    <t>['19', '65', '90']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1106,6 +1109,9 @@
   </si>
   <si>
     <t>['13', '64']</t>
+  </si>
+  <si>
+    <t>['41', '66']</t>
   </si>
 </sst>
 </file>
@@ -1467,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP244"/>
+  <dimension ref="A1:BP249"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1723,7 +1729,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1804,7 +1810,7 @@
         <v>1</v>
       </c>
       <c r="AQ2">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2007,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ3">
         <v>1.5</v>
@@ -2341,7 +2347,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2547,7 +2553,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -3040,7 +3046,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ8">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3165,7 +3171,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3371,7 +3377,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3655,10 +3661,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ11">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3783,7 +3789,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q12">
         <v>3.75</v>
@@ -3861,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ12">
         <v>1.75</v>
@@ -3989,7 +3995,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4067,7 +4073,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ13">
         <v>1.55</v>
@@ -4195,7 +4201,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4273,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ14">
         <v>1.25</v>
@@ -4482,7 +4488,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ15">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4685,7 +4691,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ16">
         <v>0.33</v>
@@ -5225,7 +5231,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5306,7 +5312,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ19">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5512,7 +5518,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ20">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR20">
         <v>1.16</v>
@@ -5637,7 +5643,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5843,7 +5849,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6255,7 +6261,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6336,7 +6342,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ24">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR24">
         <v>2.04</v>
@@ -6667,7 +6673,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6873,7 +6879,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7079,7 +7085,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7157,7 +7163,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ28">
         <v>0.58</v>
@@ -7285,7 +7291,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7569,10 +7575,10 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ30">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR30">
         <v>1.66</v>
@@ -7775,10 +7781,10 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ31">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR31">
         <v>0.95</v>
@@ -7903,7 +7909,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8602,7 +8608,7 @@
         <v>1</v>
       </c>
       <c r="AQ35">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR35">
         <v>1.23</v>
@@ -8727,7 +8733,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -9014,7 +9020,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ37">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR37">
         <v>1.46</v>
@@ -9139,7 +9145,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9345,7 +9351,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9423,10 +9429,10 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ39">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR39">
         <v>1.18</v>
@@ -9551,7 +9557,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9629,7 +9635,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ40">
         <v>1.08</v>
@@ -9757,7 +9763,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9963,7 +9969,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10044,7 +10050,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ42">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR42">
         <v>1.4</v>
@@ -10169,7 +10175,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10659,7 +10665,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ45">
         <v>2.15</v>
@@ -10787,7 +10793,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10993,7 +10999,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11071,7 +11077,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ47">
         <v>1.75</v>
@@ -11199,7 +11205,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11277,7 +11283,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ48">
         <v>1.5</v>
@@ -11611,7 +11617,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11817,7 +11823,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -11898,7 +11904,7 @@
         <v>2</v>
       </c>
       <c r="AQ51">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR51">
         <v>1.68</v>
@@ -12104,7 +12110,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ52">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR52">
         <v>1.92</v>
@@ -12229,7 +12235,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12307,10 +12313,10 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ53">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR53">
         <v>1.05</v>
@@ -12435,7 +12441,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12641,7 +12647,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12847,7 +12853,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13053,7 +13059,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13877,7 +13883,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -13955,7 +13961,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ61">
         <v>0.83</v>
@@ -14164,7 +14170,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ62">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR62">
         <v>1.6</v>
@@ -14573,10 +14579,10 @@
         <v>0.33</v>
       </c>
       <c r="AP64">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ64">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR64">
         <v>1.02</v>
@@ -14701,7 +14707,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14907,7 +14913,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15113,7 +15119,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15191,7 +15197,7 @@
         <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ67">
         <v>0.83</v>
@@ -15319,7 +15325,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q68">
         <v>2.2</v>
@@ -15400,7 +15406,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ68">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR68">
         <v>1.44</v>
@@ -15731,7 +15737,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -15809,10 +15815,10 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ70">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR70">
         <v>0.9399999999999999</v>
@@ -16015,7 +16021,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ71">
         <v>1.55</v>
@@ -16349,7 +16355,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16839,7 +16845,7 @@
         <v>1</v>
       </c>
       <c r="AP75">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ75">
         <v>1.75</v>
@@ -16967,7 +16973,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17173,7 +17179,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17379,7 +17385,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17585,7 +17591,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17872,7 +17878,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ80">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR80">
         <v>2.02</v>
@@ -17997,7 +18003,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18281,7 +18287,7 @@
         <v>1.33</v>
       </c>
       <c r="AP82">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ82">
         <v>0.83</v>
@@ -18490,7 +18496,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ83">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR83">
         <v>1.23</v>
@@ -18696,7 +18702,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ84">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR84">
         <v>1.49</v>
@@ -18821,7 +18827,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19105,10 +19111,10 @@
         <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ86">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR86">
         <v>1.33</v>
@@ -19439,7 +19445,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19517,7 +19523,7 @@
         <v>0.2</v>
       </c>
       <c r="AP88">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ88">
         <v>0.33</v>
@@ -19645,7 +19651,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19851,7 +19857,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -19929,10 +19935,10 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR90">
         <v>1.56</v>
@@ -20057,7 +20063,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20469,7 +20475,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20675,7 +20681,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20881,7 +20887,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -20962,7 +20968,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ95">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR95">
         <v>0.91</v>
@@ -21293,7 +21299,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21371,7 +21377,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ97">
         <v>0.67</v>
@@ -21499,7 +21505,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21705,7 +21711,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22198,7 +22204,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ101">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR101">
         <v>1.42</v>
@@ -22323,7 +22329,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22401,7 +22407,7 @@
         <v>2</v>
       </c>
       <c r="AP102">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ102">
         <v>1.75</v>
@@ -22607,7 +22613,7 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ103">
         <v>1.55</v>
@@ -22735,7 +22741,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22941,7 +22947,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23147,7 +23153,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23228,7 +23234,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ106">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR106">
         <v>1.19</v>
@@ -23640,7 +23646,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ108">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR108">
         <v>0.82</v>
@@ -23843,7 +23849,7 @@
         <v>0.75</v>
       </c>
       <c r="AP109">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ109">
         <v>1.25</v>
@@ -23971,7 +23977,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24177,7 +24183,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24258,7 +24264,7 @@
         <v>1</v>
       </c>
       <c r="AQ111">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR111">
         <v>1.25</v>
@@ -24383,7 +24389,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24464,7 +24470,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ112">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR112">
         <v>1.28</v>
@@ -24589,7 +24595,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24795,7 +24801,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25079,7 +25085,7 @@
         <v>1.17</v>
       </c>
       <c r="AP115">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ115">
         <v>1.08</v>
@@ -25207,7 +25213,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25413,7 +25419,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25619,7 +25625,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25697,7 +25703,7 @@
         <v>0.6</v>
       </c>
       <c r="AP118">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ118">
         <v>1</v>
@@ -25903,7 +25909,7 @@
         <v>1.2</v>
       </c>
       <c r="AP119">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ119">
         <v>1.75</v>
@@ -26237,7 +26243,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26318,7 +26324,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ121">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR121">
         <v>1.14</v>
@@ -26649,7 +26655,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26727,7 +26733,7 @@
         <v>1.67</v>
       </c>
       <c r="AP123">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ123">
         <v>2.08</v>
@@ -26855,7 +26861,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27061,7 +27067,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27267,7 +27273,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27554,7 +27560,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ127">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR127">
         <v>1.54</v>
@@ -27885,7 +27891,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -28172,7 +28178,7 @@
         <v>1</v>
       </c>
       <c r="AQ130">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR130">
         <v>1.48</v>
@@ -28790,7 +28796,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ133">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR133">
         <v>1.55</v>
@@ -29121,7 +29127,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29199,7 +29205,7 @@
         <v>1.2</v>
       </c>
       <c r="AP135">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ135">
         <v>1.25</v>
@@ -29327,7 +29333,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29611,7 +29617,7 @@
         <v>1.5</v>
       </c>
       <c r="AP137">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ137">
         <v>1.75</v>
@@ -29739,7 +29745,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29945,7 +29951,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30769,7 +30775,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30847,7 +30853,7 @@
         <v>1.57</v>
       </c>
       <c r="AP143">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ143">
         <v>1.5</v>
@@ -30975,7 +30981,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31056,7 +31062,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ144">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR144">
         <v>1.48</v>
@@ -31259,7 +31265,7 @@
         <v>0.83</v>
       </c>
       <c r="AP145">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ145">
         <v>0.83</v>
@@ -31387,7 +31393,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31468,7 +31474,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ146">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR146">
         <v>1.08</v>
@@ -31593,7 +31599,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31674,7 +31680,7 @@
         <v>1</v>
       </c>
       <c r="AQ147">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR147">
         <v>1.55</v>
@@ -32005,7 +32011,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32083,7 +32089,7 @@
         <v>0.71</v>
       </c>
       <c r="AP149">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ149">
         <v>1.08</v>
@@ -32417,7 +32423,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32623,7 +32629,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32701,7 +32707,7 @@
         <v>2</v>
       </c>
       <c r="AP152">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ152">
         <v>2.15</v>
@@ -32829,7 +32835,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -32907,7 +32913,7 @@
         <v>0.25</v>
       </c>
       <c r="AP153">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ153">
         <v>0.33</v>
@@ -33241,7 +33247,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -33319,7 +33325,7 @@
         <v>0.43</v>
       </c>
       <c r="AP155">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ155">
         <v>1</v>
@@ -33734,7 +33740,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ157">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR157">
         <v>1.44</v>
@@ -34065,7 +34071,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34146,7 +34152,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ159">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR159">
         <v>1.56</v>
@@ -34477,7 +34483,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34683,7 +34689,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34889,7 +34895,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35301,7 +35307,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35507,7 +35513,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35588,7 +35594,7 @@
         <v>2</v>
       </c>
       <c r="AQ166">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR166">
         <v>1.76</v>
@@ -35713,7 +35719,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35791,7 +35797,7 @@
         <v>1.86</v>
       </c>
       <c r="AP167">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ167">
         <v>1.75</v>
@@ -35919,7 +35925,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -35997,7 +36003,7 @@
         <v>1</v>
       </c>
       <c r="AP168">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ168">
         <v>1.08</v>
@@ -36206,7 +36212,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ169">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR169">
         <v>1.57</v>
@@ -36409,7 +36415,7 @@
         <v>0.88</v>
       </c>
       <c r="AP170">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ170">
         <v>0.58</v>
@@ -36537,7 +36543,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36743,7 +36749,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36824,7 +36830,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ172">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR172">
         <v>1.46</v>
@@ -36949,7 +36955,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37155,7 +37161,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37233,7 +37239,7 @@
         <v>1.22</v>
       </c>
       <c r="AP174">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ174">
         <v>1.08</v>
@@ -37567,7 +37573,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -37645,7 +37651,7 @@
         <v>1.75</v>
       </c>
       <c r="AP176">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ176">
         <v>1.5</v>
@@ -37854,7 +37860,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ177">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR177">
         <v>1.56</v>
@@ -38060,7 +38066,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ178">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR178">
         <v>1.5</v>
@@ -38185,7 +38191,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38391,7 +38397,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38472,7 +38478,7 @@
         <v>1</v>
       </c>
       <c r="AQ180">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR180">
         <v>1.47</v>
@@ -38597,7 +38603,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38675,7 +38681,7 @@
         <v>2.22</v>
       </c>
       <c r="AP181">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ181">
         <v>2.15</v>
@@ -39009,7 +39015,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39087,7 +39093,7 @@
         <v>0.63</v>
       </c>
       <c r="AP183">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ183">
         <v>0.83</v>
@@ -39833,7 +39839,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39914,7 +39920,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ187">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR187">
         <v>1.47</v>
@@ -40117,7 +40123,7 @@
         <v>2</v>
       </c>
       <c r="AP188">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ188">
         <v>2.08</v>
@@ -40245,7 +40251,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40326,7 +40332,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ189">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR189">
         <v>0.97</v>
@@ -40657,7 +40663,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41150,7 +41156,7 @@
         <v>1</v>
       </c>
       <c r="AQ193">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR193">
         <v>1.41</v>
@@ -41275,7 +41281,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41356,7 +41362,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ194">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR194">
         <v>1.66</v>
@@ -41765,7 +41771,7 @@
         <v>1.67</v>
       </c>
       <c r="AP196">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ196">
         <v>1.5</v>
@@ -41893,7 +41899,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42305,7 +42311,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42511,7 +42517,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42717,7 +42723,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -43001,7 +43007,7 @@
         <v>1.56</v>
       </c>
       <c r="AP202">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ202">
         <v>1.55</v>
@@ -43129,7 +43135,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43413,7 +43419,7 @@
         <v>1.2</v>
       </c>
       <c r="AP204">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ204">
         <v>1.08</v>
@@ -43541,7 +43547,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43622,7 +43628,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ205">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR205">
         <v>1.37</v>
@@ -43825,7 +43831,7 @@
         <v>0.3</v>
       </c>
       <c r="AP206">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ206">
         <v>0.33</v>
@@ -43953,7 +43959,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44159,7 +44165,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44240,7 +44246,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ208">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR208">
         <v>1.57</v>
@@ -44777,7 +44783,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45395,7 +45401,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45601,7 +45607,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45679,10 +45685,10 @@
         <v>0.6</v>
       </c>
       <c r="AP215">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ215">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR215">
         <v>1.04</v>
@@ -45807,7 +45813,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -45888,7 +45894,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ216">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR216">
         <v>1.3</v>
@@ -46013,7 +46019,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46219,7 +46225,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46631,7 +46637,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46709,10 +46715,10 @@
         <v>0.64</v>
       </c>
       <c r="AP220">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ220">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR220">
         <v>1.37</v>
@@ -46837,7 +46843,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -46915,7 +46921,7 @@
         <v>0.36</v>
       </c>
       <c r="AP221">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ221">
         <v>0.33</v>
@@ -47121,7 +47127,7 @@
         <v>0.91</v>
       </c>
       <c r="AP222">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AQ222">
         <v>1</v>
@@ -47249,7 +47255,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47536,7 +47542,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ224">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR224">
         <v>1.75</v>
@@ -47661,7 +47667,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47739,10 +47745,10 @@
         <v>1.18</v>
       </c>
       <c r="AP225">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ225">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR225">
         <v>1.48</v>
@@ -47867,7 +47873,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -47945,7 +47951,7 @@
         <v>1.4</v>
       </c>
       <c r="AP226">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ226">
         <v>1.25</v>
@@ -48154,7 +48160,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ227">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR227">
         <v>1.73</v>
@@ -48279,7 +48285,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48485,7 +48491,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48769,10 +48775,10 @@
         <v>2.45</v>
       </c>
       <c r="AP230">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ230">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AR230">
         <v>1.55</v>
@@ -48897,7 +48903,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49103,7 +49109,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49309,7 +49315,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49515,7 +49521,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -49802,7 +49808,7 @@
         <v>1</v>
       </c>
       <c r="AQ235">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR235">
         <v>1.34</v>
@@ -49927,7 +49933,7 @@
         <v>240</v>
       </c>
       <c r="P236" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q236">
         <v>1.91</v>
@@ -50545,7 +50551,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -50957,7 +50963,7 @@
         <v>244</v>
       </c>
       <c r="P241" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q241">
         <v>2.5</v>
@@ -51369,7 +51375,7 @@
         <v>245</v>
       </c>
       <c r="P243" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q243">
         <v>3.4</v>
@@ -51732,6 +51738,1036 @@
       </c>
       <c r="BP244">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="245" spans="1:68">
+      <c r="A245" s="1">
+        <v>244</v>
+      </c>
+      <c r="B245">
+        <v>7492390</v>
+      </c>
+      <c r="C245" t="s">
+        <v>68</v>
+      </c>
+      <c r="D245" t="s">
+        <v>69</v>
+      </c>
+      <c r="E245" s="2">
+        <v>45704.35416666666</v>
+      </c>
+      <c r="F245">
+        <v>25</v>
+      </c>
+      <c r="G245" t="s">
+        <v>83</v>
+      </c>
+      <c r="H245" t="s">
+        <v>88</v>
+      </c>
+      <c r="I245">
+        <v>0</v>
+      </c>
+      <c r="J245">
+        <v>1</v>
+      </c>
+      <c r="K245">
+        <v>1</v>
+      </c>
+      <c r="L245">
+        <v>0</v>
+      </c>
+      <c r="M245">
+        <v>2</v>
+      </c>
+      <c r="N245">
+        <v>2</v>
+      </c>
+      <c r="O245" t="s">
+        <v>92</v>
+      </c>
+      <c r="P245" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q245">
+        <v>2.6</v>
+      </c>
+      <c r="R245">
+        <v>2.2</v>
+      </c>
+      <c r="S245">
+        <v>4.33</v>
+      </c>
+      <c r="T245">
+        <v>1.36</v>
+      </c>
+      <c r="U245">
+        <v>3</v>
+      </c>
+      <c r="V245">
+        <v>2.75</v>
+      </c>
+      <c r="W245">
+        <v>1.4</v>
+      </c>
+      <c r="X245">
+        <v>8</v>
+      </c>
+      <c r="Y245">
+        <v>1.08</v>
+      </c>
+      <c r="Z245">
+        <v>1.98</v>
+      </c>
+      <c r="AA245">
+        <v>3.64</v>
+      </c>
+      <c r="AB245">
+        <v>3.9</v>
+      </c>
+      <c r="AC245">
+        <v>1.05</v>
+      </c>
+      <c r="AD245">
+        <v>12</v>
+      </c>
+      <c r="AE245">
+        <v>1.3</v>
+      </c>
+      <c r="AF245">
+        <v>3.6</v>
+      </c>
+      <c r="AG245">
+        <v>1.87</v>
+      </c>
+      <c r="AH245">
+        <v>1.94</v>
+      </c>
+      <c r="AI245">
+        <v>1.7</v>
+      </c>
+      <c r="AJ245">
+        <v>2.05</v>
+      </c>
+      <c r="AK245">
+        <v>1.26</v>
+      </c>
+      <c r="AL245">
+        <v>1.29</v>
+      </c>
+      <c r="AM245">
+        <v>1.78</v>
+      </c>
+      <c r="AN245">
+        <v>2</v>
+      </c>
+      <c r="AO245">
+        <v>0.58</v>
+      </c>
+      <c r="AP245">
+        <v>1.85</v>
+      </c>
+      <c r="AQ245">
+        <v>0.77</v>
+      </c>
+      <c r="AR245">
+        <v>1.56</v>
+      </c>
+      <c r="AS245">
+        <v>1.33</v>
+      </c>
+      <c r="AT245">
+        <v>2.89</v>
+      </c>
+      <c r="AU245">
+        <v>4</v>
+      </c>
+      <c r="AV245">
+        <v>5</v>
+      </c>
+      <c r="AW245">
+        <v>2</v>
+      </c>
+      <c r="AX245">
+        <v>4</v>
+      </c>
+      <c r="AY245">
+        <v>6</v>
+      </c>
+      <c r="AZ245">
+        <v>10</v>
+      </c>
+      <c r="BA245">
+        <v>2</v>
+      </c>
+      <c r="BB245">
+        <v>1</v>
+      </c>
+      <c r="BC245">
+        <v>3</v>
+      </c>
+      <c r="BD245">
+        <v>1.66</v>
+      </c>
+      <c r="BE245">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF245">
+        <v>2.74</v>
+      </c>
+      <c r="BG245">
+        <v>1.39</v>
+      </c>
+      <c r="BH245">
+        <v>2.67</v>
+      </c>
+      <c r="BI245">
+        <v>1.73</v>
+      </c>
+      <c r="BJ245">
+        <v>1.99</v>
+      </c>
+      <c r="BK245">
+        <v>2.21</v>
+      </c>
+      <c r="BL245">
+        <v>1.56</v>
+      </c>
+      <c r="BM245">
+        <v>2.97</v>
+      </c>
+      <c r="BN245">
+        <v>1.3</v>
+      </c>
+      <c r="BO245">
+        <v>4.2</v>
+      </c>
+      <c r="BP245">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="246" spans="1:68">
+      <c r="A246" s="1">
+        <v>245</v>
+      </c>
+      <c r="B246">
+        <v>7492395</v>
+      </c>
+      <c r="C246" t="s">
+        <v>68</v>
+      </c>
+      <c r="D246" t="s">
+        <v>69</v>
+      </c>
+      <c r="E246" s="2">
+        <v>45704.45833333334</v>
+      </c>
+      <c r="F246">
+        <v>25</v>
+      </c>
+      <c r="G246" t="s">
+        <v>81</v>
+      </c>
+      <c r="H246" t="s">
+        <v>78</v>
+      </c>
+      <c r="I246">
+        <v>0</v>
+      </c>
+      <c r="J246">
+        <v>0</v>
+      </c>
+      <c r="K246">
+        <v>0</v>
+      </c>
+      <c r="L246">
+        <v>0</v>
+      </c>
+      <c r="M246">
+        <v>0</v>
+      </c>
+      <c r="N246">
+        <v>0</v>
+      </c>
+      <c r="O246" t="s">
+        <v>92</v>
+      </c>
+      <c r="P246" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q246">
+        <v>3.4</v>
+      </c>
+      <c r="R246">
+        <v>2</v>
+      </c>
+      <c r="S246">
+        <v>3.4</v>
+      </c>
+      <c r="T246">
+        <v>1.5</v>
+      </c>
+      <c r="U246">
+        <v>2.5</v>
+      </c>
+      <c r="V246">
+        <v>3.4</v>
+      </c>
+      <c r="W246">
+        <v>1.3</v>
+      </c>
+      <c r="X246">
+        <v>10</v>
+      </c>
+      <c r="Y246">
+        <v>1.06</v>
+      </c>
+      <c r="Z246">
+        <v>2.85</v>
+      </c>
+      <c r="AA246">
+        <v>3.25</v>
+      </c>
+      <c r="AB246">
+        <v>2.66</v>
+      </c>
+      <c r="AC246">
+        <v>1.08</v>
+      </c>
+      <c r="AD246">
+        <v>8</v>
+      </c>
+      <c r="AE246">
+        <v>1.42</v>
+      </c>
+      <c r="AF246">
+        <v>2.9</v>
+      </c>
+      <c r="AG246">
+        <v>1.95</v>
+      </c>
+      <c r="AH246">
+        <v>1.75</v>
+      </c>
+      <c r="AI246">
+        <v>1.95</v>
+      </c>
+      <c r="AJ246">
+        <v>1.8</v>
+      </c>
+      <c r="AK246">
+        <v>1.46</v>
+      </c>
+      <c r="AL246">
+        <v>1.34</v>
+      </c>
+      <c r="AM246">
+        <v>1.44</v>
+      </c>
+      <c r="AN246">
+        <v>0.5</v>
+      </c>
+      <c r="AO246">
+        <v>0.83</v>
+      </c>
+      <c r="AP246">
+        <v>0.54</v>
+      </c>
+      <c r="AQ246">
+        <v>0.85</v>
+      </c>
+      <c r="AR246">
+        <v>1.18</v>
+      </c>
+      <c r="AS246">
+        <v>1.12</v>
+      </c>
+      <c r="AT246">
+        <v>2.3</v>
+      </c>
+      <c r="AU246">
+        <v>4</v>
+      </c>
+      <c r="AV246">
+        <v>6</v>
+      </c>
+      <c r="AW246">
+        <v>5</v>
+      </c>
+      <c r="AX246">
+        <v>14</v>
+      </c>
+      <c r="AY246">
+        <v>10</v>
+      </c>
+      <c r="AZ246">
+        <v>23</v>
+      </c>
+      <c r="BA246">
+        <v>3</v>
+      </c>
+      <c r="BB246">
+        <v>7</v>
+      </c>
+      <c r="BC246">
+        <v>10</v>
+      </c>
+      <c r="BD246">
+        <v>1.81</v>
+      </c>
+      <c r="BE246">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF246">
+        <v>2.41</v>
+      </c>
+      <c r="BG246">
+        <v>1.33</v>
+      </c>
+      <c r="BH246">
+        <v>2.83</v>
+      </c>
+      <c r="BI246">
+        <v>1.62</v>
+      </c>
+      <c r="BJ246">
+        <v>2.1</v>
+      </c>
+      <c r="BK246">
+        <v>2.09</v>
+      </c>
+      <c r="BL246">
+        <v>1.66</v>
+      </c>
+      <c r="BM246">
+        <v>2.75</v>
+      </c>
+      <c r="BN246">
+        <v>1.37</v>
+      </c>
+      <c r="BO246">
+        <v>3.82</v>
+      </c>
+      <c r="BP246">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="247" spans="1:68">
+      <c r="A247" s="1">
+        <v>246</v>
+      </c>
+      <c r="B247">
+        <v>7492397</v>
+      </c>
+      <c r="C247" t="s">
+        <v>68</v>
+      </c>
+      <c r="D247" t="s">
+        <v>69</v>
+      </c>
+      <c r="E247" s="2">
+        <v>45704.45833333334</v>
+      </c>
+      <c r="F247">
+        <v>25</v>
+      </c>
+      <c r="G247" t="s">
+        <v>80</v>
+      </c>
+      <c r="H247" t="s">
+        <v>72</v>
+      </c>
+      <c r="I247">
+        <v>1</v>
+      </c>
+      <c r="J247">
+        <v>0</v>
+      </c>
+      <c r="K247">
+        <v>1</v>
+      </c>
+      <c r="L247">
+        <v>3</v>
+      </c>
+      <c r="M247">
+        <v>0</v>
+      </c>
+      <c r="N247">
+        <v>3</v>
+      </c>
+      <c r="O247" t="s">
+        <v>246</v>
+      </c>
+      <c r="P247" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q247">
+        <v>2.6</v>
+      </c>
+      <c r="R247">
+        <v>2.05</v>
+      </c>
+      <c r="S247">
+        <v>4.75</v>
+      </c>
+      <c r="T247">
+        <v>1.44</v>
+      </c>
+      <c r="U247">
+        <v>2.63</v>
+      </c>
+      <c r="V247">
+        <v>3.25</v>
+      </c>
+      <c r="W247">
+        <v>1.33</v>
+      </c>
+      <c r="X247">
+        <v>10</v>
+      </c>
+      <c r="Y247">
+        <v>1.06</v>
+      </c>
+      <c r="Z247">
+        <v>2.01</v>
+      </c>
+      <c r="AA247">
+        <v>3.32</v>
+      </c>
+      <c r="AB247">
+        <v>4.2</v>
+      </c>
+      <c r="AC247">
+        <v>1.07</v>
+      </c>
+      <c r="AD247">
+        <v>9</v>
+      </c>
+      <c r="AE247">
+        <v>1.38</v>
+      </c>
+      <c r="AF247">
+        <v>3.1</v>
+      </c>
+      <c r="AG247">
+        <v>1.95</v>
+      </c>
+      <c r="AH247">
+        <v>1.75</v>
+      </c>
+      <c r="AI247">
+        <v>1.95</v>
+      </c>
+      <c r="AJ247">
+        <v>1.8</v>
+      </c>
+      <c r="AK247">
+        <v>1.22</v>
+      </c>
+      <c r="AL247">
+        <v>1.32</v>
+      </c>
+      <c r="AM247">
+        <v>1.85</v>
+      </c>
+      <c r="AN247">
+        <v>1.42</v>
+      </c>
+      <c r="AO247">
+        <v>1.08</v>
+      </c>
+      <c r="AP247">
+        <v>1.54</v>
+      </c>
+      <c r="AQ247">
+        <v>1</v>
+      </c>
+      <c r="AR247">
+        <v>1.1</v>
+      </c>
+      <c r="AS247">
+        <v>0.99</v>
+      </c>
+      <c r="AT247">
+        <v>2.09</v>
+      </c>
+      <c r="AU247">
+        <v>10</v>
+      </c>
+      <c r="AV247">
+        <v>5</v>
+      </c>
+      <c r="AW247">
+        <v>8</v>
+      </c>
+      <c r="AX247">
+        <v>12</v>
+      </c>
+      <c r="AY247">
+        <v>20</v>
+      </c>
+      <c r="AZ247">
+        <v>21</v>
+      </c>
+      <c r="BA247">
+        <v>9</v>
+      </c>
+      <c r="BB247">
+        <v>5</v>
+      </c>
+      <c r="BC247">
+        <v>14</v>
+      </c>
+      <c r="BD247">
+        <v>1.63</v>
+      </c>
+      <c r="BE247">
+        <v>9</v>
+      </c>
+      <c r="BF247">
+        <v>2.76</v>
+      </c>
+      <c r="BG247">
+        <v>1.18</v>
+      </c>
+      <c r="BH247">
+        <v>3.85</v>
+      </c>
+      <c r="BI247">
+        <v>1.38</v>
+      </c>
+      <c r="BJ247">
+        <v>2.71</v>
+      </c>
+      <c r="BK247">
+        <v>1.69</v>
+      </c>
+      <c r="BL247">
+        <v>2.04</v>
+      </c>
+      <c r="BM247">
+        <v>2.12</v>
+      </c>
+      <c r="BN247">
+        <v>1.61</v>
+      </c>
+      <c r="BO247">
+        <v>2.74</v>
+      </c>
+      <c r="BP247">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="248" spans="1:68">
+      <c r="A248" s="1">
+        <v>247</v>
+      </c>
+      <c r="B248">
+        <v>7492396</v>
+      </c>
+      <c r="C248" t="s">
+        <v>68</v>
+      </c>
+      <c r="D248" t="s">
+        <v>69</v>
+      </c>
+      <c r="E248" s="2">
+        <v>45704.58333333334</v>
+      </c>
+      <c r="F248">
+        <v>25</v>
+      </c>
+      <c r="G248" t="s">
+        <v>71</v>
+      </c>
+      <c r="H248" t="s">
+        <v>86</v>
+      </c>
+      <c r="I248">
+        <v>0</v>
+      </c>
+      <c r="J248">
+        <v>1</v>
+      </c>
+      <c r="K248">
+        <v>1</v>
+      </c>
+      <c r="L248">
+        <v>0</v>
+      </c>
+      <c r="M248">
+        <v>1</v>
+      </c>
+      <c r="N248">
+        <v>1</v>
+      </c>
+      <c r="O248" t="s">
+        <v>92</v>
+      </c>
+      <c r="P248" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q248">
+        <v>4</v>
+      </c>
+      <c r="R248">
+        <v>2.3</v>
+      </c>
+      <c r="S248">
+        <v>2.5</v>
+      </c>
+      <c r="T248">
+        <v>1.33</v>
+      </c>
+      <c r="U248">
+        <v>3.25</v>
+      </c>
+      <c r="V248">
+        <v>2.5</v>
+      </c>
+      <c r="W248">
+        <v>1.5</v>
+      </c>
+      <c r="X248">
+        <v>6.5</v>
+      </c>
+      <c r="Y248">
+        <v>1.11</v>
+      </c>
+      <c r="Z248">
+        <v>4</v>
+      </c>
+      <c r="AA248">
+        <v>3.77</v>
+      </c>
+      <c r="AB248">
+        <v>1.92</v>
+      </c>
+      <c r="AC248">
+        <v>1.03</v>
+      </c>
+      <c r="AD248">
+        <v>13</v>
+      </c>
+      <c r="AE248">
+        <v>1.22</v>
+      </c>
+      <c r="AF248">
+        <v>4.33</v>
+      </c>
+      <c r="AG248">
+        <v>1.67</v>
+      </c>
+      <c r="AH248">
+        <v>2.1</v>
+      </c>
+      <c r="AI248">
+        <v>1.62</v>
+      </c>
+      <c r="AJ248">
+        <v>2.2</v>
+      </c>
+      <c r="AK248">
+        <v>1.9</v>
+      </c>
+      <c r="AL248">
+        <v>1.26</v>
+      </c>
+      <c r="AM248">
+        <v>1.24</v>
+      </c>
+      <c r="AN248">
+        <v>1</v>
+      </c>
+      <c r="AO248">
+        <v>1</v>
+      </c>
+      <c r="AP248">
+        <v>0.92</v>
+      </c>
+      <c r="AQ248">
+        <v>1.15</v>
+      </c>
+      <c r="AR248">
+        <v>1.44</v>
+      </c>
+      <c r="AS248">
+        <v>1.31</v>
+      </c>
+      <c r="AT248">
+        <v>2.75</v>
+      </c>
+      <c r="AU248">
+        <v>2</v>
+      </c>
+      <c r="AV248">
+        <v>5</v>
+      </c>
+      <c r="AW248">
+        <v>4</v>
+      </c>
+      <c r="AX248">
+        <v>12</v>
+      </c>
+      <c r="AY248">
+        <v>6</v>
+      </c>
+      <c r="AZ248">
+        <v>24</v>
+      </c>
+      <c r="BA248">
+        <v>1</v>
+      </c>
+      <c r="BB248">
+        <v>10</v>
+      </c>
+      <c r="BC248">
+        <v>11</v>
+      </c>
+      <c r="BD248">
+        <v>2.6</v>
+      </c>
+      <c r="BE248">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF248">
+        <v>1.7</v>
+      </c>
+      <c r="BG248">
+        <v>1.23</v>
+      </c>
+      <c r="BH248">
+        <v>3.42</v>
+      </c>
+      <c r="BI248">
+        <v>1.46</v>
+      </c>
+      <c r="BJ248">
+        <v>2.45</v>
+      </c>
+      <c r="BK248">
+        <v>1.83</v>
+      </c>
+      <c r="BL248">
+        <v>1.87</v>
+      </c>
+      <c r="BM248">
+        <v>2.32</v>
+      </c>
+      <c r="BN248">
+        <v>1.51</v>
+      </c>
+      <c r="BO248">
+        <v>3.08</v>
+      </c>
+      <c r="BP248">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="249" spans="1:68">
+      <c r="A249" s="1">
+        <v>248</v>
+      </c>
+      <c r="B249">
+        <v>7492392</v>
+      </c>
+      <c r="C249" t="s">
+        <v>68</v>
+      </c>
+      <c r="D249" t="s">
+        <v>69</v>
+      </c>
+      <c r="E249" s="2">
+        <v>45704.69791666666</v>
+      </c>
+      <c r="F249">
+        <v>25</v>
+      </c>
+      <c r="G249" t="s">
+        <v>79</v>
+      </c>
+      <c r="H249" t="s">
+        <v>82</v>
+      </c>
+      <c r="I249">
+        <v>0</v>
+      </c>
+      <c r="J249">
+        <v>0</v>
+      </c>
+      <c r="K249">
+        <v>0</v>
+      </c>
+      <c r="L249">
+        <v>1</v>
+      </c>
+      <c r="M249">
+        <v>0</v>
+      </c>
+      <c r="N249">
+        <v>1</v>
+      </c>
+      <c r="O249" t="s">
+        <v>202</v>
+      </c>
+      <c r="P249" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q249">
+        <v>3.75</v>
+      </c>
+      <c r="R249">
+        <v>2.05</v>
+      </c>
+      <c r="S249">
+        <v>3</v>
+      </c>
+      <c r="T249">
+        <v>1.44</v>
+      </c>
+      <c r="U249">
+        <v>2.63</v>
+      </c>
+      <c r="V249">
+        <v>3.25</v>
+      </c>
+      <c r="W249">
+        <v>1.33</v>
+      </c>
+      <c r="X249">
+        <v>9</v>
+      </c>
+      <c r="Y249">
+        <v>1.07</v>
+      </c>
+      <c r="Z249">
+        <v>3.23</v>
+      </c>
+      <c r="AA249">
+        <v>3.32</v>
+      </c>
+      <c r="AB249">
+        <v>2.35</v>
+      </c>
+      <c r="AC249">
+        <v>1.07</v>
+      </c>
+      <c r="AD249">
+        <v>9.5</v>
+      </c>
+      <c r="AE249">
+        <v>1.36</v>
+      </c>
+      <c r="AF249">
+        <v>3.2</v>
+      </c>
+      <c r="AG249">
+        <v>2</v>
+      </c>
+      <c r="AH249">
+        <v>1.75</v>
+      </c>
+      <c r="AI249">
+        <v>1.8</v>
+      </c>
+      <c r="AJ249">
+        <v>1.95</v>
+      </c>
+      <c r="AK249">
+        <v>1.6</v>
+      </c>
+      <c r="AL249">
+        <v>1.33</v>
+      </c>
+      <c r="AM249">
+        <v>1.34</v>
+      </c>
+      <c r="AN249">
+        <v>1.83</v>
+      </c>
+      <c r="AO249">
+        <v>2.25</v>
+      </c>
+      <c r="AP249">
+        <v>1.92</v>
+      </c>
+      <c r="AQ249">
+        <v>2.08</v>
+      </c>
+      <c r="AR249">
+        <v>1.57</v>
+      </c>
+      <c r="AS249">
+        <v>1.59</v>
+      </c>
+      <c r="AT249">
+        <v>3.16</v>
+      </c>
+      <c r="AU249">
+        <v>9</v>
+      </c>
+      <c r="AV249">
+        <v>3</v>
+      </c>
+      <c r="AW249">
+        <v>8</v>
+      </c>
+      <c r="AX249">
+        <v>15</v>
+      </c>
+      <c r="AY249">
+        <v>21</v>
+      </c>
+      <c r="AZ249">
+        <v>22</v>
+      </c>
+      <c r="BA249">
+        <v>7</v>
+      </c>
+      <c r="BB249">
+        <v>5</v>
+      </c>
+      <c r="BC249">
+        <v>12</v>
+      </c>
+      <c r="BD249">
+        <v>2.12</v>
+      </c>
+      <c r="BE249">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF249">
+        <v>2.02</v>
+      </c>
+      <c r="BG249">
+        <v>1.29</v>
+      </c>
+      <c r="BH249">
+        <v>3.04</v>
+      </c>
+      <c r="BI249">
+        <v>1.56</v>
+      </c>
+      <c r="BJ249">
+        <v>2.21</v>
+      </c>
+      <c r="BK249">
+        <v>1.98</v>
+      </c>
+      <c r="BL249">
+        <v>1.74</v>
+      </c>
+      <c r="BM249">
+        <v>2.57</v>
+      </c>
+      <c r="BN249">
+        <v>1.42</v>
+      </c>
+      <c r="BO249">
+        <v>3.5</v>
+      </c>
+      <c r="BP249">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="367">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -757,6 +757,9 @@
     <t>['19', '65', '90']</t>
   </si>
   <si>
+    <t>['82', '86']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1473,7 +1476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP249"/>
+  <dimension ref="A1:BP250"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1729,7 +1732,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1807,7 +1810,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ2">
         <v>2.08</v>
@@ -2347,7 +2350,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2553,7 +2556,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -3171,7 +3174,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3252,7 +3255,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ9">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3377,7 +3380,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3789,7 +3792,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q12">
         <v>3.75</v>
@@ -3995,7 +3998,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4201,7 +4204,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4694,7 +4697,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ16">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5231,7 +5234,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5643,7 +5646,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5849,7 +5852,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6261,7 +6264,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6673,7 +6676,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6879,7 +6882,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7085,7 +7088,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7291,7 +7294,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7369,7 +7372,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ29">
         <v>1</v>
@@ -7909,7 +7912,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8402,7 +8405,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ34">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR34">
         <v>2.22</v>
@@ -8605,7 +8608,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ35">
         <v>1.15</v>
@@ -8733,7 +8736,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -9145,7 +9148,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9351,7 +9354,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9557,7 +9560,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9763,7 +9766,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9969,7 +9972,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10175,7 +10178,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10793,7 +10796,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10999,7 +11002,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11205,7 +11208,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11617,7 +11620,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11823,7 +11826,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12235,7 +12238,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12441,7 +12444,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12519,7 +12522,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ54">
         <v>1.75</v>
@@ -12647,7 +12650,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12853,7 +12856,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13059,7 +13062,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13346,7 +13349,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ58">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR58">
         <v>2.07</v>
@@ -13883,7 +13886,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14376,7 +14379,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ63">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR63">
         <v>0.9</v>
@@ -14707,7 +14710,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14913,7 +14916,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15119,7 +15122,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15325,7 +15328,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q68">
         <v>2.2</v>
@@ -15737,7 +15740,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -16355,7 +16358,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16433,7 +16436,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ73">
         <v>1.5</v>
@@ -16973,7 +16976,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17179,7 +17182,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17385,7 +17388,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17591,7 +17594,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -18003,7 +18006,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18827,7 +18830,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19445,7 +19448,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19526,7 +19529,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ88">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR88">
         <v>0.85</v>
@@ -19651,7 +19654,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19857,7 +19860,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20063,7 +20066,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20475,7 +20478,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20681,7 +20684,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20887,7 +20890,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -21299,7 +21302,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21505,7 +21508,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21583,7 +21586,7 @@
         <v>1.25</v>
       </c>
       <c r="AP98">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ98">
         <v>1.5</v>
@@ -21711,7 +21714,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22329,7 +22332,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22741,7 +22744,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22947,7 +22950,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23153,7 +23156,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23440,7 +23443,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ107">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR107">
         <v>1.54</v>
@@ -23977,7 +23980,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24183,7 +24186,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24261,7 +24264,7 @@
         <v>0.57</v>
       </c>
       <c r="AP111">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ111">
         <v>0.77</v>
@@ -24389,7 +24392,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24595,7 +24598,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24801,7 +24804,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25213,7 +25216,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25419,7 +25422,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25625,7 +25628,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -26243,7 +26246,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26655,7 +26658,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26861,7 +26864,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26939,7 +26942,7 @@
         <v>0.8</v>
       </c>
       <c r="AP124">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ124">
         <v>0.83</v>
@@ -27067,7 +27070,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27273,7 +27276,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27891,7 +27894,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -29002,7 +29005,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ134">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR134">
         <v>1.52</v>
@@ -29127,7 +29130,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29333,7 +29336,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29745,7 +29748,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29951,7 +29954,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30647,7 +30650,7 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ142">
         <v>1.08</v>
@@ -30775,7 +30778,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30981,7 +30984,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31393,7 +31396,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31599,7 +31602,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -32011,7 +32014,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32423,7 +32426,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32629,7 +32632,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32835,7 +32838,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -32916,7 +32919,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ153">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR153">
         <v>1.41</v>
@@ -33247,7 +33250,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -34071,7 +34074,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34483,7 +34486,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34689,7 +34692,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34767,7 +34770,7 @@
         <v>2.13</v>
       </c>
       <c r="AP162">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ162">
         <v>2.15</v>
@@ -34895,7 +34898,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35307,7 +35310,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35513,7 +35516,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35719,7 +35722,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35925,7 +35928,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36543,7 +36546,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36749,7 +36752,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36955,7 +36958,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37161,7 +37164,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37448,7 +37451,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ175">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR175">
         <v>1.48</v>
@@ -37573,7 +37576,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -38191,7 +38194,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38397,7 +38400,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38603,7 +38606,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39015,7 +39018,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39839,7 +39842,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40251,7 +40254,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40663,7 +40666,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -40947,7 +40950,7 @@
         <v>0.89</v>
       </c>
       <c r="AP192">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ192">
         <v>0.67</v>
@@ -41281,7 +41284,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41899,7 +41902,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42311,7 +42314,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42517,7 +42520,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42723,7 +42726,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -43135,7 +43138,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43547,7 +43550,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43834,7 +43837,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ206">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR206">
         <v>1.29</v>
@@ -43959,7 +43962,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44165,7 +44168,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44783,7 +44786,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45401,7 +45404,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45607,7 +45610,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45813,7 +45816,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -46019,7 +46022,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46225,7 +46228,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46509,7 +46512,7 @@
         <v>0.7</v>
       </c>
       <c r="AP219">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ219">
         <v>0.58</v>
@@ -46637,7 +46640,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46843,7 +46846,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -46924,7 +46927,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ221">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR221">
         <v>1.06</v>
@@ -47255,7 +47258,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47667,7 +47670,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47873,7 +47876,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -48285,7 +48288,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48491,7 +48494,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48903,7 +48906,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49109,7 +49112,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49315,7 +49318,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49521,7 +49524,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -49933,7 +49936,7 @@
         <v>240</v>
       </c>
       <c r="P236" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q236">
         <v>1.91</v>
@@ -50551,7 +50554,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -50963,7 +50966,7 @@
         <v>244</v>
       </c>
       <c r="P241" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q241">
         <v>2.5</v>
@@ -51375,7 +51378,7 @@
         <v>245</v>
       </c>
       <c r="P243" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q243">
         <v>3.4</v>
@@ -51787,7 +51790,7 @@
         <v>92</v>
       </c>
       <c r="P245" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q245">
         <v>2.6</v>
@@ -52405,7 +52408,7 @@
         <v>92</v>
       </c>
       <c r="P248" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q248">
         <v>4</v>
@@ -52768,6 +52771,212 @@
       </c>
       <c r="BP249">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="250" spans="1:68">
+      <c r="A250" s="1">
+        <v>249</v>
+      </c>
+      <c r="B250">
+        <v>7492391</v>
+      </c>
+      <c r="C250" t="s">
+        <v>68</v>
+      </c>
+      <c r="D250" t="s">
+        <v>69</v>
+      </c>
+      <c r="E250" s="2">
+        <v>45705.69791666666</v>
+      </c>
+      <c r="F250">
+        <v>25</v>
+      </c>
+      <c r="G250" t="s">
+        <v>70</v>
+      </c>
+      <c r="H250" t="s">
+        <v>87</v>
+      </c>
+      <c r="I250">
+        <v>0</v>
+      </c>
+      <c r="J250">
+        <v>0</v>
+      </c>
+      <c r="K250">
+        <v>0</v>
+      </c>
+      <c r="L250">
+        <v>2</v>
+      </c>
+      <c r="M250">
+        <v>0</v>
+      </c>
+      <c r="N250">
+        <v>2</v>
+      </c>
+      <c r="O250" t="s">
+        <v>247</v>
+      </c>
+      <c r="P250" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q250">
+        <v>2.63</v>
+      </c>
+      <c r="R250">
+        <v>2.1</v>
+      </c>
+      <c r="S250">
+        <v>4.5</v>
+      </c>
+      <c r="T250">
+        <v>1.44</v>
+      </c>
+      <c r="U250">
+        <v>2.63</v>
+      </c>
+      <c r="V250">
+        <v>3.25</v>
+      </c>
+      <c r="W250">
+        <v>1.33</v>
+      </c>
+      <c r="X250">
+        <v>9</v>
+      </c>
+      <c r="Y250">
+        <v>1.07</v>
+      </c>
+      <c r="Z250">
+        <v>2</v>
+      </c>
+      <c r="AA250">
+        <v>3.47</v>
+      </c>
+      <c r="AB250">
+        <v>4</v>
+      </c>
+      <c r="AC250">
+        <v>1.07</v>
+      </c>
+      <c r="AD250">
+        <v>9.5</v>
+      </c>
+      <c r="AE250">
+        <v>1.36</v>
+      </c>
+      <c r="AF250">
+        <v>3.2</v>
+      </c>
+      <c r="AG250">
+        <v>2</v>
+      </c>
+      <c r="AH250">
+        <v>1.73</v>
+      </c>
+      <c r="AI250">
+        <v>1.91</v>
+      </c>
+      <c r="AJ250">
+        <v>1.91</v>
+      </c>
+      <c r="AK250">
+        <v>1.25</v>
+      </c>
+      <c r="AL250">
+        <v>1.3</v>
+      </c>
+      <c r="AM250">
+        <v>1.82</v>
+      </c>
+      <c r="AN250">
+        <v>1</v>
+      </c>
+      <c r="AO250">
+        <v>0.33</v>
+      </c>
+      <c r="AP250">
+        <v>1.15</v>
+      </c>
+      <c r="AQ250">
+        <v>0.31</v>
+      </c>
+      <c r="AR250">
+        <v>1.32</v>
+      </c>
+      <c r="AS250">
+        <v>0.95</v>
+      </c>
+      <c r="AT250">
+        <v>2.27</v>
+      </c>
+      <c r="AU250">
+        <v>6</v>
+      </c>
+      <c r="AV250">
+        <v>4</v>
+      </c>
+      <c r="AW250">
+        <v>9</v>
+      </c>
+      <c r="AX250">
+        <v>4</v>
+      </c>
+      <c r="AY250">
+        <v>18</v>
+      </c>
+      <c r="AZ250">
+        <v>8</v>
+      </c>
+      <c r="BA250">
+        <v>4</v>
+      </c>
+      <c r="BB250">
+        <v>5</v>
+      </c>
+      <c r="BC250">
+        <v>9</v>
+      </c>
+      <c r="BD250">
+        <v>1.49</v>
+      </c>
+      <c r="BE250">
+        <v>6.75</v>
+      </c>
+      <c r="BF250">
+        <v>2.9</v>
+      </c>
+      <c r="BG250">
+        <v>1.28</v>
+      </c>
+      <c r="BH250">
+        <v>3.3</v>
+      </c>
+      <c r="BI250">
+        <v>1.49</v>
+      </c>
+      <c r="BJ250">
+        <v>2.4</v>
+      </c>
+      <c r="BK250">
+        <v>1.79</v>
+      </c>
+      <c r="BL250">
+        <v>1.9</v>
+      </c>
+      <c r="BM250">
+        <v>2.23</v>
+      </c>
+      <c r="BN250">
+        <v>1.56</v>
+      </c>
+      <c r="BO250">
+        <v>2.9</v>
+      </c>
+      <c r="BP250">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="367">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -736,10 +736,10 @@
     <t>['45+2']</t>
   </si>
   <si>
-    <t>['31', '57', '63', '77', '88']</t>
+    <t>['57', '70']</t>
   </si>
   <si>
-    <t>['57', '70']</t>
+    <t>['31', '57', '63', '77', '88']</t>
   </si>
   <si>
     <t>['37']</t>
@@ -1476,7 +1476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP250"/>
+  <dimension ref="A1:BP251"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2637,7 +2637,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ6">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -3458,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ10">
         <v>2.08</v>
@@ -6548,7 +6548,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ25">
         <v>0.83</v>
@@ -9641,7 +9641,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ40">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR40">
         <v>1.32</v>
@@ -10874,7 +10874,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ46">
         <v>0.67</v>
@@ -11495,7 +11495,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ49">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR49">
         <v>2.26</v>
@@ -16645,7 +16645,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ74">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR74">
         <v>1.89</v>
@@ -17260,7 +17260,7 @@
         <v>0.67</v>
       </c>
       <c r="AP77">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ77">
         <v>1.5</v>
@@ -20350,7 +20350,7 @@
         <v>0.75</v>
       </c>
       <c r="AP92">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ92">
         <v>1</v>
@@ -20765,7 +20765,7 @@
         <v>1</v>
       </c>
       <c r="AQ94">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR94">
         <v>1.33</v>
@@ -24470,7 +24470,7 @@
         <v>1.6</v>
       </c>
       <c r="AP112">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ112">
         <v>1</v>
@@ -25297,7 +25297,7 @@
         <v>2</v>
       </c>
       <c r="AQ116">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR116">
         <v>1.85</v>
@@ -27975,7 +27975,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ129">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR129">
         <v>0.88</v>
@@ -29826,7 +29826,7 @@
         <v>2</v>
       </c>
       <c r="AP138">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ138">
         <v>1.75</v>
@@ -32095,7 +32095,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ149">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR149">
         <v>1</v>
@@ -33122,7 +33122,7 @@
         <v>1</v>
       </c>
       <c r="AP154">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ154">
         <v>0.58</v>
@@ -34976,7 +34976,7 @@
         <v>1.5</v>
       </c>
       <c r="AP163">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ163">
         <v>1.75</v>
@@ -36009,7 +36009,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ168">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR168">
         <v>1.6</v>
@@ -38893,7 +38893,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ182">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR182">
         <v>1.12</v>
@@ -39302,7 +39302,7 @@
         <v>1.63</v>
       </c>
       <c r="AP184">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ184">
         <v>1.25</v>
@@ -44455,7 +44455,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ209">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR209">
         <v>1.52</v>
@@ -45894,7 +45894,7 @@
         <v>2.56</v>
       </c>
       <c r="AP216">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ216">
         <v>2.08</v>
@@ -49894,7 +49894,7 @@
         <v>235</v>
       </c>
       <c r="B236">
-        <v>7492383</v>
+        <v>7492378</v>
       </c>
       <c r="C236" t="s">
         <v>68</v>
@@ -49909,49 +49909,49 @@
         <v>24</v>
       </c>
       <c r="G236" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H236" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="I236">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J236">
         <v>0</v>
       </c>
       <c r="K236">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L236">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M236">
         <v>1</v>
       </c>
       <c r="N236">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O236" t="s">
         <v>240</v>
       </c>
       <c r="P236" t="s">
-        <v>258</v>
+        <v>217</v>
       </c>
       <c r="Q236">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="R236">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S236">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="T236">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="U236">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V236">
         <v>2.63</v>
@@ -49960,19 +49960,19 @@
         <v>1.44</v>
       </c>
       <c r="X236">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Y236">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z236">
-        <v>1.45</v>
+        <v>1.93</v>
       </c>
       <c r="AA236">
-        <v>4.8</v>
+        <v>3.74</v>
       </c>
       <c r="AB236">
-        <v>7.4</v>
+        <v>4</v>
       </c>
       <c r="AC236">
         <v>1.04</v>
@@ -49981,118 +49981,118 @@
         <v>13</v>
       </c>
       <c r="AE236">
+        <v>1.24</v>
+      </c>
+      <c r="AF236">
+        <v>4.2</v>
+      </c>
+      <c r="AG236">
+        <v>1.7</v>
+      </c>
+      <c r="AH236">
+        <v>2.1</v>
+      </c>
+      <c r="AI236">
+        <v>1.62</v>
+      </c>
+      <c r="AJ236">
+        <v>2.2</v>
+      </c>
+      <c r="AK236">
         <v>1.26</v>
       </c>
-      <c r="AF236">
+      <c r="AL236">
+        <v>1.28</v>
+      </c>
+      <c r="AM236">
+        <v>1.83</v>
+      </c>
+      <c r="AN236">
+        <v>1</v>
+      </c>
+      <c r="AO236">
+        <v>0.73</v>
+      </c>
+      <c r="AP236">
+        <v>1.15</v>
+      </c>
+      <c r="AQ236">
+        <v>0.67</v>
+      </c>
+      <c r="AR236">
+        <v>1.47</v>
+      </c>
+      <c r="AS236">
+        <v>1.2</v>
+      </c>
+      <c r="AT236">
+        <v>2.67</v>
+      </c>
+      <c r="AU236">
         <v>4</v>
       </c>
-      <c r="AG236">
-        <v>1.81</v>
-      </c>
-      <c r="AH236">
-        <v>2.01</v>
-      </c>
-      <c r="AI236">
-        <v>2</v>
-      </c>
-      <c r="AJ236">
-        <v>1.75</v>
-      </c>
-      <c r="AK236">
-        <v>1.1</v>
-      </c>
-      <c r="AL236">
-        <v>1.19</v>
-      </c>
-      <c r="AM236">
-        <v>2.75</v>
-      </c>
-      <c r="AN236">
-        <v>1.91</v>
-      </c>
-      <c r="AO236">
-        <v>0.64</v>
-      </c>
-      <c r="AP236">
-        <v>1.92</v>
-      </c>
-      <c r="AQ236">
-        <v>0.58</v>
-      </c>
-      <c r="AR236">
-        <v>1.52</v>
-      </c>
-      <c r="AS236">
-        <v>0.88</v>
-      </c>
-      <c r="AT236">
-        <v>2.4</v>
-      </c>
-      <c r="AU236">
-        <v>10</v>
-      </c>
       <c r="AV236">
         <v>2</v>
       </c>
       <c r="AW236">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AX236">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AY236">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="AZ236">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="BA236">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB236">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BC236">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BD236">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="BE236">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BF236">
-        <v>5.25</v>
+        <v>2.88</v>
       </c>
       <c r="BG236">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BH236">
-        <v>3.86</v>
+        <v>4.4</v>
       </c>
       <c r="BI236">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="BJ236">
-        <v>2.71</v>
+        <v>2.97</v>
       </c>
       <c r="BK236">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="BL236">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="BM236">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="BN236">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="BO236">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="BP236">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="237" spans="1:68">
@@ -50100,7 +50100,7 @@
         <v>236</v>
       </c>
       <c r="B237">
-        <v>7492378</v>
+        <v>7492383</v>
       </c>
       <c r="C237" t="s">
         <v>68</v>
@@ -50115,49 +50115,49 @@
         <v>24</v>
       </c>
       <c r="G237" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H237" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="I237">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J237">
         <v>0</v>
       </c>
       <c r="K237">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L237">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M237">
         <v>1</v>
       </c>
       <c r="N237">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O237" t="s">
         <v>241</v>
       </c>
       <c r="P237" t="s">
-        <v>217</v>
+        <v>258</v>
       </c>
       <c r="Q237">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="R237">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S237">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="T237">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="U237">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="V237">
         <v>2.63</v>
@@ -50166,19 +50166,19 @@
         <v>1.44</v>
       </c>
       <c r="X237">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Y237">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z237">
-        <v>1.93</v>
+        <v>1.45</v>
       </c>
       <c r="AA237">
-        <v>3.74</v>
+        <v>4.8</v>
       </c>
       <c r="AB237">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="AC237">
         <v>1.04</v>
@@ -50187,118 +50187,118 @@
         <v>13</v>
       </c>
       <c r="AE237">
+        <v>1.26</v>
+      </c>
+      <c r="AF237">
+        <v>4</v>
+      </c>
+      <c r="AG237">
+        <v>1.81</v>
+      </c>
+      <c r="AH237">
+        <v>2.01</v>
+      </c>
+      <c r="AI237">
+        <v>2</v>
+      </c>
+      <c r="AJ237">
+        <v>1.75</v>
+      </c>
+      <c r="AK237">
+        <v>1.1</v>
+      </c>
+      <c r="AL237">
+        <v>1.19</v>
+      </c>
+      <c r="AM237">
+        <v>2.75</v>
+      </c>
+      <c r="AN237">
+        <v>1.91</v>
+      </c>
+      <c r="AO237">
+        <v>0.64</v>
+      </c>
+      <c r="AP237">
+        <v>1.92</v>
+      </c>
+      <c r="AQ237">
+        <v>0.58</v>
+      </c>
+      <c r="AR237">
+        <v>1.52</v>
+      </c>
+      <c r="AS237">
+        <v>0.88</v>
+      </c>
+      <c r="AT237">
+        <v>2.4</v>
+      </c>
+      <c r="AU237">
+        <v>10</v>
+      </c>
+      <c r="AV237">
+        <v>2</v>
+      </c>
+      <c r="AW237">
+        <v>17</v>
+      </c>
+      <c r="AX237">
+        <v>2</v>
+      </c>
+      <c r="AY237">
+        <v>31</v>
+      </c>
+      <c r="AZ237">
+        <v>4</v>
+      </c>
+      <c r="BA237">
+        <v>8</v>
+      </c>
+      <c r="BB237">
+        <v>1</v>
+      </c>
+      <c r="BC237">
+        <v>9</v>
+      </c>
+      <c r="BD237">
         <v>1.24</v>
       </c>
-      <c r="AF237">
-        <v>4.2</v>
-      </c>
-      <c r="AG237">
-        <v>1.7</v>
-      </c>
-      <c r="AH237">
+      <c r="BE237">
+        <v>11</v>
+      </c>
+      <c r="BF237">
+        <v>5.25</v>
+      </c>
+      <c r="BG237">
+        <v>1.18</v>
+      </c>
+      <c r="BH237">
+        <v>3.86</v>
+      </c>
+      <c r="BI237">
+        <v>1.38</v>
+      </c>
+      <c r="BJ237">
+        <v>2.71</v>
+      </c>
+      <c r="BK237">
+        <v>1.68</v>
+      </c>
+      <c r="BL237">
+        <v>2.06</v>
+      </c>
+      <c r="BM237">
         <v>2.1</v>
       </c>
-      <c r="AI237">
+      <c r="BN237">
         <v>1.62</v>
       </c>
-      <c r="AJ237">
-        <v>2.2</v>
-      </c>
-      <c r="AK237">
-        <v>1.26</v>
-      </c>
-      <c r="AL237">
-        <v>1.28</v>
-      </c>
-      <c r="AM237">
-        <v>1.83</v>
-      </c>
-      <c r="AN237">
-        <v>1</v>
-      </c>
-      <c r="AO237">
-        <v>0.73</v>
-      </c>
-      <c r="AP237">
-        <v>1.15</v>
-      </c>
-      <c r="AQ237">
-        <v>0.67</v>
-      </c>
-      <c r="AR237">
-        <v>1.47</v>
-      </c>
-      <c r="AS237">
-        <v>1.2</v>
-      </c>
-      <c r="AT237">
-        <v>2.67</v>
-      </c>
-      <c r="AU237">
-        <v>4</v>
-      </c>
-      <c r="AV237">
-        <v>2</v>
-      </c>
-      <c r="AW237">
-        <v>11</v>
-      </c>
-      <c r="AX237">
-        <v>8</v>
-      </c>
-      <c r="AY237">
-        <v>16</v>
-      </c>
-      <c r="AZ237">
-        <v>13</v>
-      </c>
-      <c r="BA237">
-        <v>7</v>
-      </c>
-      <c r="BB237">
-        <v>6</v>
-      </c>
-      <c r="BC237">
-        <v>13</v>
-      </c>
-      <c r="BD237">
-        <v>1.58</v>
-      </c>
-      <c r="BE237">
-        <v>9.4</v>
-      </c>
-      <c r="BF237">
-        <v>2.88</v>
-      </c>
-      <c r="BG237">
-        <v>1.14</v>
-      </c>
-      <c r="BH237">
-        <v>4.4</v>
-      </c>
-      <c r="BI237">
-        <v>1.3</v>
-      </c>
-      <c r="BJ237">
-        <v>2.97</v>
-      </c>
-      <c r="BK237">
-        <v>1.55</v>
-      </c>
-      <c r="BL237">
-        <v>2.23</v>
-      </c>
-      <c r="BM237">
-        <v>1.94</v>
-      </c>
-      <c r="BN237">
-        <v>1.77</v>
-      </c>
       <c r="BO237">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="BP237">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="238" spans="1:68">
@@ -50426,7 +50426,7 @@
         <v>1.55</v>
       </c>
       <c r="AP238">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ238">
         <v>1.5</v>
@@ -50635,7 +50635,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ239">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR239">
         <v>1.57</v>
@@ -52977,6 +52977,212 @@
       </c>
       <c r="BP250">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="251" spans="1:68">
+      <c r="A251" s="1">
+        <v>250</v>
+      </c>
+      <c r="B251">
+        <v>7492403</v>
+      </c>
+      <c r="C251" t="s">
+        <v>68</v>
+      </c>
+      <c r="D251" t="s">
+        <v>69</v>
+      </c>
+      <c r="E251" s="2">
+        <v>45709.69791666666</v>
+      </c>
+      <c r="F251">
+        <v>26</v>
+      </c>
+      <c r="G251" t="s">
+        <v>78</v>
+      </c>
+      <c r="H251" t="s">
+        <v>80</v>
+      </c>
+      <c r="I251">
+        <v>0</v>
+      </c>
+      <c r="J251">
+        <v>1</v>
+      </c>
+      <c r="K251">
+        <v>1</v>
+      </c>
+      <c r="L251">
+        <v>0</v>
+      </c>
+      <c r="M251">
+        <v>1</v>
+      </c>
+      <c r="N251">
+        <v>1</v>
+      </c>
+      <c r="O251" t="s">
+        <v>92</v>
+      </c>
+      <c r="P251" t="s">
+        <v>341</v>
+      </c>
+      <c r="Q251">
+        <v>3.6</v>
+      </c>
+      <c r="R251">
+        <v>2</v>
+      </c>
+      <c r="S251">
+        <v>3.25</v>
+      </c>
+      <c r="T251">
+        <v>1.5</v>
+      </c>
+      <c r="U251">
+        <v>2.5</v>
+      </c>
+      <c r="V251">
+        <v>3.4</v>
+      </c>
+      <c r="W251">
+        <v>1.3</v>
+      </c>
+      <c r="X251">
+        <v>10</v>
+      </c>
+      <c r="Y251">
+        <v>1.06</v>
+      </c>
+      <c r="Z251">
+        <v>2.94</v>
+      </c>
+      <c r="AA251">
+        <v>3.14</v>
+      </c>
+      <c r="AB251">
+        <v>2.65</v>
+      </c>
+      <c r="AC251">
+        <v>1.09</v>
+      </c>
+      <c r="AD251">
+        <v>8</v>
+      </c>
+      <c r="AE251">
+        <v>1.42</v>
+      </c>
+      <c r="AF251">
+        <v>2.9</v>
+      </c>
+      <c r="AG251">
+        <v>2.15</v>
+      </c>
+      <c r="AH251">
+        <v>1.61</v>
+      </c>
+      <c r="AI251">
+        <v>1.95</v>
+      </c>
+      <c r="AJ251">
+        <v>1.8</v>
+      </c>
+      <c r="AK251">
+        <v>1.49</v>
+      </c>
+      <c r="AL251">
+        <v>1.34</v>
+      </c>
+      <c r="AM251">
+        <v>1.41</v>
+      </c>
+      <c r="AN251">
+        <v>1.17</v>
+      </c>
+      <c r="AO251">
+        <v>1.08</v>
+      </c>
+      <c r="AP251">
+        <v>1.08</v>
+      </c>
+      <c r="AQ251">
+        <v>1.23</v>
+      </c>
+      <c r="AR251">
+        <v>1.3</v>
+      </c>
+      <c r="AS251">
+        <v>1.33</v>
+      </c>
+      <c r="AT251">
+        <v>2.63</v>
+      </c>
+      <c r="AU251">
+        <v>2</v>
+      </c>
+      <c r="AV251">
+        <v>6</v>
+      </c>
+      <c r="AW251">
+        <v>9</v>
+      </c>
+      <c r="AX251">
+        <v>7</v>
+      </c>
+      <c r="AY251">
+        <v>14</v>
+      </c>
+      <c r="AZ251">
+        <v>17</v>
+      </c>
+      <c r="BA251">
+        <v>11</v>
+      </c>
+      <c r="BB251">
+        <v>8</v>
+      </c>
+      <c r="BC251">
+        <v>19</v>
+      </c>
+      <c r="BD251">
+        <v>1.81</v>
+      </c>
+      <c r="BE251">
+        <v>6.5</v>
+      </c>
+      <c r="BF251">
+        <v>2.18</v>
+      </c>
+      <c r="BG251">
+        <v>1.29</v>
+      </c>
+      <c r="BH251">
+        <v>3.15</v>
+      </c>
+      <c r="BI251">
+        <v>1.5</v>
+      </c>
+      <c r="BJ251">
+        <v>2.38</v>
+      </c>
+      <c r="BK251">
+        <v>1.82</v>
+      </c>
+      <c r="BL251">
+        <v>1.86</v>
+      </c>
+      <c r="BM251">
+        <v>2.3</v>
+      </c>
+      <c r="BN251">
+        <v>1.54</v>
+      </c>
+      <c r="BO251">
+        <v>2.95</v>
+      </c>
+      <c r="BP251">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="369">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -760,6 +760,12 @@
     <t>['82', '86']</t>
   </si>
   <si>
+    <t>['37', '79']</t>
+  </si>
+  <si>
+    <t>['5', '76']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1476,7 +1482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP251"/>
+  <dimension ref="A1:BP255"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1732,7 +1738,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2016,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ3">
         <v>1.5</v>
@@ -2350,7 +2356,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2556,7 +2562,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -3174,7 +3180,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3380,7 +3386,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3792,7 +3798,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q12">
         <v>3.75</v>
@@ -3873,7 +3879,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ12">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3998,7 +4004,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4076,10 +4082,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ13">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR13">
         <v>1.45</v>
@@ -4204,7 +4210,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4285,7 +4291,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ14">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4488,7 +4494,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ15">
         <v>0.85</v>
@@ -4900,7 +4906,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ17">
         <v>2.08</v>
@@ -5109,7 +5115,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ18">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5234,7 +5240,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5646,7 +5652,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5852,7 +5858,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6136,7 +6142,7 @@
         <v>1.5</v>
       </c>
       <c r="AP23">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ23">
         <v>2.08</v>
@@ -6264,7 +6270,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6676,7 +6682,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6757,7 +6763,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ26">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR26">
         <v>1.67</v>
@@ -6882,7 +6888,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7088,7 +7094,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7294,7 +7300,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7912,7 +7918,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7993,7 +7999,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ32">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR32">
         <v>0</v>
@@ -8736,7 +8742,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -9020,7 +9026,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ37">
         <v>0.85</v>
@@ -9148,7 +9154,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9354,7 +9360,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9560,7 +9566,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9638,7 +9644,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ40">
         <v>1.23</v>
@@ -9766,7 +9772,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9972,7 +9978,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10178,7 +10184,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10465,7 +10471,7 @@
         <v>1</v>
       </c>
       <c r="AQ44">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR44">
         <v>1.37</v>
@@ -10796,7 +10802,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -11002,7 +11008,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11083,7 +11089,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ47">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR47">
         <v>1.69</v>
@@ -11208,7 +11214,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11289,7 +11295,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ48">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR48">
         <v>0.9399999999999999</v>
@@ -11620,7 +11626,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11698,10 +11704,10 @@
         <v>0.5</v>
       </c>
       <c r="AP50">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ50">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR50">
         <v>1.2</v>
@@ -11826,7 +11832,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12238,7 +12244,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12444,7 +12450,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12650,7 +12656,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12856,7 +12862,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -12934,10 +12940,10 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ56">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR56">
         <v>1.02</v>
@@ -13062,7 +13068,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13886,7 +13892,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -13964,7 +13970,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ61">
         <v>0.83</v>
@@ -14710,7 +14716,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14791,7 +14797,7 @@
         <v>2</v>
       </c>
       <c r="AQ65">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR65">
         <v>1.65</v>
@@ -14916,7 +14922,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -14994,7 +15000,7 @@
         <v>2.33</v>
       </c>
       <c r="AP66">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ66">
         <v>1.08</v>
@@ -15122,7 +15128,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15328,7 +15334,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q68">
         <v>2.2</v>
@@ -15740,7 +15746,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -16027,7 +16033,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ71">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR71">
         <v>1.68</v>
@@ -16358,7 +16364,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16439,7 +16445,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ73">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR73">
         <v>1.29</v>
@@ -16851,7 +16857,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ75">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR75">
         <v>1.37</v>
@@ -16976,7 +16982,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17182,7 +17188,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17388,7 +17394,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17594,7 +17600,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -18006,7 +18012,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18496,7 +18502,7 @@
         <v>0.8</v>
       </c>
       <c r="AP83">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ83">
         <v>0.77</v>
@@ -18830,7 +18836,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19114,7 +19120,7 @@
         <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ86">
         <v>1</v>
@@ -19323,7 +19329,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ87">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR87">
         <v>1.49</v>
@@ -19448,7 +19454,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19654,7 +19660,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19732,7 +19738,7 @@
         <v>2.33</v>
       </c>
       <c r="AP89">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ89">
         <v>1.75</v>
@@ -19860,7 +19866,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20066,7 +20072,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20147,7 +20153,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ91">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR91">
         <v>1.35</v>
@@ -20478,7 +20484,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20684,7 +20690,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20890,7 +20896,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -21302,7 +21308,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21508,7 +21514,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21714,7 +21720,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21795,7 +21801,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ99">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR99">
         <v>1.62</v>
@@ -22332,7 +22338,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22619,7 +22625,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ103">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR103">
         <v>0.9399999999999999</v>
@@ -22744,7 +22750,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22950,7 +22956,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23028,7 +23034,7 @@
         <v>1.6</v>
       </c>
       <c r="AP105">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ105">
         <v>1.5</v>
@@ -23156,7 +23162,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23440,7 +23446,7 @@
         <v>0.33</v>
       </c>
       <c r="AP107">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ107">
         <v>0.31</v>
@@ -23852,10 +23858,10 @@
         <v>0.75</v>
       </c>
       <c r="AP109">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ109">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR109">
         <v>1.36</v>
@@ -23980,7 +23986,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24186,7 +24192,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24392,7 +24398,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24598,7 +24604,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24804,7 +24810,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -24885,7 +24891,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ114">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR114">
         <v>1.3</v>
@@ -25216,7 +25222,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25422,7 +25428,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25503,7 +25509,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ117">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR117">
         <v>1.63</v>
@@ -25628,7 +25634,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25915,7 +25921,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ119">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR119">
         <v>0.96</v>
@@ -26118,7 +26124,7 @@
         <v>2</v>
       </c>
       <c r="AP120">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ120">
         <v>2.15</v>
@@ -26246,7 +26252,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26658,7 +26664,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26736,7 +26742,7 @@
         <v>1.67</v>
       </c>
       <c r="AP123">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ123">
         <v>2.08</v>
@@ -26864,7 +26870,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27070,7 +27076,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27276,7 +27282,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27354,7 +27360,7 @@
         <v>1</v>
       </c>
       <c r="AP126">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ126">
         <v>0.58</v>
@@ -27769,7 +27775,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ128">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR128">
         <v>1.58</v>
@@ -27894,7 +27900,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -29130,7 +29136,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29211,7 +29217,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ135">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR135">
         <v>1.11</v>
@@ -29336,7 +29342,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29414,7 +29420,7 @@
         <v>1.83</v>
       </c>
       <c r="AP136">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ136">
         <v>2.15</v>
@@ -29620,10 +29626,10 @@
         <v>1.5</v>
       </c>
       <c r="AP137">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ137">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR137">
         <v>1.24</v>
@@ -29748,7 +29754,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29954,7 +29960,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30238,7 +30244,7 @@
         <v>1.17</v>
       </c>
       <c r="AP140">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ140">
         <v>0.67</v>
@@ -30447,7 +30453,7 @@
         <v>2</v>
       </c>
       <c r="AQ141">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR141">
         <v>1.73</v>
@@ -30778,7 +30784,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30859,7 +30865,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ143">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR143">
         <v>1.47</v>
@@ -30984,7 +30990,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31396,7 +31402,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31602,7 +31608,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31889,7 +31895,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ148">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR148">
         <v>1.5</v>
@@ -32014,7 +32020,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32426,7 +32432,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32632,7 +32638,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32838,7 +32844,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -33250,7 +33256,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -33328,7 +33334,7 @@
         <v>0.43</v>
       </c>
       <c r="AP155">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ155">
         <v>1</v>
@@ -33949,7 +33955,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ158">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR158">
         <v>1.52</v>
@@ -34074,7 +34080,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34361,7 +34367,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ160">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR160">
         <v>1.12</v>
@@ -34486,7 +34492,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34564,10 +34570,10 @@
         <v>1.5</v>
       </c>
       <c r="AP161">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ161">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR161">
         <v>1.07</v>
@@ -34692,7 +34698,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34898,7 +34904,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -34979,7 +34985,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ163">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR163">
         <v>1.36</v>
@@ -35310,7 +35316,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35516,7 +35522,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35722,7 +35728,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35928,7 +35934,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36212,7 +36218,7 @@
         <v>0.67</v>
       </c>
       <c r="AP169">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ169">
         <v>0.77</v>
@@ -36418,7 +36424,7 @@
         <v>0.88</v>
       </c>
       <c r="AP170">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ170">
         <v>0.58</v>
@@ -36546,7 +36552,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36627,7 +36633,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ171">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR171">
         <v>0.88</v>
@@ -36752,7 +36758,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36958,7 +36964,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37164,7 +37170,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37576,7 +37582,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -38194,7 +38200,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38400,7 +38406,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38606,7 +38612,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39018,7 +39024,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39305,7 +39311,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ184">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR184">
         <v>1.31</v>
@@ -39508,7 +39514,7 @@
         <v>0.88</v>
       </c>
       <c r="AP185">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ185">
         <v>0.67</v>
@@ -39717,7 +39723,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ186">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR186">
         <v>1.62</v>
@@ -39842,7 +39848,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40254,7 +40260,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40538,7 +40544,7 @@
         <v>2</v>
       </c>
       <c r="AP190">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ190">
         <v>1.75</v>
@@ -40666,7 +40672,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41284,7 +41290,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41902,7 +41908,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -41983,7 +41989,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ197">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR197">
         <v>1.54</v>
@@ -42314,7 +42320,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42392,10 +42398,10 @@
         <v>1.67</v>
       </c>
       <c r="AP199">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ199">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR199">
         <v>1.57</v>
@@ -42520,7 +42526,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42601,7 +42607,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ200">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR200">
         <v>1.55</v>
@@ -42726,7 +42732,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -43013,7 +43019,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ202">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR202">
         <v>1.44</v>
@@ -43138,7 +43144,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43550,7 +43556,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43834,7 +43840,7 @@
         <v>0.3</v>
       </c>
       <c r="AP206">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ206">
         <v>0.31</v>
@@ -43962,7 +43968,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44043,7 +44049,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ207">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR207">
         <v>1.12</v>
@@ -44168,7 +44174,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44246,7 +44252,7 @@
         <v>1.3</v>
       </c>
       <c r="AP208">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ208">
         <v>1</v>
@@ -44658,7 +44664,7 @@
         <v>0.9</v>
       </c>
       <c r="AP210">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ210">
         <v>0.83</v>
@@ -44786,7 +44792,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45279,7 +45285,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ213">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR213">
         <v>1.04</v>
@@ -45404,7 +45410,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45610,7 +45616,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45816,7 +45822,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -46022,7 +46028,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46228,7 +46234,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46640,7 +46646,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46718,7 +46724,7 @@
         <v>0.64</v>
       </c>
       <c r="AP220">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ220">
         <v>0.85</v>
@@ -46846,7 +46852,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47258,7 +47264,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47670,7 +47676,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47876,7 +47882,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -47957,7 +47963,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ226">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR226">
         <v>1.59</v>
@@ -48288,7 +48294,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48494,7 +48500,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48575,7 +48581,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ229">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR229">
         <v>1.45</v>
@@ -48906,7 +48912,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49112,7 +49118,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49318,7 +49324,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49399,7 +49405,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ233">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR233">
         <v>0.99</v>
@@ -49524,7 +49530,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -49602,10 +49608,10 @@
         <v>1.27</v>
       </c>
       <c r="AP234">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ234">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR234">
         <v>1.14</v>
@@ -50142,7 +50148,7 @@
         <v>241</v>
       </c>
       <c r="P237" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q237">
         <v>1.91</v>
@@ -50429,7 +50435,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ238">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR238">
         <v>1.34</v>
@@ -50554,7 +50560,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -50838,7 +50844,7 @@
         <v>1.64</v>
       </c>
       <c r="AP240">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ240">
         <v>1.5</v>
@@ -50966,7 +50972,7 @@
         <v>244</v>
       </c>
       <c r="P241" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q241">
         <v>2.5</v>
@@ -51378,7 +51384,7 @@
         <v>245</v>
       </c>
       <c r="P243" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q243">
         <v>3.4</v>
@@ -51790,7 +51796,7 @@
         <v>92</v>
       </c>
       <c r="P245" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q245">
         <v>2.6</v>
@@ -52408,7 +52414,7 @@
         <v>92</v>
       </c>
       <c r="P248" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q248">
         <v>4</v>
@@ -52486,7 +52492,7 @@
         <v>1</v>
       </c>
       <c r="AP248">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ248">
         <v>1.15</v>
@@ -53026,7 +53032,7 @@
         <v>92</v>
       </c>
       <c r="P251" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q251">
         <v>3.6</v>
@@ -53183,6 +53189,830 @@
       </c>
       <c r="BP251">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="252" spans="1:68">
+      <c r="A252" s="1">
+        <v>251</v>
+      </c>
+      <c r="B252">
+        <v>7492404</v>
+      </c>
+      <c r="C252" t="s">
+        <v>68</v>
+      </c>
+      <c r="D252" t="s">
+        <v>69</v>
+      </c>
+      <c r="E252" s="2">
+        <v>45710.45833333334</v>
+      </c>
+      <c r="F252">
+        <v>26</v>
+      </c>
+      <c r="G252" t="s">
+        <v>71</v>
+      </c>
+      <c r="H252" t="s">
+        <v>74</v>
+      </c>
+      <c r="I252">
+        <v>1</v>
+      </c>
+      <c r="J252">
+        <v>0</v>
+      </c>
+      <c r="K252">
+        <v>1</v>
+      </c>
+      <c r="L252">
+        <v>2</v>
+      </c>
+      <c r="M252">
+        <v>0</v>
+      </c>
+      <c r="N252">
+        <v>2</v>
+      </c>
+      <c r="O252" t="s">
+        <v>248</v>
+      </c>
+      <c r="P252" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q252">
+        <v>4.33</v>
+      </c>
+      <c r="R252">
+        <v>2.2</v>
+      </c>
+      <c r="S252">
+        <v>2.6</v>
+      </c>
+      <c r="T252">
+        <v>1.36</v>
+      </c>
+      <c r="U252">
+        <v>3</v>
+      </c>
+      <c r="V252">
+        <v>2.75</v>
+      </c>
+      <c r="W252">
+        <v>1.4</v>
+      </c>
+      <c r="X252">
+        <v>8</v>
+      </c>
+      <c r="Y252">
+        <v>1.08</v>
+      </c>
+      <c r="Z252">
+        <v>4.1</v>
+      </c>
+      <c r="AA252">
+        <v>3.72</v>
+      </c>
+      <c r="AB252">
+        <v>1.91</v>
+      </c>
+      <c r="AC252">
+        <v>1.03</v>
+      </c>
+      <c r="AD252">
+        <v>10</v>
+      </c>
+      <c r="AE252">
+        <v>1.23</v>
+      </c>
+      <c r="AF252">
+        <v>3.62</v>
+      </c>
+      <c r="AG252">
+        <v>1.85</v>
+      </c>
+      <c r="AH252">
+        <v>1.96</v>
+      </c>
+      <c r="AI252">
+        <v>1.75</v>
+      </c>
+      <c r="AJ252">
+        <v>2</v>
+      </c>
+      <c r="AK252">
+        <v>1.87</v>
+      </c>
+      <c r="AL252">
+        <v>1.28</v>
+      </c>
+      <c r="AM252">
+        <v>1.24</v>
+      </c>
+      <c r="AN252">
+        <v>0.92</v>
+      </c>
+      <c r="AO252">
+        <v>1.5</v>
+      </c>
+      <c r="AP252">
+        <v>1.07</v>
+      </c>
+      <c r="AQ252">
+        <v>1.38</v>
+      </c>
+      <c r="AR252">
+        <v>1.39</v>
+      </c>
+      <c r="AS252">
+        <v>1.25</v>
+      </c>
+      <c r="AT252">
+        <v>2.64</v>
+      </c>
+      <c r="AU252">
+        <v>4</v>
+      </c>
+      <c r="AV252">
+        <v>2</v>
+      </c>
+      <c r="AW252">
+        <v>1</v>
+      </c>
+      <c r="AX252">
+        <v>15</v>
+      </c>
+      <c r="AY252">
+        <v>6</v>
+      </c>
+      <c r="AZ252">
+        <v>18</v>
+      </c>
+      <c r="BA252">
+        <v>0</v>
+      </c>
+      <c r="BB252">
+        <v>4</v>
+      </c>
+      <c r="BC252">
+        <v>4</v>
+      </c>
+      <c r="BD252">
+        <v>2.32</v>
+      </c>
+      <c r="BE252">
+        <v>6.5</v>
+      </c>
+      <c r="BF252">
+        <v>1.74</v>
+      </c>
+      <c r="BG252">
+        <v>1.32</v>
+      </c>
+      <c r="BH252">
+        <v>3.05</v>
+      </c>
+      <c r="BI252">
+        <v>1.54</v>
+      </c>
+      <c r="BJ252">
+        <v>2.3</v>
+      </c>
+      <c r="BK252">
+        <v>1.88</v>
+      </c>
+      <c r="BL252">
+        <v>1.81</v>
+      </c>
+      <c r="BM252">
+        <v>2.38</v>
+      </c>
+      <c r="BN252">
+        <v>1.5</v>
+      </c>
+      <c r="BO252">
+        <v>3.05</v>
+      </c>
+      <c r="BP252">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="253" spans="1:68">
+      <c r="A253" s="1">
+        <v>252</v>
+      </c>
+      <c r="B253">
+        <v>7492407</v>
+      </c>
+      <c r="C253" t="s">
+        <v>68</v>
+      </c>
+      <c r="D253" t="s">
+        <v>69</v>
+      </c>
+      <c r="E253" s="2">
+        <v>45710.45833333334</v>
+      </c>
+      <c r="F253">
+        <v>26</v>
+      </c>
+      <c r="G253" t="s">
+        <v>87</v>
+      </c>
+      <c r="H253" t="s">
+        <v>77</v>
+      </c>
+      <c r="I253">
+        <v>0</v>
+      </c>
+      <c r="J253">
+        <v>0</v>
+      </c>
+      <c r="K253">
+        <v>0</v>
+      </c>
+      <c r="L253">
+        <v>0</v>
+      </c>
+      <c r="M253">
+        <v>0</v>
+      </c>
+      <c r="N253">
+        <v>0</v>
+      </c>
+      <c r="O253" t="s">
+        <v>92</v>
+      </c>
+      <c r="P253" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q253">
+        <v>5</v>
+      </c>
+      <c r="R253">
+        <v>2.3</v>
+      </c>
+      <c r="S253">
+        <v>2.25</v>
+      </c>
+      <c r="T253">
+        <v>1.33</v>
+      </c>
+      <c r="U253">
+        <v>3.25</v>
+      </c>
+      <c r="V253">
+        <v>2.63</v>
+      </c>
+      <c r="W253">
+        <v>1.44</v>
+      </c>
+      <c r="X253">
+        <v>6.5</v>
+      </c>
+      <c r="Y253">
+        <v>1.11</v>
+      </c>
+      <c r="Z253">
+        <v>4.6</v>
+      </c>
+      <c r="AA253">
+        <v>4.1</v>
+      </c>
+      <c r="AB253">
+        <v>1.75</v>
+      </c>
+      <c r="AC253">
+        <v>1.02</v>
+      </c>
+      <c r="AD253">
+        <v>11</v>
+      </c>
+      <c r="AE253">
+        <v>1.2</v>
+      </c>
+      <c r="AF253">
+        <v>3.94</v>
+      </c>
+      <c r="AG253">
+        <v>1.8</v>
+      </c>
+      <c r="AH253">
+        <v>2.02</v>
+      </c>
+      <c r="AI253">
+        <v>1.75</v>
+      </c>
+      <c r="AJ253">
+        <v>2</v>
+      </c>
+      <c r="AK253">
+        <v>2.18</v>
+      </c>
+      <c r="AL253">
+        <v>1.25</v>
+      </c>
+      <c r="AM253">
+        <v>1.19</v>
+      </c>
+      <c r="AN253">
+        <v>1</v>
+      </c>
+      <c r="AO253">
+        <v>1.75</v>
+      </c>
+      <c r="AP253">
+        <v>1</v>
+      </c>
+      <c r="AQ253">
+        <v>1.69</v>
+      </c>
+      <c r="AR253">
+        <v>1.35</v>
+      </c>
+      <c r="AS253">
+        <v>1.58</v>
+      </c>
+      <c r="AT253">
+        <v>2.93</v>
+      </c>
+      <c r="AU253">
+        <v>3</v>
+      </c>
+      <c r="AV253">
+        <v>4</v>
+      </c>
+      <c r="AW253">
+        <v>7</v>
+      </c>
+      <c r="AX253">
+        <v>6</v>
+      </c>
+      <c r="AY253">
+        <v>13</v>
+      </c>
+      <c r="AZ253">
+        <v>12</v>
+      </c>
+      <c r="BA253">
+        <v>6</v>
+      </c>
+      <c r="BB253">
+        <v>6</v>
+      </c>
+      <c r="BC253">
+        <v>12</v>
+      </c>
+      <c r="BD253">
+        <v>2.7</v>
+      </c>
+      <c r="BE253">
+        <v>6.75</v>
+      </c>
+      <c r="BF253">
+        <v>1.54</v>
+      </c>
+      <c r="BG253">
+        <v>1.22</v>
+      </c>
+      <c r="BH253">
+        <v>3.65</v>
+      </c>
+      <c r="BI253">
+        <v>1.4</v>
+      </c>
+      <c r="BJ253">
+        <v>2.65</v>
+      </c>
+      <c r="BK253">
+        <v>1.67</v>
+      </c>
+      <c r="BL253">
+        <v>2.04</v>
+      </c>
+      <c r="BM253">
+        <v>2.06</v>
+      </c>
+      <c r="BN253">
+        <v>1.66</v>
+      </c>
+      <c r="BO253">
+        <v>2.6</v>
+      </c>
+      <c r="BP253">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="254" spans="1:68">
+      <c r="A254" s="1">
+        <v>253</v>
+      </c>
+      <c r="B254">
+        <v>7492406</v>
+      </c>
+      <c r="C254" t="s">
+        <v>68</v>
+      </c>
+      <c r="D254" t="s">
+        <v>69</v>
+      </c>
+      <c r="E254" s="2">
+        <v>45710.58333333334</v>
+      </c>
+      <c r="F254">
+        <v>26</v>
+      </c>
+      <c r="G254" t="s">
+        <v>84</v>
+      </c>
+      <c r="H254" t="s">
+        <v>73</v>
+      </c>
+      <c r="I254">
+        <v>1</v>
+      </c>
+      <c r="J254">
+        <v>0</v>
+      </c>
+      <c r="K254">
+        <v>1</v>
+      </c>
+      <c r="L254">
+        <v>2</v>
+      </c>
+      <c r="M254">
+        <v>1</v>
+      </c>
+      <c r="N254">
+        <v>3</v>
+      </c>
+      <c r="O254" t="s">
+        <v>249</v>
+      </c>
+      <c r="P254" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q254">
+        <v>4</v>
+      </c>
+      <c r="R254">
+        <v>2.1</v>
+      </c>
+      <c r="S254">
+        <v>2.75</v>
+      </c>
+      <c r="T254">
+        <v>1.44</v>
+      </c>
+      <c r="U254">
+        <v>2.63</v>
+      </c>
+      <c r="V254">
+        <v>3.25</v>
+      </c>
+      <c r="W254">
+        <v>1.33</v>
+      </c>
+      <c r="X254">
+        <v>9</v>
+      </c>
+      <c r="Y254">
+        <v>1.07</v>
+      </c>
+      <c r="Z254">
+        <v>3.77</v>
+      </c>
+      <c r="AA254">
+        <v>3.5</v>
+      </c>
+      <c r="AB254">
+        <v>2.06</v>
+      </c>
+      <c r="AC254">
+        <v>1.03</v>
+      </c>
+      <c r="AD254">
+        <v>9</v>
+      </c>
+      <c r="AE254">
+        <v>1.28</v>
+      </c>
+      <c r="AF254">
+        <v>3.25</v>
+      </c>
+      <c r="AG254">
+        <v>2</v>
+      </c>
+      <c r="AH254">
+        <v>1.82</v>
+      </c>
+      <c r="AI254">
+        <v>1.91</v>
+      </c>
+      <c r="AJ254">
+        <v>1.91</v>
+      </c>
+      <c r="AK254">
+        <v>1.75</v>
+      </c>
+      <c r="AL254">
+        <v>1.3</v>
+      </c>
+      <c r="AM254">
+        <v>1.28</v>
+      </c>
+      <c r="AN254">
+        <v>1.17</v>
+      </c>
+      <c r="AO254">
+        <v>1.55</v>
+      </c>
+      <c r="AP254">
+        <v>1.31</v>
+      </c>
+      <c r="AQ254">
+        <v>1.42</v>
+      </c>
+      <c r="AR254">
+        <v>1.15</v>
+      </c>
+      <c r="AS254">
+        <v>1.48</v>
+      </c>
+      <c r="AT254">
+        <v>2.63</v>
+      </c>
+      <c r="AU254">
+        <v>4</v>
+      </c>
+      <c r="AV254">
+        <v>9</v>
+      </c>
+      <c r="AW254">
+        <v>6</v>
+      </c>
+      <c r="AX254">
+        <v>18</v>
+      </c>
+      <c r="AY254">
+        <v>12</v>
+      </c>
+      <c r="AZ254">
+        <v>31</v>
+      </c>
+      <c r="BA254">
+        <v>4</v>
+      </c>
+      <c r="BB254">
+        <v>11</v>
+      </c>
+      <c r="BC254">
+        <v>15</v>
+      </c>
+      <c r="BD254">
+        <v>2.4</v>
+      </c>
+      <c r="BE254">
+        <v>6.4</v>
+      </c>
+      <c r="BF254">
+        <v>1.71</v>
+      </c>
+      <c r="BG254">
+        <v>1.4</v>
+      </c>
+      <c r="BH254">
+        <v>2.65</v>
+      </c>
+      <c r="BI254">
+        <v>1.67</v>
+      </c>
+      <c r="BJ254">
+        <v>2.05</v>
+      </c>
+      <c r="BK254">
+        <v>2.08</v>
+      </c>
+      <c r="BL254">
+        <v>1.65</v>
+      </c>
+      <c r="BM254">
+        <v>2.65</v>
+      </c>
+      <c r="BN254">
+        <v>1.4</v>
+      </c>
+      <c r="BO254">
+        <v>3.55</v>
+      </c>
+      <c r="BP254">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="255" spans="1:68">
+      <c r="A255" s="1">
+        <v>254</v>
+      </c>
+      <c r="B255">
+        <v>7492402</v>
+      </c>
+      <c r="C255" t="s">
+        <v>68</v>
+      </c>
+      <c r="D255" t="s">
+        <v>69</v>
+      </c>
+      <c r="E255" s="2">
+        <v>45710.69791666666</v>
+      </c>
+      <c r="F255">
+        <v>26</v>
+      </c>
+      <c r="G255" t="s">
+        <v>82</v>
+      </c>
+      <c r="H255" t="s">
+        <v>70</v>
+      </c>
+      <c r="I255">
+        <v>0</v>
+      </c>
+      <c r="J255">
+        <v>0</v>
+      </c>
+      <c r="K255">
+        <v>0</v>
+      </c>
+      <c r="L255">
+        <v>1</v>
+      </c>
+      <c r="M255">
+        <v>0</v>
+      </c>
+      <c r="N255">
+        <v>1</v>
+      </c>
+      <c r="O255" t="s">
+        <v>217</v>
+      </c>
+      <c r="P255" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q255">
+        <v>1.73</v>
+      </c>
+      <c r="R255">
+        <v>2.6</v>
+      </c>
+      <c r="S255">
+        <v>9</v>
+      </c>
+      <c r="T255">
+        <v>1.3</v>
+      </c>
+      <c r="U255">
+        <v>3.4</v>
+      </c>
+      <c r="V255">
+        <v>2.5</v>
+      </c>
+      <c r="W255">
+        <v>1.5</v>
+      </c>
+      <c r="X255">
+        <v>6</v>
+      </c>
+      <c r="Y255">
+        <v>1.13</v>
+      </c>
+      <c r="Z255">
+        <v>1.28</v>
+      </c>
+      <c r="AA255">
+        <v>6.2</v>
+      </c>
+      <c r="AB255">
+        <v>11</v>
+      </c>
+      <c r="AC255">
+        <v>1.01</v>
+      </c>
+      <c r="AD255">
+        <v>12</v>
+      </c>
+      <c r="AE255">
+        <v>1.17</v>
+      </c>
+      <c r="AF255">
+        <v>4.25</v>
+      </c>
+      <c r="AG255">
+        <v>1.65</v>
+      </c>
+      <c r="AH255">
+        <v>2.15</v>
+      </c>
+      <c r="AI255">
+        <v>2.1</v>
+      </c>
+      <c r="AJ255">
+        <v>1.67</v>
+      </c>
+      <c r="AK255">
+        <v>1.06</v>
+      </c>
+      <c r="AL255">
+        <v>1.14</v>
+      </c>
+      <c r="AM255">
+        <v>3.6</v>
+      </c>
+      <c r="AN255">
+        <v>2.25</v>
+      </c>
+      <c r="AO255">
+        <v>1.25</v>
+      </c>
+      <c r="AP255">
+        <v>2.31</v>
+      </c>
+      <c r="AQ255">
+        <v>1.15</v>
+      </c>
+      <c r="AR255">
+        <v>1.71</v>
+      </c>
+      <c r="AS255">
+        <v>1.03</v>
+      </c>
+      <c r="AT255">
+        <v>2.74</v>
+      </c>
+      <c r="AU255">
+        <v>6</v>
+      </c>
+      <c r="AV255">
+        <v>3</v>
+      </c>
+      <c r="AW255">
+        <v>13</v>
+      </c>
+      <c r="AX255">
+        <v>9</v>
+      </c>
+      <c r="AY255">
+        <v>26</v>
+      </c>
+      <c r="AZ255">
+        <v>16</v>
+      </c>
+      <c r="BA255">
+        <v>6</v>
+      </c>
+      <c r="BB255">
+        <v>7</v>
+      </c>
+      <c r="BC255">
+        <v>13</v>
+      </c>
+      <c r="BD255">
+        <v>1.16</v>
+      </c>
+      <c r="BE255">
+        <v>9</v>
+      </c>
+      <c r="BF255">
+        <v>5.6</v>
+      </c>
+      <c r="BG255">
+        <v>1.28</v>
+      </c>
+      <c r="BH255">
+        <v>3.2</v>
+      </c>
+      <c r="BI255">
+        <v>1.49</v>
+      </c>
+      <c r="BJ255">
+        <v>2.4</v>
+      </c>
+      <c r="BK255">
+        <v>1.8</v>
+      </c>
+      <c r="BL255">
+        <v>1.89</v>
+      </c>
+      <c r="BM255">
+        <v>2.25</v>
+      </c>
+      <c r="BN255">
+        <v>1.55</v>
+      </c>
+      <c r="BO255">
+        <v>2.9</v>
+      </c>
+      <c r="BP255">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="372">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -766,6 +766,12 @@
     <t>['5', '76']</t>
   </si>
   <si>
+    <t>['7', '77']</t>
+  </si>
+  <si>
+    <t>['90+5']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -779,9 +785,6 @@
   </si>
   <si>
     <t>['35', '45', '57', '66']</t>
-  </si>
-  <si>
-    <t>['90+5']</t>
   </si>
   <si>
     <t>['66']</t>
@@ -1121,6 +1124,12 @@
   </si>
   <si>
     <t>['41', '66']</t>
+  </si>
+  <si>
+    <t>['27', '33', '43', '55', '74']</t>
+  </si>
+  <si>
+    <t>['12']</t>
   </si>
 </sst>
 </file>
@@ -1482,7 +1491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP255"/>
+  <dimension ref="A1:BP259"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1738,7 +1747,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2025,7 +2034,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ3">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2228,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ4">
         <v>0.58</v>
@@ -2356,7 +2365,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2562,7 +2571,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2846,10 +2855,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ7">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3052,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ8">
         <v>1.15</v>
@@ -3180,7 +3189,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3386,7 +3395,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3467,7 +3476,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ10">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3798,7 +3807,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="Q12">
         <v>3.75</v>
@@ -4004,7 +4013,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4210,7 +4219,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4909,7 +4918,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ17">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5240,7 +5249,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5524,7 +5533,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ20">
         <v>0.77</v>
@@ -5652,7 +5661,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5730,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ21">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR21">
         <v>1.14</v>
@@ -5858,7 +5867,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6145,7 +6154,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ23">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR23">
         <v>1.3</v>
@@ -6270,7 +6279,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6682,7 +6691,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6888,7 +6897,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7094,7 +7103,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7300,7 +7309,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7918,7 +7927,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -7996,7 +8005,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ32">
         <v>1.38</v>
@@ -8202,10 +8211,10 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ33">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR33">
         <v>0.96</v>
@@ -8742,7 +8751,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -8823,7 +8832,7 @@
         <v>2</v>
       </c>
       <c r="AQ36">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR36">
         <v>0</v>
@@ -9154,7 +9163,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9232,10 +9241,10 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ38">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AR38">
         <v>1.24</v>
@@ -9360,7 +9369,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9566,7 +9575,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9772,7 +9781,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9978,7 +9987,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10056,7 +10065,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ42">
         <v>1</v>
@@ -10184,7 +10193,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10262,7 +10271,7 @@
         <v>2</v>
       </c>
       <c r="AP43">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ43">
         <v>1.08</v>
@@ -10677,7 +10686,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ45">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AR45">
         <v>1.23</v>
@@ -10802,7 +10811,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -11008,7 +11017,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11214,7 +11223,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11626,7 +11635,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11832,7 +11841,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12244,7 +12253,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12450,7 +12459,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12531,7 +12540,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ54">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR54">
         <v>1.48</v>
@@ -12656,7 +12665,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12737,7 +12746,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ55">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR55">
         <v>1.78</v>
@@ -12862,7 +12871,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13068,7 +13077,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13146,7 +13155,7 @@
         <v>1.5</v>
       </c>
       <c r="AP57">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ57">
         <v>1</v>
@@ -13558,10 +13567,10 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ59">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR59">
         <v>0.91</v>
@@ -13892,7 +13901,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14382,7 +14391,7 @@
         <v>0.25</v>
       </c>
       <c r="AP63">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ63">
         <v>0.31</v>
@@ -14716,7 +14725,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14922,7 +14931,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15128,7 +15137,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15334,7 +15343,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q68">
         <v>2.2</v>
@@ -15746,7 +15755,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -16236,7 +16245,7 @@
         <v>0.67</v>
       </c>
       <c r="AP72">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ72">
         <v>0.67</v>
@@ -16364,7 +16373,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16982,7 +16991,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17060,10 +17069,10 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ76">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AR76">
         <v>0.85</v>
@@ -17188,7 +17197,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17269,7 +17278,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ77">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR77">
         <v>1.41</v>
@@ -17394,7 +17403,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17475,7 +17484,7 @@
         <v>1</v>
       </c>
       <c r="AQ78">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR78">
         <v>1.31</v>
@@ -17600,7 +17609,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17678,7 +17687,7 @@
         <v>1.75</v>
       </c>
       <c r="AP79">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ79">
         <v>1.08</v>
@@ -18012,7 +18021,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18090,7 +18099,7 @@
         <v>0.67</v>
       </c>
       <c r="AP81">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ81">
         <v>0.58</v>
@@ -18836,7 +18845,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19454,7 +19463,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19660,7 +19669,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19741,7 +19750,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ89">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR89">
         <v>1.46</v>
@@ -19866,7 +19875,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20072,7 +20081,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20150,7 +20159,7 @@
         <v>1.25</v>
       </c>
       <c r="AP91">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ91">
         <v>1.38</v>
@@ -20484,7 +20493,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20565,7 +20574,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ93">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AR93">
         <v>1.71</v>
@@ -20690,7 +20699,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20896,7 +20905,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -20974,7 +20983,7 @@
         <v>2</v>
       </c>
       <c r="AP95">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ95">
         <v>2.08</v>
@@ -21308,7 +21317,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21514,7 +21523,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21595,7 +21604,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ98">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR98">
         <v>1.23</v>
@@ -21720,7 +21729,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21798,7 +21807,7 @@
         <v>0.75</v>
       </c>
       <c r="AP99">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ99">
         <v>1.69</v>
@@ -22338,7 +22347,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22419,7 +22428,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ102">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR102">
         <v>1.16</v>
@@ -22750,7 +22759,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22831,7 +22840,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ104">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR104">
         <v>1.61</v>
@@ -22956,7 +22965,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23037,7 +23046,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ105">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR105">
         <v>1.14</v>
@@ -23162,7 +23171,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23240,7 +23249,7 @@
         <v>0.8</v>
       </c>
       <c r="AP106">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ106">
         <v>1.15</v>
@@ -23652,7 +23661,7 @@
         <v>0.67</v>
       </c>
       <c r="AP108">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ108">
         <v>0.77</v>
@@ -23986,7 +23995,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24192,7 +24201,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24398,7 +24407,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24604,7 +24613,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24810,7 +24819,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -24888,7 +24897,7 @@
         <v>1.4</v>
       </c>
       <c r="AP114">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ114">
         <v>1.42</v>
@@ -25222,7 +25231,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25428,7 +25437,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25634,7 +25643,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -26127,7 +26136,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ120">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AR120">
         <v>1.62</v>
@@ -26252,7 +26261,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26330,7 +26339,7 @@
         <v>2.2</v>
       </c>
       <c r="AP121">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ121">
         <v>2.08</v>
@@ -26539,7 +26548,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ122">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR122">
         <v>1.69</v>
@@ -26664,7 +26673,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26745,7 +26754,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ123">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR123">
         <v>1.29</v>
@@ -26870,7 +26879,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27076,7 +27085,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27154,10 +27163,10 @@
         <v>1.83</v>
       </c>
       <c r="AP125">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ125">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR125">
         <v>1.5</v>
@@ -27282,7 +27291,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27900,7 +27909,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -27978,7 +27987,7 @@
         <v>0.67</v>
       </c>
       <c r="AP129">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ129">
         <v>1.23</v>
@@ -28390,7 +28399,7 @@
         <v>0.5</v>
       </c>
       <c r="AP131">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ131">
         <v>1</v>
@@ -28596,7 +28605,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ132">
         <v>0.58</v>
@@ -29136,7 +29145,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29342,7 +29351,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29423,7 +29432,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ136">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AR136">
         <v>1.14</v>
@@ -29754,7 +29763,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29835,7 +29844,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ138">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR138">
         <v>1.39</v>
@@ -29960,7 +29969,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30041,7 +30050,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ139">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR139">
         <v>1.59</v>
@@ -30784,7 +30793,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30990,7 +30999,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31402,7 +31411,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31480,7 +31489,7 @@
         <v>1.29</v>
       </c>
       <c r="AP146">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ146">
         <v>1</v>
@@ -31608,7 +31617,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -32020,7 +32029,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32304,7 +32313,7 @@
         <v>1</v>
       </c>
       <c r="AP150">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ150">
         <v>1.08</v>
@@ -32432,7 +32441,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32510,10 +32519,10 @@
         <v>2</v>
       </c>
       <c r="AP151">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ151">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR151">
         <v>1.42</v>
@@ -32638,7 +32647,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32719,7 +32728,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ152">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AR152">
         <v>1.05</v>
@@ -32844,7 +32853,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -33256,7 +33265,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -33543,7 +33552,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ156">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR156">
         <v>1.61</v>
@@ -33746,7 +33755,7 @@
         <v>0.57</v>
       </c>
       <c r="AP157">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ157">
         <v>1.15</v>
@@ -34080,7 +34089,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34364,7 +34373,7 @@
         <v>1.14</v>
       </c>
       <c r="AP160">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ160">
         <v>1.42</v>
@@ -34492,7 +34501,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34698,7 +34707,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34779,7 +34788,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ162">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AR162">
         <v>1.24</v>
@@ -34904,7 +34913,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35316,7 +35325,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35522,7 +35531,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35728,7 +35737,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35809,7 +35818,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ167">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR167">
         <v>1.14</v>
@@ -35934,7 +35943,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36552,7 +36561,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36630,7 +36639,7 @@
         <v>1.43</v>
       </c>
       <c r="AP171">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ171">
         <v>1.15</v>
@@ -36758,7 +36767,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36836,7 +36845,7 @@
         <v>2.43</v>
       </c>
       <c r="AP172">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ172">
         <v>2.08</v>
@@ -36964,7 +36973,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37045,7 +37054,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ173">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR173">
         <v>1.48</v>
@@ -37170,7 +37179,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37582,7 +37591,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -37663,7 +37672,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ176">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR176">
         <v>1.42</v>
@@ -38072,7 +38081,7 @@
         <v>0.5</v>
       </c>
       <c r="AP178">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ178">
         <v>0.85</v>
@@ -38200,7 +38209,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38406,7 +38415,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38612,7 +38621,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38693,7 +38702,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ181">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AR181">
         <v>1.57</v>
@@ -38896,7 +38905,7 @@
         <v>1.22</v>
       </c>
       <c r="AP182">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ182">
         <v>1.23</v>
@@ -39024,7 +39033,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39848,7 +39857,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40135,7 +40144,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ188">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR188">
         <v>1.04</v>
@@ -40260,7 +40269,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40338,7 +40347,7 @@
         <v>0.44</v>
       </c>
       <c r="AP189">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ189">
         <v>0.85</v>
@@ -40547,7 +40556,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ190">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR190">
         <v>1.04</v>
@@ -40672,7 +40681,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41290,7 +41299,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41783,7 +41792,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ196">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR196">
         <v>1.17</v>
@@ -41908,7 +41917,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -41986,7 +41995,7 @@
         <v>1.38</v>
       </c>
       <c r="AP197">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ197">
         <v>1.42</v>
@@ -42195,7 +42204,7 @@
         <v>2</v>
       </c>
       <c r="AQ198">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR198">
         <v>1.78</v>
@@ -42320,7 +42329,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42526,7 +42535,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42732,7 +42741,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -43144,7 +43153,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43225,7 +43234,7 @@
         <v>2</v>
       </c>
       <c r="AQ203">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AR203">
         <v>1.78</v>
@@ -43556,7 +43565,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43634,7 +43643,7 @@
         <v>0.7</v>
       </c>
       <c r="AP205">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ205">
         <v>0.85</v>
@@ -43968,7 +43977,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44046,7 +44055,7 @@
         <v>1.5</v>
       </c>
       <c r="AP207">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ207">
         <v>1.69</v>
@@ -44174,7 +44183,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44458,7 +44467,7 @@
         <v>1.2</v>
       </c>
       <c r="AP209">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ209">
         <v>1.23</v>
@@ -44792,7 +44801,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -44870,10 +44879,10 @@
         <v>1.91</v>
       </c>
       <c r="AP211">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ211">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR211">
         <v>1.53</v>
@@ -45079,7 +45088,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ212">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR212">
         <v>1.61</v>
@@ -45282,7 +45291,7 @@
         <v>1.6</v>
       </c>
       <c r="AP213">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ213">
         <v>1.38</v>
@@ -45410,7 +45419,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45616,7 +45625,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45822,7 +45831,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -46028,7 +46037,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46109,7 +46118,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ217">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR217">
         <v>1.44</v>
@@ -46234,7 +46243,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46646,7 +46655,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46852,7 +46861,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47264,7 +47273,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47676,7 +47685,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47882,7 +47891,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -48294,7 +48303,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48375,7 +48384,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ228">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AR228">
         <v>1.58</v>
@@ -48500,7 +48509,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48578,7 +48587,7 @@
         <v>1.64</v>
       </c>
       <c r="AP229">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ229">
         <v>1.69</v>
@@ -48912,7 +48921,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -48990,10 +48999,10 @@
         <v>1.64</v>
       </c>
       <c r="AP231">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ231">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR231">
         <v>1.56</v>
@@ -49118,7 +49127,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49196,10 +49205,10 @@
         <v>2</v>
       </c>
       <c r="AP232">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ232">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR232">
         <v>1.18</v>
@@ -49324,7 +49333,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49402,7 +49411,7 @@
         <v>1.4</v>
       </c>
       <c r="AP233">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ233">
         <v>1.42</v>
@@ -49530,7 +49539,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -50020,7 +50029,7 @@
         <v>0.73</v>
       </c>
       <c r="AP236">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ236">
         <v>0.67</v>
@@ -50148,7 +50157,7 @@
         <v>241</v>
       </c>
       <c r="P237" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q237">
         <v>1.91</v>
@@ -50560,7 +50569,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -50847,7 +50856,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ240">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR240">
         <v>1.63</v>
@@ -50972,7 +50981,7 @@
         <v>244</v>
       </c>
       <c r="P241" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q241">
         <v>2.5</v>
@@ -51384,7 +51393,7 @@
         <v>245</v>
       </c>
       <c r="P243" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q243">
         <v>3.4</v>
@@ -51465,7 +51474,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ243">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AR243">
         <v>1.63</v>
@@ -51796,7 +51805,7 @@
         <v>92</v>
       </c>
       <c r="P245" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q245">
         <v>2.6</v>
@@ -52414,7 +52423,7 @@
         <v>92</v>
       </c>
       <c r="P248" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q248">
         <v>4</v>
@@ -53032,7 +53041,7 @@
         <v>92</v>
       </c>
       <c r="P251" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q251">
         <v>3.6</v>
@@ -54013,6 +54022,830 @@
       </c>
       <c r="BP255">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="256" spans="1:68">
+      <c r="A256" s="1">
+        <v>255</v>
+      </c>
+      <c r="B256">
+        <v>7492399</v>
+      </c>
+      <c r="C256" t="s">
+        <v>68</v>
+      </c>
+      <c r="D256" t="s">
+        <v>69</v>
+      </c>
+      <c r="E256" s="2">
+        <v>45711.35416666666</v>
+      </c>
+      <c r="F256">
+        <v>26</v>
+      </c>
+      <c r="G256" t="s">
+        <v>88</v>
+      </c>
+      <c r="H256" t="s">
+        <v>85</v>
+      </c>
+      <c r="I256">
+        <v>1</v>
+      </c>
+      <c r="J256">
+        <v>1</v>
+      </c>
+      <c r="K256">
+        <v>2</v>
+      </c>
+      <c r="L256">
+        <v>2</v>
+      </c>
+      <c r="M256">
+        <v>1</v>
+      </c>
+      <c r="N256">
+        <v>3</v>
+      </c>
+      <c r="O256" t="s">
+        <v>250</v>
+      </c>
+      <c r="P256" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q256">
+        <v>4</v>
+      </c>
+      <c r="R256">
+        <v>2.05</v>
+      </c>
+      <c r="S256">
+        <v>2.88</v>
+      </c>
+      <c r="T256">
+        <v>1.44</v>
+      </c>
+      <c r="U256">
+        <v>2.63</v>
+      </c>
+      <c r="V256">
+        <v>3.25</v>
+      </c>
+      <c r="W256">
+        <v>1.33</v>
+      </c>
+      <c r="X256">
+        <v>10</v>
+      </c>
+      <c r="Y256">
+        <v>1.06</v>
+      </c>
+      <c r="Z256">
+        <v>3.61</v>
+      </c>
+      <c r="AA256">
+        <v>3.23</v>
+      </c>
+      <c r="AB256">
+        <v>2.23</v>
+      </c>
+      <c r="AC256">
+        <v>1.08</v>
+      </c>
+      <c r="AD256">
+        <v>8.5</v>
+      </c>
+      <c r="AE256">
+        <v>1.4</v>
+      </c>
+      <c r="AF256">
+        <v>3</v>
+      </c>
+      <c r="AG256">
+        <v>1.8</v>
+      </c>
+      <c r="AH256">
+        <v>1.95</v>
+      </c>
+      <c r="AI256">
+        <v>1.95</v>
+      </c>
+      <c r="AJ256">
+        <v>1.8</v>
+      </c>
+      <c r="AK256">
+        <v>1.68</v>
+      </c>
+      <c r="AL256">
+        <v>1.32</v>
+      </c>
+      <c r="AM256">
+        <v>1.3</v>
+      </c>
+      <c r="AN256">
+        <v>1.25</v>
+      </c>
+      <c r="AO256">
+        <v>2.15</v>
+      </c>
+      <c r="AP256">
+        <v>1.38</v>
+      </c>
+      <c r="AQ256">
+        <v>2</v>
+      </c>
+      <c r="AR256">
+        <v>1.57</v>
+      </c>
+      <c r="AS256">
+        <v>1.15</v>
+      </c>
+      <c r="AT256">
+        <v>2.72</v>
+      </c>
+      <c r="AU256">
+        <v>4</v>
+      </c>
+      <c r="AV256">
+        <v>5</v>
+      </c>
+      <c r="AW256">
+        <v>5</v>
+      </c>
+      <c r="AX256">
+        <v>9</v>
+      </c>
+      <c r="AY256">
+        <v>11</v>
+      </c>
+      <c r="AZ256">
+        <v>17</v>
+      </c>
+      <c r="BA256">
+        <v>4</v>
+      </c>
+      <c r="BB256">
+        <v>6</v>
+      </c>
+      <c r="BC256">
+        <v>10</v>
+      </c>
+      <c r="BD256">
+        <v>2.33</v>
+      </c>
+      <c r="BE256">
+        <v>6.25</v>
+      </c>
+      <c r="BF256">
+        <v>1.74</v>
+      </c>
+      <c r="BG256">
+        <v>1.41</v>
+      </c>
+      <c r="BH256">
+        <v>2.65</v>
+      </c>
+      <c r="BI256">
+        <v>1.7</v>
+      </c>
+      <c r="BJ256">
+        <v>2</v>
+      </c>
+      <c r="BK256">
+        <v>2.12</v>
+      </c>
+      <c r="BL256">
+        <v>1.62</v>
+      </c>
+      <c r="BM256">
+        <v>2.7</v>
+      </c>
+      <c r="BN256">
+        <v>1.38</v>
+      </c>
+      <c r="BO256">
+        <v>3.65</v>
+      </c>
+      <c r="BP256">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="257" spans="1:68">
+      <c r="A257" s="1">
+        <v>256</v>
+      </c>
+      <c r="B257">
+        <v>7492401</v>
+      </c>
+      <c r="C257" t="s">
+        <v>68</v>
+      </c>
+      <c r="D257" t="s">
+        <v>69</v>
+      </c>
+      <c r="E257" s="2">
+        <v>45711.45833333334</v>
+      </c>
+      <c r="F257">
+        <v>26</v>
+      </c>
+      <c r="G257" t="s">
+        <v>75</v>
+      </c>
+      <c r="H257" t="s">
+        <v>83</v>
+      </c>
+      <c r="I257">
+        <v>0</v>
+      </c>
+      <c r="J257">
+        <v>0</v>
+      </c>
+      <c r="K257">
+        <v>0</v>
+      </c>
+      <c r="L257">
+        <v>1</v>
+      </c>
+      <c r="M257">
+        <v>0</v>
+      </c>
+      <c r="N257">
+        <v>1</v>
+      </c>
+      <c r="O257" t="s">
+        <v>251</v>
+      </c>
+      <c r="P257" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q257">
+        <v>4.5</v>
+      </c>
+      <c r="R257">
+        <v>2.2</v>
+      </c>
+      <c r="S257">
+        <v>2.5</v>
+      </c>
+      <c r="T257">
+        <v>1.4</v>
+      </c>
+      <c r="U257">
+        <v>2.75</v>
+      </c>
+      <c r="V257">
+        <v>3</v>
+      </c>
+      <c r="W257">
+        <v>1.36</v>
+      </c>
+      <c r="X257">
+        <v>8</v>
+      </c>
+      <c r="Y257">
+        <v>1.08</v>
+      </c>
+      <c r="Z257">
+        <v>3.87</v>
+      </c>
+      <c r="AA257">
+        <v>3.58</v>
+      </c>
+      <c r="AB257">
+        <v>2.01</v>
+      </c>
+      <c r="AC257">
+        <v>1.06</v>
+      </c>
+      <c r="AD257">
+        <v>10</v>
+      </c>
+      <c r="AE257">
+        <v>1.35</v>
+      </c>
+      <c r="AF257">
+        <v>3.25</v>
+      </c>
+      <c r="AG257">
+        <v>1.89</v>
+      </c>
+      <c r="AH257">
+        <v>1.92</v>
+      </c>
+      <c r="AI257">
+        <v>1.8</v>
+      </c>
+      <c r="AJ257">
+        <v>1.95</v>
+      </c>
+      <c r="AK257">
+        <v>1.87</v>
+      </c>
+      <c r="AL257">
+        <v>1.29</v>
+      </c>
+      <c r="AM257">
+        <v>1.23</v>
+      </c>
+      <c r="AN257">
+        <v>0.83</v>
+      </c>
+      <c r="AO257">
+        <v>1.5</v>
+      </c>
+      <c r="AP257">
+        <v>1</v>
+      </c>
+      <c r="AQ257">
+        <v>1.38</v>
+      </c>
+      <c r="AR257">
+        <v>1.24</v>
+      </c>
+      <c r="AS257">
+        <v>1.22</v>
+      </c>
+      <c r="AT257">
+        <v>2.46</v>
+      </c>
+      <c r="AU257">
+        <v>4</v>
+      </c>
+      <c r="AV257">
+        <v>4</v>
+      </c>
+      <c r="AW257">
+        <v>4</v>
+      </c>
+      <c r="AX257">
+        <v>5</v>
+      </c>
+      <c r="AY257">
+        <v>10</v>
+      </c>
+      <c r="AZ257">
+        <v>10</v>
+      </c>
+      <c r="BA257">
+        <v>4</v>
+      </c>
+      <c r="BB257">
+        <v>1</v>
+      </c>
+      <c r="BC257">
+        <v>5</v>
+      </c>
+      <c r="BD257">
+        <v>2.48</v>
+      </c>
+      <c r="BE257">
+        <v>6.5</v>
+      </c>
+      <c r="BF257">
+        <v>1.67</v>
+      </c>
+      <c r="BG257">
+        <v>1.33</v>
+      </c>
+      <c r="BH257">
+        <v>2.95</v>
+      </c>
+      <c r="BI257">
+        <v>1.57</v>
+      </c>
+      <c r="BJ257">
+        <v>2.23</v>
+      </c>
+      <c r="BK257">
+        <v>1.94</v>
+      </c>
+      <c r="BL257">
+        <v>1.76</v>
+      </c>
+      <c r="BM257">
+        <v>2.43</v>
+      </c>
+      <c r="BN257">
+        <v>1.47</v>
+      </c>
+      <c r="BO257">
+        <v>3.15</v>
+      </c>
+      <c r="BP257">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="258" spans="1:68">
+      <c r="A258" s="1">
+        <v>257</v>
+      </c>
+      <c r="B258">
+        <v>7492400</v>
+      </c>
+      <c r="C258" t="s">
+        <v>68</v>
+      </c>
+      <c r="D258" t="s">
+        <v>69</v>
+      </c>
+      <c r="E258" s="2">
+        <v>45711.58333333334</v>
+      </c>
+      <c r="F258">
+        <v>26</v>
+      </c>
+      <c r="G258" t="s">
+        <v>72</v>
+      </c>
+      <c r="H258" t="s">
+        <v>89</v>
+      </c>
+      <c r="I258">
+        <v>0</v>
+      </c>
+      <c r="J258">
+        <v>3</v>
+      </c>
+      <c r="K258">
+        <v>3</v>
+      </c>
+      <c r="L258">
+        <v>0</v>
+      </c>
+      <c r="M258">
+        <v>5</v>
+      </c>
+      <c r="N258">
+        <v>5</v>
+      </c>
+      <c r="O258" t="s">
+        <v>92</v>
+      </c>
+      <c r="P258" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q258">
+        <v>6</v>
+      </c>
+      <c r="R258">
+        <v>2.3</v>
+      </c>
+      <c r="S258">
+        <v>2.1</v>
+      </c>
+      <c r="T258">
+        <v>1.36</v>
+      </c>
+      <c r="U258">
+        <v>3</v>
+      </c>
+      <c r="V258">
+        <v>2.63</v>
+      </c>
+      <c r="W258">
+        <v>1.44</v>
+      </c>
+      <c r="X258">
+        <v>7</v>
+      </c>
+      <c r="Y258">
+        <v>1.1</v>
+      </c>
+      <c r="Z258">
+        <v>5.6</v>
+      </c>
+      <c r="AA258">
+        <v>4.3</v>
+      </c>
+      <c r="AB258">
+        <v>1.61</v>
+      </c>
+      <c r="AC258">
+        <v>1.04</v>
+      </c>
+      <c r="AD258">
+        <v>13</v>
+      </c>
+      <c r="AE258">
+        <v>1.25</v>
+      </c>
+      <c r="AF258">
+        <v>4</v>
+      </c>
+      <c r="AG258">
+        <v>1.81</v>
+      </c>
+      <c r="AH258">
+        <v>2.01</v>
+      </c>
+      <c r="AI258">
+        <v>1.91</v>
+      </c>
+      <c r="AJ258">
+        <v>1.91</v>
+      </c>
+      <c r="AK258">
+        <v>2.4</v>
+      </c>
+      <c r="AL258">
+        <v>1.22</v>
+      </c>
+      <c r="AM258">
+        <v>1.14</v>
+      </c>
+      <c r="AN258">
+        <v>0.67</v>
+      </c>
+      <c r="AO258">
+        <v>2.08</v>
+      </c>
+      <c r="AP258">
+        <v>0.62</v>
+      </c>
+      <c r="AQ258">
+        <v>2.14</v>
+      </c>
+      <c r="AR258">
+        <v>0.97</v>
+      </c>
+      <c r="AS258">
+        <v>1.6</v>
+      </c>
+      <c r="AT258">
+        <v>2.57</v>
+      </c>
+      <c r="AU258">
+        <v>3</v>
+      </c>
+      <c r="AV258">
+        <v>3</v>
+      </c>
+      <c r="AW258">
+        <v>9</v>
+      </c>
+      <c r="AX258">
+        <v>6</v>
+      </c>
+      <c r="AY258">
+        <v>13</v>
+      </c>
+      <c r="AZ258">
+        <v>10</v>
+      </c>
+      <c r="BA258">
+        <v>3</v>
+      </c>
+      <c r="BB258">
+        <v>4</v>
+      </c>
+      <c r="BC258">
+        <v>7</v>
+      </c>
+      <c r="BD258">
+        <v>3.4</v>
+      </c>
+      <c r="BE258">
+        <v>7</v>
+      </c>
+      <c r="BF258">
+        <v>1.38</v>
+      </c>
+      <c r="BG258">
+        <v>1.34</v>
+      </c>
+      <c r="BH258">
+        <v>2.9</v>
+      </c>
+      <c r="BI258">
+        <v>1.58</v>
+      </c>
+      <c r="BJ258">
+        <v>2.18</v>
+      </c>
+      <c r="BK258">
+        <v>1.96</v>
+      </c>
+      <c r="BL258">
+        <v>1.74</v>
+      </c>
+      <c r="BM258">
+        <v>2.48</v>
+      </c>
+      <c r="BN258">
+        <v>1.47</v>
+      </c>
+      <c r="BO258">
+        <v>3.3</v>
+      </c>
+      <c r="BP258">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="259" spans="1:68">
+      <c r="A259" s="1">
+        <v>258</v>
+      </c>
+      <c r="B259">
+        <v>7492398</v>
+      </c>
+      <c r="C259" t="s">
+        <v>68</v>
+      </c>
+      <c r="D259" t="s">
+        <v>69</v>
+      </c>
+      <c r="E259" s="2">
+        <v>45711.69791666666</v>
+      </c>
+      <c r="F259">
+        <v>26</v>
+      </c>
+      <c r="G259" t="s">
+        <v>76</v>
+      </c>
+      <c r="H259" t="s">
+        <v>79</v>
+      </c>
+      <c r="I259">
+        <v>0</v>
+      </c>
+      <c r="J259">
+        <v>1</v>
+      </c>
+      <c r="K259">
+        <v>1</v>
+      </c>
+      <c r="L259">
+        <v>0</v>
+      </c>
+      <c r="M259">
+        <v>1</v>
+      </c>
+      <c r="N259">
+        <v>1</v>
+      </c>
+      <c r="O259" t="s">
+        <v>92</v>
+      </c>
+      <c r="P259" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q259">
+        <v>4.75</v>
+      </c>
+      <c r="R259">
+        <v>2.2</v>
+      </c>
+      <c r="S259">
+        <v>2.5</v>
+      </c>
+      <c r="T259">
+        <v>1.4</v>
+      </c>
+      <c r="U259">
+        <v>2.75</v>
+      </c>
+      <c r="V259">
+        <v>3</v>
+      </c>
+      <c r="W259">
+        <v>1.36</v>
+      </c>
+      <c r="X259">
+        <v>8</v>
+      </c>
+      <c r="Y259">
+        <v>1.08</v>
+      </c>
+      <c r="Z259">
+        <v>4.75</v>
+      </c>
+      <c r="AA259">
+        <v>3.77</v>
+      </c>
+      <c r="AB259">
+        <v>1.79</v>
+      </c>
+      <c r="AC259">
+        <v>1.05</v>
+      </c>
+      <c r="AD259">
+        <v>11</v>
+      </c>
+      <c r="AE259">
+        <v>1.33</v>
+      </c>
+      <c r="AF259">
+        <v>3.4</v>
+      </c>
+      <c r="AG259">
+        <v>1.93</v>
+      </c>
+      <c r="AH259">
+        <v>1.83</v>
+      </c>
+      <c r="AI259">
+        <v>1.8</v>
+      </c>
+      <c r="AJ259">
+        <v>1.95</v>
+      </c>
+      <c r="AK259">
+        <v>1.95</v>
+      </c>
+      <c r="AL259">
+        <v>1.28</v>
+      </c>
+      <c r="AM259">
+        <v>1.21</v>
+      </c>
+      <c r="AN259">
+        <v>1.15</v>
+      </c>
+      <c r="AO259">
+        <v>1.75</v>
+      </c>
+      <c r="AP259">
+        <v>1.07</v>
+      </c>
+      <c r="AQ259">
+        <v>1.85</v>
+      </c>
+      <c r="AR259">
+        <v>1.48</v>
+      </c>
+      <c r="AS259">
+        <v>1.28</v>
+      </c>
+      <c r="AT259">
+        <v>2.76</v>
+      </c>
+      <c r="AU259">
+        <v>3</v>
+      </c>
+      <c r="AV259">
+        <v>8</v>
+      </c>
+      <c r="AW259">
+        <v>6</v>
+      </c>
+      <c r="AX259">
+        <v>7</v>
+      </c>
+      <c r="AY259">
+        <v>11</v>
+      </c>
+      <c r="AZ259">
+        <v>16</v>
+      </c>
+      <c r="BA259">
+        <v>3</v>
+      </c>
+      <c r="BB259">
+        <v>4</v>
+      </c>
+      <c r="BC259">
+        <v>7</v>
+      </c>
+      <c r="BD259">
+        <v>2.33</v>
+      </c>
+      <c r="BE259">
+        <v>6.75</v>
+      </c>
+      <c r="BF259">
+        <v>1.73</v>
+      </c>
+      <c r="BG259">
+        <v>1.24</v>
+      </c>
+      <c r="BH259">
+        <v>3.55</v>
+      </c>
+      <c r="BI259">
+        <v>1.44</v>
+      </c>
+      <c r="BJ259">
+        <v>2.55</v>
+      </c>
+      <c r="BK259">
+        <v>1.72</v>
+      </c>
+      <c r="BL259">
+        <v>1.98</v>
+      </c>
+      <c r="BM259">
+        <v>2.12</v>
+      </c>
+      <c r="BN259">
+        <v>1.63</v>
+      </c>
+      <c r="BO259">
+        <v>2.65</v>
+      </c>
+      <c r="BP259">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="373">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -772,6 +772,9 @@
     <t>['90+5']</t>
   </si>
   <si>
+    <t>['10', '32', '73', '88']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1491,7 +1494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP259"/>
+  <dimension ref="A1:BP260"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1747,7 +1750,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2240,7 +2243,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ4">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2365,7 +2368,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2571,7 +2574,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -3189,7 +3192,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3395,7 +3398,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -4013,7 +4016,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4219,7 +4222,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -5249,7 +5252,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5327,7 +5330,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -5661,7 +5664,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5867,7 +5870,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6279,7 +6282,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6691,7 +6694,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6897,7 +6900,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7103,7 +7106,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7184,7 +7187,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ28">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR28">
         <v>1.74</v>
@@ -7309,7 +7312,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7927,7 +7930,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8751,7 +8754,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -9163,7 +9166,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9369,7 +9372,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9575,7 +9578,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9781,7 +9784,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9987,7 +9990,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10193,7 +10196,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10811,7 +10814,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -11017,7 +11020,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11223,7 +11226,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11507,7 +11510,7 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ49">
         <v>1.23</v>
@@ -11635,7 +11638,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11841,7 +11844,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12253,7 +12256,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12459,7 +12462,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12665,7 +12668,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12871,7 +12874,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13077,7 +13080,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13361,7 +13364,7 @@
         <v>0.33</v>
       </c>
       <c r="AP58">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ58">
         <v>0.31</v>
@@ -13776,7 +13779,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ60">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR60">
         <v>1.84</v>
@@ -13901,7 +13904,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14725,7 +14728,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14931,7 +14934,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15137,7 +15140,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15343,7 +15346,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q68">
         <v>2.2</v>
@@ -15755,7 +15758,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -16373,7 +16376,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16991,7 +16994,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17197,7 +17200,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17403,7 +17406,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17609,7 +17612,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17893,7 +17896,7 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ80">
         <v>2.08</v>
@@ -18021,7 +18024,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18102,7 +18105,7 @@
         <v>1</v>
       </c>
       <c r="AQ81">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR81">
         <v>1.08</v>
@@ -18845,7 +18848,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19463,7 +19466,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19669,7 +19672,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19875,7 +19878,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20081,7 +20084,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20493,7 +20496,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20699,7 +20702,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20905,7 +20908,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -21192,7 +21195,7 @@
         <v>2</v>
       </c>
       <c r="AQ96">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR96">
         <v>1.88</v>
@@ -21317,7 +21320,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21523,7 +21526,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21729,7 +21732,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22013,7 +22016,7 @@
         <v>1.4</v>
       </c>
       <c r="AP100">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ100">
         <v>1.08</v>
@@ -22347,7 +22350,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22759,7 +22762,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22965,7 +22968,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23171,7 +23174,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23995,7 +23998,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24201,7 +24204,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24407,7 +24410,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24613,7 +24616,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24819,7 +24822,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25231,7 +25234,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25437,7 +25440,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25515,7 +25518,7 @@
         <v>1.6</v>
       </c>
       <c r="AP117">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ117">
         <v>1.38</v>
@@ -25643,7 +25646,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -26261,7 +26264,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26673,7 +26676,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26879,7 +26882,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27085,7 +27088,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27291,7 +27294,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27372,7 +27375,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ126">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR126">
         <v>1.11</v>
@@ -27909,7 +27912,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -28608,7 +28611,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ132">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR132">
         <v>1.48</v>
@@ -29145,7 +29148,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29351,7 +29354,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29763,7 +29766,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29969,7 +29972,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30047,7 +30050,7 @@
         <v>1.86</v>
       </c>
       <c r="AP139">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ139">
         <v>2.14</v>
@@ -30793,7 +30796,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30999,7 +31002,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31077,7 +31080,7 @@
         <v>0.57</v>
       </c>
       <c r="AP144">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ144">
         <v>0.85</v>
@@ -31411,7 +31414,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31617,7 +31620,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -32029,7 +32032,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32441,7 +32444,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32647,7 +32650,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32853,7 +32856,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -33140,7 +33143,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ154">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR154">
         <v>1.38</v>
@@ -33265,7 +33268,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -34089,7 +34092,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34501,7 +34504,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34707,7 +34710,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34913,7 +34916,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35197,7 +35200,7 @@
         <v>1</v>
       </c>
       <c r="AP164">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ164">
         <v>0.67</v>
@@ -35325,7 +35328,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35531,7 +35534,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35737,7 +35740,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35943,7 +35946,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36436,7 +36439,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ170">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR170">
         <v>1.34</v>
@@ -36561,7 +36564,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36767,7 +36770,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36973,7 +36976,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37179,7 +37182,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37591,7 +37594,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -38209,7 +38212,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38415,7 +38418,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38621,7 +38624,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39033,7 +39036,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39729,7 +39732,7 @@
         <v>1.67</v>
       </c>
       <c r="AP186">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ186">
         <v>1.69</v>
@@ -39857,7 +39860,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40269,7 +40272,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40681,7 +40684,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41299,7 +41302,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41917,7 +41920,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42329,7 +42332,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42535,7 +42538,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42613,7 +42616,7 @@
         <v>1.56</v>
       </c>
       <c r="AP200">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ200">
         <v>1.15</v>
@@ -42741,7 +42744,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -42822,7 +42825,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ201">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR201">
         <v>1.71</v>
@@ -43153,7 +43156,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43565,7 +43568,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43977,7 +43980,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44183,7 +44186,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44801,7 +44804,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45419,7 +45422,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45625,7 +45628,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45831,7 +45834,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -46037,7 +46040,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46243,7 +46246,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46530,7 +46533,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ219">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR219">
         <v>1.25</v>
@@ -46655,7 +46658,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46861,7 +46864,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47273,7 +47276,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47685,7 +47688,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47891,7 +47894,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -48303,7 +48306,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48381,7 +48384,7 @@
         <v>2.36</v>
       </c>
       <c r="AP228">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ228">
         <v>2</v>
@@ -48509,7 +48512,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48921,7 +48924,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49127,7 +49130,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49333,7 +49336,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49539,7 +49542,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -50157,7 +50160,7 @@
         <v>241</v>
       </c>
       <c r="P237" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q237">
         <v>1.91</v>
@@ -50238,7 +50241,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ237">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR237">
         <v>1.52</v>
@@ -50569,7 +50572,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -50981,7 +50984,7 @@
         <v>244</v>
       </c>
       <c r="P241" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q241">
         <v>2.5</v>
@@ -51393,7 +51396,7 @@
         <v>245</v>
       </c>
       <c r="P243" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q243">
         <v>3.4</v>
@@ -51805,7 +51808,7 @@
         <v>92</v>
       </c>
       <c r="P245" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q245">
         <v>2.6</v>
@@ -52423,7 +52426,7 @@
         <v>92</v>
       </c>
       <c r="P248" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q248">
         <v>4</v>
@@ -53041,7 +53044,7 @@
         <v>92</v>
       </c>
       <c r="P251" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q251">
         <v>3.6</v>
@@ -54071,7 +54074,7 @@
         <v>250</v>
       </c>
       <c r="P256" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q256">
         <v>4</v>
@@ -54483,7 +54486,7 @@
         <v>92</v>
       </c>
       <c r="P258" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q258">
         <v>6</v>
@@ -54689,7 +54692,7 @@
         <v>92</v>
       </c>
       <c r="P259" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q259">
         <v>4.75</v>
@@ -54846,6 +54849,212 @@
       </c>
       <c r="BP259">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="260" spans="1:68">
+      <c r="A260" s="1">
+        <v>259</v>
+      </c>
+      <c r="B260">
+        <v>7492405</v>
+      </c>
+      <c r="C260" t="s">
+        <v>68</v>
+      </c>
+      <c r="D260" t="s">
+        <v>69</v>
+      </c>
+      <c r="E260" s="2">
+        <v>45712.69791666666</v>
+      </c>
+      <c r="F260">
+        <v>26</v>
+      </c>
+      <c r="G260" t="s">
+        <v>86</v>
+      </c>
+      <c r="H260" t="s">
+        <v>81</v>
+      </c>
+      <c r="I260">
+        <v>2</v>
+      </c>
+      <c r="J260">
+        <v>0</v>
+      </c>
+      <c r="K260">
+        <v>2</v>
+      </c>
+      <c r="L260">
+        <v>4</v>
+      </c>
+      <c r="M260">
+        <v>0</v>
+      </c>
+      <c r="N260">
+        <v>4</v>
+      </c>
+      <c r="O260" t="s">
+        <v>252</v>
+      </c>
+      <c r="P260" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q260">
+        <v>1.8</v>
+      </c>
+      <c r="R260">
+        <v>2.5</v>
+      </c>
+      <c r="S260">
+        <v>8.5</v>
+      </c>
+      <c r="T260">
+        <v>1.33</v>
+      </c>
+      <c r="U260">
+        <v>3.25</v>
+      </c>
+      <c r="V260">
+        <v>2.5</v>
+      </c>
+      <c r="W260">
+        <v>1.5</v>
+      </c>
+      <c r="X260">
+        <v>6.5</v>
+      </c>
+      <c r="Y260">
+        <v>1.11</v>
+      </c>
+      <c r="Z260">
+        <v>1.33</v>
+      </c>
+      <c r="AA260">
+        <v>5.5</v>
+      </c>
+      <c r="AB260">
+        <v>10</v>
+      </c>
+      <c r="AC260">
+        <v>1.01</v>
+      </c>
+      <c r="AD260">
+        <v>15.5</v>
+      </c>
+      <c r="AE260">
+        <v>1.19</v>
+      </c>
+      <c r="AF260">
+        <v>4.05</v>
+      </c>
+      <c r="AG260">
+        <v>1.8</v>
+      </c>
+      <c r="AH260">
+        <v>1.95</v>
+      </c>
+      <c r="AI260">
+        <v>2.05</v>
+      </c>
+      <c r="AJ260">
+        <v>1.7</v>
+      </c>
+      <c r="AK260">
+        <v>1.06</v>
+      </c>
+      <c r="AL260">
+        <v>1.16</v>
+      </c>
+      <c r="AM260">
+        <v>3.3</v>
+      </c>
+      <c r="AN260">
+        <v>1.83</v>
+      </c>
+      <c r="AO260">
+        <v>0.58</v>
+      </c>
+      <c r="AP260">
+        <v>1.92</v>
+      </c>
+      <c r="AQ260">
+        <v>0.54</v>
+      </c>
+      <c r="AR260">
+        <v>1.56</v>
+      </c>
+      <c r="AS260">
+        <v>0.85</v>
+      </c>
+      <c r="AT260">
+        <v>2.41</v>
+      </c>
+      <c r="AU260">
+        <v>7</v>
+      </c>
+      <c r="AV260">
+        <v>3</v>
+      </c>
+      <c r="AW260">
+        <v>17</v>
+      </c>
+      <c r="AX260">
+        <v>3</v>
+      </c>
+      <c r="AY260">
+        <v>33</v>
+      </c>
+      <c r="AZ260">
+        <v>7</v>
+      </c>
+      <c r="BA260">
+        <v>6</v>
+      </c>
+      <c r="BB260">
+        <v>3</v>
+      </c>
+      <c r="BC260">
+        <v>9</v>
+      </c>
+      <c r="BD260">
+        <v>1.23</v>
+      </c>
+      <c r="BE260">
+        <v>8</v>
+      </c>
+      <c r="BF260">
+        <v>4.6</v>
+      </c>
+      <c r="BG260">
+        <v>1.36</v>
+      </c>
+      <c r="BH260">
+        <v>2.8</v>
+      </c>
+      <c r="BI260">
+        <v>1.63</v>
+      </c>
+      <c r="BJ260">
+        <v>2.12</v>
+      </c>
+      <c r="BK260">
+        <v>2</v>
+      </c>
+      <c r="BL260">
+        <v>1.71</v>
+      </c>
+      <c r="BM260">
+        <v>2.55</v>
+      </c>
+      <c r="BN260">
+        <v>1.44</v>
+      </c>
+      <c r="BO260">
+        <v>3.3</v>
+      </c>
+      <c r="BP260">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="374">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -775,6 +775,9 @@
     <t>['10', '32', '73', '88']</t>
   </si>
   <si>
+    <t>['48', '82']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1494,7 +1497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP260"/>
+  <dimension ref="A1:BP261"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1750,7 +1753,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2368,7 +2371,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2574,7 +2577,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2652,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
         <v>1.23</v>
@@ -3192,7 +3195,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3398,7 +3401,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -4016,7 +4019,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4097,7 +4100,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ13">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR13">
         <v>1.45</v>
@@ -4222,7 +4225,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -5252,7 +5255,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5664,7 +5667,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5870,7 +5873,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6282,7 +6285,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6360,7 +6363,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ24">
         <v>1</v>
@@ -6694,7 +6697,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6775,7 +6778,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ26">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR26">
         <v>1.67</v>
@@ -6900,7 +6903,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7106,7 +7109,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7312,7 +7315,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7930,7 +7933,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8754,7 +8757,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -9166,7 +9169,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9372,7 +9375,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9578,7 +9581,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9784,7 +9787,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9990,7 +9993,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10196,7 +10199,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10814,7 +10817,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -11020,7 +11023,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11226,7 +11229,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11638,7 +11641,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11719,7 +11722,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ50">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR50">
         <v>1.2</v>
@@ -11844,7 +11847,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12256,7 +12259,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12462,7 +12465,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12668,7 +12671,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12746,7 +12749,7 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ55">
         <v>2.14</v>
@@ -12874,7 +12877,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13080,7 +13083,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13904,7 +13907,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14728,7 +14731,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14934,7 +14937,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15140,7 +15143,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15346,7 +15349,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q68">
         <v>2.2</v>
@@ -15630,7 +15633,7 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ69">
         <v>0.67</v>
@@ -15758,7 +15761,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -16045,7 +16048,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ71">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR71">
         <v>1.68</v>
@@ -16376,7 +16379,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16994,7 +16997,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17200,7 +17203,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17406,7 +17409,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17612,7 +17615,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -18024,7 +18027,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18848,7 +18851,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19466,7 +19469,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19672,7 +19675,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19878,7 +19881,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20084,7 +20087,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20496,7 +20499,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20702,7 +20705,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20908,7 +20911,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -21320,7 +21323,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21526,7 +21529,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21732,7 +21735,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22222,7 +22225,7 @@
         <v>0.2</v>
       </c>
       <c r="AP101">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ101">
         <v>0.85</v>
@@ -22350,7 +22353,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22637,7 +22640,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ103">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR103">
         <v>0.9399999999999999</v>
@@ -22762,7 +22765,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22968,7 +22971,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23174,7 +23177,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23998,7 +24001,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24204,7 +24207,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24410,7 +24413,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24616,7 +24619,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24822,7 +24825,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -24903,7 +24906,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ114">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR114">
         <v>1.3</v>
@@ -25234,7 +25237,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25440,7 +25443,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25646,7 +25649,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -26264,7 +26267,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26676,7 +26679,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26882,7 +26885,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27088,7 +27091,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27294,7 +27297,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27912,7 +27915,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -29020,7 +29023,7 @@
         <v>0.29</v>
       </c>
       <c r="AP134">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ134">
         <v>0.31</v>
@@ -29148,7 +29151,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29354,7 +29357,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29766,7 +29769,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29972,7 +29975,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30465,7 +30468,7 @@
         <v>2</v>
       </c>
       <c r="AQ141">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR141">
         <v>1.73</v>
@@ -30796,7 +30799,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -31002,7 +31005,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31414,7 +31417,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31620,7 +31623,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -32032,7 +32035,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32444,7 +32447,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32650,7 +32653,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32856,7 +32859,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -33268,7 +33271,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -33552,7 +33555,7 @@
         <v>2</v>
       </c>
       <c r="AP156">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ156">
         <v>1.38</v>
@@ -34092,7 +34095,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34379,7 +34382,7 @@
         <v>1</v>
       </c>
       <c r="AQ160">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR160">
         <v>1.12</v>
@@ -34504,7 +34507,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34710,7 +34713,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34916,7 +34919,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35328,7 +35331,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35534,7 +35537,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35740,7 +35743,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35946,7 +35949,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36564,7 +36567,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36770,7 +36773,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36976,7 +36979,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37182,7 +37185,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37594,7 +37597,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -38212,7 +38215,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38290,7 +38293,7 @@
         <v>0.75</v>
       </c>
       <c r="AP179">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ179">
         <v>1</v>
@@ -38418,7 +38421,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38624,7 +38627,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39036,7 +39039,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39860,7 +39863,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40272,7 +40275,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40684,7 +40687,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41302,7 +41305,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41380,7 +41383,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP194">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ194">
         <v>1.15</v>
@@ -41920,7 +41923,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42001,7 +42004,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ197">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR197">
         <v>1.54</v>
@@ -42332,7 +42335,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42538,7 +42541,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42744,7 +42747,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -42822,7 +42825,7 @@
         <v>0.78</v>
       </c>
       <c r="AP201">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ201">
         <v>0.54</v>
@@ -43031,7 +43034,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ202">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR202">
         <v>1.44</v>
@@ -43156,7 +43159,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43568,7 +43571,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43980,7 +43983,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44186,7 +44189,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44804,7 +44807,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45422,7 +45425,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45628,7 +45631,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45834,7 +45837,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -46040,7 +46043,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46246,7 +46249,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46658,7 +46661,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46864,7 +46867,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47276,7 +47279,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47560,7 +47563,7 @@
         <v>0.64</v>
       </c>
       <c r="AP224">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ224">
         <v>0.77</v>
@@ -47688,7 +47691,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47894,7 +47897,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -48306,7 +48309,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48512,7 +48515,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48924,7 +48927,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49130,7 +49133,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49336,7 +49339,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49417,7 +49420,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ233">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR233">
         <v>0.99</v>
@@ -49542,7 +49545,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -50160,7 +50163,7 @@
         <v>241</v>
       </c>
       <c r="P237" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q237">
         <v>1.91</v>
@@ -50572,7 +50575,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -50984,7 +50987,7 @@
         <v>244</v>
       </c>
       <c r="P241" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q241">
         <v>2.5</v>
@@ -51062,7 +51065,7 @@
         <v>1.17</v>
       </c>
       <c r="AP241">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ241">
         <v>1.08</v>
@@ -51396,7 +51399,7 @@
         <v>245</v>
       </c>
       <c r="P243" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q243">
         <v>3.4</v>
@@ -51808,7 +51811,7 @@
         <v>92</v>
       </c>
       <c r="P245" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q245">
         <v>2.6</v>
@@ -52426,7 +52429,7 @@
         <v>92</v>
       </c>
       <c r="P248" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q248">
         <v>4</v>
@@ -53044,7 +53047,7 @@
         <v>92</v>
       </c>
       <c r="P251" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q251">
         <v>3.6</v>
@@ -53743,7 +53746,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ254">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR254">
         <v>1.15</v>
@@ -54074,7 +54077,7 @@
         <v>250</v>
       </c>
       <c r="P256" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q256">
         <v>4</v>
@@ -54486,7 +54489,7 @@
         <v>92</v>
       </c>
       <c r="P258" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q258">
         <v>6</v>
@@ -54692,7 +54695,7 @@
         <v>92</v>
       </c>
       <c r="P259" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q259">
         <v>4.75</v>
@@ -55055,6 +55058,212 @@
       </c>
       <c r="BP260">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="261" spans="1:68">
+      <c r="A261" s="1">
+        <v>260</v>
+      </c>
+      <c r="B261">
+        <v>7492229</v>
+      </c>
+      <c r="C261" t="s">
+        <v>68</v>
+      </c>
+      <c r="D261" t="s">
+        <v>69</v>
+      </c>
+      <c r="E261" s="2">
+        <v>45715.69791666666</v>
+      </c>
+      <c r="F261">
+        <v>9</v>
+      </c>
+      <c r="G261" t="s">
+        <v>74</v>
+      </c>
+      <c r="H261" t="s">
+        <v>73</v>
+      </c>
+      <c r="I261">
+        <v>0</v>
+      </c>
+      <c r="J261">
+        <v>1</v>
+      </c>
+      <c r="K261">
+        <v>1</v>
+      </c>
+      <c r="L261">
+        <v>2</v>
+      </c>
+      <c r="M261">
+        <v>1</v>
+      </c>
+      <c r="N261">
+        <v>3</v>
+      </c>
+      <c r="O261" t="s">
+        <v>253</v>
+      </c>
+      <c r="P261" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q261">
+        <v>4</v>
+      </c>
+      <c r="R261">
+        <v>2.25</v>
+      </c>
+      <c r="S261">
+        <v>2.63</v>
+      </c>
+      <c r="T261">
+        <v>1.36</v>
+      </c>
+      <c r="U261">
+        <v>3</v>
+      </c>
+      <c r="V261">
+        <v>2.63</v>
+      </c>
+      <c r="W261">
+        <v>1.44</v>
+      </c>
+      <c r="X261">
+        <v>7</v>
+      </c>
+      <c r="Y261">
+        <v>1.1</v>
+      </c>
+      <c r="Z261">
+        <v>2.62</v>
+      </c>
+      <c r="AA261">
+        <v>3.3</v>
+      </c>
+      <c r="AB261">
+        <v>2.86</v>
+      </c>
+      <c r="AC261">
+        <v>1.05</v>
+      </c>
+      <c r="AD261">
+        <v>9.5</v>
+      </c>
+      <c r="AE261">
+        <v>1.25</v>
+      </c>
+      <c r="AF261">
+        <v>3.8</v>
+      </c>
+      <c r="AG261">
+        <v>1.98</v>
+      </c>
+      <c r="AH261">
+        <v>1.83</v>
+      </c>
+      <c r="AI261">
+        <v>1.67</v>
+      </c>
+      <c r="AJ261">
+        <v>2.1</v>
+      </c>
+      <c r="AK261">
+        <v>1.75</v>
+      </c>
+      <c r="AL261">
+        <v>1.25</v>
+      </c>
+      <c r="AM261">
+        <v>1.28</v>
+      </c>
+      <c r="AN261">
+        <v>1.92</v>
+      </c>
+      <c r="AO261">
+        <v>1.42</v>
+      </c>
+      <c r="AP261">
+        <v>2</v>
+      </c>
+      <c r="AQ261">
+        <v>1.31</v>
+      </c>
+      <c r="AR261">
+        <v>1.8</v>
+      </c>
+      <c r="AS261">
+        <v>1.6</v>
+      </c>
+      <c r="AT261">
+        <v>3.4</v>
+      </c>
+      <c r="AU261">
+        <v>5</v>
+      </c>
+      <c r="AV261">
+        <v>5</v>
+      </c>
+      <c r="AW261">
+        <v>11</v>
+      </c>
+      <c r="AX261">
+        <v>4</v>
+      </c>
+      <c r="AY261">
+        <v>18</v>
+      </c>
+      <c r="AZ261">
+        <v>11</v>
+      </c>
+      <c r="BA261">
+        <v>4</v>
+      </c>
+      <c r="BB261">
+        <v>5</v>
+      </c>
+      <c r="BC261">
+        <v>9</v>
+      </c>
+      <c r="BD261">
+        <v>2.38</v>
+      </c>
+      <c r="BE261">
+        <v>6.4</v>
+      </c>
+      <c r="BF261">
+        <v>1.72</v>
+      </c>
+      <c r="BG261">
+        <v>1.3</v>
+      </c>
+      <c r="BH261">
+        <v>3.05</v>
+      </c>
+      <c r="BI261">
+        <v>1.54</v>
+      </c>
+      <c r="BJ261">
+        <v>2.3</v>
+      </c>
+      <c r="BK261">
+        <v>1.88</v>
+      </c>
+      <c r="BL261">
+        <v>1.8</v>
+      </c>
+      <c r="BM261">
+        <v>2.4</v>
+      </c>
+      <c r="BN261">
+        <v>1.49</v>
+      </c>
+      <c r="BO261">
+        <v>3.15</v>
+      </c>
+      <c r="BP261">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="374">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -778,6 +778,9 @@
     <t>['48', '82']</t>
   </si>
   <si>
+    <t>['9']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -881,9 +884,6 @@
   </si>
   <si>
     <t>['36', '87']</t>
-  </si>
-  <si>
-    <t>['9']</t>
   </si>
   <si>
     <t>['61']</t>
@@ -1497,7 +1497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP261"/>
+  <dimension ref="A1:BP262"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1753,7 +1753,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2371,7 +2371,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2577,7 +2577,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -3195,7 +3195,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3401,7 +3401,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -4019,7 +4019,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4225,7 +4225,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4512,7 +4512,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ15">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4715,7 +4715,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ16">
         <v>0.31</v>
@@ -5255,7 +5255,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5667,7 +5667,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5873,7 +5873,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6285,7 +6285,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6697,7 +6697,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6903,7 +6903,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7109,7 +7109,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7187,7 +7187,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ28">
         <v>0.54</v>
@@ -7315,7 +7315,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7933,7 +7933,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8757,7 +8757,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -9044,7 +9044,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ37">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR37">
         <v>1.46</v>
@@ -9169,7 +9169,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9375,7 +9375,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9581,7 +9581,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9787,7 +9787,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9993,7 +9993,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10199,7 +10199,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10817,7 +10817,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -11023,7 +11023,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11101,7 +11101,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ47">
         <v>1.69</v>
@@ -11229,7 +11229,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11641,7 +11641,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11847,7 +11847,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12134,7 +12134,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ52">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR52">
         <v>1.92</v>
@@ -12259,7 +12259,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12465,7 +12465,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12671,7 +12671,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12877,7 +12877,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13083,7 +13083,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13907,7 +13907,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14606,7 +14606,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ64">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR64">
         <v>1.02</v>
@@ -14731,7 +14731,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14937,7 +14937,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15143,7 +15143,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15349,7 +15349,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>289</v>
+        <v>254</v>
       </c>
       <c r="Q68">
         <v>2.2</v>
@@ -16045,7 +16045,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ71">
         <v>1.31</v>
@@ -18726,7 +18726,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ84">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR84">
         <v>1.49</v>
@@ -19959,7 +19959,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ90">
         <v>1.15</v>
@@ -22228,7 +22228,7 @@
         <v>2</v>
       </c>
       <c r="AQ101">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR101">
         <v>1.42</v>
@@ -22971,7 +22971,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -24001,7 +24001,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -25727,7 +25727,7 @@
         <v>0.6</v>
       </c>
       <c r="AP118">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ118">
         <v>1</v>
@@ -28202,7 +28202,7 @@
         <v>1</v>
       </c>
       <c r="AQ130">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR130">
         <v>1.48</v>
@@ -29769,7 +29769,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -31086,7 +31086,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ144">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR144">
         <v>1.48</v>
@@ -31289,7 +31289,7 @@
         <v>0.83</v>
       </c>
       <c r="AP145">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ145">
         <v>0.83</v>
@@ -32447,7 +32447,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -36027,7 +36027,7 @@
         <v>1</v>
       </c>
       <c r="AP168">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ168">
         <v>1.23</v>
@@ -36979,7 +36979,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -38090,7 +38090,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ178">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR178">
         <v>1.5</v>
@@ -38705,7 +38705,7 @@
         <v>2.22</v>
       </c>
       <c r="AP181">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ181">
         <v>2</v>
@@ -40356,7 +40356,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ189">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR189">
         <v>0.97</v>
@@ -43443,7 +43443,7 @@
         <v>1.2</v>
       </c>
       <c r="AP204">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ204">
         <v>1.08</v>
@@ -43652,7 +43652,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ205">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR205">
         <v>1.37</v>
@@ -45425,7 +45425,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -46742,7 +46742,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ220">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR220">
         <v>1.37</v>
@@ -47975,7 +47975,7 @@
         <v>1.4</v>
       </c>
       <c r="AP226">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ226">
         <v>1.15</v>
@@ -48799,7 +48799,7 @@
         <v>2.45</v>
       </c>
       <c r="AP230">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ230">
         <v>2.08</v>
@@ -49545,7 +49545,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -50163,7 +50163,7 @@
         <v>241</v>
       </c>
       <c r="P237" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q237">
         <v>1.91</v>
@@ -51889,7 +51889,7 @@
         <v>0.58</v>
       </c>
       <c r="AP245">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ245">
         <v>0.77</v>
@@ -52098,7 +52098,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ246">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR246">
         <v>1.18</v>
@@ -55264,6 +55264,212 @@
       </c>
       <c r="BP261">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="262" spans="1:68">
+      <c r="A262" s="1">
+        <v>261</v>
+      </c>
+      <c r="B262">
+        <v>7492410</v>
+      </c>
+      <c r="C262" t="s">
+        <v>68</v>
+      </c>
+      <c r="D262" t="s">
+        <v>69</v>
+      </c>
+      <c r="E262" s="2">
+        <v>45716.69791666666</v>
+      </c>
+      <c r="F262">
+        <v>27</v>
+      </c>
+      <c r="G262" t="s">
+        <v>83</v>
+      </c>
+      <c r="H262" t="s">
+        <v>78</v>
+      </c>
+      <c r="I262">
+        <v>1</v>
+      </c>
+      <c r="J262">
+        <v>0</v>
+      </c>
+      <c r="K262">
+        <v>1</v>
+      </c>
+      <c r="L262">
+        <v>1</v>
+      </c>
+      <c r="M262">
+        <v>0</v>
+      </c>
+      <c r="N262">
+        <v>1</v>
+      </c>
+      <c r="O262" t="s">
+        <v>254</v>
+      </c>
+      <c r="P262" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q262">
+        <v>2.38</v>
+      </c>
+      <c r="R262">
+        <v>2.2</v>
+      </c>
+      <c r="S262">
+        <v>5.5</v>
+      </c>
+      <c r="T262">
+        <v>1.44</v>
+      </c>
+      <c r="U262">
+        <v>2.63</v>
+      </c>
+      <c r="V262">
+        <v>3</v>
+      </c>
+      <c r="W262">
+        <v>1.36</v>
+      </c>
+      <c r="X262">
+        <v>9</v>
+      </c>
+      <c r="Y262">
+        <v>1.07</v>
+      </c>
+      <c r="Z262">
+        <v>1.75</v>
+      </c>
+      <c r="AA262">
+        <v>3.5</v>
+      </c>
+      <c r="AB262">
+        <v>4.6</v>
+      </c>
+      <c r="AC262">
+        <v>1.06</v>
+      </c>
+      <c r="AD262">
+        <v>10</v>
+      </c>
+      <c r="AE262">
+        <v>1.35</v>
+      </c>
+      <c r="AF262">
+        <v>3.25</v>
+      </c>
+      <c r="AG262">
+        <v>1.8</v>
+      </c>
+      <c r="AH262">
+        <v>1.95</v>
+      </c>
+      <c r="AI262">
+        <v>1.95</v>
+      </c>
+      <c r="AJ262">
+        <v>1.8</v>
+      </c>
+      <c r="AK262">
+        <v>1.15</v>
+      </c>
+      <c r="AL262">
+        <v>1.26</v>
+      </c>
+      <c r="AM262">
+        <v>2.2</v>
+      </c>
+      <c r="AN262">
+        <v>1.85</v>
+      </c>
+      <c r="AO262">
+        <v>0.85</v>
+      </c>
+      <c r="AP262">
+        <v>1.93</v>
+      </c>
+      <c r="AQ262">
+        <v>0.79</v>
+      </c>
+      <c r="AR262">
+        <v>1.51</v>
+      </c>
+      <c r="AS262">
+        <v>1.18</v>
+      </c>
+      <c r="AT262">
+        <v>2.69</v>
+      </c>
+      <c r="AU262">
+        <v>4</v>
+      </c>
+      <c r="AV262">
+        <v>4</v>
+      </c>
+      <c r="AW262">
+        <v>7</v>
+      </c>
+      <c r="AX262">
+        <v>5</v>
+      </c>
+      <c r="AY262">
+        <v>11</v>
+      </c>
+      <c r="AZ262">
+        <v>9</v>
+      </c>
+      <c r="BA262">
+        <v>5</v>
+      </c>
+      <c r="BB262">
+        <v>2</v>
+      </c>
+      <c r="BC262">
+        <v>7</v>
+      </c>
+      <c r="BD262">
+        <v>1.36</v>
+      </c>
+      <c r="BE262">
+        <v>7</v>
+      </c>
+      <c r="BF262">
+        <v>3.55</v>
+      </c>
+      <c r="BG262">
+        <v>1.35</v>
+      </c>
+      <c r="BH262">
+        <v>2.9</v>
+      </c>
+      <c r="BI262">
+        <v>1.61</v>
+      </c>
+      <c r="BJ262">
+        <v>2.15</v>
+      </c>
+      <c r="BK262">
+        <v>1.98</v>
+      </c>
+      <c r="BL262">
+        <v>1.72</v>
+      </c>
+      <c r="BM262">
+        <v>2.55</v>
+      </c>
+      <c r="BN262">
+        <v>1.43</v>
+      </c>
+      <c r="BO262">
+        <v>3.3</v>
+      </c>
+      <c r="BP262">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="375">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -781,6 +781,9 @@
     <t>['9']</t>
   </si>
   <si>
+    <t>['87']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1497,7 +1500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP262"/>
+  <dimension ref="A1:BP265"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1753,7 +1756,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1834,7 +1837,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ2">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2371,7 +2374,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2577,7 +2580,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -3195,7 +3198,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3276,7 +3279,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ9">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3401,7 +3404,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3891,7 +3894,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ12">
         <v>1.69</v>
@@ -4019,7 +4022,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4225,7 +4228,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4718,7 +4721,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ16">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5127,7 +5130,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ18">
         <v>1.38</v>
@@ -5255,7 +5258,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5667,7 +5670,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5873,7 +5876,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6285,7 +6288,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6697,7 +6700,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6903,7 +6906,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -6981,10 +6984,10 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ27">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR27">
         <v>1.28</v>
@@ -7109,7 +7112,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7315,7 +7318,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7805,7 +7808,7 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ31">
         <v>0.77</v>
@@ -7933,7 +7936,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8426,7 +8429,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ34">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="AR34">
         <v>2.22</v>
@@ -8757,7 +8760,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -8835,7 +8838,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ36">
         <v>1.38</v>
@@ -9169,7 +9172,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9375,7 +9378,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9456,7 +9459,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ39">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR39">
         <v>1.18</v>
@@ -9581,7 +9584,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9787,7 +9790,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9993,7 +9996,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10199,7 +10202,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10817,7 +10820,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10898,7 +10901,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ46">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR46">
         <v>1.54</v>
@@ -11023,7 +11026,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11229,7 +11232,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11641,7 +11644,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11847,7 +11850,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -11925,7 +11928,7 @@
         <v>0.33</v>
       </c>
       <c r="AP51">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ51">
         <v>0.77</v>
@@ -12259,7 +12262,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12337,10 +12340,10 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ53">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR53">
         <v>1.05</v>
@@ -12465,7 +12468,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12671,7 +12674,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12877,7 +12880,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13083,7 +13086,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13370,7 +13373,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ58">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="AR58">
         <v>2.07</v>
@@ -13779,7 +13782,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ60">
         <v>0.54</v>
@@ -13907,7 +13910,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14191,7 +14194,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ62">
         <v>0.77</v>
@@ -14400,7 +14403,7 @@
         <v>1</v>
       </c>
       <c r="AQ63">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="AR63">
         <v>0.9</v>
@@ -14603,7 +14606,7 @@
         <v>0.33</v>
       </c>
       <c r="AP64">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ64">
         <v>0.79</v>
@@ -14731,7 +14734,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14809,7 +14812,7 @@
         <v>1.5</v>
       </c>
       <c r="AP65">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ65">
         <v>1.15</v>
@@ -14937,7 +14940,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15143,7 +15146,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15636,7 +15639,7 @@
         <v>2</v>
       </c>
       <c r="AQ69">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR69">
         <v>1.35</v>
@@ -15761,7 +15764,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -16254,7 +16257,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ72">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR72">
         <v>1.87</v>
@@ -16379,7 +16382,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16997,7 +17000,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17203,7 +17206,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17409,7 +17412,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17615,7 +17618,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17902,7 +17905,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ80">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR80">
         <v>2.02</v>
@@ -18027,7 +18030,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18311,7 +18314,7 @@
         <v>1.33</v>
       </c>
       <c r="AP82">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ82">
         <v>0.83</v>
@@ -18723,7 +18726,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ84">
         <v>0.79</v>
@@ -18851,7 +18854,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -18929,7 +18932,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ85">
         <v>1</v>
@@ -19469,7 +19472,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19550,7 +19553,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ88">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="AR88">
         <v>0.85</v>
@@ -19675,7 +19678,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19881,7 +19884,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20087,7 +20090,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20499,7 +20502,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20705,7 +20708,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20911,7 +20914,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -20992,7 +20995,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ95">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR95">
         <v>0.91</v>
@@ -21195,7 +21198,7 @@
         <v>1.25</v>
       </c>
       <c r="AP96">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ96">
         <v>0.54</v>
@@ -21323,7 +21326,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21404,7 +21407,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ97">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR97">
         <v>1.44</v>
@@ -21529,7 +21532,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21735,7 +21738,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22353,7 +22356,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22431,7 +22434,7 @@
         <v>2</v>
       </c>
       <c r="AP102">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ102">
         <v>1.85</v>
@@ -22765,7 +22768,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22843,7 +22846,7 @@
         <v>1.4</v>
       </c>
       <c r="AP104">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ104">
         <v>2.14</v>
@@ -22971,7 +22974,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23177,7 +23180,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23464,7 +23467,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ107">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="AR107">
         <v>1.54</v>
@@ -24001,7 +24004,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24207,7 +24210,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24413,7 +24416,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24619,7 +24622,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24700,7 +24703,7 @@
         <v>1</v>
       </c>
       <c r="AQ113">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR113">
         <v>1.44</v>
@@ -24825,7 +24828,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25237,7 +25240,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25315,7 +25318,7 @@
         <v>0.8</v>
       </c>
       <c r="AP116">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ116">
         <v>1.23</v>
@@ -25443,7 +25446,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25649,7 +25652,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -26267,7 +26270,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26348,7 +26351,7 @@
         <v>1</v>
       </c>
       <c r="AQ121">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR121">
         <v>1.14</v>
@@ -26679,7 +26682,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26885,7 +26888,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27091,7 +27094,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27297,7 +27300,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27581,7 +27584,7 @@
         <v>0.67</v>
       </c>
       <c r="AP127">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ127">
         <v>1.15</v>
@@ -27915,7 +27918,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -29026,7 +29029,7 @@
         <v>2</v>
       </c>
       <c r="AQ134">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="AR134">
         <v>1.52</v>
@@ -29151,7 +29154,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29229,7 +29232,7 @@
         <v>1.2</v>
       </c>
       <c r="AP135">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ135">
         <v>1.15</v>
@@ -29357,7 +29360,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29769,7 +29772,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29975,7 +29978,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30262,7 +30265,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ140">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR140">
         <v>1.57</v>
@@ -30465,7 +30468,7 @@
         <v>1.33</v>
       </c>
       <c r="AP141">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ141">
         <v>1.31</v>
@@ -30799,7 +30802,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -31005,7 +31008,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31417,7 +31420,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31623,7 +31626,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31907,7 +31910,7 @@
         <v>1.29</v>
       </c>
       <c r="AP148">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ148">
         <v>1.69</v>
@@ -32035,7 +32038,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32447,7 +32450,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32653,7 +32656,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32731,7 +32734,7 @@
         <v>2</v>
       </c>
       <c r="AP152">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ152">
         <v>2</v>
@@ -32859,7 +32862,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -32940,7 +32943,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ153">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="AR153">
         <v>1.41</v>
@@ -33271,7 +33274,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -34095,7 +34098,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34176,7 +34179,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ159">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR159">
         <v>1.56</v>
@@ -34507,7 +34510,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34713,7 +34716,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34919,7 +34922,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35206,7 +35209,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ164">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR164">
         <v>1.54</v>
@@ -35331,7 +35334,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35537,7 +35540,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35615,7 +35618,7 @@
         <v>1.5</v>
       </c>
       <c r="AP166">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ166">
         <v>1</v>
@@ -35743,7 +35746,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35949,7 +35952,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36567,7 +36570,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36773,7 +36776,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36854,7 +36857,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ172">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR172">
         <v>1.46</v>
@@ -36979,7 +36982,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37185,7 +37188,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37263,7 +37266,7 @@
         <v>1.22</v>
       </c>
       <c r="AP174">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ174">
         <v>1.08</v>
@@ -37469,10 +37472,10 @@
         <v>0.33</v>
       </c>
       <c r="AP175">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ175">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="AR175">
         <v>1.48</v>
@@ -37597,7 +37600,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -38215,7 +38218,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38421,7 +38424,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38627,7 +38630,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39039,7 +39042,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39532,7 +39535,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ185">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR185">
         <v>1</v>
@@ -39863,7 +39866,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40147,7 +40150,7 @@
         <v>2</v>
       </c>
       <c r="AP188">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ188">
         <v>2.14</v>
@@ -40275,7 +40278,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40687,7 +40690,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -40974,7 +40977,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ192">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR192">
         <v>1.24</v>
@@ -41180,7 +41183,7 @@
         <v>1</v>
       </c>
       <c r="AQ193">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR193">
         <v>1.41</v>
@@ -41305,7 +41308,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41589,7 +41592,7 @@
         <v>1</v>
       </c>
       <c r="AP195">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ195">
         <v>1</v>
@@ -41923,7 +41926,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42207,7 +42210,7 @@
         <v>1.89</v>
       </c>
       <c r="AP198">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ198">
         <v>1.85</v>
@@ -42335,7 +42338,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42541,7 +42544,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42747,7 +42750,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -43159,7 +43162,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43237,7 +43240,7 @@
         <v>2.3</v>
       </c>
       <c r="AP203">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ203">
         <v>2</v>
@@ -43571,7 +43574,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43858,7 +43861,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ206">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="AR206">
         <v>1.29</v>
@@ -43983,7 +43986,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44189,7 +44192,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44807,7 +44810,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45091,7 +45094,7 @@
         <v>1.8</v>
       </c>
       <c r="AP212">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ212">
         <v>1.85</v>
@@ -45425,7 +45428,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45506,7 +45509,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ214">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR214">
         <v>1.72</v>
@@ -45631,7 +45634,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45709,7 +45712,7 @@
         <v>0.6</v>
       </c>
       <c r="AP215">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ215">
         <v>1.15</v>
@@ -45837,7 +45840,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -45918,7 +45921,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ216">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR216">
         <v>1.3</v>
@@ -46043,7 +46046,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46249,7 +46252,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46661,7 +46664,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46867,7 +46870,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -46945,10 +46948,10 @@
         <v>0.36</v>
       </c>
       <c r="AP221">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ221">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="AR221">
         <v>1.06</v>
@@ -47279,7 +47282,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47357,7 +47360,7 @@
         <v>1.18</v>
       </c>
       <c r="AP223">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ223">
         <v>1.08</v>
@@ -47691,7 +47694,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47897,7 +47900,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -48184,7 +48187,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ227">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR227">
         <v>1.73</v>
@@ -48309,7 +48312,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48515,7 +48518,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48802,7 +48805,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ230">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR230">
         <v>1.55</v>
@@ -48927,7 +48930,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49133,7 +49136,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49339,7 +49342,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49545,7 +49548,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -50038,7 +50041,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ236">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR236">
         <v>1.47</v>
@@ -50163,7 +50166,7 @@
         <v>241</v>
       </c>
       <c r="P237" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q237">
         <v>1.91</v>
@@ -50575,7 +50578,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -50653,7 +50656,7 @@
         <v>1.09</v>
       </c>
       <c r="AP239">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ239">
         <v>1.23</v>
@@ -50987,7 +50990,7 @@
         <v>244</v>
       </c>
       <c r="P241" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q241">
         <v>2.5</v>
@@ -51271,7 +51274,7 @@
         <v>0.82</v>
       </c>
       <c r="AP242">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ242">
         <v>0.83</v>
@@ -51399,7 +51402,7 @@
         <v>245</v>
       </c>
       <c r="P243" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q243">
         <v>3.4</v>
@@ -51811,7 +51814,7 @@
         <v>92</v>
       </c>
       <c r="P245" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q245">
         <v>2.6</v>
@@ -52301,7 +52304,7 @@
         <v>1.08</v>
       </c>
       <c r="AP247">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ247">
         <v>1</v>
@@ -52429,7 +52432,7 @@
         <v>92</v>
       </c>
       <c r="P248" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q248">
         <v>4</v>
@@ -52716,7 +52719,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ249">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR249">
         <v>1.57</v>
@@ -52922,7 +52925,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ250">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="AR250">
         <v>1.32</v>
@@ -53047,7 +53050,7 @@
         <v>92</v>
       </c>
       <c r="P251" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q251">
         <v>3.6</v>
@@ -54077,7 +54080,7 @@
         <v>250</v>
       </c>
       <c r="P256" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q256">
         <v>4</v>
@@ -54489,7 +54492,7 @@
         <v>92</v>
       </c>
       <c r="P258" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q258">
         <v>6</v>
@@ -54695,7 +54698,7 @@
         <v>92</v>
       </c>
       <c r="P259" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q259">
         <v>4.75</v>
@@ -55470,6 +55473,624 @@
       </c>
       <c r="BP262">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="263" spans="1:68">
+      <c r="A263" s="1">
+        <v>262</v>
+      </c>
+      <c r="B263">
+        <v>7492408</v>
+      </c>
+      <c r="C263" t="s">
+        <v>68</v>
+      </c>
+      <c r="D263" t="s">
+        <v>69</v>
+      </c>
+      <c r="E263" s="2">
+        <v>45717.45833333334</v>
+      </c>
+      <c r="F263">
+        <v>27</v>
+      </c>
+      <c r="G263" t="s">
+        <v>89</v>
+      </c>
+      <c r="H263" t="s">
+        <v>87</v>
+      </c>
+      <c r="I263">
+        <v>0</v>
+      </c>
+      <c r="J263">
+        <v>0</v>
+      </c>
+      <c r="K263">
+        <v>0</v>
+      </c>
+      <c r="L263">
+        <v>0</v>
+      </c>
+      <c r="M263">
+        <v>0</v>
+      </c>
+      <c r="N263">
+        <v>0</v>
+      </c>
+      <c r="O263" t="s">
+        <v>92</v>
+      </c>
+      <c r="P263" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q263">
+        <v>1.62</v>
+      </c>
+      <c r="R263">
+        <v>2.75</v>
+      </c>
+      <c r="S263">
+        <v>10</v>
+      </c>
+      <c r="T263">
+        <v>1.29</v>
+      </c>
+      <c r="U263">
+        <v>3.5</v>
+      </c>
+      <c r="V263">
+        <v>2.25</v>
+      </c>
+      <c r="W263">
+        <v>1.57</v>
+      </c>
+      <c r="X263">
+        <v>5.5</v>
+      </c>
+      <c r="Y263">
+        <v>1.14</v>
+      </c>
+      <c r="Z263">
+        <v>1.23</v>
+      </c>
+      <c r="AA263">
+        <v>6.9</v>
+      </c>
+      <c r="AB263">
+        <v>13</v>
+      </c>
+      <c r="AC263">
+        <v>1.01</v>
+      </c>
+      <c r="AD263">
+        <v>23</v>
+      </c>
+      <c r="AE263">
+        <v>1.15</v>
+      </c>
+      <c r="AF263">
+        <v>5.5</v>
+      </c>
+      <c r="AG263">
+        <v>1.6</v>
+      </c>
+      <c r="AH263">
+        <v>2.34</v>
+      </c>
+      <c r="AI263">
+        <v>2.1</v>
+      </c>
+      <c r="AJ263">
+        <v>1.67</v>
+      </c>
+      <c r="AK263">
+        <v>1.05</v>
+      </c>
+      <c r="AL263">
+        <v>1.12</v>
+      </c>
+      <c r="AM263">
+        <v>3.8</v>
+      </c>
+      <c r="AN263">
+        <v>2</v>
+      </c>
+      <c r="AO263">
+        <v>0.31</v>
+      </c>
+      <c r="AP263">
+        <v>1.92</v>
+      </c>
+      <c r="AQ263">
+        <v>0.36</v>
+      </c>
+      <c r="AR263">
+        <v>1.84</v>
+      </c>
+      <c r="AS263">
+        <v>0.96</v>
+      </c>
+      <c r="AT263">
+        <v>2.8</v>
+      </c>
+      <c r="AU263">
+        <v>4</v>
+      </c>
+      <c r="AV263">
+        <v>3</v>
+      </c>
+      <c r="AW263">
+        <v>15</v>
+      </c>
+      <c r="AX263">
+        <v>6</v>
+      </c>
+      <c r="AY263">
+        <v>22</v>
+      </c>
+      <c r="AZ263">
+        <v>10</v>
+      </c>
+      <c r="BA263">
+        <v>3</v>
+      </c>
+      <c r="BB263">
+        <v>2</v>
+      </c>
+      <c r="BC263">
+        <v>5</v>
+      </c>
+      <c r="BD263">
+        <v>1.13</v>
+      </c>
+      <c r="BE263">
+        <v>9.5</v>
+      </c>
+      <c r="BF263">
+        <v>6.25</v>
+      </c>
+      <c r="BG263">
+        <v>1.28</v>
+      </c>
+      <c r="BH263">
+        <v>3.3</v>
+      </c>
+      <c r="BI263">
+        <v>1.48</v>
+      </c>
+      <c r="BJ263">
+        <v>2.43</v>
+      </c>
+      <c r="BK263">
+        <v>1.76</v>
+      </c>
+      <c r="BL263">
+        <v>1.93</v>
+      </c>
+      <c r="BM263">
+        <v>2.18</v>
+      </c>
+      <c r="BN263">
+        <v>1.58</v>
+      </c>
+      <c r="BO263">
+        <v>2.8</v>
+      </c>
+      <c r="BP263">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="264" spans="1:68">
+      <c r="A264" s="1">
+        <v>263</v>
+      </c>
+      <c r="B264">
+        <v>7492415</v>
+      </c>
+      <c r="C264" t="s">
+        <v>68</v>
+      </c>
+      <c r="D264" t="s">
+        <v>69</v>
+      </c>
+      <c r="E264" s="2">
+        <v>45717.58333333334</v>
+      </c>
+      <c r="F264">
+        <v>27</v>
+      </c>
+      <c r="G264" t="s">
+        <v>85</v>
+      </c>
+      <c r="H264" t="s">
+        <v>82</v>
+      </c>
+      <c r="I264">
+        <v>0</v>
+      </c>
+      <c r="J264">
+        <v>1</v>
+      </c>
+      <c r="K264">
+        <v>1</v>
+      </c>
+      <c r="L264">
+        <v>1</v>
+      </c>
+      <c r="M264">
+        <v>1</v>
+      </c>
+      <c r="N264">
+        <v>2</v>
+      </c>
+      <c r="O264" t="s">
+        <v>255</v>
+      </c>
+      <c r="P264" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q264">
+        <v>3.75</v>
+      </c>
+      <c r="R264">
+        <v>2.05</v>
+      </c>
+      <c r="S264">
+        <v>3.1</v>
+      </c>
+      <c r="T264">
+        <v>1.44</v>
+      </c>
+      <c r="U264">
+        <v>2.63</v>
+      </c>
+      <c r="V264">
+        <v>3.25</v>
+      </c>
+      <c r="W264">
+        <v>1.33</v>
+      </c>
+      <c r="X264">
+        <v>10</v>
+      </c>
+      <c r="Y264">
+        <v>1.06</v>
+      </c>
+      <c r="Z264">
+        <v>3.11</v>
+      </c>
+      <c r="AA264">
+        <v>3.23</v>
+      </c>
+      <c r="AB264">
+        <v>2.47</v>
+      </c>
+      <c r="AC264">
+        <v>1.08</v>
+      </c>
+      <c r="AD264">
+        <v>8.5</v>
+      </c>
+      <c r="AE264">
+        <v>1.4</v>
+      </c>
+      <c r="AF264">
+        <v>3</v>
+      </c>
+      <c r="AG264">
+        <v>2.05</v>
+      </c>
+      <c r="AH264">
+        <v>1.7</v>
+      </c>
+      <c r="AI264">
+        <v>1.91</v>
+      </c>
+      <c r="AJ264">
+        <v>1.91</v>
+      </c>
+      <c r="AK264">
+        <v>1.53</v>
+      </c>
+      <c r="AL264">
+        <v>1.35</v>
+      </c>
+      <c r="AM264">
+        <v>1.37</v>
+      </c>
+      <c r="AN264">
+        <v>2.33</v>
+      </c>
+      <c r="AO264">
+        <v>2.08</v>
+      </c>
+      <c r="AP264">
+        <v>2.23</v>
+      </c>
+      <c r="AQ264">
+        <v>2</v>
+      </c>
+      <c r="AR264">
+        <v>1.6</v>
+      </c>
+      <c r="AS264">
+        <v>1.6</v>
+      </c>
+      <c r="AT264">
+        <v>3.2</v>
+      </c>
+      <c r="AU264">
+        <v>5</v>
+      </c>
+      <c r="AV264">
+        <v>2</v>
+      </c>
+      <c r="AW264">
+        <v>15</v>
+      </c>
+      <c r="AX264">
+        <v>5</v>
+      </c>
+      <c r="AY264">
+        <v>29</v>
+      </c>
+      <c r="AZ264">
+        <v>9</v>
+      </c>
+      <c r="BA264">
+        <v>12</v>
+      </c>
+      <c r="BB264">
+        <v>3</v>
+      </c>
+      <c r="BC264">
+        <v>15</v>
+      </c>
+      <c r="BD264">
+        <v>1.98</v>
+      </c>
+      <c r="BE264">
+        <v>6.25</v>
+      </c>
+      <c r="BF264">
+        <v>1.98</v>
+      </c>
+      <c r="BG264">
+        <v>1.4</v>
+      </c>
+      <c r="BH264">
+        <v>2.7</v>
+      </c>
+      <c r="BI264">
+        <v>1.67</v>
+      </c>
+      <c r="BJ264">
+        <v>2.05</v>
+      </c>
+      <c r="BK264">
+        <v>2.08</v>
+      </c>
+      <c r="BL264">
+        <v>1.65</v>
+      </c>
+      <c r="BM264">
+        <v>2.7</v>
+      </c>
+      <c r="BN264">
+        <v>1.4</v>
+      </c>
+      <c r="BO264">
+        <v>3.65</v>
+      </c>
+      <c r="BP264">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="265" spans="1:68">
+      <c r="A265" s="1">
+        <v>264</v>
+      </c>
+      <c r="B265">
+        <v>7492417</v>
+      </c>
+      <c r="C265" t="s">
+        <v>68</v>
+      </c>
+      <c r="D265" t="s">
+        <v>69</v>
+      </c>
+      <c r="E265" s="2">
+        <v>45717.69791666666</v>
+      </c>
+      <c r="F265">
+        <v>27</v>
+      </c>
+      <c r="G265" t="s">
+        <v>80</v>
+      </c>
+      <c r="H265" t="s">
+        <v>71</v>
+      </c>
+      <c r="I265">
+        <v>1</v>
+      </c>
+      <c r="J265">
+        <v>0</v>
+      </c>
+      <c r="K265">
+        <v>1</v>
+      </c>
+      <c r="L265">
+        <v>1</v>
+      </c>
+      <c r="M265">
+        <v>0</v>
+      </c>
+      <c r="N265">
+        <v>1</v>
+      </c>
+      <c r="O265" t="s">
+        <v>223</v>
+      </c>
+      <c r="P265" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q265">
+        <v>2.38</v>
+      </c>
+      <c r="R265">
+        <v>2.25</v>
+      </c>
+      <c r="S265">
+        <v>4.75</v>
+      </c>
+      <c r="T265">
+        <v>1.36</v>
+      </c>
+      <c r="U265">
+        <v>3</v>
+      </c>
+      <c r="V265">
+        <v>2.75</v>
+      </c>
+      <c r="W265">
+        <v>1.4</v>
+      </c>
+      <c r="X265">
+        <v>7</v>
+      </c>
+      <c r="Y265">
+        <v>1.1</v>
+      </c>
+      <c r="Z265">
+        <v>1.83</v>
+      </c>
+      <c r="AA265">
+        <v>3.69</v>
+      </c>
+      <c r="AB265">
+        <v>4.6</v>
+      </c>
+      <c r="AC265">
+        <v>1.05</v>
+      </c>
+      <c r="AD265">
+        <v>12</v>
+      </c>
+      <c r="AE265">
+        <v>1.28</v>
+      </c>
+      <c r="AF265">
+        <v>3.75</v>
+      </c>
+      <c r="AG265">
+        <v>1.82</v>
+      </c>
+      <c r="AH265">
+        <v>2</v>
+      </c>
+      <c r="AI265">
+        <v>1.75</v>
+      </c>
+      <c r="AJ265">
+        <v>2</v>
+      </c>
+      <c r="AK265">
+        <v>1.2</v>
+      </c>
+      <c r="AL265">
+        <v>1.28</v>
+      </c>
+      <c r="AM265">
+        <v>1.98</v>
+      </c>
+      <c r="AN265">
+        <v>1.54</v>
+      </c>
+      <c r="AO265">
+        <v>0.67</v>
+      </c>
+      <c r="AP265">
+        <v>1.64</v>
+      </c>
+      <c r="AQ265">
+        <v>0.62</v>
+      </c>
+      <c r="AR265">
+        <v>1.18</v>
+      </c>
+      <c r="AS265">
+        <v>1.19</v>
+      </c>
+      <c r="AT265">
+        <v>2.37</v>
+      </c>
+      <c r="AU265">
+        <v>7</v>
+      </c>
+      <c r="AV265">
+        <v>5</v>
+      </c>
+      <c r="AW265">
+        <v>15</v>
+      </c>
+      <c r="AX265">
+        <v>5</v>
+      </c>
+      <c r="AY265">
+        <v>26</v>
+      </c>
+      <c r="AZ265">
+        <v>12</v>
+      </c>
+      <c r="BA265">
+        <v>7</v>
+      </c>
+      <c r="BB265">
+        <v>7</v>
+      </c>
+      <c r="BC265">
+        <v>14</v>
+      </c>
+      <c r="BD265">
+        <v>1.58</v>
+      </c>
+      <c r="BE265">
+        <v>6.75</v>
+      </c>
+      <c r="BF265">
+        <v>2.63</v>
+      </c>
+      <c r="BG265">
+        <v>1.2</v>
+      </c>
+      <c r="BH265">
+        <v>3.9</v>
+      </c>
+      <c r="BI265">
+        <v>1.37</v>
+      </c>
+      <c r="BJ265">
+        <v>2.8</v>
+      </c>
+      <c r="BK265">
+        <v>1.61</v>
+      </c>
+      <c r="BL265">
+        <v>2.15</v>
+      </c>
+      <c r="BM265">
+        <v>1.96</v>
+      </c>
+      <c r="BN265">
+        <v>1.73</v>
+      </c>
+      <c r="BO265">
+        <v>2.48</v>
+      </c>
+      <c r="BP265">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="375">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1500,7 +1500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP265"/>
+  <dimension ref="A1:BP266"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2455,7 +2455,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ5">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -4306,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ14">
         <v>1.15</v>
@@ -5957,7 +5957,7 @@
         <v>1</v>
       </c>
       <c r="AQ22">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -9456,7 +9456,7 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ39">
         <v>2</v>
@@ -10283,7 +10283,7 @@
         <v>1</v>
       </c>
       <c r="AQ43">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR43">
         <v>0.93</v>
@@ -11310,7 +11310,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ48">
         <v>1.38</v>
@@ -15021,7 +15021,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ66">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR66">
         <v>1.21</v>
@@ -15842,7 +15842,7 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ70">
         <v>1.15</v>
@@ -17699,7 +17699,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ79">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR79">
         <v>1.44</v>
@@ -19550,7 +19550,7 @@
         <v>0.2</v>
       </c>
       <c r="AP88">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ88">
         <v>0.36</v>
@@ -22025,7 +22025,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ100">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR100">
         <v>1.81</v>
@@ -22640,7 +22640,7 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ103">
         <v>1.31</v>
@@ -25115,7 +25115,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ115">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR115">
         <v>1.54</v>
@@ -25936,7 +25936,7 @@
         <v>1.2</v>
       </c>
       <c r="AP119">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ119">
         <v>1.69</v>
@@ -30677,7 +30677,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ142">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR142">
         <v>1.3</v>
@@ -32116,7 +32116,7 @@
         <v>0.71</v>
       </c>
       <c r="AP149">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ149">
         <v>1.23</v>
@@ -32325,7 +32325,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ150">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR150">
         <v>0.84</v>
@@ -35824,7 +35824,7 @@
         <v>1.86</v>
       </c>
       <c r="AP167">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ167">
         <v>1.85</v>
@@ -37269,7 +37269,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ174">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR174">
         <v>1.03</v>
@@ -39120,7 +39120,7 @@
         <v>0.63</v>
       </c>
       <c r="AP183">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ183">
         <v>0.83</v>
@@ -41798,7 +41798,7 @@
         <v>1.67</v>
       </c>
       <c r="AP196">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ196">
         <v>1.38</v>
@@ -43449,7 +43449,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ204">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR204">
         <v>1.51</v>
@@ -47154,7 +47154,7 @@
         <v>0.91</v>
       </c>
       <c r="AP222">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ222">
         <v>1</v>
@@ -47363,7 +47363,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ223">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR223">
         <v>1.8</v>
@@ -51071,7 +51071,7 @@
         <v>2</v>
       </c>
       <c r="AQ241">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR241">
         <v>1.74</v>
@@ -52098,7 +52098,7 @@
         <v>0.83</v>
       </c>
       <c r="AP246">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ246">
         <v>0.79</v>
@@ -56091,6 +56091,212 @@
       </c>
       <c r="BP265">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="266" spans="1:68">
+      <c r="A266" s="1">
+        <v>265</v>
+      </c>
+      <c r="B266">
+        <v>7492414</v>
+      </c>
+      <c r="C266" t="s">
+        <v>68</v>
+      </c>
+      <c r="D266" t="s">
+        <v>69</v>
+      </c>
+      <c r="E266" s="2">
+        <v>45718.35416666666</v>
+      </c>
+      <c r="F266">
+        <v>27</v>
+      </c>
+      <c r="G266" t="s">
+        <v>81</v>
+      </c>
+      <c r="H266" t="s">
+        <v>84</v>
+      </c>
+      <c r="I266">
+        <v>0</v>
+      </c>
+      <c r="J266">
+        <v>1</v>
+      </c>
+      <c r="K266">
+        <v>1</v>
+      </c>
+      <c r="L266">
+        <v>0</v>
+      </c>
+      <c r="M266">
+        <v>2</v>
+      </c>
+      <c r="N266">
+        <v>2</v>
+      </c>
+      <c r="O266" t="s">
+        <v>92</v>
+      </c>
+      <c r="P266" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q266">
+        <v>4.75</v>
+      </c>
+      <c r="R266">
+        <v>2</v>
+      </c>
+      <c r="S266">
+        <v>2.75</v>
+      </c>
+      <c r="T266">
+        <v>1.5</v>
+      </c>
+      <c r="U266">
+        <v>2.5</v>
+      </c>
+      <c r="V266">
+        <v>3.5</v>
+      </c>
+      <c r="W266">
+        <v>1.29</v>
+      </c>
+      <c r="X266">
+        <v>11</v>
+      </c>
+      <c r="Y266">
+        <v>1.05</v>
+      </c>
+      <c r="Z266">
+        <v>3.45</v>
+      </c>
+      <c r="AA266">
+        <v>3.23</v>
+      </c>
+      <c r="AB266">
+        <v>2.3</v>
+      </c>
+      <c r="AC266">
+        <v>1.09</v>
+      </c>
+      <c r="AD266">
+        <v>8</v>
+      </c>
+      <c r="AE266">
+        <v>1.45</v>
+      </c>
+      <c r="AF266">
+        <v>2.8</v>
+      </c>
+      <c r="AG266">
+        <v>2.3</v>
+      </c>
+      <c r="AH266">
+        <v>1.57</v>
+      </c>
+      <c r="AI266">
+        <v>2.05</v>
+      </c>
+      <c r="AJ266">
+        <v>1.7</v>
+      </c>
+      <c r="AK266">
+        <v>1.72</v>
+      </c>
+      <c r="AL266">
+        <v>1.33</v>
+      </c>
+      <c r="AM266">
+        <v>1.26</v>
+      </c>
+      <c r="AN266">
+        <v>0.54</v>
+      </c>
+      <c r="AO266">
+        <v>1.08</v>
+      </c>
+      <c r="AP266">
+        <v>0.5</v>
+      </c>
+      <c r="AQ266">
+        <v>1.21</v>
+      </c>
+      <c r="AR266">
+        <v>1.18</v>
+      </c>
+      <c r="AS266">
+        <v>1.08</v>
+      </c>
+      <c r="AT266">
+        <v>2.26</v>
+      </c>
+      <c r="AU266">
+        <v>3</v>
+      </c>
+      <c r="AV266">
+        <v>8</v>
+      </c>
+      <c r="AW266">
+        <v>7</v>
+      </c>
+      <c r="AX266">
+        <v>6</v>
+      </c>
+      <c r="AY266">
+        <v>12</v>
+      </c>
+      <c r="AZ266">
+        <v>14</v>
+      </c>
+      <c r="BA266">
+        <v>1</v>
+      </c>
+      <c r="BB266">
+        <v>4</v>
+      </c>
+      <c r="BC266">
+        <v>5</v>
+      </c>
+      <c r="BD266">
+        <v>2.25</v>
+      </c>
+      <c r="BE266">
+        <v>6.35</v>
+      </c>
+      <c r="BF266">
+        <v>2.06</v>
+      </c>
+      <c r="BG266">
+        <v>1.37</v>
+      </c>
+      <c r="BH266">
+        <v>2.75</v>
+      </c>
+      <c r="BI266">
+        <v>1.69</v>
+      </c>
+      <c r="BJ266">
+        <v>2.04</v>
+      </c>
+      <c r="BK266">
+        <v>2.15</v>
+      </c>
+      <c r="BL266">
+        <v>1.59</v>
+      </c>
+      <c r="BM266">
+        <v>2.88</v>
+      </c>
+      <c r="BN266">
+        <v>1.32</v>
+      </c>
+      <c r="BO266">
+        <v>4.05</v>
+      </c>
+      <c r="BP266">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1676" uniqueCount="377">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -784,6 +784,12 @@
     <t>['87']</t>
   </si>
   <si>
+    <t>['48', '56']</t>
+  </si>
+  <si>
+    <t>['61', '76']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1500,7 +1506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP266"/>
+  <dimension ref="A1:BP269"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1756,7 +1762,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1834,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ2">
         <v>2</v>
@@ -2374,7 +2380,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2580,7 +2586,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2658,7 +2664,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ6">
         <v>1.23</v>
@@ -3198,7 +3204,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3404,7 +3410,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3691,7 +3697,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ11">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4022,7 +4028,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4228,7 +4234,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -5258,7 +5264,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5336,7 +5342,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -5545,7 +5551,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ20">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR20">
         <v>1.16</v>
@@ -5670,7 +5676,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5876,7 +5882,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6288,7 +6294,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6366,7 +6372,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ24">
         <v>1</v>
@@ -6575,7 +6581,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ25">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR25">
         <v>1.74</v>
@@ -6700,7 +6706,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6906,7 +6912,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7112,7 +7118,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7318,7 +7324,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7396,7 +7402,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ29">
         <v>1</v>
@@ -7811,7 +7817,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ31">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR31">
         <v>0.95</v>
@@ -7936,7 +7942,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8632,7 +8638,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ35">
         <v>1.15</v>
@@ -8760,7 +8766,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -9172,7 +9178,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9378,7 +9384,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9584,7 +9590,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9790,7 +9796,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9996,7 +10002,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10202,7 +10208,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10820,7 +10826,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -11026,7 +11032,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11232,7 +11238,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11516,7 +11522,7 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ49">
         <v>1.23</v>
@@ -11644,7 +11650,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11850,7 +11856,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -11931,7 +11937,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ51">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR51">
         <v>1.68</v>
@@ -12262,7 +12268,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12468,7 +12474,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12546,7 +12552,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ54">
         <v>1.85</v>
@@ -12674,7 +12680,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12752,7 +12758,7 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ55">
         <v>2.14</v>
@@ -12880,7 +12886,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13086,7 +13092,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13370,7 +13376,7 @@
         <v>0.33</v>
       </c>
       <c r="AP58">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ58">
         <v>0.36</v>
@@ -13910,7 +13916,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -13991,7 +13997,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ61">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR61">
         <v>1.23</v>
@@ -14197,7 +14203,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ62">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR62">
         <v>1.6</v>
@@ -14734,7 +14740,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14940,7 +14946,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15146,7 +15152,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15227,7 +15233,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ67">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR67">
         <v>1.09</v>
@@ -15636,7 +15642,7 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ69">
         <v>0.62</v>
@@ -15764,7 +15770,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -16382,7 +16388,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16460,7 +16466,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ73">
         <v>1.38</v>
@@ -17000,7 +17006,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17206,7 +17212,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17412,7 +17418,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17618,7 +17624,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17902,7 +17908,7 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ80">
         <v>2</v>
@@ -18030,7 +18036,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18317,7 +18323,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ82">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR82">
         <v>1.1</v>
@@ -18523,7 +18529,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ83">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR83">
         <v>1.23</v>
@@ -18854,7 +18860,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19472,7 +19478,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19678,7 +19684,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19884,7 +19890,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20090,7 +20096,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20502,7 +20508,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20708,7 +20714,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20914,7 +20920,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -21326,7 +21332,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21532,7 +21538,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21610,7 +21616,7 @@
         <v>1.25</v>
       </c>
       <c r="AP98">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ98">
         <v>1.38</v>
@@ -21738,7 +21744,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22022,7 +22028,7 @@
         <v>1.4</v>
       </c>
       <c r="AP100">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ100">
         <v>1.21</v>
@@ -22228,7 +22234,7 @@
         <v>0.2</v>
       </c>
       <c r="AP101">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ101">
         <v>0.79</v>
@@ -22356,7 +22362,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22768,7 +22774,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22974,7 +22980,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23180,7 +23186,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23673,7 +23679,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ108">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR108">
         <v>0.82</v>
@@ -24004,7 +24010,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24085,7 +24091,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ110">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR110">
         <v>1.55</v>
@@ -24210,7 +24216,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24288,10 +24294,10 @@
         <v>0.57</v>
       </c>
       <c r="AP111">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ111">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR111">
         <v>1.25</v>
@@ -24416,7 +24422,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24622,7 +24628,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24828,7 +24834,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25240,7 +25246,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25446,7 +25452,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25524,7 +25530,7 @@
         <v>1.6</v>
       </c>
       <c r="AP117">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ117">
         <v>1.38</v>
@@ -25652,7 +25658,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -26270,7 +26276,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26682,7 +26688,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26888,7 +26894,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26966,10 +26972,10 @@
         <v>0.8</v>
       </c>
       <c r="AP124">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ124">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR124">
         <v>1.24</v>
@@ -27094,7 +27100,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27300,7 +27306,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27918,7 +27924,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -29026,7 +29032,7 @@
         <v>0.29</v>
       </c>
       <c r="AP134">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ134">
         <v>0.36</v>
@@ -29154,7 +29160,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29360,7 +29366,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29772,7 +29778,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29978,7 +29984,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30056,7 +30062,7 @@
         <v>1.86</v>
       </c>
       <c r="AP139">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ139">
         <v>2.14</v>
@@ -30674,7 +30680,7 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ142">
         <v>1.21</v>
@@ -30802,7 +30808,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -31008,7 +31014,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31086,7 +31092,7 @@
         <v>0.57</v>
       </c>
       <c r="AP144">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ144">
         <v>0.79</v>
@@ -31295,7 +31301,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ145">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR145">
         <v>1.69</v>
@@ -31420,7 +31426,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31626,7 +31632,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31707,7 +31713,7 @@
         <v>1</v>
       </c>
       <c r="AQ147">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR147">
         <v>1.55</v>
@@ -32038,7 +32044,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32450,7 +32456,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32656,7 +32662,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32862,7 +32868,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -33274,7 +33280,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -33558,7 +33564,7 @@
         <v>2</v>
       </c>
       <c r="AP156">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ156">
         <v>1.38</v>
@@ -34098,7 +34104,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34510,7 +34516,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34716,7 +34722,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34794,7 +34800,7 @@
         <v>2.13</v>
       </c>
       <c r="AP162">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ162">
         <v>2</v>
@@ -34922,7 +34928,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35206,7 +35212,7 @@
         <v>1</v>
       </c>
       <c r="AP164">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ164">
         <v>0.62</v>
@@ -35334,7 +35340,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35415,7 +35421,7 @@
         <v>1</v>
       </c>
       <c r="AQ165">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR165">
         <v>1.48</v>
@@ -35540,7 +35546,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35746,7 +35752,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35952,7 +35958,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36239,7 +36245,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ169">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR169">
         <v>1.57</v>
@@ -36570,7 +36576,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36776,7 +36782,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36982,7 +36988,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37188,7 +37194,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37600,7 +37606,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -38218,7 +38224,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38296,7 +38302,7 @@
         <v>0.75</v>
       </c>
       <c r="AP179">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ179">
         <v>1</v>
@@ -38424,7 +38430,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38630,7 +38636,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39042,7 +39048,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39123,7 +39129,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ183">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR183">
         <v>1.19</v>
@@ -39738,7 +39744,7 @@
         <v>1.67</v>
       </c>
       <c r="AP186">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ186">
         <v>1.69</v>
@@ -39866,7 +39872,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39947,7 +39953,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ187">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR187">
         <v>1.47</v>
@@ -40278,7 +40284,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40690,7 +40696,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -40771,7 +40777,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ191">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR191">
         <v>1.6</v>
@@ -40974,7 +40980,7 @@
         <v>0.89</v>
       </c>
       <c r="AP192">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ192">
         <v>0.62</v>
@@ -41308,7 +41314,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41386,7 +41392,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP194">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ194">
         <v>1.15</v>
@@ -41926,7 +41932,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42338,7 +42344,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42544,7 +42550,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42622,7 +42628,7 @@
         <v>1.56</v>
       </c>
       <c r="AP200">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ200">
         <v>1.15</v>
@@ -42750,7 +42756,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -42828,7 +42834,7 @@
         <v>0.78</v>
       </c>
       <c r="AP201">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ201">
         <v>0.54</v>
@@ -43162,7 +43168,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43574,7 +43580,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43986,7 +43992,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44192,7 +44198,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44685,7 +44691,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ210">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR210">
         <v>1.04</v>
@@ -44810,7 +44816,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45428,7 +45434,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45634,7 +45640,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45840,7 +45846,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -46046,7 +46052,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46252,7 +46258,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46536,7 +46542,7 @@
         <v>0.7</v>
       </c>
       <c r="AP219">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ219">
         <v>0.54</v>
@@ -46664,7 +46670,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46870,7 +46876,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47282,7 +47288,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47566,10 +47572,10 @@
         <v>0.64</v>
       </c>
       <c r="AP224">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ224">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR224">
         <v>1.75</v>
@@ -47694,7 +47700,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47900,7 +47906,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -48312,7 +48318,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48390,7 +48396,7 @@
         <v>2.36</v>
       </c>
       <c r="AP228">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ228">
         <v>2</v>
@@ -48518,7 +48524,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48930,7 +48936,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49136,7 +49142,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49342,7 +49348,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49548,7 +49554,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -50166,7 +50172,7 @@
         <v>241</v>
       </c>
       <c r="P237" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q237">
         <v>1.91</v>
@@ -50578,7 +50584,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -50990,7 +50996,7 @@
         <v>244</v>
       </c>
       <c r="P241" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q241">
         <v>2.5</v>
@@ -51068,7 +51074,7 @@
         <v>1.17</v>
       </c>
       <c r="AP241">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ241">
         <v>1.21</v>
@@ -51277,7 +51283,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ242">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR242">
         <v>1.88</v>
@@ -51402,7 +51408,7 @@
         <v>245</v>
       </c>
       <c r="P243" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q243">
         <v>3.4</v>
@@ -51814,7 +51820,7 @@
         <v>92</v>
       </c>
       <c r="P245" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q245">
         <v>2.6</v>
@@ -51895,7 +51901,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ245">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR245">
         <v>1.56</v>
@@ -52432,7 +52438,7 @@
         <v>92</v>
       </c>
       <c r="P248" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q248">
         <v>4</v>
@@ -52922,7 +52928,7 @@
         <v>0.33</v>
       </c>
       <c r="AP250">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ250">
         <v>0.36</v>
@@ -53050,7 +53056,7 @@
         <v>92</v>
       </c>
       <c r="P251" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q251">
         <v>3.6</v>
@@ -54080,7 +54086,7 @@
         <v>250</v>
       </c>
       <c r="P256" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q256">
         <v>4</v>
@@ -54492,7 +54498,7 @@
         <v>92</v>
       </c>
       <c r="P258" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q258">
         <v>6</v>
@@ -54698,7 +54704,7 @@
         <v>92</v>
       </c>
       <c r="P259" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q259">
         <v>4.75</v>
@@ -54982,7 +54988,7 @@
         <v>0.58</v>
       </c>
       <c r="AP260">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ260">
         <v>0.54</v>
@@ -55188,7 +55194,7 @@
         <v>1.42</v>
       </c>
       <c r="AP261">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ261">
         <v>1.31</v>
@@ -56140,7 +56146,7 @@
         <v>92</v>
       </c>
       <c r="P266" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q266">
         <v>4.75</v>
@@ -56297,6 +56303,624 @@
       </c>
       <c r="BP266">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="267" spans="1:68">
+      <c r="A267" s="1">
+        <v>266</v>
+      </c>
+      <c r="B267">
+        <v>7492409</v>
+      </c>
+      <c r="C267" t="s">
+        <v>68</v>
+      </c>
+      <c r="D267" t="s">
+        <v>69</v>
+      </c>
+      <c r="E267" s="2">
+        <v>45718.45833333334</v>
+      </c>
+      <c r="F267">
+        <v>27</v>
+      </c>
+      <c r="G267" t="s">
+        <v>74</v>
+      </c>
+      <c r="H267" t="s">
+        <v>76</v>
+      </c>
+      <c r="I267">
+        <v>0</v>
+      </c>
+      <c r="J267">
+        <v>1</v>
+      </c>
+      <c r="K267">
+        <v>1</v>
+      </c>
+      <c r="L267">
+        <v>2</v>
+      </c>
+      <c r="M267">
+        <v>1</v>
+      </c>
+      <c r="N267">
+        <v>3</v>
+      </c>
+      <c r="O267" t="s">
+        <v>256</v>
+      </c>
+      <c r="P267" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q267">
+        <v>2.2</v>
+      </c>
+      <c r="R267">
+        <v>2.2</v>
+      </c>
+      <c r="S267">
+        <v>6</v>
+      </c>
+      <c r="T267">
+        <v>1.44</v>
+      </c>
+      <c r="U267">
+        <v>2.63</v>
+      </c>
+      <c r="V267">
+        <v>3.25</v>
+      </c>
+      <c r="W267">
+        <v>1.33</v>
+      </c>
+      <c r="X267">
+        <v>9</v>
+      </c>
+      <c r="Y267">
+        <v>1.07</v>
+      </c>
+      <c r="Z267">
+        <v>1.62</v>
+      </c>
+      <c r="AA267">
+        <v>4</v>
+      </c>
+      <c r="AB267">
+        <v>6</v>
+      </c>
+      <c r="AC267">
+        <v>1.06</v>
+      </c>
+      <c r="AD267">
+        <v>10</v>
+      </c>
+      <c r="AE267">
+        <v>1.36</v>
+      </c>
+      <c r="AF267">
+        <v>3.2</v>
+      </c>
+      <c r="AG267">
+        <v>2</v>
+      </c>
+      <c r="AH267">
+        <v>1.73</v>
+      </c>
+      <c r="AI267">
+        <v>2.05</v>
+      </c>
+      <c r="AJ267">
+        <v>1.7</v>
+      </c>
+      <c r="AK267">
+        <v>1.13</v>
+      </c>
+      <c r="AL267">
+        <v>1.25</v>
+      </c>
+      <c r="AM267">
+        <v>2.3</v>
+      </c>
+      <c r="AN267">
+        <v>2</v>
+      </c>
+      <c r="AO267">
+        <v>0.83</v>
+      </c>
+      <c r="AP267">
+        <v>2.07</v>
+      </c>
+      <c r="AQ267">
+        <v>0.77</v>
+      </c>
+      <c r="AR267">
+        <v>1.79</v>
+      </c>
+      <c r="AS267">
+        <v>1.01</v>
+      </c>
+      <c r="AT267">
+        <v>2.8</v>
+      </c>
+      <c r="AU267">
+        <v>6</v>
+      </c>
+      <c r="AV267">
+        <v>2</v>
+      </c>
+      <c r="AW267">
+        <v>10</v>
+      </c>
+      <c r="AX267">
+        <v>1</v>
+      </c>
+      <c r="AY267">
+        <v>16</v>
+      </c>
+      <c r="AZ267">
+        <v>3</v>
+      </c>
+      <c r="BA267">
+        <v>4</v>
+      </c>
+      <c r="BB267">
+        <v>1</v>
+      </c>
+      <c r="BC267">
+        <v>5</v>
+      </c>
+      <c r="BD267">
+        <v>1.34</v>
+      </c>
+      <c r="BE267">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BF267">
+        <v>4.2</v>
+      </c>
+      <c r="BG267">
+        <v>1.3</v>
+      </c>
+      <c r="BH267">
+        <v>2.97</v>
+      </c>
+      <c r="BI267">
+        <v>1.57</v>
+      </c>
+      <c r="BJ267">
+        <v>2.19</v>
+      </c>
+      <c r="BK267">
+        <v>1.99</v>
+      </c>
+      <c r="BL267">
+        <v>1.73</v>
+      </c>
+      <c r="BM267">
+        <v>2.6</v>
+      </c>
+      <c r="BN267">
+        <v>1.41</v>
+      </c>
+      <c r="BO267">
+        <v>3.5</v>
+      </c>
+      <c r="BP267">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="268" spans="1:68">
+      <c r="A268" s="1">
+        <v>267</v>
+      </c>
+      <c r="B268">
+        <v>7492411</v>
+      </c>
+      <c r="C268" t="s">
+        <v>68</v>
+      </c>
+      <c r="D268" t="s">
+        <v>69</v>
+      </c>
+      <c r="E268" s="2">
+        <v>45718.45833333334</v>
+      </c>
+      <c r="F268">
+        <v>27</v>
+      </c>
+      <c r="G268" t="s">
+        <v>70</v>
+      </c>
+      <c r="H268" t="s">
+        <v>72</v>
+      </c>
+      <c r="I268">
+        <v>0</v>
+      </c>
+      <c r="J268">
+        <v>1</v>
+      </c>
+      <c r="K268">
+        <v>1</v>
+      </c>
+      <c r="L268">
+        <v>1</v>
+      </c>
+      <c r="M268">
+        <v>1</v>
+      </c>
+      <c r="N268">
+        <v>2</v>
+      </c>
+      <c r="O268" t="s">
+        <v>116</v>
+      </c>
+      <c r="P268" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q268">
+        <v>2.63</v>
+      </c>
+      <c r="R268">
+        <v>2</v>
+      </c>
+      <c r="S268">
+        <v>4.75</v>
+      </c>
+      <c r="T268">
+        <v>1.5</v>
+      </c>
+      <c r="U268">
+        <v>2.5</v>
+      </c>
+      <c r="V268">
+        <v>3.5</v>
+      </c>
+      <c r="W268">
+        <v>1.29</v>
+      </c>
+      <c r="X268">
+        <v>10</v>
+      </c>
+      <c r="Y268">
+        <v>1.06</v>
+      </c>
+      <c r="Z268">
+        <v>1.95</v>
+      </c>
+      <c r="AA268">
+        <v>3.33</v>
+      </c>
+      <c r="AB268">
+        <v>4.5</v>
+      </c>
+      <c r="AC268">
+        <v>1.09</v>
+      </c>
+      <c r="AD268">
+        <v>8</v>
+      </c>
+      <c r="AE268">
+        <v>1.44</v>
+      </c>
+      <c r="AF268">
+        <v>2.8</v>
+      </c>
+      <c r="AG268">
+        <v>2.2</v>
+      </c>
+      <c r="AH268">
+        <v>1.61</v>
+      </c>
+      <c r="AI268">
+        <v>2</v>
+      </c>
+      <c r="AJ268">
+        <v>1.75</v>
+      </c>
+      <c r="AK268">
+        <v>1.22</v>
+      </c>
+      <c r="AL268">
+        <v>1.33</v>
+      </c>
+      <c r="AM268">
+        <v>1.82</v>
+      </c>
+      <c r="AN268">
+        <v>1.15</v>
+      </c>
+      <c r="AO268">
+        <v>1</v>
+      </c>
+      <c r="AP268">
+        <v>1.14</v>
+      </c>
+      <c r="AQ268">
+        <v>1</v>
+      </c>
+      <c r="AR268">
+        <v>1.35</v>
+      </c>
+      <c r="AS268">
+        <v>1.05</v>
+      </c>
+      <c r="AT268">
+        <v>2.4</v>
+      </c>
+      <c r="AU268">
+        <v>3</v>
+      </c>
+      <c r="AV268">
+        <v>2</v>
+      </c>
+      <c r="AW268">
+        <v>3</v>
+      </c>
+      <c r="AX268">
+        <v>6</v>
+      </c>
+      <c r="AY268">
+        <v>7</v>
+      </c>
+      <c r="AZ268">
+        <v>11</v>
+      </c>
+      <c r="BA268">
+        <v>3</v>
+      </c>
+      <c r="BB268">
+        <v>6</v>
+      </c>
+      <c r="BC268">
+        <v>9</v>
+      </c>
+      <c r="BD268">
+        <v>1.56</v>
+      </c>
+      <c r="BE268">
+        <v>9</v>
+      </c>
+      <c r="BF268">
+        <v>2.98</v>
+      </c>
+      <c r="BG268">
+        <v>1.22</v>
+      </c>
+      <c r="BH268">
+        <v>3.5</v>
+      </c>
+      <c r="BI268">
+        <v>1.44</v>
+      </c>
+      <c r="BJ268">
+        <v>2.5</v>
+      </c>
+      <c r="BK268">
+        <v>1.8</v>
+      </c>
+      <c r="BL268">
+        <v>1.9</v>
+      </c>
+      <c r="BM268">
+        <v>2.28</v>
+      </c>
+      <c r="BN268">
+        <v>1.53</v>
+      </c>
+      <c r="BO268">
+        <v>3.04</v>
+      </c>
+      <c r="BP268">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="269" spans="1:68">
+      <c r="A269" s="1">
+        <v>268</v>
+      </c>
+      <c r="B269">
+        <v>7492416</v>
+      </c>
+      <c r="C269" t="s">
+        <v>68</v>
+      </c>
+      <c r="D269" t="s">
+        <v>69</v>
+      </c>
+      <c r="E269" s="2">
+        <v>45718.58333333334</v>
+      </c>
+      <c r="F269">
+        <v>27</v>
+      </c>
+      <c r="G269" t="s">
+        <v>86</v>
+      </c>
+      <c r="H269" t="s">
+        <v>88</v>
+      </c>
+      <c r="I269">
+        <v>0</v>
+      </c>
+      <c r="J269">
+        <v>1</v>
+      </c>
+      <c r="K269">
+        <v>1</v>
+      </c>
+      <c r="L269">
+        <v>2</v>
+      </c>
+      <c r="M269">
+        <v>1</v>
+      </c>
+      <c r="N269">
+        <v>3</v>
+      </c>
+      <c r="O269" t="s">
+        <v>257</v>
+      </c>
+      <c r="P269" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q269">
+        <v>2.6</v>
+      </c>
+      <c r="R269">
+        <v>2.2</v>
+      </c>
+      <c r="S269">
+        <v>4.5</v>
+      </c>
+      <c r="T269">
+        <v>1.4</v>
+      </c>
+      <c r="U269">
+        <v>2.75</v>
+      </c>
+      <c r="V269">
+        <v>3</v>
+      </c>
+      <c r="W269">
+        <v>1.36</v>
+      </c>
+      <c r="X269">
+        <v>8</v>
+      </c>
+      <c r="Y269">
+        <v>1.08</v>
+      </c>
+      <c r="Z269">
+        <v>1.97</v>
+      </c>
+      <c r="AA269">
+        <v>3.74</v>
+      </c>
+      <c r="AB269">
+        <v>3.84</v>
+      </c>
+      <c r="AC269">
+        <v>1.05</v>
+      </c>
+      <c r="AD269">
+        <v>11</v>
+      </c>
+      <c r="AE269">
+        <v>1.33</v>
+      </c>
+      <c r="AF269">
+        <v>3.4</v>
+      </c>
+      <c r="AG269">
+        <v>1.9</v>
+      </c>
+      <c r="AH269">
+        <v>1.9</v>
+      </c>
+      <c r="AI269">
+        <v>1.8</v>
+      </c>
+      <c r="AJ269">
+        <v>1.95</v>
+      </c>
+      <c r="AK269">
+        <v>1.25</v>
+      </c>
+      <c r="AL269">
+        <v>1.3</v>
+      </c>
+      <c r="AM269">
+        <v>1.82</v>
+      </c>
+      <c r="AN269">
+        <v>1.92</v>
+      </c>
+      <c r="AO269">
+        <v>0.77</v>
+      </c>
+      <c r="AP269">
+        <v>2</v>
+      </c>
+      <c r="AQ269">
+        <v>0.71</v>
+      </c>
+      <c r="AR269">
+        <v>1.63</v>
+      </c>
+      <c r="AS269">
+        <v>1.31</v>
+      </c>
+      <c r="AT269">
+        <v>2.94</v>
+      </c>
+      <c r="AU269">
+        <v>-1</v>
+      </c>
+      <c r="AV269">
+        <v>-1</v>
+      </c>
+      <c r="AW269">
+        <v>-1</v>
+      </c>
+      <c r="AX269">
+        <v>-1</v>
+      </c>
+      <c r="AY269">
+        <v>-1</v>
+      </c>
+      <c r="AZ269">
+        <v>-1</v>
+      </c>
+      <c r="BA269">
+        <v>-1</v>
+      </c>
+      <c r="BB269">
+        <v>-1</v>
+      </c>
+      <c r="BC269">
+        <v>-1</v>
+      </c>
+      <c r="BD269">
+        <v>1.55</v>
+      </c>
+      <c r="BE269">
+        <v>8.5</v>
+      </c>
+      <c r="BF269">
+        <v>3.08</v>
+      </c>
+      <c r="BG269">
+        <v>1.4</v>
+      </c>
+      <c r="BH269">
+        <v>2.64</v>
+      </c>
+      <c r="BI269">
+        <v>1.74</v>
+      </c>
+      <c r="BJ269">
+        <v>1.98</v>
+      </c>
+      <c r="BK269">
+        <v>2.21</v>
+      </c>
+      <c r="BL269">
+        <v>1.56</v>
+      </c>
+      <c r="BM269">
+        <v>2.97</v>
+      </c>
+      <c r="BN269">
+        <v>1.3</v>
+      </c>
+      <c r="BO269">
+        <v>4.2</v>
+      </c>
+      <c r="BP269">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1676" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="378">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -790,6 +790,9 @@
     <t>['61', '76']</t>
   </si>
   <si>
+    <t>['84']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1096,9 +1099,6 @@
     <t>['2', '21', '58']</t>
   </si>
   <si>
-    <t>['84']</t>
-  </si>
-  <si>
     <t>['56', '70']</t>
   </si>
   <si>
@@ -1145,6 +1145,9 @@
   </si>
   <si>
     <t>['12']</t>
+  </si>
+  <si>
+    <t>['28', '90+8']</t>
   </si>
 </sst>
 </file>
@@ -1506,7 +1509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP269"/>
+  <dimension ref="A1:BP270"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1762,7 +1765,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2380,7 +2383,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2458,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ5">
         <v>1.21</v>
@@ -2586,7 +2589,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -3204,7 +3207,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3410,7 +3413,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3903,7 +3906,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ12">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4028,7 +4031,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4234,7 +4237,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -5264,7 +5267,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5676,7 +5679,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5882,7 +5885,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6294,7 +6297,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6706,7 +6709,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6912,7 +6915,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7118,7 +7121,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7324,7 +7327,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7942,7 +7945,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8432,7 +8435,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ34">
         <v>0.36</v>
@@ -8766,7 +8769,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -9178,7 +9181,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9384,7 +9387,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9590,7 +9593,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9796,7 +9799,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -10002,7 +10005,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10208,7 +10211,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10826,7 +10829,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -11032,7 +11035,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11113,7 +11116,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ47">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR47">
         <v>1.69</v>
@@ -11238,7 +11241,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11650,7 +11653,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11856,7 +11859,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12140,7 +12143,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ52">
         <v>0.79</v>
@@ -12268,7 +12271,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12474,7 +12477,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12680,7 +12683,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12886,7 +12889,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -12967,7 +12970,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ56">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR56">
         <v>1.02</v>
@@ -13092,7 +13095,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13916,7 +13919,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14740,7 +14743,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14946,7 +14949,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15152,7 +15155,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15770,7 +15773,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -16388,7 +16391,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16672,7 +16675,7 @@
         <v>1.33</v>
       </c>
       <c r="AP74">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ74">
         <v>1.23</v>
@@ -16881,7 +16884,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ75">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR75">
         <v>1.37</v>
@@ -17006,7 +17009,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17212,7 +17215,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17418,7 +17421,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17624,7 +17627,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -18036,7 +18039,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18860,7 +18863,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19478,7 +19481,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19684,7 +19687,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19890,7 +19893,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20096,7 +20099,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20508,7 +20511,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20586,7 +20589,7 @@
         <v>1.75</v>
       </c>
       <c r="AP93">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ93">
         <v>2</v>
@@ -20714,7 +20717,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20920,7 +20923,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -21332,7 +21335,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21538,7 +21541,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21744,7 +21747,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21825,7 +21828,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ99">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR99">
         <v>1.62</v>
@@ -22362,7 +22365,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22774,7 +22777,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22980,7 +22983,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23186,7 +23189,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -24010,7 +24013,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24216,7 +24219,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24422,7 +24425,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24628,7 +24631,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24834,7 +24837,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25246,7 +25249,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25452,7 +25455,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25658,7 +25661,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25945,7 +25948,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ119">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR119">
         <v>0.96</v>
@@ -26276,7 +26279,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26560,7 +26563,7 @@
         <v>2.2</v>
       </c>
       <c r="AP122">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ122">
         <v>1.85</v>
@@ -26688,7 +26691,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26894,7 +26897,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27100,7 +27103,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27306,7 +27309,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27924,7 +27927,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -28826,7 +28829,7 @@
         <v>1.5</v>
       </c>
       <c r="AP133">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ133">
         <v>1</v>
@@ -29160,7 +29163,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29366,7 +29369,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29653,7 +29656,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ137">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR137">
         <v>1.24</v>
@@ -29778,7 +29781,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29984,7 +29987,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30808,7 +30811,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -31014,7 +31017,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31426,7 +31429,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31632,7 +31635,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31919,7 +31922,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ148">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR148">
         <v>1.5</v>
@@ -32044,7 +32047,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32456,7 +32459,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32662,7 +32665,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32868,7 +32871,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -33280,7 +33283,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -33976,7 +33979,7 @@
         <v>1.5</v>
       </c>
       <c r="AP158">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ158">
         <v>1.15</v>
@@ -34104,7 +34107,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34516,7 +34519,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34722,7 +34725,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34928,7 +34931,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35009,7 +35012,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ163">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR163">
         <v>1.36</v>
@@ -35340,7 +35343,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35546,7 +35549,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35752,7 +35755,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35958,7 +35961,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36576,7 +36579,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36782,7 +36785,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36988,7 +36991,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37194,7 +37197,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37606,7 +37609,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -37890,7 +37893,7 @@
         <v>0.5</v>
       </c>
       <c r="AP177">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ177">
         <v>1.15</v>
@@ -38224,7 +38227,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38430,7 +38433,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38636,7 +38639,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39048,7 +39051,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39747,7 +39750,7 @@
         <v>2</v>
       </c>
       <c r="AQ186">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR186">
         <v>1.62</v>
@@ -39872,7 +39875,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40284,7 +40287,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40696,7 +40699,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -40774,7 +40777,7 @@
         <v>0.89</v>
       </c>
       <c r="AP191">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ191">
         <v>0.77</v>
@@ -41314,7 +41317,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41932,7 +41935,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42344,7 +42347,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42550,7 +42553,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42756,7 +42759,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -43168,7 +43171,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43580,7 +43583,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43992,7 +43995,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44073,7 +44076,7 @@
         <v>1</v>
       </c>
       <c r="AQ207">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR207">
         <v>1.12</v>
@@ -44198,7 +44201,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>360</v>
+        <v>258</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -45434,7 +45437,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45512,7 +45515,7 @@
         <v>0.8</v>
       </c>
       <c r="AP214">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ214">
         <v>0.62</v>
@@ -46258,7 +46261,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -47288,7 +47291,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47700,7 +47703,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47906,7 +47909,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -48190,7 +48193,7 @@
         <v>2.6</v>
       </c>
       <c r="AP227">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ227">
         <v>2</v>
@@ -48605,7 +48608,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ229">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR229">
         <v>1.45</v>
@@ -49554,7 +49557,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -50172,7 +50175,7 @@
         <v>241</v>
       </c>
       <c r="P237" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q237">
         <v>1.91</v>
@@ -50584,7 +50587,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -51692,7 +51695,7 @@
         <v>1.08</v>
       </c>
       <c r="AP244">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ244">
         <v>1</v>
@@ -52438,7 +52441,7 @@
         <v>92</v>
       </c>
       <c r="P248" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q248">
         <v>4</v>
@@ -53056,7 +53059,7 @@
         <v>92</v>
       </c>
       <c r="P251" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q251">
         <v>3.6</v>
@@ -53549,7 +53552,7 @@
         <v>1</v>
       </c>
       <c r="AQ253">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR253">
         <v>1.35</v>
@@ -54086,7 +54089,7 @@
         <v>250</v>
       </c>
       <c r="P256" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q256">
         <v>4</v>
@@ -56857,31 +56860,31 @@
         <v>2.94</v>
       </c>
       <c r="AU269">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AV269">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW269">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AX269">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AY269">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AZ269">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="BA269">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BB269">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC269">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BD269">
         <v>1.55</v>
@@ -56921,6 +56924,212 @@
       </c>
       <c r="BP269">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="270" spans="1:68">
+      <c r="A270" s="1">
+        <v>269</v>
+      </c>
+      <c r="B270">
+        <v>7492413</v>
+      </c>
+      <c r="C270" t="s">
+        <v>68</v>
+      </c>
+      <c r="D270" t="s">
+        <v>69</v>
+      </c>
+      <c r="E270" s="2">
+        <v>45718.69791666666</v>
+      </c>
+      <c r="F270">
+        <v>27</v>
+      </c>
+      <c r="G270" t="s">
+        <v>73</v>
+      </c>
+      <c r="H270" t="s">
+        <v>77</v>
+      </c>
+      <c r="I270">
+        <v>0</v>
+      </c>
+      <c r="J270">
+        <v>1</v>
+      </c>
+      <c r="K270">
+        <v>1</v>
+      </c>
+      <c r="L270">
+        <v>1</v>
+      </c>
+      <c r="M270">
+        <v>2</v>
+      </c>
+      <c r="N270">
+        <v>3</v>
+      </c>
+      <c r="O270" t="s">
+        <v>258</v>
+      </c>
+      <c r="P270" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q270">
+        <v>2.63</v>
+      </c>
+      <c r="R270">
+        <v>2.25</v>
+      </c>
+      <c r="S270">
+        <v>4</v>
+      </c>
+      <c r="T270">
+        <v>1.36</v>
+      </c>
+      <c r="U270">
+        <v>3</v>
+      </c>
+      <c r="V270">
+        <v>2.63</v>
+      </c>
+      <c r="W270">
+        <v>1.44</v>
+      </c>
+      <c r="X270">
+        <v>7</v>
+      </c>
+      <c r="Y270">
+        <v>1.1</v>
+      </c>
+      <c r="Z270">
+        <v>2.05</v>
+      </c>
+      <c r="AA270">
+        <v>3.8</v>
+      </c>
+      <c r="AB270">
+        <v>3.53</v>
+      </c>
+      <c r="AC270">
+        <v>1.04</v>
+      </c>
+      <c r="AD270">
+        <v>13</v>
+      </c>
+      <c r="AE270">
+        <v>1.26</v>
+      </c>
+      <c r="AF270">
+        <v>4</v>
+      </c>
+      <c r="AG270">
+        <v>1.84</v>
+      </c>
+      <c r="AH270">
+        <v>1.97</v>
+      </c>
+      <c r="AI270">
+        <v>1.7</v>
+      </c>
+      <c r="AJ270">
+        <v>2.05</v>
+      </c>
+      <c r="AK270">
+        <v>1.3</v>
+      </c>
+      <c r="AL270">
+        <v>1.28</v>
+      </c>
+      <c r="AM270">
+        <v>1.73</v>
+      </c>
+      <c r="AN270">
+        <v>1.85</v>
+      </c>
+      <c r="AO270">
+        <v>1.69</v>
+      </c>
+      <c r="AP270">
+        <v>1.71</v>
+      </c>
+      <c r="AQ270">
+        <v>1.79</v>
+      </c>
+      <c r="AR270">
+        <v>1.71</v>
+      </c>
+      <c r="AS270">
+        <v>1.55</v>
+      </c>
+      <c r="AT270">
+        <v>3.26</v>
+      </c>
+      <c r="AU270">
+        <v>5</v>
+      </c>
+      <c r="AV270">
+        <v>9</v>
+      </c>
+      <c r="AW270">
+        <v>11</v>
+      </c>
+      <c r="AX270">
+        <v>13</v>
+      </c>
+      <c r="AY270">
+        <v>17</v>
+      </c>
+      <c r="AZ270">
+        <v>23</v>
+      </c>
+      <c r="BA270">
+        <v>3</v>
+      </c>
+      <c r="BB270">
+        <v>5</v>
+      </c>
+      <c r="BC270">
+        <v>8</v>
+      </c>
+      <c r="BD270">
+        <v>1.69</v>
+      </c>
+      <c r="BE270">
+        <v>9</v>
+      </c>
+      <c r="BF270">
+        <v>2.6</v>
+      </c>
+      <c r="BG270">
+        <v>1.16</v>
+      </c>
+      <c r="BH270">
+        <v>4.1</v>
+      </c>
+      <c r="BI270">
+        <v>1.34</v>
+      </c>
+      <c r="BJ270">
+        <v>2.78</v>
+      </c>
+      <c r="BK270">
+        <v>1.62</v>
+      </c>
+      <c r="BL270">
+        <v>2.1</v>
+      </c>
+      <c r="BM270">
+        <v>2.04</v>
+      </c>
+      <c r="BN270">
+        <v>1.69</v>
+      </c>
+      <c r="BO270">
+        <v>2.67</v>
+      </c>
+      <c r="BP270">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -56654,7 +56654,7 @@
         <v>2.4</v>
       </c>
       <c r="AU268">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV268">
         <v>2</v>
@@ -56663,13 +56663,13 @@
         <v>3</v>
       </c>
       <c r="AX268">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY268">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ268">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA268">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="379">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -790,7 +790,7 @@
     <t>['61', '76']</t>
   </si>
   <si>
-    <t>['84']</t>
+    <t>['72', '90']</t>
   </si>
   <si>
     <t>['30', '82']</t>
@@ -1097,6 +1097,9 @@
   </si>
   <si>
     <t>['2', '21', '58']</t>
+  </si>
+  <si>
+    <t>['84']</t>
   </si>
   <si>
     <t>['56', '70']</t>
@@ -1509,7 +1512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP270"/>
+  <dimension ref="A1:BP271"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3697,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
         <v>0.71</v>
@@ -7408,7 +7411,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ29">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR29">
         <v>1.56</v>
@@ -7611,7 +7614,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
         <v>1.15</v>
@@ -9880,7 +9883,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ41">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR41">
         <v>1.35</v>
@@ -10701,7 +10704,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ45">
         <v>2</v>
@@ -13176,7 +13179,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ57">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR57">
         <v>1.29</v>
@@ -15233,7 +15236,7 @@
         <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ67">
         <v>0.77</v>
@@ -16881,7 +16884,7 @@
         <v>1</v>
       </c>
       <c r="AP75">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ75">
         <v>1.79</v>
@@ -18944,7 +18947,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ85">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR85">
         <v>1.74</v>
@@ -20386,7 +20389,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ92">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR92">
         <v>1.25</v>
@@ -21413,7 +21416,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ97">
         <v>0.62</v>
@@ -25121,7 +25124,7 @@
         <v>1.17</v>
       </c>
       <c r="AP115">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ115">
         <v>1.21</v>
@@ -25742,7 +25745,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ118">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR118">
         <v>1.7</v>
@@ -28420,7 +28423,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ131">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR131">
         <v>1.36</v>
@@ -30889,7 +30892,7 @@
         <v>1.57</v>
       </c>
       <c r="AP143">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ143">
         <v>1.38</v>
@@ -32949,7 +32952,7 @@
         <v>0.25</v>
       </c>
       <c r="AP153">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ153">
         <v>0.36</v>
@@ -33364,7 +33367,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ155">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR155">
         <v>1.24</v>
@@ -37687,7 +37690,7 @@
         <v>1.75</v>
       </c>
       <c r="AP176">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ176">
         <v>1.38</v>
@@ -38308,7 +38311,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ179">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR179">
         <v>1.61</v>
@@ -41604,7 +41607,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ195">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR195">
         <v>1.59</v>
@@ -43043,7 +43046,7 @@
         <v>1.56</v>
       </c>
       <c r="AP202">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ202">
         <v>1.31</v>
@@ -44201,7 +44204,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>258</v>
+        <v>361</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44819,7 +44822,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45643,7 +45646,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45849,7 +45852,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -46055,7 +46058,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46342,7 +46345,7 @@
         <v>1</v>
       </c>
       <c r="AQ218">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR218">
         <v>1.35</v>
@@ -46673,7 +46676,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46879,7 +46882,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47166,7 +47169,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ222">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR222">
         <v>1.17</v>
@@ -47781,7 +47784,7 @@
         <v>1.18</v>
       </c>
       <c r="AP225">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ225">
         <v>1</v>
@@ -48321,7 +48324,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48527,7 +48530,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48939,7 +48942,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49145,7 +49148,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49351,7 +49354,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -50999,7 +51002,7 @@
         <v>244</v>
       </c>
       <c r="P241" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q241">
         <v>2.5</v>
@@ -51411,7 +51414,7 @@
         <v>245</v>
       </c>
       <c r="P243" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q243">
         <v>3.4</v>
@@ -51698,7 +51701,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ244">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR244">
         <v>1.7</v>
@@ -51823,7 +51826,7 @@
         <v>92</v>
       </c>
       <c r="P245" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q245">
         <v>2.6</v>
@@ -52725,7 +52728,7 @@
         <v>2.25</v>
       </c>
       <c r="AP249">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ249">
         <v>2</v>
@@ -54501,7 +54504,7 @@
         <v>92</v>
       </c>
       <c r="P258" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q258">
         <v>6</v>
@@ -54707,7 +54710,7 @@
         <v>92</v>
       </c>
       <c r="P259" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q259">
         <v>4.75</v>
@@ -56149,7 +56152,7 @@
         <v>92</v>
       </c>
       <c r="P266" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q266">
         <v>4.75</v>
@@ -56970,10 +56973,10 @@
         <v>3</v>
       </c>
       <c r="O270" t="s">
-        <v>258</v>
+        <v>146</v>
       </c>
       <c r="P270" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q270">
         <v>2.63</v>
@@ -57130,6 +57133,212 @@
       </c>
       <c r="BP270">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="271" spans="1:68">
+      <c r="A271" s="1">
+        <v>270</v>
+      </c>
+      <c r="B271">
+        <v>7492412</v>
+      </c>
+      <c r="C271" t="s">
+        <v>68</v>
+      </c>
+      <c r="D271" t="s">
+        <v>69</v>
+      </c>
+      <c r="E271" s="2">
+        <v>45719.69791666666</v>
+      </c>
+      <c r="F271">
+        <v>27</v>
+      </c>
+      <c r="G271" t="s">
+        <v>79</v>
+      </c>
+      <c r="H271" t="s">
+        <v>75</v>
+      </c>
+      <c r="I271">
+        <v>0</v>
+      </c>
+      <c r="J271">
+        <v>0</v>
+      </c>
+      <c r="K271">
+        <v>0</v>
+      </c>
+      <c r="L271">
+        <v>2</v>
+      </c>
+      <c r="M271">
+        <v>0</v>
+      </c>
+      <c r="N271">
+        <v>2</v>
+      </c>
+      <c r="O271" t="s">
+        <v>258</v>
+      </c>
+      <c r="P271" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q271">
+        <v>1.8</v>
+      </c>
+      <c r="R271">
+        <v>2.5</v>
+      </c>
+      <c r="S271">
+        <v>9.5</v>
+      </c>
+      <c r="T271">
+        <v>1.33</v>
+      </c>
+      <c r="U271">
+        <v>3.25</v>
+      </c>
+      <c r="V271">
+        <v>2.63</v>
+      </c>
+      <c r="W271">
+        <v>1.44</v>
+      </c>
+      <c r="X271">
+        <v>7</v>
+      </c>
+      <c r="Y271">
+        <v>1.1</v>
+      </c>
+      <c r="Z271">
+        <v>1.33</v>
+      </c>
+      <c r="AA271">
+        <v>5.4</v>
+      </c>
+      <c r="AB271">
+        <v>10</v>
+      </c>
+      <c r="AC271">
+        <v>1.03</v>
+      </c>
+      <c r="AD271">
+        <v>15</v>
+      </c>
+      <c r="AE271">
+        <v>1.25</v>
+      </c>
+      <c r="AF271">
+        <v>4</v>
+      </c>
+      <c r="AG271">
+        <v>1.82</v>
+      </c>
+      <c r="AH271">
+        <v>2</v>
+      </c>
+      <c r="AI271">
+        <v>2.25</v>
+      </c>
+      <c r="AJ271">
+        <v>1.57</v>
+      </c>
+      <c r="AK271">
+        <v>1.02</v>
+      </c>
+      <c r="AL271">
+        <v>1.12</v>
+      </c>
+      <c r="AM271">
+        <v>3.6</v>
+      </c>
+      <c r="AN271">
+        <v>1.92</v>
+      </c>
+      <c r="AO271">
+        <v>1</v>
+      </c>
+      <c r="AP271">
+        <v>2</v>
+      </c>
+      <c r="AQ271">
+        <v>0.93</v>
+      </c>
+      <c r="AR271">
+        <v>1.6</v>
+      </c>
+      <c r="AS271">
+        <v>1.08</v>
+      </c>
+      <c r="AT271">
+        <v>2.68</v>
+      </c>
+      <c r="AU271">
+        <v>10</v>
+      </c>
+      <c r="AV271">
+        <v>3</v>
+      </c>
+      <c r="AW271">
+        <v>18</v>
+      </c>
+      <c r="AX271">
+        <v>3</v>
+      </c>
+      <c r="AY271">
+        <v>35</v>
+      </c>
+      <c r="AZ271">
+        <v>8</v>
+      </c>
+      <c r="BA271">
+        <v>6</v>
+      </c>
+      <c r="BB271">
+        <v>0</v>
+      </c>
+      <c r="BC271">
+        <v>6</v>
+      </c>
+      <c r="BD271">
+        <v>1.2</v>
+      </c>
+      <c r="BE271">
+        <v>9</v>
+      </c>
+      <c r="BF271">
+        <v>4.9</v>
+      </c>
+      <c r="BG271">
+        <v>1.27</v>
+      </c>
+      <c r="BH271">
+        <v>3.3</v>
+      </c>
+      <c r="BI271">
+        <v>1.48</v>
+      </c>
+      <c r="BJ271">
+        <v>2.43</v>
+      </c>
+      <c r="BK271">
+        <v>1.76</v>
+      </c>
+      <c r="BL271">
+        <v>1.93</v>
+      </c>
+      <c r="BM271">
+        <v>2.18</v>
+      </c>
+      <c r="BN271">
+        <v>1.58</v>
+      </c>
+      <c r="BO271">
+        <v>2.8</v>
+      </c>
+      <c r="BP271">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="385">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -793,6 +793,18 @@
     <t>['72', '90']</t>
   </si>
   <si>
+    <t>['18']</t>
+  </si>
+  <si>
+    <t>['60', '82']</t>
+  </si>
+  <si>
+    <t>['7', '59']</t>
+  </si>
+  <si>
+    <t>['45+1', '64', '77']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -979,9 +991,6 @@
     <t>['25', '66', '77']</t>
   </si>
   <si>
-    <t>['18']</t>
-  </si>
-  <si>
     <t>['17', '22', '25', '31', '41']</t>
   </si>
   <si>
@@ -1151,6 +1160,15 @@
   </si>
   <si>
     <t>['28', '90+8']</t>
+  </si>
+  <si>
+    <t>['19', '72']</t>
+  </si>
+  <si>
+    <t>['68', '73', '81']</t>
+  </si>
+  <si>
+    <t>['32', '44']</t>
   </si>
 </sst>
 </file>
@@ -1512,7 +1530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP271"/>
+  <dimension ref="A1:BP276"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1768,7 +1786,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2261,7 +2279,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ4">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2386,7 +2404,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2467,7 +2485,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ5">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2592,7 +2610,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -3210,7 +3228,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3291,7 +3309,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ9">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3416,7 +3434,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3494,7 +3512,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ10">
         <v>2.14</v>
@@ -4034,7 +4052,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4115,7 +4133,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ13">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR13">
         <v>1.45</v>
@@ -4240,7 +4258,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4321,7 +4339,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ14">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4524,7 +4542,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ15">
         <v>0.79</v>
@@ -4733,7 +4751,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ16">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5270,7 +5288,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5682,7 +5700,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5888,7 +5906,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5969,7 +5987,7 @@
         <v>1</v>
       </c>
       <c r="AQ22">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6172,7 +6190,7 @@
         <v>1.5</v>
       </c>
       <c r="AP23">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ23">
         <v>2.14</v>
@@ -6300,7 +6318,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6584,7 +6602,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ25">
         <v>0.77</v>
@@ -6712,7 +6730,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6793,7 +6811,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ26">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR26">
         <v>1.67</v>
@@ -6918,7 +6936,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7124,7 +7142,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7205,7 +7223,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ28">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR28">
         <v>1.74</v>
@@ -7330,7 +7348,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7948,7 +7966,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8026,7 +8044,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ32">
         <v>1.38</v>
@@ -8441,7 +8459,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ34">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR34">
         <v>2.22</v>
@@ -8772,7 +8790,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -9184,7 +9202,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9390,7 +9408,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9596,7 +9614,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9802,7 +9820,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -10008,7 +10026,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10214,7 +10232,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10295,7 +10313,7 @@
         <v>1</v>
       </c>
       <c r="AQ43">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR43">
         <v>0.93</v>
@@ -10501,7 +10519,7 @@
         <v>1</v>
       </c>
       <c r="AQ44">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR44">
         <v>1.37</v>
@@ -10832,7 +10850,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10910,7 +10928,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ46">
         <v>0.62</v>
@@ -11038,7 +11056,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11244,7 +11262,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11656,7 +11674,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11734,10 +11752,10 @@
         <v>0.5</v>
       </c>
       <c r="AP50">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ50">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR50">
         <v>1.2</v>
@@ -11862,7 +11880,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12274,7 +12292,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12480,7 +12498,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12686,7 +12704,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12892,7 +12910,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13098,7 +13116,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13176,7 +13194,7 @@
         <v>1.5</v>
       </c>
       <c r="AP57">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ57">
         <v>0.93</v>
@@ -13385,7 +13403,7 @@
         <v>2</v>
       </c>
       <c r="AQ58">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR58">
         <v>2.07</v>
@@ -13797,7 +13815,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ60">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR60">
         <v>1.84</v>
@@ -13922,7 +13940,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14415,7 +14433,7 @@
         <v>1</v>
       </c>
       <c r="AQ63">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR63">
         <v>0.9</v>
@@ -14746,7 +14764,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14827,7 +14845,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ65">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR65">
         <v>1.65</v>
@@ -14952,7 +14970,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15030,10 +15048,10 @@
         <v>2.33</v>
       </c>
       <c r="AP66">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ66">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR66">
         <v>1.21</v>
@@ -15158,7 +15176,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15776,7 +15794,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -16063,7 +16081,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ71">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR71">
         <v>1.68</v>
@@ -16266,7 +16284,7 @@
         <v>0.67</v>
       </c>
       <c r="AP72">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ72">
         <v>0.62</v>
@@ -16394,7 +16412,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -17012,7 +17030,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17218,7 +17236,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17296,7 +17314,7 @@
         <v>0.67</v>
       </c>
       <c r="AP77">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ77">
         <v>1.38</v>
@@ -17424,7 +17442,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17630,7 +17648,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17711,7 +17729,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ79">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR79">
         <v>1.44</v>
@@ -18042,7 +18060,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18123,7 +18141,7 @@
         <v>1</v>
       </c>
       <c r="AQ81">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR81">
         <v>1.08</v>
@@ -18866,7 +18884,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19359,7 +19377,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ87">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR87">
         <v>1.49</v>
@@ -19484,7 +19502,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19565,7 +19583,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ88">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR88">
         <v>0.85</v>
@@ -19690,7 +19708,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19768,7 +19786,7 @@
         <v>2.33</v>
       </c>
       <c r="AP89">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ89">
         <v>1.85</v>
@@ -19896,7 +19914,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20102,7 +20120,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20386,7 +20404,7 @@
         <v>0.75</v>
       </c>
       <c r="AP92">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ92">
         <v>0.93</v>
@@ -20514,7 +20532,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20720,7 +20738,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20926,7 +20944,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -21213,7 +21231,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ96">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR96">
         <v>1.88</v>
@@ -21338,7 +21356,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21544,7 +21562,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21750,7 +21768,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21828,7 +21846,7 @@
         <v>0.75</v>
       </c>
       <c r="AP99">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ99">
         <v>1.79</v>
@@ -22037,7 +22055,7 @@
         <v>2</v>
       </c>
       <c r="AQ100">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR100">
         <v>1.81</v>
@@ -22368,7 +22386,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22655,7 +22673,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ103">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR103">
         <v>0.9399999999999999</v>
@@ -22780,7 +22798,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22986,7 +23004,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23192,7 +23210,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23476,10 +23494,10 @@
         <v>0.33</v>
       </c>
       <c r="AP107">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ107">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR107">
         <v>1.54</v>
@@ -23891,7 +23909,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ109">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR109">
         <v>1.36</v>
@@ -24016,7 +24034,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24222,7 +24240,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24428,7 +24446,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24506,7 +24524,7 @@
         <v>1.6</v>
       </c>
       <c r="AP112">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ112">
         <v>1</v>
@@ -24634,7 +24652,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24840,7 +24858,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -24921,7 +24939,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ114">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR114">
         <v>1.3</v>
@@ -25127,7 +25145,7 @@
         <v>2</v>
       </c>
       <c r="AQ115">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR115">
         <v>1.54</v>
@@ -25252,7 +25270,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25458,7 +25476,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25664,7 +25682,7 @@
         <v>172</v>
       </c>
       <c r="P118" t="s">
-        <v>321</v>
+        <v>259</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -26154,7 +26172,7 @@
         <v>2</v>
       </c>
       <c r="AP120">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ120">
         <v>2</v>
@@ -26282,7 +26300,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26694,7 +26712,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26900,7 +26918,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27106,7 +27124,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27184,7 +27202,7 @@
         <v>1.83</v>
       </c>
       <c r="AP125">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ125">
         <v>1.38</v>
@@ -27312,7 +27330,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27393,7 +27411,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ126">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR126">
         <v>1.11</v>
@@ -27930,7 +27948,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -28626,10 +28644,10 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ132">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR132">
         <v>1.48</v>
@@ -29041,7 +29059,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ134">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR134">
         <v>1.52</v>
@@ -29166,7 +29184,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29247,7 +29265,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ135">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR135">
         <v>1.11</v>
@@ -29372,7 +29390,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29784,7 +29802,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29862,7 +29880,7 @@
         <v>2</v>
       </c>
       <c r="AP138">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ138">
         <v>1.85</v>
@@ -29990,7 +30008,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30274,7 +30292,7 @@
         <v>1.17</v>
       </c>
       <c r="AP140">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ140">
         <v>0.62</v>
@@ -30483,7 +30501,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ141">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR141">
         <v>1.73</v>
@@ -30689,7 +30707,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ142">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR142">
         <v>1.3</v>
@@ -30814,7 +30832,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -31020,7 +31038,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31432,7 +31450,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31638,7 +31656,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -32050,7 +32068,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32337,7 +32355,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ150">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR150">
         <v>0.84</v>
@@ -32462,7 +32480,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32668,7 +32686,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32874,7 +32892,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -32955,7 +32973,7 @@
         <v>2</v>
       </c>
       <c r="AQ153">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR153">
         <v>1.41</v>
@@ -33158,10 +33176,10 @@
         <v>1</v>
       </c>
       <c r="AP154">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ154">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR154">
         <v>1.38</v>
@@ -33286,7 +33304,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -33776,7 +33794,7 @@
         <v>0.57</v>
       </c>
       <c r="AP157">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ157">
         <v>1.15</v>
@@ -33985,7 +34003,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ158">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR158">
         <v>1.52</v>
@@ -34110,7 +34128,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34397,7 +34415,7 @@
         <v>1</v>
       </c>
       <c r="AQ160">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR160">
         <v>1.12</v>
@@ -34522,7 +34540,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34728,7 +34746,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34934,7 +34952,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35012,7 +35030,7 @@
         <v>1.5</v>
       </c>
       <c r="AP163">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ163">
         <v>1.79</v>
@@ -35346,7 +35364,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35552,7 +35570,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35758,7 +35776,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35964,7 +35982,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36248,7 +36266,7 @@
         <v>0.67</v>
       </c>
       <c r="AP169">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ169">
         <v>0.71</v>
@@ -36457,7 +36475,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ170">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR170">
         <v>1.34</v>
@@ -36582,7 +36600,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36663,7 +36681,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ171">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR171">
         <v>0.88</v>
@@ -36788,7 +36806,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36994,7 +37012,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37200,7 +37218,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37281,7 +37299,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ174">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR174">
         <v>1.03</v>
@@ -37487,7 +37505,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ175">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR175">
         <v>1.48</v>
@@ -37612,7 +37630,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -38102,7 +38120,7 @@
         <v>0.5</v>
       </c>
       <c r="AP178">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ178">
         <v>0.79</v>
@@ -38230,7 +38248,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38436,7 +38454,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38642,7 +38660,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39054,7 +39072,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39338,10 +39356,10 @@
         <v>1.63</v>
       </c>
       <c r="AP184">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ184">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR184">
         <v>1.31</v>
@@ -39878,7 +39896,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40290,7 +40308,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40702,7 +40720,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41320,7 +41338,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41938,7 +41956,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42016,10 +42034,10 @@
         <v>1.38</v>
       </c>
       <c r="AP197">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ197">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR197">
         <v>1.54</v>
@@ -42350,7 +42368,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42428,7 +42446,7 @@
         <v>1.67</v>
       </c>
       <c r="AP199">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ199">
         <v>1.38</v>
@@ -42556,7 +42574,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42637,7 +42655,7 @@
         <v>2</v>
       </c>
       <c r="AQ200">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR200">
         <v>1.55</v>
@@ -42762,7 +42780,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -42843,7 +42861,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ201">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR201">
         <v>1.71</v>
@@ -43049,7 +43067,7 @@
         <v>2</v>
       </c>
       <c r="AQ202">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR202">
         <v>1.44</v>
@@ -43174,7 +43192,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43461,7 +43479,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ204">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR204">
         <v>1.51</v>
@@ -43586,7 +43604,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43873,7 +43891,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ206">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR206">
         <v>1.29</v>
@@ -43998,7 +44016,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44204,7 +44222,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44282,7 +44300,7 @@
         <v>1.3</v>
       </c>
       <c r="AP208">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ208">
         <v>1</v>
@@ -44488,7 +44506,7 @@
         <v>1.2</v>
       </c>
       <c r="AP209">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ209">
         <v>1.23</v>
@@ -44822,7 +44840,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -44900,7 +44918,7 @@
         <v>1.91</v>
       </c>
       <c r="AP211">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ211">
         <v>2.14</v>
@@ -45440,7 +45458,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45646,7 +45664,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45852,7 +45870,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -45930,7 +45948,7 @@
         <v>2.56</v>
       </c>
       <c r="AP216">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ216">
         <v>2</v>
@@ -46058,7 +46076,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46264,7 +46282,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46551,7 +46569,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ219">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR219">
         <v>1.25</v>
@@ -46676,7 +46694,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46882,7 +46900,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -46963,7 +46981,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ221">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR221">
         <v>1.06</v>
@@ -47294,7 +47312,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47375,7 +47393,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ223">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR223">
         <v>1.8</v>
@@ -47706,7 +47724,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47912,7 +47930,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -47993,7 +48011,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ226">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR226">
         <v>1.59</v>
@@ -48324,7 +48342,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48530,7 +48548,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48942,7 +48960,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49020,7 +49038,7 @@
         <v>1.64</v>
       </c>
       <c r="AP231">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ231">
         <v>1.85</v>
@@ -49148,7 +49166,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49354,7 +49372,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49435,7 +49453,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ233">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR233">
         <v>0.99</v>
@@ -49560,7 +49578,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -49641,7 +49659,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ234">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR234">
         <v>1.14</v>
@@ -50178,7 +50196,7 @@
         <v>241</v>
       </c>
       <c r="P237" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q237">
         <v>1.91</v>
@@ -50259,7 +50277,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ237">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR237">
         <v>1.52</v>
@@ -50462,7 +50480,7 @@
         <v>1.55</v>
       </c>
       <c r="AP238">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ238">
         <v>1.38</v>
@@ -50590,7 +50608,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -50874,7 +50892,7 @@
         <v>1.64</v>
       </c>
       <c r="AP240">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ240">
         <v>1.38</v>
@@ -51002,7 +51020,7 @@
         <v>244</v>
       </c>
       <c r="P241" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q241">
         <v>2.5</v>
@@ -51083,7 +51101,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ241">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR241">
         <v>1.74</v>
@@ -51414,7 +51432,7 @@
         <v>245</v>
       </c>
       <c r="P243" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Q243">
         <v>3.4</v>
@@ -51826,7 +51844,7 @@
         <v>92</v>
       </c>
       <c r="P245" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q245">
         <v>2.6</v>
@@ -52444,7 +52462,7 @@
         <v>92</v>
       </c>
       <c r="P248" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q248">
         <v>4</v>
@@ -52937,7 +52955,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ250">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR250">
         <v>1.32</v>
@@ -53062,7 +53080,7 @@
         <v>92</v>
       </c>
       <c r="P251" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q251">
         <v>3.6</v>
@@ -53140,7 +53158,7 @@
         <v>1.08</v>
       </c>
       <c r="AP251">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ251">
         <v>1.23</v>
@@ -53761,7 +53779,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ254">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR254">
         <v>1.15</v>
@@ -53964,10 +53982,10 @@
         <v>1.25</v>
       </c>
       <c r="AP255">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ255">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR255">
         <v>1.71</v>
@@ -54092,7 +54110,7 @@
         <v>250</v>
       </c>
       <c r="P256" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q256">
         <v>4</v>
@@ -54170,7 +54188,7 @@
         <v>2.15</v>
       </c>
       <c r="AP256">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ256">
         <v>2</v>
@@ -54504,7 +54522,7 @@
         <v>92</v>
       </c>
       <c r="P258" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q258">
         <v>6</v>
@@ -54710,7 +54728,7 @@
         <v>92</v>
       </c>
       <c r="P259" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Q259">
         <v>4.75</v>
@@ -54997,7 +55015,7 @@
         <v>2</v>
       </c>
       <c r="AQ260">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR260">
         <v>1.56</v>
@@ -55203,7 +55221,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ261">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR261">
         <v>1.8</v>
@@ -55615,7 +55633,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ263">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR263">
         <v>1.84</v>
@@ -56152,7 +56170,7 @@
         <v>92</v>
       </c>
       <c r="P266" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q266">
         <v>4.75</v>
@@ -56233,7 +56251,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ266">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR266">
         <v>1.18</v>
@@ -56976,7 +56994,7 @@
         <v>146</v>
       </c>
       <c r="P270" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q270">
         <v>2.63</v>
@@ -57339,6 +57357,1036 @@
       </c>
       <c r="BP271">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="272" spans="1:68">
+      <c r="A272" s="1">
+        <v>271</v>
+      </c>
+      <c r="B272">
+        <v>7492418</v>
+      </c>
+      <c r="C272" t="s">
+        <v>68</v>
+      </c>
+      <c r="D272" t="s">
+        <v>69</v>
+      </c>
+      <c r="E272" s="2">
+        <v>45723.69791666666</v>
+      </c>
+      <c r="F272">
+        <v>28</v>
+      </c>
+      <c r="G272" t="s">
+        <v>76</v>
+      </c>
+      <c r="H272" t="s">
+        <v>70</v>
+      </c>
+      <c r="I272">
+        <v>1</v>
+      </c>
+      <c r="J272">
+        <v>0</v>
+      </c>
+      <c r="K272">
+        <v>1</v>
+      </c>
+      <c r="L272">
+        <v>1</v>
+      </c>
+      <c r="M272">
+        <v>1</v>
+      </c>
+      <c r="N272">
+        <v>2</v>
+      </c>
+      <c r="O272" t="s">
+        <v>259</v>
+      </c>
+      <c r="P272" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q272">
+        <v>3.2</v>
+      </c>
+      <c r="R272">
+        <v>1.95</v>
+      </c>
+      <c r="S272">
+        <v>3.75</v>
+      </c>
+      <c r="T272">
+        <v>1.53</v>
+      </c>
+      <c r="U272">
+        <v>2.38</v>
+      </c>
+      <c r="V272">
+        <v>3.5</v>
+      </c>
+      <c r="W272">
+        <v>1.29</v>
+      </c>
+      <c r="X272">
+        <v>11</v>
+      </c>
+      <c r="Y272">
+        <v>1.05</v>
+      </c>
+      <c r="Z272">
+        <v>2.46</v>
+      </c>
+      <c r="AA272">
+        <v>3.13</v>
+      </c>
+      <c r="AB272">
+        <v>3.23</v>
+      </c>
+      <c r="AC272">
+        <v>1.09</v>
+      </c>
+      <c r="AD272">
+        <v>8</v>
+      </c>
+      <c r="AE272">
+        <v>1.44</v>
+      </c>
+      <c r="AF272">
+        <v>2.8</v>
+      </c>
+      <c r="AG272">
+        <v>2</v>
+      </c>
+      <c r="AH272">
+        <v>1.73</v>
+      </c>
+      <c r="AI272">
+        <v>2</v>
+      </c>
+      <c r="AJ272">
+        <v>1.75</v>
+      </c>
+      <c r="AK272">
+        <v>1.37</v>
+      </c>
+      <c r="AL272">
+        <v>1.35</v>
+      </c>
+      <c r="AM272">
+        <v>1.53</v>
+      </c>
+      <c r="AN272">
+        <v>1.07</v>
+      </c>
+      <c r="AO272">
+        <v>1.15</v>
+      </c>
+      <c r="AP272">
+        <v>1.07</v>
+      </c>
+      <c r="AQ272">
+        <v>1.14</v>
+      </c>
+      <c r="AR272">
+        <v>1.46</v>
+      </c>
+      <c r="AS272">
+        <v>1.04</v>
+      </c>
+      <c r="AT272">
+        <v>2.5</v>
+      </c>
+      <c r="AU272">
+        <v>2</v>
+      </c>
+      <c r="AV272">
+        <v>3</v>
+      </c>
+      <c r="AW272">
+        <v>8</v>
+      </c>
+      <c r="AX272">
+        <v>6</v>
+      </c>
+      <c r="AY272">
+        <v>12</v>
+      </c>
+      <c r="AZ272">
+        <v>11</v>
+      </c>
+      <c r="BA272">
+        <v>2</v>
+      </c>
+      <c r="BB272">
+        <v>5</v>
+      </c>
+      <c r="BC272">
+        <v>7</v>
+      </c>
+      <c r="BD272">
+        <v>1.58</v>
+      </c>
+      <c r="BE272">
+        <v>6.75</v>
+      </c>
+      <c r="BF272">
+        <v>2.55</v>
+      </c>
+      <c r="BG272">
+        <v>1.29</v>
+      </c>
+      <c r="BH272">
+        <v>3.2</v>
+      </c>
+      <c r="BI272">
+        <v>1.5</v>
+      </c>
+      <c r="BJ272">
+        <v>2.4</v>
+      </c>
+      <c r="BK272">
+        <v>1.81</v>
+      </c>
+      <c r="BL272">
+        <v>1.88</v>
+      </c>
+      <c r="BM272">
+        <v>2.28</v>
+      </c>
+      <c r="BN272">
+        <v>1.55</v>
+      </c>
+      <c r="BO272">
+        <v>2.9</v>
+      </c>
+      <c r="BP272">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="273" spans="1:68">
+      <c r="A273" s="1">
+        <v>272</v>
+      </c>
+      <c r="B273">
+        <v>7492427</v>
+      </c>
+      <c r="C273" t="s">
+        <v>68</v>
+      </c>
+      <c r="D273" t="s">
+        <v>69</v>
+      </c>
+      <c r="E273" s="2">
+        <v>45724.45833333334</v>
+      </c>
+      <c r="F273">
+        <v>28</v>
+      </c>
+      <c r="G273" t="s">
+        <v>71</v>
+      </c>
+      <c r="H273" t="s">
+        <v>84</v>
+      </c>
+      <c r="I273">
+        <v>0</v>
+      </c>
+      <c r="J273">
+        <v>1</v>
+      </c>
+      <c r="K273">
+        <v>1</v>
+      </c>
+      <c r="L273">
+        <v>2</v>
+      </c>
+      <c r="M273">
+        <v>2</v>
+      </c>
+      <c r="N273">
+        <v>4</v>
+      </c>
+      <c r="O273" t="s">
+        <v>260</v>
+      </c>
+      <c r="P273" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q273">
+        <v>3.5</v>
+      </c>
+      <c r="R273">
+        <v>2.1</v>
+      </c>
+      <c r="S273">
+        <v>3.2</v>
+      </c>
+      <c r="T273">
+        <v>1.44</v>
+      </c>
+      <c r="U273">
+        <v>2.63</v>
+      </c>
+      <c r="V273">
+        <v>3.25</v>
+      </c>
+      <c r="W273">
+        <v>1.33</v>
+      </c>
+      <c r="X273">
+        <v>9</v>
+      </c>
+      <c r="Y273">
+        <v>1.07</v>
+      </c>
+      <c r="Z273">
+        <v>2.71</v>
+      </c>
+      <c r="AA273">
+        <v>3.37</v>
+      </c>
+      <c r="AB273">
+        <v>2.71</v>
+      </c>
+      <c r="AC273">
+        <v>1.06</v>
+      </c>
+      <c r="AD273">
+        <v>9.5</v>
+      </c>
+      <c r="AE273">
+        <v>1.33</v>
+      </c>
+      <c r="AF273">
+        <v>3.4</v>
+      </c>
+      <c r="AG273">
+        <v>2.02</v>
+      </c>
+      <c r="AH273">
+        <v>1.8</v>
+      </c>
+      <c r="AI273">
+        <v>1.8</v>
+      </c>
+      <c r="AJ273">
+        <v>1.95</v>
+      </c>
+      <c r="AK273">
+        <v>1.52</v>
+      </c>
+      <c r="AL273">
+        <v>1.32</v>
+      </c>
+      <c r="AM273">
+        <v>1.41</v>
+      </c>
+      <c r="AN273">
+        <v>1.07</v>
+      </c>
+      <c r="AO273">
+        <v>1.21</v>
+      </c>
+      <c r="AP273">
+        <v>1.07</v>
+      </c>
+      <c r="AQ273">
+        <v>1.2</v>
+      </c>
+      <c r="AR273">
+        <v>1.34</v>
+      </c>
+      <c r="AS273">
+        <v>1.13</v>
+      </c>
+      <c r="AT273">
+        <v>2.47</v>
+      </c>
+      <c r="AU273">
+        <v>5</v>
+      </c>
+      <c r="AV273">
+        <v>3</v>
+      </c>
+      <c r="AW273">
+        <v>9</v>
+      </c>
+      <c r="AX273">
+        <v>4</v>
+      </c>
+      <c r="AY273">
+        <v>14</v>
+      </c>
+      <c r="AZ273">
+        <v>8</v>
+      </c>
+      <c r="BA273">
+        <v>7</v>
+      </c>
+      <c r="BB273">
+        <v>4</v>
+      </c>
+      <c r="BC273">
+        <v>11</v>
+      </c>
+      <c r="BD273">
+        <v>1.9</v>
+      </c>
+      <c r="BE273">
+        <v>6.4</v>
+      </c>
+      <c r="BF273">
+        <v>2.08</v>
+      </c>
+      <c r="BG273">
+        <v>1.27</v>
+      </c>
+      <c r="BH273">
+        <v>3.3</v>
+      </c>
+      <c r="BI273">
+        <v>1.48</v>
+      </c>
+      <c r="BJ273">
+        <v>2.43</v>
+      </c>
+      <c r="BK273">
+        <v>1.79</v>
+      </c>
+      <c r="BL273">
+        <v>1.9</v>
+      </c>
+      <c r="BM273">
+        <v>2.25</v>
+      </c>
+      <c r="BN273">
+        <v>1.55</v>
+      </c>
+      <c r="BO273">
+        <v>2.9</v>
+      </c>
+      <c r="BP273">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="274" spans="1:68">
+      <c r="A274" s="1">
+        <v>273</v>
+      </c>
+      <c r="B274">
+        <v>7492419</v>
+      </c>
+      <c r="C274" t="s">
+        <v>68</v>
+      </c>
+      <c r="D274" t="s">
+        <v>69</v>
+      </c>
+      <c r="E274" s="2">
+        <v>45724.45833333334</v>
+      </c>
+      <c r="F274">
+        <v>28</v>
+      </c>
+      <c r="G274" t="s">
+        <v>88</v>
+      </c>
+      <c r="H274" t="s">
+        <v>87</v>
+      </c>
+      <c r="I274">
+        <v>0</v>
+      </c>
+      <c r="J274">
+        <v>0</v>
+      </c>
+      <c r="K274">
+        <v>0</v>
+      </c>
+      <c r="L274">
+        <v>1</v>
+      </c>
+      <c r="M274">
+        <v>1</v>
+      </c>
+      <c r="N274">
+        <v>2</v>
+      </c>
+      <c r="O274" t="s">
+        <v>173</v>
+      </c>
+      <c r="P274" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q274">
+        <v>2.1</v>
+      </c>
+      <c r="R274">
+        <v>2.25</v>
+      </c>
+      <c r="S274">
+        <v>6</v>
+      </c>
+      <c r="T274">
+        <v>1.4</v>
+      </c>
+      <c r="U274">
+        <v>2.75</v>
+      </c>
+      <c r="V274">
+        <v>3</v>
+      </c>
+      <c r="W274">
+        <v>1.36</v>
+      </c>
+      <c r="X274">
+        <v>8</v>
+      </c>
+      <c r="Y274">
+        <v>1.08</v>
+      </c>
+      <c r="Z274">
+        <v>1.61</v>
+      </c>
+      <c r="AA274">
+        <v>4.1</v>
+      </c>
+      <c r="AB274">
+        <v>5.8</v>
+      </c>
+      <c r="AC274">
+        <v>1.05</v>
+      </c>
+      <c r="AD274">
+        <v>11</v>
+      </c>
+      <c r="AE274">
+        <v>1.3</v>
+      </c>
+      <c r="AF274">
+        <v>3.6</v>
+      </c>
+      <c r="AG274">
+        <v>1.96</v>
+      </c>
+      <c r="AH274">
+        <v>1.85</v>
+      </c>
+      <c r="AI274">
+        <v>1.95</v>
+      </c>
+      <c r="AJ274">
+        <v>1.8</v>
+      </c>
+      <c r="AK274">
+        <v>1.14</v>
+      </c>
+      <c r="AL274">
+        <v>1.24</v>
+      </c>
+      <c r="AM274">
+        <v>2.3</v>
+      </c>
+      <c r="AN274">
+        <v>1.38</v>
+      </c>
+      <c r="AO274">
+        <v>0.36</v>
+      </c>
+      <c r="AP274">
+        <v>1.36</v>
+      </c>
+      <c r="AQ274">
+        <v>0.4</v>
+      </c>
+      <c r="AR274">
+        <v>1.53</v>
+      </c>
+      <c r="AS274">
+        <v>0.96</v>
+      </c>
+      <c r="AT274">
+        <v>2.49</v>
+      </c>
+      <c r="AU274">
+        <v>8</v>
+      </c>
+      <c r="AV274">
+        <v>5</v>
+      </c>
+      <c r="AW274">
+        <v>6</v>
+      </c>
+      <c r="AX274">
+        <v>5</v>
+      </c>
+      <c r="AY274">
+        <v>15</v>
+      </c>
+      <c r="AZ274">
+        <v>13</v>
+      </c>
+      <c r="BA274">
+        <v>3</v>
+      </c>
+      <c r="BB274">
+        <v>5</v>
+      </c>
+      <c r="BC274">
+        <v>8</v>
+      </c>
+      <c r="BD274">
+        <v>1.33</v>
+      </c>
+      <c r="BE274">
+        <v>7</v>
+      </c>
+      <c r="BF274">
+        <v>3.65</v>
+      </c>
+      <c r="BG274">
+        <v>1.3</v>
+      </c>
+      <c r="BH274">
+        <v>3.15</v>
+      </c>
+      <c r="BI274">
+        <v>1.52</v>
+      </c>
+      <c r="BJ274">
+        <v>2.33</v>
+      </c>
+      <c r="BK274">
+        <v>1.84</v>
+      </c>
+      <c r="BL274">
+        <v>1.84</v>
+      </c>
+      <c r="BM274">
+        <v>2.3</v>
+      </c>
+      <c r="BN274">
+        <v>1.54</v>
+      </c>
+      <c r="BO274">
+        <v>2.9</v>
+      </c>
+      <c r="BP274">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="275" spans="1:68">
+      <c r="A275" s="1">
+        <v>274</v>
+      </c>
+      <c r="B275">
+        <v>7492425</v>
+      </c>
+      <c r="C275" t="s">
+        <v>68</v>
+      </c>
+      <c r="D275" t="s">
+        <v>69</v>
+      </c>
+      <c r="E275" s="2">
+        <v>45724.58333333334</v>
+      </c>
+      <c r="F275">
+        <v>28</v>
+      </c>
+      <c r="G275" t="s">
+        <v>78</v>
+      </c>
+      <c r="H275" t="s">
+        <v>73</v>
+      </c>
+      <c r="I275">
+        <v>1</v>
+      </c>
+      <c r="J275">
+        <v>0</v>
+      </c>
+      <c r="K275">
+        <v>1</v>
+      </c>
+      <c r="L275">
+        <v>2</v>
+      </c>
+      <c r="M275">
+        <v>3</v>
+      </c>
+      <c r="N275">
+        <v>5</v>
+      </c>
+      <c r="O275" t="s">
+        <v>261</v>
+      </c>
+      <c r="P275" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q275">
+        <v>5</v>
+      </c>
+      <c r="R275">
+        <v>2.25</v>
+      </c>
+      <c r="S275">
+        <v>2.3</v>
+      </c>
+      <c r="T275">
+        <v>1.36</v>
+      </c>
+      <c r="U275">
+        <v>3</v>
+      </c>
+      <c r="V275">
+        <v>2.75</v>
+      </c>
+      <c r="W275">
+        <v>1.4</v>
+      </c>
+      <c r="X275">
+        <v>7</v>
+      </c>
+      <c r="Y275">
+        <v>1.1</v>
+      </c>
+      <c r="Z275">
+        <v>5.1</v>
+      </c>
+      <c r="AA275">
+        <v>4.1</v>
+      </c>
+      <c r="AB275">
+        <v>1.68</v>
+      </c>
+      <c r="AC275">
+        <v>1.03</v>
+      </c>
+      <c r="AD275">
+        <v>13</v>
+      </c>
+      <c r="AE275">
+        <v>1.24</v>
+      </c>
+      <c r="AF275">
+        <v>4.2</v>
+      </c>
+      <c r="AG275">
+        <v>1.81</v>
+      </c>
+      <c r="AH275">
+        <v>2.01</v>
+      </c>
+      <c r="AI275">
+        <v>1.75</v>
+      </c>
+      <c r="AJ275">
+        <v>2</v>
+      </c>
+      <c r="AK275">
+        <v>2.1</v>
+      </c>
+      <c r="AL275">
+        <v>1.25</v>
+      </c>
+      <c r="AM275">
+        <v>1.18</v>
+      </c>
+      <c r="AN275">
+        <v>1.08</v>
+      </c>
+      <c r="AO275">
+        <v>1.31</v>
+      </c>
+      <c r="AP275">
+        <v>1</v>
+      </c>
+      <c r="AQ275">
+        <v>1.43</v>
+      </c>
+      <c r="AR275">
+        <v>1.29</v>
+      </c>
+      <c r="AS275">
+        <v>1.56</v>
+      </c>
+      <c r="AT275">
+        <v>2.85</v>
+      </c>
+      <c r="AU275">
+        <v>4</v>
+      </c>
+      <c r="AV275">
+        <v>10</v>
+      </c>
+      <c r="AW275">
+        <v>8</v>
+      </c>
+      <c r="AX275">
+        <v>7</v>
+      </c>
+      <c r="AY275">
+        <v>14</v>
+      </c>
+      <c r="AZ275">
+        <v>18</v>
+      </c>
+      <c r="BA275">
+        <v>2</v>
+      </c>
+      <c r="BB275">
+        <v>7</v>
+      </c>
+      <c r="BC275">
+        <v>9</v>
+      </c>
+      <c r="BD275">
+        <v>2.8</v>
+      </c>
+      <c r="BE275">
+        <v>6.75</v>
+      </c>
+      <c r="BF275">
+        <v>1.5</v>
+      </c>
+      <c r="BG275">
+        <v>1.3</v>
+      </c>
+      <c r="BH275">
+        <v>3.15</v>
+      </c>
+      <c r="BI275">
+        <v>1.52</v>
+      </c>
+      <c r="BJ275">
+        <v>2.33</v>
+      </c>
+      <c r="BK275">
+        <v>1.84</v>
+      </c>
+      <c r="BL275">
+        <v>1.84</v>
+      </c>
+      <c r="BM275">
+        <v>2.33</v>
+      </c>
+      <c r="BN275">
+        <v>1.52</v>
+      </c>
+      <c r="BO275">
+        <v>3.05</v>
+      </c>
+      <c r="BP275">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="276" spans="1:68">
+      <c r="A276" s="1">
+        <v>275</v>
+      </c>
+      <c r="B276">
+        <v>7492422</v>
+      </c>
+      <c r="C276" t="s">
+        <v>68</v>
+      </c>
+      <c r="D276" t="s">
+        <v>69</v>
+      </c>
+      <c r="E276" s="2">
+        <v>45724.69791666666</v>
+      </c>
+      <c r="F276">
+        <v>28</v>
+      </c>
+      <c r="G276" t="s">
+        <v>82</v>
+      </c>
+      <c r="H276" t="s">
+        <v>81</v>
+      </c>
+      <c r="I276">
+        <v>1</v>
+      </c>
+      <c r="J276">
+        <v>2</v>
+      </c>
+      <c r="K276">
+        <v>3</v>
+      </c>
+      <c r="L276">
+        <v>3</v>
+      </c>
+      <c r="M276">
+        <v>2</v>
+      </c>
+      <c r="N276">
+        <v>5</v>
+      </c>
+      <c r="O276" t="s">
+        <v>262</v>
+      </c>
+      <c r="P276" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q276">
+        <v>1.5</v>
+      </c>
+      <c r="R276">
+        <v>3</v>
+      </c>
+      <c r="S276">
+        <v>15</v>
+      </c>
+      <c r="T276">
+        <v>1.25</v>
+      </c>
+      <c r="U276">
+        <v>3.75</v>
+      </c>
+      <c r="V276">
+        <v>2.2</v>
+      </c>
+      <c r="W276">
+        <v>1.62</v>
+      </c>
+      <c r="X276">
+        <v>5</v>
+      </c>
+      <c r="Y276">
+        <v>1.17</v>
+      </c>
+      <c r="Z276">
+        <v>1.12</v>
+      </c>
+      <c r="AA276">
+        <v>11</v>
+      </c>
+      <c r="AB276">
+        <v>19</v>
+      </c>
+      <c r="AC276">
+        <v>1.01</v>
+      </c>
+      <c r="AD276">
+        <v>17</v>
+      </c>
+      <c r="AE276">
+        <v>1.15</v>
+      </c>
+      <c r="AF276">
+        <v>5.5</v>
+      </c>
+      <c r="AG276">
+        <v>1.6</v>
+      </c>
+      <c r="AH276">
+        <v>2.25</v>
+      </c>
+      <c r="AI276">
+        <v>2.5</v>
+      </c>
+      <c r="AJ276">
+        <v>1.5</v>
+      </c>
+      <c r="AK276">
+        <v>1.01</v>
+      </c>
+      <c r="AL276">
+        <v>1.07</v>
+      </c>
+      <c r="AM276">
+        <v>5.75</v>
+      </c>
+      <c r="AN276">
+        <v>2.31</v>
+      </c>
+      <c r="AO276">
+        <v>0.54</v>
+      </c>
+      <c r="AP276">
+        <v>2.36</v>
+      </c>
+      <c r="AQ276">
+        <v>0.5</v>
+      </c>
+      <c r="AR276">
+        <v>1.74</v>
+      </c>
+      <c r="AS276">
+        <v>0.84</v>
+      </c>
+      <c r="AT276">
+        <v>2.58</v>
+      </c>
+      <c r="AU276">
+        <v>11</v>
+      </c>
+      <c r="AV276">
+        <v>5</v>
+      </c>
+      <c r="AW276">
+        <v>21</v>
+      </c>
+      <c r="AX276">
+        <v>4</v>
+      </c>
+      <c r="AY276">
+        <v>41</v>
+      </c>
+      <c r="AZ276">
+        <v>11</v>
+      </c>
+      <c r="BA276">
+        <v>13</v>
+      </c>
+      <c r="BB276">
+        <v>1</v>
+      </c>
+      <c r="BC276">
+        <v>14</v>
+      </c>
+      <c r="BD276">
+        <v>1.13</v>
+      </c>
+      <c r="BE276">
+        <v>10</v>
+      </c>
+      <c r="BF276">
+        <v>6.1</v>
+      </c>
+      <c r="BG276">
+        <v>1.32</v>
+      </c>
+      <c r="BH276">
+        <v>3.05</v>
+      </c>
+      <c r="BI276">
+        <v>1.54</v>
+      </c>
+      <c r="BJ276">
+        <v>2.28</v>
+      </c>
+      <c r="BK276">
+        <v>1.88</v>
+      </c>
+      <c r="BL276">
+        <v>1.81</v>
+      </c>
+      <c r="BM276">
+        <v>2.38</v>
+      </c>
+      <c r="BN276">
+        <v>1.5</v>
+      </c>
+      <c r="BO276">
+        <v>3.05</v>
+      </c>
+      <c r="BP276">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -58341,13 +58341,13 @@
         <v>11</v>
       </c>
       <c r="BA276">
+        <v>7</v>
+      </c>
+      <c r="BB276">
+        <v>6</v>
+      </c>
+      <c r="BC276">
         <v>13</v>
-      </c>
-      <c r="BB276">
-        <v>1</v>
-      </c>
-      <c r="BC276">
-        <v>14</v>
       </c>
       <c r="BD276">
         <v>1.13</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="389">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -805,6 +805,9 @@
     <t>['45+1', '64', '77']</t>
   </si>
   <si>
+    <t>['26', '60']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1170,6 +1173,15 @@
   <si>
     <t>['32', '44']</t>
   </si>
+  <si>
+    <t>['40', '78']</t>
+  </si>
+  <si>
+    <t>['1']</t>
+  </si>
+  <si>
+    <t>['29', '46', '66', '77']</t>
+  </si>
 </sst>
 </file>
 
@@ -1530,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP276"/>
+  <dimension ref="A1:BP280"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1786,7 +1798,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2073,7 +2085,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ3">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2276,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ4">
         <v>0.5</v>
@@ -2404,7 +2416,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2610,7 +2622,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2894,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ7">
         <v>2</v>
@@ -3103,7 +3115,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ8">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3228,7 +3240,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3434,7 +3446,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3515,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="AQ10">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3718,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AQ11">
         <v>0.71</v>
@@ -4052,7 +4064,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4258,7 +4270,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4957,7 +4969,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ17">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5160,10 +5172,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ18">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5288,7 +5300,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5700,7 +5712,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5778,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ21">
         <v>1.85</v>
@@ -5906,7 +5918,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6193,7 +6205,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ23">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR23">
         <v>1.3</v>
@@ -6318,7 +6330,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6730,7 +6742,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6936,7 +6948,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7014,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ27">
         <v>0.62</v>
@@ -7142,7 +7154,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7348,7 +7360,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7632,10 +7644,10 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AQ30">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR30">
         <v>1.66</v>
@@ -7966,7 +7978,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8047,7 +8059,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ32">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR32">
         <v>0</v>
@@ -8250,7 +8262,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ33">
         <v>1.85</v>
@@ -8665,7 +8677,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ35">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR35">
         <v>1.23</v>
@@ -8790,7 +8802,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -8871,7 +8883,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ36">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR36">
         <v>0</v>
@@ -9202,7 +9214,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9408,7 +9420,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9614,7 +9626,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9820,7 +9832,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -10026,7 +10038,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10232,7 +10244,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10310,7 +10322,7 @@
         <v>2</v>
       </c>
       <c r="AP43">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ43">
         <v>1.2</v>
@@ -10722,7 +10734,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AQ45">
         <v>2</v>
@@ -10850,7 +10862,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -11056,7 +11068,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11262,7 +11274,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11343,7 +11355,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ48">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR48">
         <v>0.9399999999999999</v>
@@ -11674,7 +11686,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11880,7 +11892,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12292,7 +12304,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12498,7 +12510,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12704,7 +12716,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12785,7 +12797,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ55">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR55">
         <v>1.78</v>
@@ -12910,7 +12922,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13116,7 +13128,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13606,10 +13618,10 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ59">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR59">
         <v>0.91</v>
@@ -13812,7 +13824,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ60">
         <v>0.5</v>
@@ -13940,7 +13952,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14224,7 +14236,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ62">
         <v>0.71</v>
@@ -14430,7 +14442,7 @@
         <v>0.25</v>
       </c>
       <c r="AP63">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ63">
         <v>0.4</v>
@@ -14764,7 +14776,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14970,7 +14982,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15176,7 +15188,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15254,7 +15266,7 @@
         <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AQ67">
         <v>0.77</v>
@@ -15794,7 +15806,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -15875,7 +15887,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ70">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR70">
         <v>0.9399999999999999</v>
@@ -16412,7 +16424,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16493,7 +16505,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ73">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR73">
         <v>1.29</v>
@@ -16902,7 +16914,7 @@
         <v>1</v>
       </c>
       <c r="AP75">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AQ75">
         <v>1.79</v>
@@ -17030,7 +17042,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17108,7 +17120,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ76">
         <v>2</v>
@@ -17236,7 +17248,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17317,7 +17329,7 @@
         <v>1</v>
       </c>
       <c r="AQ77">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR77">
         <v>1.41</v>
@@ -17442,7 +17454,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17523,7 +17535,7 @@
         <v>1</v>
       </c>
       <c r="AQ78">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR78">
         <v>1.31</v>
@@ -17648,7 +17660,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -18060,7 +18072,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18138,7 +18150,7 @@
         <v>0.67</v>
       </c>
       <c r="AP81">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ81">
         <v>0.5</v>
@@ -18756,7 +18768,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ84">
         <v>0.79</v>
@@ -18884,7 +18896,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19502,7 +19514,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19708,7 +19720,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19914,7 +19926,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -19995,7 +20007,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ90">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR90">
         <v>1.56</v>
@@ -20120,7 +20132,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20201,7 +20213,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ91">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR91">
         <v>1.35</v>
@@ -20532,7 +20544,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20738,7 +20750,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20944,7 +20956,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -21022,7 +21034,7 @@
         <v>2</v>
       </c>
       <c r="AP95">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ95">
         <v>2</v>
@@ -21356,7 +21368,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21434,7 +21446,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AQ97">
         <v>0.62</v>
@@ -21562,7 +21574,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21643,7 +21655,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ98">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR98">
         <v>1.23</v>
@@ -21768,7 +21780,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22386,7 +22398,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22798,7 +22810,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22876,10 +22888,10 @@
         <v>1.4</v>
       </c>
       <c r="AP104">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ104">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR104">
         <v>1.61</v>
@@ -23004,7 +23016,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23085,7 +23097,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ105">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR105">
         <v>1.14</v>
@@ -23210,7 +23222,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23288,10 +23300,10 @@
         <v>0.8</v>
       </c>
       <c r="AP106">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ106">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR106">
         <v>1.19</v>
@@ -23700,7 +23712,7 @@
         <v>0.67</v>
       </c>
       <c r="AP108">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ108">
         <v>0.71</v>
@@ -24034,7 +24046,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24240,7 +24252,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24446,7 +24458,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24652,7 +24664,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24858,7 +24870,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25142,7 +25154,7 @@
         <v>1.17</v>
       </c>
       <c r="AP115">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AQ115">
         <v>1.2</v>
@@ -25270,7 +25282,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25476,7 +25488,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25557,7 +25569,7 @@
         <v>2</v>
       </c>
       <c r="AQ117">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR117">
         <v>1.63</v>
@@ -26300,7 +26312,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26378,7 +26390,7 @@
         <v>2.2</v>
       </c>
       <c r="AP121">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ121">
         <v>2</v>
@@ -26712,7 +26724,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26793,7 +26805,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ123">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR123">
         <v>1.29</v>
@@ -26918,7 +26930,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27124,7 +27136,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27205,7 +27217,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ125">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR125">
         <v>1.5</v>
@@ -27330,7 +27342,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27614,10 +27626,10 @@
         <v>0.67</v>
       </c>
       <c r="AP127">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ127">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR127">
         <v>1.54</v>
@@ -27823,7 +27835,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ128">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR128">
         <v>1.58</v>
@@ -27948,7 +27960,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -28026,7 +28038,7 @@
         <v>0.67</v>
       </c>
       <c r="AP129">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ129">
         <v>1.23</v>
@@ -29184,7 +29196,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29390,7 +29402,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29802,7 +29814,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -30008,7 +30020,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30089,7 +30101,7 @@
         <v>2</v>
       </c>
       <c r="AQ139">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR139">
         <v>1.59</v>
@@ -30832,7 +30844,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30910,10 +30922,10 @@
         <v>1.57</v>
       </c>
       <c r="AP143">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AQ143">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR143">
         <v>1.47</v>
@@ -31038,7 +31050,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31450,7 +31462,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31528,7 +31540,7 @@
         <v>1.29</v>
       </c>
       <c r="AP146">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ146">
         <v>1</v>
@@ -31656,7 +31668,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31940,7 +31952,7 @@
         <v>1.29</v>
       </c>
       <c r="AP148">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ148">
         <v>1.79</v>
@@ -32068,7 +32080,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32352,7 +32364,7 @@
         <v>1</v>
       </c>
       <c r="AP150">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ150">
         <v>1.2</v>
@@ -32480,7 +32492,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32561,7 +32573,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ151">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR151">
         <v>1.42</v>
@@ -32686,7 +32698,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32892,7 +32904,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -32970,7 +32982,7 @@
         <v>0.25</v>
       </c>
       <c r="AP153">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AQ153">
         <v>0.4</v>
@@ -33304,7 +33316,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -33591,7 +33603,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ156">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR156">
         <v>1.61</v>
@@ -33797,7 +33809,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ157">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR157">
         <v>1.44</v>
@@ -34128,7 +34140,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34412,7 +34424,7 @@
         <v>1.14</v>
       </c>
       <c r="AP160">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ160">
         <v>1.43</v>
@@ -34540,7 +34552,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34621,7 +34633,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ161">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR161">
         <v>1.07</v>
@@ -34746,7 +34758,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34952,7 +34964,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35364,7 +35376,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35570,7 +35582,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35776,7 +35788,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35982,7 +35994,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36600,7 +36612,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36678,7 +36690,7 @@
         <v>1.43</v>
       </c>
       <c r="AP171">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ171">
         <v>1.14</v>
@@ -36806,7 +36818,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -37012,7 +37024,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37093,7 +37105,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ173">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR173">
         <v>1.48</v>
@@ -37218,7 +37230,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37502,7 +37514,7 @@
         <v>0.33</v>
       </c>
       <c r="AP175">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ175">
         <v>0.4</v>
@@ -37630,7 +37642,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -37708,10 +37720,10 @@
         <v>1.75</v>
       </c>
       <c r="AP176">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AQ176">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR176">
         <v>1.42</v>
@@ -37917,7 +37929,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ177">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR177">
         <v>1.56</v>
@@ -38248,7 +38260,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38454,7 +38466,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38660,7 +38672,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38944,7 +38956,7 @@
         <v>1.22</v>
       </c>
       <c r="AP182">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ182">
         <v>1.23</v>
@@ -39072,7 +39084,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39896,7 +39908,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40183,7 +40195,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ188">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR188">
         <v>1.04</v>
@@ -40308,7 +40320,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40386,7 +40398,7 @@
         <v>0.44</v>
       </c>
       <c r="AP189">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ189">
         <v>0.79</v>
@@ -40720,7 +40732,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41338,7 +41350,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41419,7 +41431,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ194">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR194">
         <v>1.66</v>
@@ -41622,7 +41634,7 @@
         <v>1</v>
       </c>
       <c r="AP195">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ195">
         <v>0.93</v>
@@ -41831,7 +41843,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ196">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR196">
         <v>1.17</v>
@@ -41956,7 +41968,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42368,7 +42380,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42449,7 +42461,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ199">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR199">
         <v>1.57</v>
@@ -42574,7 +42586,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42780,7 +42792,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -43064,7 +43076,7 @@
         <v>1.56</v>
       </c>
       <c r="AP202">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AQ202">
         <v>1.43</v>
@@ -43192,7 +43204,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43604,7 +43616,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -44016,7 +44028,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44094,7 +44106,7 @@
         <v>1.5</v>
       </c>
       <c r="AP207">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ207">
         <v>1.79</v>
@@ -44222,7 +44234,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44840,7 +44852,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -44921,7 +44933,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ211">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR211">
         <v>1.53</v>
@@ -45124,7 +45136,7 @@
         <v>1.8</v>
       </c>
       <c r="AP212">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ212">
         <v>1.85</v>
@@ -45330,10 +45342,10 @@
         <v>1.6</v>
       </c>
       <c r="AP213">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ213">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR213">
         <v>1.04</v>
@@ -45458,7 +45470,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45664,7 +45676,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45745,7 +45757,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ215">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR215">
         <v>1.04</v>
@@ -45870,7 +45882,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -46076,7 +46088,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46157,7 +46169,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ217">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR217">
         <v>1.44</v>
@@ -46282,7 +46294,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46694,7 +46706,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46900,7 +46912,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47312,7 +47324,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47724,7 +47736,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47802,7 +47814,7 @@
         <v>1.18</v>
       </c>
       <c r="AP225">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AQ225">
         <v>1</v>
@@ -47930,7 +47942,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -48342,7 +48354,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48548,7 +48560,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48960,7 +48972,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49166,7 +49178,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49244,10 +49256,10 @@
         <v>2</v>
       </c>
       <c r="AP232">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ232">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR232">
         <v>1.18</v>
@@ -49372,7 +49384,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49450,7 +49462,7 @@
         <v>1.4</v>
       </c>
       <c r="AP233">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ233">
         <v>1.43</v>
@@ -49578,7 +49590,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -49865,7 +49877,7 @@
         <v>1</v>
       </c>
       <c r="AQ235">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR235">
         <v>1.34</v>
@@ -50196,7 +50208,7 @@
         <v>241</v>
       </c>
       <c r="P237" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q237">
         <v>1.91</v>
@@ -50483,7 +50495,7 @@
         <v>1</v>
       </c>
       <c r="AQ238">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR238">
         <v>1.34</v>
@@ -50608,7 +50620,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -50686,7 +50698,7 @@
         <v>1.09</v>
       </c>
       <c r="AP239">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ239">
         <v>1.23</v>
@@ -50895,7 +50907,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ240">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR240">
         <v>1.63</v>
@@ -51020,7 +51032,7 @@
         <v>244</v>
       </c>
       <c r="P241" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q241">
         <v>2.5</v>
@@ -51432,7 +51444,7 @@
         <v>245</v>
       </c>
       <c r="P243" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q243">
         <v>3.4</v>
@@ -51844,7 +51856,7 @@
         <v>92</v>
       </c>
       <c r="P245" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q245">
         <v>2.6</v>
@@ -52462,7 +52474,7 @@
         <v>92</v>
       </c>
       <c r="P248" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q248">
         <v>4</v>
@@ -52543,7 +52555,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ248">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR248">
         <v>1.44</v>
@@ -52746,7 +52758,7 @@
         <v>2.25</v>
       </c>
       <c r="AP249">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AQ249">
         <v>2</v>
@@ -53080,7 +53092,7 @@
         <v>92</v>
       </c>
       <c r="P251" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q251">
         <v>3.6</v>
@@ -53367,7 +53379,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ252">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR252">
         <v>1.39</v>
@@ -54110,7 +54122,7 @@
         <v>250</v>
       </c>
       <c r="P256" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q256">
         <v>4</v>
@@ -54394,10 +54406,10 @@
         <v>1.5</v>
       </c>
       <c r="AP257">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ257">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR257">
         <v>1.24</v>
@@ -54522,7 +54534,7 @@
         <v>92</v>
       </c>
       <c r="P258" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q258">
         <v>6</v>
@@ -54600,10 +54612,10 @@
         <v>2.08</v>
       </c>
       <c r="AP258">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ258">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR258">
         <v>0.97</v>
@@ -54728,7 +54740,7 @@
         <v>92</v>
       </c>
       <c r="P259" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q259">
         <v>4.75</v>
@@ -55836,7 +55848,7 @@
         <v>2.08</v>
       </c>
       <c r="AP264">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ264">
         <v>2</v>
@@ -56170,7 +56182,7 @@
         <v>92</v>
       </c>
       <c r="P266" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q266">
         <v>4.75</v>
@@ -56994,7 +57006,7 @@
         <v>146</v>
       </c>
       <c r="P270" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q270">
         <v>2.63</v>
@@ -57278,7 +57290,7 @@
         <v>1</v>
       </c>
       <c r="AP271">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AQ271">
         <v>0.93</v>
@@ -57612,7 +57624,7 @@
         <v>260</v>
       </c>
       <c r="P273" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q273">
         <v>3.5</v>
@@ -58024,7 +58036,7 @@
         <v>261</v>
       </c>
       <c r="P275" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q275">
         <v>5</v>
@@ -58230,7 +58242,7 @@
         <v>262</v>
       </c>
       <c r="P276" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q276">
         <v>1.5</v>
@@ -58341,13 +58353,13 @@
         <v>11</v>
       </c>
       <c r="BA276">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BB276">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BC276">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD276">
         <v>1.13</v>
@@ -58387,6 +58399,830 @@
       </c>
       <c r="BP276">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="277" spans="1:68">
+      <c r="A277" s="1">
+        <v>276</v>
+      </c>
+      <c r="B277">
+        <v>7492421</v>
+      </c>
+      <c r="C277" t="s">
+        <v>68</v>
+      </c>
+      <c r="D277" t="s">
+        <v>69</v>
+      </c>
+      <c r="E277" s="2">
+        <v>45725.35416666666</v>
+      </c>
+      <c r="F277">
+        <v>28</v>
+      </c>
+      <c r="G277" t="s">
+        <v>75</v>
+      </c>
+      <c r="H277" t="s">
+        <v>74</v>
+      </c>
+      <c r="I277">
+        <v>0</v>
+      </c>
+      <c r="J277">
+        <v>1</v>
+      </c>
+      <c r="K277">
+        <v>1</v>
+      </c>
+      <c r="L277">
+        <v>1</v>
+      </c>
+      <c r="M277">
+        <v>2</v>
+      </c>
+      <c r="N277">
+        <v>3</v>
+      </c>
+      <c r="O277" t="s">
+        <v>103</v>
+      </c>
+      <c r="P277" t="s">
+        <v>386</v>
+      </c>
+      <c r="Q277">
+        <v>5.5</v>
+      </c>
+      <c r="R277">
+        <v>2.05</v>
+      </c>
+      <c r="S277">
+        <v>2.5</v>
+      </c>
+      <c r="T277">
+        <v>1.5</v>
+      </c>
+      <c r="U277">
+        <v>2.5</v>
+      </c>
+      <c r="V277">
+        <v>3.4</v>
+      </c>
+      <c r="W277">
+        <v>1.3</v>
+      </c>
+      <c r="X277">
+        <v>10</v>
+      </c>
+      <c r="Y277">
+        <v>1.06</v>
+      </c>
+      <c r="Z277">
+        <v>5</v>
+      </c>
+      <c r="AA277">
+        <v>3.55</v>
+      </c>
+      <c r="AB277">
+        <v>1.81</v>
+      </c>
+      <c r="AC277">
+        <v>1.1</v>
+      </c>
+      <c r="AD277">
+        <v>7.5</v>
+      </c>
+      <c r="AE277">
+        <v>1.44</v>
+      </c>
+      <c r="AF277">
+        <v>2.8</v>
+      </c>
+      <c r="AG277">
+        <v>1.91</v>
+      </c>
+      <c r="AH277">
+        <v>1.8</v>
+      </c>
+      <c r="AI277">
+        <v>2.05</v>
+      </c>
+      <c r="AJ277">
+        <v>1.7</v>
+      </c>
+      <c r="AK277">
+        <v>1.95</v>
+      </c>
+      <c r="AL277">
+        <v>1.3</v>
+      </c>
+      <c r="AM277">
+        <v>1.19</v>
+      </c>
+      <c r="AN277">
+        <v>1</v>
+      </c>
+      <c r="AO277">
+        <v>1.38</v>
+      </c>
+      <c r="AP277">
+        <v>0.93</v>
+      </c>
+      <c r="AQ277">
+        <v>1.5</v>
+      </c>
+      <c r="AR277">
+        <v>1.23</v>
+      </c>
+      <c r="AS277">
+        <v>1.28</v>
+      </c>
+      <c r="AT277">
+        <v>2.51</v>
+      </c>
+      <c r="AU277">
+        <v>3</v>
+      </c>
+      <c r="AV277">
+        <v>7</v>
+      </c>
+      <c r="AW277">
+        <v>5</v>
+      </c>
+      <c r="AX277">
+        <v>6</v>
+      </c>
+      <c r="AY277">
+        <v>9</v>
+      </c>
+      <c r="AZ277">
+        <v>14</v>
+      </c>
+      <c r="BA277">
+        <v>1</v>
+      </c>
+      <c r="BB277">
+        <v>3</v>
+      </c>
+      <c r="BC277">
+        <v>4</v>
+      </c>
+      <c r="BD277">
+        <v>2.8</v>
+      </c>
+      <c r="BE277">
+        <v>6.4</v>
+      </c>
+      <c r="BF277">
+        <v>1.54</v>
+      </c>
+      <c r="BG277">
+        <v>1.44</v>
+      </c>
+      <c r="BH277">
+        <v>2.55</v>
+      </c>
+      <c r="BI277">
+        <v>1.73</v>
+      </c>
+      <c r="BJ277">
+        <v>1.97</v>
+      </c>
+      <c r="BK277">
+        <v>2.18</v>
+      </c>
+      <c r="BL277">
+        <v>1.58</v>
+      </c>
+      <c r="BM277">
+        <v>2.8</v>
+      </c>
+      <c r="BN277">
+        <v>1.36</v>
+      </c>
+      <c r="BO277">
+        <v>3.8</v>
+      </c>
+      <c r="BP277">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="278" spans="1:68">
+      <c r="A278" s="1">
+        <v>277</v>
+      </c>
+      <c r="B278">
+        <v>7492426</v>
+      </c>
+      <c r="C278" t="s">
+        <v>68</v>
+      </c>
+      <c r="D278" t="s">
+        <v>69</v>
+      </c>
+      <c r="E278" s="2">
+        <v>45725.45833333334</v>
+      </c>
+      <c r="F278">
+        <v>28</v>
+      </c>
+      <c r="G278" t="s">
+        <v>85</v>
+      </c>
+      <c r="H278" t="s">
+        <v>83</v>
+      </c>
+      <c r="I278">
+        <v>1</v>
+      </c>
+      <c r="J278">
+        <v>0</v>
+      </c>
+      <c r="K278">
+        <v>1</v>
+      </c>
+      <c r="L278">
+        <v>2</v>
+      </c>
+      <c r="M278">
+        <v>1</v>
+      </c>
+      <c r="N278">
+        <v>3</v>
+      </c>
+      <c r="O278" t="s">
+        <v>263</v>
+      </c>
+      <c r="P278" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q278">
+        <v>2.2</v>
+      </c>
+      <c r="R278">
+        <v>2.2</v>
+      </c>
+      <c r="S278">
+        <v>6</v>
+      </c>
+      <c r="T278">
+        <v>1.44</v>
+      </c>
+      <c r="U278">
+        <v>2.63</v>
+      </c>
+      <c r="V278">
+        <v>3.25</v>
+      </c>
+      <c r="W278">
+        <v>1.33</v>
+      </c>
+      <c r="X278">
+        <v>9</v>
+      </c>
+      <c r="Y278">
+        <v>1.07</v>
+      </c>
+      <c r="Z278">
+        <v>1.72</v>
+      </c>
+      <c r="AA278">
+        <v>3.79</v>
+      </c>
+      <c r="AB278">
+        <v>5.3</v>
+      </c>
+      <c r="AC278">
+        <v>1.06</v>
+      </c>
+      <c r="AD278">
+        <v>10</v>
+      </c>
+      <c r="AE278">
+        <v>1.36</v>
+      </c>
+      <c r="AF278">
+        <v>3.2</v>
+      </c>
+      <c r="AG278">
+        <v>2.1</v>
+      </c>
+      <c r="AH278">
+        <v>1.67</v>
+      </c>
+      <c r="AI278">
+        <v>2.05</v>
+      </c>
+      <c r="AJ278">
+        <v>1.7</v>
+      </c>
+      <c r="AK278">
+        <v>1.15</v>
+      </c>
+      <c r="AL278">
+        <v>1.27</v>
+      </c>
+      <c r="AM278">
+        <v>2.15</v>
+      </c>
+      <c r="AN278">
+        <v>2.23</v>
+      </c>
+      <c r="AO278">
+        <v>1.38</v>
+      </c>
+      <c r="AP278">
+        <v>2.29</v>
+      </c>
+      <c r="AQ278">
+        <v>1.29</v>
+      </c>
+      <c r="AR278">
+        <v>1.64</v>
+      </c>
+      <c r="AS278">
+        <v>1.21</v>
+      </c>
+      <c r="AT278">
+        <v>2.85</v>
+      </c>
+      <c r="AU278">
+        <v>12</v>
+      </c>
+      <c r="AV278">
+        <v>3</v>
+      </c>
+      <c r="AW278">
+        <v>8</v>
+      </c>
+      <c r="AX278">
+        <v>5</v>
+      </c>
+      <c r="AY278">
+        <v>22</v>
+      </c>
+      <c r="AZ278">
+        <v>13</v>
+      </c>
+      <c r="BA278">
+        <v>4</v>
+      </c>
+      <c r="BB278">
+        <v>4</v>
+      </c>
+      <c r="BC278">
+        <v>8</v>
+      </c>
+      <c r="BD278">
+        <v>1.46</v>
+      </c>
+      <c r="BE278">
+        <v>6.5</v>
+      </c>
+      <c r="BF278">
+        <v>3.05</v>
+      </c>
+      <c r="BG278">
+        <v>1.41</v>
+      </c>
+      <c r="BH278">
+        <v>2.65</v>
+      </c>
+      <c r="BI278">
+        <v>1.68</v>
+      </c>
+      <c r="BJ278">
+        <v>2.02</v>
+      </c>
+      <c r="BK278">
+        <v>2.1</v>
+      </c>
+      <c r="BL278">
+        <v>1.64</v>
+      </c>
+      <c r="BM278">
+        <v>2.7</v>
+      </c>
+      <c r="BN278">
+        <v>1.38</v>
+      </c>
+      <c r="BO278">
+        <v>3.55</v>
+      </c>
+      <c r="BP278">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="279" spans="1:68">
+      <c r="A279" s="1">
+        <v>278</v>
+      </c>
+      <c r="B279">
+        <v>7492420</v>
+      </c>
+      <c r="C279" t="s">
+        <v>68</v>
+      </c>
+      <c r="D279" t="s">
+        <v>69</v>
+      </c>
+      <c r="E279" s="2">
+        <v>45725.58333333334</v>
+      </c>
+      <c r="F279">
+        <v>28</v>
+      </c>
+      <c r="G279" t="s">
+        <v>72</v>
+      </c>
+      <c r="H279" t="s">
+        <v>86</v>
+      </c>
+      <c r="I279">
+        <v>0</v>
+      </c>
+      <c r="J279">
+        <v>1</v>
+      </c>
+      <c r="K279">
+        <v>1</v>
+      </c>
+      <c r="L279">
+        <v>0</v>
+      </c>
+      <c r="M279">
+        <v>1</v>
+      </c>
+      <c r="N279">
+        <v>1</v>
+      </c>
+      <c r="O279" t="s">
+        <v>92</v>
+      </c>
+      <c r="P279" t="s">
+        <v>387</v>
+      </c>
+      <c r="Q279">
+        <v>4</v>
+      </c>
+      <c r="R279">
+        <v>2.1</v>
+      </c>
+      <c r="S279">
+        <v>2.75</v>
+      </c>
+      <c r="T279">
+        <v>1.4</v>
+      </c>
+      <c r="U279">
+        <v>2.75</v>
+      </c>
+      <c r="V279">
+        <v>3</v>
+      </c>
+      <c r="W279">
+        <v>1.36</v>
+      </c>
+      <c r="X279">
+        <v>8</v>
+      </c>
+      <c r="Y279">
+        <v>1.08</v>
+      </c>
+      <c r="Z279">
+        <v>4.2</v>
+      </c>
+      <c r="AA279">
+        <v>3.59</v>
+      </c>
+      <c r="AB279">
+        <v>1.93</v>
+      </c>
+      <c r="AC279">
+        <v>1.05</v>
+      </c>
+      <c r="AD279">
+        <v>10</v>
+      </c>
+      <c r="AE279">
+        <v>1.33</v>
+      </c>
+      <c r="AF279">
+        <v>3.4</v>
+      </c>
+      <c r="AG279">
+        <v>1.93</v>
+      </c>
+      <c r="AH279">
+        <v>1.77</v>
+      </c>
+      <c r="AI279">
+        <v>1.8</v>
+      </c>
+      <c r="AJ279">
+        <v>1.95</v>
+      </c>
+      <c r="AK279">
+        <v>1.83</v>
+      </c>
+      <c r="AL279">
+        <v>1.29</v>
+      </c>
+      <c r="AM279">
+        <v>1.24</v>
+      </c>
+      <c r="AN279">
+        <v>0.62</v>
+      </c>
+      <c r="AO279">
+        <v>1.15</v>
+      </c>
+      <c r="AP279">
+        <v>0.57</v>
+      </c>
+      <c r="AQ279">
+        <v>1.29</v>
+      </c>
+      <c r="AR279">
+        <v>0.99</v>
+      </c>
+      <c r="AS279">
+        <v>1.36</v>
+      </c>
+      <c r="AT279">
+        <v>2.35</v>
+      </c>
+      <c r="AU279">
+        <v>2</v>
+      </c>
+      <c r="AV279">
+        <v>8</v>
+      </c>
+      <c r="AW279">
+        <v>2</v>
+      </c>
+      <c r="AX279">
+        <v>9</v>
+      </c>
+      <c r="AY279">
+        <v>5</v>
+      </c>
+      <c r="AZ279">
+        <v>19</v>
+      </c>
+      <c r="BA279">
+        <v>1</v>
+      </c>
+      <c r="BB279">
+        <v>9</v>
+      </c>
+      <c r="BC279">
+        <v>10</v>
+      </c>
+      <c r="BD279">
+        <v>2.48</v>
+      </c>
+      <c r="BE279">
+        <v>6.5</v>
+      </c>
+      <c r="BF279">
+        <v>1.66</v>
+      </c>
+      <c r="BG279">
+        <v>1.3</v>
+      </c>
+      <c r="BH279">
+        <v>3.05</v>
+      </c>
+      <c r="BI279">
+        <v>1.55</v>
+      </c>
+      <c r="BJ279">
+        <v>2.28</v>
+      </c>
+      <c r="BK279">
+        <v>1.9</v>
+      </c>
+      <c r="BL279">
+        <v>1.79</v>
+      </c>
+      <c r="BM279">
+        <v>2.43</v>
+      </c>
+      <c r="BN279">
+        <v>1.48</v>
+      </c>
+      <c r="BO279">
+        <v>3.15</v>
+      </c>
+      <c r="BP279">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="280" spans="1:68">
+      <c r="A280" s="1">
+        <v>279</v>
+      </c>
+      <c r="B280">
+        <v>7492423</v>
+      </c>
+      <c r="C280" t="s">
+        <v>68</v>
+      </c>
+      <c r="D280" t="s">
+        <v>69</v>
+      </c>
+      <c r="E280" s="2">
+        <v>45725.69791666666</v>
+      </c>
+      <c r="F280">
+        <v>28</v>
+      </c>
+      <c r="G280" t="s">
+        <v>79</v>
+      </c>
+      <c r="H280" t="s">
+        <v>89</v>
+      </c>
+      <c r="I280">
+        <v>0</v>
+      </c>
+      <c r="J280">
+        <v>1</v>
+      </c>
+      <c r="K280">
+        <v>1</v>
+      </c>
+      <c r="L280">
+        <v>0</v>
+      </c>
+      <c r="M280">
+        <v>4</v>
+      </c>
+      <c r="N280">
+        <v>4</v>
+      </c>
+      <c r="O280" t="s">
+        <v>92</v>
+      </c>
+      <c r="P280" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q280">
+        <v>3.1</v>
+      </c>
+      <c r="R280">
+        <v>2.1</v>
+      </c>
+      <c r="S280">
+        <v>3.5</v>
+      </c>
+      <c r="T280">
+        <v>1.4</v>
+      </c>
+      <c r="U280">
+        <v>2.75</v>
+      </c>
+      <c r="V280">
+        <v>3</v>
+      </c>
+      <c r="W280">
+        <v>1.36</v>
+      </c>
+      <c r="X280">
+        <v>8</v>
+      </c>
+      <c r="Y280">
+        <v>1.08</v>
+      </c>
+      <c r="Z280">
+        <v>2.48</v>
+      </c>
+      <c r="AA280">
+        <v>3.41</v>
+      </c>
+      <c r="AB280">
+        <v>2.94</v>
+      </c>
+      <c r="AC280">
+        <v>1.06</v>
+      </c>
+      <c r="AD280">
+        <v>10</v>
+      </c>
+      <c r="AE280">
+        <v>1.3</v>
+      </c>
+      <c r="AF280">
+        <v>3.6</v>
+      </c>
+      <c r="AG280">
+        <v>1.95</v>
+      </c>
+      <c r="AH280">
+        <v>1.86</v>
+      </c>
+      <c r="AI280">
+        <v>1.75</v>
+      </c>
+      <c r="AJ280">
+        <v>2</v>
+      </c>
+      <c r="AK280">
+        <v>1.4</v>
+      </c>
+      <c r="AL280">
+        <v>1.3</v>
+      </c>
+      <c r="AM280">
+        <v>1.55</v>
+      </c>
+      <c r="AN280">
+        <v>2</v>
+      </c>
+      <c r="AO280">
+        <v>2.14</v>
+      </c>
+      <c r="AP280">
+        <v>1.87</v>
+      </c>
+      <c r="AQ280">
+        <v>2.2</v>
+      </c>
+      <c r="AR280">
+        <v>1.71</v>
+      </c>
+      <c r="AS280">
+        <v>1.57</v>
+      </c>
+      <c r="AT280">
+        <v>3.28</v>
+      </c>
+      <c r="AU280">
+        <v>3</v>
+      </c>
+      <c r="AV280">
+        <v>10</v>
+      </c>
+      <c r="AW280">
+        <v>7</v>
+      </c>
+      <c r="AX280">
+        <v>10</v>
+      </c>
+      <c r="AY280">
+        <v>15</v>
+      </c>
+      <c r="AZ280">
+        <v>25</v>
+      </c>
+      <c r="BA280">
+        <v>2</v>
+      </c>
+      <c r="BB280">
+        <v>5</v>
+      </c>
+      <c r="BC280">
+        <v>7</v>
+      </c>
+      <c r="BD280">
+        <v>1.89</v>
+      </c>
+      <c r="BE280">
+        <v>6.4</v>
+      </c>
+      <c r="BF280">
+        <v>2.12</v>
+      </c>
+      <c r="BG280">
+        <v>1.41</v>
+      </c>
+      <c r="BH280">
+        <v>2.65</v>
+      </c>
+      <c r="BI280">
+        <v>1.71</v>
+      </c>
+      <c r="BJ280">
+        <v>2</v>
+      </c>
+      <c r="BK280">
+        <v>2.15</v>
+      </c>
+      <c r="BL280">
+        <v>1.61</v>
+      </c>
+      <c r="BM280">
+        <v>2.75</v>
+      </c>
+      <c r="BN280">
+        <v>1.38</v>
+      </c>
+      <c r="BO280">
+        <v>3.7</v>
+      </c>
+      <c r="BP280">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -58356,10 +58356,10 @@
         <v>13</v>
       </c>
       <c r="BB276">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BC276">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="BD276">
         <v>1.13</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="389">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -808,6 +808,9 @@
     <t>['26', '60']</t>
   </si>
   <si>
+    <t>['32']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1076,9 +1079,6 @@
   </si>
   <si>
     <t>['38', '45+2', '88']</t>
-  </si>
-  <si>
-    <t>['32']</t>
   </si>
   <si>
     <t>['29', '54', '68']</t>
@@ -1542,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP280"/>
+  <dimension ref="A1:BP281"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1798,7 +1798,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2416,7 +2416,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2622,7 +2622,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2703,7 +2703,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ6">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ9">
         <v>0.4</v>
@@ -3446,7 +3446,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -4064,7 +4064,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4270,7 +4270,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -5300,7 +5300,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5712,7 +5712,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5918,7 +5918,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6330,7 +6330,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6742,7 +6742,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6820,7 +6820,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ26">
         <v>1.43</v>
@@ -6948,7 +6948,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7154,7 +7154,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7360,7 +7360,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7978,7 +7978,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8802,7 +8802,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -9214,7 +9214,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9420,7 +9420,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9626,7 +9626,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9707,7 +9707,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ40">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR40">
         <v>1.32</v>
@@ -9832,7 +9832,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9910,7 +9910,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ41">
         <v>0.93</v>
@@ -10038,7 +10038,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10244,7 +10244,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10862,7 +10862,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -11068,7 +11068,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11274,7 +11274,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11561,7 +11561,7 @@
         <v>2</v>
       </c>
       <c r="AQ49">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR49">
         <v>2.26</v>
@@ -11686,7 +11686,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11892,7 +11892,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12304,7 +12304,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12510,7 +12510,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12716,7 +12716,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12922,7 +12922,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13128,7 +13128,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13952,7 +13952,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14776,7 +14776,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14982,7 +14982,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15188,7 +15188,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15472,7 +15472,7 @@
         <v>2.33</v>
       </c>
       <c r="AP68">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ68">
         <v>1</v>
@@ -15806,7 +15806,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -16424,7 +16424,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16711,7 +16711,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ74">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR74">
         <v>1.89</v>
@@ -17042,7 +17042,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17248,7 +17248,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17454,7 +17454,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17660,7 +17660,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -18072,7 +18072,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18896,7 +18896,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19386,7 +19386,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ87">
         <v>1.14</v>
@@ -19514,7 +19514,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19720,7 +19720,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19926,7 +19926,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20132,7 +20132,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20544,7 +20544,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20750,7 +20750,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20831,7 +20831,7 @@
         <v>1</v>
       </c>
       <c r="AQ94">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR94">
         <v>1.33</v>
@@ -20956,7 +20956,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -21368,7 +21368,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21574,7 +21574,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21780,7 +21780,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22398,7 +22398,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22810,7 +22810,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -23016,7 +23016,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23222,7 +23222,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -24046,7 +24046,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24124,7 +24124,7 @@
         <v>1</v>
       </c>
       <c r="AP110">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ110">
         <v>0.77</v>
@@ -24252,7 +24252,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24458,7 +24458,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24664,7 +24664,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24870,7 +24870,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25282,7 +25282,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25363,7 +25363,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ116">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR116">
         <v>1.85</v>
@@ -25488,7 +25488,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -26312,7 +26312,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26724,7 +26724,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26930,7 +26930,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27136,7 +27136,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27342,7 +27342,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27832,7 +27832,7 @@
         <v>1.83</v>
       </c>
       <c r="AP128">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ128">
         <v>1.5</v>
@@ -27960,7 +27960,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -28041,7 +28041,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ129">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR129">
         <v>0.88</v>
@@ -29196,7 +29196,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29402,7 +29402,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29814,7 +29814,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -30020,7 +30020,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30844,7 +30844,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -31050,7 +31050,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31462,7 +31462,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31668,7 +31668,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -32080,7 +32080,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32161,7 +32161,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ149">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR149">
         <v>1</v>
@@ -32492,7 +32492,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32698,7 +32698,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32904,7 +32904,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -33316,7 +33316,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -34140,7 +34140,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34218,7 +34218,7 @@
         <v>2.33</v>
       </c>
       <c r="AP159">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ159">
         <v>2</v>
@@ -34552,7 +34552,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34758,7 +34758,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34964,7 +34964,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35376,7 +35376,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35582,7 +35582,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35788,7 +35788,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35994,7 +35994,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36075,7 +36075,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ168">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR168">
         <v>1.6</v>
@@ -36612,7 +36612,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36818,7 +36818,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -37024,7 +37024,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37102,7 +37102,7 @@
         <v>2.11</v>
       </c>
       <c r="AP173">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ173">
         <v>2.2</v>
@@ -37230,7 +37230,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37642,7 +37642,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -38260,7 +38260,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38466,7 +38466,7 @@
         <v>167</v>
       </c>
       <c r="P180" t="s">
-        <v>354</v>
+        <v>264</v>
       </c>
       <c r="Q180">
         <v>3.1</v>
@@ -38959,7 +38959,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ182">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR182">
         <v>1.12</v>
@@ -39908,7 +39908,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39986,7 +39986,7 @@
         <v>0.6</v>
       </c>
       <c r="AP187">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ187">
         <v>0.71</v>
@@ -42586,7 +42586,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -43616,7 +43616,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -44521,7 +44521,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ209">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR209">
         <v>1.52</v>
@@ -45470,7 +45470,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -46166,7 +46166,7 @@
         <v>1.5</v>
       </c>
       <c r="AP217">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ217">
         <v>1.29</v>
@@ -46294,7 +46294,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -47324,7 +47324,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -49590,7 +49590,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -50208,7 +50208,7 @@
         <v>241</v>
       </c>
       <c r="P237" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q237">
         <v>1.91</v>
@@ -50286,7 +50286,7 @@
         <v>0.64</v>
       </c>
       <c r="AP237">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ237">
         <v>0.5</v>
@@ -50620,7 +50620,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -50701,7 +50701,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ239">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR239">
         <v>1.57</v>
@@ -51522,7 +51522,7 @@
         <v>2.25</v>
       </c>
       <c r="AP243">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ243">
         <v>2</v>
@@ -52474,7 +52474,7 @@
         <v>92</v>
       </c>
       <c r="P248" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q248">
         <v>4</v>
@@ -53092,7 +53092,7 @@
         <v>92</v>
       </c>
       <c r="P251" t="s">
-        <v>354</v>
+        <v>264</v>
       </c>
       <c r="Q251">
         <v>3.6</v>
@@ -53173,7 +53173,7 @@
         <v>1</v>
       </c>
       <c r="AQ251">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR251">
         <v>1.3</v>
@@ -54122,7 +54122,7 @@
         <v>250</v>
       </c>
       <c r="P256" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q256">
         <v>4</v>
@@ -58654,7 +58654,7 @@
         <v>263</v>
       </c>
       <c r="P278" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q278">
         <v>2.2</v>
@@ -59223,6 +59223,212 @@
       </c>
       <c r="BP280">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="281" spans="1:68">
+      <c r="A281" s="1">
+        <v>280</v>
+      </c>
+      <c r="B281">
+        <v>7492424</v>
+      </c>
+      <c r="C281" t="s">
+        <v>68</v>
+      </c>
+      <c r="D281" t="s">
+        <v>69</v>
+      </c>
+      <c r="E281" s="2">
+        <v>45726.69791666666</v>
+      </c>
+      <c r="F281">
+        <v>28</v>
+      </c>
+      <c r="G281" t="s">
+        <v>77</v>
+      </c>
+      <c r="H281" t="s">
+        <v>80</v>
+      </c>
+      <c r="I281">
+        <v>1</v>
+      </c>
+      <c r="J281">
+        <v>1</v>
+      </c>
+      <c r="K281">
+        <v>2</v>
+      </c>
+      <c r="L281">
+        <v>1</v>
+      </c>
+      <c r="M281">
+        <v>1</v>
+      </c>
+      <c r="N281">
+        <v>2</v>
+      </c>
+      <c r="O281" t="s">
+        <v>264</v>
+      </c>
+      <c r="P281" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q281">
+        <v>2.3</v>
+      </c>
+      <c r="R281">
+        <v>2.2</v>
+      </c>
+      <c r="S281">
+        <v>5</v>
+      </c>
+      <c r="T281">
+        <v>1.4</v>
+      </c>
+      <c r="U281">
+        <v>2.75</v>
+      </c>
+      <c r="V281">
+        <v>2.75</v>
+      </c>
+      <c r="W281">
+        <v>1.4</v>
+      </c>
+      <c r="X281">
+        <v>8</v>
+      </c>
+      <c r="Y281">
+        <v>1.08</v>
+      </c>
+      <c r="Z281">
+        <v>1.71</v>
+      </c>
+      <c r="AA281">
+        <v>3.84</v>
+      </c>
+      <c r="AB281">
+        <v>5.3</v>
+      </c>
+      <c r="AC281">
+        <v>1.05</v>
+      </c>
+      <c r="AD281">
+        <v>11</v>
+      </c>
+      <c r="AE281">
+        <v>1.3</v>
+      </c>
+      <c r="AF281">
+        <v>3.6</v>
+      </c>
+      <c r="AG281">
+        <v>1.93</v>
+      </c>
+      <c r="AH281">
+        <v>1.88</v>
+      </c>
+      <c r="AI281">
+        <v>1.8</v>
+      </c>
+      <c r="AJ281">
+        <v>1.95</v>
+      </c>
+      <c r="AK281">
+        <v>1.18</v>
+      </c>
+      <c r="AL281">
+        <v>1.26</v>
+      </c>
+      <c r="AM281">
+        <v>2.1</v>
+      </c>
+      <c r="AN281">
+        <v>1.92</v>
+      </c>
+      <c r="AO281">
+        <v>1.23</v>
+      </c>
+      <c r="AP281">
+        <v>1.86</v>
+      </c>
+      <c r="AQ281">
+        <v>1.21</v>
+      </c>
+      <c r="AR281">
+        <v>1.63</v>
+      </c>
+      <c r="AS281">
+        <v>1.36</v>
+      </c>
+      <c r="AT281">
+        <v>2.99</v>
+      </c>
+      <c r="AU281">
+        <v>6</v>
+      </c>
+      <c r="AV281">
+        <v>5</v>
+      </c>
+      <c r="AW281">
+        <v>5</v>
+      </c>
+      <c r="AX281">
+        <v>11</v>
+      </c>
+      <c r="AY281">
+        <v>14</v>
+      </c>
+      <c r="AZ281">
+        <v>20</v>
+      </c>
+      <c r="BA281">
+        <v>4</v>
+      </c>
+      <c r="BB281">
+        <v>9</v>
+      </c>
+      <c r="BC281">
+        <v>13</v>
+      </c>
+      <c r="BD281">
+        <v>1.21</v>
+      </c>
+      <c r="BE281">
+        <v>9.25</v>
+      </c>
+      <c r="BF281">
+        <v>6</v>
+      </c>
+      <c r="BG281">
+        <v>1.2</v>
+      </c>
+      <c r="BH281">
+        <v>3.88</v>
+      </c>
+      <c r="BI281">
+        <v>1.39</v>
+      </c>
+      <c r="BJ281">
+        <v>2.75</v>
+      </c>
+      <c r="BK281">
+        <v>1.88</v>
+      </c>
+      <c r="BL281">
+        <v>1.92</v>
+      </c>
+      <c r="BM281">
+        <v>2.06</v>
+      </c>
+      <c r="BN281">
+        <v>1.71</v>
+      </c>
+      <c r="BO281">
+        <v>2.6</v>
+      </c>
+      <c r="BP281">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -58356,10 +58356,10 @@
         <v>13</v>
       </c>
       <c r="BB276">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BC276">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BD276">
         <v>1.13</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="391">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -811,6 +811,12 @@
     <t>['32']</t>
   </si>
   <si>
+    <t>['16', '45+2']</t>
+  </si>
+  <si>
+    <t>['53', '75']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1542,7 +1548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP281"/>
+  <dimension ref="A1:BP286"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1798,7 +1804,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1876,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ2">
         <v>2</v>
@@ -2416,7 +2422,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2494,7 +2500,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ5">
         <v>1.2</v>
@@ -2622,7 +2628,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -3240,7 +3246,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3446,7 +3452,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3733,7 +3739,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ11">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3936,7 +3942,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AQ12">
         <v>1.79</v>
@@ -4064,7 +4070,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4270,7 +4276,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4348,7 +4354,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AQ14">
         <v>1.14</v>
@@ -4557,7 +4563,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ15">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4966,7 +4972,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ17">
         <v>2.2</v>
@@ -5300,7 +5306,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5381,7 +5387,7 @@
         <v>2</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5587,7 +5593,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ20">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR20">
         <v>1.16</v>
@@ -5712,7 +5718,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5918,7 +5924,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6330,7 +6336,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6411,7 +6417,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ24">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR24">
         <v>2.04</v>
@@ -6742,7 +6748,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6948,7 +6954,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7029,7 +7035,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ27">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR27">
         <v>1.28</v>
@@ -7154,7 +7160,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7360,7 +7366,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7438,10 +7444,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ29">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR29">
         <v>1.56</v>
@@ -7850,10 +7856,10 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AQ31">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR31">
         <v>0.95</v>
@@ -7978,7 +7984,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8468,7 +8474,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ34">
         <v>0.4</v>
@@ -8674,7 +8680,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ35">
         <v>1.29</v>
@@ -8802,7 +8808,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -9086,10 +9092,10 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ37">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR37">
         <v>1.46</v>
@@ -9214,7 +9220,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9420,7 +9426,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9498,7 +9504,7 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AQ39">
         <v>2</v>
@@ -9626,7 +9632,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9832,7 +9838,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9913,7 +9919,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ41">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR41">
         <v>1.35</v>
@@ -10038,7 +10044,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10119,7 +10125,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ42">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR42">
         <v>1.4</v>
@@ -10244,7 +10250,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10862,7 +10868,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10943,7 +10949,7 @@
         <v>1</v>
       </c>
       <c r="AQ46">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR46">
         <v>1.54</v>
@@ -11068,7 +11074,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11274,7 +11280,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11352,7 +11358,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AQ48">
         <v>1.5</v>
@@ -11686,7 +11692,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11892,7 +11898,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -11973,7 +11979,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ51">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR51">
         <v>1.68</v>
@@ -12176,10 +12182,10 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ52">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR52">
         <v>1.92</v>
@@ -12304,7 +12310,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12382,7 +12388,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AQ53">
         <v>2</v>
@@ -12510,7 +12516,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12588,7 +12594,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ54">
         <v>1.85</v>
@@ -12716,7 +12722,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12922,7 +12928,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13000,7 +13006,7 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ56">
         <v>1.79</v>
@@ -13128,7 +13134,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13209,7 +13215,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ57">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR57">
         <v>1.29</v>
@@ -13952,7 +13958,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14239,7 +14245,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ62">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR62">
         <v>1.6</v>
@@ -14648,10 +14654,10 @@
         <v>0.33</v>
       </c>
       <c r="AP64">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AQ64">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR64">
         <v>1.02</v>
@@ -14776,7 +14782,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14982,7 +14988,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15188,7 +15194,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15475,7 +15481,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ68">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR68">
         <v>1.44</v>
@@ -15681,7 +15687,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ69">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR69">
         <v>1.35</v>
@@ -15806,7 +15812,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -15884,7 +15890,7 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AQ70">
         <v>1.29</v>
@@ -16299,7 +16305,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ72">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR72">
         <v>1.87</v>
@@ -16424,7 +16430,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16502,7 +16508,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ73">
         <v>1.5</v>
@@ -16708,7 +16714,7 @@
         <v>1.33</v>
       </c>
       <c r="AP74">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ74">
         <v>1.21</v>
@@ -17042,7 +17048,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17248,7 +17254,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17454,7 +17460,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17660,7 +17666,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -18072,7 +18078,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18356,7 +18362,7 @@
         <v>1.33</v>
       </c>
       <c r="AP82">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AQ82">
         <v>0.77</v>
@@ -18562,10 +18568,10 @@
         <v>0.8</v>
       </c>
       <c r="AP83">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ83">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR83">
         <v>1.23</v>
@@ -18771,7 +18777,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ84">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR84">
         <v>1.49</v>
@@ -18896,7 +18902,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -18977,7 +18983,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ85">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR85">
         <v>1.74</v>
@@ -19183,7 +19189,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ86">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR86">
         <v>1.33</v>
@@ -19514,7 +19520,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19592,7 +19598,7 @@
         <v>0.2</v>
       </c>
       <c r="AP88">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AQ88">
         <v>0.4</v>
@@ -19720,7 +19726,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19926,7 +19932,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20132,7 +20138,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20419,7 +20425,7 @@
         <v>1</v>
       </c>
       <c r="AQ92">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR92">
         <v>1.25</v>
@@ -20544,7 +20550,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20622,7 +20628,7 @@
         <v>1.75</v>
       </c>
       <c r="AP93">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ93">
         <v>2</v>
@@ -20750,7 +20756,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20956,7 +20962,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -21368,7 +21374,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21449,7 +21455,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ97">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR97">
         <v>1.44</v>
@@ -21574,7 +21580,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21652,7 +21658,7 @@
         <v>1.25</v>
       </c>
       <c r="AP98">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ98">
         <v>1.29</v>
@@ -21780,7 +21786,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22273,7 +22279,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ101">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR101">
         <v>1.42</v>
@@ -22398,7 +22404,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22476,7 +22482,7 @@
         <v>2</v>
       </c>
       <c r="AP102">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AQ102">
         <v>1.85</v>
@@ -22682,7 +22688,7 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AQ103">
         <v>1.43</v>
@@ -22810,7 +22816,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -23016,7 +23022,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23094,7 +23100,7 @@
         <v>1.6</v>
       </c>
       <c r="AP105">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ105">
         <v>1.29</v>
@@ -23222,7 +23228,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23715,7 +23721,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ108">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR108">
         <v>0.82</v>
@@ -24046,7 +24052,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24252,7 +24258,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24330,10 +24336,10 @@
         <v>0.57</v>
       </c>
       <c r="AP111">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ111">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR111">
         <v>1.25</v>
@@ -24458,7 +24464,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24539,7 +24545,7 @@
         <v>1</v>
       </c>
       <c r="AQ112">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR112">
         <v>1.28</v>
@@ -24664,7 +24670,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24745,7 +24751,7 @@
         <v>1</v>
       </c>
       <c r="AQ113">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR113">
         <v>1.44</v>
@@ -24870,7 +24876,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25282,7 +25288,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25488,7 +25494,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25775,7 +25781,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ118">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR118">
         <v>1.7</v>
@@ -25978,7 +25984,7 @@
         <v>1.2</v>
       </c>
       <c r="AP119">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AQ119">
         <v>1.79</v>
@@ -26312,7 +26318,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26596,7 +26602,7 @@
         <v>2.2</v>
       </c>
       <c r="AP122">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ122">
         <v>1.85</v>
@@ -26724,7 +26730,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26930,7 +26936,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27008,7 +27014,7 @@
         <v>0.8</v>
       </c>
       <c r="AP124">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ124">
         <v>0.77</v>
@@ -27136,7 +27142,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27342,7 +27348,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27420,7 +27426,7 @@
         <v>1</v>
       </c>
       <c r="AP126">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ126">
         <v>0.5</v>
@@ -27960,7 +27966,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -28247,7 +28253,7 @@
         <v>1</v>
       </c>
       <c r="AQ130">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR130">
         <v>1.48</v>
@@ -28453,7 +28459,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ131">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR131">
         <v>1.36</v>
@@ -28862,10 +28868,10 @@
         <v>1.5</v>
       </c>
       <c r="AP133">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ133">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR133">
         <v>1.55</v>
@@ -29196,7 +29202,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29274,7 +29280,7 @@
         <v>1.2</v>
       </c>
       <c r="AP135">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AQ135">
         <v>1.14</v>
@@ -29402,7 +29408,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29480,7 +29486,7 @@
         <v>1.83</v>
       </c>
       <c r="AP136">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ136">
         <v>2</v>
@@ -29814,7 +29820,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -30020,7 +30026,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30307,7 +30313,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ140">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR140">
         <v>1.57</v>
@@ -30716,7 +30722,7 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ142">
         <v>1.2</v>
@@ -30844,7 +30850,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -31050,7 +31056,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31131,7 +31137,7 @@
         <v>2</v>
       </c>
       <c r="AQ144">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR144">
         <v>1.48</v>
@@ -31462,7 +31468,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31543,7 +31549,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ146">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR146">
         <v>1.08</v>
@@ -31668,7 +31674,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31749,7 +31755,7 @@
         <v>1</v>
       </c>
       <c r="AQ147">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR147">
         <v>1.55</v>
@@ -32080,7 +32086,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32158,7 +32164,7 @@
         <v>0.71</v>
       </c>
       <c r="AP149">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AQ149">
         <v>1.21</v>
@@ -32492,7 +32498,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32698,7 +32704,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32776,7 +32782,7 @@
         <v>2</v>
       </c>
       <c r="AP152">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AQ152">
         <v>2</v>
@@ -32904,7 +32910,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -33316,7 +33322,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -33397,7 +33403,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ155">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR155">
         <v>1.24</v>
@@ -34012,7 +34018,7 @@
         <v>1.5</v>
       </c>
       <c r="AP158">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ158">
         <v>1.14</v>
@@ -34140,7 +34146,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34552,7 +34558,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34630,7 +34636,7 @@
         <v>1.5</v>
       </c>
       <c r="AP161">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ161">
         <v>1.5</v>
@@ -34758,7 +34764,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34836,7 +34842,7 @@
         <v>2.13</v>
       </c>
       <c r="AP162">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ162">
         <v>2</v>
@@ -34964,7 +34970,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35251,7 +35257,7 @@
         <v>2</v>
       </c>
       <c r="AQ164">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR164">
         <v>1.54</v>
@@ -35376,7 +35382,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35582,7 +35588,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35663,7 +35669,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ166">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR166">
         <v>1.76</v>
@@ -35788,7 +35794,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35866,7 +35872,7 @@
         <v>1.86</v>
       </c>
       <c r="AP167">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AQ167">
         <v>1.85</v>
@@ -35994,7 +36000,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36281,7 +36287,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ169">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR169">
         <v>1.57</v>
@@ -36612,7 +36618,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36818,7 +36824,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -37024,7 +37030,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37230,7 +37236,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37308,7 +37314,7 @@
         <v>1.22</v>
       </c>
       <c r="AP174">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AQ174">
         <v>1.2</v>
@@ -37642,7 +37648,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -37926,7 +37932,7 @@
         <v>0.5</v>
       </c>
       <c r="AP177">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ177">
         <v>1.29</v>
@@ -38135,7 +38141,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ178">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR178">
         <v>1.5</v>
@@ -38260,7 +38266,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38341,7 +38347,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ179">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR179">
         <v>1.61</v>
@@ -38547,7 +38553,7 @@
         <v>1</v>
       </c>
       <c r="AQ180">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR180">
         <v>1.47</v>
@@ -38672,7 +38678,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39084,7 +39090,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39162,7 +39168,7 @@
         <v>0.63</v>
       </c>
       <c r="AP183">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AQ183">
         <v>0.77</v>
@@ -39574,10 +39580,10 @@
         <v>0.88</v>
       </c>
       <c r="AP185">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ185">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR185">
         <v>1</v>
@@ -39908,7 +39914,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -39989,7 +39995,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ187">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR187">
         <v>1.47</v>
@@ -40192,7 +40198,7 @@
         <v>2</v>
       </c>
       <c r="AP188">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AQ188">
         <v>2.2</v>
@@ -40320,7 +40326,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40401,7 +40407,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ189">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR189">
         <v>0.97</v>
@@ -40604,7 +40610,7 @@
         <v>2</v>
       </c>
       <c r="AP190">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ190">
         <v>1.85</v>
@@ -40732,7 +40738,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -40810,7 +40816,7 @@
         <v>0.89</v>
       </c>
       <c r="AP191">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ191">
         <v>0.77</v>
@@ -41016,10 +41022,10 @@
         <v>0.89</v>
       </c>
       <c r="AP192">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ192">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR192">
         <v>1.24</v>
@@ -41350,7 +41356,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41637,7 +41643,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ195">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR195">
         <v>1.59</v>
@@ -41840,7 +41846,7 @@
         <v>1.67</v>
       </c>
       <c r="AP196">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AQ196">
         <v>1.29</v>
@@ -41968,7 +41974,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42380,7 +42386,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42586,7 +42592,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42792,7 +42798,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -43204,7 +43210,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43616,7 +43622,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43697,7 +43703,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ205">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR205">
         <v>1.37</v>
@@ -44028,7 +44034,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44234,7 +44240,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44315,7 +44321,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ208">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR208">
         <v>1.57</v>
@@ -44724,7 +44730,7 @@
         <v>0.9</v>
       </c>
       <c r="AP210">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ210">
         <v>0.77</v>
@@ -44852,7 +44858,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45470,7 +45476,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45548,10 +45554,10 @@
         <v>0.8</v>
       </c>
       <c r="AP214">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ214">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR214">
         <v>1.72</v>
@@ -45676,7 +45682,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45754,7 +45760,7 @@
         <v>0.6</v>
       </c>
       <c r="AP215">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AQ215">
         <v>1.29</v>
@@ -45882,7 +45888,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -46088,7 +46094,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46294,7 +46300,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46375,7 +46381,7 @@
         <v>1</v>
       </c>
       <c r="AQ218">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR218">
         <v>1.35</v>
@@ -46578,7 +46584,7 @@
         <v>0.7</v>
       </c>
       <c r="AP219">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ219">
         <v>0.5</v>
@@ -46706,7 +46712,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46787,7 +46793,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ220">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR220">
         <v>1.37</v>
@@ -46912,7 +46918,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -46990,7 +46996,7 @@
         <v>0.36</v>
       </c>
       <c r="AP221">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AQ221">
         <v>0.4</v>
@@ -47196,10 +47202,10 @@
         <v>0.91</v>
       </c>
       <c r="AP222">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AQ222">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR222">
         <v>1.17</v>
@@ -47324,7 +47330,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47611,7 +47617,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ224">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR224">
         <v>1.75</v>
@@ -47736,7 +47742,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47817,7 +47823,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ225">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR225">
         <v>1.48</v>
@@ -47942,7 +47948,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -48226,7 +48232,7 @@
         <v>2.6</v>
       </c>
       <c r="AP227">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ227">
         <v>2</v>
@@ -48354,7 +48360,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48560,7 +48566,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48972,7 +48978,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49178,7 +49184,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49384,7 +49390,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49590,7 +49596,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -49668,7 +49674,7 @@
         <v>1.27</v>
       </c>
       <c r="AP234">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ234">
         <v>1.14</v>
@@ -50083,7 +50089,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ236">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR236">
         <v>1.47</v>
@@ -50208,7 +50214,7 @@
         <v>241</v>
       </c>
       <c r="P237" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q237">
         <v>1.91</v>
@@ -50620,7 +50626,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -51032,7 +51038,7 @@
         <v>244</v>
       </c>
       <c r="P241" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q241">
         <v>2.5</v>
@@ -51444,7 +51450,7 @@
         <v>245</v>
       </c>
       <c r="P243" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q243">
         <v>3.4</v>
@@ -51728,10 +51734,10 @@
         <v>1.08</v>
       </c>
       <c r="AP244">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ244">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR244">
         <v>1.7</v>
@@ -51856,7 +51862,7 @@
         <v>92</v>
       </c>
       <c r="P245" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q245">
         <v>2.6</v>
@@ -51937,7 +51943,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ245">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR245">
         <v>1.56</v>
@@ -52140,10 +52146,10 @@
         <v>0.83</v>
       </c>
       <c r="AP246">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AQ246">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR246">
         <v>1.18</v>
@@ -52346,10 +52352,10 @@
         <v>1.08</v>
       </c>
       <c r="AP247">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AQ247">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR247">
         <v>1.1</v>
@@ -52474,7 +52480,7 @@
         <v>92</v>
       </c>
       <c r="P248" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q248">
         <v>4</v>
@@ -52964,7 +52970,7 @@
         <v>0.33</v>
       </c>
       <c r="AP250">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ250">
         <v>0.4</v>
@@ -53788,7 +53794,7 @@
         <v>1.55</v>
       </c>
       <c r="AP254">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ254">
         <v>1.43</v>
@@ -54122,7 +54128,7 @@
         <v>250</v>
       </c>
       <c r="P256" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q256">
         <v>4</v>
@@ -54534,7 +54540,7 @@
         <v>92</v>
       </c>
       <c r="P258" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q258">
         <v>6</v>
@@ -54740,7 +54746,7 @@
         <v>92</v>
       </c>
       <c r="P259" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q259">
         <v>4.75</v>
@@ -55439,7 +55445,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ262">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR262">
         <v>1.51</v>
@@ -56054,10 +56060,10 @@
         <v>0.67</v>
       </c>
       <c r="AP265">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AQ265">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR265">
         <v>1.18</v>
@@ -56182,7 +56188,7 @@
         <v>92</v>
       </c>
       <c r="P266" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q266">
         <v>4.75</v>
@@ -56260,7 +56266,7 @@
         <v>1.08</v>
       </c>
       <c r="AP266">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AQ266">
         <v>1.2</v>
@@ -56672,10 +56678,10 @@
         <v>1</v>
       </c>
       <c r="AP268">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ268">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR268">
         <v>1.35</v>
@@ -56881,7 +56887,7 @@
         <v>2</v>
       </c>
       <c r="AQ269">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR269">
         <v>1.63</v>
@@ -57006,7 +57012,7 @@
         <v>146</v>
       </c>
       <c r="P270" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q270">
         <v>2.63</v>
@@ -57084,7 +57090,7 @@
         <v>1.69</v>
       </c>
       <c r="AP270">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ270">
         <v>1.79</v>
@@ -57293,7 +57299,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ271">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR271">
         <v>1.6</v>
@@ -57624,7 +57630,7 @@
         <v>260</v>
       </c>
       <c r="P273" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q273">
         <v>3.5</v>
@@ -58036,7 +58042,7 @@
         <v>261</v>
       </c>
       <c r="P275" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q275">
         <v>5</v>
@@ -58242,7 +58248,7 @@
         <v>262</v>
       </c>
       <c r="P276" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q276">
         <v>1.5</v>
@@ -58448,7 +58454,7 @@
         <v>103</v>
       </c>
       <c r="P277" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q277">
         <v>5.5</v>
@@ -58654,7 +58660,7 @@
         <v>263</v>
       </c>
       <c r="P278" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q278">
         <v>2.2</v>
@@ -58860,7 +58866,7 @@
         <v>92</v>
       </c>
       <c r="P279" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q279">
         <v>4</v>
@@ -59066,7 +59072,7 @@
         <v>92</v>
       </c>
       <c r="P280" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q280">
         <v>3.1</v>
@@ -59429,6 +59435,1036 @@
       </c>
       <c r="BP281">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="282" spans="1:68">
+      <c r="A282" s="1">
+        <v>281</v>
+      </c>
+      <c r="B282">
+        <v>7492431</v>
+      </c>
+      <c r="C282" t="s">
+        <v>68</v>
+      </c>
+      <c r="D282" t="s">
+        <v>69</v>
+      </c>
+      <c r="E282" s="2">
+        <v>45730.69791666666</v>
+      </c>
+      <c r="F282">
+        <v>29</v>
+      </c>
+      <c r="G282" t="s">
+        <v>70</v>
+      </c>
+      <c r="H282" t="s">
+        <v>78</v>
+      </c>
+      <c r="I282">
+        <v>2</v>
+      </c>
+      <c r="J282">
+        <v>0</v>
+      </c>
+      <c r="K282">
+        <v>2</v>
+      </c>
+      <c r="L282">
+        <v>2</v>
+      </c>
+      <c r="M282">
+        <v>1</v>
+      </c>
+      <c r="N282">
+        <v>3</v>
+      </c>
+      <c r="O282" t="s">
+        <v>265</v>
+      </c>
+      <c r="P282" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q282">
+        <v>2.75</v>
+      </c>
+      <c r="R282">
+        <v>1.91</v>
+      </c>
+      <c r="S282">
+        <v>5</v>
+      </c>
+      <c r="T282">
+        <v>1.57</v>
+      </c>
+      <c r="U282">
+        <v>2.25</v>
+      </c>
+      <c r="V282">
+        <v>3.75</v>
+      </c>
+      <c r="W282">
+        <v>1.25</v>
+      </c>
+      <c r="X282">
+        <v>13</v>
+      </c>
+      <c r="Y282">
+        <v>1.04</v>
+      </c>
+      <c r="Z282">
+        <v>2.06</v>
+      </c>
+      <c r="AA282">
+        <v>3.1</v>
+      </c>
+      <c r="AB282">
+        <v>4.4</v>
+      </c>
+      <c r="AC282">
+        <v>1.11</v>
+      </c>
+      <c r="AD282">
+        <v>6</v>
+      </c>
+      <c r="AE282">
+        <v>1.5</v>
+      </c>
+      <c r="AF282">
+        <v>2.5</v>
+      </c>
+      <c r="AG282">
+        <v>2.25</v>
+      </c>
+      <c r="AH282">
+        <v>1.6</v>
+      </c>
+      <c r="AI282">
+        <v>2.1</v>
+      </c>
+      <c r="AJ282">
+        <v>1.67</v>
+      </c>
+      <c r="AK282">
+        <v>1.22</v>
+      </c>
+      <c r="AL282">
+        <v>1.36</v>
+      </c>
+      <c r="AM282">
+        <v>1.75</v>
+      </c>
+      <c r="AN282">
+        <v>1.14</v>
+      </c>
+      <c r="AO282">
+        <v>0.79</v>
+      </c>
+      <c r="AP282">
+        <v>1.27</v>
+      </c>
+      <c r="AQ282">
+        <v>0.73</v>
+      </c>
+      <c r="AR282">
+        <v>1.31</v>
+      </c>
+      <c r="AS282">
+        <v>1.18</v>
+      </c>
+      <c r="AT282">
+        <v>2.49</v>
+      </c>
+      <c r="AU282">
+        <v>3</v>
+      </c>
+      <c r="AV282">
+        <v>3</v>
+      </c>
+      <c r="AW282">
+        <v>6</v>
+      </c>
+      <c r="AX282">
+        <v>13</v>
+      </c>
+      <c r="AY282">
+        <v>11</v>
+      </c>
+      <c r="AZ282">
+        <v>22</v>
+      </c>
+      <c r="BA282">
+        <v>3</v>
+      </c>
+      <c r="BB282">
+        <v>3</v>
+      </c>
+      <c r="BC282">
+        <v>6</v>
+      </c>
+      <c r="BD282">
+        <v>1.54</v>
+      </c>
+      <c r="BE282">
+        <v>6.5</v>
+      </c>
+      <c r="BF282">
+        <v>2.75</v>
+      </c>
+      <c r="BG282">
+        <v>1.34</v>
+      </c>
+      <c r="BH282">
+        <v>2.9</v>
+      </c>
+      <c r="BI282">
+        <v>1.58</v>
+      </c>
+      <c r="BJ282">
+        <v>2.18</v>
+      </c>
+      <c r="BK282">
+        <v>1.95</v>
+      </c>
+      <c r="BL282">
+        <v>1.75</v>
+      </c>
+      <c r="BM282">
+        <v>2.48</v>
+      </c>
+      <c r="BN282">
+        <v>1.47</v>
+      </c>
+      <c r="BO282">
+        <v>3.25</v>
+      </c>
+      <c r="BP282">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="283" spans="1:68">
+      <c r="A283" s="1">
+        <v>282</v>
+      </c>
+      <c r="B283">
+        <v>7492433</v>
+      </c>
+      <c r="C283" t="s">
+        <v>68</v>
+      </c>
+      <c r="D283" t="s">
+        <v>69</v>
+      </c>
+      <c r="E283" s="2">
+        <v>45731.45833333334</v>
+      </c>
+      <c r="F283">
+        <v>29</v>
+      </c>
+      <c r="G283" t="s">
+        <v>81</v>
+      </c>
+      <c r="H283" t="s">
+        <v>71</v>
+      </c>
+      <c r="I283">
+        <v>0</v>
+      </c>
+      <c r="J283">
+        <v>0</v>
+      </c>
+      <c r="K283">
+        <v>0</v>
+      </c>
+      <c r="L283">
+        <v>1</v>
+      </c>
+      <c r="M283">
+        <v>1</v>
+      </c>
+      <c r="N283">
+        <v>2</v>
+      </c>
+      <c r="O283" t="s">
+        <v>216</v>
+      </c>
+      <c r="P283" t="s">
+        <v>367</v>
+      </c>
+      <c r="Q283">
+        <v>3.6</v>
+      </c>
+      <c r="R283">
+        <v>2.05</v>
+      </c>
+      <c r="S283">
+        <v>3.2</v>
+      </c>
+      <c r="T283">
+        <v>1.44</v>
+      </c>
+      <c r="U283">
+        <v>2.63</v>
+      </c>
+      <c r="V283">
+        <v>3.25</v>
+      </c>
+      <c r="W283">
+        <v>1.33</v>
+      </c>
+      <c r="X283">
+        <v>9</v>
+      </c>
+      <c r="Y283">
+        <v>1.07</v>
+      </c>
+      <c r="Z283">
+        <v>3.31</v>
+      </c>
+      <c r="AA283">
+        <v>3.03</v>
+      </c>
+      <c r="AB283">
+        <v>2.48</v>
+      </c>
+      <c r="AC283">
+        <v>1.07</v>
+      </c>
+      <c r="AD283">
+        <v>8</v>
+      </c>
+      <c r="AE283">
+        <v>1.36</v>
+      </c>
+      <c r="AF283">
+        <v>3.1</v>
+      </c>
+      <c r="AG283">
+        <v>2.02</v>
+      </c>
+      <c r="AH283">
+        <v>1.8</v>
+      </c>
+      <c r="AI283">
+        <v>1.8</v>
+      </c>
+      <c r="AJ283">
+        <v>1.95</v>
+      </c>
+      <c r="AK283">
+        <v>1.53</v>
+      </c>
+      <c r="AL283">
+        <v>1.34</v>
+      </c>
+      <c r="AM283">
+        <v>1.38</v>
+      </c>
+      <c r="AN283">
+        <v>0.5</v>
+      </c>
+      <c r="AO283">
+        <v>0.62</v>
+      </c>
+      <c r="AP283">
+        <v>0.53</v>
+      </c>
+      <c r="AQ283">
+        <v>0.64</v>
+      </c>
+      <c r="AR283">
+        <v>1.17</v>
+      </c>
+      <c r="AS283">
+        <v>1.19</v>
+      </c>
+      <c r="AT283">
+        <v>2.36</v>
+      </c>
+      <c r="AU283">
+        <v>5</v>
+      </c>
+      <c r="AV283">
+        <v>7</v>
+      </c>
+      <c r="AW283">
+        <v>8</v>
+      </c>
+      <c r="AX283">
+        <v>8</v>
+      </c>
+      <c r="AY283">
+        <v>14</v>
+      </c>
+      <c r="AZ283">
+        <v>18</v>
+      </c>
+      <c r="BA283">
+        <v>6</v>
+      </c>
+      <c r="BB283">
+        <v>3</v>
+      </c>
+      <c r="BC283">
+        <v>9</v>
+      </c>
+      <c r="BD283">
+        <v>2.13</v>
+      </c>
+      <c r="BE283">
+        <v>6.45</v>
+      </c>
+      <c r="BF283">
+        <v>2.16</v>
+      </c>
+      <c r="BG283">
+        <v>1.24</v>
+      </c>
+      <c r="BH283">
+        <v>3.34</v>
+      </c>
+      <c r="BI283">
+        <v>1.48</v>
+      </c>
+      <c r="BJ283">
+        <v>2.4</v>
+      </c>
+      <c r="BK283">
+        <v>1.85</v>
+      </c>
+      <c r="BL283">
+        <v>1.85</v>
+      </c>
+      <c r="BM283">
+        <v>2.38</v>
+      </c>
+      <c r="BN283">
+        <v>1.49</v>
+      </c>
+      <c r="BO283">
+        <v>3.14</v>
+      </c>
+      <c r="BP283">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="284" spans="1:68">
+      <c r="A284" s="1">
+        <v>283</v>
+      </c>
+      <c r="B284">
+        <v>7492436</v>
+      </c>
+      <c r="C284" t="s">
+        <v>68</v>
+      </c>
+      <c r="D284" t="s">
+        <v>69</v>
+      </c>
+      <c r="E284" s="2">
+        <v>45731.45833333334</v>
+      </c>
+      <c r="F284">
+        <v>29</v>
+      </c>
+      <c r="G284" t="s">
+        <v>80</v>
+      </c>
+      <c r="H284" t="s">
+        <v>75</v>
+      </c>
+      <c r="I284">
+        <v>0</v>
+      </c>
+      <c r="J284">
+        <v>0</v>
+      </c>
+      <c r="K284">
+        <v>0</v>
+      </c>
+      <c r="L284">
+        <v>0</v>
+      </c>
+      <c r="M284">
+        <v>1</v>
+      </c>
+      <c r="N284">
+        <v>1</v>
+      </c>
+      <c r="O284" t="s">
+        <v>92</v>
+      </c>
+      <c r="P284" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q284">
+        <v>2.4</v>
+      </c>
+      <c r="R284">
+        <v>2.1</v>
+      </c>
+      <c r="S284">
+        <v>5</v>
+      </c>
+      <c r="T284">
+        <v>1.44</v>
+      </c>
+      <c r="U284">
+        <v>2.63</v>
+      </c>
+      <c r="V284">
+        <v>3.25</v>
+      </c>
+      <c r="W284">
+        <v>1.33</v>
+      </c>
+      <c r="X284">
+        <v>9</v>
+      </c>
+      <c r="Y284">
+        <v>1.07</v>
+      </c>
+      <c r="Z284">
+        <v>1.86</v>
+      </c>
+      <c r="AA284">
+        <v>3.51</v>
+      </c>
+      <c r="AB284">
+        <v>4.7</v>
+      </c>
+      <c r="AC284">
+        <v>1.06</v>
+      </c>
+      <c r="AD284">
+        <v>8.5</v>
+      </c>
+      <c r="AE284">
+        <v>1.35</v>
+      </c>
+      <c r="AF284">
+        <v>3.1</v>
+      </c>
+      <c r="AG284">
+        <v>2</v>
+      </c>
+      <c r="AH284">
+        <v>1.73</v>
+      </c>
+      <c r="AI284">
+        <v>1.95</v>
+      </c>
+      <c r="AJ284">
+        <v>1.8</v>
+      </c>
+      <c r="AK284">
+        <v>1.19</v>
+      </c>
+      <c r="AL284">
+        <v>1.29</v>
+      </c>
+      <c r="AM284">
+        <v>2</v>
+      </c>
+      <c r="AN284">
+        <v>1.64</v>
+      </c>
+      <c r="AO284">
+        <v>0.93</v>
+      </c>
+      <c r="AP284">
+        <v>1.53</v>
+      </c>
+      <c r="AQ284">
+        <v>1.07</v>
+      </c>
+      <c r="AR284">
+        <v>1.25</v>
+      </c>
+      <c r="AS284">
+        <v>1.06</v>
+      </c>
+      <c r="AT284">
+        <v>2.31</v>
+      </c>
+      <c r="AU284">
+        <v>4</v>
+      </c>
+      <c r="AV284">
+        <v>3</v>
+      </c>
+      <c r="AW284">
+        <v>8</v>
+      </c>
+      <c r="AX284">
+        <v>5</v>
+      </c>
+      <c r="AY284">
+        <v>12</v>
+      </c>
+      <c r="AZ284">
+        <v>10</v>
+      </c>
+      <c r="BA284">
+        <v>2</v>
+      </c>
+      <c r="BB284">
+        <v>1</v>
+      </c>
+      <c r="BC284">
+        <v>3</v>
+      </c>
+      <c r="BD284">
+        <v>1.49</v>
+      </c>
+      <c r="BE284">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF284">
+        <v>3.25</v>
+      </c>
+      <c r="BG284">
+        <v>1.22</v>
+      </c>
+      <c r="BH284">
+        <v>3.5</v>
+      </c>
+      <c r="BI284">
+        <v>1.44</v>
+      </c>
+      <c r="BJ284">
+        <v>2.51</v>
+      </c>
+      <c r="BK284">
+        <v>1.79</v>
+      </c>
+      <c r="BL284">
+        <v>1.92</v>
+      </c>
+      <c r="BM284">
+        <v>2.28</v>
+      </c>
+      <c r="BN284">
+        <v>1.53</v>
+      </c>
+      <c r="BO284">
+        <v>2.97</v>
+      </c>
+      <c r="BP284">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="285" spans="1:68">
+      <c r="A285" s="1">
+        <v>284</v>
+      </c>
+      <c r="B285">
+        <v>7492432</v>
+      </c>
+      <c r="C285" t="s">
+        <v>68</v>
+      </c>
+      <c r="D285" t="s">
+        <v>69</v>
+      </c>
+      <c r="E285" s="2">
+        <v>45731.58333333334</v>
+      </c>
+      <c r="F285">
+        <v>29</v>
+      </c>
+      <c r="G285" t="s">
+        <v>73</v>
+      </c>
+      <c r="H285" t="s">
+        <v>88</v>
+      </c>
+      <c r="I285">
+        <v>0</v>
+      </c>
+      <c r="J285">
+        <v>1</v>
+      </c>
+      <c r="K285">
+        <v>1</v>
+      </c>
+      <c r="L285">
+        <v>2</v>
+      </c>
+      <c r="M285">
+        <v>1</v>
+      </c>
+      <c r="N285">
+        <v>3</v>
+      </c>
+      <c r="O285" t="s">
+        <v>266</v>
+      </c>
+      <c r="P285" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q285">
+        <v>2.4</v>
+      </c>
+      <c r="R285">
+        <v>2.25</v>
+      </c>
+      <c r="S285">
+        <v>4.5</v>
+      </c>
+      <c r="T285">
+        <v>1.33</v>
+      </c>
+      <c r="U285">
+        <v>3.25</v>
+      </c>
+      <c r="V285">
+        <v>2.63</v>
+      </c>
+      <c r="W285">
+        <v>1.44</v>
+      </c>
+      <c r="X285">
+        <v>7</v>
+      </c>
+      <c r="Y285">
+        <v>1.1</v>
+      </c>
+      <c r="Z285">
+        <v>1.86</v>
+      </c>
+      <c r="AA285">
+        <v>3.83</v>
+      </c>
+      <c r="AB285">
+        <v>4.2</v>
+      </c>
+      <c r="AC285">
+        <v>1.05</v>
+      </c>
+      <c r="AD285">
+        <v>9.5</v>
+      </c>
+      <c r="AE285">
+        <v>1.25</v>
+      </c>
+      <c r="AF285">
+        <v>3.85</v>
+      </c>
+      <c r="AG285">
+        <v>1.82</v>
+      </c>
+      <c r="AH285">
+        <v>2</v>
+      </c>
+      <c r="AI285">
+        <v>1.7</v>
+      </c>
+      <c r="AJ285">
+        <v>2.05</v>
+      </c>
+      <c r="AK285">
+        <v>1.22</v>
+      </c>
+      <c r="AL285">
+        <v>1.27</v>
+      </c>
+      <c r="AM285">
+        <v>1.93</v>
+      </c>
+      <c r="AN285">
+        <v>1.71</v>
+      </c>
+      <c r="AO285">
+        <v>0.71</v>
+      </c>
+      <c r="AP285">
+        <v>1.8</v>
+      </c>
+      <c r="AQ285">
+        <v>0.67</v>
+      </c>
+      <c r="AR285">
+        <v>1.72</v>
+      </c>
+      <c r="AS285">
+        <v>1.3</v>
+      </c>
+      <c r="AT285">
+        <v>3.02</v>
+      </c>
+      <c r="AU285">
+        <v>4</v>
+      </c>
+      <c r="AV285">
+        <v>7</v>
+      </c>
+      <c r="AW285">
+        <v>6</v>
+      </c>
+      <c r="AX285">
+        <v>9</v>
+      </c>
+      <c r="AY285">
+        <v>11</v>
+      </c>
+      <c r="AZ285">
+        <v>17</v>
+      </c>
+      <c r="BA285">
+        <v>0</v>
+      </c>
+      <c r="BB285">
+        <v>5</v>
+      </c>
+      <c r="BC285">
+        <v>5</v>
+      </c>
+      <c r="BD285">
+        <v>1.61</v>
+      </c>
+      <c r="BE285">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF285">
+        <v>2.84</v>
+      </c>
+      <c r="BG285">
+        <v>1.26</v>
+      </c>
+      <c r="BH285">
+        <v>3.22</v>
+      </c>
+      <c r="BI285">
+        <v>1.51</v>
+      </c>
+      <c r="BJ285">
+        <v>2.32</v>
+      </c>
+      <c r="BK285">
+        <v>1.88</v>
+      </c>
+      <c r="BL285">
+        <v>1.82</v>
+      </c>
+      <c r="BM285">
+        <v>2.42</v>
+      </c>
+      <c r="BN285">
+        <v>1.47</v>
+      </c>
+      <c r="BO285">
+        <v>3.28</v>
+      </c>
+      <c r="BP285">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="286" spans="1:68">
+      <c r="A286" s="1">
+        <v>285</v>
+      </c>
+      <c r="B286">
+        <v>7492435</v>
+      </c>
+      <c r="C286" t="s">
+        <v>68</v>
+      </c>
+      <c r="D286" t="s">
+        <v>69</v>
+      </c>
+      <c r="E286" s="2">
+        <v>45731.69791666666</v>
+      </c>
+      <c r="F286">
+        <v>29</v>
+      </c>
+      <c r="G286" t="s">
+        <v>84</v>
+      </c>
+      <c r="H286" t="s">
+        <v>72</v>
+      </c>
+      <c r="I286">
+        <v>0</v>
+      </c>
+      <c r="J286">
+        <v>0</v>
+      </c>
+      <c r="K286">
+        <v>0</v>
+      </c>
+      <c r="L286">
+        <v>1</v>
+      </c>
+      <c r="M286">
+        <v>0</v>
+      </c>
+      <c r="N286">
+        <v>1</v>
+      </c>
+      <c r="O286" t="s">
+        <v>141</v>
+      </c>
+      <c r="P286" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q286">
+        <v>2.5</v>
+      </c>
+      <c r="R286">
+        <v>2.05</v>
+      </c>
+      <c r="S286">
+        <v>5</v>
+      </c>
+      <c r="T286">
+        <v>1.5</v>
+      </c>
+      <c r="U286">
+        <v>2.5</v>
+      </c>
+      <c r="V286">
+        <v>3.4</v>
+      </c>
+      <c r="W286">
+        <v>1.3</v>
+      </c>
+      <c r="X286">
+        <v>10</v>
+      </c>
+      <c r="Y286">
+        <v>1.06</v>
+      </c>
+      <c r="Z286">
+        <v>1.88</v>
+      </c>
+      <c r="AA286">
+        <v>3.41</v>
+      </c>
+      <c r="AB286">
+        <v>4.75</v>
+      </c>
+      <c r="AC286">
+        <v>1.08</v>
+      </c>
+      <c r="AD286">
+        <v>7.5</v>
+      </c>
+      <c r="AE286">
+        <v>1.4</v>
+      </c>
+      <c r="AF286">
+        <v>2.9</v>
+      </c>
+      <c r="AG286">
+        <v>2.3</v>
+      </c>
+      <c r="AH286">
+        <v>1.55</v>
+      </c>
+      <c r="AI286">
+        <v>2</v>
+      </c>
+      <c r="AJ286">
+        <v>1.75</v>
+      </c>
+      <c r="AK286">
+        <v>1.2</v>
+      </c>
+      <c r="AL286">
+        <v>1.31</v>
+      </c>
+      <c r="AM286">
+        <v>1.9</v>
+      </c>
+      <c r="AN286">
+        <v>1.31</v>
+      </c>
+      <c r="AO286">
+        <v>1</v>
+      </c>
+      <c r="AP286">
+        <v>1.43</v>
+      </c>
+      <c r="AQ286">
+        <v>0.93</v>
+      </c>
+      <c r="AR286">
+        <v>1.15</v>
+      </c>
+      <c r="AS286">
+        <v>1.04</v>
+      </c>
+      <c r="AT286">
+        <v>2.19</v>
+      </c>
+      <c r="AU286">
+        <v>4</v>
+      </c>
+      <c r="AV286">
+        <v>3</v>
+      </c>
+      <c r="AW286">
+        <v>10</v>
+      </c>
+      <c r="AX286">
+        <v>14</v>
+      </c>
+      <c r="AY286">
+        <v>17</v>
+      </c>
+      <c r="AZ286">
+        <v>18</v>
+      </c>
+      <c r="BA286">
+        <v>5</v>
+      </c>
+      <c r="BB286">
+        <v>5</v>
+      </c>
+      <c r="BC286">
+        <v>10</v>
+      </c>
+      <c r="BD286">
+        <v>1.53</v>
+      </c>
+      <c r="BE286">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF286">
+        <v>3.12</v>
+      </c>
+      <c r="BG286">
+        <v>1.25</v>
+      </c>
+      <c r="BH286">
+        <v>3.28</v>
+      </c>
+      <c r="BI286">
+        <v>1.49</v>
+      </c>
+      <c r="BJ286">
+        <v>2.38</v>
+      </c>
+      <c r="BK286">
+        <v>1.87</v>
+      </c>
+      <c r="BL286">
+        <v>1.83</v>
+      </c>
+      <c r="BM286">
+        <v>2.4</v>
+      </c>
+      <c r="BN286">
+        <v>1.48</v>
+      </c>
+      <c r="BO286">
+        <v>3.2</v>
+      </c>
+      <c r="BP286">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="392">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -817,6 +817,9 @@
     <t>['53', '75']</t>
   </si>
   <si>
+    <t>['16', '48', '49', '74', '84']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1548,7 +1551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP286"/>
+  <dimension ref="A1:BP288"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1804,7 +1807,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2422,7 +2425,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2628,7 +2631,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2706,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ6">
         <v>1.21</v>
@@ -2915,7 +2918,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ7">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3246,7 +3249,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3452,7 +3455,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3945,7 +3948,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ12">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4070,7 +4073,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4276,7 +4279,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -5306,7 +5309,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5718,7 +5721,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5924,7 +5927,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6336,7 +6339,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6414,7 +6417,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ24">
         <v>0.93</v>
@@ -6748,7 +6751,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6954,7 +6957,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7160,7 +7163,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7366,7 +7369,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7984,7 +7987,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8808,7 +8811,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -9220,7 +9223,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9301,7 +9304,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ38">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR38">
         <v>1.24</v>
@@ -9426,7 +9429,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9632,7 +9635,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9838,7 +9841,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -10044,7 +10047,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10250,7 +10253,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10743,7 +10746,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ45">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR45">
         <v>1.23</v>
@@ -10868,7 +10871,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -11074,7 +11077,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11155,7 +11158,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ47">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR47">
         <v>1.69</v>
@@ -11280,7 +11283,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11692,7 +11695,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11898,7 +11901,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12310,7 +12313,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12516,7 +12519,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12722,7 +12725,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12800,7 +12803,7 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ55">
         <v>2.2</v>
@@ -12928,7 +12931,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13009,7 +13012,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ56">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR56">
         <v>1.02</v>
@@ -13134,7 +13137,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13958,7 +13961,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14782,7 +14785,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14988,7 +14991,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15194,7 +15197,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15684,7 +15687,7 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ69">
         <v>0.64</v>
@@ -15812,7 +15815,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -16430,7 +16433,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16923,7 +16926,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ75">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR75">
         <v>1.37</v>
@@ -17048,7 +17051,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17129,7 +17132,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ76">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR76">
         <v>0.85</v>
@@ -17254,7 +17257,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17460,7 +17463,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17666,7 +17669,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -18078,7 +18081,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18902,7 +18905,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19520,7 +19523,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19726,7 +19729,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19932,7 +19935,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20138,7 +20141,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20550,7 +20553,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20631,7 +20634,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ93">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR93">
         <v>1.71</v>
@@ -20756,7 +20759,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20962,7 +20965,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -21374,7 +21377,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21580,7 +21583,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21786,7 +21789,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21867,7 +21870,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ99">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR99">
         <v>1.62</v>
@@ -22276,7 +22279,7 @@
         <v>0.2</v>
       </c>
       <c r="AP101">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ101">
         <v>0.73</v>
@@ -22404,7 +22407,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22816,7 +22819,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -23022,7 +23025,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23228,7 +23231,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -24052,7 +24055,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24258,7 +24261,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24464,7 +24467,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24670,7 +24673,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24876,7 +24879,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25288,7 +25291,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25494,7 +25497,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25987,7 +25990,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ119">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR119">
         <v>0.96</v>
@@ -26193,7 +26196,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ120">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR120">
         <v>1.62</v>
@@ -26318,7 +26321,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26730,7 +26733,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26936,7 +26939,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27142,7 +27145,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27348,7 +27351,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27966,7 +27969,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -29074,7 +29077,7 @@
         <v>0.29</v>
       </c>
       <c r="AP134">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ134">
         <v>0.4</v>
@@ -29202,7 +29205,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29408,7 +29411,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29489,7 +29492,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ136">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR136">
         <v>1.14</v>
@@ -29695,7 +29698,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ137">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR137">
         <v>1.24</v>
@@ -29820,7 +29823,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -30026,7 +30029,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30850,7 +30853,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -31056,7 +31059,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31468,7 +31471,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31674,7 +31677,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31961,7 +31964,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ148">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR148">
         <v>1.5</v>
@@ -32086,7 +32089,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32498,7 +32501,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32704,7 +32707,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32785,7 +32788,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ152">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR152">
         <v>1.05</v>
@@ -32910,7 +32913,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -33322,7 +33325,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -33606,7 +33609,7 @@
         <v>2</v>
       </c>
       <c r="AP156">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ156">
         <v>1.29</v>
@@ -34146,7 +34149,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34558,7 +34561,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34764,7 +34767,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34845,7 +34848,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ162">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR162">
         <v>1.24</v>
@@ -34970,7 +34973,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35051,7 +35054,7 @@
         <v>1</v>
       </c>
       <c r="AQ163">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR163">
         <v>1.36</v>
@@ -35382,7 +35385,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35588,7 +35591,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35794,7 +35797,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -36000,7 +36003,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36618,7 +36621,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36824,7 +36827,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -37030,7 +37033,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37236,7 +37239,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37648,7 +37651,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -38266,7 +38269,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38344,7 +38347,7 @@
         <v>0.75</v>
       </c>
       <c r="AP179">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ179">
         <v>1.07</v>
@@ -38678,7 +38681,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38759,7 +38762,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ181">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR181">
         <v>1.57</v>
@@ -39090,7 +39093,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39789,7 +39792,7 @@
         <v>2</v>
       </c>
       <c r="AQ186">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR186">
         <v>1.62</v>
@@ -39914,7 +39917,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40326,7 +40329,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40738,7 +40741,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41356,7 +41359,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41434,7 +41437,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP194">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ194">
         <v>1.29</v>
@@ -41974,7 +41977,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42386,7 +42389,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42592,7 +42595,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42798,7 +42801,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -42876,7 +42879,7 @@
         <v>0.78</v>
       </c>
       <c r="AP201">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ201">
         <v>0.5</v>
@@ -43210,7 +43213,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43291,7 +43294,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ203">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR203">
         <v>1.78</v>
@@ -43622,7 +43625,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -44034,7 +44037,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44115,7 +44118,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ207">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR207">
         <v>1.12</v>
@@ -44240,7 +44243,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44858,7 +44861,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45476,7 +45479,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45682,7 +45685,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45888,7 +45891,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -46094,7 +46097,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46300,7 +46303,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46712,7 +46715,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46918,7 +46921,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47330,7 +47333,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47614,7 +47617,7 @@
         <v>0.64</v>
       </c>
       <c r="AP224">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ224">
         <v>0.67</v>
@@ -47742,7 +47745,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47948,7 +47951,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -48360,7 +48363,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48441,7 +48444,7 @@
         <v>2</v>
       </c>
       <c r="AQ228">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR228">
         <v>1.58</v>
@@ -48566,7 +48569,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48647,7 +48650,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ229">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR229">
         <v>1.45</v>
@@ -48978,7 +48981,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49184,7 +49187,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49390,7 +49393,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49596,7 +49599,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -50214,7 +50217,7 @@
         <v>241</v>
       </c>
       <c r="P237" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q237">
         <v>1.91</v>
@@ -50626,7 +50629,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -51038,7 +51041,7 @@
         <v>244</v>
       </c>
       <c r="P241" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q241">
         <v>2.5</v>
@@ -51116,7 +51119,7 @@
         <v>1.17</v>
       </c>
       <c r="AP241">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ241">
         <v>1.2</v>
@@ -51450,7 +51453,7 @@
         <v>245</v>
       </c>
       <c r="P243" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q243">
         <v>3.4</v>
@@ -51531,7 +51534,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ243">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR243">
         <v>1.63</v>
@@ -51862,7 +51865,7 @@
         <v>92</v>
       </c>
       <c r="P245" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q245">
         <v>2.6</v>
@@ -52480,7 +52483,7 @@
         <v>92</v>
       </c>
       <c r="P248" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q248">
         <v>4</v>
@@ -53591,7 +53594,7 @@
         <v>1</v>
       </c>
       <c r="AQ253">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR253">
         <v>1.35</v>
@@ -54128,7 +54131,7 @@
         <v>250</v>
       </c>
       <c r="P256" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q256">
         <v>4</v>
@@ -54209,7 +54212,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ256">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AR256">
         <v>1.57</v>
@@ -54540,7 +54543,7 @@
         <v>92</v>
       </c>
       <c r="P258" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q258">
         <v>6</v>
@@ -54746,7 +54749,7 @@
         <v>92</v>
       </c>
       <c r="P259" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q259">
         <v>4.75</v>
@@ -55236,7 +55239,7 @@
         <v>1.42</v>
       </c>
       <c r="AP261">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ261">
         <v>1.43</v>
@@ -56188,7 +56191,7 @@
         <v>92</v>
       </c>
       <c r="P266" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q266">
         <v>4.75</v>
@@ -56472,7 +56475,7 @@
         <v>0.83</v>
       </c>
       <c r="AP267">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ267">
         <v>0.77</v>
@@ -57012,7 +57015,7 @@
         <v>146</v>
       </c>
       <c r="P270" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q270">
         <v>2.63</v>
@@ -57093,7 +57096,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ270">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR270">
         <v>1.71</v>
@@ -57630,7 +57633,7 @@
         <v>260</v>
       </c>
       <c r="P273" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q273">
         <v>3.5</v>
@@ -58042,7 +58045,7 @@
         <v>261</v>
       </c>
       <c r="P275" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q275">
         <v>5</v>
@@ -58248,7 +58251,7 @@
         <v>262</v>
       </c>
       <c r="P276" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q276">
         <v>1.5</v>
@@ -58454,7 +58457,7 @@
         <v>103</v>
       </c>
       <c r="P277" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q277">
         <v>5.5</v>
@@ -58660,7 +58663,7 @@
         <v>263</v>
       </c>
       <c r="P278" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q278">
         <v>2.2</v>
@@ -58866,7 +58869,7 @@
         <v>92</v>
       </c>
       <c r="P279" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q279">
         <v>4</v>
@@ -59072,7 +59075,7 @@
         <v>92</v>
       </c>
       <c r="P280" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q280">
         <v>3.1</v>
@@ -59484,7 +59487,7 @@
         <v>265</v>
       </c>
       <c r="P282" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q282">
         <v>2.75</v>
@@ -59648,7 +59651,7 @@
         <v>282</v>
       </c>
       <c r="B283">
-        <v>7492433</v>
+        <v>7492436</v>
       </c>
       <c r="C283" t="s">
         <v>68</v>
@@ -59663,10 +59666,10 @@
         <v>29</v>
       </c>
       <c r="G283" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H283" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I283">
         <v>0</v>
@@ -59678,28 +59681,28 @@
         <v>0</v>
       </c>
       <c r="L283">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M283">
         <v>1</v>
       </c>
       <c r="N283">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O283" t="s">
-        <v>216</v>
+        <v>92</v>
       </c>
       <c r="P283" t="s">
-        <v>367</v>
+        <v>319</v>
       </c>
       <c r="Q283">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="R283">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S283">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="T283">
         <v>1.44</v>
@@ -59720,133 +59723,133 @@
         <v>1.07</v>
       </c>
       <c r="Z283">
-        <v>3.31</v>
+        <v>1.86</v>
       </c>
       <c r="AA283">
-        <v>3.03</v>
+        <v>3.51</v>
       </c>
       <c r="AB283">
-        <v>2.48</v>
+        <v>4.7</v>
       </c>
       <c r="AC283">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AD283">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AE283">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AF283">
         <v>3.1</v>
       </c>
       <c r="AG283">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH283">
+        <v>1.73</v>
+      </c>
+      <c r="AI283">
+        <v>1.95</v>
+      </c>
+      <c r="AJ283">
         <v>1.8</v>
       </c>
-      <c r="AI283">
-        <v>1.8</v>
-      </c>
-      <c r="AJ283">
-        <v>1.95</v>
-      </c>
       <c r="AK283">
+        <v>1.19</v>
+      </c>
+      <c r="AL283">
+        <v>1.29</v>
+      </c>
+      <c r="AM283">
+        <v>2</v>
+      </c>
+      <c r="AN283">
+        <v>1.64</v>
+      </c>
+      <c r="AO283">
+        <v>0.93</v>
+      </c>
+      <c r="AP283">
         <v>1.53</v>
       </c>
-      <c r="AL283">
-        <v>1.34</v>
-      </c>
-      <c r="AM283">
-        <v>1.38</v>
-      </c>
-      <c r="AN283">
-        <v>0.5</v>
-      </c>
-      <c r="AO283">
-        <v>0.62</v>
-      </c>
-      <c r="AP283">
-        <v>0.53</v>
-      </c>
       <c r="AQ283">
-        <v>0.64</v>
+        <v>1.07</v>
       </c>
       <c r="AR283">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AS283">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AT283">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="AU283">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV283">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AW283">
         <v>8</v>
       </c>
       <c r="AX283">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AY283">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ283">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="BA283">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BB283">
+        <v>1</v>
+      </c>
+      <c r="BC283">
         <v>3</v>
       </c>
-      <c r="BC283">
-        <v>9</v>
-      </c>
       <c r="BD283">
-        <v>2.13</v>
+        <v>1.49</v>
       </c>
       <c r="BE283">
-        <v>6.45</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF283">
-        <v>2.16</v>
+        <v>3.25</v>
       </c>
       <c r="BG283">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BH283">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="BI283">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="BJ283">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="BK283">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="BL283">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="BM283">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="BN283">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="BO283">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="BP283">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="284" spans="1:68">
@@ -59854,7 +59857,7 @@
         <v>283</v>
       </c>
       <c r="B284">
-        <v>7492436</v>
+        <v>7492433</v>
       </c>
       <c r="C284" t="s">
         <v>68</v>
@@ -59869,10 +59872,10 @@
         <v>29</v>
       </c>
       <c r="G284" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H284" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I284">
         <v>0</v>
@@ -59884,28 +59887,28 @@
         <v>0</v>
       </c>
       <c r="L284">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M284">
         <v>1</v>
       </c>
       <c r="N284">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O284" t="s">
-        <v>92</v>
+        <v>216</v>
       </c>
       <c r="P284" t="s">
-        <v>318</v>
+        <v>368</v>
       </c>
       <c r="Q284">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="R284">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S284">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="T284">
         <v>1.44</v>
@@ -59926,133 +59929,133 @@
         <v>1.07</v>
       </c>
       <c r="Z284">
-        <v>1.86</v>
+        <v>3.31</v>
       </c>
       <c r="AA284">
-        <v>3.51</v>
+        <v>3.03</v>
       </c>
       <c r="AB284">
-        <v>4.7</v>
+        <v>2.48</v>
       </c>
       <c r="AC284">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AD284">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AE284">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AF284">
         <v>3.1</v>
       </c>
       <c r="AG284">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH284">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AI284">
+        <v>1.8</v>
+      </c>
+      <c r="AJ284">
         <v>1.95</v>
       </c>
-      <c r="AJ284">
-        <v>1.8</v>
-      </c>
       <c r="AK284">
+        <v>1.53</v>
+      </c>
+      <c r="AL284">
+        <v>1.34</v>
+      </c>
+      <c r="AM284">
+        <v>1.38</v>
+      </c>
+      <c r="AN284">
+        <v>0.5</v>
+      </c>
+      <c r="AO284">
+        <v>0.62</v>
+      </c>
+      <c r="AP284">
+        <v>0.53</v>
+      </c>
+      <c r="AQ284">
+        <v>0.64</v>
+      </c>
+      <c r="AR284">
+        <v>1.17</v>
+      </c>
+      <c r="AS284">
         <v>1.19</v>
       </c>
-      <c r="AL284">
-        <v>1.29</v>
-      </c>
-      <c r="AM284">
-        <v>2</v>
-      </c>
-      <c r="AN284">
-        <v>1.64</v>
-      </c>
-      <c r="AO284">
-        <v>0.93</v>
-      </c>
-      <c r="AP284">
-        <v>1.53</v>
-      </c>
-      <c r="AQ284">
-        <v>1.07</v>
-      </c>
-      <c r="AR284">
-        <v>1.25</v>
-      </c>
-      <c r="AS284">
-        <v>1.06</v>
-      </c>
       <c r="AT284">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AU284">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV284">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AW284">
         <v>8</v>
       </c>
       <c r="AX284">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY284">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ284">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="BA284">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BB284">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BC284">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="BD284">
+        <v>2.13</v>
+      </c>
+      <c r="BE284">
+        <v>6.45</v>
+      </c>
+      <c r="BF284">
+        <v>2.16</v>
+      </c>
+      <c r="BG284">
+        <v>1.24</v>
+      </c>
+      <c r="BH284">
+        <v>3.34</v>
+      </c>
+      <c r="BI284">
+        <v>1.48</v>
+      </c>
+      <c r="BJ284">
+        <v>2.4</v>
+      </c>
+      <c r="BK284">
+        <v>1.85</v>
+      </c>
+      <c r="BL284">
+        <v>1.85</v>
+      </c>
+      <c r="BM284">
+        <v>2.38</v>
+      </c>
+      <c r="BN284">
         <v>1.49</v>
       </c>
-      <c r="BE284">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF284">
-        <v>3.25</v>
-      </c>
-      <c r="BG284">
-        <v>1.22</v>
-      </c>
-      <c r="BH284">
-        <v>3.5</v>
-      </c>
-      <c r="BI284">
-        <v>1.44</v>
-      </c>
-      <c r="BJ284">
-        <v>2.51</v>
-      </c>
-      <c r="BK284">
-        <v>1.79</v>
-      </c>
-      <c r="BL284">
-        <v>1.92</v>
-      </c>
-      <c r="BM284">
-        <v>2.28</v>
-      </c>
-      <c r="BN284">
-        <v>1.53</v>
-      </c>
       <c r="BO284">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="BP284">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="285" spans="1:68">
@@ -60102,7 +60105,7 @@
         <v>266</v>
       </c>
       <c r="P285" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q285">
         <v>2.4</v>
@@ -60201,16 +60204,16 @@
         <v>7</v>
       </c>
       <c r="AW285">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX285">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AY285">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ285">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA285">
         <v>0</v>
@@ -60465,6 +60468,418 @@
       </c>
       <c r="BP286">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="287" spans="1:68">
+      <c r="A287" s="1">
+        <v>286</v>
+      </c>
+      <c r="B287">
+        <v>7492437</v>
+      </c>
+      <c r="C287" t="s">
+        <v>68</v>
+      </c>
+      <c r="D287" t="s">
+        <v>69</v>
+      </c>
+      <c r="E287" s="2">
+        <v>45732.35416666666</v>
+      </c>
+      <c r="F287">
+        <v>29</v>
+      </c>
+      <c r="G287" t="s">
+        <v>87</v>
+      </c>
+      <c r="H287" t="s">
+        <v>85</v>
+      </c>
+      <c r="I287">
+        <v>0</v>
+      </c>
+      <c r="J287">
+        <v>0</v>
+      </c>
+      <c r="K287">
+        <v>0</v>
+      </c>
+      <c r="L287">
+        <v>0</v>
+      </c>
+      <c r="M287">
+        <v>0</v>
+      </c>
+      <c r="N287">
+        <v>0</v>
+      </c>
+      <c r="O287" t="s">
+        <v>92</v>
+      </c>
+      <c r="P287" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q287">
+        <v>6.5</v>
+      </c>
+      <c r="R287">
+        <v>2.2</v>
+      </c>
+      <c r="S287">
+        <v>2.1</v>
+      </c>
+      <c r="T287">
+        <v>1.4</v>
+      </c>
+      <c r="U287">
+        <v>2.75</v>
+      </c>
+      <c r="V287">
+        <v>3</v>
+      </c>
+      <c r="W287">
+        <v>1.36</v>
+      </c>
+      <c r="X287">
+        <v>8</v>
+      </c>
+      <c r="Y287">
+        <v>1.08</v>
+      </c>
+      <c r="Z287">
+        <v>6.9</v>
+      </c>
+      <c r="AA287">
+        <v>4.2</v>
+      </c>
+      <c r="AB287">
+        <v>1.53</v>
+      </c>
+      <c r="AC287">
+        <v>1.05</v>
+      </c>
+      <c r="AD287">
+        <v>9</v>
+      </c>
+      <c r="AE287">
+        <v>1.3</v>
+      </c>
+      <c r="AF287">
+        <v>3.35</v>
+      </c>
+      <c r="AG287">
+        <v>2.02</v>
+      </c>
+      <c r="AH287">
+        <v>1.8</v>
+      </c>
+      <c r="AI287">
+        <v>2.1</v>
+      </c>
+      <c r="AJ287">
+        <v>1.67</v>
+      </c>
+      <c r="AK287">
+        <v>2.5</v>
+      </c>
+      <c r="AL287">
+        <v>1.23</v>
+      </c>
+      <c r="AM287">
+        <v>1.11</v>
+      </c>
+      <c r="AN287">
+        <v>1</v>
+      </c>
+      <c r="AO287">
+        <v>2</v>
+      </c>
+      <c r="AP287">
+        <v>1</v>
+      </c>
+      <c r="AQ287">
+        <v>1.93</v>
+      </c>
+      <c r="AR287">
+        <v>1.33</v>
+      </c>
+      <c r="AS287">
+        <v>1.18</v>
+      </c>
+      <c r="AT287">
+        <v>2.51</v>
+      </c>
+      <c r="AU287">
+        <v>5</v>
+      </c>
+      <c r="AV287">
+        <v>8</v>
+      </c>
+      <c r="AW287">
+        <v>9</v>
+      </c>
+      <c r="AX287">
+        <v>8</v>
+      </c>
+      <c r="AY287">
+        <v>17</v>
+      </c>
+      <c r="AZ287">
+        <v>18</v>
+      </c>
+      <c r="BA287">
+        <v>3</v>
+      </c>
+      <c r="BB287">
+        <v>8</v>
+      </c>
+      <c r="BC287">
+        <v>11</v>
+      </c>
+      <c r="BD287">
+        <v>4.3</v>
+      </c>
+      <c r="BE287">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BF287">
+        <v>1.33</v>
+      </c>
+      <c r="BG287">
+        <v>1.25</v>
+      </c>
+      <c r="BH287">
+        <v>3.28</v>
+      </c>
+      <c r="BI287">
+        <v>1.49</v>
+      </c>
+      <c r="BJ287">
+        <v>2.38</v>
+      </c>
+      <c r="BK287">
+        <v>1.86</v>
+      </c>
+      <c r="BL287">
+        <v>1.84</v>
+      </c>
+      <c r="BM287">
+        <v>2.4</v>
+      </c>
+      <c r="BN287">
+        <v>1.48</v>
+      </c>
+      <c r="BO287">
+        <v>3.2</v>
+      </c>
+      <c r="BP287">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="288" spans="1:68">
+      <c r="A288" s="1">
+        <v>287</v>
+      </c>
+      <c r="B288">
+        <v>7492429</v>
+      </c>
+      <c r="C288" t="s">
+        <v>68</v>
+      </c>
+      <c r="D288" t="s">
+        <v>69</v>
+      </c>
+      <c r="E288" s="2">
+        <v>45732.45833333334</v>
+      </c>
+      <c r="F288">
+        <v>29</v>
+      </c>
+      <c r="G288" t="s">
+        <v>74</v>
+      </c>
+      <c r="H288" t="s">
+        <v>77</v>
+      </c>
+      <c r="I288">
+        <v>1</v>
+      </c>
+      <c r="J288">
+        <v>0</v>
+      </c>
+      <c r="K288">
+        <v>1</v>
+      </c>
+      <c r="L288">
+        <v>5</v>
+      </c>
+      <c r="M288">
+        <v>0</v>
+      </c>
+      <c r="N288">
+        <v>5</v>
+      </c>
+      <c r="O288" t="s">
+        <v>267</v>
+      </c>
+      <c r="P288" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q288">
+        <v>3.1</v>
+      </c>
+      <c r="R288">
+        <v>2.05</v>
+      </c>
+      <c r="S288">
+        <v>3.75</v>
+      </c>
+      <c r="T288">
+        <v>1.5</v>
+      </c>
+      <c r="U288">
+        <v>2.5</v>
+      </c>
+      <c r="V288">
+        <v>3.4</v>
+      </c>
+      <c r="W288">
+        <v>1.3</v>
+      </c>
+      <c r="X288">
+        <v>10</v>
+      </c>
+      <c r="Y288">
+        <v>1.06</v>
+      </c>
+      <c r="Z288">
+        <v>2.46</v>
+      </c>
+      <c r="AA288">
+        <v>3.13</v>
+      </c>
+      <c r="AB288">
+        <v>3.23</v>
+      </c>
+      <c r="AC288">
+        <v>1.08</v>
+      </c>
+      <c r="AD288">
+        <v>7.5</v>
+      </c>
+      <c r="AE288">
+        <v>1.4</v>
+      </c>
+      <c r="AF288">
+        <v>2.9</v>
+      </c>
+      <c r="AG288">
+        <v>1.91</v>
+      </c>
+      <c r="AH288">
+        <v>1.83</v>
+      </c>
+      <c r="AI288">
+        <v>1.91</v>
+      </c>
+      <c r="AJ288">
+        <v>1.91</v>
+      </c>
+      <c r="AK288">
+        <v>1.35</v>
+      </c>
+      <c r="AL288">
+        <v>1.35</v>
+      </c>
+      <c r="AM288">
+        <v>1.55</v>
+      </c>
+      <c r="AN288">
+        <v>2.07</v>
+      </c>
+      <c r="AO288">
+        <v>1.79</v>
+      </c>
+      <c r="AP288">
+        <v>2.13</v>
+      </c>
+      <c r="AQ288">
+        <v>1.67</v>
+      </c>
+      <c r="AR288">
+        <v>1.79</v>
+      </c>
+      <c r="AS288">
+        <v>1.6</v>
+      </c>
+      <c r="AT288">
+        <v>3.39</v>
+      </c>
+      <c r="AU288">
+        <v>8</v>
+      </c>
+      <c r="AV288">
+        <v>3</v>
+      </c>
+      <c r="AW288">
+        <v>6</v>
+      </c>
+      <c r="AX288">
+        <v>5</v>
+      </c>
+      <c r="AY288">
+        <v>17</v>
+      </c>
+      <c r="AZ288">
+        <v>11</v>
+      </c>
+      <c r="BA288">
+        <v>7</v>
+      </c>
+      <c r="BB288">
+        <v>1</v>
+      </c>
+      <c r="BC288">
+        <v>8</v>
+      </c>
+      <c r="BD288">
+        <v>1.77</v>
+      </c>
+      <c r="BE288">
+        <v>8.4</v>
+      </c>
+      <c r="BF288">
+        <v>2.48</v>
+      </c>
+      <c r="BG288">
+        <v>1.3</v>
+      </c>
+      <c r="BH288">
+        <v>2.97</v>
+      </c>
+      <c r="BI288">
+        <v>1.57</v>
+      </c>
+      <c r="BJ288">
+        <v>2.19</v>
+      </c>
+      <c r="BK288">
+        <v>1.99</v>
+      </c>
+      <c r="BL288">
+        <v>1.73</v>
+      </c>
+      <c r="BM288">
+        <v>2.6</v>
+      </c>
+      <c r="BN288">
+        <v>1.41</v>
+      </c>
+      <c r="BO288">
+        <v>3.5</v>
+      </c>
+      <c r="BP288">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="395">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -820,6 +820,12 @@
     <t>['16', '48', '49', '74', '84']</t>
   </si>
   <si>
+    <t>['62']</t>
+  </si>
+  <si>
+    <t>['15', '18', '53']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1191,6 +1197,9 @@
   <si>
     <t>['29', '46', '66', '77']</t>
   </si>
+  <si>
+    <t>['54', '87']</t>
+  </si>
 </sst>
 </file>
 
@@ -1551,7 +1560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP288"/>
+  <dimension ref="A1:BP291"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1807,7 +1816,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1888,7 +1897,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ2">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2425,7 +2434,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2631,7 +2640,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -3249,7 +3258,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3455,7 +3464,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -4073,7 +4082,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4279,7 +4288,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4769,7 +4778,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>0.4</v>
@@ -5309,7 +5318,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5387,7 +5396,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ19">
         <v>0.93</v>
@@ -5721,7 +5730,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5802,7 +5811,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ21">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR21">
         <v>1.14</v>
@@ -5927,7 +5936,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6339,7 +6348,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6626,7 +6635,7 @@
         <v>1</v>
       </c>
       <c r="AQ25">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR25">
         <v>1.74</v>
@@ -6751,7 +6760,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6957,7 +6966,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7163,7 +7172,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7241,7 +7250,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ28">
         <v>0.5</v>
@@ -7369,7 +7378,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7987,7 +7996,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8274,7 +8283,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ33">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR33">
         <v>0.96</v>
@@ -8811,7 +8820,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -8889,7 +8898,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ36">
         <v>1.29</v>
@@ -9223,7 +9232,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9429,7 +9438,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9510,7 +9519,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ39">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR39">
         <v>1.18</v>
@@ -9635,7 +9644,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9841,7 +9850,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -10047,7 +10056,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10253,7 +10262,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10871,7 +10880,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -11077,7 +11086,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11155,7 +11164,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ47">
         <v>1.67</v>
@@ -11283,7 +11292,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11567,7 +11576,7 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ49">
         <v>1.21</v>
@@ -11695,7 +11704,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11901,7 +11910,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -11979,7 +11988,7 @@
         <v>0.33</v>
       </c>
       <c r="AP51">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ51">
         <v>0.67</v>
@@ -12313,7 +12322,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12394,7 +12403,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ53">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR53">
         <v>1.05</v>
@@ -12519,7 +12528,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12600,7 +12609,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ54">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR54">
         <v>1.48</v>
@@ -12725,7 +12734,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12931,7 +12940,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13137,7 +13146,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13421,7 +13430,7 @@
         <v>0.33</v>
       </c>
       <c r="AP58">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ58">
         <v>0.4</v>
@@ -13961,7 +13970,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14042,7 +14051,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ61">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR61">
         <v>1.23</v>
@@ -14785,7 +14794,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14863,7 +14872,7 @@
         <v>1.5</v>
       </c>
       <c r="AP65">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ65">
         <v>1.14</v>
@@ -14991,7 +15000,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15197,7 +15206,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15278,7 +15287,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ67">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR67">
         <v>1.09</v>
@@ -15815,7 +15824,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -16099,7 +16108,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ71">
         <v>1.43</v>
@@ -16433,7 +16442,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -17051,7 +17060,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17257,7 +17266,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17463,7 +17472,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17669,7 +17678,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17953,10 +17962,10 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ80">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR80">
         <v>2.02</v>
@@ -18081,7 +18090,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18368,7 +18377,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ82">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR82">
         <v>1.1</v>
@@ -18905,7 +18914,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -18983,7 +18992,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ85">
         <v>1.07</v>
@@ -19523,7 +19532,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19729,7 +19738,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19810,7 +19819,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ89">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR89">
         <v>1.46</v>
@@ -19935,7 +19944,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20013,7 +20022,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ90">
         <v>1.29</v>
@@ -20141,7 +20150,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20553,7 +20562,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20759,7 +20768,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20965,7 +20974,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -21046,7 +21055,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ95">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR95">
         <v>0.91</v>
@@ -21249,7 +21258,7 @@
         <v>1.25</v>
       </c>
       <c r="AP96">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ96">
         <v>0.5</v>
@@ -21377,7 +21386,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21583,7 +21592,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21789,7 +21798,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22073,7 +22082,7 @@
         <v>1.4</v>
       </c>
       <c r="AP100">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ100">
         <v>1.2</v>
@@ -22407,7 +22416,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22488,7 +22497,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ102">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR102">
         <v>1.16</v>
@@ -22819,7 +22828,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -23025,7 +23034,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23231,7 +23240,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -24055,7 +24064,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24136,7 +24145,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ110">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR110">
         <v>1.55</v>
@@ -24261,7 +24270,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24467,7 +24476,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24673,7 +24682,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24879,7 +24888,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25291,7 +25300,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25369,7 +25378,7 @@
         <v>0.8</v>
       </c>
       <c r="AP116">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ116">
         <v>1.21</v>
@@ -25497,7 +25506,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25575,7 +25584,7 @@
         <v>1.6</v>
       </c>
       <c r="AP117">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ117">
         <v>1.5</v>
@@ -25781,7 +25790,7 @@
         <v>0.6</v>
       </c>
       <c r="AP118">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ118">
         <v>1.07</v>
@@ -26321,7 +26330,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26402,7 +26411,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ121">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR121">
         <v>1.14</v>
@@ -26608,7 +26617,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ122">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR122">
         <v>1.69</v>
@@ -26733,7 +26742,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26939,7 +26948,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27020,7 +27029,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ124">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR124">
         <v>1.24</v>
@@ -27145,7 +27154,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27351,7 +27360,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27969,7 +27978,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -29205,7 +29214,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29411,7 +29420,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29823,7 +29832,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29904,7 +29913,7 @@
         <v>1</v>
       </c>
       <c r="AQ138">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR138">
         <v>1.39</v>
@@ -30029,7 +30038,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30107,7 +30116,7 @@
         <v>1.86</v>
       </c>
       <c r="AP139">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ139">
         <v>2.2</v>
@@ -30519,7 +30528,7 @@
         <v>1.33</v>
       </c>
       <c r="AP141">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ141">
         <v>1.43</v>
@@ -30853,7 +30862,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -31059,7 +31068,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31137,7 +31146,7 @@
         <v>0.57</v>
       </c>
       <c r="AP144">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ144">
         <v>0.73</v>
@@ -31343,10 +31352,10 @@
         <v>0.83</v>
       </c>
       <c r="AP145">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ145">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR145">
         <v>1.69</v>
@@ -31471,7 +31480,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31677,7 +31686,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -32089,7 +32098,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32501,7 +32510,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32707,7 +32716,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32913,7 +32922,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -33325,7 +33334,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -34149,7 +34158,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34230,7 +34239,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ159">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR159">
         <v>1.56</v>
@@ -34561,7 +34570,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34767,7 +34776,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34973,7 +34982,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35257,7 +35266,7 @@
         <v>1</v>
       </c>
       <c r="AP164">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ164">
         <v>0.64</v>
@@ -35385,7 +35394,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35466,7 +35475,7 @@
         <v>1</v>
       </c>
       <c r="AQ165">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR165">
         <v>1.48</v>
@@ -35591,7 +35600,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35669,7 +35678,7 @@
         <v>1.5</v>
       </c>
       <c r="AP166">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ166">
         <v>0.93</v>
@@ -35797,7 +35806,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35878,7 +35887,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ167">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR167">
         <v>1.14</v>
@@ -36003,7 +36012,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36081,7 +36090,7 @@
         <v>1</v>
       </c>
       <c r="AP168">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ168">
         <v>1.21</v>
@@ -36621,7 +36630,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36827,7 +36836,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36908,7 +36917,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ172">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR172">
         <v>1.46</v>
@@ -37033,7 +37042,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37239,7 +37248,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37651,7 +37660,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -38269,7 +38278,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38681,7 +38690,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38759,7 +38768,7 @@
         <v>2.22</v>
       </c>
       <c r="AP181">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ181">
         <v>1.93</v>
@@ -39093,7 +39102,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39174,7 +39183,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ183">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR183">
         <v>1.19</v>
@@ -39789,7 +39798,7 @@
         <v>1.67</v>
       </c>
       <c r="AP186">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ186">
         <v>1.67</v>
@@ -39917,7 +39926,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40329,7 +40338,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40616,7 +40625,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ190">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR190">
         <v>1.04</v>
@@ -40741,7 +40750,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -40822,7 +40831,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ191">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR191">
         <v>1.6</v>
@@ -41234,7 +41243,7 @@
         <v>1</v>
       </c>
       <c r="AQ193">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR193">
         <v>1.41</v>
@@ -41359,7 +41368,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41977,7 +41986,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42261,10 +42270,10 @@
         <v>1.89</v>
       </c>
       <c r="AP198">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ198">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR198">
         <v>1.78</v>
@@ -42389,7 +42398,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42595,7 +42604,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42673,7 +42682,7 @@
         <v>1.56</v>
       </c>
       <c r="AP200">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ200">
         <v>1.14</v>
@@ -42801,7 +42810,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -43213,7 +43222,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43291,7 +43300,7 @@
         <v>2.3</v>
       </c>
       <c r="AP203">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ203">
         <v>1.93</v>
@@ -43497,7 +43506,7 @@
         <v>1.2</v>
       </c>
       <c r="AP204">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ204">
         <v>1.2</v>
@@ -43625,7 +43634,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -44037,7 +44046,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44243,7 +44252,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44736,7 +44745,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ210">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR210">
         <v>1.04</v>
@@ -44861,7 +44870,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45148,7 +45157,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ212">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR212">
         <v>1.61</v>
@@ -45479,7 +45488,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45685,7 +45694,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45891,7 +45900,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -45972,7 +45981,7 @@
         <v>1</v>
       </c>
       <c r="AQ216">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR216">
         <v>1.3</v>
@@ -46097,7 +46106,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46303,7 +46312,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46715,7 +46724,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46921,7 +46930,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47333,7 +47342,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47411,7 +47420,7 @@
         <v>1.18</v>
       </c>
       <c r="AP223">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ223">
         <v>1.2</v>
@@ -47745,7 +47754,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47951,7 +47960,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -48029,7 +48038,7 @@
         <v>1.4</v>
       </c>
       <c r="AP226">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ226">
         <v>1.14</v>
@@ -48238,7 +48247,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ227">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR227">
         <v>1.73</v>
@@ -48363,7 +48372,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48441,7 +48450,7 @@
         <v>2.36</v>
       </c>
       <c r="AP228">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ228">
         <v>1.93</v>
@@ -48569,7 +48578,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48853,10 +48862,10 @@
         <v>2.45</v>
       </c>
       <c r="AP230">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ230">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR230">
         <v>1.55</v>
@@ -48981,7 +48990,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49062,7 +49071,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ231">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR231">
         <v>1.56</v>
@@ -49187,7 +49196,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49393,7 +49402,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49599,7 +49608,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -50217,7 +50226,7 @@
         <v>241</v>
       </c>
       <c r="P237" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q237">
         <v>1.91</v>
@@ -50629,7 +50638,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -51041,7 +51050,7 @@
         <v>244</v>
       </c>
       <c r="P241" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q241">
         <v>2.5</v>
@@ -51325,10 +51334,10 @@
         <v>0.82</v>
       </c>
       <c r="AP242">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ242">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR242">
         <v>1.88</v>
@@ -51453,7 +51462,7 @@
         <v>245</v>
       </c>
       <c r="P243" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q243">
         <v>3.4</v>
@@ -51865,7 +51874,7 @@
         <v>92</v>
       </c>
       <c r="P245" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q245">
         <v>2.6</v>
@@ -51943,7 +51952,7 @@
         <v>0.58</v>
       </c>
       <c r="AP245">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ245">
         <v>0.67</v>
@@ -52483,7 +52492,7 @@
         <v>92</v>
       </c>
       <c r="P248" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q248">
         <v>4</v>
@@ -52770,7 +52779,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ249">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR249">
         <v>1.57</v>
@@ -54131,7 +54140,7 @@
         <v>250</v>
       </c>
       <c r="P256" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q256">
         <v>4</v>
@@ -54543,7 +54552,7 @@
         <v>92</v>
       </c>
       <c r="P258" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q258">
         <v>6</v>
@@ -54749,7 +54758,7 @@
         <v>92</v>
       </c>
       <c r="P259" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q259">
         <v>4.75</v>
@@ -54830,7 +54839,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ259">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR259">
         <v>1.48</v>
@@ -55033,7 +55042,7 @@
         <v>0.58</v>
       </c>
       <c r="AP260">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ260">
         <v>0.5</v>
@@ -55445,7 +55454,7 @@
         <v>0.85</v>
       </c>
       <c r="AP262">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ262">
         <v>0.73</v>
@@ -55651,7 +55660,7 @@
         <v>0.31</v>
       </c>
       <c r="AP263">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ263">
         <v>0.4</v>
@@ -55860,7 +55869,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ264">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR264">
         <v>1.6</v>
@@ -56191,7 +56200,7 @@
         <v>92</v>
       </c>
       <c r="P266" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q266">
         <v>4.75</v>
@@ -56478,7 +56487,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ267">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR267">
         <v>1.79</v>
@@ -56887,7 +56896,7 @@
         <v>0.77</v>
       </c>
       <c r="AP269">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ269">
         <v>0.67</v>
@@ -57015,7 +57024,7 @@
         <v>146</v>
       </c>
       <c r="P270" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q270">
         <v>2.63</v>
@@ -57633,7 +57642,7 @@
         <v>260</v>
       </c>
       <c r="P273" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q273">
         <v>3.5</v>
@@ -58045,7 +58054,7 @@
         <v>261</v>
       </c>
       <c r="P275" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q275">
         <v>5</v>
@@ -58251,7 +58260,7 @@
         <v>262</v>
       </c>
       <c r="P276" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q276">
         <v>1.5</v>
@@ -58457,7 +58466,7 @@
         <v>103</v>
       </c>
       <c r="P277" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q277">
         <v>5.5</v>
@@ -58663,7 +58672,7 @@
         <v>263</v>
       </c>
       <c r="P278" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q278">
         <v>2.2</v>
@@ -58869,7 +58878,7 @@
         <v>92</v>
       </c>
       <c r="P279" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q279">
         <v>4</v>
@@ -59075,7 +59084,7 @@
         <v>92</v>
       </c>
       <c r="P280" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Q280">
         <v>3.1</v>
@@ -59487,7 +59496,7 @@
         <v>265</v>
       </c>
       <c r="P282" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q282">
         <v>2.75</v>
@@ -59693,7 +59702,7 @@
         <v>92</v>
       </c>
       <c r="P283" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q283">
         <v>2.4</v>
@@ -59899,7 +59908,7 @@
         <v>216</v>
       </c>
       <c r="P284" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q284">
         <v>3.6</v>
@@ -60105,7 +60114,7 @@
         <v>266</v>
       </c>
       <c r="P285" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q285">
         <v>2.4</v>
@@ -60880,6 +60889,624 @@
       </c>
       <c r="BP288">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="289" spans="1:68">
+      <c r="A289" s="1">
+        <v>288</v>
+      </c>
+      <c r="B289">
+        <v>7492434</v>
+      </c>
+      <c r="C289" t="s">
+        <v>68</v>
+      </c>
+      <c r="D289" t="s">
+        <v>69</v>
+      </c>
+      <c r="E289" s="2">
+        <v>45732.5</v>
+      </c>
+      <c r="F289">
+        <v>29</v>
+      </c>
+      <c r="G289" t="s">
+        <v>86</v>
+      </c>
+      <c r="H289" t="s">
+        <v>76</v>
+      </c>
+      <c r="I289">
+        <v>0</v>
+      </c>
+      <c r="J289">
+        <v>0</v>
+      </c>
+      <c r="K289">
+        <v>0</v>
+      </c>
+      <c r="L289">
+        <v>1</v>
+      </c>
+      <c r="M289">
+        <v>0</v>
+      </c>
+      <c r="N289">
+        <v>1</v>
+      </c>
+      <c r="O289" t="s">
+        <v>268</v>
+      </c>
+      <c r="P289" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q289">
+        <v>2.1</v>
+      </c>
+      <c r="R289">
+        <v>2.25</v>
+      </c>
+      <c r="S289">
+        <v>6</v>
+      </c>
+      <c r="T289">
+        <v>1.4</v>
+      </c>
+      <c r="U289">
+        <v>2.75</v>
+      </c>
+      <c r="V289">
+        <v>3</v>
+      </c>
+      <c r="W289">
+        <v>1.36</v>
+      </c>
+      <c r="X289">
+        <v>8</v>
+      </c>
+      <c r="Y289">
+        <v>1.08</v>
+      </c>
+      <c r="Z289">
+        <v>1.59</v>
+      </c>
+      <c r="AA289">
+        <v>4.1</v>
+      </c>
+      <c r="AB289">
+        <v>6</v>
+      </c>
+      <c r="AC289">
+        <v>1.05</v>
+      </c>
+      <c r="AD289">
+        <v>9.5</v>
+      </c>
+      <c r="AE289">
+        <v>1.3</v>
+      </c>
+      <c r="AF289">
+        <v>3.45</v>
+      </c>
+      <c r="AG289">
+        <v>1.95</v>
+      </c>
+      <c r="AH289">
+        <v>1.86</v>
+      </c>
+      <c r="AI289">
+        <v>2</v>
+      </c>
+      <c r="AJ289">
+        <v>1.75</v>
+      </c>
+      <c r="AK289">
+        <v>1.14</v>
+      </c>
+      <c r="AL289">
+        <v>1.24</v>
+      </c>
+      <c r="AM289">
+        <v>2.3</v>
+      </c>
+      <c r="AN289">
+        <v>2</v>
+      </c>
+      <c r="AO289">
+        <v>0.77</v>
+      </c>
+      <c r="AP289">
+        <v>2.07</v>
+      </c>
+      <c r="AQ289">
+        <v>0.71</v>
+      </c>
+      <c r="AR289">
+        <v>1.61</v>
+      </c>
+      <c r="AS289">
+        <v>0.97</v>
+      </c>
+      <c r="AT289">
+        <v>2.58</v>
+      </c>
+      <c r="AU289">
+        <v>2</v>
+      </c>
+      <c r="AV289">
+        <v>6</v>
+      </c>
+      <c r="AW289">
+        <v>12</v>
+      </c>
+      <c r="AX289">
+        <v>6</v>
+      </c>
+      <c r="AY289">
+        <v>19</v>
+      </c>
+      <c r="AZ289">
+        <v>16</v>
+      </c>
+      <c r="BA289">
+        <v>8</v>
+      </c>
+      <c r="BB289">
+        <v>3</v>
+      </c>
+      <c r="BC289">
+        <v>11</v>
+      </c>
+      <c r="BD289">
+        <v>1.33</v>
+      </c>
+      <c r="BE289">
+        <v>10</v>
+      </c>
+      <c r="BF289">
+        <v>4.25</v>
+      </c>
+      <c r="BG289">
+        <v>1.27</v>
+      </c>
+      <c r="BH289">
+        <v>3.14</v>
+      </c>
+      <c r="BI289">
+        <v>1.53</v>
+      </c>
+      <c r="BJ289">
+        <v>2.28</v>
+      </c>
+      <c r="BK289">
+        <v>1.92</v>
+      </c>
+      <c r="BL289">
+        <v>1.79</v>
+      </c>
+      <c r="BM289">
+        <v>2.5</v>
+      </c>
+      <c r="BN289">
+        <v>1.44</v>
+      </c>
+      <c r="BO289">
+        <v>3.34</v>
+      </c>
+      <c r="BP289">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="290" spans="1:68">
+      <c r="A290" s="1">
+        <v>289</v>
+      </c>
+      <c r="B290">
+        <v>7492430</v>
+      </c>
+      <c r="C290" t="s">
+        <v>68</v>
+      </c>
+      <c r="D290" t="s">
+        <v>69</v>
+      </c>
+      <c r="E290" s="2">
+        <v>45732.58333333334</v>
+      </c>
+      <c r="F290">
+        <v>29</v>
+      </c>
+      <c r="G290" t="s">
+        <v>83</v>
+      </c>
+      <c r="H290" t="s">
+        <v>79</v>
+      </c>
+      <c r="I290">
+        <v>2</v>
+      </c>
+      <c r="J290">
+        <v>0</v>
+      </c>
+      <c r="K290">
+        <v>2</v>
+      </c>
+      <c r="L290">
+        <v>3</v>
+      </c>
+      <c r="M290">
+        <v>0</v>
+      </c>
+      <c r="N290">
+        <v>3</v>
+      </c>
+      <c r="O290" t="s">
+        <v>269</v>
+      </c>
+      <c r="P290" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q290">
+        <v>4</v>
+      </c>
+      <c r="R290">
+        <v>2</v>
+      </c>
+      <c r="S290">
+        <v>3</v>
+      </c>
+      <c r="T290">
+        <v>1.5</v>
+      </c>
+      <c r="U290">
+        <v>2.5</v>
+      </c>
+      <c r="V290">
+        <v>3.4</v>
+      </c>
+      <c r="W290">
+        <v>1.3</v>
+      </c>
+      <c r="X290">
+        <v>10</v>
+      </c>
+      <c r="Y290">
+        <v>1.06</v>
+      </c>
+      <c r="Z290">
+        <v>3.41</v>
+      </c>
+      <c r="AA290">
+        <v>3.32</v>
+      </c>
+      <c r="AB290">
+        <v>2.26</v>
+      </c>
+      <c r="AC290">
+        <v>1.08</v>
+      </c>
+      <c r="AD290">
+        <v>7.5</v>
+      </c>
+      <c r="AE290">
+        <v>1.42</v>
+      </c>
+      <c r="AF290">
+        <v>2.8</v>
+      </c>
+      <c r="AG290">
+        <v>2.1</v>
+      </c>
+      <c r="AH290">
+        <v>1.67</v>
+      </c>
+      <c r="AI290">
+        <v>1.95</v>
+      </c>
+      <c r="AJ290">
+        <v>1.8</v>
+      </c>
+      <c r="AK290">
+        <v>1.65</v>
+      </c>
+      <c r="AL290">
+        <v>1.33</v>
+      </c>
+      <c r="AM290">
+        <v>1.3</v>
+      </c>
+      <c r="AN290">
+        <v>1.93</v>
+      </c>
+      <c r="AO290">
+        <v>1.85</v>
+      </c>
+      <c r="AP290">
+        <v>2</v>
+      </c>
+      <c r="AQ290">
+        <v>1.71</v>
+      </c>
+      <c r="AR290">
+        <v>1.49</v>
+      </c>
+      <c r="AS290">
+        <v>1.33</v>
+      </c>
+      <c r="AT290">
+        <v>2.82</v>
+      </c>
+      <c r="AU290">
+        <v>4</v>
+      </c>
+      <c r="AV290">
+        <v>3</v>
+      </c>
+      <c r="AW290">
+        <v>6</v>
+      </c>
+      <c r="AX290">
+        <v>9</v>
+      </c>
+      <c r="AY290">
+        <v>11</v>
+      </c>
+      <c r="AZ290">
+        <v>15</v>
+      </c>
+      <c r="BA290">
+        <v>1</v>
+      </c>
+      <c r="BB290">
+        <v>6</v>
+      </c>
+      <c r="BC290">
+        <v>7</v>
+      </c>
+      <c r="BD290">
+        <v>2.05</v>
+      </c>
+      <c r="BE290">
+        <v>6.3</v>
+      </c>
+      <c r="BF290">
+        <v>2.27</v>
+      </c>
+      <c r="BG290">
+        <v>1.38</v>
+      </c>
+      <c r="BH290">
+        <v>2.71</v>
+      </c>
+      <c r="BI290">
+        <v>1.7</v>
+      </c>
+      <c r="BJ290">
+        <v>2.03</v>
+      </c>
+      <c r="BK290">
+        <v>2.15</v>
+      </c>
+      <c r="BL290">
+        <v>1.59</v>
+      </c>
+      <c r="BM290">
+        <v>2.88</v>
+      </c>
+      <c r="BN290">
+        <v>1.32</v>
+      </c>
+      <c r="BO290">
+        <v>4.1</v>
+      </c>
+      <c r="BP290">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="291" spans="1:68">
+      <c r="A291" s="1">
+        <v>290</v>
+      </c>
+      <c r="B291">
+        <v>7492428</v>
+      </c>
+      <c r="C291" t="s">
+        <v>68</v>
+      </c>
+      <c r="D291" t="s">
+        <v>69</v>
+      </c>
+      <c r="E291" s="2">
+        <v>45732.69791666666</v>
+      </c>
+      <c r="F291">
+        <v>29</v>
+      </c>
+      <c r="G291" t="s">
+        <v>89</v>
+      </c>
+      <c r="H291" t="s">
+        <v>82</v>
+      </c>
+      <c r="I291">
+        <v>0</v>
+      </c>
+      <c r="J291">
+        <v>0</v>
+      </c>
+      <c r="K291">
+        <v>0</v>
+      </c>
+      <c r="L291">
+        <v>0</v>
+      </c>
+      <c r="M291">
+        <v>2</v>
+      </c>
+      <c r="N291">
+        <v>2</v>
+      </c>
+      <c r="O291" t="s">
+        <v>92</v>
+      </c>
+      <c r="P291" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q291">
+        <v>3.2</v>
+      </c>
+      <c r="R291">
+        <v>2.2</v>
+      </c>
+      <c r="S291">
+        <v>3.25</v>
+      </c>
+      <c r="T291">
+        <v>1.4</v>
+      </c>
+      <c r="U291">
+        <v>2.75</v>
+      </c>
+      <c r="V291">
+        <v>2.75</v>
+      </c>
+      <c r="W291">
+        <v>1.4</v>
+      </c>
+      <c r="X291">
+        <v>8</v>
+      </c>
+      <c r="Y291">
+        <v>1.08</v>
+      </c>
+      <c r="Z291">
+        <v>2.66</v>
+      </c>
+      <c r="AA291">
+        <v>3.45</v>
+      </c>
+      <c r="AB291">
+        <v>2.7</v>
+      </c>
+      <c r="AC291">
+        <v>1.05</v>
+      </c>
+      <c r="AD291">
+        <v>9</v>
+      </c>
+      <c r="AE291">
+        <v>1.28</v>
+      </c>
+      <c r="AF291">
+        <v>3.55</v>
+      </c>
+      <c r="AG291">
+        <v>1.84</v>
+      </c>
+      <c r="AH291">
+        <v>1.97</v>
+      </c>
+      <c r="AI291">
+        <v>1.7</v>
+      </c>
+      <c r="AJ291">
+        <v>2.05</v>
+      </c>
+      <c r="AK291">
+        <v>1.47</v>
+      </c>
+      <c r="AL291">
+        <v>1.31</v>
+      </c>
+      <c r="AM291">
+        <v>1.47</v>
+      </c>
+      <c r="AN291">
+        <v>1.92</v>
+      </c>
+      <c r="AO291">
+        <v>2</v>
+      </c>
+      <c r="AP291">
+        <v>1.79</v>
+      </c>
+      <c r="AQ291">
+        <v>2.07</v>
+      </c>
+      <c r="AR291">
+        <v>1.86</v>
+      </c>
+      <c r="AS291">
+        <v>1.54</v>
+      </c>
+      <c r="AT291">
+        <v>3.4</v>
+      </c>
+      <c r="AU291">
+        <v>4</v>
+      </c>
+      <c r="AV291">
+        <v>6</v>
+      </c>
+      <c r="AW291">
+        <v>13</v>
+      </c>
+      <c r="AX291">
+        <v>9</v>
+      </c>
+      <c r="AY291">
+        <v>22</v>
+      </c>
+      <c r="AZ291">
+        <v>19</v>
+      </c>
+      <c r="BA291">
+        <v>2</v>
+      </c>
+      <c r="BB291">
+        <v>6</v>
+      </c>
+      <c r="BC291">
+        <v>8</v>
+      </c>
+      <c r="BD291">
+        <v>1.68</v>
+      </c>
+      <c r="BE291">
+        <v>6.55</v>
+      </c>
+      <c r="BF291">
+        <v>2.94</v>
+      </c>
+      <c r="BG291">
+        <v>1.4</v>
+      </c>
+      <c r="BH291">
+        <v>2.64</v>
+      </c>
+      <c r="BI291">
+        <v>1.75</v>
+      </c>
+      <c r="BJ291">
+        <v>1.96</v>
+      </c>
+      <c r="BK291">
+        <v>2.23</v>
+      </c>
+      <c r="BL291">
+        <v>1.55</v>
+      </c>
+      <c r="BM291">
+        <v>3.04</v>
+      </c>
+      <c r="BN291">
+        <v>1.29</v>
+      </c>
+      <c r="BO291">
+        <v>4.3</v>
+      </c>
+      <c r="BP291">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1850" uniqueCount="399">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -826,6 +826,18 @@
     <t>['15', '18', '53']</t>
   </si>
   <si>
+    <t>['61']</t>
+  </si>
+  <si>
+    <t>['25']</t>
+  </si>
+  <si>
+    <t>['49', '73', '90+2']</t>
+  </si>
+  <si>
+    <t>['12', '29']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -929,9 +941,6 @@
   </si>
   <si>
     <t>['36', '87']</t>
-  </si>
-  <si>
-    <t>['61']</t>
   </si>
   <si>
     <t>['37', '56']</t>
@@ -1199,6 +1208,9 @@
   </si>
   <si>
     <t>['54', '87']</t>
+  </si>
+  <si>
+    <t>['71']</t>
   </si>
 </sst>
 </file>
@@ -1560,7 +1572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP291"/>
+  <dimension ref="A1:BP298"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1816,7 +1828,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2309,7 +2321,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ4">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2434,7 +2446,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2640,7 +2652,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2721,7 +2733,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ6">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -3130,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ8">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3258,7 +3270,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3464,7 +3476,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3542,10 +3554,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ10">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3748,7 +3760,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ11">
         <v>0.67</v>
@@ -4082,7 +4094,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4288,7 +4300,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4369,7 +4381,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ14">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4572,7 +4584,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ15">
         <v>0.73</v>
@@ -4778,7 +4790,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ16">
         <v>0.4</v>
@@ -4987,7 +4999,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ17">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5193,7 +5205,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ18">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5318,7 +5330,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5399,7 +5411,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ19">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5602,7 +5614,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ20">
         <v>0.67</v>
@@ -5730,7 +5742,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5936,7 +5948,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6014,7 +6026,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ22">
         <v>1.2</v>
@@ -6220,10 +6232,10 @@
         <v>1.5</v>
       </c>
       <c r="AP23">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ23">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR23">
         <v>1.3</v>
@@ -6348,7 +6360,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6429,7 +6441,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ24">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR24">
         <v>2.04</v>
@@ -6632,7 +6644,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ25">
         <v>0.71</v>
@@ -6760,7 +6772,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6966,7 +6978,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7172,7 +7184,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7250,10 +7262,10 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ28">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR28">
         <v>1.74</v>
@@ -7378,7 +7390,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7662,10 +7674,10 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ30">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR30">
         <v>1.66</v>
@@ -7996,7 +8008,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8074,10 +8086,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ32">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR32">
         <v>0</v>
@@ -8695,7 +8707,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ35">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR35">
         <v>1.23</v>
@@ -8820,7 +8832,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -9232,7 +9244,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9310,7 +9322,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ38">
         <v>1.93</v>
@@ -9438,7 +9450,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9644,7 +9656,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9725,7 +9737,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ40">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR40">
         <v>1.32</v>
@@ -9850,7 +9862,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -10056,7 +10068,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10134,10 +10146,10 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ42">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR42">
         <v>1.4</v>
@@ -10262,7 +10274,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10546,10 +10558,10 @@
         <v>3</v>
       </c>
       <c r="AP44">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ44">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR44">
         <v>1.37</v>
@@ -10752,7 +10764,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ45">
         <v>1.93</v>
@@ -10880,7 +10892,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10958,7 +10970,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ46">
         <v>0.64</v>
@@ -11086,7 +11098,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11164,7 +11176,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ47">
         <v>1.67</v>
@@ -11292,7 +11304,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11373,7 +11385,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ48">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR48">
         <v>0.9399999999999999</v>
@@ -11579,7 +11591,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ49">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR49">
         <v>2.26</v>
@@ -11704,7 +11716,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11782,7 +11794,7 @@
         <v>0.5</v>
       </c>
       <c r="AP50">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ50">
         <v>1.43</v>
@@ -11910,7 +11922,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12322,7 +12334,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12528,7 +12540,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12734,7 +12746,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12815,7 +12827,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ55">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR55">
         <v>1.78</v>
@@ -12940,7 +12952,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13146,7 +13158,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13224,7 +13236,7 @@
         <v>1.5</v>
       </c>
       <c r="AP57">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ57">
         <v>1.07</v>
@@ -13845,7 +13857,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ60">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR60">
         <v>1.84</v>
@@ -13970,7 +13982,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14794,7 +14806,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14875,7 +14887,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ65">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR65">
         <v>1.65</v>
@@ -15000,7 +15012,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15078,7 +15090,7 @@
         <v>2.33</v>
       </c>
       <c r="AP66">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ66">
         <v>1.2</v>
@@ -15206,7 +15218,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15284,7 +15296,7 @@
         <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ67">
         <v>0.71</v>
@@ -15493,7 +15505,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ68">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR68">
         <v>1.44</v>
@@ -15824,7 +15836,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>305</v>
+        <v>270</v>
       </c>
       <c r="Q70">
         <v>4.75</v>
@@ -15905,7 +15917,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ70">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR70">
         <v>0.9399999999999999</v>
@@ -16108,7 +16120,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ71">
         <v>1.43</v>
@@ -16314,7 +16326,7 @@
         <v>0.67</v>
       </c>
       <c r="AP72">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ72">
         <v>0.64</v>
@@ -16442,7 +16454,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16523,7 +16535,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ73">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR73">
         <v>1.29</v>
@@ -16729,7 +16741,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ74">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR74">
         <v>1.89</v>
@@ -16932,7 +16944,7 @@
         <v>1</v>
       </c>
       <c r="AP75">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ75">
         <v>1.67</v>
@@ -17060,7 +17072,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17266,7 +17278,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17344,7 +17356,7 @@
         <v>0.67</v>
       </c>
       <c r="AP77">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ77">
         <v>1.29</v>
@@ -17472,7 +17484,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17550,10 +17562,10 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ78">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR78">
         <v>1.31</v>
@@ -17678,7 +17690,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17756,7 +17768,7 @@
         <v>1.75</v>
       </c>
       <c r="AP79">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ79">
         <v>1.2</v>
@@ -18090,7 +18102,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18171,7 +18183,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ81">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR81">
         <v>1.08</v>
@@ -18914,7 +18926,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19201,7 +19213,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ86">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR86">
         <v>1.33</v>
@@ -19407,7 +19419,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ87">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR87">
         <v>1.49</v>
@@ -19532,7 +19544,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19738,7 +19750,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19816,7 +19828,7 @@
         <v>2.33</v>
       </c>
       <c r="AP89">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ89">
         <v>1.71</v>
@@ -19944,7 +19956,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20022,10 +20034,10 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ90">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR90">
         <v>1.56</v>
@@ -20150,7 +20162,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20228,10 +20240,10 @@
         <v>1.25</v>
       </c>
       <c r="AP91">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ91">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR91">
         <v>1.35</v>
@@ -20434,7 +20446,7 @@
         <v>0.75</v>
       </c>
       <c r="AP92">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ92">
         <v>1.07</v>
@@ -20562,7 +20574,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20768,7 +20780,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20846,10 +20858,10 @@
         <v>1</v>
       </c>
       <c r="AP94">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ94">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR94">
         <v>1.33</v>
@@ -20974,7 +20986,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -21261,7 +21273,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ96">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR96">
         <v>1.88</v>
@@ -21386,7 +21398,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21464,7 +21476,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ97">
         <v>0.64</v>
@@ -21592,7 +21604,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21798,7 +21810,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21876,7 +21888,7 @@
         <v>0.75</v>
       </c>
       <c r="AP99">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ99">
         <v>1.67</v>
@@ -22416,7 +22428,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22828,7 +22840,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22909,7 +22921,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ104">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR104">
         <v>1.61</v>
@@ -23034,7 +23046,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23240,7 +23252,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23321,7 +23333,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ106">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR106">
         <v>1.19</v>
@@ -23524,7 +23536,7 @@
         <v>0.33</v>
       </c>
       <c r="AP107">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ107">
         <v>0.4</v>
@@ -23939,7 +23951,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ109">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR109">
         <v>1.36</v>
@@ -24064,7 +24076,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24270,7 +24282,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24476,7 +24488,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24554,10 +24566,10 @@
         <v>1.6</v>
       </c>
       <c r="AP112">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ112">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR112">
         <v>1.28</v>
@@ -24682,7 +24694,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24760,7 +24772,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ113">
         <v>0.64</v>
@@ -24888,7 +24900,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -24966,7 +24978,7 @@
         <v>1.4</v>
       </c>
       <c r="AP114">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ114">
         <v>1.43</v>
@@ -25172,7 +25184,7 @@
         <v>1.17</v>
       </c>
       <c r="AP115">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ115">
         <v>1.2</v>
@@ -25300,7 +25312,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25381,7 +25393,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ116">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR116">
         <v>1.85</v>
@@ -25506,7 +25518,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25587,7 +25599,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ117">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR117">
         <v>1.63</v>
@@ -25790,7 +25802,7 @@
         <v>0.6</v>
       </c>
       <c r="AP118">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ118">
         <v>1.07</v>
@@ -26202,7 +26214,7 @@
         <v>2</v>
       </c>
       <c r="AP120">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ120">
         <v>1.93</v>
@@ -26330,7 +26342,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26742,7 +26754,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26823,7 +26835,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ123">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR123">
         <v>1.29</v>
@@ -26948,7 +26960,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27154,7 +27166,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27232,7 +27244,7 @@
         <v>1.83</v>
       </c>
       <c r="AP125">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ125">
         <v>1.29</v>
@@ -27360,7 +27372,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27441,7 +27453,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ126">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR126">
         <v>1.11</v>
@@ -27647,7 +27659,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ127">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR127">
         <v>1.54</v>
@@ -27853,7 +27865,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ128">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR128">
         <v>1.58</v>
@@ -27978,7 +27990,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -28059,7 +28071,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ129">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR129">
         <v>0.88</v>
@@ -28262,7 +28274,7 @@
         <v>0.17</v>
       </c>
       <c r="AP130">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ130">
         <v>0.73</v>
@@ -28468,7 +28480,7 @@
         <v>0.5</v>
       </c>
       <c r="AP131">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ131">
         <v>1.07</v>
@@ -28674,10 +28686,10 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ132">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR132">
         <v>1.48</v>
@@ -28883,7 +28895,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ133">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR133">
         <v>1.55</v>
@@ -29214,7 +29226,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29295,7 +29307,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ135">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR135">
         <v>1.11</v>
@@ -29420,7 +29432,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29832,7 +29844,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29910,7 +29922,7 @@
         <v>2</v>
       </c>
       <c r="AP138">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ138">
         <v>1.71</v>
@@ -30038,7 +30050,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30119,7 +30131,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ139">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR139">
         <v>1.59</v>
@@ -30322,7 +30334,7 @@
         <v>1.17</v>
       </c>
       <c r="AP140">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ140">
         <v>0.64</v>
@@ -30862,7 +30874,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30940,10 +30952,10 @@
         <v>1.57</v>
       </c>
       <c r="AP143">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ143">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR143">
         <v>1.47</v>
@@ -31068,7 +31080,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31352,7 +31364,7 @@
         <v>0.83</v>
       </c>
       <c r="AP145">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ145">
         <v>0.71</v>
@@ -31480,7 +31492,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31561,7 +31573,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ146">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR146">
         <v>1.08</v>
@@ -31686,7 +31698,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31764,7 +31776,7 @@
         <v>0.63</v>
       </c>
       <c r="AP147">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ147">
         <v>0.67</v>
@@ -32098,7 +32110,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32179,7 +32191,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ149">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR149">
         <v>1</v>
@@ -32510,7 +32522,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32588,10 +32600,10 @@
         <v>2</v>
       </c>
       <c r="AP151">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ151">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR151">
         <v>1.42</v>
@@ -32716,7 +32728,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32922,7 +32934,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -33000,7 +33012,7 @@
         <v>0.25</v>
       </c>
       <c r="AP153">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ153">
         <v>0.4</v>
@@ -33206,10 +33218,10 @@
         <v>1</v>
       </c>
       <c r="AP154">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ154">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR154">
         <v>1.38</v>
@@ -33334,7 +33346,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -33824,10 +33836,10 @@
         <v>0.57</v>
       </c>
       <c r="AP157">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ157">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR157">
         <v>1.44</v>
@@ -34033,7 +34045,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ158">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR158">
         <v>1.52</v>
@@ -34158,7 +34170,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34570,7 +34582,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34651,7 +34663,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ161">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR161">
         <v>1.07</v>
@@ -34776,7 +34788,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34982,7 +34994,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35060,7 +35072,7 @@
         <v>1.5</v>
       </c>
       <c r="AP163">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ163">
         <v>1.67</v>
@@ -35394,7 +35406,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35472,7 +35484,7 @@
         <v>0.71</v>
       </c>
       <c r="AP165">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ165">
         <v>0.71</v>
@@ -35600,7 +35612,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35681,7 +35693,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ166">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR166">
         <v>1.76</v>
@@ -35806,7 +35818,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -36012,7 +36024,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36090,10 +36102,10 @@
         <v>1</v>
       </c>
       <c r="AP168">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ168">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR168">
         <v>1.6</v>
@@ -36296,7 +36308,7 @@
         <v>0.67</v>
       </c>
       <c r="AP169">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ169">
         <v>0.67</v>
@@ -36505,7 +36517,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ170">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR170">
         <v>1.34</v>
@@ -36630,7 +36642,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36711,7 +36723,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ171">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR171">
         <v>0.88</v>
@@ -36836,7 +36848,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36914,7 +36926,7 @@
         <v>2.43</v>
       </c>
       <c r="AP172">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ172">
         <v>2.07</v>
@@ -37042,7 +37054,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37123,7 +37135,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ173">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR173">
         <v>1.48</v>
@@ -37248,7 +37260,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37660,7 +37672,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -37738,7 +37750,7 @@
         <v>1.75</v>
       </c>
       <c r="AP176">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ176">
         <v>1.29</v>
@@ -37947,7 +37959,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ177">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR177">
         <v>1.56</v>
@@ -38150,7 +38162,7 @@
         <v>0.5</v>
       </c>
       <c r="AP178">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ178">
         <v>0.73</v>
@@ -38278,7 +38290,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38562,10 +38574,10 @@
         <v>1.33</v>
       </c>
       <c r="AP180">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ180">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR180">
         <v>1.47</v>
@@ -38690,7 +38702,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38768,7 +38780,7 @@
         <v>2.22</v>
       </c>
       <c r="AP181">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ181">
         <v>1.93</v>
@@ -38977,7 +38989,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ182">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR182">
         <v>1.12</v>
@@ -39102,7 +39114,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39386,10 +39398,10 @@
         <v>1.63</v>
       </c>
       <c r="AP184">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ184">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR184">
         <v>1.31</v>
@@ -39926,7 +39938,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40213,7 +40225,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ188">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR188">
         <v>1.04</v>
@@ -40338,7 +40350,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40750,7 +40762,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41240,7 +41252,7 @@
         <v>2.5</v>
       </c>
       <c r="AP193">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ193">
         <v>2.07</v>
@@ -41368,7 +41380,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41449,7 +41461,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ194">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR194">
         <v>1.66</v>
@@ -41986,7 +41998,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42064,7 +42076,7 @@
         <v>1.38</v>
       </c>
       <c r="AP197">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ197">
         <v>1.43</v>
@@ -42398,7 +42410,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42476,10 +42488,10 @@
         <v>1.67</v>
       </c>
       <c r="AP199">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ199">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR199">
         <v>1.57</v>
@@ -42604,7 +42616,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42685,7 +42697,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ200">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR200">
         <v>1.55</v>
@@ -42810,7 +42822,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -42891,7 +42903,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ201">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR201">
         <v>1.71</v>
@@ -43094,7 +43106,7 @@
         <v>1.56</v>
       </c>
       <c r="AP202">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ202">
         <v>1.43</v>
@@ -43222,7 +43234,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43506,7 +43518,7 @@
         <v>1.2</v>
       </c>
       <c r="AP204">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ204">
         <v>1.2</v>
@@ -43634,7 +43646,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43712,7 +43724,7 @@
         <v>0.7</v>
       </c>
       <c r="AP205">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ205">
         <v>0.73</v>
@@ -44046,7 +44058,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44252,7 +44264,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44330,10 +44342,10 @@
         <v>1.3</v>
       </c>
       <c r="AP208">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ208">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR208">
         <v>1.57</v>
@@ -44536,10 +44548,10 @@
         <v>1.2</v>
       </c>
       <c r="AP209">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ209">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR209">
         <v>1.52</v>
@@ -44870,7 +44882,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -44948,10 +44960,10 @@
         <v>1.91</v>
       </c>
       <c r="AP211">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ211">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR211">
         <v>1.53</v>
@@ -45363,7 +45375,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ213">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR213">
         <v>1.04</v>
@@ -45488,7 +45500,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45694,7 +45706,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45775,7 +45787,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ215">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR215">
         <v>1.04</v>
@@ -45900,7 +45912,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -45978,7 +45990,7 @@
         <v>2.56</v>
       </c>
       <c r="AP216">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ216">
         <v>2.07</v>
@@ -46106,7 +46118,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46312,7 +46324,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46390,7 +46402,7 @@
         <v>0.9</v>
       </c>
       <c r="AP218">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ218">
         <v>1.07</v>
@@ -46599,7 +46611,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ219">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR219">
         <v>1.25</v>
@@ -46724,7 +46736,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46930,7 +46942,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47342,7 +47354,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47754,7 +47766,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47832,10 +47844,10 @@
         <v>1.18</v>
       </c>
       <c r="AP225">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ225">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR225">
         <v>1.48</v>
@@ -47960,7 +47972,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -48038,10 +48050,10 @@
         <v>1.4</v>
       </c>
       <c r="AP226">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ226">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR226">
         <v>1.59</v>
@@ -48372,7 +48384,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48578,7 +48590,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48656,7 +48668,7 @@
         <v>1.64</v>
       </c>
       <c r="AP229">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ229">
         <v>1.67</v>
@@ -48862,7 +48874,7 @@
         <v>2.45</v>
       </c>
       <c r="AP230">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ230">
         <v>2.07</v>
@@ -48990,7 +49002,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49068,7 +49080,7 @@
         <v>1.64</v>
       </c>
       <c r="AP231">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ231">
         <v>1.71</v>
@@ -49196,7 +49208,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49277,7 +49289,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ232">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR232">
         <v>1.18</v>
@@ -49402,7 +49414,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49608,7 +49620,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -49689,7 +49701,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ234">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR234">
         <v>1.14</v>
@@ -49892,10 +49904,10 @@
         <v>0.82</v>
       </c>
       <c r="AP235">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ235">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR235">
         <v>1.34</v>
@@ -50098,7 +50110,7 @@
         <v>0.73</v>
       </c>
       <c r="AP236">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ236">
         <v>0.64</v>
@@ -50226,7 +50238,7 @@
         <v>241</v>
       </c>
       <c r="P237" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q237">
         <v>1.91</v>
@@ -50307,7 +50319,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ237">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR237">
         <v>1.52</v>
@@ -50510,10 +50522,10 @@
         <v>1.55</v>
       </c>
       <c r="AP238">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ238">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR238">
         <v>1.34</v>
@@ -50638,7 +50650,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -50719,7 +50731,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ239">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR239">
         <v>1.57</v>
@@ -50922,7 +50934,7 @@
         <v>1.64</v>
       </c>
       <c r="AP240">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ240">
         <v>1.29</v>
@@ -51050,7 +51062,7 @@
         <v>244</v>
       </c>
       <c r="P241" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q241">
         <v>2.5</v>
@@ -51462,7 +51474,7 @@
         <v>245</v>
       </c>
       <c r="P243" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q243">
         <v>3.4</v>
@@ -51874,7 +51886,7 @@
         <v>92</v>
       </c>
       <c r="P245" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="Q245">
         <v>2.6</v>
@@ -51952,7 +51964,7 @@
         <v>0.58</v>
       </c>
       <c r="AP245">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ245">
         <v>0.67</v>
@@ -52367,7 +52379,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ247">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR247">
         <v>1.1</v>
@@ -52492,7 +52504,7 @@
         <v>92</v>
       </c>
       <c r="P248" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q248">
         <v>4</v>
@@ -52573,7 +52585,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ248">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR248">
         <v>1.44</v>
@@ -52776,7 +52788,7 @@
         <v>2.25</v>
       </c>
       <c r="AP249">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ249">
         <v>2.07</v>
@@ -53188,10 +53200,10 @@
         <v>1.08</v>
       </c>
       <c r="AP251">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ251">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR251">
         <v>1.3</v>
@@ -53397,7 +53409,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ252">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR252">
         <v>1.39</v>
@@ -53600,7 +53612,7 @@
         <v>1.75</v>
       </c>
       <c r="AP253">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ253">
         <v>1.67</v>
@@ -54012,10 +54024,10 @@
         <v>1.25</v>
       </c>
       <c r="AP255">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ255">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR255">
         <v>1.71</v>
@@ -54140,7 +54152,7 @@
         <v>250</v>
       </c>
       <c r="P256" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q256">
         <v>4</v>
@@ -54218,7 +54230,7 @@
         <v>2.15</v>
       </c>
       <c r="AP256">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ256">
         <v>1.93</v>
@@ -54552,7 +54564,7 @@
         <v>92</v>
       </c>
       <c r="P258" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="Q258">
         <v>6</v>
@@ -54633,7 +54645,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ258">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR258">
         <v>0.97</v>
@@ -54758,7 +54770,7 @@
         <v>92</v>
       </c>
       <c r="P259" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Q259">
         <v>4.75</v>
@@ -54836,7 +54848,7 @@
         <v>1.75</v>
       </c>
       <c r="AP259">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ259">
         <v>1.71</v>
@@ -55045,7 +55057,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ260">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR260">
         <v>1.56</v>
@@ -55454,7 +55466,7 @@
         <v>0.85</v>
       </c>
       <c r="AP262">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ262">
         <v>0.73</v>
@@ -56200,7 +56212,7 @@
         <v>92</v>
       </c>
       <c r="P266" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="Q266">
         <v>4.75</v>
@@ -56693,7 +56705,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ268">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR268">
         <v>1.35</v>
@@ -57024,7 +57036,7 @@
         <v>146</v>
       </c>
       <c r="P270" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Q270">
         <v>2.63</v>
@@ -57308,7 +57320,7 @@
         <v>1</v>
       </c>
       <c r="AP271">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ271">
         <v>1.07</v>
@@ -57514,10 +57526,10 @@
         <v>1.15</v>
       </c>
       <c r="AP272">
+        <v>1.19</v>
+      </c>
+      <c r="AQ272">
         <v>1.07</v>
-      </c>
-      <c r="AQ272">
-        <v>1.14</v>
       </c>
       <c r="AR272">
         <v>1.46</v>
@@ -57642,7 +57654,7 @@
         <v>260</v>
       </c>
       <c r="P273" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="Q273">
         <v>3.5</v>
@@ -57926,7 +57938,7 @@
         <v>0.36</v>
       </c>
       <c r="AP274">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ274">
         <v>0.4</v>
@@ -58054,7 +58066,7 @@
         <v>261</v>
       </c>
       <c r="P275" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Q275">
         <v>5</v>
@@ -58132,7 +58144,7 @@
         <v>1.31</v>
       </c>
       <c r="AP275">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ275">
         <v>1.43</v>
@@ -58260,7 +58272,7 @@
         <v>262</v>
       </c>
       <c r="P276" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="Q276">
         <v>1.5</v>
@@ -58338,10 +58350,10 @@
         <v>0.54</v>
       </c>
       <c r="AP276">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ276">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR276">
         <v>1.74</v>
@@ -58466,7 +58478,7 @@
         <v>103</v>
       </c>
       <c r="P277" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Q277">
         <v>5.5</v>
@@ -58547,7 +58559,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ277">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR277">
         <v>1.23</v>
@@ -58672,7 +58684,7 @@
         <v>263</v>
       </c>
       <c r="P278" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q278">
         <v>2.2</v>
@@ -58878,7 +58890,7 @@
         <v>92</v>
       </c>
       <c r="P279" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="Q279">
         <v>4</v>
@@ -58959,7 +58971,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ279">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR279">
         <v>0.99</v>
@@ -59084,7 +59096,7 @@
         <v>92</v>
       </c>
       <c r="P280" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="Q280">
         <v>3.1</v>
@@ -59162,10 +59174,10 @@
         <v>2.14</v>
       </c>
       <c r="AP280">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ280">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AR280">
         <v>1.71</v>
@@ -59371,7 +59383,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ281">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR281">
         <v>1.63</v>
@@ -59496,7 +59508,7 @@
         <v>265</v>
       </c>
       <c r="P282" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q282">
         <v>2.75</v>
@@ -59702,7 +59714,7 @@
         <v>92</v>
       </c>
       <c r="P283" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q283">
         <v>2.4</v>
@@ -59908,7 +59920,7 @@
         <v>216</v>
       </c>
       <c r="P284" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q284">
         <v>3.6</v>
@@ -60114,7 +60126,7 @@
         <v>266</v>
       </c>
       <c r="P285" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q285">
         <v>2.4</v>
@@ -60401,7 +60413,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ286">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR286">
         <v>1.15</v>
@@ -60604,7 +60616,7 @@
         <v>2</v>
       </c>
       <c r="AP287">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ287">
         <v>1.93</v>
@@ -61222,7 +61234,7 @@
         <v>1.85</v>
       </c>
       <c r="AP290">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ290">
         <v>1.71</v>
@@ -61350,7 +61362,7 @@
         <v>92</v>
       </c>
       <c r="P291" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Q291">
         <v>3.2</v>
@@ -61507,6 +61519,1448 @@
       </c>
       <c r="BP291">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="292" spans="1:68">
+      <c r="A292" s="1">
+        <v>291</v>
+      </c>
+      <c r="B292">
+        <v>7492439</v>
+      </c>
+      <c r="C292" t="s">
+        <v>68</v>
+      </c>
+      <c r="D292" t="s">
+        <v>69</v>
+      </c>
+      <c r="E292" s="2">
+        <v>45745.45833333334</v>
+      </c>
+      <c r="F292">
+        <v>30</v>
+      </c>
+      <c r="G292" t="s">
+        <v>88</v>
+      </c>
+      <c r="H292" t="s">
+        <v>72</v>
+      </c>
+      <c r="I292">
+        <v>0</v>
+      </c>
+      <c r="J292">
+        <v>0</v>
+      </c>
+      <c r="K292">
+        <v>0</v>
+      </c>
+      <c r="L292">
+        <v>1</v>
+      </c>
+      <c r="M292">
+        <v>1</v>
+      </c>
+      <c r="N292">
+        <v>2</v>
+      </c>
+      <c r="O292" t="s">
+        <v>270</v>
+      </c>
+      <c r="P292" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q292">
+        <v>2.38</v>
+      </c>
+      <c r="R292">
+        <v>2.1</v>
+      </c>
+      <c r="S292">
+        <v>5</v>
+      </c>
+      <c r="T292">
+        <v>1.44</v>
+      </c>
+      <c r="U292">
+        <v>2.63</v>
+      </c>
+      <c r="V292">
+        <v>3</v>
+      </c>
+      <c r="W292">
+        <v>1.36</v>
+      </c>
+      <c r="X292">
+        <v>9</v>
+      </c>
+      <c r="Y292">
+        <v>1.07</v>
+      </c>
+      <c r="Z292">
+        <v>1.76</v>
+      </c>
+      <c r="AA292">
+        <v>3.45</v>
+      </c>
+      <c r="AB292">
+        <v>5.6</v>
+      </c>
+      <c r="AC292">
+        <v>0</v>
+      </c>
+      <c r="AD292">
+        <v>0</v>
+      </c>
+      <c r="AE292">
+        <v>0</v>
+      </c>
+      <c r="AF292">
+        <v>0</v>
+      </c>
+      <c r="AG292">
+        <v>2</v>
+      </c>
+      <c r="AH292">
+        <v>1.75</v>
+      </c>
+      <c r="AI292">
+        <v>1.95</v>
+      </c>
+      <c r="AJ292">
+        <v>1.8</v>
+      </c>
+      <c r="AK292">
+        <v>0</v>
+      </c>
+      <c r="AL292">
+        <v>0</v>
+      </c>
+      <c r="AM292">
+        <v>0</v>
+      </c>
+      <c r="AN292">
+        <v>1.36</v>
+      </c>
+      <c r="AO292">
+        <v>0.93</v>
+      </c>
+      <c r="AP292">
+        <v>1.33</v>
+      </c>
+      <c r="AQ292">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AR292">
+        <v>1.55</v>
+      </c>
+      <c r="AS292">
+        <v>1.09</v>
+      </c>
+      <c r="AT292">
+        <v>2.64</v>
+      </c>
+      <c r="AU292">
+        <v>6</v>
+      </c>
+      <c r="AV292">
+        <v>5</v>
+      </c>
+      <c r="AW292">
+        <v>10</v>
+      </c>
+      <c r="AX292">
+        <v>10</v>
+      </c>
+      <c r="AY292">
+        <v>21</v>
+      </c>
+      <c r="AZ292">
+        <v>16</v>
+      </c>
+      <c r="BA292">
+        <v>4</v>
+      </c>
+      <c r="BB292">
+        <v>1</v>
+      </c>
+      <c r="BC292">
+        <v>5</v>
+      </c>
+      <c r="BD292">
+        <v>0</v>
+      </c>
+      <c r="BE292">
+        <v>0</v>
+      </c>
+      <c r="BF292">
+        <v>0</v>
+      </c>
+      <c r="BG292">
+        <v>0</v>
+      </c>
+      <c r="BH292">
+        <v>0</v>
+      </c>
+      <c r="BI292">
+        <v>0</v>
+      </c>
+      <c r="BJ292">
+        <v>0</v>
+      </c>
+      <c r="BK292">
+        <v>0</v>
+      </c>
+      <c r="BL292">
+        <v>0</v>
+      </c>
+      <c r="BM292">
+        <v>0</v>
+      </c>
+      <c r="BN292">
+        <v>0</v>
+      </c>
+      <c r="BO292">
+        <v>0</v>
+      </c>
+      <c r="BP292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:68">
+      <c r="A293" s="1">
+        <v>292</v>
+      </c>
+      <c r="B293">
+        <v>7492447</v>
+      </c>
+      <c r="C293" t="s">
+        <v>68</v>
+      </c>
+      <c r="D293" t="s">
+        <v>69</v>
+      </c>
+      <c r="E293" s="2">
+        <v>45745.45833333334</v>
+      </c>
+      <c r="F293">
+        <v>30</v>
+      </c>
+      <c r="G293" t="s">
+        <v>87</v>
+      </c>
+      <c r="H293" t="s">
+        <v>74</v>
+      </c>
+      <c r="I293">
+        <v>0</v>
+      </c>
+      <c r="J293">
+        <v>0</v>
+      </c>
+      <c r="K293">
+        <v>0</v>
+      </c>
+      <c r="L293">
+        <v>0</v>
+      </c>
+      <c r="M293">
+        <v>1</v>
+      </c>
+      <c r="N293">
+        <v>1</v>
+      </c>
+      <c r="O293" t="s">
+        <v>92</v>
+      </c>
+      <c r="P293" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q293">
+        <v>5</v>
+      </c>
+      <c r="R293">
+        <v>2.1</v>
+      </c>
+      <c r="S293">
+        <v>2.5</v>
+      </c>
+      <c r="T293">
+        <v>1.44</v>
+      </c>
+      <c r="U293">
+        <v>2.63</v>
+      </c>
+      <c r="V293">
+        <v>3.25</v>
+      </c>
+      <c r="W293">
+        <v>1.33</v>
+      </c>
+      <c r="X293">
+        <v>9</v>
+      </c>
+      <c r="Y293">
+        <v>1.07</v>
+      </c>
+      <c r="Z293">
+        <v>4.6</v>
+      </c>
+      <c r="AA293">
+        <v>3.63</v>
+      </c>
+      <c r="AB293">
+        <v>1.85</v>
+      </c>
+      <c r="AC293">
+        <v>0</v>
+      </c>
+      <c r="AD293">
+        <v>0</v>
+      </c>
+      <c r="AE293">
+        <v>2.86</v>
+      </c>
+      <c r="AF293">
+        <v>1.45</v>
+      </c>
+      <c r="AG293">
+        <v>2</v>
+      </c>
+      <c r="AH293">
+        <v>1.75</v>
+      </c>
+      <c r="AI293">
+        <v>1.95</v>
+      </c>
+      <c r="AJ293">
+        <v>1.8</v>
+      </c>
+      <c r="AK293">
+        <v>0</v>
+      </c>
+      <c r="AL293">
+        <v>0</v>
+      </c>
+      <c r="AM293">
+        <v>0</v>
+      </c>
+      <c r="AN293">
+        <v>1</v>
+      </c>
+      <c r="AO293">
+        <v>1.5</v>
+      </c>
+      <c r="AP293">
+        <v>0.93</v>
+      </c>
+      <c r="AQ293">
+        <v>1.6</v>
+      </c>
+      <c r="AR293">
+        <v>1.36</v>
+      </c>
+      <c r="AS293">
+        <v>1.31</v>
+      </c>
+      <c r="AT293">
+        <v>2.67</v>
+      </c>
+      <c r="AU293">
+        <v>4</v>
+      </c>
+      <c r="AV293">
+        <v>5</v>
+      </c>
+      <c r="AW293">
+        <v>4</v>
+      </c>
+      <c r="AX293">
+        <v>9</v>
+      </c>
+      <c r="AY293">
+        <v>9</v>
+      </c>
+      <c r="AZ293">
+        <v>18</v>
+      </c>
+      <c r="BA293">
+        <v>2</v>
+      </c>
+      <c r="BB293">
+        <v>3</v>
+      </c>
+      <c r="BC293">
+        <v>5</v>
+      </c>
+      <c r="BD293">
+        <v>0</v>
+      </c>
+      <c r="BE293">
+        <v>0</v>
+      </c>
+      <c r="BF293">
+        <v>0</v>
+      </c>
+      <c r="BG293">
+        <v>0</v>
+      </c>
+      <c r="BH293">
+        <v>0</v>
+      </c>
+      <c r="BI293">
+        <v>0</v>
+      </c>
+      <c r="BJ293">
+        <v>0</v>
+      </c>
+      <c r="BK293">
+        <v>0</v>
+      </c>
+      <c r="BL293">
+        <v>0</v>
+      </c>
+      <c r="BM293">
+        <v>0</v>
+      </c>
+      <c r="BN293">
+        <v>0</v>
+      </c>
+      <c r="BO293">
+        <v>0</v>
+      </c>
+      <c r="BP293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:68">
+      <c r="A294" s="1">
+        <v>293</v>
+      </c>
+      <c r="B294">
+        <v>7492443</v>
+      </c>
+      <c r="C294" t="s">
+        <v>68</v>
+      </c>
+      <c r="D294" t="s">
+        <v>69</v>
+      </c>
+      <c r="E294" s="2">
+        <v>45745.58333333334</v>
+      </c>
+      <c r="F294">
+        <v>30</v>
+      </c>
+      <c r="G294" t="s">
+        <v>79</v>
+      </c>
+      <c r="H294" t="s">
+        <v>70</v>
+      </c>
+      <c r="I294">
+        <v>1</v>
+      </c>
+      <c r="J294">
+        <v>0</v>
+      </c>
+      <c r="K294">
+        <v>1</v>
+      </c>
+      <c r="L294">
+        <v>1</v>
+      </c>
+      <c r="M294">
+        <v>0</v>
+      </c>
+      <c r="N294">
+        <v>1</v>
+      </c>
+      <c r="O294" t="s">
+        <v>271</v>
+      </c>
+      <c r="P294" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q294">
+        <v>2.2</v>
+      </c>
+      <c r="R294">
+        <v>2.1</v>
+      </c>
+      <c r="S294">
+        <v>6.5</v>
+      </c>
+      <c r="T294">
+        <v>1.44</v>
+      </c>
+      <c r="U294">
+        <v>2.63</v>
+      </c>
+      <c r="V294">
+        <v>3.25</v>
+      </c>
+      <c r="W294">
+        <v>1.33</v>
+      </c>
+      <c r="X294">
+        <v>10</v>
+      </c>
+      <c r="Y294">
+        <v>1.06</v>
+      </c>
+      <c r="Z294">
+        <v>1.59</v>
+      </c>
+      <c r="AA294">
+        <v>3.98</v>
+      </c>
+      <c r="AB294">
+        <v>6.5</v>
+      </c>
+      <c r="AC294">
+        <v>0</v>
+      </c>
+      <c r="AD294">
+        <v>0</v>
+      </c>
+      <c r="AE294">
+        <v>2.04</v>
+      </c>
+      <c r="AF294">
+        <v>1.84</v>
+      </c>
+      <c r="AG294">
+        <v>2.1</v>
+      </c>
+      <c r="AH294">
+        <v>1.67</v>
+      </c>
+      <c r="AI294">
+        <v>2.2</v>
+      </c>
+      <c r="AJ294">
+        <v>1.62</v>
+      </c>
+      <c r="AK294">
+        <v>0</v>
+      </c>
+      <c r="AL294">
+        <v>0</v>
+      </c>
+      <c r="AM294">
+        <v>0</v>
+      </c>
+      <c r="AN294">
+        <v>1.87</v>
+      </c>
+      <c r="AO294">
+        <v>1.14</v>
+      </c>
+      <c r="AP294">
+        <v>1.94</v>
+      </c>
+      <c r="AQ294">
+        <v>1.07</v>
+      </c>
+      <c r="AR294">
+        <v>1.68</v>
+      </c>
+      <c r="AS294">
+        <v>1.04</v>
+      </c>
+      <c r="AT294">
+        <v>2.72</v>
+      </c>
+      <c r="AU294">
+        <v>7</v>
+      </c>
+      <c r="AV294">
+        <v>4</v>
+      </c>
+      <c r="AW294">
+        <v>4</v>
+      </c>
+      <c r="AX294">
+        <v>6</v>
+      </c>
+      <c r="AY294">
+        <v>11</v>
+      </c>
+      <c r="AZ294">
+        <v>11</v>
+      </c>
+      <c r="BA294">
+        <v>4</v>
+      </c>
+      <c r="BB294">
+        <v>3</v>
+      </c>
+      <c r="BC294">
+        <v>7</v>
+      </c>
+      <c r="BD294">
+        <v>0</v>
+      </c>
+      <c r="BE294">
+        <v>0</v>
+      </c>
+      <c r="BF294">
+        <v>0</v>
+      </c>
+      <c r="BG294">
+        <v>0</v>
+      </c>
+      <c r="BH294">
+        <v>0</v>
+      </c>
+      <c r="BI294">
+        <v>0</v>
+      </c>
+      <c r="BJ294">
+        <v>0</v>
+      </c>
+      <c r="BK294">
+        <v>0</v>
+      </c>
+      <c r="BL294">
+        <v>0</v>
+      </c>
+      <c r="BM294">
+        <v>0</v>
+      </c>
+      <c r="BN294">
+        <v>0</v>
+      </c>
+      <c r="BO294">
+        <v>0</v>
+      </c>
+      <c r="BP294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:68">
+      <c r="A295" s="1">
+        <v>294</v>
+      </c>
+      <c r="B295">
+        <v>7492445</v>
+      </c>
+      <c r="C295" t="s">
+        <v>68</v>
+      </c>
+      <c r="D295" t="s">
+        <v>69</v>
+      </c>
+      <c r="E295" s="2">
+        <v>45745.69791666666</v>
+      </c>
+      <c r="F295">
+        <v>30</v>
+      </c>
+      <c r="G295" t="s">
+        <v>78</v>
+      </c>
+      <c r="H295" t="s">
+        <v>86</v>
+      </c>
+      <c r="I295">
+        <v>0</v>
+      </c>
+      <c r="J295">
+        <v>0</v>
+      </c>
+      <c r="K295">
+        <v>0</v>
+      </c>
+      <c r="L295">
+        <v>0</v>
+      </c>
+      <c r="M295">
+        <v>1</v>
+      </c>
+      <c r="N295">
+        <v>1</v>
+      </c>
+      <c r="O295" t="s">
+        <v>92</v>
+      </c>
+      <c r="P295" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q295">
+        <v>5</v>
+      </c>
+      <c r="R295">
+        <v>2.05</v>
+      </c>
+      <c r="S295">
+        <v>2.6</v>
+      </c>
+      <c r="T295">
+        <v>1.44</v>
+      </c>
+      <c r="U295">
+        <v>2.63</v>
+      </c>
+      <c r="V295">
+        <v>3.25</v>
+      </c>
+      <c r="W295">
+        <v>1.33</v>
+      </c>
+      <c r="X295">
+        <v>10</v>
+      </c>
+      <c r="Y295">
+        <v>1.06</v>
+      </c>
+      <c r="Z295">
+        <v>4.5</v>
+      </c>
+      <c r="AA295">
+        <v>3.45</v>
+      </c>
+      <c r="AB295">
+        <v>1.91</v>
+      </c>
+      <c r="AC295">
+        <v>0</v>
+      </c>
+      <c r="AD295">
+        <v>0</v>
+      </c>
+      <c r="AE295">
+        <v>2.07</v>
+      </c>
+      <c r="AF295">
+        <v>1.8</v>
+      </c>
+      <c r="AG295">
+        <v>2</v>
+      </c>
+      <c r="AH295">
+        <v>1.73</v>
+      </c>
+      <c r="AI295">
+        <v>2</v>
+      </c>
+      <c r="AJ295">
+        <v>1.75</v>
+      </c>
+      <c r="AK295">
+        <v>0</v>
+      </c>
+      <c r="AL295">
+        <v>0</v>
+      </c>
+      <c r="AM295">
+        <v>0</v>
+      </c>
+      <c r="AN295">
+        <v>1</v>
+      </c>
+      <c r="AO295">
+        <v>1.29</v>
+      </c>
+      <c r="AP295">
+        <v>0.93</v>
+      </c>
+      <c r="AQ295">
+        <v>1.4</v>
+      </c>
+      <c r="AR295">
+        <v>1.28</v>
+      </c>
+      <c r="AS295">
+        <v>1.41</v>
+      </c>
+      <c r="AT295">
+        <v>2.69</v>
+      </c>
+      <c r="AU295">
+        <v>5</v>
+      </c>
+      <c r="AV295">
+        <v>7</v>
+      </c>
+      <c r="AW295">
+        <v>13</v>
+      </c>
+      <c r="AX295">
+        <v>10</v>
+      </c>
+      <c r="AY295">
+        <v>21</v>
+      </c>
+      <c r="AZ295">
+        <v>22</v>
+      </c>
+      <c r="BA295">
+        <v>6</v>
+      </c>
+      <c r="BB295">
+        <v>6</v>
+      </c>
+      <c r="BC295">
+        <v>12</v>
+      </c>
+      <c r="BD295">
+        <v>0</v>
+      </c>
+      <c r="BE295">
+        <v>0</v>
+      </c>
+      <c r="BF295">
+        <v>0</v>
+      </c>
+      <c r="BG295">
+        <v>0</v>
+      </c>
+      <c r="BH295">
+        <v>0</v>
+      </c>
+      <c r="BI295">
+        <v>0</v>
+      </c>
+      <c r="BJ295">
+        <v>0</v>
+      </c>
+      <c r="BK295">
+        <v>0</v>
+      </c>
+      <c r="BL295">
+        <v>0</v>
+      </c>
+      <c r="BM295">
+        <v>0</v>
+      </c>
+      <c r="BN295">
+        <v>0</v>
+      </c>
+      <c r="BO295">
+        <v>0</v>
+      </c>
+      <c r="BP295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:68">
+      <c r="A296" s="1">
+        <v>295</v>
+      </c>
+      <c r="B296">
+        <v>7492438</v>
+      </c>
+      <c r="C296" t="s">
+        <v>68</v>
+      </c>
+      <c r="D296" t="s">
+        <v>69</v>
+      </c>
+      <c r="E296" s="2">
+        <v>45746.3125</v>
+      </c>
+      <c r="F296">
+        <v>30</v>
+      </c>
+      <c r="G296" t="s">
+        <v>76</v>
+      </c>
+      <c r="H296" t="s">
+        <v>81</v>
+      </c>
+      <c r="I296">
+        <v>0</v>
+      </c>
+      <c r="J296">
+        <v>0</v>
+      </c>
+      <c r="K296">
+        <v>0</v>
+      </c>
+      <c r="L296">
+        <v>3</v>
+      </c>
+      <c r="M296">
+        <v>0</v>
+      </c>
+      <c r="N296">
+        <v>3</v>
+      </c>
+      <c r="O296" t="s">
+        <v>272</v>
+      </c>
+      <c r="P296" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q296">
+        <v>2.38</v>
+      </c>
+      <c r="R296">
+        <v>2.1</v>
+      </c>
+      <c r="S296">
+        <v>5.5</v>
+      </c>
+      <c r="T296">
+        <v>1.44</v>
+      </c>
+      <c r="U296">
+        <v>2.63</v>
+      </c>
+      <c r="V296">
+        <v>3.25</v>
+      </c>
+      <c r="W296">
+        <v>1.33</v>
+      </c>
+      <c r="X296">
+        <v>10</v>
+      </c>
+      <c r="Y296">
+        <v>1.06</v>
+      </c>
+      <c r="Z296">
+        <v>1.74</v>
+      </c>
+      <c r="AA296">
+        <v>3.67</v>
+      </c>
+      <c r="AB296">
+        <v>5.3</v>
+      </c>
+      <c r="AC296">
+        <v>1.07</v>
+      </c>
+      <c r="AD296">
+        <v>8</v>
+      </c>
+      <c r="AE296">
+        <v>1.35</v>
+      </c>
+      <c r="AF296">
+        <v>3.1</v>
+      </c>
+      <c r="AG296">
+        <v>2.05</v>
+      </c>
+      <c r="AH296">
+        <v>1.7</v>
+      </c>
+      <c r="AI296">
+        <v>2.05</v>
+      </c>
+      <c r="AJ296">
+        <v>1.7</v>
+      </c>
+      <c r="AK296">
+        <v>1.15</v>
+      </c>
+      <c r="AL296">
+        <v>1.28</v>
+      </c>
+      <c r="AM296">
+        <v>2.15</v>
+      </c>
+      <c r="AN296">
+        <v>1.07</v>
+      </c>
+      <c r="AO296">
+        <v>0.5</v>
+      </c>
+      <c r="AP296">
+        <v>1.19</v>
+      </c>
+      <c r="AQ296">
+        <v>0.47</v>
+      </c>
+      <c r="AR296">
+        <v>1.43</v>
+      </c>
+      <c r="AS296">
+        <v>0.85</v>
+      </c>
+      <c r="AT296">
+        <v>2.28</v>
+      </c>
+      <c r="AU296">
+        <v>5</v>
+      </c>
+      <c r="AV296">
+        <v>4</v>
+      </c>
+      <c r="AW296">
+        <v>7</v>
+      </c>
+      <c r="AX296">
+        <v>9</v>
+      </c>
+      <c r="AY296">
+        <v>14</v>
+      </c>
+      <c r="AZ296">
+        <v>16</v>
+      </c>
+      <c r="BA296">
+        <v>4</v>
+      </c>
+      <c r="BB296">
+        <v>6</v>
+      </c>
+      <c r="BC296">
+        <v>10</v>
+      </c>
+      <c r="BD296">
+        <v>1.35</v>
+      </c>
+      <c r="BE296">
+        <v>7.5</v>
+      </c>
+      <c r="BF296">
+        <v>4.2</v>
+      </c>
+      <c r="BG296">
+        <v>1.24</v>
+      </c>
+      <c r="BH296">
+        <v>3.7</v>
+      </c>
+      <c r="BI296">
+        <v>1.46</v>
+      </c>
+      <c r="BJ296">
+        <v>2.5</v>
+      </c>
+      <c r="BK296">
+        <v>1.8</v>
+      </c>
+      <c r="BL296">
+        <v>1.88</v>
+      </c>
+      <c r="BM296">
+        <v>2.35</v>
+      </c>
+      <c r="BN296">
+        <v>1.52</v>
+      </c>
+      <c r="BO296">
+        <v>3.25</v>
+      </c>
+      <c r="BP296">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="297" spans="1:68">
+      <c r="A297" s="1">
+        <v>296</v>
+      </c>
+      <c r="B297">
+        <v>7492440</v>
+      </c>
+      <c r="C297" t="s">
+        <v>68</v>
+      </c>
+      <c r="D297" t="s">
+        <v>69</v>
+      </c>
+      <c r="E297" s="2">
+        <v>45746.41666666666</v>
+      </c>
+      <c r="F297">
+        <v>30</v>
+      </c>
+      <c r="G297" t="s">
+        <v>83</v>
+      </c>
+      <c r="H297" t="s">
+        <v>89</v>
+      </c>
+      <c r="I297">
+        <v>1</v>
+      </c>
+      <c r="J297">
+        <v>0</v>
+      </c>
+      <c r="K297">
+        <v>1</v>
+      </c>
+      <c r="L297">
+        <v>1</v>
+      </c>
+      <c r="M297">
+        <v>0</v>
+      </c>
+      <c r="N297">
+        <v>1</v>
+      </c>
+      <c r="O297" t="s">
+        <v>143</v>
+      </c>
+      <c r="P297" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q297">
+        <v>4</v>
+      </c>
+      <c r="R297">
+        <v>2.2</v>
+      </c>
+      <c r="S297">
+        <v>2.75</v>
+      </c>
+      <c r="T297">
+        <v>1.4</v>
+      </c>
+      <c r="U297">
+        <v>2.75</v>
+      </c>
+      <c r="V297">
+        <v>2.75</v>
+      </c>
+      <c r="W297">
+        <v>1.4</v>
+      </c>
+      <c r="X297">
+        <v>8</v>
+      </c>
+      <c r="Y297">
+        <v>1.08</v>
+      </c>
+      <c r="Z297">
+        <v>4</v>
+      </c>
+      <c r="AA297">
+        <v>3.62</v>
+      </c>
+      <c r="AB297">
+        <v>1.96</v>
+      </c>
+      <c r="AC297">
+        <v>1.06</v>
+      </c>
+      <c r="AD297">
+        <v>8.5</v>
+      </c>
+      <c r="AE297">
+        <v>1.3</v>
+      </c>
+      <c r="AF297">
+        <v>3.45</v>
+      </c>
+      <c r="AG297">
+        <v>1.89</v>
+      </c>
+      <c r="AH297">
+        <v>1.81</v>
+      </c>
+      <c r="AI297">
+        <v>1.75</v>
+      </c>
+      <c r="AJ297">
+        <v>2</v>
+      </c>
+      <c r="AK297">
+        <v>1.75</v>
+      </c>
+      <c r="AL297">
+        <v>1.29</v>
+      </c>
+      <c r="AM297">
+        <v>1.28</v>
+      </c>
+      <c r="AN297">
+        <v>2</v>
+      </c>
+      <c r="AO297">
+        <v>2.2</v>
+      </c>
+      <c r="AP297">
+        <v>2.06</v>
+      </c>
+      <c r="AQ297">
+        <v>2.06</v>
+      </c>
+      <c r="AR297">
+        <v>1.47</v>
+      </c>
+      <c r="AS297">
+        <v>1.62</v>
+      </c>
+      <c r="AT297">
+        <v>3.09</v>
+      </c>
+      <c r="AU297">
+        <v>5</v>
+      </c>
+      <c r="AV297">
+        <v>0</v>
+      </c>
+      <c r="AW297">
+        <v>8</v>
+      </c>
+      <c r="AX297">
+        <v>10</v>
+      </c>
+      <c r="AY297">
+        <v>13</v>
+      </c>
+      <c r="AZ297">
+        <v>13</v>
+      </c>
+      <c r="BA297">
+        <v>2</v>
+      </c>
+      <c r="BB297">
+        <v>4</v>
+      </c>
+      <c r="BC297">
+        <v>6</v>
+      </c>
+      <c r="BD297">
+        <v>2.87</v>
+      </c>
+      <c r="BE297">
+        <v>6.5</v>
+      </c>
+      <c r="BF297">
+        <v>1.63</v>
+      </c>
+      <c r="BG297">
+        <v>1.47</v>
+      </c>
+      <c r="BH297">
+        <v>2.45</v>
+      </c>
+      <c r="BI297">
+        <v>1.87</v>
+      </c>
+      <c r="BJ297">
+        <v>1.82</v>
+      </c>
+      <c r="BK297">
+        <v>2.5</v>
+      </c>
+      <c r="BL297">
+        <v>1.46</v>
+      </c>
+      <c r="BM297">
+        <v>3.6</v>
+      </c>
+      <c r="BN297">
+        <v>1.25</v>
+      </c>
+      <c r="BO297">
+        <v>5.5</v>
+      </c>
+      <c r="BP297">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="298" spans="1:68">
+      <c r="A298" s="1">
+        <v>297</v>
+      </c>
+      <c r="B298">
+        <v>7492442</v>
+      </c>
+      <c r="C298" t="s">
+        <v>68</v>
+      </c>
+      <c r="D298" t="s">
+        <v>69</v>
+      </c>
+      <c r="E298" s="2">
+        <v>45746.54166666666</v>
+      </c>
+      <c r="F298">
+        <v>30</v>
+      </c>
+      <c r="G298" t="s">
+        <v>82</v>
+      </c>
+      <c r="H298" t="s">
+        <v>80</v>
+      </c>
+      <c r="I298">
+        <v>2</v>
+      </c>
+      <c r="J298">
+        <v>0</v>
+      </c>
+      <c r="K298">
+        <v>2</v>
+      </c>
+      <c r="L298">
+        <v>2</v>
+      </c>
+      <c r="M298">
+        <v>1</v>
+      </c>
+      <c r="N298">
+        <v>3</v>
+      </c>
+      <c r="O298" t="s">
+        <v>273</v>
+      </c>
+      <c r="P298" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q298">
+        <v>1.95</v>
+      </c>
+      <c r="R298">
+        <v>2.38</v>
+      </c>
+      <c r="S298">
+        <v>7</v>
+      </c>
+      <c r="T298">
+        <v>1.36</v>
+      </c>
+      <c r="U298">
+        <v>3</v>
+      </c>
+      <c r="V298">
+        <v>2.63</v>
+      </c>
+      <c r="W298">
+        <v>1.44</v>
+      </c>
+      <c r="X298">
+        <v>7</v>
+      </c>
+      <c r="Y298">
+        <v>1.1</v>
+      </c>
+      <c r="Z298">
+        <v>1.39</v>
+      </c>
+      <c r="AA298">
+        <v>5</v>
+      </c>
+      <c r="AB298">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AC298">
+        <v>1.05</v>
+      </c>
+      <c r="AD298">
+        <v>9.5</v>
+      </c>
+      <c r="AE298">
+        <v>1.28</v>
+      </c>
+      <c r="AF298">
+        <v>3.65</v>
+      </c>
+      <c r="AG298">
+        <v>1.81</v>
+      </c>
+      <c r="AH298">
+        <v>2.01</v>
+      </c>
+      <c r="AI298">
+        <v>2</v>
+      </c>
+      <c r="AJ298">
+        <v>1.75</v>
+      </c>
+      <c r="AK298">
+        <v>1.08</v>
+      </c>
+      <c r="AL298">
+        <v>1.19</v>
+      </c>
+      <c r="AM298">
+        <v>2.87</v>
+      </c>
+      <c r="AN298">
+        <v>2.36</v>
+      </c>
+      <c r="AO298">
+        <v>1.21</v>
+      </c>
+      <c r="AP298">
+        <v>2.4</v>
+      </c>
+      <c r="AQ298">
+        <v>1.13</v>
+      </c>
+      <c r="AR298">
+        <v>1.87</v>
+      </c>
+      <c r="AS298">
+        <v>1.38</v>
+      </c>
+      <c r="AT298">
+        <v>3.25</v>
+      </c>
+      <c r="AU298">
+        <v>3</v>
+      </c>
+      <c r="AV298">
+        <v>5</v>
+      </c>
+      <c r="AW298">
+        <v>11</v>
+      </c>
+      <c r="AX298">
+        <v>7</v>
+      </c>
+      <c r="AY298">
+        <v>18</v>
+      </c>
+      <c r="AZ298">
+        <v>16</v>
+      </c>
+      <c r="BA298">
+        <v>2</v>
+      </c>
+      <c r="BB298">
+        <v>4</v>
+      </c>
+      <c r="BC298">
+        <v>6</v>
+      </c>
+      <c r="BD298">
+        <v>1.18</v>
+      </c>
+      <c r="BE298">
+        <v>9.5</v>
+      </c>
+      <c r="BF298">
+        <v>6.75</v>
+      </c>
+      <c r="BG298">
+        <v>1.19</v>
+      </c>
+      <c r="BH298">
+        <v>4.2</v>
+      </c>
+      <c r="BI298">
+        <v>1.37</v>
+      </c>
+      <c r="BJ298">
+        <v>2.8</v>
+      </c>
+      <c r="BK298">
+        <v>1.66</v>
+      </c>
+      <c r="BL298">
+        <v>2.05</v>
+      </c>
+      <c r="BM298">
+        <v>2.1</v>
+      </c>
+      <c r="BN298">
+        <v>1.63</v>
+      </c>
+      <c r="BO298">
+        <v>2.85</v>
+      </c>
+      <c r="BP298">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1850" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1856" uniqueCount="400">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -838,6 +838,9 @@
     <t>['12', '29']</t>
   </si>
   <si>
+    <t>['2', '19']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1572,7 +1575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP298"/>
+  <dimension ref="A1:BP299"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1828,7 +1831,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2446,7 +2449,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2652,7 +2655,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -3270,7 +3273,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3476,7 +3479,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -4094,7 +4097,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4175,7 +4178,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ13">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR13">
         <v>1.45</v>
@@ -4300,7 +4303,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -5202,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ18">
         <v>1.6</v>
@@ -5330,7 +5333,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5742,7 +5745,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5948,7 +5951,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6360,7 +6363,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6772,7 +6775,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6853,7 +6856,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ26">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR26">
         <v>1.67</v>
@@ -6978,7 +6981,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7056,7 +7059,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ27">
         <v>0.64</v>
@@ -7184,7 +7187,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7390,7 +7393,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -8008,7 +8011,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8832,7 +8835,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -9244,7 +9247,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9450,7 +9453,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9656,7 +9659,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9862,7 +9865,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -10068,7 +10071,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10274,7 +10277,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10892,7 +10895,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -11098,7 +11101,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11304,7 +11307,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11716,7 +11719,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11797,7 +11800,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ50">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR50">
         <v>1.2</v>
@@ -11922,7 +11925,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12334,7 +12337,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12540,7 +12543,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12746,7 +12749,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12952,7 +12955,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13158,7 +13161,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13854,7 +13857,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ60">
         <v>0.47</v>
@@ -13982,7 +13985,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14266,7 +14269,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ62">
         <v>0.67</v>
@@ -14806,7 +14809,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -15012,7 +15015,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15218,7 +15221,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -16123,7 +16126,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ71">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR71">
         <v>1.68</v>
@@ -16454,7 +16457,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -17072,7 +17075,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17278,7 +17281,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17484,7 +17487,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17690,7 +17693,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -18102,7 +18105,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18798,7 +18801,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ84">
         <v>0.73</v>
@@ -18926,7 +18929,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19544,7 +19547,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19750,7 +19753,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19956,7 +19959,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20162,7 +20165,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20574,7 +20577,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20780,7 +20783,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20986,7 +20989,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -21398,7 +21401,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21604,7 +21607,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21810,7 +21813,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22428,7 +22431,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22715,7 +22718,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ103">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR103">
         <v>0.9399999999999999</v>
@@ -22840,7 +22843,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -22918,7 +22921,7 @@
         <v>1.4</v>
       </c>
       <c r="AP104">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ104">
         <v>2.06</v>
@@ -23046,7 +23049,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23252,7 +23255,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -24076,7 +24079,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24282,7 +24285,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24488,7 +24491,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24694,7 +24697,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24900,7 +24903,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -24981,7 +24984,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ114">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR114">
         <v>1.3</v>
@@ -25312,7 +25315,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25518,7 +25521,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -26342,7 +26345,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26754,7 +26757,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26960,7 +26963,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27166,7 +27169,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27372,7 +27375,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27656,7 +27659,7 @@
         <v>0.67</v>
       </c>
       <c r="AP127">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ127">
         <v>1.4</v>
@@ -27990,7 +27993,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -29226,7 +29229,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29432,7 +29435,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29844,7 +29847,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -30050,7 +30053,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30543,7 +30546,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ141">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR141">
         <v>1.73</v>
@@ -30874,7 +30877,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -31080,7 +31083,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31492,7 +31495,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31698,7 +31701,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31982,7 +31985,7 @@
         <v>1.29</v>
       </c>
       <c r="AP148">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ148">
         <v>1.67</v>
@@ -32110,7 +32113,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32522,7 +32525,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32728,7 +32731,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32934,7 +32937,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -33346,7 +33349,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -34170,7 +34173,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34457,7 +34460,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ160">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR160">
         <v>1.12</v>
@@ -34582,7 +34585,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34788,7 +34791,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34994,7 +34997,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35406,7 +35409,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35612,7 +35615,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35818,7 +35821,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -36024,7 +36027,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36642,7 +36645,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36848,7 +36851,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -37054,7 +37057,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37260,7 +37263,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37544,7 +37547,7 @@
         <v>0.33</v>
       </c>
       <c r="AP175">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ175">
         <v>0.4</v>
@@ -37672,7 +37675,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -38290,7 +38293,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38702,7 +38705,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39114,7 +39117,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39938,7 +39941,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40350,7 +40353,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40762,7 +40765,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41380,7 +41383,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41664,7 +41667,7 @@
         <v>1</v>
       </c>
       <c r="AP195">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ195">
         <v>1.07</v>
@@ -41998,7 +42001,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42079,7 +42082,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ197">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR197">
         <v>1.54</v>
@@ -42410,7 +42413,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42616,7 +42619,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42822,7 +42825,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -43109,7 +43112,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ202">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR202">
         <v>1.44</v>
@@ -43234,7 +43237,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43646,7 +43649,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -44058,7 +44061,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44264,7 +44267,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44882,7 +44885,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45166,7 +45169,7 @@
         <v>1.8</v>
       </c>
       <c r="AP212">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ212">
         <v>1.71</v>
@@ -45500,7 +45503,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45706,7 +45709,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45912,7 +45915,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -46118,7 +46121,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46324,7 +46327,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46736,7 +46739,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46942,7 +46945,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47354,7 +47357,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47766,7 +47769,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47972,7 +47975,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -48384,7 +48387,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48590,7 +48593,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -49002,7 +49005,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49208,7 +49211,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49414,7 +49417,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49495,7 +49498,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ233">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR233">
         <v>0.99</v>
@@ -49620,7 +49623,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -50238,7 +50241,7 @@
         <v>241</v>
       </c>
       <c r="P237" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q237">
         <v>1.91</v>
@@ -50650,7 +50653,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -50728,7 +50731,7 @@
         <v>1.09</v>
       </c>
       <c r="AP239">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ239">
         <v>1.13</v>
@@ -51062,7 +51065,7 @@
         <v>244</v>
       </c>
       <c r="P241" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q241">
         <v>2.5</v>
@@ -51474,7 +51477,7 @@
         <v>245</v>
       </c>
       <c r="P243" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q243">
         <v>3.4</v>
@@ -51886,7 +51889,7 @@
         <v>92</v>
       </c>
       <c r="P245" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q245">
         <v>2.6</v>
@@ -52504,7 +52507,7 @@
         <v>92</v>
       </c>
       <c r="P248" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q248">
         <v>4</v>
@@ -53821,7 +53824,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ254">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR254">
         <v>1.15</v>
@@ -54152,7 +54155,7 @@
         <v>250</v>
       </c>
       <c r="P256" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q256">
         <v>4</v>
@@ -54564,7 +54567,7 @@
         <v>92</v>
       </c>
       <c r="P258" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q258">
         <v>6</v>
@@ -54770,7 +54773,7 @@
         <v>92</v>
       </c>
       <c r="P259" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q259">
         <v>4.75</v>
@@ -55263,7 +55266,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ261">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR261">
         <v>1.8</v>
@@ -55878,7 +55881,7 @@
         <v>2.08</v>
       </c>
       <c r="AP264">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ264">
         <v>2.07</v>
@@ -56212,7 +56215,7 @@
         <v>92</v>
       </c>
       <c r="P266" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q266">
         <v>4.75</v>
@@ -57036,7 +57039,7 @@
         <v>146</v>
       </c>
       <c r="P270" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q270">
         <v>2.63</v>
@@ -57654,7 +57657,7 @@
         <v>260</v>
       </c>
       <c r="P273" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q273">
         <v>3.5</v>
@@ -58066,7 +58069,7 @@
         <v>261</v>
       </c>
       <c r="P275" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q275">
         <v>5</v>
@@ -58147,7 +58150,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ275">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR275">
         <v>1.29</v>
@@ -58272,7 +58275,7 @@
         <v>262</v>
       </c>
       <c r="P276" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q276">
         <v>1.5</v>
@@ -58478,7 +58481,7 @@
         <v>103</v>
       </c>
       <c r="P277" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q277">
         <v>5.5</v>
@@ -58684,7 +58687,7 @@
         <v>263</v>
       </c>
       <c r="P278" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q278">
         <v>2.2</v>
@@ -58762,7 +58765,7 @@
         <v>1.38</v>
       </c>
       <c r="AP278">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ278">
         <v>1.29</v>
@@ -58890,7 +58893,7 @@
         <v>92</v>
       </c>
       <c r="P279" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q279">
         <v>4</v>
@@ -59096,7 +59099,7 @@
         <v>92</v>
       </c>
       <c r="P280" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q280">
         <v>3.1</v>
@@ -59508,7 +59511,7 @@
         <v>265</v>
       </c>
       <c r="P282" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q282">
         <v>2.75</v>
@@ -59714,7 +59717,7 @@
         <v>92</v>
       </c>
       <c r="P283" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q283">
         <v>2.4</v>
@@ -59920,7 +59923,7 @@
         <v>216</v>
       </c>
       <c r="P284" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q284">
         <v>3.6</v>
@@ -60126,7 +60129,7 @@
         <v>266</v>
       </c>
       <c r="P285" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q285">
         <v>2.4</v>
@@ -61362,7 +61365,7 @@
         <v>92</v>
       </c>
       <c r="P291" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q291">
         <v>3.2</v>
@@ -62804,7 +62807,7 @@
         <v>273</v>
       </c>
       <c r="P298" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q298">
         <v>1.95</v>
@@ -62961,6 +62964,212 @@
       </c>
       <c r="BP298">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="299" spans="1:68">
+      <c r="A299" s="1">
+        <v>298</v>
+      </c>
+      <c r="B299">
+        <v>7492446</v>
+      </c>
+      <c r="C299" t="s">
+        <v>68</v>
+      </c>
+      <c r="D299" t="s">
+        <v>69</v>
+      </c>
+      <c r="E299" s="2">
+        <v>45746.65625</v>
+      </c>
+      <c r="F299">
+        <v>30</v>
+      </c>
+      <c r="G299" t="s">
+        <v>85</v>
+      </c>
+      <c r="H299" t="s">
+        <v>73</v>
+      </c>
+      <c r="I299">
+        <v>2</v>
+      </c>
+      <c r="J299">
+        <v>0</v>
+      </c>
+      <c r="K299">
+        <v>2</v>
+      </c>
+      <c r="L299">
+        <v>2</v>
+      </c>
+      <c r="M299">
+        <v>1</v>
+      </c>
+      <c r="N299">
+        <v>3</v>
+      </c>
+      <c r="O299" t="s">
+        <v>274</v>
+      </c>
+      <c r="P299" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q299">
+        <v>2.6</v>
+      </c>
+      <c r="R299">
+        <v>2.2</v>
+      </c>
+      <c r="S299">
+        <v>4.33</v>
+      </c>
+      <c r="T299">
+        <v>1.4</v>
+      </c>
+      <c r="U299">
+        <v>2.75</v>
+      </c>
+      <c r="V299">
+        <v>3</v>
+      </c>
+      <c r="W299">
+        <v>1.36</v>
+      </c>
+      <c r="X299">
+        <v>8</v>
+      </c>
+      <c r="Y299">
+        <v>1.08</v>
+      </c>
+      <c r="Z299">
+        <v>1.93</v>
+      </c>
+      <c r="AA299">
+        <v>3.74</v>
+      </c>
+      <c r="AB299">
+        <v>4</v>
+      </c>
+      <c r="AC299">
+        <v>1.06</v>
+      </c>
+      <c r="AD299">
+        <v>8.5</v>
+      </c>
+      <c r="AE299">
+        <v>1.33</v>
+      </c>
+      <c r="AF299">
+        <v>3.25</v>
+      </c>
+      <c r="AG299">
+        <v>1.89</v>
+      </c>
+      <c r="AH299">
+        <v>1.92</v>
+      </c>
+      <c r="AI299">
+        <v>1.8</v>
+      </c>
+      <c r="AJ299">
+        <v>1.95</v>
+      </c>
+      <c r="AK299">
+        <v>1.26</v>
+      </c>
+      <c r="AL299">
+        <v>1.3</v>
+      </c>
+      <c r="AM299">
+        <v>1.8</v>
+      </c>
+      <c r="AN299">
+        <v>2.29</v>
+      </c>
+      <c r="AO299">
+        <v>1.43</v>
+      </c>
+      <c r="AP299">
+        <v>2.33</v>
+      </c>
+      <c r="AQ299">
+        <v>1.33</v>
+      </c>
+      <c r="AR299">
+        <v>1.7</v>
+      </c>
+      <c r="AS299">
+        <v>1.61</v>
+      </c>
+      <c r="AT299">
+        <v>3.31</v>
+      </c>
+      <c r="AU299">
+        <v>4</v>
+      </c>
+      <c r="AV299">
+        <v>5</v>
+      </c>
+      <c r="AW299">
+        <v>5</v>
+      </c>
+      <c r="AX299">
+        <v>13</v>
+      </c>
+      <c r="AY299">
+        <v>10</v>
+      </c>
+      <c r="AZ299">
+        <v>22</v>
+      </c>
+      <c r="BA299">
+        <v>2</v>
+      </c>
+      <c r="BB299">
+        <v>6</v>
+      </c>
+      <c r="BC299">
+        <v>8</v>
+      </c>
+      <c r="BD299">
+        <v>1.5</v>
+      </c>
+      <c r="BE299">
+        <v>7</v>
+      </c>
+      <c r="BF299">
+        <v>3.25</v>
+      </c>
+      <c r="BG299">
+        <v>1.21</v>
+      </c>
+      <c r="BH299">
+        <v>4</v>
+      </c>
+      <c r="BI299">
+        <v>1.41</v>
+      </c>
+      <c r="BJ299">
+        <v>2.65</v>
+      </c>
+      <c r="BK299">
+        <v>1.72</v>
+      </c>
+      <c r="BL299">
+        <v>1.98</v>
+      </c>
+      <c r="BM299">
+        <v>2.2</v>
+      </c>
+      <c r="BN299">
+        <v>1.58</v>
+      </c>
+      <c r="BO299">
+        <v>3</v>
+      </c>
+      <c r="BP299">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1856" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1868" uniqueCount="401">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1215,6 +1215,9 @@
   <si>
     <t>['71']</t>
   </si>
+  <si>
+    <t>['82']</t>
+  </si>
 </sst>
 </file>
 
@@ -1575,7 +1578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP299"/>
+  <dimension ref="A1:BP301"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2530,7 +2533,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ5">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -3351,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ9">
         <v>0.4</v>
@@ -6032,7 +6035,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ22">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6853,7 +6856,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ26">
         <v>1.33</v>
@@ -7062,7 +7065,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ27">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR27">
         <v>1.28</v>
@@ -9943,7 +9946,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ41">
         <v>1.07</v>
@@ -10358,7 +10361,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ43">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR43">
         <v>0.93</v>
@@ -10976,7 +10979,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ46">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR46">
         <v>1.54</v>
@@ -15096,7 +15099,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ66">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR66">
         <v>1.21</v>
@@ -15505,7 +15508,7 @@
         <v>2.33</v>
       </c>
       <c r="AP68">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ68">
         <v>0.9399999999999999</v>
@@ -15714,7 +15717,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ69">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR69">
         <v>1.35</v>
@@ -16332,7 +16335,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ72">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR72">
         <v>1.87</v>
@@ -17774,7 +17777,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ79">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR79">
         <v>1.44</v>
@@ -19419,7 +19422,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ87">
         <v>1.07</v>
@@ -21482,7 +21485,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ97">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR97">
         <v>1.44</v>
@@ -22100,7 +22103,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ100">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR100">
         <v>1.81</v>
@@ -24157,7 +24160,7 @@
         <v>1</v>
       </c>
       <c r="AP110">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ110">
         <v>0.71</v>
@@ -24778,7 +24781,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ113">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR113">
         <v>1.44</v>
@@ -25190,7 +25193,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ115">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR115">
         <v>1.54</v>
@@ -27865,7 +27868,7 @@
         <v>1.83</v>
       </c>
       <c r="AP128">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ128">
         <v>1.6</v>
@@ -30340,7 +30343,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ140">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR140">
         <v>1.57</v>
@@ -30752,7 +30755,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ142">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR142">
         <v>1.3</v>
@@ -32400,7 +32403,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ150">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR150">
         <v>0.84</v>
@@ -34251,7 +34254,7 @@
         <v>2.33</v>
       </c>
       <c r="AP159">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ159">
         <v>2.07</v>
@@ -35284,7 +35287,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ164">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR164">
         <v>1.54</v>
@@ -37135,7 +37138,7 @@
         <v>2.11</v>
       </c>
       <c r="AP173">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ173">
         <v>2.06</v>
@@ -37344,7 +37347,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ174">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR174">
         <v>1.03</v>
@@ -39610,7 +39613,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ185">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR185">
         <v>1</v>
@@ -40019,7 +40022,7 @@
         <v>0.6</v>
       </c>
       <c r="AP187">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ187">
         <v>0.67</v>
@@ -41052,7 +41055,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ192">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR192">
         <v>1.24</v>
@@ -43524,7 +43527,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ204">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR204">
         <v>1.51</v>
@@ -45584,7 +45587,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ214">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR214">
         <v>1.72</v>
@@ -46199,7 +46202,7 @@
         <v>1.5</v>
       </c>
       <c r="AP217">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ217">
         <v>1.29</v>
@@ -47438,7 +47441,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ223">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR223">
         <v>1.8</v>
@@ -50116,7 +50119,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ236">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR236">
         <v>1.47</v>
@@ -50319,7 +50322,7 @@
         <v>0.64</v>
       </c>
       <c r="AP237">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ237">
         <v>0.47</v>
@@ -51146,7 +51149,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ241">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR241">
         <v>1.74</v>
@@ -51555,7 +51558,7 @@
         <v>2.25</v>
       </c>
       <c r="AP243">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ243">
         <v>1.93</v>
@@ -56090,7 +56093,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ265">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR265">
         <v>1.18</v>
@@ -56296,7 +56299,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ266">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR266">
         <v>1.18</v>
@@ -57738,7 +57741,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ273">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR273">
         <v>1.34</v>
@@ -59383,7 +59386,7 @@
         <v>1.23</v>
       </c>
       <c r="AP281">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ281">
         <v>1.13</v>
@@ -60004,7 +60007,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ284">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AR284">
         <v>1.17</v>
@@ -63170,6 +63173,418 @@
       </c>
       <c r="BP299">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="300" spans="1:68">
+      <c r="A300" s="1">
+        <v>299</v>
+      </c>
+      <c r="B300">
+        <v>7492441</v>
+      </c>
+      <c r="C300" t="s">
+        <v>68</v>
+      </c>
+      <c r="D300" t="s">
+        <v>69</v>
+      </c>
+      <c r="E300" s="2">
+        <v>45747.5625</v>
+      </c>
+      <c r="F300">
+        <v>30</v>
+      </c>
+      <c r="G300" t="s">
+        <v>75</v>
+      </c>
+      <c r="H300" t="s">
+        <v>71</v>
+      </c>
+      <c r="I300">
+        <v>0</v>
+      </c>
+      <c r="J300">
+        <v>0</v>
+      </c>
+      <c r="K300">
+        <v>0</v>
+      </c>
+      <c r="L300">
+        <v>0</v>
+      </c>
+      <c r="M300">
+        <v>0</v>
+      </c>
+      <c r="N300">
+        <v>0</v>
+      </c>
+      <c r="O300" t="s">
+        <v>92</v>
+      </c>
+      <c r="P300" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q300">
+        <v>3.1</v>
+      </c>
+      <c r="R300">
+        <v>2.05</v>
+      </c>
+      <c r="S300">
+        <v>3.75</v>
+      </c>
+      <c r="T300">
+        <v>1.44</v>
+      </c>
+      <c r="U300">
+        <v>2.63</v>
+      </c>
+      <c r="V300">
+        <v>3.25</v>
+      </c>
+      <c r="W300">
+        <v>1.33</v>
+      </c>
+      <c r="X300">
+        <v>9</v>
+      </c>
+      <c r="Y300">
+        <v>1.07</v>
+      </c>
+      <c r="Z300">
+        <v>2.4</v>
+      </c>
+      <c r="AA300">
+        <v>3.27</v>
+      </c>
+      <c r="AB300">
+        <v>3.2</v>
+      </c>
+      <c r="AC300">
+        <v>1.07</v>
+      </c>
+      <c r="AD300">
+        <v>8</v>
+      </c>
+      <c r="AE300">
+        <v>1.36</v>
+      </c>
+      <c r="AF300">
+        <v>3.1</v>
+      </c>
+      <c r="AG300">
+        <v>1.95</v>
+      </c>
+      <c r="AH300">
+        <v>1.75</v>
+      </c>
+      <c r="AI300">
+        <v>1.8</v>
+      </c>
+      <c r="AJ300">
+        <v>1.95</v>
+      </c>
+      <c r="AK300">
+        <v>1.36</v>
+      </c>
+      <c r="AL300">
+        <v>1.35</v>
+      </c>
+      <c r="AM300">
+        <v>1.55</v>
+      </c>
+      <c r="AN300">
+        <v>0.93</v>
+      </c>
+      <c r="AO300">
+        <v>0.64</v>
+      </c>
+      <c r="AP300">
+        <v>0.93</v>
+      </c>
+      <c r="AQ300">
+        <v>0.67</v>
+      </c>
+      <c r="AR300">
+        <v>1.21</v>
+      </c>
+      <c r="AS300">
+        <v>1.23</v>
+      </c>
+      <c r="AT300">
+        <v>2.44</v>
+      </c>
+      <c r="AU300">
+        <v>0</v>
+      </c>
+      <c r="AV300">
+        <v>3</v>
+      </c>
+      <c r="AW300">
+        <v>7</v>
+      </c>
+      <c r="AX300">
+        <v>9</v>
+      </c>
+      <c r="AY300">
+        <v>10</v>
+      </c>
+      <c r="AZ300">
+        <v>15</v>
+      </c>
+      <c r="BA300">
+        <v>5</v>
+      </c>
+      <c r="BB300">
+        <v>5</v>
+      </c>
+      <c r="BC300">
+        <v>10</v>
+      </c>
+      <c r="BD300">
+        <v>1.78</v>
+      </c>
+      <c r="BE300">
+        <v>6.75</v>
+      </c>
+      <c r="BF300">
+        <v>2.45</v>
+      </c>
+      <c r="BG300">
+        <v>1.21</v>
+      </c>
+      <c r="BH300">
+        <v>4</v>
+      </c>
+      <c r="BI300">
+        <v>1.4</v>
+      </c>
+      <c r="BJ300">
+        <v>2.7</v>
+      </c>
+      <c r="BK300">
+        <v>1.71</v>
+      </c>
+      <c r="BL300">
+        <v>1.98</v>
+      </c>
+      <c r="BM300">
+        <v>2.2</v>
+      </c>
+      <c r="BN300">
+        <v>1.58</v>
+      </c>
+      <c r="BO300">
+        <v>3</v>
+      </c>
+      <c r="BP300">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="301" spans="1:68">
+      <c r="A301" s="1">
+        <v>300</v>
+      </c>
+      <c r="B301">
+        <v>7492444</v>
+      </c>
+      <c r="C301" t="s">
+        <v>68</v>
+      </c>
+      <c r="D301" t="s">
+        <v>69</v>
+      </c>
+      <c r="E301" s="2">
+        <v>45747.65625</v>
+      </c>
+      <c r="F301">
+        <v>30</v>
+      </c>
+      <c r="G301" t="s">
+        <v>77</v>
+      </c>
+      <c r="H301" t="s">
+        <v>84</v>
+      </c>
+      <c r="I301">
+        <v>0</v>
+      </c>
+      <c r="J301">
+        <v>0</v>
+      </c>
+      <c r="K301">
+        <v>0</v>
+      </c>
+      <c r="L301">
+        <v>1</v>
+      </c>
+      <c r="M301">
+        <v>1</v>
+      </c>
+      <c r="N301">
+        <v>2</v>
+      </c>
+      <c r="O301" t="s">
+        <v>94</v>
+      </c>
+      <c r="P301" t="s">
+        <v>400</v>
+      </c>
+      <c r="Q301">
+        <v>2.4</v>
+      </c>
+      <c r="R301">
+        <v>2.1</v>
+      </c>
+      <c r="S301">
+        <v>5</v>
+      </c>
+      <c r="T301">
+        <v>1.44</v>
+      </c>
+      <c r="U301">
+        <v>2.63</v>
+      </c>
+      <c r="V301">
+        <v>3</v>
+      </c>
+      <c r="W301">
+        <v>1.36</v>
+      </c>
+      <c r="X301">
+        <v>9</v>
+      </c>
+      <c r="Y301">
+        <v>1.07</v>
+      </c>
+      <c r="Z301">
+        <v>1.74</v>
+      </c>
+      <c r="AA301">
+        <v>3.77</v>
+      </c>
+      <c r="AB301">
+        <v>5.1</v>
+      </c>
+      <c r="AC301">
+        <v>1.06</v>
+      </c>
+      <c r="AD301">
+        <v>8.5</v>
+      </c>
+      <c r="AE301">
+        <v>1.33</v>
+      </c>
+      <c r="AF301">
+        <v>3.2</v>
+      </c>
+      <c r="AG301">
+        <v>2.01</v>
+      </c>
+      <c r="AH301">
+        <v>1.81</v>
+      </c>
+      <c r="AI301">
+        <v>1.91</v>
+      </c>
+      <c r="AJ301">
+        <v>1.91</v>
+      </c>
+      <c r="AK301">
+        <v>1.18</v>
+      </c>
+      <c r="AL301">
+        <v>1.28</v>
+      </c>
+      <c r="AM301">
+        <v>2.05</v>
+      </c>
+      <c r="AN301">
+        <v>1.86</v>
+      </c>
+      <c r="AO301">
+        <v>1.2</v>
+      </c>
+      <c r="AP301">
+        <v>1.8</v>
+      </c>
+      <c r="AQ301">
+        <v>1.19</v>
+      </c>
+      <c r="AR301">
+        <v>1.61</v>
+      </c>
+      <c r="AS301">
+        <v>1.11</v>
+      </c>
+      <c r="AT301">
+        <v>2.72</v>
+      </c>
+      <c r="AU301">
+        <v>7</v>
+      </c>
+      <c r="AV301">
+        <v>3</v>
+      </c>
+      <c r="AW301">
+        <v>9</v>
+      </c>
+      <c r="AX301">
+        <v>5</v>
+      </c>
+      <c r="AY301">
+        <v>18</v>
+      </c>
+      <c r="AZ301">
+        <v>9</v>
+      </c>
+      <c r="BA301">
+        <v>5</v>
+      </c>
+      <c r="BB301">
+        <v>3</v>
+      </c>
+      <c r="BC301">
+        <v>8</v>
+      </c>
+      <c r="BD301">
+        <v>1.28</v>
+      </c>
+      <c r="BE301">
+        <v>8</v>
+      </c>
+      <c r="BF301">
+        <v>4.8</v>
+      </c>
+      <c r="BG301">
+        <v>1.24</v>
+      </c>
+      <c r="BH301">
+        <v>3.6</v>
+      </c>
+      <c r="BI301">
+        <v>1.46</v>
+      </c>
+      <c r="BJ301">
+        <v>2.5</v>
+      </c>
+      <c r="BK301">
+        <v>1.8</v>
+      </c>
+      <c r="BL301">
+        <v>1.88</v>
+      </c>
+      <c r="BM301">
+        <v>2.35</v>
+      </c>
+      <c r="BN301">
+        <v>1.51</v>
+      </c>
+      <c r="BO301">
+        <v>3.25</v>
+      </c>
+      <c r="BP301">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1868" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="401">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1578,7 +1578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP301"/>
+  <dimension ref="A1:BP302"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1912,7 +1912,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ2">
         <v>2.07</v>
@@ -2739,7 +2739,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ6">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ29">
         <v>1.07</v>
@@ -8710,7 +8710,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ35">
         <v>1.4</v>
@@ -9743,7 +9743,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ40">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR40">
         <v>1.32</v>
@@ -11597,7 +11597,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ49">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR49">
         <v>2.26</v>
@@ -12624,7 +12624,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ54">
         <v>1.71</v>
@@ -16538,7 +16538,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ73">
         <v>1.6</v>
@@ -16747,7 +16747,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ74">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR74">
         <v>1.89</v>
@@ -20867,7 +20867,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ94">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR94">
         <v>1.33</v>
@@ -21688,7 +21688,7 @@
         <v>1.25</v>
       </c>
       <c r="AP98">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ98">
         <v>1.29</v>
@@ -24366,7 +24366,7 @@
         <v>0.57</v>
       </c>
       <c r="AP111">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ111">
         <v>0.67</v>
@@ -25399,7 +25399,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ116">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR116">
         <v>1.85</v>
@@ -27044,7 +27044,7 @@
         <v>0.8</v>
       </c>
       <c r="AP124">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ124">
         <v>0.71</v>
@@ -28077,7 +28077,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ129">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR129">
         <v>0.88</v>
@@ -30752,7 +30752,7 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ142">
         <v>1.19</v>
@@ -32197,7 +32197,7 @@
         <v>0.53</v>
       </c>
       <c r="AQ149">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR149">
         <v>1</v>
@@ -34872,7 +34872,7 @@
         <v>2.13</v>
       </c>
       <c r="AP162">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ162">
         <v>1.93</v>
@@ -36111,7 +36111,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ168">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR168">
         <v>1.6</v>
@@ -38995,7 +38995,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ182">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR182">
         <v>1.12</v>
@@ -41052,7 +41052,7 @@
         <v>0.89</v>
       </c>
       <c r="AP192">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ192">
         <v>0.67</v>
@@ -44557,7 +44557,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ209">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR209">
         <v>1.52</v>
@@ -46614,7 +46614,7 @@
         <v>0.7</v>
       </c>
       <c r="AP219">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ219">
         <v>0.47</v>
@@ -50737,7 +50737,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ239">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR239">
         <v>1.57</v>
@@ -53000,7 +53000,7 @@
         <v>0.33</v>
       </c>
       <c r="AP250">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ250">
         <v>0.4</v>
@@ -53209,7 +53209,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ251">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR251">
         <v>1.3</v>
@@ -56708,7 +56708,7 @@
         <v>1</v>
       </c>
       <c r="AP268">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ268">
         <v>0.9399999999999999</v>
@@ -59389,7 +59389,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ281">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR281">
         <v>1.63</v>
@@ -59592,7 +59592,7 @@
         <v>0.79</v>
       </c>
       <c r="AP282">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ282">
         <v>0.73</v>
@@ -62891,7 +62891,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ298">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR298">
         <v>1.87</v>
@@ -63585,6 +63585,212 @@
       </c>
       <c r="BP301">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="302" spans="1:68">
+      <c r="A302" s="1">
+        <v>301</v>
+      </c>
+      <c r="B302">
+        <v>7492451</v>
+      </c>
+      <c r="C302" t="s">
+        <v>68</v>
+      </c>
+      <c r="D302" t="s">
+        <v>69</v>
+      </c>
+      <c r="E302" s="2">
+        <v>45751.65625</v>
+      </c>
+      <c r="F302">
+        <v>31</v>
+      </c>
+      <c r="G302" t="s">
+        <v>70</v>
+      </c>
+      <c r="H302" t="s">
+        <v>80</v>
+      </c>
+      <c r="I302">
+        <v>0</v>
+      </c>
+      <c r="J302">
+        <v>0</v>
+      </c>
+      <c r="K302">
+        <v>0</v>
+      </c>
+      <c r="L302">
+        <v>1</v>
+      </c>
+      <c r="M302">
+        <v>0</v>
+      </c>
+      <c r="N302">
+        <v>1</v>
+      </c>
+      <c r="O302" t="s">
+        <v>166</v>
+      </c>
+      <c r="P302" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q302">
+        <v>3.4</v>
+      </c>
+      <c r="R302">
+        <v>1.91</v>
+      </c>
+      <c r="S302">
+        <v>3.75</v>
+      </c>
+      <c r="T302">
+        <v>1.57</v>
+      </c>
+      <c r="U302">
+        <v>2.25</v>
+      </c>
+      <c r="V302">
+        <v>3.75</v>
+      </c>
+      <c r="W302">
+        <v>1.25</v>
+      </c>
+      <c r="X302">
+        <v>13</v>
+      </c>
+      <c r="Y302">
+        <v>1.04</v>
+      </c>
+      <c r="Z302">
+        <v>2.51</v>
+      </c>
+      <c r="AA302">
+        <v>3.14</v>
+      </c>
+      <c r="AB302">
+        <v>3.15</v>
+      </c>
+      <c r="AC302">
+        <v>1.1</v>
+      </c>
+      <c r="AD302">
+        <v>6.5</v>
+      </c>
+      <c r="AE302">
+        <v>1.5</v>
+      </c>
+      <c r="AF302">
+        <v>2.5</v>
+      </c>
+      <c r="AG302">
+        <v>2.25</v>
+      </c>
+      <c r="AH302">
+        <v>1.57</v>
+      </c>
+      <c r="AI302">
+        <v>2.05</v>
+      </c>
+      <c r="AJ302">
+        <v>1.7</v>
+      </c>
+      <c r="AK302">
+        <v>1.36</v>
+      </c>
+      <c r="AL302">
+        <v>1.37</v>
+      </c>
+      <c r="AM302">
+        <v>1.51</v>
+      </c>
+      <c r="AN302">
+        <v>1.27</v>
+      </c>
+      <c r="AO302">
+        <v>1.13</v>
+      </c>
+      <c r="AP302">
+        <v>1.38</v>
+      </c>
+      <c r="AQ302">
+        <v>1.06</v>
+      </c>
+      <c r="AR302">
+        <v>1.29</v>
+      </c>
+      <c r="AS302">
+        <v>1.37</v>
+      </c>
+      <c r="AT302">
+        <v>2.66</v>
+      </c>
+      <c r="AU302">
+        <v>8</v>
+      </c>
+      <c r="AV302">
+        <v>3</v>
+      </c>
+      <c r="AW302">
+        <v>6</v>
+      </c>
+      <c r="AX302">
+        <v>3</v>
+      </c>
+      <c r="AY302">
+        <v>16</v>
+      </c>
+      <c r="AZ302">
+        <v>7</v>
+      </c>
+      <c r="BA302">
+        <v>1</v>
+      </c>
+      <c r="BB302">
+        <v>2</v>
+      </c>
+      <c r="BC302">
+        <v>3</v>
+      </c>
+      <c r="BD302">
+        <v>1.83</v>
+      </c>
+      <c r="BE302">
+        <v>8.5</v>
+      </c>
+      <c r="BF302">
+        <v>2.36</v>
+      </c>
+      <c r="BG302">
+        <v>1.25</v>
+      </c>
+      <c r="BH302">
+        <v>3.28</v>
+      </c>
+      <c r="BI302">
+        <v>1.49</v>
+      </c>
+      <c r="BJ302">
+        <v>2.38</v>
+      </c>
+      <c r="BK302">
+        <v>1.86</v>
+      </c>
+      <c r="BL302">
+        <v>1.84</v>
+      </c>
+      <c r="BM302">
+        <v>2.4</v>
+      </c>
+      <c r="BN302">
+        <v>1.48</v>
+      </c>
+      <c r="BO302">
+        <v>3.2</v>
+      </c>
+      <c r="BP302">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="406">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -841,6 +841,12 @@
     <t>['2', '19']</t>
   </si>
   <si>
+    <t>['60', '69']</t>
+  </si>
+  <si>
+    <t>['23', '64']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1218,6 +1224,15 @@
   <si>
     <t>['82']</t>
   </si>
+  <si>
+    <t>['16', '39', '51']</t>
+  </si>
+  <si>
+    <t>['15', '45']</t>
+  </si>
+  <si>
+    <t>['7', '10']</t>
+  </si>
 </sst>
 </file>
 
@@ -1578,7 +1593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP302"/>
+  <dimension ref="A1:BP305"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1834,7 +1849,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1915,7 +1930,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ2">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2118,10 +2133,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ3">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2452,7 +2467,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2530,7 +2545,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ5">
         <v>1.19</v>
@@ -2658,7 +2673,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -3276,7 +3291,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3482,7 +3497,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3769,7 +3784,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ11">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4100,7 +4115,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4178,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ13">
         <v>1.33</v>
@@ -4306,7 +4321,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4384,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ14">
         <v>1.07</v>
@@ -5336,7 +5351,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5623,7 +5638,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ20">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR20">
         <v>1.16</v>
@@ -5748,7 +5763,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5954,7 +5969,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6366,7 +6381,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6778,7 +6793,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6984,7 +6999,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7190,7 +7205,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7396,7 +7411,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7889,7 +7904,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ31">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR31">
         <v>0.95</v>
@@ -8014,7 +8029,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8504,7 +8519,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ34">
         <v>0.4</v>
@@ -8838,7 +8853,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -8919,7 +8934,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ36">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR36">
         <v>0</v>
@@ -9250,7 +9265,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9456,7 +9471,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9534,10 +9549,10 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ39">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AR39">
         <v>1.18</v>
@@ -9662,7 +9677,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9740,7 +9755,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ40">
         <v>1.06</v>
@@ -9868,7 +9883,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -10074,7 +10089,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10280,7 +10295,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10898,7 +10913,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -11104,7 +11119,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11310,7 +11325,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11388,7 +11403,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ48">
         <v>1.6</v>
@@ -11722,7 +11737,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11928,7 +11943,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12009,7 +12024,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ51">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR51">
         <v>1.68</v>
@@ -12212,7 +12227,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ52">
         <v>0.73</v>
@@ -12340,7 +12355,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12421,7 +12436,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ53">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AR53">
         <v>1.05</v>
@@ -12546,7 +12561,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12752,7 +12767,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12958,7 +12973,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13164,7 +13179,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13657,7 +13672,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ59">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR59">
         <v>0.91</v>
@@ -13988,7 +14003,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14066,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ61">
         <v>0.71</v>
@@ -14275,7 +14290,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ62">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR62">
         <v>1.6</v>
@@ -14812,7 +14827,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -15018,7 +15033,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15224,7 +15239,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15920,7 +15935,7 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ70">
         <v>1.4</v>
@@ -16460,7 +16475,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16744,7 +16759,7 @@
         <v>1.33</v>
       </c>
       <c r="AP74">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ74">
         <v>1.06</v>
@@ -17078,7 +17093,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17284,7 +17299,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17365,7 +17380,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ77">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR77">
         <v>1.41</v>
@@ -17490,7 +17505,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17696,7 +17711,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17983,7 +17998,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ80">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AR80">
         <v>2.02</v>
@@ -18108,7 +18123,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18601,7 +18616,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ83">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR83">
         <v>1.23</v>
@@ -18932,7 +18947,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19216,7 +19231,7 @@
         <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ86">
         <v>0.9399999999999999</v>
@@ -19550,7 +19565,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19628,7 +19643,7 @@
         <v>0.2</v>
       </c>
       <c r="AP88">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ88">
         <v>0.4</v>
@@ -19756,7 +19771,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19962,7 +19977,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20168,7 +20183,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20580,7 +20595,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20658,7 +20673,7 @@
         <v>1.75</v>
       </c>
       <c r="AP93">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ93">
         <v>1.93</v>
@@ -20786,7 +20801,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20992,7 +21007,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -21073,7 +21088,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ95">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AR95">
         <v>0.91</v>
@@ -21404,7 +21419,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21610,7 +21625,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21691,7 +21706,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ98">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR98">
         <v>1.23</v>
@@ -21816,7 +21831,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22434,7 +22449,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22718,7 +22733,7 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ103">
         <v>1.33</v>
@@ -22846,7 +22861,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -23052,7 +23067,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23133,7 +23148,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ105">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR105">
         <v>1.14</v>
@@ -23258,7 +23273,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23751,7 +23766,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ108">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR108">
         <v>0.82</v>
@@ -23954,7 +23969,7 @@
         <v>0.75</v>
       </c>
       <c r="AP109">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ109">
         <v>1.07</v>
@@ -24082,7 +24097,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24288,7 +24303,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24369,7 +24384,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ111">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR111">
         <v>1.25</v>
@@ -24494,7 +24509,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24700,7 +24715,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24906,7 +24921,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25318,7 +25333,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25524,7 +25539,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -26014,7 +26029,7 @@
         <v>1.2</v>
       </c>
       <c r="AP119">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ119">
         <v>1.67</v>
@@ -26348,7 +26363,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26429,7 +26444,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ121">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AR121">
         <v>1.14</v>
@@ -26632,7 +26647,7 @@
         <v>2.2</v>
       </c>
       <c r="AP122">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ122">
         <v>1.71</v>
@@ -26760,7 +26775,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26838,7 +26853,7 @@
         <v>1.67</v>
       </c>
       <c r="AP123">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ123">
         <v>2.06</v>
@@ -26966,7 +26981,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27172,7 +27187,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27253,7 +27268,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ125">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR125">
         <v>1.5</v>
@@ -27378,7 +27393,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27996,7 +28011,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -28898,7 +28913,7 @@
         <v>1.5</v>
       </c>
       <c r="AP133">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ133">
         <v>0.9399999999999999</v>
@@ -29232,7 +29247,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29438,7 +29453,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29722,7 +29737,7 @@
         <v>1.5</v>
       </c>
       <c r="AP137">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ137">
         <v>1.67</v>
@@ -29850,7 +29865,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -30056,7 +30071,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30880,7 +30895,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -31086,7 +31101,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31498,7 +31513,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31704,7 +31719,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31785,7 +31800,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ147">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR147">
         <v>1.55</v>
@@ -32116,7 +32131,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32194,7 +32209,7 @@
         <v>0.71</v>
       </c>
       <c r="AP149">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ149">
         <v>1.06</v>
@@ -32528,7 +32543,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32734,7 +32749,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32940,7 +32955,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -33352,7 +33367,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -33430,7 +33445,7 @@
         <v>0.43</v>
       </c>
       <c r="AP155">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ155">
         <v>1.07</v>
@@ -33639,7 +33654,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ156">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR156">
         <v>1.61</v>
@@ -34048,7 +34063,7 @@
         <v>1.5</v>
       </c>
       <c r="AP158">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ158">
         <v>1.07</v>
@@ -34176,7 +34191,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34257,7 +34272,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ159">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AR159">
         <v>1.56</v>
@@ -34588,7 +34603,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34794,7 +34809,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -35000,7 +35015,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35412,7 +35427,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35618,7 +35633,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35824,7 +35839,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35902,7 +35917,7 @@
         <v>1.86</v>
       </c>
       <c r="AP167">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ167">
         <v>1.71</v>
@@ -36030,7 +36045,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36317,7 +36332,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ169">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR169">
         <v>1.57</v>
@@ -36520,7 +36535,7 @@
         <v>0.88</v>
       </c>
       <c r="AP170">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ170">
         <v>0.47</v>
@@ -36648,7 +36663,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36854,7 +36869,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -36935,7 +36950,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ172">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AR172">
         <v>1.46</v>
@@ -37060,7 +37075,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37266,7 +37281,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37678,7 +37693,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -37759,7 +37774,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ176">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR176">
         <v>1.42</v>
@@ -37962,7 +37977,7 @@
         <v>0.5</v>
       </c>
       <c r="AP177">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ177">
         <v>1.4</v>
@@ -38296,7 +38311,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38708,7 +38723,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39120,7 +39135,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39198,7 +39213,7 @@
         <v>0.63</v>
       </c>
       <c r="AP183">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ183">
         <v>0.71</v>
@@ -39944,7 +39959,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40025,7 +40040,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ187">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR187">
         <v>1.47</v>
@@ -40356,7 +40371,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40768,7 +40783,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -40846,7 +40861,7 @@
         <v>0.89</v>
       </c>
       <c r="AP191">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ191">
         <v>0.71</v>
@@ -41261,7 +41276,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ193">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AR193">
         <v>1.41</v>
@@ -41386,7 +41401,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41876,10 +41891,10 @@
         <v>1.67</v>
       </c>
       <c r="AP196">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ196">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR196">
         <v>1.17</v>
@@ -42004,7 +42019,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42416,7 +42431,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42622,7 +42637,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42828,7 +42843,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -43240,7 +43255,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43652,7 +43667,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43936,7 +43951,7 @@
         <v>0.3</v>
       </c>
       <c r="AP206">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ206">
         <v>0.4</v>
@@ -44064,7 +44079,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44270,7 +44285,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44888,7 +44903,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45506,7 +45521,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45584,7 +45599,7 @@
         <v>0.8</v>
       </c>
       <c r="AP214">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ214">
         <v>0.67</v>
@@ -45712,7 +45727,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45918,7 +45933,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -45999,7 +46014,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ216">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AR216">
         <v>1.3</v>
@@ -46124,7 +46139,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46205,7 +46220,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ217">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR217">
         <v>1.44</v>
@@ -46330,7 +46345,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46742,7 +46757,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46820,7 +46835,7 @@
         <v>0.64</v>
       </c>
       <c r="AP220">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ220">
         <v>0.73</v>
@@ -46948,7 +46963,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47232,7 +47247,7 @@
         <v>0.91</v>
       </c>
       <c r="AP222">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ222">
         <v>1.07</v>
@@ -47360,7 +47375,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47647,7 +47662,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ224">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR224">
         <v>1.75</v>
@@ -47772,7 +47787,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47978,7 +47993,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -48262,10 +48277,10 @@
         <v>2.6</v>
       </c>
       <c r="AP227">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ227">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AR227">
         <v>1.73</v>
@@ -48390,7 +48405,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48596,7 +48611,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48883,7 +48898,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ230">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AR230">
         <v>1.55</v>
@@ -49008,7 +49023,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49214,7 +49229,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49420,7 +49435,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49626,7 +49641,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -50244,7 +50259,7 @@
         <v>241</v>
       </c>
       <c r="P237" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q237">
         <v>1.91</v>
@@ -50656,7 +50671,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -50943,7 +50958,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ240">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR240">
         <v>1.63</v>
@@ -51068,7 +51083,7 @@
         <v>244</v>
       </c>
       <c r="P241" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q241">
         <v>2.5</v>
@@ -51480,7 +51495,7 @@
         <v>245</v>
       </c>
       <c r="P243" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q243">
         <v>3.4</v>
@@ -51764,7 +51779,7 @@
         <v>1.08</v>
       </c>
       <c r="AP244">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ244">
         <v>1.07</v>
@@ -51892,7 +51907,7 @@
         <v>92</v>
       </c>
       <c r="P245" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q245">
         <v>2.6</v>
@@ -51973,7 +51988,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ245">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR245">
         <v>1.56</v>
@@ -52176,7 +52191,7 @@
         <v>0.83</v>
       </c>
       <c r="AP246">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ246">
         <v>0.73</v>
@@ -52510,7 +52525,7 @@
         <v>92</v>
       </c>
       <c r="P248" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q248">
         <v>4</v>
@@ -52588,7 +52603,7 @@
         <v>1</v>
       </c>
       <c r="AP248">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ248">
         <v>1.4</v>
@@ -52797,7 +52812,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ249">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AR249">
         <v>1.57</v>
@@ -53412,7 +53427,7 @@
         <v>1.5</v>
       </c>
       <c r="AP252">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ252">
         <v>1.6</v>
@@ -54158,7 +54173,7 @@
         <v>250</v>
       </c>
       <c r="P256" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q256">
         <v>4</v>
@@ -54445,7 +54460,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ257">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR257">
         <v>1.24</v>
@@ -54570,7 +54585,7 @@
         <v>92</v>
       </c>
       <c r="P258" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q258">
         <v>6</v>
@@ -54776,7 +54791,7 @@
         <v>92</v>
       </c>
       <c r="P259" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q259">
         <v>4.75</v>
@@ -55887,7 +55902,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ264">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AR264">
         <v>1.6</v>
@@ -56218,7 +56233,7 @@
         <v>92</v>
       </c>
       <c r="P266" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q266">
         <v>4.75</v>
@@ -56296,7 +56311,7 @@
         <v>1.08</v>
       </c>
       <c r="AP266">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ266">
         <v>1.19</v>
@@ -56917,7 +56932,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ269">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR269">
         <v>1.63</v>
@@ -57042,7 +57057,7 @@
         <v>146</v>
       </c>
       <c r="P270" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Q270">
         <v>2.63</v>
@@ -57120,7 +57135,7 @@
         <v>1.69</v>
       </c>
       <c r="AP270">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ270">
         <v>1.67</v>
@@ -57660,7 +57675,7 @@
         <v>260</v>
       </c>
       <c r="P273" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q273">
         <v>3.5</v>
@@ -57738,7 +57753,7 @@
         <v>1.21</v>
       </c>
       <c r="AP273">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ273">
         <v>1.19</v>
@@ -58072,7 +58087,7 @@
         <v>261</v>
       </c>
       <c r="P275" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q275">
         <v>5</v>
@@ -58278,7 +58293,7 @@
         <v>262</v>
       </c>
       <c r="P276" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q276">
         <v>1.5</v>
@@ -58484,7 +58499,7 @@
         <v>103</v>
       </c>
       <c r="P277" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Q277">
         <v>5.5</v>
@@ -58690,7 +58705,7 @@
         <v>263</v>
       </c>
       <c r="P278" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q278">
         <v>2.2</v>
@@ -58771,7 +58786,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ278">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR278">
         <v>1.64</v>
@@ -58896,7 +58911,7 @@
         <v>92</v>
       </c>
       <c r="P279" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Q279">
         <v>4</v>
@@ -59102,7 +59117,7 @@
         <v>92</v>
       </c>
       <c r="P280" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Q280">
         <v>3.1</v>
@@ -59514,7 +59529,7 @@
         <v>265</v>
       </c>
       <c r="P282" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q282">
         <v>2.75</v>
@@ -59720,7 +59735,7 @@
         <v>92</v>
       </c>
       <c r="P283" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q283">
         <v>2.4</v>
@@ -59926,7 +59941,7 @@
         <v>216</v>
       </c>
       <c r="P284" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q284">
         <v>3.6</v>
@@ -60004,7 +60019,7 @@
         <v>0.62</v>
       </c>
       <c r="AP284">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AQ284">
         <v>0.67</v>
@@ -60132,7 +60147,7 @@
         <v>266</v>
       </c>
       <c r="P285" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q285">
         <v>2.4</v>
@@ -60210,10 +60225,10 @@
         <v>0.71</v>
       </c>
       <c r="AP285">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ285">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR285">
         <v>1.72</v>
@@ -61368,7 +61383,7 @@
         <v>92</v>
       </c>
       <c r="P291" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Q291">
         <v>3.2</v>
@@ -61449,7 +61464,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ291">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AR291">
         <v>1.86</v>
@@ -62810,7 +62825,7 @@
         <v>273</v>
       </c>
       <c r="P298" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Q298">
         <v>1.95</v>
@@ -63016,7 +63031,7 @@
         <v>274</v>
       </c>
       <c r="P299" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q299">
         <v>2.6</v>
@@ -63428,7 +63443,7 @@
         <v>94</v>
       </c>
       <c r="P301" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="Q301">
         <v>2.4</v>
@@ -63791,6 +63806,624 @@
       </c>
       <c r="BP302">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="303" spans="1:68">
+      <c r="A303" s="1">
+        <v>302</v>
+      </c>
+      <c r="B303">
+        <v>7492454</v>
+      </c>
+      <c r="C303" t="s">
+        <v>68</v>
+      </c>
+      <c r="D303" t="s">
+        <v>69</v>
+      </c>
+      <c r="E303" s="2">
+        <v>45752.41666666666</v>
+      </c>
+      <c r="F303">
+        <v>31</v>
+      </c>
+      <c r="G303" t="s">
+        <v>81</v>
+      </c>
+      <c r="H303" t="s">
+        <v>88</v>
+      </c>
+      <c r="I303">
+        <v>1</v>
+      </c>
+      <c r="J303">
+        <v>2</v>
+      </c>
+      <c r="K303">
+        <v>3</v>
+      </c>
+      <c r="L303">
+        <v>1</v>
+      </c>
+      <c r="M303">
+        <v>3</v>
+      </c>
+      <c r="N303">
+        <v>4</v>
+      </c>
+      <c r="O303" t="s">
+        <v>167</v>
+      </c>
+      <c r="P303" t="s">
+        <v>403</v>
+      </c>
+      <c r="Q303">
+        <v>5.5</v>
+      </c>
+      <c r="R303">
+        <v>2.2</v>
+      </c>
+      <c r="S303">
+        <v>2.3</v>
+      </c>
+      <c r="T303">
+        <v>1.4</v>
+      </c>
+      <c r="U303">
+        <v>2.75</v>
+      </c>
+      <c r="V303">
+        <v>3</v>
+      </c>
+      <c r="W303">
+        <v>1.36</v>
+      </c>
+      <c r="X303">
+        <v>8</v>
+      </c>
+      <c r="Y303">
+        <v>1.08</v>
+      </c>
+      <c r="Z303">
+        <v>4.6</v>
+      </c>
+      <c r="AA303">
+        <v>3.74</v>
+      </c>
+      <c r="AB303">
+        <v>1.81</v>
+      </c>
+      <c r="AC303">
+        <v>1</v>
+      </c>
+      <c r="AD303">
+        <v>9</v>
+      </c>
+      <c r="AE303">
+        <v>1.29</v>
+      </c>
+      <c r="AF303">
+        <v>3.79</v>
+      </c>
+      <c r="AG303">
+        <v>1.98</v>
+      </c>
+      <c r="AH303">
+        <v>1.83</v>
+      </c>
+      <c r="AI303">
+        <v>1.95</v>
+      </c>
+      <c r="AJ303">
+        <v>1.8</v>
+      </c>
+      <c r="AK303">
+        <v>2.25</v>
+      </c>
+      <c r="AL303">
+        <v>1.29</v>
+      </c>
+      <c r="AM303">
+        <v>1.18</v>
+      </c>
+      <c r="AN303">
+        <v>0.53</v>
+      </c>
+      <c r="AO303">
+        <v>0.67</v>
+      </c>
+      <c r="AP303">
+        <v>0.5</v>
+      </c>
+      <c r="AQ303">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AR303">
+        <v>1.2</v>
+      </c>
+      <c r="AS303">
+        <v>1.33</v>
+      </c>
+      <c r="AT303">
+        <v>2.53</v>
+      </c>
+      <c r="AU303">
+        <v>5</v>
+      </c>
+      <c r="AV303">
+        <v>8</v>
+      </c>
+      <c r="AW303">
+        <v>4</v>
+      </c>
+      <c r="AX303">
+        <v>10</v>
+      </c>
+      <c r="AY303">
+        <v>11</v>
+      </c>
+      <c r="AZ303">
+        <v>20</v>
+      </c>
+      <c r="BA303">
+        <v>2</v>
+      </c>
+      <c r="BB303">
+        <v>2</v>
+      </c>
+      <c r="BC303">
+        <v>4</v>
+      </c>
+      <c r="BD303">
+        <v>3.2</v>
+      </c>
+      <c r="BE303">
+        <v>8.5</v>
+      </c>
+      <c r="BF303">
+        <v>1.52</v>
+      </c>
+      <c r="BG303">
+        <v>1.45</v>
+      </c>
+      <c r="BH303">
+        <v>2.58</v>
+      </c>
+      <c r="BI303">
+        <v>1.8</v>
+      </c>
+      <c r="BJ303">
+        <v>2.01</v>
+      </c>
+      <c r="BK303">
+        <v>2.23</v>
+      </c>
+      <c r="BL303">
+        <v>1.61</v>
+      </c>
+      <c r="BM303">
+        <v>3.08</v>
+      </c>
+      <c r="BN303">
+        <v>1.28</v>
+      </c>
+      <c r="BO303">
+        <v>4.4</v>
+      </c>
+      <c r="BP303">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="304" spans="1:68">
+      <c r="A304" s="1">
+        <v>303</v>
+      </c>
+      <c r="B304">
+        <v>7492455</v>
+      </c>
+      <c r="C304" t="s">
+        <v>68</v>
+      </c>
+      <c r="D304" t="s">
+        <v>69</v>
+      </c>
+      <c r="E304" s="2">
+        <v>45752.54166666666</v>
+      </c>
+      <c r="F304">
+        <v>31</v>
+      </c>
+      <c r="G304" t="s">
+        <v>71</v>
+      </c>
+      <c r="H304" t="s">
+        <v>82</v>
+      </c>
+      <c r="I304">
+        <v>0</v>
+      </c>
+      <c r="J304">
+        <v>2</v>
+      </c>
+      <c r="K304">
+        <v>2</v>
+      </c>
+      <c r="L304">
+        <v>2</v>
+      </c>
+      <c r="M304">
+        <v>2</v>
+      </c>
+      <c r="N304">
+        <v>4</v>
+      </c>
+      <c r="O304" t="s">
+        <v>275</v>
+      </c>
+      <c r="P304" t="s">
+        <v>404</v>
+      </c>
+      <c r="Q304">
+        <v>6</v>
+      </c>
+      <c r="R304">
+        <v>2.4</v>
+      </c>
+      <c r="S304">
+        <v>2</v>
+      </c>
+      <c r="T304">
+        <v>1.3</v>
+      </c>
+      <c r="U304">
+        <v>3.4</v>
+      </c>
+      <c r="V304">
+        <v>2.5</v>
+      </c>
+      <c r="W304">
+        <v>1.5</v>
+      </c>
+      <c r="X304">
+        <v>6</v>
+      </c>
+      <c r="Y304">
+        <v>1.13</v>
+      </c>
+      <c r="Z304">
+        <v>6.5</v>
+      </c>
+      <c r="AA304">
+        <v>4.75</v>
+      </c>
+      <c r="AB304">
+        <v>1.49</v>
+      </c>
+      <c r="AC304">
+        <v>0</v>
+      </c>
+      <c r="AD304">
+        <v>0</v>
+      </c>
+      <c r="AE304">
+        <v>1.16</v>
+      </c>
+      <c r="AF304">
+        <v>4.1</v>
+      </c>
+      <c r="AG304">
+        <v>1.61</v>
+      </c>
+      <c r="AH304">
+        <v>2.2</v>
+      </c>
+      <c r="AI304">
+        <v>1.8</v>
+      </c>
+      <c r="AJ304">
+        <v>1.95</v>
+      </c>
+      <c r="AK304">
+        <v>2.92</v>
+      </c>
+      <c r="AL304">
+        <v>1.22</v>
+      </c>
+      <c r="AM304">
+        <v>1.11</v>
+      </c>
+      <c r="AN304">
+        <v>1.07</v>
+      </c>
+      <c r="AO304">
+        <v>2.07</v>
+      </c>
+      <c r="AP304">
+        <v>1.06</v>
+      </c>
+      <c r="AQ304">
+        <v>2</v>
+      </c>
+      <c r="AR304">
+        <v>1.35</v>
+      </c>
+      <c r="AS304">
+        <v>1.55</v>
+      </c>
+      <c r="AT304">
+        <v>2.9</v>
+      </c>
+      <c r="AU304">
+        <v>5</v>
+      </c>
+      <c r="AV304">
+        <v>5</v>
+      </c>
+      <c r="AW304">
+        <v>4</v>
+      </c>
+      <c r="AX304">
+        <v>16</v>
+      </c>
+      <c r="AY304">
+        <v>11</v>
+      </c>
+      <c r="AZ304">
+        <v>23</v>
+      </c>
+      <c r="BA304">
+        <v>2</v>
+      </c>
+      <c r="BB304">
+        <v>4</v>
+      </c>
+      <c r="BC304">
+        <v>6</v>
+      </c>
+      <c r="BD304">
+        <v>3.9</v>
+      </c>
+      <c r="BE304">
+        <v>9.9</v>
+      </c>
+      <c r="BF304">
+        <v>1.37</v>
+      </c>
+      <c r="BG304">
+        <v>1.2</v>
+      </c>
+      <c r="BH304">
+        <v>3.7</v>
+      </c>
+      <c r="BI304">
+        <v>1.47</v>
+      </c>
+      <c r="BJ304">
+        <v>2.55</v>
+      </c>
+      <c r="BK304">
+        <v>1.78</v>
+      </c>
+      <c r="BL304">
+        <v>2</v>
+      </c>
+      <c r="BM304">
+        <v>2.2</v>
+      </c>
+      <c r="BN304">
+        <v>1.64</v>
+      </c>
+      <c r="BO304">
+        <v>2.88</v>
+      </c>
+      <c r="BP304">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="305" spans="1:68">
+      <c r="A305" s="1">
+        <v>304</v>
+      </c>
+      <c r="B305">
+        <v>7492453</v>
+      </c>
+      <c r="C305" t="s">
+        <v>68</v>
+      </c>
+      <c r="D305" t="s">
+        <v>69</v>
+      </c>
+      <c r="E305" s="2">
+        <v>45752.65625</v>
+      </c>
+      <c r="F305">
+        <v>31</v>
+      </c>
+      <c r="G305" t="s">
+        <v>73</v>
+      </c>
+      <c r="H305" t="s">
+        <v>83</v>
+      </c>
+      <c r="I305">
+        <v>1</v>
+      </c>
+      <c r="J305">
+        <v>2</v>
+      </c>
+      <c r="K305">
+        <v>3</v>
+      </c>
+      <c r="L305">
+        <v>2</v>
+      </c>
+      <c r="M305">
+        <v>2</v>
+      </c>
+      <c r="N305">
+        <v>4</v>
+      </c>
+      <c r="O305" t="s">
+        <v>276</v>
+      </c>
+      <c r="P305" t="s">
+        <v>405</v>
+      </c>
+      <c r="Q305">
+        <v>2.5</v>
+      </c>
+      <c r="R305">
+        <v>2.3</v>
+      </c>
+      <c r="S305">
+        <v>4.33</v>
+      </c>
+      <c r="T305">
+        <v>1.33</v>
+      </c>
+      <c r="U305">
+        <v>3.25</v>
+      </c>
+      <c r="V305">
+        <v>2.63</v>
+      </c>
+      <c r="W305">
+        <v>1.44</v>
+      </c>
+      <c r="X305">
+        <v>6.5</v>
+      </c>
+      <c r="Y305">
+        <v>1.11</v>
+      </c>
+      <c r="Z305">
+        <v>1.79</v>
+      </c>
+      <c r="AA305">
+        <v>3.99</v>
+      </c>
+      <c r="AB305">
+        <v>4.4</v>
+      </c>
+      <c r="AC305">
+        <v>1.06</v>
+      </c>
+      <c r="AD305">
+        <v>10.5</v>
+      </c>
+      <c r="AE305">
+        <v>1.19</v>
+      </c>
+      <c r="AF305">
+        <v>4.05</v>
+      </c>
+      <c r="AG305">
+        <v>1.7</v>
+      </c>
+      <c r="AH305">
+        <v>2.05</v>
+      </c>
+      <c r="AI305">
+        <v>1.67</v>
+      </c>
+      <c r="AJ305">
+        <v>2.1</v>
+      </c>
+      <c r="AK305">
+        <v>1.25</v>
+      </c>
+      <c r="AL305">
+        <v>1.3</v>
+      </c>
+      <c r="AM305">
+        <v>2.01</v>
+      </c>
+      <c r="AN305">
+        <v>1.8</v>
+      </c>
+      <c r="AO305">
+        <v>1.29</v>
+      </c>
+      <c r="AP305">
+        <v>1.75</v>
+      </c>
+      <c r="AQ305">
+        <v>1.27</v>
+      </c>
+      <c r="AR305">
+        <v>1.68</v>
+      </c>
+      <c r="AS305">
+        <v>1.19</v>
+      </c>
+      <c r="AT305">
+        <v>2.87</v>
+      </c>
+      <c r="AU305">
+        <v>7</v>
+      </c>
+      <c r="AV305">
+        <v>9</v>
+      </c>
+      <c r="AW305">
+        <v>13</v>
+      </c>
+      <c r="AX305">
+        <v>7</v>
+      </c>
+      <c r="AY305">
+        <v>25</v>
+      </c>
+      <c r="AZ305">
+        <v>18</v>
+      </c>
+      <c r="BA305">
+        <v>7</v>
+      </c>
+      <c r="BB305">
+        <v>4</v>
+      </c>
+      <c r="BC305">
+        <v>11</v>
+      </c>
+      <c r="BD305">
+        <v>1.55</v>
+      </c>
+      <c r="BE305">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF305">
+        <v>3.06</v>
+      </c>
+      <c r="BG305">
+        <v>1.32</v>
+      </c>
+      <c r="BH305">
+        <v>2.88</v>
+      </c>
+      <c r="BI305">
+        <v>1.66</v>
+      </c>
+      <c r="BJ305">
+        <v>2.16</v>
+      </c>
+      <c r="BK305">
+        <v>2.09</v>
+      </c>
+      <c r="BL305">
+        <v>1.7</v>
+      </c>
+      <c r="BM305">
+        <v>2.57</v>
+      </c>
+      <c r="BN305">
+        <v>1.46</v>
+      </c>
+      <c r="BO305">
+        <v>3.74</v>
+      </c>
+      <c r="BP305">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1922" uniqueCount="408">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -847,6 +847,9 @@
     <t>['23', '64']</t>
   </si>
   <si>
+    <t>['67']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1233,6 +1236,9 @@
   <si>
     <t>['7', '10']</t>
   </si>
+  <si>
+    <t>['64']</t>
+  </si>
 </sst>
 </file>
 
@@ -1593,7 +1599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP305"/>
+  <dimension ref="A1:BP310"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1849,7 +1855,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2339,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ4">
         <v>0.47</v>
@@ -2467,7 +2473,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2673,7 +2679,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -3291,7 +3297,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3372,7 +3378,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ9">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3497,7 +3503,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -3575,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ10">
         <v>2.06</v>
@@ -3990,7 +3996,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ12">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4115,7 +4121,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4321,7 +4327,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4814,7 +4820,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ16">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5017,7 +5023,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ17">
         <v>2.06</v>
@@ -5351,7 +5357,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5429,7 +5435,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ19">
         <v>0.9399999999999999</v>
@@ -5763,7 +5769,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5844,7 +5850,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ21">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR21">
         <v>1.14</v>
@@ -5969,7 +5975,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6381,7 +6387,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6665,10 +6671,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ25">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR25">
         <v>1.74</v>
@@ -6793,7 +6799,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -6999,7 +7005,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7205,7 +7211,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7411,7 +7417,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -7492,7 +7498,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ29">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR29">
         <v>1.56</v>
@@ -8029,7 +8035,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8313,10 +8319,10 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ33">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR33">
         <v>0.96</v>
@@ -8522,7 +8528,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ34">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR34">
         <v>2.22</v>
@@ -8853,7 +8859,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -8931,7 +8937,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ36">
         <v>1.27</v>
@@ -9137,7 +9143,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ37">
         <v>0.73</v>
@@ -9265,7 +9271,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9471,7 +9477,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9677,7 +9683,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9883,7 +9889,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -9964,7 +9970,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ41">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR41">
         <v>1.35</v>
@@ -10089,7 +10095,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10295,7 +10301,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10913,7 +10919,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -10991,7 +10997,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ46">
         <v>0.67</v>
@@ -11119,7 +11125,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11200,7 +11206,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ47">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR47">
         <v>1.69</v>
@@ -11325,7 +11331,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11609,7 +11615,7 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ49">
         <v>1.06</v>
@@ -11737,7 +11743,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11943,7 +11949,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12021,7 +12027,7 @@
         <v>0.33</v>
       </c>
       <c r="AP51">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ51">
         <v>0.8100000000000001</v>
@@ -12355,7 +12361,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12561,7 +12567,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12642,7 +12648,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ54">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR54">
         <v>1.48</v>
@@ -12767,7 +12773,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12973,7 +12979,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13051,10 +13057,10 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ56">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR56">
         <v>1.02</v>
@@ -13179,7 +13185,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13260,7 +13266,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ57">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR57">
         <v>1.29</v>
@@ -13463,10 +13469,10 @@
         <v>0.33</v>
       </c>
       <c r="AP58">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ58">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR58">
         <v>2.07</v>
@@ -13669,7 +13675,7 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ59">
         <v>1.27</v>
@@ -14003,7 +14009,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14084,7 +14090,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ61">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR61">
         <v>1.23</v>
@@ -14496,7 +14502,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ63">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR63">
         <v>0.9</v>
@@ -14827,7 +14833,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -14905,7 +14911,7 @@
         <v>1.5</v>
       </c>
       <c r="AP65">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ65">
         <v>1.07</v>
@@ -15033,7 +15039,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15239,7 +15245,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15320,7 +15326,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ67">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR67">
         <v>1.09</v>
@@ -16475,7 +16481,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16968,7 +16974,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ75">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR75">
         <v>1.37</v>
@@ -17093,7 +17099,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17171,7 +17177,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ76">
         <v>1.93</v>
@@ -17299,7 +17305,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17377,7 +17383,7 @@
         <v>0.67</v>
       </c>
       <c r="AP77">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ77">
         <v>1.27</v>
@@ -17505,7 +17511,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17711,7 +17717,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -17995,7 +18001,7 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ80">
         <v>2</v>
@@ -18123,7 +18129,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18410,7 +18416,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ82">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR82">
         <v>1.1</v>
@@ -18613,7 +18619,7 @@
         <v>0.8</v>
       </c>
       <c r="AP83">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ83">
         <v>0.8100000000000001</v>
@@ -18947,7 +18953,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19025,10 +19031,10 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ85">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR85">
         <v>1.74</v>
@@ -19565,7 +19571,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19646,7 +19652,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ88">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR88">
         <v>0.85</v>
@@ -19771,7 +19777,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19852,7 +19858,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ89">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR89">
         <v>1.46</v>
@@ -19977,7 +19983,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20183,7 +20189,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20467,10 +20473,10 @@
         <v>0.75</v>
       </c>
       <c r="AP92">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ92">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR92">
         <v>1.25</v>
@@ -20595,7 +20601,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20801,7 +20807,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -21007,7 +21013,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -21085,7 +21091,7 @@
         <v>2</v>
       </c>
       <c r="AP95">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ95">
         <v>2</v>
@@ -21291,7 +21297,7 @@
         <v>1.25</v>
       </c>
       <c r="AP96">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ96">
         <v>0.47</v>
@@ -21419,7 +21425,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21625,7 +21631,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21831,7 +21837,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21912,7 +21918,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ99">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR99">
         <v>1.62</v>
@@ -22115,7 +22121,7 @@
         <v>1.4</v>
       </c>
       <c r="AP100">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ100">
         <v>1.19</v>
@@ -22449,7 +22455,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22530,7 +22536,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ102">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR102">
         <v>1.16</v>
@@ -22861,7 +22867,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -23067,7 +23073,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23145,7 +23151,7 @@
         <v>1.6</v>
       </c>
       <c r="AP105">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ105">
         <v>1.27</v>
@@ -23273,7 +23279,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -23560,7 +23566,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ107">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR107">
         <v>1.54</v>
@@ -23763,7 +23769,7 @@
         <v>0.67</v>
       </c>
       <c r="AP108">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ108">
         <v>0.8100000000000001</v>
@@ -24097,7 +24103,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24178,7 +24184,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ110">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR110">
         <v>1.55</v>
@@ -24303,7 +24309,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24509,7 +24515,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24587,7 +24593,7 @@
         <v>1.6</v>
       </c>
       <c r="AP112">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ112">
         <v>0.9399999999999999</v>
@@ -24715,7 +24721,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24921,7 +24927,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25333,7 +25339,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25411,7 +25417,7 @@
         <v>0.8</v>
       </c>
       <c r="AP116">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ116">
         <v>1.06</v>
@@ -25539,7 +25545,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25617,7 +25623,7 @@
         <v>1.6</v>
       </c>
       <c r="AP117">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ117">
         <v>1.6</v>
@@ -25826,7 +25832,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ118">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR118">
         <v>1.7</v>
@@ -26032,7 +26038,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ119">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR119">
         <v>0.96</v>
@@ -26363,7 +26369,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26650,7 +26656,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ122">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR122">
         <v>1.69</v>
@@ -26775,7 +26781,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26981,7 +26987,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27062,7 +27068,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ124">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR124">
         <v>1.24</v>
@@ -27187,7 +27193,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27393,7 +27399,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -27471,7 +27477,7 @@
         <v>1</v>
       </c>
       <c r="AP126">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ126">
         <v>0.47</v>
@@ -28011,7 +28017,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -28089,7 +28095,7 @@
         <v>0.67</v>
       </c>
       <c r="AP129">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ129">
         <v>1.06</v>
@@ -28504,7 +28510,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ131">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR131">
         <v>1.36</v>
@@ -29122,7 +29128,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ134">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR134">
         <v>1.52</v>
@@ -29247,7 +29253,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29453,7 +29459,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29531,7 +29537,7 @@
         <v>1.83</v>
       </c>
       <c r="AP136">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ136">
         <v>1.93</v>
@@ -29740,7 +29746,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ137">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR137">
         <v>1.24</v>
@@ -29865,7 +29871,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -29943,10 +29949,10 @@
         <v>2</v>
       </c>
       <c r="AP138">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ138">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR138">
         <v>1.39</v>
@@ -30071,7 +30077,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30149,7 +30155,7 @@
         <v>1.86</v>
       </c>
       <c r="AP139">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ139">
         <v>2.06</v>
@@ -30561,7 +30567,7 @@
         <v>1.33</v>
       </c>
       <c r="AP141">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ141">
         <v>1.33</v>
@@ -30895,7 +30901,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -31101,7 +31107,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31179,7 +31185,7 @@
         <v>0.57</v>
       </c>
       <c r="AP144">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ144">
         <v>0.73</v>
@@ -31388,7 +31394,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ145">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR145">
         <v>1.69</v>
@@ -31513,7 +31519,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31719,7 +31725,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -32006,7 +32012,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ148">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR148">
         <v>1.5</v>
@@ -32131,7 +32137,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32415,7 +32421,7 @@
         <v>1</v>
       </c>
       <c r="AP150">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ150">
         <v>1.19</v>
@@ -32543,7 +32549,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32749,7 +32755,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32955,7 +32961,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -33036,7 +33042,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ153">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR153">
         <v>1.41</v>
@@ -33239,7 +33245,7 @@
         <v>1</v>
       </c>
       <c r="AP154">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ154">
         <v>0.47</v>
@@ -33367,7 +33373,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -33448,7 +33454,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ155">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR155">
         <v>1.24</v>
@@ -34191,7 +34197,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34603,7 +34609,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34681,7 +34687,7 @@
         <v>1.5</v>
       </c>
       <c r="AP161">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ161">
         <v>1.6</v>
@@ -34809,7 +34815,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -35015,7 +35021,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35093,10 +35099,10 @@
         <v>1.5</v>
       </c>
       <c r="AP163">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ163">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR163">
         <v>1.36</v>
@@ -35299,7 +35305,7 @@
         <v>1</v>
       </c>
       <c r="AP164">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ164">
         <v>0.67</v>
@@ -35427,7 +35433,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35508,7 +35514,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ165">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR165">
         <v>1.48</v>
@@ -35633,7 +35639,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35711,7 +35717,7 @@
         <v>1.5</v>
       </c>
       <c r="AP166">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ166">
         <v>0.9399999999999999</v>
@@ -35839,7 +35845,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -35920,7 +35926,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ167">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR167">
         <v>1.14</v>
@@ -36045,7 +36051,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36663,7 +36669,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36741,7 +36747,7 @@
         <v>1.43</v>
       </c>
       <c r="AP171">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ171">
         <v>1.07</v>
@@ -36869,7 +36875,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -37075,7 +37081,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37281,7 +37287,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37568,7 +37574,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ175">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR175">
         <v>1.48</v>
@@ -37693,7 +37699,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -38311,7 +38317,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38392,7 +38398,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ179">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR179">
         <v>1.61</v>
@@ -38723,7 +38729,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39135,7 +39141,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39216,7 +39222,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ183">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR183">
         <v>1.19</v>
@@ -39419,7 +39425,7 @@
         <v>1.63</v>
       </c>
       <c r="AP184">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ184">
         <v>1.07</v>
@@ -39625,7 +39631,7 @@
         <v>0.88</v>
       </c>
       <c r="AP185">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ185">
         <v>0.67</v>
@@ -39831,10 +39837,10 @@
         <v>1.67</v>
       </c>
       <c r="AP186">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ186">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR186">
         <v>1.62</v>
@@ -39959,7 +39965,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40371,7 +40377,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40449,7 +40455,7 @@
         <v>0.44</v>
       </c>
       <c r="AP189">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ189">
         <v>0.73</v>
@@ -40655,10 +40661,10 @@
         <v>2</v>
       </c>
       <c r="AP190">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ190">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR190">
         <v>1.04</v>
@@ -40783,7 +40789,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -40864,7 +40870,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ191">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR191">
         <v>1.6</v>
@@ -41401,7 +41407,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41688,7 +41694,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ195">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR195">
         <v>1.59</v>
@@ -42019,7 +42025,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42303,10 +42309,10 @@
         <v>1.89</v>
       </c>
       <c r="AP198">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ198">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR198">
         <v>1.78</v>
@@ -42431,7 +42437,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42637,7 +42643,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42715,7 +42721,7 @@
         <v>1.56</v>
       </c>
       <c r="AP200">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ200">
         <v>1.07</v>
@@ -42843,7 +42849,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -43255,7 +43261,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43333,7 +43339,7 @@
         <v>2.3</v>
       </c>
       <c r="AP203">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ203">
         <v>1.93</v>
@@ -43667,7 +43673,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -43954,7 +43960,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ206">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR206">
         <v>1.29</v>
@@ -44079,7 +44085,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44160,7 +44166,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ207">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR207">
         <v>1.12</v>
@@ -44285,7 +44291,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44775,10 +44781,10 @@
         <v>0.9</v>
       </c>
       <c r="AP210">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ210">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR210">
         <v>1.04</v>
@@ -44903,7 +44909,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45190,7 +45196,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ212">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR212">
         <v>1.61</v>
@@ -45393,7 +45399,7 @@
         <v>1.6</v>
       </c>
       <c r="AP213">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ213">
         <v>1.6</v>
@@ -45521,7 +45527,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45727,7 +45733,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45933,7 +45939,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -46011,7 +46017,7 @@
         <v>2.56</v>
       </c>
       <c r="AP216">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ216">
         <v>2</v>
@@ -46139,7 +46145,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46345,7 +46351,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46426,7 +46432,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ218">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR218">
         <v>1.35</v>
@@ -46757,7 +46763,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46963,7 +46969,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47044,7 +47050,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ221">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR221">
         <v>1.06</v>
@@ -47250,7 +47256,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ222">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR222">
         <v>1.17</v>
@@ -47375,7 +47381,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47453,7 +47459,7 @@
         <v>1.18</v>
       </c>
       <c r="AP223">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ223">
         <v>1.19</v>
@@ -47787,7 +47793,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47993,7 +47999,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -48405,7 +48411,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48483,7 +48489,7 @@
         <v>2.36</v>
       </c>
       <c r="AP228">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ228">
         <v>1.93</v>
@@ -48611,7 +48617,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -48692,7 +48698,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ229">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR229">
         <v>1.45</v>
@@ -49023,7 +49029,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49104,7 +49110,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ231">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR231">
         <v>1.56</v>
@@ -49229,7 +49235,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49435,7 +49441,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49513,7 +49519,7 @@
         <v>1.4</v>
       </c>
       <c r="AP233">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ233">
         <v>1.33</v>
@@ -49641,7 +49647,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -49719,7 +49725,7 @@
         <v>1.27</v>
       </c>
       <c r="AP234">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ234">
         <v>1.07</v>
@@ -50259,7 +50265,7 @@
         <v>241</v>
       </c>
       <c r="P237" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q237">
         <v>1.91</v>
@@ -50543,7 +50549,7 @@
         <v>1.55</v>
       </c>
       <c r="AP238">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ238">
         <v>1.6</v>
@@ -50671,7 +50677,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -51083,7 +51089,7 @@
         <v>244</v>
       </c>
       <c r="P241" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q241">
         <v>2.5</v>
@@ -51367,10 +51373,10 @@
         <v>0.82</v>
       </c>
       <c r="AP242">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ242">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR242">
         <v>1.88</v>
@@ -51495,7 +51501,7 @@
         <v>245</v>
       </c>
       <c r="P243" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q243">
         <v>3.4</v>
@@ -51782,7 +51788,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ244">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR244">
         <v>1.7</v>
@@ -51907,7 +51913,7 @@
         <v>92</v>
       </c>
       <c r="P245" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q245">
         <v>2.6</v>
@@ -52525,7 +52531,7 @@
         <v>92</v>
       </c>
       <c r="P248" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q248">
         <v>4</v>
@@ -53018,7 +53024,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ250">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR250">
         <v>1.32</v>
@@ -53221,7 +53227,7 @@
         <v>1.08</v>
       </c>
       <c r="AP251">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ251">
         <v>1.06</v>
@@ -53636,7 +53642,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ253">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR253">
         <v>1.35</v>
@@ -53839,7 +53845,7 @@
         <v>1.55</v>
       </c>
       <c r="AP254">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ254">
         <v>1.33</v>
@@ -54173,7 +54179,7 @@
         <v>250</v>
       </c>
       <c r="P256" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q256">
         <v>4</v>
@@ -54585,7 +54591,7 @@
         <v>92</v>
       </c>
       <c r="P258" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q258">
         <v>6</v>
@@ -54663,7 +54669,7 @@
         <v>2.08</v>
       </c>
       <c r="AP258">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ258">
         <v>2.06</v>
@@ -54791,7 +54797,7 @@
         <v>92</v>
       </c>
       <c r="P259" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q259">
         <v>4.75</v>
@@ -54872,7 +54878,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ259">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR259">
         <v>1.48</v>
@@ -55075,7 +55081,7 @@
         <v>0.58</v>
       </c>
       <c r="AP260">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ260">
         <v>0.47</v>
@@ -55693,10 +55699,10 @@
         <v>0.31</v>
       </c>
       <c r="AP263">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ263">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR263">
         <v>1.84</v>
@@ -56233,7 +56239,7 @@
         <v>92</v>
       </c>
       <c r="P266" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q266">
         <v>4.75</v>
@@ -56520,7 +56526,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ267">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR267">
         <v>1.79</v>
@@ -56929,7 +56935,7 @@
         <v>0.77</v>
       </c>
       <c r="AP269">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ269">
         <v>0.8100000000000001</v>
@@ -57057,7 +57063,7 @@
         <v>146</v>
       </c>
       <c r="P270" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q270">
         <v>2.63</v>
@@ -57138,7 +57144,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ270">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR270">
         <v>1.71</v>
@@ -57344,7 +57350,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ271">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR271">
         <v>1.6</v>
@@ -57675,7 +57681,7 @@
         <v>260</v>
       </c>
       <c r="P273" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q273">
         <v>3.5</v>
@@ -57962,7 +57968,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ274">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR274">
         <v>1.53</v>
@@ -58087,7 +58093,7 @@
         <v>261</v>
       </c>
       <c r="P275" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q275">
         <v>5</v>
@@ -58165,7 +58171,7 @@
         <v>1.31</v>
       </c>
       <c r="AP275">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ275">
         <v>1.33</v>
@@ -58293,7 +58299,7 @@
         <v>262</v>
       </c>
       <c r="P276" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q276">
         <v>1.5</v>
@@ -58499,7 +58505,7 @@
         <v>103</v>
       </c>
       <c r="P277" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q277">
         <v>5.5</v>
@@ -58705,7 +58711,7 @@
         <v>263</v>
       </c>
       <c r="P278" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q278">
         <v>2.2</v>
@@ -58911,7 +58917,7 @@
         <v>92</v>
       </c>
       <c r="P279" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q279">
         <v>4</v>
@@ -58989,7 +58995,7 @@
         <v>1.15</v>
       </c>
       <c r="AP279">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ279">
         <v>1.4</v>
@@ -59117,7 +59123,7 @@
         <v>92</v>
       </c>
       <c r="P280" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q280">
         <v>3.1</v>
@@ -59529,7 +59535,7 @@
         <v>265</v>
       </c>
       <c r="P282" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q282">
         <v>2.75</v>
@@ -59735,7 +59741,7 @@
         <v>92</v>
       </c>
       <c r="P283" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q283">
         <v>2.4</v>
@@ -59816,7 +59822,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ283">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR283">
         <v>1.25</v>
@@ -59941,7 +59947,7 @@
         <v>216</v>
       </c>
       <c r="P284" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q284">
         <v>3.6</v>
@@ -60147,7 +60153,7 @@
         <v>266</v>
       </c>
       <c r="P285" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q285">
         <v>2.4</v>
@@ -60431,7 +60437,7 @@
         <v>1</v>
       </c>
       <c r="AP286">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ286">
         <v>0.9399999999999999</v>
@@ -60846,7 +60852,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ288">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR288">
         <v>1.79</v>
@@ -61049,10 +61055,10 @@
         <v>0.77</v>
       </c>
       <c r="AP289">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ289">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR289">
         <v>1.61</v>
@@ -61258,7 +61264,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ290">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR290">
         <v>1.49</v>
@@ -61383,7 +61389,7 @@
         <v>92</v>
       </c>
       <c r="P291" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q291">
         <v>3.2</v>
@@ -61461,7 +61467,7 @@
         <v>2</v>
       </c>
       <c r="AP291">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ291">
         <v>2</v>
@@ -62285,7 +62291,7 @@
         <v>1.29</v>
       </c>
       <c r="AP295">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ295">
         <v>1.4</v>
@@ -62825,7 +62831,7 @@
         <v>273</v>
       </c>
       <c r="P298" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q298">
         <v>1.95</v>
@@ -63031,7 +63037,7 @@
         <v>274</v>
       </c>
       <c r="P299" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q299">
         <v>2.6</v>
@@ -63443,7 +63449,7 @@
         <v>94</v>
       </c>
       <c r="P301" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q301">
         <v>2.4</v>
@@ -63855,7 +63861,7 @@
         <v>167</v>
       </c>
       <c r="P303" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q303">
         <v>5.5</v>
@@ -63954,16 +63960,16 @@
         <v>8</v>
       </c>
       <c r="AW303">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AX303">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AY303">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ303">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA303">
         <v>2</v>
@@ -64061,7 +64067,7 @@
         <v>275</v>
       </c>
       <c r="P304" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q304">
         <v>6</v>
@@ -64160,16 +64166,16 @@
         <v>5</v>
       </c>
       <c r="AW304">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX304">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AY304">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ304">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA304">
         <v>2</v>
@@ -64267,7 +64273,7 @@
         <v>276</v>
       </c>
       <c r="P305" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q305">
         <v>2.5</v>
@@ -64424,6 +64430,1036 @@
       </c>
       <c r="BP305">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="306" spans="1:68">
+      <c r="A306" s="1">
+        <v>305</v>
+      </c>
+      <c r="B306">
+        <v>7492452</v>
+      </c>
+      <c r="C306" t="s">
+        <v>68</v>
+      </c>
+      <c r="D306" t="s">
+        <v>69</v>
+      </c>
+      <c r="E306" s="2">
+        <v>45753.3125</v>
+      </c>
+      <c r="F306">
+        <v>31</v>
+      </c>
+      <c r="G306" t="s">
+        <v>78</v>
+      </c>
+      <c r="H306" t="s">
+        <v>87</v>
+      </c>
+      <c r="I306">
+        <v>0</v>
+      </c>
+      <c r="J306">
+        <v>0</v>
+      </c>
+      <c r="K306">
+        <v>0</v>
+      </c>
+      <c r="L306">
+        <v>1</v>
+      </c>
+      <c r="M306">
+        <v>1</v>
+      </c>
+      <c r="N306">
+        <v>2</v>
+      </c>
+      <c r="O306" t="s">
+        <v>162</v>
+      </c>
+      <c r="P306" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q306">
+        <v>3</v>
+      </c>
+      <c r="R306">
+        <v>2</v>
+      </c>
+      <c r="S306">
+        <v>4</v>
+      </c>
+      <c r="T306">
+        <v>1.5</v>
+      </c>
+      <c r="U306">
+        <v>2.5</v>
+      </c>
+      <c r="V306">
+        <v>3.4</v>
+      </c>
+      <c r="W306">
+        <v>1.3</v>
+      </c>
+      <c r="X306">
+        <v>10</v>
+      </c>
+      <c r="Y306">
+        <v>1.06</v>
+      </c>
+      <c r="Z306">
+        <v>2.3</v>
+      </c>
+      <c r="AA306">
+        <v>3.11</v>
+      </c>
+      <c r="AB306">
+        <v>3.6</v>
+      </c>
+      <c r="AC306">
+        <v>1.09</v>
+      </c>
+      <c r="AD306">
+        <v>7</v>
+      </c>
+      <c r="AE306">
+        <v>1.42</v>
+      </c>
+      <c r="AF306">
+        <v>2.8</v>
+      </c>
+      <c r="AG306">
+        <v>2.2</v>
+      </c>
+      <c r="AH306">
+        <v>1.6</v>
+      </c>
+      <c r="AI306">
+        <v>1.95</v>
+      </c>
+      <c r="AJ306">
+        <v>1.8</v>
+      </c>
+      <c r="AK306">
+        <v>1.33</v>
+      </c>
+      <c r="AL306">
+        <v>1.35</v>
+      </c>
+      <c r="AM306">
+        <v>1.6</v>
+      </c>
+      <c r="AN306">
+        <v>0.93</v>
+      </c>
+      <c r="AO306">
+        <v>0.4</v>
+      </c>
+      <c r="AP306">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AQ306">
+        <v>0.44</v>
+      </c>
+      <c r="AR306">
+        <v>1.32</v>
+      </c>
+      <c r="AS306">
+        <v>0.98</v>
+      </c>
+      <c r="AT306">
+        <v>2.3</v>
+      </c>
+      <c r="AU306">
+        <v>5</v>
+      </c>
+      <c r="AV306">
+        <v>4</v>
+      </c>
+      <c r="AW306">
+        <v>19</v>
+      </c>
+      <c r="AX306">
+        <v>10</v>
+      </c>
+      <c r="AY306">
+        <v>27</v>
+      </c>
+      <c r="AZ306">
+        <v>14</v>
+      </c>
+      <c r="BA306">
+        <v>8</v>
+      </c>
+      <c r="BB306">
+        <v>3</v>
+      </c>
+      <c r="BC306">
+        <v>11</v>
+      </c>
+      <c r="BD306">
+        <v>1.69</v>
+      </c>
+      <c r="BE306">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF306">
+        <v>2.62</v>
+      </c>
+      <c r="BG306">
+        <v>1.24</v>
+      </c>
+      <c r="BH306">
+        <v>3.34</v>
+      </c>
+      <c r="BI306">
+        <v>1.48</v>
+      </c>
+      <c r="BJ306">
+        <v>2.4</v>
+      </c>
+      <c r="BK306">
+        <v>1.85</v>
+      </c>
+      <c r="BL306">
+        <v>1.85</v>
+      </c>
+      <c r="BM306">
+        <v>2.38</v>
+      </c>
+      <c r="BN306">
+        <v>1.49</v>
+      </c>
+      <c r="BO306">
+        <v>3.14</v>
+      </c>
+      <c r="BP306">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="307" spans="1:68">
+      <c r="A307" s="1">
+        <v>306</v>
+      </c>
+      <c r="B307">
+        <v>7492457</v>
+      </c>
+      <c r="C307" t="s">
+        <v>68</v>
+      </c>
+      <c r="D307" t="s">
+        <v>69</v>
+      </c>
+      <c r="E307" s="2">
+        <v>45753.41666666666</v>
+      </c>
+      <c r="F307">
+        <v>31</v>
+      </c>
+      <c r="G307" t="s">
+        <v>84</v>
+      </c>
+      <c r="H307" t="s">
+        <v>75</v>
+      </c>
+      <c r="I307">
+        <v>0</v>
+      </c>
+      <c r="J307">
+        <v>0</v>
+      </c>
+      <c r="K307">
+        <v>0</v>
+      </c>
+      <c r="L307">
+        <v>1</v>
+      </c>
+      <c r="M307">
+        <v>1</v>
+      </c>
+      <c r="N307">
+        <v>2</v>
+      </c>
+      <c r="O307" t="s">
+        <v>277</v>
+      </c>
+      <c r="P307" t="s">
+        <v>407</v>
+      </c>
+      <c r="Q307">
+        <v>2.5</v>
+      </c>
+      <c r="R307">
+        <v>2</v>
+      </c>
+      <c r="S307">
+        <v>5.5</v>
+      </c>
+      <c r="T307">
+        <v>1.5</v>
+      </c>
+      <c r="U307">
+        <v>2.5</v>
+      </c>
+      <c r="V307">
+        <v>3.5</v>
+      </c>
+      <c r="W307">
+        <v>1.29</v>
+      </c>
+      <c r="X307">
+        <v>11</v>
+      </c>
+      <c r="Y307">
+        <v>1.05</v>
+      </c>
+      <c r="Z307">
+        <v>1.85</v>
+      </c>
+      <c r="AA307">
+        <v>3.45</v>
+      </c>
+      <c r="AB307">
+        <v>4.9</v>
+      </c>
+      <c r="AC307">
+        <v>1.08</v>
+      </c>
+      <c r="AD307">
+        <v>7.5</v>
+      </c>
+      <c r="AE307">
+        <v>1.42</v>
+      </c>
+      <c r="AF307">
+        <v>2.8</v>
+      </c>
+      <c r="AG307">
+        <v>2.15</v>
+      </c>
+      <c r="AH307">
+        <v>1.65</v>
+      </c>
+      <c r="AI307">
+        <v>2.1</v>
+      </c>
+      <c r="AJ307">
+        <v>1.67</v>
+      </c>
+      <c r="AK307">
+        <v>1.19</v>
+      </c>
+      <c r="AL307">
+        <v>1.3</v>
+      </c>
+      <c r="AM307">
+        <v>1.95</v>
+      </c>
+      <c r="AN307">
+        <v>1.43</v>
+      </c>
+      <c r="AO307">
+        <v>1.07</v>
+      </c>
+      <c r="AP307">
+        <v>1.4</v>
+      </c>
+      <c r="AQ307">
+        <v>1.06</v>
+      </c>
+      <c r="AR307">
+        <v>1.17</v>
+      </c>
+      <c r="AS307">
+        <v>1.06</v>
+      </c>
+      <c r="AT307">
+        <v>2.23</v>
+      </c>
+      <c r="AU307">
+        <v>4</v>
+      </c>
+      <c r="AV307">
+        <v>2</v>
+      </c>
+      <c r="AW307">
+        <v>4</v>
+      </c>
+      <c r="AX307">
+        <v>12</v>
+      </c>
+      <c r="AY307">
+        <v>9</v>
+      </c>
+      <c r="AZ307">
+        <v>18</v>
+      </c>
+      <c r="BA307">
+        <v>1</v>
+      </c>
+      <c r="BB307">
+        <v>6</v>
+      </c>
+      <c r="BC307">
+        <v>7</v>
+      </c>
+      <c r="BD307">
+        <v>1.54</v>
+      </c>
+      <c r="BE307">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF307">
+        <v>3.08</v>
+      </c>
+      <c r="BG307">
+        <v>1.3</v>
+      </c>
+      <c r="BH307">
+        <v>2.97</v>
+      </c>
+      <c r="BI307">
+        <v>1.57</v>
+      </c>
+      <c r="BJ307">
+        <v>2.19</v>
+      </c>
+      <c r="BK307">
+        <v>1.99</v>
+      </c>
+      <c r="BL307">
+        <v>1.73</v>
+      </c>
+      <c r="BM307">
+        <v>2.6</v>
+      </c>
+      <c r="BN307">
+        <v>1.41</v>
+      </c>
+      <c r="BO307">
+        <v>3.5</v>
+      </c>
+      <c r="BP307">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="308" spans="1:68">
+      <c r="A308" s="1">
+        <v>307</v>
+      </c>
+      <c r="B308">
+        <v>7492450</v>
+      </c>
+      <c r="C308" t="s">
+        <v>68</v>
+      </c>
+      <c r="D308" t="s">
+        <v>69</v>
+      </c>
+      <c r="E308" s="2">
+        <v>45753.41666666666</v>
+      </c>
+      <c r="F308">
+        <v>31</v>
+      </c>
+      <c r="G308" t="s">
+        <v>72</v>
+      </c>
+      <c r="H308" t="s">
+        <v>76</v>
+      </c>
+      <c r="I308">
+        <v>0</v>
+      </c>
+      <c r="J308">
+        <v>0</v>
+      </c>
+      <c r="K308">
+        <v>0</v>
+      </c>
+      <c r="L308">
+        <v>0</v>
+      </c>
+      <c r="M308">
+        <v>0</v>
+      </c>
+      <c r="N308">
+        <v>0</v>
+      </c>
+      <c r="O308" t="s">
+        <v>92</v>
+      </c>
+      <c r="P308" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q308">
+        <v>3.25</v>
+      </c>
+      <c r="R308">
+        <v>2.05</v>
+      </c>
+      <c r="S308">
+        <v>3.6</v>
+      </c>
+      <c r="T308">
+        <v>1.44</v>
+      </c>
+      <c r="U308">
+        <v>2.63</v>
+      </c>
+      <c r="V308">
+        <v>3.25</v>
+      </c>
+      <c r="W308">
+        <v>1.33</v>
+      </c>
+      <c r="X308">
+        <v>10</v>
+      </c>
+      <c r="Y308">
+        <v>1.06</v>
+      </c>
+      <c r="Z308">
+        <v>2.64</v>
+      </c>
+      <c r="AA308">
+        <v>3.08</v>
+      </c>
+      <c r="AB308">
+        <v>3.02</v>
+      </c>
+      <c r="AC308">
+        <v>1.08</v>
+      </c>
+      <c r="AD308">
+        <v>7.5</v>
+      </c>
+      <c r="AE308">
+        <v>1.38</v>
+      </c>
+      <c r="AF308">
+        <v>2.95</v>
+      </c>
+      <c r="AG308">
+        <v>2.05</v>
+      </c>
+      <c r="AH308">
+        <v>1.7</v>
+      </c>
+      <c r="AI308">
+        <v>1.8</v>
+      </c>
+      <c r="AJ308">
+        <v>1.95</v>
+      </c>
+      <c r="AK308">
+        <v>1.42</v>
+      </c>
+      <c r="AL308">
+        <v>1.35</v>
+      </c>
+      <c r="AM308">
+        <v>1.47</v>
+      </c>
+      <c r="AN308">
+        <v>0.57</v>
+      </c>
+      <c r="AO308">
+        <v>0.71</v>
+      </c>
+      <c r="AP308">
+        <v>0.6</v>
+      </c>
+      <c r="AQ308">
+        <v>0.73</v>
+      </c>
+      <c r="AR308">
+        <v>0.96</v>
+      </c>
+      <c r="AS308">
+        <v>1</v>
+      </c>
+      <c r="AT308">
+        <v>1.96</v>
+      </c>
+      <c r="AU308">
+        <v>2</v>
+      </c>
+      <c r="AV308">
+        <v>2</v>
+      </c>
+      <c r="AW308">
+        <v>4</v>
+      </c>
+      <c r="AX308">
+        <v>6</v>
+      </c>
+      <c r="AY308">
+        <v>7</v>
+      </c>
+      <c r="AZ308">
+        <v>10</v>
+      </c>
+      <c r="BA308">
+        <v>2</v>
+      </c>
+      <c r="BB308">
+        <v>3</v>
+      </c>
+      <c r="BC308">
+        <v>5</v>
+      </c>
+      <c r="BD308">
+        <v>1.88</v>
+      </c>
+      <c r="BE308">
+        <v>8.4</v>
+      </c>
+      <c r="BF308">
+        <v>2.29</v>
+      </c>
+      <c r="BG308">
+        <v>1.23</v>
+      </c>
+      <c r="BH308">
+        <v>3.42</v>
+      </c>
+      <c r="BI308">
+        <v>1.46</v>
+      </c>
+      <c r="BJ308">
+        <v>2.45</v>
+      </c>
+      <c r="BK308">
+        <v>1.82</v>
+      </c>
+      <c r="BL308">
+        <v>1.88</v>
+      </c>
+      <c r="BM308">
+        <v>2.32</v>
+      </c>
+      <c r="BN308">
+        <v>1.51</v>
+      </c>
+      <c r="BO308">
+        <v>3.08</v>
+      </c>
+      <c r="BP308">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="309" spans="1:68">
+      <c r="A309" s="1">
+        <v>308</v>
+      </c>
+      <c r="B309">
+        <v>7492448</v>
+      </c>
+      <c r="C309" t="s">
+        <v>68</v>
+      </c>
+      <c r="D309" t="s">
+        <v>69</v>
+      </c>
+      <c r="E309" s="2">
+        <v>45753.54166666666</v>
+      </c>
+      <c r="F309">
+        <v>31</v>
+      </c>
+      <c r="G309" t="s">
+        <v>89</v>
+      </c>
+      <c r="H309" t="s">
+        <v>77</v>
+      </c>
+      <c r="I309">
+        <v>0</v>
+      </c>
+      <c r="J309">
+        <v>0</v>
+      </c>
+      <c r="K309">
+        <v>0</v>
+      </c>
+      <c r="L309">
+        <v>0</v>
+      </c>
+      <c r="M309">
+        <v>1</v>
+      </c>
+      <c r="N309">
+        <v>1</v>
+      </c>
+      <c r="O309" t="s">
+        <v>92</v>
+      </c>
+      <c r="P309" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q309">
+        <v>2.3</v>
+      </c>
+      <c r="R309">
+        <v>2.3</v>
+      </c>
+      <c r="S309">
+        <v>5</v>
+      </c>
+      <c r="T309">
+        <v>1.36</v>
+      </c>
+      <c r="U309">
+        <v>3</v>
+      </c>
+      <c r="V309">
+        <v>2.63</v>
+      </c>
+      <c r="W309">
+        <v>1.44</v>
+      </c>
+      <c r="X309">
+        <v>7</v>
+      </c>
+      <c r="Y309">
+        <v>1.1</v>
+      </c>
+      <c r="Z309">
+        <v>1.76</v>
+      </c>
+      <c r="AA309">
+        <v>4</v>
+      </c>
+      <c r="AB309">
+        <v>4.6</v>
+      </c>
+      <c r="AC309">
+        <v>1.04</v>
+      </c>
+      <c r="AD309">
+        <v>10</v>
+      </c>
+      <c r="AE309">
+        <v>1.25</v>
+      </c>
+      <c r="AF309">
+        <v>3.85</v>
+      </c>
+      <c r="AG309">
+        <v>1.82</v>
+      </c>
+      <c r="AH309">
+        <v>2</v>
+      </c>
+      <c r="AI309">
+        <v>1.75</v>
+      </c>
+      <c r="AJ309">
+        <v>2</v>
+      </c>
+      <c r="AK309">
+        <v>1.19</v>
+      </c>
+      <c r="AL309">
+        <v>1.25</v>
+      </c>
+      <c r="AM309">
+        <v>2.1</v>
+      </c>
+      <c r="AN309">
+        <v>1.79</v>
+      </c>
+      <c r="AO309">
+        <v>1.67</v>
+      </c>
+      <c r="AP309">
+        <v>1.67</v>
+      </c>
+      <c r="AQ309">
+        <v>1.75</v>
+      </c>
+      <c r="AR309">
+        <v>1.84</v>
+      </c>
+      <c r="AS309">
+        <v>1.55</v>
+      </c>
+      <c r="AT309">
+        <v>3.39</v>
+      </c>
+      <c r="AU309">
+        <v>3</v>
+      </c>
+      <c r="AV309">
+        <v>4</v>
+      </c>
+      <c r="AW309">
+        <v>8</v>
+      </c>
+      <c r="AX309">
+        <v>5</v>
+      </c>
+      <c r="AY309">
+        <v>15</v>
+      </c>
+      <c r="AZ309">
+        <v>11</v>
+      </c>
+      <c r="BA309">
+        <v>11</v>
+      </c>
+      <c r="BB309">
+        <v>4</v>
+      </c>
+      <c r="BC309">
+        <v>15</v>
+      </c>
+      <c r="BD309">
+        <v>1.51</v>
+      </c>
+      <c r="BE309">
+        <v>8.9</v>
+      </c>
+      <c r="BF309">
+        <v>3.2</v>
+      </c>
+      <c r="BG309">
+        <v>1.29</v>
+      </c>
+      <c r="BH309">
+        <v>3.04</v>
+      </c>
+      <c r="BI309">
+        <v>1.56</v>
+      </c>
+      <c r="BJ309">
+        <v>2.21</v>
+      </c>
+      <c r="BK309">
+        <v>1.98</v>
+      </c>
+      <c r="BL309">
+        <v>1.74</v>
+      </c>
+      <c r="BM309">
+        <v>2.57</v>
+      </c>
+      <c r="BN309">
+        <v>1.42</v>
+      </c>
+      <c r="BO309">
+        <v>3.5</v>
+      </c>
+      <c r="BP309">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="310" spans="1:68">
+      <c r="A310" s="1">
+        <v>309</v>
+      </c>
+      <c r="B310">
+        <v>7492456</v>
+      </c>
+      <c r="C310" t="s">
+        <v>68</v>
+      </c>
+      <c r="D310" t="s">
+        <v>69</v>
+      </c>
+      <c r="E310" s="2">
+        <v>45753.65625</v>
+      </c>
+      <c r="F310">
+        <v>31</v>
+      </c>
+      <c r="G310" t="s">
+        <v>86</v>
+      </c>
+      <c r="H310" t="s">
+        <v>79</v>
+      </c>
+      <c r="I310">
+        <v>0</v>
+      </c>
+      <c r="J310">
+        <v>1</v>
+      </c>
+      <c r="K310">
+        <v>1</v>
+      </c>
+      <c r="L310">
+        <v>1</v>
+      </c>
+      <c r="M310">
+        <v>1</v>
+      </c>
+      <c r="N310">
+        <v>2</v>
+      </c>
+      <c r="O310" t="s">
+        <v>173</v>
+      </c>
+      <c r="P310" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q310">
+        <v>3.2</v>
+      </c>
+      <c r="R310">
+        <v>2.05</v>
+      </c>
+      <c r="S310">
+        <v>3.6</v>
+      </c>
+      <c r="T310">
+        <v>1.5</v>
+      </c>
+      <c r="U310">
+        <v>2.5</v>
+      </c>
+      <c r="V310">
+        <v>3.4</v>
+      </c>
+      <c r="W310">
+        <v>1.3</v>
+      </c>
+      <c r="X310">
+        <v>10</v>
+      </c>
+      <c r="Y310">
+        <v>1.06</v>
+      </c>
+      <c r="Z310">
+        <v>2.37</v>
+      </c>
+      <c r="AA310">
+        <v>3.23</v>
+      </c>
+      <c r="AB310">
+        <v>3.29</v>
+      </c>
+      <c r="AC310">
+        <v>1.04</v>
+      </c>
+      <c r="AD310">
+        <v>7.1</v>
+      </c>
+      <c r="AE310">
+        <v>1.36</v>
+      </c>
+      <c r="AF310">
+        <v>2.83</v>
+      </c>
+      <c r="AG310">
+        <v>2.1</v>
+      </c>
+      <c r="AH310">
+        <v>1.67</v>
+      </c>
+      <c r="AI310">
+        <v>1.91</v>
+      </c>
+      <c r="AJ310">
+        <v>1.91</v>
+      </c>
+      <c r="AK310">
+        <v>1.35</v>
+      </c>
+      <c r="AL310">
+        <v>1.34</v>
+      </c>
+      <c r="AM310">
+        <v>1.57</v>
+      </c>
+      <c r="AN310">
+        <v>2.07</v>
+      </c>
+      <c r="AO310">
+        <v>1.71</v>
+      </c>
+      <c r="AP310">
+        <v>2</v>
+      </c>
+      <c r="AQ310">
+        <v>1.67</v>
+      </c>
+      <c r="AR310">
+        <v>1.59</v>
+      </c>
+      <c r="AS310">
+        <v>1.34</v>
+      </c>
+      <c r="AT310">
+        <v>2.93</v>
+      </c>
+      <c r="AU310">
+        <v>5</v>
+      </c>
+      <c r="AV310">
+        <v>7</v>
+      </c>
+      <c r="AW310">
+        <v>7</v>
+      </c>
+      <c r="AX310">
+        <v>4</v>
+      </c>
+      <c r="AY310">
+        <v>16</v>
+      </c>
+      <c r="AZ310">
+        <v>14</v>
+      </c>
+      <c r="BA310">
+        <v>4</v>
+      </c>
+      <c r="BB310">
+        <v>4</v>
+      </c>
+      <c r="BC310">
+        <v>8</v>
+      </c>
+      <c r="BD310">
+        <v>1.76</v>
+      </c>
+      <c r="BE310">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF310">
+        <v>2.51</v>
+      </c>
+      <c r="BG310">
+        <v>1.38</v>
+      </c>
+      <c r="BH310">
+        <v>2.71</v>
+      </c>
+      <c r="BI310">
+        <v>1.71</v>
+      </c>
+      <c r="BJ310">
+        <v>2.02</v>
+      </c>
+      <c r="BK310">
+        <v>2.17</v>
+      </c>
+      <c r="BL310">
+        <v>1.58</v>
+      </c>
+      <c r="BM310">
+        <v>2.88</v>
+      </c>
+      <c r="BN310">
+        <v>1.32</v>
+      </c>
+      <c r="BO310">
+        <v>4.1</v>
+      </c>
+      <c r="BP310">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1922" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1928" uniqueCount="408">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -850,6 +850,9 @@
     <t>['67']</t>
   </si>
   <si>
+    <t>['64']</t>
+  </si>
+  <si>
     <t>['30', '82']</t>
   </si>
   <si>
@@ -1236,9 +1239,6 @@
   <si>
     <t>['7', '10']</t>
   </si>
-  <si>
-    <t>['64']</t>
-  </si>
 </sst>
 </file>
 
@@ -1599,7 +1599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP310"/>
+  <dimension ref="A1:BP311"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1855,7 +1855,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -2473,7 +2473,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -2679,7 +2679,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2757,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AQ6">
         <v>1.06</v>
@@ -2966,7 +2966,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ7">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3297,7 +3297,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3503,7 +3503,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q10">
         <v>4.5</v>
@@ -4121,7 +4121,7 @@
         <v>99</v>
       </c>
       <c r="P13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q13">
         <v>4.75</v>
@@ -4327,7 +4327,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -5357,7 +5357,7 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q19">
         <v>2.05</v>
@@ -5769,7 +5769,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q21">
         <v>5.5</v>
@@ -5975,7 +5975,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -6387,7 +6387,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q24">
         <v>2.25</v>
@@ -6465,7 +6465,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AQ24">
         <v>0.9399999999999999</v>
@@ -6799,7 +6799,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q26">
         <v>3.4</v>
@@ -7005,7 +7005,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q27">
         <v>2</v>
@@ -7211,7 +7211,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7417,7 +7417,7 @@
         <v>92</v>
       </c>
       <c r="P29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q29">
         <v>2.75</v>
@@ -8035,7 +8035,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q32">
         <v>3.5</v>
@@ -8859,7 +8859,7 @@
         <v>115</v>
       </c>
       <c r="P36" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q36">
         <v>2.38</v>
@@ -9271,7 +9271,7 @@
         <v>92</v>
       </c>
       <c r="P38" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -9352,7 +9352,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ38">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AR38">
         <v>1.24</v>
@@ -9477,7 +9477,7 @@
         <v>116</v>
       </c>
       <c r="P39" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q39">
         <v>6.5</v>
@@ -9683,7 +9683,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9889,7 +9889,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q41">
         <v>2.2</v>
@@ -10095,7 +10095,7 @@
         <v>92</v>
       </c>
       <c r="P42" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -10301,7 +10301,7 @@
         <v>119</v>
       </c>
       <c r="P43" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10794,7 +10794,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ45">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AR45">
         <v>1.23</v>
@@ -10919,7 +10919,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q46">
         <v>2.88</v>
@@ -11125,7 +11125,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11331,7 +11331,7 @@
         <v>111</v>
       </c>
       <c r="P48" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q48">
         <v>3.75</v>
@@ -11743,7 +11743,7 @@
         <v>124</v>
       </c>
       <c r="P50" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
@@ -11949,7 +11949,7 @@
         <v>125</v>
       </c>
       <c r="P51" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
@@ -12361,7 +12361,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q53">
         <v>6</v>
@@ -12567,7 +12567,7 @@
         <v>92</v>
       </c>
       <c r="P54" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q54">
         <v>5.5</v>
@@ -12773,7 +12773,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q55">
         <v>3.4</v>
@@ -12851,7 +12851,7 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AQ55">
         <v>2.06</v>
@@ -12979,7 +12979,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q56">
         <v>3.4</v>
@@ -13185,7 +13185,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -14009,7 +14009,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14833,7 +14833,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q65">
         <v>2.05</v>
@@ -15039,7 +15039,7 @@
         <v>138</v>
       </c>
       <c r="P66" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q66">
         <v>1.8</v>
@@ -15245,7 +15245,7 @@
         <v>139</v>
       </c>
       <c r="P67" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q67">
         <v>1.91</v>
@@ -15735,7 +15735,7 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AQ69">
         <v>0.67</v>
@@ -16481,7 +16481,7 @@
         <v>144</v>
       </c>
       <c r="P73" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -17099,7 +17099,7 @@
         <v>92</v>
       </c>
       <c r="P76" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q76">
         <v>5.5</v>
@@ -17180,7 +17180,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ76">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AR76">
         <v>0.85</v>
@@ -17305,7 +17305,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -17511,7 +17511,7 @@
         <v>92</v>
       </c>
       <c r="P78" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q78">
         <v>5</v>
@@ -17717,7 +17717,7 @@
         <v>147</v>
       </c>
       <c r="P79" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q79">
         <v>3.4</v>
@@ -18129,7 +18129,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -18953,7 +18953,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q85">
         <v>1.83</v>
@@ -19571,7 +19571,7 @@
         <v>152</v>
       </c>
       <c r="P88" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19777,7 +19777,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q89">
         <v>2.4</v>
@@ -19983,7 +19983,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20189,7 +20189,7 @@
         <v>92</v>
       </c>
       <c r="P91" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q91">
         <v>3.5</v>
@@ -20601,7 +20601,7 @@
         <v>92</v>
       </c>
       <c r="P93" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
@@ -20682,7 +20682,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ93">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AR93">
         <v>1.71</v>
@@ -20807,7 +20807,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -21013,7 +21013,7 @@
         <v>92</v>
       </c>
       <c r="P95" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
@@ -21425,7 +21425,7 @@
         <v>158</v>
       </c>
       <c r="P97" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q97">
         <v>1.95</v>
@@ -21631,7 +21631,7 @@
         <v>92</v>
       </c>
       <c r="P98" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21837,7 +21837,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -22327,7 +22327,7 @@
         <v>0.2</v>
       </c>
       <c r="AP101">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AQ101">
         <v>0.73</v>
@@ -22455,7 +22455,7 @@
         <v>92</v>
       </c>
       <c r="P102" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22867,7 +22867,7 @@
         <v>92</v>
       </c>
       <c r="P104" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q104">
         <v>2.6</v>
@@ -23073,7 +23073,7 @@
         <v>92</v>
       </c>
       <c r="P105" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q105">
         <v>3.75</v>
@@ -23279,7 +23279,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q106">
         <v>4.75</v>
@@ -24103,7 +24103,7 @@
         <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q110">
         <v>2.1</v>
@@ -24309,7 +24309,7 @@
         <v>165</v>
       </c>
       <c r="P111" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q111">
         <v>3.75</v>
@@ -24515,7 +24515,7 @@
         <v>166</v>
       </c>
       <c r="P112" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24721,7 +24721,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q113">
         <v>3.1</v>
@@ -24927,7 +24927,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q114">
         <v>4.75</v>
@@ -25339,7 +25339,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q116">
         <v>1.83</v>
@@ -25545,7 +25545,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -26244,7 +26244,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ120">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AR120">
         <v>1.62</v>
@@ -26369,7 +26369,7 @@
         <v>92</v>
       </c>
       <c r="P121" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q121">
         <v>7</v>
@@ -26781,7 +26781,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26987,7 +26987,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27193,7 +27193,7 @@
         <v>92</v>
       </c>
       <c r="P125" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -27399,7 +27399,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q126">
         <v>2.88</v>
@@ -28017,7 +28017,7 @@
         <v>178</v>
       </c>
       <c r="P129" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q129">
         <v>3.6</v>
@@ -29125,7 +29125,7 @@
         <v>0.29</v>
       </c>
       <c r="AP134">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AQ134">
         <v>0.44</v>
@@ -29253,7 +29253,7 @@
         <v>92</v>
       </c>
       <c r="P135" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q135">
         <v>2.75</v>
@@ -29459,7 +29459,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q136">
         <v>5</v>
@@ -29540,7 +29540,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ136">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AR136">
         <v>1.14</v>
@@ -29871,7 +29871,7 @@
         <v>183</v>
       </c>
       <c r="P138" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q138">
         <v>6</v>
@@ -30077,7 +30077,7 @@
         <v>92</v>
       </c>
       <c r="P139" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q139">
         <v>3.6</v>
@@ -30901,7 +30901,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -31107,7 +31107,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q144">
         <v>2.1</v>
@@ -31519,7 +31519,7 @@
         <v>189</v>
       </c>
       <c r="P146" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31725,7 +31725,7 @@
         <v>190</v>
       </c>
       <c r="P147" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -32137,7 +32137,7 @@
         <v>163</v>
       </c>
       <c r="P149" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q149">
         <v>3.4</v>
@@ -32549,7 +32549,7 @@
         <v>92</v>
       </c>
       <c r="P151" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q151">
         <v>5</v>
@@ -32755,7 +32755,7 @@
         <v>91</v>
       </c>
       <c r="P152" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q152">
         <v>5.5</v>
@@ -32836,7 +32836,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ152">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AR152">
         <v>1.05</v>
@@ -32961,7 +32961,7 @@
         <v>191</v>
       </c>
       <c r="P153" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q153">
         <v>1.91</v>
@@ -33373,7 +33373,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q155">
         <v>2.4</v>
@@ -33657,7 +33657,7 @@
         <v>2</v>
       </c>
       <c r="AP156">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AQ156">
         <v>1.27</v>
@@ -34197,7 +34197,7 @@
         <v>92</v>
       </c>
       <c r="P159" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q159">
         <v>3.75</v>
@@ -34609,7 +34609,7 @@
         <v>92</v>
       </c>
       <c r="P161" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34815,7 +34815,7 @@
         <v>155</v>
       </c>
       <c r="P162" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q162">
         <v>5.5</v>
@@ -34896,7 +34896,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ162">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AR162">
         <v>1.24</v>
@@ -35021,7 +35021,7 @@
         <v>195</v>
       </c>
       <c r="P163" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q163">
         <v>5.5</v>
@@ -35433,7 +35433,7 @@
         <v>197</v>
       </c>
       <c r="P165" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35639,7 +35639,7 @@
         <v>198</v>
       </c>
       <c r="P166" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q166">
         <v>1.73</v>
@@ -35845,7 +35845,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -36051,7 +36051,7 @@
         <v>199</v>
       </c>
       <c r="P168" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q168">
         <v>2.2</v>
@@ -36669,7 +36669,7 @@
         <v>202</v>
       </c>
       <c r="P171" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q171">
         <v>3.25</v>
@@ -36875,7 +36875,7 @@
         <v>92</v>
       </c>
       <c r="P172" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q172">
         <v>6</v>
@@ -37081,7 +37081,7 @@
         <v>124</v>
       </c>
       <c r="P173" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q173">
         <v>3.5</v>
@@ -37287,7 +37287,7 @@
         <v>203</v>
       </c>
       <c r="P174" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q174">
         <v>3.1</v>
@@ -37699,7 +37699,7 @@
         <v>205</v>
       </c>
       <c r="P176" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q176">
         <v>2.6</v>
@@ -38317,7 +38317,7 @@
         <v>208</v>
       </c>
       <c r="P179" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q179">
         <v>2.05</v>
@@ -38395,7 +38395,7 @@
         <v>0.75</v>
       </c>
       <c r="AP179">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AQ179">
         <v>1.06</v>
@@ -38729,7 +38729,7 @@
         <v>92</v>
       </c>
       <c r="P181" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38810,7 +38810,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ181">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AR181">
         <v>1.57</v>
@@ -39141,7 +39141,7 @@
         <v>209</v>
       </c>
       <c r="P183" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q183">
         <v>3.1</v>
@@ -39965,7 +39965,7 @@
         <v>211</v>
       </c>
       <c r="P187" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40377,7 +40377,7 @@
         <v>163</v>
       </c>
       <c r="P189" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q189">
         <v>2.75</v>
@@ -40789,7 +40789,7 @@
         <v>155</v>
       </c>
       <c r="P191" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q191">
         <v>1.83</v>
@@ -41407,7 +41407,7 @@
         <v>213</v>
       </c>
       <c r="P194" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q194">
         <v>3.6</v>
@@ -41485,7 +41485,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP194">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AQ194">
         <v>1.4</v>
@@ -42025,7 +42025,7 @@
         <v>216</v>
       </c>
       <c r="P197" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q197">
         <v>4.33</v>
@@ -42437,7 +42437,7 @@
         <v>218</v>
       </c>
       <c r="P199" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q199">
         <v>1.95</v>
@@ -42643,7 +42643,7 @@
         <v>219</v>
       </c>
       <c r="P200" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q200">
         <v>2.2</v>
@@ -42849,7 +42849,7 @@
         <v>220</v>
       </c>
       <c r="P201" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -42927,7 +42927,7 @@
         <v>0.78</v>
       </c>
       <c r="AP201">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AQ201">
         <v>0.47</v>
@@ -43261,7 +43261,7 @@
         <v>222</v>
       </c>
       <c r="P203" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q203">
         <v>3</v>
@@ -43342,7 +43342,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ203">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AR203">
         <v>1.78</v>
@@ -43673,7 +43673,7 @@
         <v>224</v>
       </c>
       <c r="P205" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q205">
         <v>2.6</v>
@@ -44085,7 +44085,7 @@
         <v>92</v>
       </c>
       <c r="P207" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q207">
         <v>5</v>
@@ -44291,7 +44291,7 @@
         <v>226</v>
       </c>
       <c r="P208" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q208">
         <v>1.62</v>
@@ -44909,7 +44909,7 @@
         <v>229</v>
       </c>
       <c r="P211" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45527,7 +45527,7 @@
         <v>231</v>
       </c>
       <c r="P214" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q214">
         <v>1.73</v>
@@ -45733,7 +45733,7 @@
         <v>223</v>
       </c>
       <c r="P215" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q215">
         <v>4</v>
@@ -45939,7 +45939,7 @@
         <v>92</v>
       </c>
       <c r="P216" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q216">
         <v>8</v>
@@ -46145,7 +46145,7 @@
         <v>165</v>
       </c>
       <c r="P217" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q217">
         <v>2.63</v>
@@ -46351,7 +46351,7 @@
         <v>232</v>
       </c>
       <c r="P218" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q218">
         <v>2.88</v>
@@ -46763,7 +46763,7 @@
         <v>211</v>
       </c>
       <c r="P220" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q220">
         <v>2.75</v>
@@ -46969,7 +46969,7 @@
         <v>234</v>
       </c>
       <c r="P221" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q221">
         <v>2.5</v>
@@ -47381,7 +47381,7 @@
         <v>189</v>
       </c>
       <c r="P223" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q223">
         <v>1.95</v>
@@ -47665,7 +47665,7 @@
         <v>0.64</v>
       </c>
       <c r="AP224">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AQ224">
         <v>0.8100000000000001</v>
@@ -47793,7 +47793,7 @@
         <v>236</v>
       </c>
       <c r="P225" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q225">
         <v>1.91</v>
@@ -47999,7 +47999,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q226">
         <v>2.25</v>
@@ -48411,7 +48411,7 @@
         <v>165</v>
       </c>
       <c r="P228" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q228">
         <v>3.6</v>
@@ -48492,7 +48492,7 @@
         <v>2</v>
       </c>
       <c r="AQ228">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AR228">
         <v>1.58</v>
@@ -48617,7 +48617,7 @@
         <v>225</v>
       </c>
       <c r="P229" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -49029,7 +49029,7 @@
         <v>212</v>
       </c>
       <c r="P231" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q231">
         <v>4.33</v>
@@ -49235,7 +49235,7 @@
         <v>92</v>
       </c>
       <c r="P232" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q232">
         <v>6</v>
@@ -49441,7 +49441,7 @@
         <v>92</v>
       </c>
       <c r="P233" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q233">
         <v>5.5</v>
@@ -49647,7 +49647,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q234">
         <v>3</v>
@@ -50265,7 +50265,7 @@
         <v>241</v>
       </c>
       <c r="P237" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q237">
         <v>1.91</v>
@@ -50677,7 +50677,7 @@
         <v>242</v>
       </c>
       <c r="P239" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q239">
         <v>1.95</v>
@@ -51089,7 +51089,7 @@
         <v>244</v>
       </c>
       <c r="P241" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q241">
         <v>2.5</v>
@@ -51167,7 +51167,7 @@
         <v>1.17</v>
       </c>
       <c r="AP241">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AQ241">
         <v>1.19</v>
@@ -51501,7 +51501,7 @@
         <v>245</v>
       </c>
       <c r="P243" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q243">
         <v>3.4</v>
@@ -51582,7 +51582,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ243">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AR243">
         <v>1.63</v>
@@ -51913,7 +51913,7 @@
         <v>92</v>
       </c>
       <c r="P245" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q245">
         <v>2.6</v>
@@ -52531,7 +52531,7 @@
         <v>92</v>
       </c>
       <c r="P248" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q248">
         <v>4</v>
@@ -54179,7 +54179,7 @@
         <v>250</v>
       </c>
       <c r="P256" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q256">
         <v>4</v>
@@ -54260,7 +54260,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ256">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AR256">
         <v>1.57</v>
@@ -54591,7 +54591,7 @@
         <v>92</v>
       </c>
       <c r="P258" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q258">
         <v>6</v>
@@ -54797,7 +54797,7 @@
         <v>92</v>
       </c>
       <c r="P259" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q259">
         <v>4.75</v>
@@ -55287,7 +55287,7 @@
         <v>1.42</v>
       </c>
       <c r="AP261">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AQ261">
         <v>1.33</v>
@@ -56239,7 +56239,7 @@
         <v>92</v>
       </c>
       <c r="P266" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q266">
         <v>4.75</v>
@@ -56523,7 +56523,7 @@
         <v>0.83</v>
       </c>
       <c r="AP267">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AQ267">
         <v>0.73</v>
@@ -57063,7 +57063,7 @@
         <v>146</v>
       </c>
       <c r="P270" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q270">
         <v>2.63</v>
@@ -57681,7 +57681,7 @@
         <v>260</v>
       </c>
       <c r="P273" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q273">
         <v>3.5</v>
@@ -58093,7 +58093,7 @@
         <v>261</v>
       </c>
       <c r="P275" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q275">
         <v>5</v>
@@ -58299,7 +58299,7 @@
         <v>262</v>
       </c>
       <c r="P276" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q276">
         <v>1.5</v>
@@ -58505,7 +58505,7 @@
         <v>103</v>
       </c>
       <c r="P277" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q277">
         <v>5.5</v>
@@ -58711,7 +58711,7 @@
         <v>263</v>
       </c>
       <c r="P278" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q278">
         <v>2.2</v>
@@ -58917,7 +58917,7 @@
         <v>92</v>
       </c>
       <c r="P279" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q279">
         <v>4</v>
@@ -59123,7 +59123,7 @@
         <v>92</v>
       </c>
       <c r="P280" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q280">
         <v>3.1</v>
@@ -59535,7 +59535,7 @@
         <v>265</v>
       </c>
       <c r="P282" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q282">
         <v>2.75</v>
@@ -59741,7 +59741,7 @@
         <v>92</v>
       </c>
       <c r="P283" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q283">
         <v>2.4</v>
@@ -59947,7 +59947,7 @@
         <v>216</v>
       </c>
       <c r="P284" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q284">
         <v>3.6</v>
@@ -60153,7 +60153,7 @@
         <v>266</v>
       </c>
       <c r="P285" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q285">
         <v>2.4</v>
@@ -60646,7 +60646,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ287">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AR287">
         <v>1.33</v>
@@ -60849,7 +60849,7 @@
         <v>1.79</v>
       </c>
       <c r="AP288">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AQ288">
         <v>1.75</v>
@@ -61389,7 +61389,7 @@
         <v>92</v>
       </c>
       <c r="P291" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q291">
         <v>3.2</v>
@@ -62831,7 +62831,7 @@
         <v>273</v>
       </c>
       <c r="P298" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q298">
         <v>1.95</v>
@@ -63037,7 +63037,7 @@
         <v>274</v>
       </c>
       <c r="P299" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q299">
         <v>2.6</v>
@@ -63449,7 +63449,7 @@
         <v>94</v>
       </c>
       <c r="P301" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q301">
         <v>2.4</v>
@@ -63861,7 +63861,7 @@
         <v>167</v>
       </c>
       <c r="P303" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q303">
         <v>5.5</v>
@@ -64067,7 +64067,7 @@
         <v>275</v>
       </c>
       <c r="P304" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q304">
         <v>6</v>
@@ -64273,7 +64273,7 @@
         <v>276</v>
       </c>
       <c r="P305" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q305">
         <v>2.5</v>
@@ -64685,7 +64685,7 @@
         <v>277</v>
       </c>
       <c r="P307" t="s">
-        <v>407</v>
+        <v>278</v>
       </c>
       <c r="Q307">
         <v>2.5</v>
@@ -65303,7 +65303,7 @@
         <v>173</v>
       </c>
       <c r="P310" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q310">
         <v>3.2</v>
@@ -65460,6 +65460,212 @@
       </c>
       <c r="BP310">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="311" spans="1:68">
+      <c r="A311" s="1">
+        <v>310</v>
+      </c>
+      <c r="B311">
+        <v>7492449</v>
+      </c>
+      <c r="C311" t="s">
+        <v>68</v>
+      </c>
+      <c r="D311" t="s">
+        <v>69</v>
+      </c>
+      <c r="E311" s="2">
+        <v>45754.65625</v>
+      </c>
+      <c r="F311">
+        <v>31</v>
+      </c>
+      <c r="G311" t="s">
+        <v>74</v>
+      </c>
+      <c r="H311" t="s">
+        <v>85</v>
+      </c>
+      <c r="I311">
+        <v>0</v>
+      </c>
+      <c r="J311">
+        <v>1</v>
+      </c>
+      <c r="K311">
+        <v>1</v>
+      </c>
+      <c r="L311">
+        <v>1</v>
+      </c>
+      <c r="M311">
+        <v>1</v>
+      </c>
+      <c r="N311">
+        <v>2</v>
+      </c>
+      <c r="O311" t="s">
+        <v>278</v>
+      </c>
+      <c r="P311" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q311">
+        <v>3.6</v>
+      </c>
+      <c r="R311">
+        <v>1.95</v>
+      </c>
+      <c r="S311">
+        <v>3.4</v>
+      </c>
+      <c r="T311">
+        <v>1.53</v>
+      </c>
+      <c r="U311">
+        <v>2.38</v>
+      </c>
+      <c r="V311">
+        <v>3.75</v>
+      </c>
+      <c r="W311">
+        <v>1.25</v>
+      </c>
+      <c r="X311">
+        <v>11</v>
+      </c>
+      <c r="Y311">
+        <v>1.05</v>
+      </c>
+      <c r="Z311">
+        <v>2.96</v>
+      </c>
+      <c r="AA311">
+        <v>3.08</v>
+      </c>
+      <c r="AB311">
+        <v>2.69</v>
+      </c>
+      <c r="AC311">
+        <v>1.1</v>
+      </c>
+      <c r="AD311">
+        <v>6.5</v>
+      </c>
+      <c r="AE311">
+        <v>1.48</v>
+      </c>
+      <c r="AF311">
+        <v>2.6</v>
+      </c>
+      <c r="AG311">
+        <v>2.3</v>
+      </c>
+      <c r="AH311">
+        <v>1.57</v>
+      </c>
+      <c r="AI311">
+        <v>2</v>
+      </c>
+      <c r="AJ311">
+        <v>1.75</v>
+      </c>
+      <c r="AK311">
+        <v>1.47</v>
+      </c>
+      <c r="AL311">
+        <v>1.36</v>
+      </c>
+      <c r="AM311">
+        <v>1.41</v>
+      </c>
+      <c r="AN311">
+        <v>2.13</v>
+      </c>
+      <c r="AO311">
+        <v>1.93</v>
+      </c>
+      <c r="AP311">
+        <v>2.06</v>
+      </c>
+      <c r="AQ311">
+        <v>1.88</v>
+      </c>
+      <c r="AR311">
+        <v>1.79</v>
+      </c>
+      <c r="AS311">
+        <v>1.24</v>
+      </c>
+      <c r="AT311">
+        <v>3.03</v>
+      </c>
+      <c r="AU311">
+        <v>5</v>
+      </c>
+      <c r="AV311">
+        <v>3</v>
+      </c>
+      <c r="AW311">
+        <v>8</v>
+      </c>
+      <c r="AX311">
+        <v>4</v>
+      </c>
+      <c r="AY311">
+        <v>13</v>
+      </c>
+      <c r="AZ311">
+        <v>8</v>
+      </c>
+      <c r="BA311">
+        <v>8</v>
+      </c>
+      <c r="BB311">
+        <v>3</v>
+      </c>
+      <c r="BC311">
+        <v>11</v>
+      </c>
+      <c r="BD311">
+        <v>1.86</v>
+      </c>
+      <c r="BE311">
+        <v>8.1</v>
+      </c>
+      <c r="BF311">
+        <v>2.35</v>
+      </c>
+      <c r="BG311">
+        <v>1.42</v>
+      </c>
+      <c r="BH311">
+        <v>2.57</v>
+      </c>
+      <c r="BI311">
+        <v>1.78</v>
+      </c>
+      <c r="BJ311">
+        <v>1.93</v>
+      </c>
+      <c r="BK311">
+        <v>2.3</v>
+      </c>
+      <c r="BL311">
+        <v>1.52</v>
+      </c>
+      <c r="BM311">
+        <v>3.08</v>
+      </c>
+      <c r="BN311">
+        <v>1.28</v>
+      </c>
+      <c r="BO311">
+        <v>4.45</v>
+      </c>
+      <c r="BP311">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie A_20242025.xlsx
@@ -64799,10 +64799,10 @@
         <v>1</v>
       </c>
       <c r="BB307">
+        <v>5</v>
+      </c>
+      <c r="BC307">
         <v>6</v>
-      </c>
-      <c r="BC307">
-        <v>7</v>
       </c>
       <c r="BD307">
         <v>1.54</v>
